--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B2" t="n">
-        <v>746.2840072815898</v>
+        <v>754.9954213012545</v>
       </c>
       <c r="C2" t="n">
-        <v>755.095155276553</v>
+        <v>771.5412279036273</v>
       </c>
       <c r="D2" t="n">
-        <v>741.330272625368</v>
+        <v>749.5333431691193</v>
       </c>
       <c r="E2" t="n">
-        <v>753.1216430664062</v>
+        <v>762.2018432617188</v>
       </c>
       <c r="F2" t="n">
-        <v>8248600</v>
+        <v>10533800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B3" t="n">
-        <v>754.9954213012545</v>
+        <v>764.494341124313</v>
       </c>
       <c r="C3" t="n">
-        <v>771.5412279036273</v>
+        <v>778.8074148399552</v>
       </c>
       <c r="D3" t="n">
-        <v>749.5333431691193</v>
+        <v>762.6005237676653</v>
       </c>
       <c r="E3" t="n">
-        <v>762.2018432617188</v>
+        <v>776.4551391601562</v>
       </c>
       <c r="F3" t="n">
-        <v>10533800</v>
+        <v>11782500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B4" t="n">
-        <v>764.494341124313</v>
+        <v>777.4419223006557</v>
       </c>
       <c r="C4" t="n">
-        <v>778.8074148399552</v>
+        <v>780.7311297077449</v>
       </c>
       <c r="D4" t="n">
-        <v>762.6005237676653</v>
+        <v>763.8066193659058</v>
       </c>
       <c r="E4" t="n">
-        <v>776.4551391601562</v>
+        <v>773.1858520507812</v>
       </c>
       <c r="F4" t="n">
-        <v>11782500</v>
+        <v>9400900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B5" t="n">
-        <v>777.4419223006557</v>
+        <v>778.1994774600552</v>
       </c>
       <c r="C5" t="n">
-        <v>780.7311297077449</v>
+        <v>786.203274581819</v>
       </c>
       <c r="D5" t="n">
-        <v>763.8066193659058</v>
+        <v>770.8336042127465</v>
       </c>
       <c r="E5" t="n">
-        <v>773.1858520507812</v>
+        <v>777.7011108398438</v>
       </c>
       <c r="F5" t="n">
-        <v>9400900</v>
+        <v>10955000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B6" t="n">
-        <v>778.1994774600552</v>
+        <v>783.8508708699721</v>
       </c>
       <c r="C6" t="n">
-        <v>786.203274581819</v>
+        <v>788.2165669565625</v>
       </c>
       <c r="D6" t="n">
-        <v>770.8336042127465</v>
+        <v>766.6771780735046</v>
       </c>
       <c r="E6" t="n">
-        <v>777.7011108398438</v>
+        <v>775.837158203125</v>
       </c>
       <c r="F6" t="n">
-        <v>10955000</v>
+        <v>23696800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,25 +599,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B7" t="n">
-        <v>783.8508708699721</v>
+        <v>779.8218176027002</v>
       </c>
       <c r="C7" t="n">
-        <v>788.2165669565625</v>
+        <v>783.6917575585782</v>
       </c>
       <c r="D7" t="n">
-        <v>766.6771780735046</v>
+        <v>762.4868973227559</v>
       </c>
       <c r="E7" t="n">
-        <v>775.837158203125</v>
+        <v>763.1751098632812</v>
       </c>
       <c r="F7" t="n">
-        <v>23696800</v>
+        <v>11706900</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -625,25 +625,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B8" t="n">
-        <v>779.8218176027002</v>
+        <v>767.254476840496</v>
       </c>
       <c r="C8" t="n">
-        <v>783.6917575585782</v>
+        <v>768.6009504341728</v>
       </c>
       <c r="D8" t="n">
-        <v>762.4868973227559</v>
+        <v>749.1216451610411</v>
       </c>
       <c r="E8" t="n">
-        <v>763.1751098632812</v>
+        <v>753.4404296875</v>
       </c>
       <c r="F8" t="n">
-        <v>11706900</v>
+        <v>10872600</v>
       </c>
       <c r="G8" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B9" t="n">
-        <v>767.2545389947088</v>
+        <v>755.5349916265823</v>
       </c>
       <c r="C9" t="n">
-        <v>768.6010126974617</v>
+        <v>759.1356124217834</v>
       </c>
       <c r="D9" t="n">
-        <v>749.1217058463387</v>
+        <v>750.5779133776451</v>
       </c>
       <c r="E9" t="n">
-        <v>753.4404907226562</v>
+        <v>758.686767578125</v>
       </c>
       <c r="F9" t="n">
-        <v>10872600</v>
+        <v>8828200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B10" t="n">
-        <v>755.5349916265823</v>
+        <v>751.4954858581857</v>
       </c>
       <c r="C10" t="n">
-        <v>759.1356124217834</v>
+        <v>754.8068807440363</v>
       </c>
       <c r="D10" t="n">
-        <v>750.5779133776451</v>
+        <v>742.6185490172081</v>
       </c>
       <c r="E10" t="n">
-        <v>758.686767578125</v>
+        <v>746.9672241210938</v>
       </c>
       <c r="F10" t="n">
-        <v>8828200</v>
+        <v>10591100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B11" t="n">
-        <v>751.4954858581857</v>
+        <v>748.0544043789391</v>
       </c>
       <c r="C11" t="n">
-        <v>754.8068807440363</v>
+        <v>749.9793904076555</v>
       </c>
       <c r="D11" t="n">
-        <v>742.6185490172081</v>
+        <v>735.4371957410184</v>
       </c>
       <c r="E11" t="n">
-        <v>746.9672241210938</v>
+        <v>741.8206176757812</v>
       </c>
       <c r="F11" t="n">
-        <v>10591100</v>
+        <v>9696300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B12" t="n">
-        <v>748.0544043789391</v>
+        <v>746.777703342028</v>
       </c>
       <c r="C12" t="n">
-        <v>749.9793904076555</v>
+        <v>748.8324179023273</v>
       </c>
       <c r="D12" t="n">
-        <v>735.4371957410184</v>
+        <v>737.2325826153279</v>
       </c>
       <c r="E12" t="n">
-        <v>741.8206176757812</v>
+        <v>741.4715576171875</v>
       </c>
       <c r="F12" t="n">
-        <v>9696300</v>
+        <v>9246800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B13" t="n">
-        <v>746.7777648139662</v>
+        <v>740.3245554260684</v>
       </c>
       <c r="C13" t="n">
-        <v>748.832479543402</v>
+        <v>741.0426584785586</v>
       </c>
       <c r="D13" t="n">
-        <v>737.2326433015477</v>
+        <v>724.4159185837501</v>
       </c>
       <c r="E13" t="n">
-        <v>741.4716186523438</v>
+        <v>732.4749755859375</v>
       </c>
       <c r="F13" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B14" t="n">
-        <v>740.3244937368279</v>
+        <v>719.6183236513255</v>
       </c>
       <c r="C14" t="n">
-        <v>741.0425967294805</v>
+        <v>719.9773751402398</v>
       </c>
       <c r="D14" t="n">
-        <v>724.4158582201331</v>
+        <v>708.357633728991</v>
       </c>
       <c r="E14" t="n">
-        <v>732.4749145507812</v>
+        <v>715.4791259765625</v>
       </c>
       <c r="F14" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B15" t="n">
-        <v>719.618385039583</v>
+        <v>720.7055653205383</v>
       </c>
       <c r="C15" t="n">
-        <v>719.9774365591268</v>
+        <v>725.8821043267139</v>
       </c>
       <c r="D15" t="n">
-        <v>708.3576941566364</v>
+        <v>716.2770807321521</v>
       </c>
       <c r="E15" t="n">
-        <v>715.4791870117188</v>
+        <v>725.1639404296875</v>
       </c>
       <c r="F15" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B16" t="n">
-        <v>720.7055653205383</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C16" t="n">
-        <v>725.8821043267139</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D16" t="n">
-        <v>716.2770807321521</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E16" t="n">
-        <v>725.1639404296875</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F16" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B17" t="n">
-        <v>727.7372737109582</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C17" t="n">
-        <v>729.1037149276121</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D17" t="n">
-        <v>708.3377167266436</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E17" t="n">
-        <v>708.7167358398438</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F17" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B18" t="n">
-        <v>703.3607165744016</v>
+        <v>715.8581417735932</v>
       </c>
       <c r="C18" t="n">
-        <v>715.0203947681905</v>
+        <v>716.6361476056489</v>
       </c>
       <c r="D18" t="n">
-        <v>688.718804278428</v>
+        <v>703.9192222306009</v>
       </c>
       <c r="E18" t="n">
-        <v>713.8035278320312</v>
+        <v>711.230224609375</v>
       </c>
       <c r="F18" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B19" t="n">
-        <v>715.8581417735932</v>
+        <v>711.599278595462</v>
       </c>
       <c r="C19" t="n">
-        <v>716.6361476056489</v>
+        <v>717.7832075860277</v>
       </c>
       <c r="D19" t="n">
-        <v>703.9192222306009</v>
+        <v>705.9738944950672</v>
       </c>
       <c r="E19" t="n">
-        <v>711.230224609375</v>
+        <v>715.9779052734375</v>
       </c>
       <c r="F19" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B20" t="n">
-        <v>711.599278595462</v>
+        <v>716.4167658258609</v>
       </c>
       <c r="C20" t="n">
-        <v>717.7832075860277</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="D20" t="n">
-        <v>705.9738944950672</v>
+        <v>710.5918883665408</v>
       </c>
       <c r="E20" t="n">
-        <v>715.9779052734375</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="F20" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B21" t="n">
-        <v>716.4167658258609</v>
+        <v>729.0239332852144</v>
       </c>
       <c r="C21" t="n">
-        <v>731.6072387695312</v>
+        <v>733.3626856542741</v>
       </c>
       <c r="D21" t="n">
-        <v>710.5918883665408</v>
+        <v>702.6824691715568</v>
       </c>
       <c r="E21" t="n">
-        <v>731.6072387695312</v>
+        <v>703.4703979492188</v>
       </c>
       <c r="F21" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B22" t="n">
-        <v>729.0239332852144</v>
+        <v>711.1603595995662</v>
       </c>
       <c r="C22" t="n">
-        <v>733.3626856542741</v>
+        <v>718.072374881022</v>
       </c>
       <c r="D22" t="n">
-        <v>702.6824691715568</v>
+        <v>705.8042950194317</v>
       </c>
       <c r="E22" t="n">
-        <v>703.4703979492188</v>
+        <v>713.8433837890625</v>
       </c>
       <c r="F22" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B23" t="n">
-        <v>711.1603595995662</v>
+        <v>705.9439682909708</v>
       </c>
       <c r="C23" t="n">
-        <v>718.072374881022</v>
+        <v>713.6937706407739</v>
       </c>
       <c r="D23" t="n">
-        <v>705.8042950194317</v>
+        <v>697.5158763660478</v>
       </c>
       <c r="E23" t="n">
-        <v>713.8433837890625</v>
+        <v>706.8117065429688</v>
       </c>
       <c r="F23" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B24" t="n">
-        <v>705.9440292511955</v>
+        <v>715.1998794771447</v>
       </c>
       <c r="C24" t="n">
-        <v>713.6938322702155</v>
+        <v>722.0221626881838</v>
       </c>
       <c r="D24" t="n">
-        <v>697.5159365984832</v>
+        <v>707.6694770310874</v>
       </c>
       <c r="E24" t="n">
-        <v>706.811767578125</v>
+        <v>715.6885986328125</v>
       </c>
       <c r="F24" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B25" t="n">
-        <v>715.1998794771447</v>
+        <v>715.6886043056783</v>
       </c>
       <c r="C25" t="n">
-        <v>722.0221626881838</v>
+        <v>723.6080097298942</v>
       </c>
       <c r="D25" t="n">
-        <v>707.6694770310874</v>
+        <v>702.0540824517458</v>
       </c>
       <c r="E25" t="n">
-        <v>715.6885986328125</v>
+        <v>710.2228393554688</v>
       </c>
       <c r="F25" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B26" t="n">
-        <v>715.6886043056783</v>
+        <v>705.2458014471516</v>
       </c>
       <c r="C26" t="n">
-        <v>723.6080097298942</v>
+        <v>716.6760344343375</v>
       </c>
       <c r="D26" t="n">
-        <v>702.0540824517458</v>
+        <v>704.2882698394852</v>
       </c>
       <c r="E26" t="n">
-        <v>710.2228393554688</v>
+        <v>715.0602416992188</v>
       </c>
       <c r="F26" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B27" t="n">
-        <v>705.2458014471516</v>
+        <v>719.3191931642514</v>
       </c>
       <c r="C27" t="n">
-        <v>716.6760344343375</v>
+        <v>731.8665769499745</v>
       </c>
       <c r="D27" t="n">
-        <v>704.2882698394852</v>
+        <v>718.3118034233538</v>
       </c>
       <c r="E27" t="n">
-        <v>715.0602416992188</v>
+        <v>730.2706909179688</v>
       </c>
       <c r="F27" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B28" t="n">
-        <v>719.3191931642514</v>
+        <v>734.1107251683979</v>
       </c>
       <c r="C28" t="n">
-        <v>731.8665769499745</v>
+        <v>736.5842723709278</v>
       </c>
       <c r="D28" t="n">
-        <v>718.3118034233538</v>
+        <v>726.8595646449745</v>
       </c>
       <c r="E28" t="n">
-        <v>730.2706909179688</v>
+        <v>731.3678588867188</v>
       </c>
       <c r="F28" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>734.1107251683979</v>
+        <v>731.9264006052239</v>
       </c>
       <c r="C29" t="n">
-        <v>736.5842723709278</v>
+        <v>738.6787972623451</v>
       </c>
       <c r="D29" t="n">
-        <v>726.8595646449745</v>
+        <v>722.1518348008319</v>
       </c>
       <c r="E29" t="n">
-        <v>731.3678588867188</v>
+        <v>731.5074462890625</v>
       </c>
       <c r="F29" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B30" t="n">
-        <v>731.9264006052239</v>
+        <v>732.7941435868839</v>
       </c>
       <c r="C30" t="n">
-        <v>738.6787972623451</v>
+        <v>740.4841042897723</v>
       </c>
       <c r="D30" t="n">
-        <v>722.1518348008319</v>
+        <v>731.1982575844598</v>
       </c>
       <c r="E30" t="n">
-        <v>731.5074462890625</v>
+        <v>732.095947265625</v>
       </c>
       <c r="F30" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B31" t="n">
-        <v>732.7941435868839</v>
+        <v>734.8787064697904</v>
       </c>
       <c r="C31" t="n">
-        <v>740.4841042897723</v>
+        <v>739.2872845910176</v>
       </c>
       <c r="D31" t="n">
-        <v>731.1982575844598</v>
+        <v>729.253383189777</v>
       </c>
       <c r="E31" t="n">
-        <v>732.095947265625</v>
+        <v>736.4446411132812</v>
       </c>
       <c r="F31" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B32" t="n">
-        <v>734.8786455644157</v>
+        <v>747.7850542762595</v>
       </c>
       <c r="C32" t="n">
-        <v>739.2872233202683</v>
+        <v>753.7894568601143</v>
       </c>
       <c r="D32" t="n">
-        <v>729.2533227506186</v>
+        <v>746.0695454676272</v>
       </c>
       <c r="E32" t="n">
-        <v>736.444580078125</v>
+        <v>748.8722534179688</v>
       </c>
       <c r="F32" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B33" t="n">
-        <v>747.7851152228061</v>
+        <v>750.6776381609803</v>
       </c>
       <c r="C33" t="n">
-        <v>753.7895182960361</v>
+        <v>756.4326899204912</v>
       </c>
       <c r="D33" t="n">
-        <v>746.069606274355</v>
+        <v>743.5860965317024</v>
       </c>
       <c r="E33" t="n">
-        <v>748.872314453125</v>
+        <v>749.49072265625</v>
       </c>
       <c r="F33" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B34" t="n">
-        <v>750.6776381609803</v>
+        <v>752.7921200604676</v>
       </c>
       <c r="C34" t="n">
-        <v>756.4326899204912</v>
+        <v>757.1906533932021</v>
       </c>
       <c r="D34" t="n">
-        <v>743.5860965317024</v>
+        <v>740.5838813084906</v>
       </c>
       <c r="E34" t="n">
-        <v>749.49072265625</v>
+        <v>749.7200927734375</v>
       </c>
       <c r="F34" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B35" t="n">
-        <v>752.7921813457194</v>
+        <v>667.4142515632169</v>
       </c>
       <c r="C35" t="n">
-        <v>757.1907150365412</v>
+        <v>679.1936140289573</v>
       </c>
       <c r="D35" t="n">
-        <v>740.5839415998626</v>
+        <v>648.4834442213796</v>
       </c>
       <c r="E35" t="n">
-        <v>749.7201538085938</v>
+        <v>664.7411499023438</v>
       </c>
       <c r="F35" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B36" t="n">
-        <v>667.414190282622</v>
+        <v>672.7602632515434</v>
       </c>
       <c r="C36" t="n">
-        <v>679.1935516668058</v>
+        <v>673.1392823636344</v>
       </c>
       <c r="D36" t="n">
-        <v>648.4833846789722</v>
+        <v>643.8953340746643</v>
       </c>
       <c r="E36" t="n">
-        <v>664.7410888671875</v>
+        <v>646.6680908203125</v>
       </c>
       <c r="F36" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B37" t="n">
-        <v>672.7602632515434</v>
+        <v>654.298319497033</v>
       </c>
       <c r="C37" t="n">
-        <v>673.1392823636344</v>
+        <v>657.6196984387726</v>
       </c>
       <c r="D37" t="n">
-        <v>643.8953340746643</v>
+        <v>634.5297257704245</v>
       </c>
       <c r="E37" t="n">
-        <v>646.6680908203125</v>
+        <v>636.0557861328125</v>
       </c>
       <c r="F37" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B38" t="n">
-        <v>654.298319497033</v>
+        <v>626.4107910285981</v>
       </c>
       <c r="C38" t="n">
-        <v>657.6196984387726</v>
+        <v>640.0752642850032</v>
       </c>
       <c r="D38" t="n">
-        <v>634.5297257704245</v>
+        <v>624.3860886703497</v>
       </c>
       <c r="E38" t="n">
-        <v>636.0557861328125</v>
+        <v>625.6926879882812</v>
       </c>
       <c r="F38" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B39" t="n">
-        <v>626.4107910285981</v>
+        <v>630.6697208898194</v>
       </c>
       <c r="C39" t="n">
-        <v>640.0752642850032</v>
+        <v>640.5639703518489</v>
       </c>
       <c r="D39" t="n">
-        <v>624.3860886703497</v>
+        <v>624.9146693781357</v>
       </c>
       <c r="E39" t="n">
-        <v>625.6926879882812</v>
+        <v>634.30029296875</v>
       </c>
       <c r="F39" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B40" t="n">
-        <v>630.6697208898194</v>
+        <v>634.2005186436334</v>
       </c>
       <c r="C40" t="n">
-        <v>640.5639703518489</v>
+        <v>634.3501538797125</v>
       </c>
       <c r="D40" t="n">
-        <v>624.9146693781357</v>
+        <v>616.3968476378337</v>
       </c>
       <c r="E40" t="n">
-        <v>634.30029296875</v>
+        <v>617.3344116210938</v>
       </c>
       <c r="F40" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B41" t="n">
-        <v>634.2005186436334</v>
+        <v>614.8907386759073</v>
       </c>
       <c r="C41" t="n">
-        <v>634.3501538797125</v>
+        <v>620.5161224262619</v>
       </c>
       <c r="D41" t="n">
-        <v>616.3968476378337</v>
+        <v>599.6404247494841</v>
       </c>
       <c r="E41" t="n">
-        <v>617.3344116210938</v>
+        <v>620.0972290039062</v>
       </c>
       <c r="F41" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B42" t="n">
-        <v>614.8907386759073</v>
+        <v>629.4529708548182</v>
       </c>
       <c r="C42" t="n">
-        <v>620.5161224262619</v>
+        <v>633.3528014765299</v>
       </c>
       <c r="D42" t="n">
-        <v>599.6404247494841</v>
+        <v>616.5065997528014</v>
       </c>
       <c r="E42" t="n">
-        <v>620.0972290039062</v>
+        <v>630.1212158203125</v>
       </c>
       <c r="F42" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B43" t="n">
-        <v>629.4529098843899</v>
+        <v>626.3709656116134</v>
       </c>
       <c r="C43" t="n">
-        <v>633.3527401283538</v>
+        <v>627.9269165306073</v>
       </c>
       <c r="D43" t="n">
-        <v>616.5065400363918</v>
+        <v>617.7833145947981</v>
       </c>
       <c r="E43" t="n">
-        <v>630.1211547851562</v>
+        <v>625.453369140625</v>
       </c>
       <c r="F43" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B44" t="n">
-        <v>626.3709656116134</v>
+        <v>626.5005716840028</v>
       </c>
       <c r="C44" t="n">
-        <v>627.9269165306073</v>
+        <v>627.3583261459861</v>
       </c>
       <c r="D44" t="n">
-        <v>617.7833145947981</v>
+        <v>606.1934022078184</v>
       </c>
       <c r="E44" t="n">
-        <v>625.453369140625</v>
+        <v>607.43017578125</v>
       </c>
       <c r="F44" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B45" t="n">
-        <v>626.5005716840028</v>
+        <v>611.4796659420805</v>
       </c>
       <c r="C45" t="n">
-        <v>627.3583261459861</v>
+        <v>616.0478021853295</v>
       </c>
       <c r="D45" t="n">
-        <v>606.1934022078184</v>
+        <v>601.4357808374693</v>
       </c>
       <c r="E45" t="n">
-        <v>607.43017578125</v>
+        <v>608.3079223632812</v>
       </c>
       <c r="F45" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B46" t="n">
-        <v>611.4796659420805</v>
+        <v>600.2288811530552</v>
       </c>
       <c r="C46" t="n">
-        <v>616.0478021853295</v>
+        <v>612.088052043071</v>
       </c>
       <c r="D46" t="n">
-        <v>601.4357808374693</v>
+        <v>593.6560102918138</v>
       </c>
       <c r="E46" t="n">
-        <v>608.3079223632812</v>
+        <v>607.8790283203125</v>
       </c>
       <c r="F46" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B47" t="n">
-        <v>600.2288811530552</v>
+        <v>607.4600346656293</v>
       </c>
       <c r="C47" t="n">
-        <v>612.088052043071</v>
+        <v>610.1031845088386</v>
       </c>
       <c r="D47" t="n">
-        <v>593.6560102918138</v>
+        <v>593.8554651895852</v>
       </c>
       <c r="E47" t="n">
-        <v>607.8790283203125</v>
+        <v>600.4483032226562</v>
       </c>
       <c r="F47" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B48" t="n">
-        <v>607.4600346656293</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C48" t="n">
-        <v>610.1031845088386</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D48" t="n">
-        <v>593.8554651895852</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E48" t="n">
-        <v>600.4483032226562</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F48" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B49" t="n">
-        <v>590.065358149623</v>
+        <v>592.1797786556917</v>
       </c>
       <c r="C49" t="n">
-        <v>602.0940719298206</v>
+        <v>593.7856483585136</v>
       </c>
       <c r="D49" t="n">
-        <v>582.2656968950795</v>
+        <v>579.7421567881397</v>
       </c>
       <c r="E49" t="n">
-        <v>596.1395874023438</v>
+        <v>588.7886352539062</v>
       </c>
       <c r="F49" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B50" t="n">
-        <v>592.1797786556917</v>
+        <v>601.9344542639864</v>
       </c>
       <c r="C50" t="n">
-        <v>593.7856483585136</v>
+        <v>605.1460720070379</v>
       </c>
       <c r="D50" t="n">
-        <v>579.7421567881397</v>
+        <v>581.8367012414765</v>
       </c>
       <c r="E50" t="n">
-        <v>588.7886352539062</v>
+        <v>587.6217041015625</v>
       </c>
       <c r="F50" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B51" t="n">
-        <v>601.9345167857809</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C51" t="n">
-        <v>605.1461348624172</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D51" t="n">
-        <v>581.8367616757555</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E51" t="n">
-        <v>587.6217651367188</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F51" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B52" t="n">
-        <v>586.9734117815261</v>
+        <v>597.1668722231478</v>
       </c>
       <c r="C52" t="n">
-        <v>596.5684523172222</v>
+        <v>615.1002729325323</v>
       </c>
       <c r="D52" t="n">
-        <v>580.3506215479276</v>
+        <v>596.0797338085368</v>
       </c>
       <c r="E52" t="n">
-        <v>592.70849609375</v>
+        <v>611.459716796875</v>
       </c>
       <c r="F52" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B53" t="n">
-        <v>597.1668722231478</v>
+        <v>622.3812488080194</v>
       </c>
       <c r="C53" t="n">
-        <v>615.1002729325323</v>
+        <v>635.3973829418613</v>
       </c>
       <c r="D53" t="n">
-        <v>596.0797338085368</v>
+        <v>616.6960233021972</v>
       </c>
       <c r="E53" t="n">
-        <v>611.459716796875</v>
+        <v>634.5695190429688</v>
       </c>
       <c r="F53" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B54" t="n">
-        <v>622.3813086708644</v>
+        <v>636.0358029520913</v>
       </c>
       <c r="C54" t="n">
-        <v>635.3974440566444</v>
+        <v>636.7040478933542</v>
       </c>
       <c r="D54" t="n">
-        <v>616.696082618217</v>
+        <v>629.9915253276793</v>
       </c>
       <c r="E54" t="n">
-        <v>634.569580078125</v>
+        <v>631.9663696289062</v>
       </c>
       <c r="F54" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B55" t="n">
-        <v>636.0358643802724</v>
+        <v>634.4299618769652</v>
       </c>
       <c r="C55" t="n">
-        <v>636.7041093860743</v>
+        <v>646.3688812783262</v>
       </c>
       <c r="D55" t="n">
-        <v>629.9915861721055</v>
+        <v>633.8514494094911</v>
       </c>
       <c r="E55" t="n">
-        <v>631.9664306640625</v>
+        <v>646.2691650390625</v>
       </c>
       <c r="F55" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B56" t="n">
-        <v>634.4299618769652</v>
+        <v>637.8909364271796</v>
       </c>
       <c r="C56" t="n">
-        <v>646.3688812783262</v>
+        <v>643.6459879981971</v>
       </c>
       <c r="D56" t="n">
-        <v>633.8514494094911</v>
+        <v>636.1056017671217</v>
       </c>
       <c r="E56" t="n">
-        <v>646.2691650390625</v>
+        <v>639.20751953125</v>
       </c>
       <c r="F56" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B57" t="n">
-        <v>637.890997336621</v>
+        <v>640.6737247939117</v>
       </c>
       <c r="C57" t="n">
-        <v>643.6460494571635</v>
+        <v>646.1893476978298</v>
       </c>
       <c r="D57" t="n">
-        <v>636.1056625060893</v>
+        <v>636.4147821721649</v>
       </c>
       <c r="E57" t="n">
-        <v>639.2075805664062</v>
+        <v>645.4213256835938</v>
       </c>
       <c r="F57" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B58" t="n">
-        <v>640.6737247939117</v>
+        <v>642.7383158920676</v>
       </c>
       <c r="C58" t="n">
-        <v>646.1893476978298</v>
+        <v>647.1668005690203</v>
       </c>
       <c r="D58" t="n">
-        <v>636.4147821721649</v>
+        <v>635.8961259576193</v>
       </c>
       <c r="E58" t="n">
-        <v>645.4213256835938</v>
+        <v>637.9407958984375</v>
       </c>
       <c r="F58" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B59" t="n">
-        <v>642.7383773862279</v>
+        <v>674.246461597851</v>
       </c>
       <c r="C59" t="n">
-        <v>647.1668624868771</v>
+        <v>674.3461778479464</v>
       </c>
       <c r="D59" t="n">
-        <v>635.8961867971512</v>
+        <v>658.3378235904052</v>
       </c>
       <c r="E59" t="n">
-        <v>637.9408569335938</v>
+        <v>659.8140258789062</v>
       </c>
       <c r="F59" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B60" t="n">
-        <v>674.2463992276428</v>
+        <v>662.2775487290173</v>
       </c>
       <c r="C60" t="n">
-        <v>674.3461154685141</v>
+        <v>672.9398207362489</v>
       </c>
       <c r="D60" t="n">
-        <v>658.3377626918029</v>
+        <v>660.6717397649775</v>
       </c>
       <c r="E60" t="n">
-        <v>659.81396484375</v>
+        <v>671.673095703125</v>
       </c>
       <c r="F60" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B61" t="n">
-        <v>662.2775487290173</v>
+        <v>667.603701448277</v>
       </c>
       <c r="C61" t="n">
-        <v>672.9398207362489</v>
+        <v>674.9545781663558</v>
       </c>
       <c r="D61" t="n">
-        <v>660.6717397649775</v>
+        <v>663.344758713728</v>
       </c>
       <c r="E61" t="n">
-        <v>671.673095703125</v>
+        <v>665.0702514648438</v>
       </c>
       <c r="F61" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B62" t="n">
-        <v>667.603701448277</v>
+        <v>662.0481917138827</v>
       </c>
       <c r="C62" t="n">
-        <v>674.9545781663558</v>
+        <v>662.7563110037405</v>
       </c>
       <c r="D62" t="n">
-        <v>663.344758713728</v>
+        <v>651.645254570885</v>
       </c>
       <c r="E62" t="n">
-        <v>665.0702514648438</v>
+        <v>655.255859375</v>
       </c>
       <c r="F62" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B63" t="n">
-        <v>662.0481300460407</v>
+        <v>648.2639556943986</v>
       </c>
       <c r="C63" t="n">
-        <v>662.7562492699393</v>
+        <v>652.8121240146866</v>
       </c>
       <c r="D63" t="n">
-        <v>651.6451938720459</v>
+        <v>641.730959438269</v>
       </c>
       <c r="E63" t="n">
-        <v>655.2557983398438</v>
+        <v>648.4434814453125</v>
       </c>
       <c r="F63" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B64" t="n">
-        <v>648.2639556943986</v>
+        <v>641.6211778682233</v>
       </c>
       <c r="C64" t="n">
-        <v>652.8121240146866</v>
+        <v>653.5801249698833</v>
       </c>
       <c r="D64" t="n">
-        <v>641.730959438269</v>
+        <v>639.1376470786419</v>
       </c>
       <c r="E64" t="n">
-        <v>648.4434814453125</v>
+        <v>651.0167846679688</v>
       </c>
       <c r="F64" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B65" t="n">
-        <v>641.6212380225077</v>
+        <v>648.1143965293088</v>
       </c>
       <c r="C65" t="n">
-        <v>653.5801862453618</v>
+        <v>709.1556549538686</v>
       </c>
       <c r="D65" t="n">
-        <v>639.1377070000864</v>
+        <v>636.9534211280841</v>
       </c>
       <c r="E65" t="n">
-        <v>651.016845703125</v>
+        <v>642.558837890625</v>
       </c>
       <c r="F65" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,25 +2133,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B66" t="n">
-        <v>648.1143965293088</v>
+        <v>644.5502809809109</v>
       </c>
       <c r="C66" t="n">
-        <v>709.1556549538686</v>
+        <v>651.8372704406642</v>
       </c>
       <c r="D66" t="n">
-        <v>636.9534211280841</v>
+        <v>637.5627451568915</v>
       </c>
       <c r="E66" t="n">
-        <v>642.558837890625</v>
+        <v>646.3570556640625</v>
       </c>
       <c r="F66" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B67" t="n">
-        <v>644.5502809809109</v>
+        <v>642.3541999133257</v>
       </c>
       <c r="C67" t="n">
-        <v>651.8372704406642</v>
+        <v>661.3602758295988</v>
       </c>
       <c r="D67" t="n">
-        <v>637.5627451568915</v>
+        <v>642.054746271156</v>
       </c>
       <c r="E67" t="n">
-        <v>646.3570556640625</v>
+        <v>655.9799194335938</v>
       </c>
       <c r="F67" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G67" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B68" t="n">
-        <v>642.3541999133257</v>
+        <v>654.4426118233187</v>
       </c>
       <c r="C68" t="n">
-        <v>661.3602758295988</v>
+        <v>660.0526000253047</v>
       </c>
       <c r="D68" t="n">
-        <v>642.054746271156</v>
+        <v>648.0440522221027</v>
       </c>
       <c r="E68" t="n">
-        <v>655.9799194335938</v>
+        <v>648.343505859375</v>
       </c>
       <c r="F68" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B69" t="n">
-        <v>654.4426118233187</v>
+        <v>655.8600753372949</v>
       </c>
       <c r="C69" t="n">
-        <v>660.0526000253047</v>
+        <v>669.3659511843067</v>
       </c>
       <c r="D69" t="n">
-        <v>648.0440522221027</v>
+        <v>655.2910830082761</v>
       </c>
       <c r="E69" t="n">
-        <v>648.343505859375</v>
+        <v>663.266845703125</v>
       </c>
       <c r="F69" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B70" t="n">
-        <v>655.8600753372949</v>
+        <v>665.2333263832898</v>
       </c>
       <c r="C70" t="n">
-        <v>669.3659511843067</v>
+        <v>669.8051880946751</v>
       </c>
       <c r="D70" t="n">
-        <v>655.2910830082761</v>
+        <v>657.0080086354003</v>
       </c>
       <c r="E70" t="n">
-        <v>663.266845703125</v>
+        <v>657.5969848632812</v>
       </c>
       <c r="F70" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B71" t="n">
-        <v>665.2333263832898</v>
+        <v>660.4719008376494</v>
       </c>
       <c r="C71" t="n">
-        <v>669.8051880946751</v>
+        <v>672.3806511570199</v>
       </c>
       <c r="D71" t="n">
-        <v>657.0080086354003</v>
+        <v>655.4808037586267</v>
       </c>
       <c r="E71" t="n">
-        <v>657.5969848632812</v>
+        <v>660.3221435546875</v>
       </c>
       <c r="F71" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B72" t="n">
-        <v>660.4719008376494</v>
+        <v>658.8746741689592</v>
       </c>
       <c r="C72" t="n">
-        <v>672.3806511570199</v>
+        <v>664.8140915262984</v>
       </c>
       <c r="D72" t="n">
-        <v>655.4808037586267</v>
+        <v>657.0778915122911</v>
       </c>
       <c r="E72" t="n">
-        <v>660.3221435546875</v>
+        <v>663.7559814453125</v>
       </c>
       <c r="F72" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B73" t="n">
-        <v>658.8746741689592</v>
+        <v>661.3503083186049</v>
       </c>
       <c r="C73" t="n">
-        <v>664.8140915262984</v>
+        <v>666.9902112020924</v>
       </c>
       <c r="D73" t="n">
-        <v>657.0778915122911</v>
+        <v>661.0208788671576</v>
       </c>
       <c r="E73" t="n">
-        <v>663.7559814453125</v>
+        <v>666.361328125</v>
       </c>
       <c r="F73" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B74" t="n">
-        <v>661.3503083186049</v>
+        <v>666.8704739599774</v>
       </c>
       <c r="C74" t="n">
-        <v>666.9902112020924</v>
+        <v>667.7589038803495</v>
       </c>
       <c r="D74" t="n">
-        <v>661.0208788671576</v>
+        <v>660.1424847097468</v>
       </c>
       <c r="E74" t="n">
-        <v>666.361328125</v>
+        <v>662.1089477539062</v>
       </c>
       <c r="F74" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B75" t="n">
-        <v>666.8704739599774</v>
+        <v>656.8383689858442</v>
       </c>
       <c r="C75" t="n">
-        <v>667.7589038803495</v>
+        <v>659.0743707339258</v>
       </c>
       <c r="D75" t="n">
-        <v>660.1424847097468</v>
+        <v>653.2248195668056</v>
       </c>
       <c r="E75" t="n">
-        <v>662.1089477539062</v>
+        <v>657.5171508789062</v>
       </c>
       <c r="F75" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B76" t="n">
-        <v>656.8383689858442</v>
+        <v>657.5171386037911</v>
       </c>
       <c r="C76" t="n">
-        <v>659.0743707339258</v>
+        <v>671.0230153954109</v>
       </c>
       <c r="D76" t="n">
-        <v>653.2248195668056</v>
+        <v>656.6686764849229</v>
       </c>
       <c r="E76" t="n">
-        <v>657.5171508789062</v>
+        <v>664.7642211914062</v>
       </c>
       <c r="F76" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B77" t="n">
-        <v>657.5171386037911</v>
+        <v>663.5662869980947</v>
       </c>
       <c r="C77" t="n">
-        <v>671.0230153954109</v>
+        <v>663.8158418258488</v>
       </c>
       <c r="D77" t="n">
-        <v>656.6686764849229</v>
+        <v>658.2657448936569</v>
       </c>
       <c r="E77" t="n">
-        <v>664.7642211914062</v>
+        <v>658.9146118164062</v>
       </c>
       <c r="F77" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B78" t="n">
-        <v>663.5662869980947</v>
+        <v>661.5499009554064</v>
       </c>
       <c r="C78" t="n">
-        <v>663.8158418258488</v>
+        <v>663.2069792218492</v>
       </c>
       <c r="D78" t="n">
-        <v>658.2657448936569</v>
+        <v>642.3541620430398</v>
       </c>
       <c r="E78" t="n">
-        <v>658.9146118164062</v>
+        <v>649.2518310546875</v>
       </c>
       <c r="F78" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B79" t="n">
-        <v>661.5499009554064</v>
+        <v>649.8508280292294</v>
       </c>
       <c r="C79" t="n">
-        <v>663.2069792218492</v>
+        <v>663.3567049684374</v>
       </c>
       <c r="D79" t="n">
-        <v>642.3541620430398</v>
+        <v>646.5966230035071</v>
       </c>
       <c r="E79" t="n">
-        <v>649.2518310546875</v>
+        <v>657.616943359375</v>
       </c>
       <c r="F79" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B80" t="n">
-        <v>649.8508280292294</v>
+        <v>658.3955464147172</v>
       </c>
       <c r="C80" t="n">
-        <v>663.3567049684374</v>
+        <v>664.3349637543794</v>
       </c>
       <c r="D80" t="n">
-        <v>646.5966230035071</v>
+        <v>650.7392210314413</v>
       </c>
       <c r="E80" t="n">
-        <v>657.616943359375</v>
+        <v>659.4436645507812</v>
       </c>
       <c r="F80" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B81" t="n">
-        <v>658.3955464147172</v>
+        <v>654.4725487720359</v>
       </c>
       <c r="C81" t="n">
-        <v>664.3349637543794</v>
+        <v>657.9763084361789</v>
       </c>
       <c r="D81" t="n">
-        <v>650.7392210314413</v>
+        <v>643.6618161601232</v>
       </c>
       <c r="E81" t="n">
-        <v>659.4436645507812</v>
+        <v>647.534912109375</v>
       </c>
       <c r="F81" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B82" t="n">
-        <v>654.4725487720359</v>
+        <v>644.7299347572825</v>
       </c>
       <c r="C82" t="n">
-        <v>657.9763084361789</v>
+        <v>645.9477331499952</v>
       </c>
       <c r="D82" t="n">
-        <v>643.6618161601232</v>
+        <v>634.5879917891143</v>
       </c>
       <c r="E82" t="n">
-        <v>647.534912109375</v>
+        <v>644.9096069335938</v>
       </c>
       <c r="F82" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B83" t="n">
-        <v>644.7299347572825</v>
+        <v>644.2907288447692</v>
       </c>
       <c r="C83" t="n">
-        <v>645.9477331499952</v>
+        <v>653.7838050409127</v>
       </c>
       <c r="D83" t="n">
-        <v>634.5879917891143</v>
+        <v>641.7053138036724</v>
       </c>
       <c r="E83" t="n">
-        <v>644.9096069335938</v>
+        <v>651.8971557617188</v>
       </c>
       <c r="F83" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B84" t="n">
-        <v>644.2907288447692</v>
+        <v>651.3680980277007</v>
       </c>
       <c r="C84" t="n">
-        <v>653.7838050409127</v>
+        <v>652.8054753941815</v>
       </c>
       <c r="D84" t="n">
-        <v>641.7053138036724</v>
+        <v>640.0881706951194</v>
       </c>
       <c r="E84" t="n">
-        <v>651.8971557617188</v>
+        <v>640.8268432617188</v>
       </c>
       <c r="F84" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B85" t="n">
-        <v>651.3680980277007</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="C85" t="n">
-        <v>652.8054753941815</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="D85" t="n">
-        <v>640.0881706951194</v>
+        <v>622.9887038024194</v>
       </c>
       <c r="E85" t="n">
-        <v>640.8268432617188</v>
+        <v>629.96630859375</v>
       </c>
       <c r="F85" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B86" t="n">
-        <v>641.1263941859123</v>
+        <v>625.3844405077801</v>
       </c>
       <c r="C86" t="n">
-        <v>641.1263941859123</v>
+        <v>627.3309804807691</v>
       </c>
       <c r="D86" t="n">
-        <v>622.9887038024194</v>
+        <v>613.7252454803604</v>
       </c>
       <c r="E86" t="n">
-        <v>629.96630859375</v>
+        <v>614.4240112304688</v>
       </c>
       <c r="F86" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B87" t="n">
-        <v>625.3844405077801</v>
+        <v>617.378703801015</v>
       </c>
       <c r="C87" t="n">
-        <v>627.3309804807691</v>
+        <v>623.0585745209008</v>
       </c>
       <c r="D87" t="n">
-        <v>613.7252454803604</v>
+        <v>613.1362714280776</v>
       </c>
       <c r="E87" t="n">
-        <v>614.4240112304688</v>
+        <v>619.694580078125</v>
       </c>
       <c r="F87" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B88" t="n">
-        <v>617.378703801015</v>
+        <v>623.0685636897582</v>
       </c>
       <c r="C88" t="n">
-        <v>623.0585745209008</v>
+        <v>627.9598630097294</v>
       </c>
       <c r="D88" t="n">
-        <v>613.1362714280776</v>
+        <v>618.9758886129073</v>
       </c>
       <c r="E88" t="n">
-        <v>619.694580078125</v>
+        <v>619.1455688476562</v>
       </c>
       <c r="F88" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B89" t="n">
-        <v>623.0685636897582</v>
+        <v>606.7976262932837</v>
       </c>
       <c r="C89" t="n">
-        <v>627.9598630097294</v>
+        <v>610.3113781504126</v>
       </c>
       <c r="D89" t="n">
-        <v>618.9758886129073</v>
+        <v>598.9316523845154</v>
       </c>
       <c r="E89" t="n">
-        <v>619.1455688476562</v>
+        <v>603.0443115234375</v>
       </c>
       <c r="F89" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B90" t="n">
-        <v>606.7976262932837</v>
+        <v>605.659634898437</v>
       </c>
       <c r="C90" t="n">
-        <v>610.3113781504126</v>
+        <v>617.169133937088</v>
       </c>
       <c r="D90" t="n">
-        <v>598.9316523845154</v>
+        <v>599.0115204374271</v>
       </c>
       <c r="E90" t="n">
-        <v>603.0443115234375</v>
+        <v>611.8685913085938</v>
       </c>
       <c r="F90" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B91" t="n">
-        <v>605.659634898437</v>
+        <v>628.2293275614567</v>
       </c>
       <c r="C91" t="n">
-        <v>617.169133937088</v>
+        <v>659.3937675491238</v>
       </c>
       <c r="D91" t="n">
-        <v>599.0115204374271</v>
+        <v>625.4343255489129</v>
       </c>
       <c r="E91" t="n">
-        <v>611.8685913085938</v>
+        <v>646.476806640625</v>
       </c>
       <c r="F91" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B92" t="n">
-        <v>628.2293275614567</v>
+        <v>643.6219561683764</v>
       </c>
       <c r="C92" t="n">
-        <v>659.3937675491238</v>
+        <v>665.3032527677875</v>
       </c>
       <c r="D92" t="n">
-        <v>625.4343255489129</v>
+        <v>643.3025186421843</v>
       </c>
       <c r="E92" t="n">
-        <v>646.476806640625</v>
+        <v>657.5870361328125</v>
       </c>
       <c r="F92" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B93" t="n">
-        <v>643.6219561683764</v>
+        <v>663.9456136216552</v>
       </c>
       <c r="C93" t="n">
-        <v>665.3032527677875</v>
+        <v>674.0775639748149</v>
       </c>
       <c r="D93" t="n">
-        <v>643.3025186421843</v>
+        <v>660.1124246688775</v>
       </c>
       <c r="E93" t="n">
-        <v>657.5870361328125</v>
+        <v>671.1627197265625</v>
       </c>
       <c r="F93" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B94" t="n">
-        <v>663.9456136216552</v>
+        <v>673.3888389297905</v>
       </c>
       <c r="C94" t="n">
-        <v>674.0775639748149</v>
+        <v>675.6148486525956</v>
       </c>
       <c r="D94" t="n">
-        <v>660.1124246688775</v>
+        <v>663.4764668627315</v>
       </c>
       <c r="E94" t="n">
-        <v>671.1627197265625</v>
+        <v>671.7716674804688</v>
       </c>
       <c r="F94" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B95" t="n">
-        <v>673.3888389297905</v>
+        <v>673.2989295276801</v>
       </c>
       <c r="C95" t="n">
-        <v>675.6148486525956</v>
+        <v>676.4732596455591</v>
       </c>
       <c r="D95" t="n">
-        <v>663.4764668627315</v>
+        <v>664.9138628916613</v>
       </c>
       <c r="E95" t="n">
-        <v>671.7716674804688</v>
+        <v>667.5391845703125</v>
       </c>
       <c r="F95" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B96" t="n">
-        <v>673.2989295276801</v>
+        <v>736.1169233837337</v>
       </c>
       <c r="C96" t="n">
-        <v>676.4732596455591</v>
+        <v>742.6752321400184</v>
       </c>
       <c r="D96" t="n">
-        <v>664.9138628916613</v>
+        <v>711.2812198864386</v>
       </c>
       <c r="E96" t="n">
-        <v>667.5391845703125</v>
+        <v>736.995361328125</v>
       </c>
       <c r="F96" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B97" t="n">
-        <v>736.1169233837337</v>
+        <v>726.2045952530067</v>
       </c>
       <c r="C97" t="n">
-        <v>742.6752321400184</v>
+        <v>730.8662626744616</v>
       </c>
       <c r="D97" t="n">
-        <v>711.2812198864386</v>
+        <v>712.3193905555435</v>
       </c>
       <c r="E97" t="n">
-        <v>736.995361328125</v>
+        <v>715.2241821289062</v>
       </c>
       <c r="F97" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B98" t="n">
-        <v>726.2045952530067</v>
+        <v>713.3275184694113</v>
       </c>
       <c r="C98" t="n">
-        <v>730.8662626744616</v>
+        <v>720.0156002559207</v>
       </c>
       <c r="D98" t="n">
-        <v>712.3193905555435</v>
+        <v>702.2672920108814</v>
       </c>
       <c r="E98" t="n">
-        <v>715.2241821289062</v>
+        <v>705.152099609375</v>
       </c>
       <c r="F98" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B99" t="n">
-        <v>713.3275184694113</v>
+        <v>706.1104025957663</v>
       </c>
       <c r="C99" t="n">
-        <v>720.0156002559207</v>
+        <v>715.7232596178901</v>
       </c>
       <c r="D99" t="n">
-        <v>702.2672920108814</v>
+        <v>685.1877035052055</v>
       </c>
       <c r="E99" t="n">
-        <v>705.152099609375</v>
+        <v>690.4683227539062</v>
       </c>
       <c r="F99" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B100" t="n">
-        <v>706.1104025957663</v>
+        <v>686.5054510943589</v>
       </c>
       <c r="C100" t="n">
-        <v>715.7232596178901</v>
+        <v>687.6035290584308</v>
       </c>
       <c r="D100" t="n">
-        <v>685.1877035052055</v>
+        <v>666.2715840299333</v>
       </c>
       <c r="E100" t="n">
-        <v>690.4683227539062</v>
+        <v>667.798828125</v>
       </c>
       <c r="F100" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B101" t="n">
-        <v>686.5054510943589</v>
+        <v>662.3984629374214</v>
       </c>
       <c r="C101" t="n">
-        <v>687.6035290584308</v>
+        <v>680.2865379695924</v>
       </c>
       <c r="D101" t="n">
-        <v>666.2715840299333</v>
+        <v>652.3363940764909</v>
       </c>
       <c r="E101" t="n">
-        <v>667.798828125</v>
+        <v>669.0166625976562</v>
       </c>
       <c r="F101" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B102" t="n">
-        <v>662.3984629374214</v>
+        <v>664.3050190645899</v>
       </c>
       <c r="C102" t="n">
-        <v>680.2865379695924</v>
+        <v>670.7934451675868</v>
       </c>
       <c r="D102" t="n">
-        <v>652.3363940764909</v>
+        <v>645.3488423980709</v>
       </c>
       <c r="E102" t="n">
-        <v>669.0166625976562</v>
+        <v>660.2822265625</v>
       </c>
       <c r="F102" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B103" t="n">
-        <v>664.3050190645899</v>
+        <v>661.9991209626965</v>
       </c>
       <c r="C103" t="n">
-        <v>670.7934451675868</v>
+        <v>682.0932819515241</v>
       </c>
       <c r="D103" t="n">
-        <v>645.3488423980709</v>
+        <v>657.6069922476072</v>
       </c>
       <c r="E103" t="n">
-        <v>660.2822265625</v>
+        <v>676.0140991210938</v>
       </c>
       <c r="F103" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B104" t="n">
-        <v>661.9991209626965</v>
+        <v>676.39338857878</v>
       </c>
       <c r="C104" t="n">
-        <v>682.0932819515241</v>
+        <v>679.4380062536881</v>
       </c>
       <c r="D104" t="n">
-        <v>657.6069922476072</v>
+        <v>668.5972981068446</v>
       </c>
       <c r="E104" t="n">
-        <v>676.0140991210938</v>
+        <v>669.525634765625</v>
       </c>
       <c r="F104" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B105" t="n">
-        <v>676.39338857878</v>
+        <v>672.7998711552045</v>
       </c>
       <c r="C105" t="n">
-        <v>679.4380062536881</v>
+        <v>678.0605068549233</v>
       </c>
       <c r="D105" t="n">
-        <v>668.5972981068446</v>
+        <v>655.9299390360635</v>
       </c>
       <c r="E105" t="n">
-        <v>669.525634765625</v>
+        <v>667.4993286132812</v>
       </c>
       <c r="F105" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B106" t="n">
-        <v>672.7998711552045</v>
+        <v>668.7770306530766</v>
       </c>
       <c r="C106" t="n">
-        <v>678.0605068549233</v>
+        <v>674.7963229561075</v>
       </c>
       <c r="D106" t="n">
-        <v>655.9299390360635</v>
+        <v>644.1310518439949</v>
       </c>
       <c r="E106" t="n">
-        <v>667.4993286132812</v>
+        <v>648.6529541015625</v>
       </c>
       <c r="F106" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B107" t="n">
-        <v>668.7770306530766</v>
+        <v>643.9512634857649</v>
       </c>
       <c r="C107" t="n">
-        <v>674.7963229561075</v>
+        <v>650.2700088851722</v>
       </c>
       <c r="D107" t="n">
-        <v>644.1310518439949</v>
+        <v>633.4400456540794</v>
       </c>
       <c r="E107" t="n">
-        <v>648.6529541015625</v>
+        <v>638.6307983398438</v>
       </c>
       <c r="F107" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B108" t="n">
-        <v>643.9512634857649</v>
+        <v>638.3613203754355</v>
       </c>
       <c r="C108" t="n">
-        <v>650.2700088851722</v>
+        <v>641.4557762130754</v>
       </c>
       <c r="D108" t="n">
-        <v>633.4400456540794</v>
+        <v>627.6803603746322</v>
       </c>
       <c r="E108" t="n">
-        <v>638.6307983398438</v>
+        <v>638.1516723632812</v>
       </c>
       <c r="F108" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B109" t="n">
-        <v>638.3613203754355</v>
+        <v>632.67143641335</v>
       </c>
       <c r="C109" t="n">
-        <v>641.4557762130754</v>
+        <v>643.8515057528024</v>
       </c>
       <c r="D109" t="n">
-        <v>627.6803603746322</v>
+        <v>627.0315334227189</v>
       </c>
       <c r="E109" t="n">
-        <v>638.1516723632812</v>
+        <v>642.0746459960938</v>
       </c>
       <c r="F109" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B110" t="n">
-        <v>632.67143641335</v>
+        <v>637.432932921519</v>
       </c>
       <c r="C110" t="n">
-        <v>643.8515057528024</v>
+        <v>646.0375787806976</v>
       </c>
       <c r="D110" t="n">
-        <v>627.0315334227189</v>
+        <v>635.5861905818066</v>
       </c>
       <c r="E110" t="n">
-        <v>642.0746459960938</v>
+        <v>643.6318969726562</v>
       </c>
       <c r="F110" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B111" t="n">
-        <v>637.432932921519</v>
+        <v>638.5510179511008</v>
       </c>
       <c r="C111" t="n">
-        <v>646.0375787806976</v>
+        <v>662.1688639053526</v>
       </c>
       <c r="D111" t="n">
-        <v>635.5861905818066</v>
+        <v>637.642665037141</v>
       </c>
       <c r="E111" t="n">
-        <v>643.6318969726562</v>
+        <v>654.4925537109375</v>
       </c>
       <c r="F111" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B112" t="n">
-        <v>638.5510179511008</v>
+        <v>651.3781101885919</v>
       </c>
       <c r="C112" t="n">
-        <v>662.1688639053526</v>
+        <v>656.5289567660449</v>
       </c>
       <c r="D112" t="n">
-        <v>637.642665037141</v>
+        <v>634.8675821094057</v>
       </c>
       <c r="E112" t="n">
-        <v>654.4925537109375</v>
+        <v>636.1153564453125</v>
       </c>
       <c r="F112" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B113" t="n">
-        <v>651.3781101885919</v>
+        <v>631.9527863953055</v>
       </c>
       <c r="C113" t="n">
-        <v>656.5289567660449</v>
+        <v>639.9684568961466</v>
       </c>
       <c r="D113" t="n">
-        <v>634.8675821094057</v>
+        <v>627.8600500948714</v>
       </c>
       <c r="E113" t="n">
-        <v>636.1153564453125</v>
+        <v>638.1616821289062</v>
       </c>
       <c r="F113" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B114" t="n">
-        <v>631.9527863953055</v>
+        <v>641.3858999809694</v>
       </c>
       <c r="C114" t="n">
-        <v>639.9684568961466</v>
+        <v>652.7156650876909</v>
       </c>
       <c r="D114" t="n">
-        <v>627.8600500948714</v>
+        <v>640.9965798171046</v>
       </c>
       <c r="E114" t="n">
-        <v>638.1616821289062</v>
+        <v>652.5260009765625</v>
       </c>
       <c r="F114" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B115" t="n">
-        <v>641.3858999809694</v>
+        <v>649.3916295582877</v>
       </c>
       <c r="C115" t="n">
-        <v>652.7156650876909</v>
+        <v>659.823034651462</v>
       </c>
       <c r="D115" t="n">
-        <v>640.9965798171046</v>
+        <v>646.3470725216666</v>
       </c>
       <c r="E115" t="n">
-        <v>652.5260009765625</v>
+        <v>655.8401489257812</v>
       </c>
       <c r="F115" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B116" t="n">
-        <v>649.3916295582877</v>
+        <v>642.3042597917192</v>
       </c>
       <c r="C116" t="n">
-        <v>659.823034651462</v>
+        <v>648.2835840137412</v>
       </c>
       <c r="D116" t="n">
-        <v>646.3470725216666</v>
+        <v>636.9837335400734</v>
       </c>
       <c r="E116" t="n">
-        <v>655.8401489257812</v>
+        <v>647.0258178710938</v>
       </c>
       <c r="F116" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B117" t="n">
-        <v>642.3042597917192</v>
+        <v>636.0254184162494</v>
       </c>
       <c r="C117" t="n">
-        <v>648.2835840137412</v>
+        <v>658.764884603327</v>
       </c>
       <c r="D117" t="n">
-        <v>636.9837335400734</v>
+        <v>633.3701817354564</v>
       </c>
       <c r="E117" t="n">
-        <v>647.0258178710938</v>
+        <v>652.396240234375</v>
       </c>
       <c r="F117" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B118" t="n">
-        <v>636.0254184162494</v>
+        <v>647.1356255764312</v>
       </c>
       <c r="C118" t="n">
-        <v>658.764884603327</v>
+        <v>657.866484005116</v>
       </c>
       <c r="D118" t="n">
-        <v>633.3701817354564</v>
+        <v>637.7025010942567</v>
       </c>
       <c r="E118" t="n">
-        <v>652.396240234375</v>
+        <v>653.91357421875</v>
       </c>
       <c r="F118" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B119" t="n">
-        <v>647.1356255764312</v>
+        <v>656.7884535878291</v>
       </c>
       <c r="C119" t="n">
-        <v>657.866484005116</v>
+        <v>671.5720803574089</v>
       </c>
       <c r="D119" t="n">
-        <v>637.7025010942567</v>
+        <v>656.4989309709863</v>
       </c>
       <c r="E119" t="n">
-        <v>653.91357421875</v>
+        <v>666.541015625</v>
       </c>
       <c r="F119" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B120" t="n">
-        <v>656.7884535878291</v>
+        <v>660.751362594833</v>
       </c>
       <c r="C120" t="n">
-        <v>671.5720803574089</v>
+        <v>669.5057662619517</v>
       </c>
       <c r="D120" t="n">
-        <v>656.4989309709863</v>
+        <v>649.1520579976961</v>
       </c>
       <c r="E120" t="n">
-        <v>666.541015625</v>
+        <v>659.393798828125</v>
       </c>
       <c r="F120" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B121" t="n">
-        <v>660.751362594833</v>
+        <v>646.7463568472266</v>
       </c>
       <c r="C121" t="n">
-        <v>669.5057662619517</v>
+        <v>648.3135076492586</v>
       </c>
       <c r="D121" t="n">
-        <v>649.1520579976961</v>
+        <v>634.9773114336934</v>
       </c>
       <c r="E121" t="n">
-        <v>659.393798828125</v>
+        <v>643.7117309570312</v>
       </c>
       <c r="F121" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B122" t="n">
-        <v>646.7463568472266</v>
+        <v>633.6497121926325</v>
       </c>
       <c r="C122" t="n">
-        <v>648.3135076492586</v>
+        <v>646.5965879982328</v>
       </c>
       <c r="D122" t="n">
-        <v>634.9773114336934</v>
+        <v>625.6639573427893</v>
       </c>
       <c r="E122" t="n">
-        <v>643.7117309570312</v>
+        <v>646.2372436523438</v>
       </c>
       <c r="F122" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B123" t="n">
-        <v>633.6497121926325</v>
+        <v>652.3962938458964</v>
       </c>
       <c r="C123" t="n">
-        <v>646.5965879982328</v>
+        <v>659.1242831137364</v>
       </c>
       <c r="D123" t="n">
-        <v>625.6639573427893</v>
+        <v>647.8444156429986</v>
       </c>
       <c r="E123" t="n">
-        <v>646.2372436523438</v>
+        <v>652.9053955078125</v>
       </c>
       <c r="F123" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B124" t="n">
-        <v>652.3962938458964</v>
+        <v>653.5941721528687</v>
       </c>
       <c r="C124" t="n">
-        <v>659.1242831137364</v>
+        <v>657.9463943013674</v>
       </c>
       <c r="D124" t="n">
-        <v>647.8444156429986</v>
+        <v>647.2055433479961</v>
       </c>
       <c r="E124" t="n">
-        <v>652.9053955078125</v>
+        <v>653.6939697265625</v>
       </c>
       <c r="F124" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B125" t="n">
-        <v>653.5941721528687</v>
+        <v>647.5948883988538</v>
       </c>
       <c r="C125" t="n">
-        <v>657.9463943013674</v>
+        <v>652.3364309343367</v>
       </c>
       <c r="D125" t="n">
-        <v>647.2055433479961</v>
+        <v>635.7660119177681</v>
       </c>
       <c r="E125" t="n">
-        <v>653.6939697265625</v>
+        <v>637.043701171875</v>
       </c>
       <c r="F125" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B126" t="n">
-        <v>647.5948883988538</v>
+        <v>622.7790526456299</v>
       </c>
       <c r="C126" t="n">
-        <v>652.3364309343367</v>
+        <v>628.0496188589474</v>
       </c>
       <c r="D126" t="n">
-        <v>635.7660119177681</v>
+        <v>608.4645611002024</v>
       </c>
       <c r="E126" t="n">
-        <v>637.043701171875</v>
+        <v>612.6171875</v>
       </c>
       <c r="F126" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,25 +3719,25 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B127" t="n">
-        <v>622.7790526456299</v>
+        <v>631.4147932406764</v>
       </c>
       <c r="C127" t="n">
-        <v>628.0496188589474</v>
+        <v>634.1622468505053</v>
       </c>
       <c r="D127" t="n">
-        <v>608.4645611002024</v>
+        <v>622.5230098937741</v>
       </c>
       <c r="E127" t="n">
-        <v>612.6171875</v>
+        <v>626.8690185546875</v>
       </c>
       <c r="F127" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -3745,25 +3745,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B128" t="n">
-        <v>631.4147932406764</v>
+        <v>627.4085169382369</v>
       </c>
       <c r="C128" t="n">
-        <v>634.1622468505053</v>
+        <v>635.9605885584036</v>
       </c>
       <c r="D128" t="n">
-        <v>622.5230098937741</v>
+        <v>621.1243629754691</v>
       </c>
       <c r="E128" t="n">
-        <v>626.8690185546875</v>
+        <v>622.0834350585938</v>
       </c>
       <c r="F128" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G128" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B129" t="n">
-        <v>627.4085169382369</v>
+        <v>615.7693473594539</v>
       </c>
       <c r="C129" t="n">
-        <v>635.9605885584036</v>
+        <v>622.0735023862151</v>
       </c>
       <c r="D129" t="n">
-        <v>621.1243629754691</v>
+        <v>614.04090772979</v>
       </c>
       <c r="E129" t="n">
-        <v>622.0834350585938</v>
+        <v>615.1099243164062</v>
       </c>
       <c r="F129" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B130" t="n">
-        <v>615.7693473594539</v>
+        <v>611.5832104537112</v>
       </c>
       <c r="C130" t="n">
-        <v>622.0735023862151</v>
+        <v>612.4323990135786</v>
       </c>
       <c r="D130" t="n">
-        <v>614.04090772979</v>
+        <v>601.7023533616688</v>
       </c>
       <c r="E130" t="n">
-        <v>615.1099243164062</v>
+        <v>606.1382446289062</v>
       </c>
       <c r="F130" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B131" t="n">
-        <v>611.5832104537112</v>
+        <v>602.9712077810872</v>
       </c>
       <c r="C131" t="n">
-        <v>612.4323990135786</v>
+        <v>603.400802317344</v>
       </c>
       <c r="D131" t="n">
-        <v>601.7023533616688</v>
+        <v>586.7062525156723</v>
       </c>
       <c r="E131" t="n">
-        <v>606.1382446289062</v>
+        <v>593.1102905273438</v>
       </c>
       <c r="F131" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B132" t="n">
-        <v>602.9712077810872</v>
+        <v>605.2290499891692</v>
       </c>
       <c r="C132" t="n">
-        <v>603.400802317344</v>
+        <v>608.0764476338709</v>
       </c>
       <c r="D132" t="n">
-        <v>586.7062525156723</v>
+        <v>598.4553596033379</v>
       </c>
       <c r="E132" t="n">
-        <v>593.1102905273438</v>
+        <v>603.5006713867188</v>
       </c>
       <c r="F132" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B133" t="n">
-        <v>605.2290499891692</v>
+        <v>598.5452420228083</v>
       </c>
       <c r="C133" t="n">
-        <v>608.0764476338709</v>
+        <v>600.443507118967</v>
       </c>
       <c r="D133" t="n">
-        <v>598.4553596033379</v>
+        <v>590.4527665679026</v>
       </c>
       <c r="E133" t="n">
-        <v>603.5006713867188</v>
+        <v>592.3709716796875</v>
       </c>
       <c r="F133" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B134" t="n">
-        <v>598.5452420228083</v>
+        <v>598.1855830392399</v>
       </c>
       <c r="C134" t="n">
-        <v>600.443507118967</v>
+        <v>603.1110107561809</v>
       </c>
       <c r="D134" t="n">
-        <v>590.4527665679026</v>
+        <v>592.8505617950721</v>
       </c>
       <c r="E134" t="n">
-        <v>592.3709716796875</v>
+        <v>594.3391723632812</v>
       </c>
       <c r="F134" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B135" t="n">
-        <v>598.1855830392399</v>
+        <v>581.9506076701073</v>
       </c>
       <c r="C135" t="n">
-        <v>603.1110107561809</v>
+        <v>582.460145169462</v>
       </c>
       <c r="D135" t="n">
-        <v>592.8505617950721</v>
+        <v>542.8468364624507</v>
       </c>
       <c r="E135" t="n">
-        <v>594.3391723632812</v>
+        <v>547.032958984375</v>
       </c>
       <c r="F135" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B136" t="n">
-        <v>581.9506076701073</v>
+        <v>539.599843303006</v>
       </c>
       <c r="C136" t="n">
-        <v>582.460145169462</v>
+        <v>543.0966023049141</v>
       </c>
       <c r="D136" t="n">
-        <v>542.8468364624507</v>
+        <v>519.7782492802263</v>
       </c>
       <c r="E136" t="n">
-        <v>547.032958984375</v>
+        <v>525.233154296875</v>
       </c>
       <c r="F136" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B137" t="n">
-        <v>539.599843303006</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="C137" t="n">
-        <v>543.0966023049141</v>
+        <v>539.0504095872608</v>
       </c>
       <c r="D137" t="n">
-        <v>519.7782492802263</v>
+        <v>528.0505941707193</v>
       </c>
       <c r="E137" t="n">
-        <v>525.233154296875</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="F137" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B138" t="n">
-        <v>535.8833618164062</v>
+        <v>549.4707059552647</v>
       </c>
       <c r="C138" t="n">
-        <v>539.0504095872608</v>
+        <v>573.1587727471259</v>
       </c>
       <c r="D138" t="n">
-        <v>528.0505941707193</v>
+        <v>546.2637174010383</v>
       </c>
       <c r="E138" t="n">
-        <v>535.8833618164062</v>
+        <v>571.6002197265625</v>
       </c>
       <c r="F138" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B139" t="n">
-        <v>549.4707059552647</v>
+        <v>579.5928556215499</v>
       </c>
       <c r="C139" t="n">
-        <v>573.1587727471259</v>
+        <v>592.0013387220274</v>
       </c>
       <c r="D139" t="n">
-        <v>546.2637174010383</v>
+        <v>573.2887005646345</v>
       </c>
       <c r="E139" t="n">
-        <v>571.6002197265625</v>
+        <v>578.6936645507812</v>
       </c>
       <c r="F139" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B140" t="n">
-        <v>579.5928556215499</v>
+        <v>565.5158531822124</v>
       </c>
       <c r="C140" t="n">
-        <v>592.0013387220274</v>
+        <v>577.9643377947169</v>
       </c>
       <c r="D140" t="n">
-        <v>573.2887005646345</v>
+        <v>559.1817578546791</v>
       </c>
       <c r="E140" t="n">
-        <v>578.6936645507812</v>
+        <v>573.9281005859375</v>
       </c>
       <c r="F140" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B141" t="n">
-        <v>565.5158531822124</v>
+        <v>577.1550997330287</v>
       </c>
       <c r="C141" t="n">
-        <v>577.9643377947169</v>
+        <v>582.2503530791108</v>
       </c>
       <c r="D141" t="n">
-        <v>559.1817578546791</v>
+        <v>571.4703658572956</v>
       </c>
       <c r="E141" t="n">
-        <v>573.9281005859375</v>
+        <v>572.4894409179688</v>
       </c>
       <c r="F141" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B142" t="n">
-        <v>577.1550997330287</v>
+        <v>571.9498894780604</v>
       </c>
       <c r="C142" t="n">
-        <v>582.2503530791108</v>
+        <v>574.6973431004155</v>
       </c>
       <c r="D142" t="n">
-        <v>571.4703658572956</v>
+        <v>564.2370671243236</v>
       </c>
       <c r="E142" t="n">
-        <v>572.4894409179688</v>
+        <v>574.5175170898438</v>
       </c>
       <c r="F142" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B143" t="n">
-        <v>571.9498894780604</v>
+        <v>605.4388670235439</v>
       </c>
       <c r="C143" t="n">
-        <v>574.6973431004155</v>
+        <v>629.3667024291958</v>
       </c>
       <c r="D143" t="n">
-        <v>564.2370671243236</v>
+        <v>591.2820049792073</v>
       </c>
       <c r="E143" t="n">
-        <v>574.5175170898438</v>
+        <v>611.8529052734375</v>
       </c>
       <c r="F143" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B144" t="n">
-        <v>605.4388670235439</v>
+        <v>626.3894374266143</v>
       </c>
       <c r="C144" t="n">
-        <v>629.3667024291958</v>
+        <v>636.9097166035551</v>
       </c>
       <c r="D144" t="n">
-        <v>591.2820049792073</v>
+        <v>622.4231426572783</v>
       </c>
       <c r="E144" t="n">
-        <v>611.8529052734375</v>
+        <v>627.8081665039062</v>
       </c>
       <c r="F144" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B145" t="n">
-        <v>626.3894374266143</v>
+        <v>633.882449891805</v>
       </c>
       <c r="C145" t="n">
-        <v>636.9097166035551</v>
+        <v>637.9886903650855</v>
       </c>
       <c r="D145" t="n">
-        <v>622.4231426572783</v>
+        <v>623.7518859014353</v>
       </c>
       <c r="E145" t="n">
-        <v>627.8081665039062</v>
+        <v>629.2767333984375</v>
       </c>
       <c r="F145" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B146" t="n">
-        <v>633.882449891805</v>
+        <v>628.9171329935918</v>
       </c>
       <c r="C146" t="n">
-        <v>637.9886903650855</v>
+        <v>634.4120404303904</v>
       </c>
       <c r="D146" t="n">
-        <v>623.7518859014353</v>
+        <v>623.8218795800174</v>
       </c>
       <c r="E146" t="n">
-        <v>629.2767333984375</v>
+        <v>633.9425048828125</v>
       </c>
       <c r="F146" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B147" t="n">
-        <v>628.9171329935918</v>
+        <v>642.624350345733</v>
       </c>
       <c r="C147" t="n">
-        <v>634.4120404303904</v>
+        <v>665.6430543798978</v>
       </c>
       <c r="D147" t="n">
-        <v>623.8218795800174</v>
+        <v>638.7779398291946</v>
       </c>
       <c r="E147" t="n">
-        <v>633.9425048828125</v>
+        <v>661.8765258789062</v>
       </c>
       <c r="F147" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B148" t="n">
-        <v>642.624350345733</v>
+        <v>666.3824145357423</v>
       </c>
       <c r="C148" t="n">
-        <v>665.6430543798978</v>
+        <v>677.8717665104965</v>
       </c>
       <c r="D148" t="n">
-        <v>638.7779398291946</v>
+        <v>663.6049593103575</v>
       </c>
       <c r="E148" t="n">
-        <v>661.8765258789062</v>
+        <v>670.9581909179688</v>
       </c>
       <c r="F148" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B149" t="n">
-        <v>666.3824145357423</v>
+        <v>675.3640350842893</v>
       </c>
       <c r="C149" t="n">
-        <v>677.8717665104965</v>
+        <v>676.9525896021297</v>
       </c>
       <c r="D149" t="n">
-        <v>663.6049593103575</v>
+        <v>667.131674939706</v>
       </c>
       <c r="E149" t="n">
-        <v>670.9581909179688</v>
+        <v>676.2432250976562</v>
       </c>
       <c r="F149" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B150" t="n">
-        <v>675.3640350842893</v>
+        <v>677.9716157075654</v>
       </c>
       <c r="C150" t="n">
-        <v>676.9525896021297</v>
+        <v>690.8796961433965</v>
       </c>
       <c r="D150" t="n">
-        <v>667.131674939706</v>
+        <v>674.5048580761284</v>
       </c>
       <c r="E150" t="n">
-        <v>676.2432250976562</v>
+        <v>687.9124145507812</v>
       </c>
       <c r="F150" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B151" t="n">
-        <v>677.9716157075654</v>
+        <v>680.7290935491282</v>
       </c>
       <c r="C151" t="n">
-        <v>690.8796961433965</v>
+        <v>682.7472426832454</v>
       </c>
       <c r="D151" t="n">
-        <v>674.5048580761284</v>
+        <v>667.381478611767</v>
       </c>
       <c r="E151" t="n">
-        <v>687.9124145507812</v>
+        <v>670.2887573242188</v>
       </c>
       <c r="F151" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B152" t="n">
-        <v>680.7290935491282</v>
+        <v>670.3786762058809</v>
       </c>
       <c r="C152" t="n">
-        <v>682.7472426832454</v>
+        <v>675.5738733736962</v>
       </c>
       <c r="D152" t="n">
-        <v>667.381478611767</v>
+        <v>666.7120915784461</v>
       </c>
       <c r="E152" t="n">
-        <v>670.2887573242188</v>
+        <v>668.220703125</v>
       </c>
       <c r="F152" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B153" t="n">
-        <v>670.3786762058809</v>
+        <v>673.7355628200382</v>
       </c>
       <c r="C153" t="n">
-        <v>675.5738733736962</v>
+        <v>677.7518600207422</v>
       </c>
       <c r="D153" t="n">
-        <v>666.7120915784461</v>
+        <v>669.1298460769134</v>
       </c>
       <c r="E153" t="n">
-        <v>668.220703125</v>
+        <v>674.09521484375</v>
       </c>
       <c r="F153" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B154" t="n">
-        <v>673.7355628200382</v>
+        <v>663.0854475032797</v>
       </c>
       <c r="C154" t="n">
-        <v>677.7518600207422</v>
+        <v>668.9400066983026</v>
       </c>
       <c r="D154" t="n">
-        <v>669.1298460769134</v>
+        <v>652.4452846667049</v>
       </c>
       <c r="E154" t="n">
-        <v>674.09521484375</v>
+        <v>658.5396728515625</v>
       </c>
       <c r="F154" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B155" t="n">
-        <v>663.0854475032797</v>
+        <v>659.7085674039201</v>
       </c>
       <c r="C155" t="n">
-        <v>668.9400066983026</v>
+        <v>680.0396994180859</v>
       </c>
       <c r="D155" t="n">
-        <v>652.4452846667049</v>
+        <v>653.2345872360809</v>
       </c>
       <c r="E155" t="n">
-        <v>658.5396728515625</v>
+        <v>674.4049682617188</v>
       </c>
       <c r="F155" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="n">
-        <v>659.7085674039201</v>
+        <v>670.3786986745525</v>
       </c>
       <c r="C156" t="n">
-        <v>680.0396994180859</v>
+        <v>681.8680504402118</v>
       </c>
       <c r="D156" t="n">
-        <v>653.2345872360809</v>
+        <v>670.2188736545023</v>
       </c>
       <c r="E156" t="n">
-        <v>674.4049682617188</v>
+        <v>677.9916381835938</v>
       </c>
       <c r="F156" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B157" t="n">
-        <v>670.3786986745525</v>
+        <v>673.6156618787633</v>
       </c>
       <c r="C157" t="n">
-        <v>681.8680504402118</v>
+        <v>677.5520159823654</v>
       </c>
       <c r="D157" t="n">
-        <v>670.2188736545023</v>
+        <v>665.0136491453696</v>
       </c>
       <c r="E157" t="n">
-        <v>677.9916381835938</v>
+        <v>670.7183837890625</v>
       </c>
       <c r="F157" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B158" t="n">
-        <v>673.6156618787633</v>
+        <v>668.2905997420939</v>
       </c>
       <c r="C158" t="n">
-        <v>677.5520159823654</v>
+        <v>673.6256820299297</v>
       </c>
       <c r="D158" t="n">
-        <v>665.0136491453696</v>
+        <v>663.1953464496755</v>
       </c>
       <c r="E158" t="n">
-        <v>670.7183837890625</v>
+        <v>668.5004272460938</v>
       </c>
       <c r="F158" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B159" t="n">
-        <v>668.2905997420939</v>
+        <v>618.7465567527638</v>
       </c>
       <c r="C159" t="n">
-        <v>673.6256820299297</v>
+        <v>620.2751083620838</v>
       </c>
       <c r="D159" t="n">
-        <v>663.1953464496755</v>
+        <v>599.4444385151393</v>
       </c>
       <c r="E159" t="n">
-        <v>668.5004272460938</v>
+        <v>611.3433837890625</v>
       </c>
       <c r="F159" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B160" t="n">
-        <v>618.7465567527638</v>
+        <v>614.120842749119</v>
       </c>
       <c r="C160" t="n">
-        <v>620.2751083620838</v>
+        <v>618.3069655430758</v>
       </c>
       <c r="D160" t="n">
-        <v>599.4444385151393</v>
+        <v>605.5487701514051</v>
       </c>
       <c r="E160" t="n">
-        <v>611.3433837890625</v>
+        <v>608.1863403320312</v>
       </c>
       <c r="F160" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B161" t="n">
-        <v>614.120842749119</v>
+        <v>607.3771038685389</v>
       </c>
       <c r="C161" t="n">
-        <v>618.3069655430758</v>
+        <v>613.4314904063681</v>
       </c>
       <c r="D161" t="n">
-        <v>605.5487701514051</v>
+        <v>602.1919069095087</v>
       </c>
       <c r="E161" t="n">
-        <v>608.1863403320312</v>
+        <v>609.8447875976562</v>
       </c>
       <c r="F161" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B162" t="n">
-        <v>607.3771038685389</v>
+        <v>612.7420849871345</v>
       </c>
       <c r="C162" t="n">
-        <v>613.4314904063681</v>
+        <v>613.7811000159977</v>
       </c>
       <c r="D162" t="n">
-        <v>602.1919069095087</v>
+        <v>599.8040642277598</v>
       </c>
       <c r="E162" t="n">
-        <v>609.8447875976562</v>
+        <v>604.3998413085938</v>
       </c>
       <c r="F162" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="n">
-        <v>612.7420849871345</v>
+        <v>600.4934370812971</v>
       </c>
       <c r="C163" t="n">
-        <v>613.7811000159977</v>
+        <v>619.3759607512419</v>
       </c>
       <c r="D163" t="n">
-        <v>599.8040642277598</v>
+        <v>597.5461564796674</v>
       </c>
       <c r="E163" t="n">
-        <v>604.3998413085938</v>
+        <v>612.3125</v>
       </c>
       <c r="F163" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B164" t="n">
-        <v>600.4934370812971</v>
+        <v>614.150739078972</v>
       </c>
       <c r="C164" t="n">
-        <v>619.3759607512419</v>
+        <v>624.4012480600104</v>
       </c>
       <c r="D164" t="n">
-        <v>597.5461564796674</v>
+        <v>612.9718390781961</v>
       </c>
       <c r="E164" t="n">
-        <v>612.3125</v>
+        <v>616.2388305664062</v>
       </c>
       <c r="F164" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B165" t="n">
-        <v>614.150739078972</v>
+        <v>614.6303402495529</v>
       </c>
       <c r="C165" t="n">
-        <v>624.4012480600104</v>
+        <v>616.1988937552933</v>
       </c>
       <c r="D165" t="n">
-        <v>612.9718390781961</v>
+        <v>605.4987892063378</v>
       </c>
       <c r="E165" t="n">
-        <v>616.2388305664062</v>
+        <v>609.0654907226562</v>
       </c>
       <c r="F165" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B166" t="n">
-        <v>614.6303402495529</v>
+        <v>604.010215830275</v>
       </c>
       <c r="C166" t="n">
-        <v>616.1988937552933</v>
+        <v>604.3498668649182</v>
       </c>
       <c r="D166" t="n">
-        <v>605.4987892063378</v>
+        <v>597.5262348938886</v>
       </c>
       <c r="E166" t="n">
-        <v>609.0654907226562</v>
+        <v>598.3054809570312</v>
       </c>
       <c r="F166" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B167" t="n">
-        <v>604.010215830275</v>
+        <v>594.2692320029287</v>
       </c>
       <c r="C167" t="n">
-        <v>604.3498668649182</v>
+        <v>603.1909559259367</v>
       </c>
       <c r="D167" t="n">
-        <v>597.5262348938886</v>
+        <v>592.0512559095129</v>
       </c>
       <c r="E167" t="n">
-        <v>598.3054809570312</v>
+        <v>602.441650390625</v>
       </c>
       <c r="F167" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B168" t="n">
-        <v>594.2692320029287</v>
+        <v>598.275515544453</v>
       </c>
       <c r="C168" t="n">
-        <v>603.1909559259367</v>
+        <v>619.3260125714435</v>
       </c>
       <c r="D168" t="n">
-        <v>592.0512559095129</v>
+        <v>596.1074810052941</v>
       </c>
       <c r="E168" t="n">
-        <v>602.441650390625</v>
+        <v>616.0590209960938</v>
       </c>
       <c r="F168" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B169" t="n">
-        <v>598.275515544453</v>
+        <v>615.4296182023591</v>
       </c>
       <c r="C169" t="n">
-        <v>619.3260125714435</v>
+        <v>623.152441138389</v>
       </c>
       <c r="D169" t="n">
-        <v>596.1074810052941</v>
+        <v>614.4305441468357</v>
       </c>
       <c r="E169" t="n">
-        <v>616.0590209960938</v>
+        <v>617.8573608398438</v>
       </c>
       <c r="F169" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B170" t="n">
-        <v>615.4296182023591</v>
+        <v>613.421486859321</v>
       </c>
       <c r="C170" t="n">
-        <v>623.152441138389</v>
+        <v>620.6248329546977</v>
       </c>
       <c r="D170" t="n">
-        <v>614.4305441468357</v>
+        <v>608.7458274653094</v>
       </c>
       <c r="E170" t="n">
-        <v>617.8573608398438</v>
+        <v>613.6612548828125</v>
       </c>
       <c r="F170" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B171" t="n">
-        <v>613.421486859321</v>
+        <v>608.5459509764945</v>
       </c>
       <c r="C171" t="n">
-        <v>620.6248329546977</v>
+        <v>615.0199919776213</v>
       </c>
       <c r="D171" t="n">
-        <v>608.7458274653094</v>
+        <v>603.1309869574205</v>
       </c>
       <c r="E171" t="n">
-        <v>613.6612548828125</v>
+        <v>610.64404296875</v>
       </c>
       <c r="F171" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B172" t="n">
-        <v>608.5459509764945</v>
+        <v>608.3561568042173</v>
       </c>
       <c r="C172" t="n">
-        <v>615.0199919776213</v>
+        <v>613.361527578881</v>
       </c>
       <c r="D172" t="n">
-        <v>603.1309869574205</v>
+        <v>599.9939118379299</v>
       </c>
       <c r="E172" t="n">
-        <v>610.64404296875</v>
+        <v>602.052001953125</v>
       </c>
       <c r="F172" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B173" t="n">
-        <v>608.3561568042173</v>
+        <v>600.2037495434126</v>
       </c>
       <c r="C173" t="n">
-        <v>613.361527578881</v>
+        <v>607.4370360716302</v>
       </c>
       <c r="D173" t="n">
-        <v>599.9939118379299</v>
+        <v>597.2564688338498</v>
       </c>
       <c r="E173" t="n">
-        <v>602.052001953125</v>
+        <v>604.499755859375</v>
       </c>
       <c r="F173" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B174" t="n">
-        <v>600.2037495434126</v>
+        <v>599.4443949814065</v>
       </c>
       <c r="C174" t="n">
-        <v>607.4370360716302</v>
+        <v>609.0354809096541</v>
       </c>
       <c r="D174" t="n">
-        <v>597.2564688338498</v>
+        <v>594.2591985256718</v>
       </c>
       <c r="E174" t="n">
-        <v>604.499755859375</v>
+        <v>606.8175659179688</v>
       </c>
       <c r="F174" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B175" t="n">
-        <v>599.4443949814065</v>
+        <v>607.3171451453314</v>
       </c>
       <c r="C175" t="n">
-        <v>609.0354809096541</v>
+        <v>614.2407210713809</v>
       </c>
       <c r="D175" t="n">
-        <v>594.2591985256718</v>
+        <v>606.3880135859368</v>
       </c>
       <c r="E175" t="n">
-        <v>606.8175659179688</v>
+        <v>609.6949462890625</v>
       </c>
       <c r="F175" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B176" t="n">
-        <v>607.3171451453314</v>
+        <v>608.3261927003538</v>
       </c>
       <c r="C176" t="n">
-        <v>614.2407210713809</v>
+        <v>613.9009818092591</v>
       </c>
       <c r="D176" t="n">
-        <v>606.3880135859368</v>
+        <v>604.7394901495815</v>
       </c>
       <c r="E176" t="n">
-        <v>609.6949462890625</v>
+        <v>611.7730102539062</v>
       </c>
       <c r="F176" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B177" t="n">
-        <v>608.3261927003538</v>
+        <v>608.8357727220844</v>
       </c>
       <c r="C177" t="n">
-        <v>613.9009818092591</v>
+        <v>637.908804248614</v>
       </c>
       <c r="D177" t="n">
-        <v>604.7394901495815</v>
+        <v>608.4361186960156</v>
       </c>
       <c r="E177" t="n">
-        <v>611.7730102539062</v>
+        <v>634.6718139648438</v>
       </c>
       <c r="F177" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B178" t="n">
-        <v>608.8357727220844</v>
+        <v>638.9078448274123</v>
       </c>
       <c r="C178" t="n">
-        <v>637.908804248614</v>
+        <v>642.4046039468743</v>
       </c>
       <c r="D178" t="n">
-        <v>608.4361186960156</v>
+        <v>628.7272779804616</v>
       </c>
       <c r="E178" t="n">
-        <v>634.6718139648438</v>
+        <v>634.7017211914062</v>
       </c>
       <c r="F178" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B179" t="n">
-        <v>638.9078448274123</v>
+        <v>632.9133899267435</v>
       </c>
       <c r="C179" t="n">
-        <v>642.4046039468743</v>
+        <v>633.9124639439917</v>
       </c>
       <c r="D179" t="n">
-        <v>628.7272779804616</v>
+        <v>622.7727642602187</v>
       </c>
       <c r="E179" t="n">
-        <v>634.7017211914062</v>
+        <v>631.92431640625</v>
       </c>
       <c r="F179" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B180" t="n">
-        <v>632.9133899267435</v>
+        <v>629.8162791560948</v>
       </c>
       <c r="C180" t="n">
-        <v>633.9124639439917</v>
+        <v>635.1613007084701</v>
       </c>
       <c r="D180" t="n">
-        <v>622.7727642602187</v>
+        <v>598.9748694014791</v>
       </c>
       <c r="E180" t="n">
-        <v>631.92431640625</v>
+        <v>599.9139404296875</v>
       </c>
       <c r="F180" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B181" t="n">
-        <v>629.8162791560948</v>
+        <v>602.6813896226799</v>
       </c>
       <c r="C181" t="n">
-        <v>635.1613007084701</v>
+        <v>608.3161816139932</v>
       </c>
       <c r="D181" t="n">
-        <v>598.9748694014791</v>
+        <v>596.1274666259658</v>
       </c>
       <c r="E181" t="n">
-        <v>599.9139404296875</v>
+        <v>597.0765991210938</v>
       </c>
       <c r="F181" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B182" t="n">
-        <v>602.6813896226799</v>
+        <v>602.4416570391962</v>
       </c>
       <c r="C182" t="n">
-        <v>608.3161816139932</v>
+        <v>623.5720977596394</v>
       </c>
       <c r="D182" t="n">
-        <v>596.1274666259658</v>
+        <v>599.7142043737263</v>
       </c>
       <c r="E182" t="n">
-        <v>597.0765991210938</v>
+        <v>622.4031372070312</v>
       </c>
       <c r="F182" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B183" t="n">
-        <v>602.4416570391962</v>
+        <v>623.0924785224576</v>
       </c>
       <c r="C183" t="n">
-        <v>623.5720977596394</v>
+        <v>641.8051764288737</v>
       </c>
       <c r="D183" t="n">
-        <v>599.7142043737263</v>
+        <v>621.8536364911718</v>
       </c>
       <c r="E183" t="n">
-        <v>622.4031372070312</v>
+        <v>626.9888916015625</v>
       </c>
       <c r="F183" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B184" t="n">
-        <v>623.0924785224576</v>
+        <v>622.8827460758752</v>
       </c>
       <c r="C184" t="n">
-        <v>641.8051764288737</v>
+        <v>628.5674800138549</v>
       </c>
       <c r="D184" t="n">
-        <v>621.8536364911718</v>
+        <v>582.3702434655938</v>
       </c>
       <c r="E184" t="n">
-        <v>626.9888916015625</v>
+        <v>592.450927734375</v>
       </c>
       <c r="F184" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B185" t="n">
-        <v>622.8827460758752</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="C185" t="n">
-        <v>628.5674800138549</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="D185" t="n">
-        <v>582.3702434655938</v>
+        <v>578.6836307521693</v>
       </c>
       <c r="E185" t="n">
-        <v>592.450927734375</v>
+        <v>584.8479614257812</v>
       </c>
       <c r="F185" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B186" t="n">
-        <v>591.4518261333767</v>
+        <v>590.4527436689563</v>
       </c>
       <c r="C186" t="n">
-        <v>591.4518261333767</v>
+        <v>597.0766092757164</v>
       </c>
       <c r="D186" t="n">
-        <v>578.6836307521693</v>
+        <v>580.4720040020986</v>
       </c>
       <c r="E186" t="n">
-        <v>584.8479614257812</v>
+        <v>584.0487060546875</v>
       </c>
       <c r="F186" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B187" t="n">
-        <v>590.4527436689563</v>
+        <v>580.192266144374</v>
       </c>
       <c r="C187" t="n">
-        <v>597.0766092757164</v>
+        <v>590.7724873942649</v>
       </c>
       <c r="D187" t="n">
-        <v>580.4720040020986</v>
+        <v>570.0716409197756</v>
       </c>
       <c r="E187" t="n">
-        <v>584.0487060546875</v>
+        <v>570.4512939453125</v>
       </c>
       <c r="F187" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B188" t="n">
-        <v>580.192266144374</v>
+        <v>565.3060574843756</v>
       </c>
       <c r="C188" t="n">
-        <v>590.7724873942649</v>
+        <v>571.6401524850257</v>
       </c>
       <c r="D188" t="n">
-        <v>570.0716409197756</v>
+        <v>556.4942175026772</v>
       </c>
       <c r="E188" t="n">
-        <v>570.4512939453125</v>
+        <v>567.9036254882812</v>
       </c>
       <c r="F188" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B189" t="n">
-        <v>565.3060574843756</v>
+        <v>572.4194595335534</v>
       </c>
       <c r="C189" t="n">
-        <v>571.6401524850257</v>
+        <v>575.5365655300229</v>
       </c>
       <c r="D189" t="n">
-        <v>556.4942175026772</v>
+        <v>560.3806300495169</v>
       </c>
       <c r="E189" t="n">
-        <v>567.9036254882812</v>
+        <v>566.4549560546875</v>
       </c>
       <c r="F189" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,25 +5357,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B190" t="n">
-        <v>572.4194595335534</v>
+        <v>579.9000244140625</v>
       </c>
       <c r="C190" t="n">
-        <v>575.5365655300229</v>
+        <v>601.27001953125</v>
       </c>
       <c r="D190" t="n">
-        <v>560.3806300495169</v>
+        <v>579.2999877929688</v>
       </c>
       <c r="E190" t="n">
-        <v>566.4549560546875</v>
+        <v>593.47998046875</v>
       </c>
       <c r="F190" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5383,25 +5383,25 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B191" t="n">
-        <v>579.9000244140625</v>
+        <v>593.6500244140625</v>
       </c>
       <c r="C191" t="n">
-        <v>601.27001953125</v>
+        <v>605.8099975585938</v>
       </c>
       <c r="D191" t="n">
-        <v>579.2999877929688</v>
+        <v>592</v>
       </c>
       <c r="E191" t="n">
-        <v>593.47998046875</v>
+        <v>600.2100219726562</v>
       </c>
       <c r="F191" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G191" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B192" t="n">
-        <v>593.6500244140625</v>
+        <v>592</v>
       </c>
       <c r="C192" t="n">
-        <v>605.8099975585938</v>
+        <v>593.8099975585938</v>
       </c>
       <c r="D192" t="n">
-        <v>592</v>
+        <v>566.1900024414062</v>
       </c>
       <c r="E192" t="n">
-        <v>600.2100219726562</v>
+        <v>567.5800170898438</v>
       </c>
       <c r="F192" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B193" t="n">
-        <v>592</v>
+        <v>572.8200073242188</v>
       </c>
       <c r="C193" t="n">
-        <v>593.8099975585938</v>
+        <v>580.219970703125</v>
       </c>
       <c r="D193" t="n">
-        <v>566.1900024414062</v>
+        <v>563.0999755859375</v>
       </c>
       <c r="E193" t="n">
-        <v>567.5800170898438</v>
+        <v>577.219970703125</v>
       </c>
       <c r="F193" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B194" t="n">
-        <v>572.8200073242188</v>
+        <v>572.02001953125</v>
       </c>
       <c r="C194" t="n">
-        <v>580.219970703125</v>
+        <v>575.8099975585938</v>
       </c>
       <c r="D194" t="n">
-        <v>563.0999755859375</v>
+        <v>559.8099975585938</v>
       </c>
       <c r="E194" t="n">
-        <v>577.219970703125</v>
+        <v>563.8499755859375</v>
       </c>
       <c r="F194" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B195" t="n">
-        <v>572.02001953125</v>
+        <v>562.25</v>
       </c>
       <c r="C195" t="n">
-        <v>575.8099975585938</v>
+        <v>572.2000122070312</v>
       </c>
       <c r="D195" t="n">
-        <v>559.8099975585938</v>
+        <v>561.02001953125</v>
       </c>
       <c r="E195" t="n">
-        <v>563.8499755859375</v>
+        <v>562.2000122070312</v>
       </c>
       <c r="F195" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B196" t="n">
-        <v>562.25</v>
+        <v>561.8900146484375</v>
       </c>
       <c r="C196" t="n">
-        <v>572.2000122070312</v>
+        <v>569.0399780273438</v>
       </c>
       <c r="D196" t="n">
-        <v>561.02001953125</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="E196" t="n">
-        <v>562.2000122070312</v>
+        <v>557.6699829101562</v>
       </c>
       <c r="F196" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B197" t="n">
-        <v>561.8900146484375</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="C197" t="n">
-        <v>569.0399780273438</v>
+        <v>556.3400268554688</v>
       </c>
       <c r="D197" t="n">
-        <v>555.5499877929688</v>
+        <v>540.1799926757812</v>
       </c>
       <c r="E197" t="n">
-        <v>557.6699829101562</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="F197" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B198" t="n">
-        <v>555.5499877929688</v>
+        <v>543.3400268554688</v>
       </c>
       <c r="C198" t="n">
-        <v>556.3400268554688</v>
+        <v>556.8499755859375</v>
       </c>
       <c r="D198" t="n">
-        <v>540.1799926757812</v>
+        <v>540.4000244140625</v>
       </c>
       <c r="E198" t="n">
-        <v>542.8699951171875</v>
+        <v>550.25</v>
       </c>
       <c r="F198" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B199" t="n">
-        <v>543.3400268554688</v>
+        <v>560</v>
       </c>
       <c r="C199" t="n">
-        <v>556.8499755859375</v>
+        <v>570.9000244140625</v>
       </c>
       <c r="D199" t="n">
-        <v>540.4000244140625</v>
+        <v>558</v>
       </c>
       <c r="E199" t="n">
-        <v>550.25</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="F199" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B200" t="n">
-        <v>560</v>
+        <v>560.9400024414062</v>
       </c>
       <c r="C200" t="n">
-        <v>570.9000244140625</v>
+        <v>565.5399780273438</v>
       </c>
       <c r="D200" t="n">
-        <v>558</v>
+        <v>551.4299926757812</v>
       </c>
       <c r="E200" t="n">
-        <v>562.5999755859375</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F200" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B201" t="n">
-        <v>560.9400024414062</v>
+        <v>607.9099731445312</v>
       </c>
       <c r="C201" t="n">
-        <v>565.5399780273438</v>
+        <v>628.280029296875</v>
       </c>
       <c r="D201" t="n">
-        <v>551.4299926757812</v>
+        <v>595.0999755859375</v>
       </c>
       <c r="E201" t="n">
-        <v>563.2899780273438</v>
+        <v>612.9099731445312</v>
       </c>
       <c r="F201" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B202" t="n">
-        <v>607.9099731445312</v>
+        <v>607.9000244140625</v>
       </c>
       <c r="C202" t="n">
-        <v>628.280029296875</v>
+        <v>610</v>
       </c>
       <c r="D202" t="n">
-        <v>595.0999755859375</v>
+        <v>580.4199829101562</v>
       </c>
       <c r="E202" t="n">
-        <v>612.9099731445312</v>
+        <v>582.9000244140625</v>
       </c>
       <c r="F202" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B203" t="n">
-        <v>607.9000244140625</v>
+        <v>594.8400268554688</v>
       </c>
       <c r="C203" t="n">
-        <v>610</v>
+        <v>603.5800170898438</v>
       </c>
       <c r="D203" t="n">
-        <v>580.4199829101562</v>
+        <v>581.760009765625</v>
       </c>
       <c r="E203" t="n">
-        <v>582.9000244140625</v>
+        <v>600.2899780273438</v>
       </c>
       <c r="F203" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B204" t="n">
-        <v>594.8400268554688</v>
+        <v>607.5900268554688</v>
       </c>
       <c r="C204" t="n">
-        <v>603.5800170898438</v>
+        <v>625.3699951171875</v>
       </c>
       <c r="D204" t="n">
-        <v>581.760009765625</v>
+        <v>603.6599731445312</v>
       </c>
       <c r="E204" t="n">
-        <v>600.2899780273438</v>
+        <v>615.5800170898438</v>
       </c>
       <c r="F204" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B205" t="n">
-        <v>607.5900268554688</v>
+        <v>614.3900146484375</v>
       </c>
       <c r="C205" t="n">
-        <v>625.3699951171875</v>
+        <v>616</v>
       </c>
       <c r="D205" t="n">
-        <v>603.6599731445312</v>
+        <v>598.010009765625</v>
       </c>
       <c r="E205" t="n">
-        <v>615.5800170898438</v>
+        <v>603.1199951171875</v>
       </c>
       <c r="F205" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B206" t="n">
-        <v>614.3900146484375</v>
+        <v>583.989990234375</v>
       </c>
       <c r="C206" t="n">
-        <v>616</v>
+        <v>633.27001953125</v>
       </c>
       <c r="D206" t="n">
-        <v>598.010009765625</v>
+        <v>577.0700073242188</v>
       </c>
       <c r="E206" t="n">
-        <v>603.1199951171875</v>
+        <v>631.47998046875</v>
       </c>
       <c r="F206" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B207" t="n">
-        <v>583.989990234375</v>
+        <v>660.3400268554688</v>
       </c>
       <c r="C207" t="n">
-        <v>633.27001953125</v>
+        <v>677.8599853515625</v>
       </c>
       <c r="D207" t="n">
-        <v>577.0700073242188</v>
+        <v>658.010009765625</v>
       </c>
       <c r="E207" t="n">
-        <v>631.47998046875</v>
+        <v>669.2100219726562</v>
       </c>
       <c r="F207" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B208" t="n">
-        <v>660.3400268554688</v>
+        <v>661.3800048828125</v>
       </c>
       <c r="C208" t="n">
-        <v>677.8599853515625</v>
+        <v>676.6199951171875</v>
       </c>
       <c r="D208" t="n">
-        <v>658.010009765625</v>
+        <v>654.2000122070312</v>
       </c>
       <c r="E208" t="n">
-        <v>669.2100219726562</v>
+        <v>656.72998046875</v>
       </c>
       <c r="F208" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>661.3800048828125</v>
+        <v>652</v>
       </c>
       <c r="C209" t="n">
-        <v>676.6199951171875</v>
+        <v>666.5</v>
       </c>
       <c r="D209" t="n">
-        <v>654.2000122070312</v>
+        <v>649.0499877929688</v>
       </c>
       <c r="E209" t="n">
-        <v>656.72998046875</v>
+        <v>661.0399780273438</v>
       </c>
       <c r="F209" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>652</v>
+        <v>663.5999755859375</v>
       </c>
       <c r="C210" t="n">
-        <v>666.5</v>
+        <v>686.0800170898438</v>
       </c>
       <c r="D210" t="n">
-        <v>649.0499877929688</v>
+        <v>656.6599731445312</v>
       </c>
       <c r="E210" t="n">
-        <v>661.0399780273438</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="F210" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>663.5999755859375</v>
+        <v>677.280029296875</v>
       </c>
       <c r="C211" t="n">
-        <v>686.0800170898438</v>
+        <v>681.9000244140625</v>
       </c>
       <c r="D211" t="n">
-        <v>656.6599731445312</v>
+        <v>660.1599731445312</v>
       </c>
       <c r="E211" t="n">
-        <v>681.3099975585938</v>
+        <v>664.5399780273438</v>
       </c>
       <c r="F211" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B212" t="n">
-        <v>677.280029296875</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C212" t="n">
-        <v>681.9000244140625</v>
+        <v>652.2000122070312</v>
       </c>
       <c r="D212" t="n">
-        <v>660.1599731445312</v>
+        <v>626</v>
       </c>
       <c r="E212" t="n">
-        <v>664.5399780273438</v>
+        <v>646.010009765625</v>
       </c>
       <c r="F212" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B213" t="n">
-        <v>647.7000122070312</v>
+        <v>646.7000122070312</v>
       </c>
       <c r="C213" t="n">
-        <v>652.2000122070312</v>
+        <v>653.2999877929688</v>
       </c>
       <c r="D213" t="n">
-        <v>626</v>
+        <v>636.010009765625</v>
       </c>
       <c r="E213" t="n">
-        <v>646.010009765625</v>
+        <v>645.8499755859375</v>
       </c>
       <c r="F213" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B214" t="n">
-        <v>646.7000122070312</v>
+        <v>654.1799926757812</v>
       </c>
       <c r="C214" t="n">
-        <v>653.2999877929688</v>
+        <v>655.8800048828125</v>
       </c>
       <c r="D214" t="n">
-        <v>636.010009765625</v>
+        <v>643.2000122070312</v>
       </c>
       <c r="E214" t="n">
-        <v>645.8499755859375</v>
+        <v>643.8099975585938</v>
       </c>
       <c r="F214" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B215" t="n">
-        <v>654.1799926757812</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C215" t="n">
-        <v>655.8800048828125</v>
+        <v>649</v>
       </c>
       <c r="D215" t="n">
-        <v>643.2000122070312</v>
+        <v>624</v>
       </c>
       <c r="E215" t="n">
-        <v>643.8099975585938</v>
+        <v>627.1699829101562</v>
       </c>
       <c r="F215" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B216" t="n">
-        <v>647.7000122070312</v>
+        <v>608.4099731445312</v>
       </c>
       <c r="C216" t="n">
-        <v>649</v>
+        <v>614.6500244140625</v>
       </c>
       <c r="D216" t="n">
-        <v>624</v>
+        <v>597.219970703125</v>
       </c>
       <c r="E216" t="n">
-        <v>627.1699829101562</v>
+        <v>606.0999755859375</v>
       </c>
       <c r="F216" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B217" t="n">
-        <v>608.4099731445312</v>
+        <v>605.2999877929688</v>
       </c>
       <c r="C217" t="n">
-        <v>614.6500244140625</v>
+        <v>609.97998046875</v>
       </c>
       <c r="D217" t="n">
-        <v>597.219970703125</v>
+        <v>594.4500122070312</v>
       </c>
       <c r="E217" t="n">
-        <v>606.0999755859375</v>
+        <v>595.1900024414062</v>
       </c>
       <c r="F217" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B218" t="n">
-        <v>605.2999877929688</v>
+        <v>607.219970703125</v>
       </c>
       <c r="C218" t="n">
-        <v>609.97998046875</v>
+        <v>611.260009765625</v>
       </c>
       <c r="D218" t="n">
-        <v>594.4500122070312</v>
+        <v>593.1300048828125</v>
       </c>
       <c r="E218" t="n">
-        <v>595.1900024414062</v>
+        <v>593.8699951171875</v>
       </c>
       <c r="F218" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B219" t="n">
-        <v>607.219970703125</v>
+        <v>596.8200073242188</v>
       </c>
       <c r="C219" t="n">
-        <v>611.260009765625</v>
+        <v>601</v>
       </c>
       <c r="D219" t="n">
-        <v>593.1300048828125</v>
+        <v>587</v>
       </c>
       <c r="E219" t="n">
-        <v>593.8699951171875</v>
+        <v>593.4099731445312</v>
       </c>
       <c r="F219" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B220" t="n">
-        <v>596.8200073242188</v>
+        <v>593.25</v>
       </c>
       <c r="C220" t="n">
-        <v>601</v>
+        <v>599.969970703125</v>
       </c>
       <c r="D220" t="n">
-        <v>587</v>
+        <v>582.219970703125</v>
       </c>
       <c r="E220" t="n">
-        <v>593.4099731445312</v>
+        <v>585.6099853515625</v>
       </c>
       <c r="F220" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B221" t="n">
-        <v>593.25</v>
+        <v>526</v>
       </c>
       <c r="C221" t="n">
-        <v>599.969970703125</v>
+        <v>539.8800048828125</v>
       </c>
       <c r="D221" t="n">
-        <v>582.219970703125</v>
+        <v>524.489990234375</v>
       </c>
       <c r="E221" t="n">
-        <v>585.6099853515625</v>
+        <v>539.030029296875</v>
       </c>
       <c r="F221" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B222" t="n">
-        <v>526</v>
+        <v>543.5999755859375</v>
       </c>
       <c r="C222" t="n">
-        <v>539.8800048828125</v>
+        <v>558.3300170898438</v>
       </c>
       <c r="D222" t="n">
-        <v>524.489990234375</v>
+        <v>540.219970703125</v>
       </c>
       <c r="E222" t="n">
-        <v>539.030029296875</v>
+        <v>556.7100219726562</v>
       </c>
       <c r="F222" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B223" t="n">
-        <v>543.5999755859375</v>
+        <v>562.239990234375</v>
       </c>
       <c r="C223" t="n">
-        <v>558.3300170898438</v>
+        <v>597.52001953125</v>
       </c>
       <c r="D223" t="n">
-        <v>540.219970703125</v>
+        <v>559.3599853515625</v>
       </c>
       <c r="E223" t="n">
-        <v>556.7100219726562</v>
+        <v>590.239990234375</v>
       </c>
       <c r="F223" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B224" t="n">
-        <v>562.239990234375</v>
+        <v>581.5</v>
       </c>
       <c r="C224" t="n">
-        <v>597.52001953125</v>
+        <v>592.7899780273438</v>
       </c>
       <c r="D224" t="n">
-        <v>559.3599853515625</v>
+        <v>578.25</v>
       </c>
       <c r="E224" t="n">
-        <v>590.239990234375</v>
+        <v>587.9400024414062</v>
       </c>
       <c r="F224" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B225" t="n">
-        <v>581.5</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="C225" t="n">
-        <v>592.7899780273438</v>
+        <v>601</v>
       </c>
       <c r="D225" t="n">
-        <v>578.25</v>
+        <v>580.1199951171875</v>
       </c>
       <c r="E225" t="n">
-        <v>587.9400024414062</v>
+        <v>588.77001953125</v>
       </c>
       <c r="F225" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B226" t="n">
-        <v>600.4600219726562</v>
+        <v>586.9500122070312</v>
       </c>
       <c r="C226" t="n">
-        <v>601</v>
+        <v>595.3099975585938</v>
       </c>
       <c r="D226" t="n">
-        <v>580.1199951171875</v>
+        <v>586</v>
       </c>
       <c r="E226" t="n">
-        <v>588.77001953125</v>
+        <v>589.9000244140625</v>
       </c>
       <c r="F226" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B227" t="n">
-        <v>586.9500122070312</v>
+        <v>585.6400146484375</v>
       </c>
       <c r="C227" t="n">
-        <v>595.3099975585938</v>
+        <v>598.739990234375</v>
       </c>
       <c r="D227" t="n">
-        <v>586</v>
+        <v>585.6199951171875</v>
       </c>
       <c r="E227" t="n">
-        <v>589.9000244140625</v>
+        <v>592.0999755859375</v>
       </c>
       <c r="F227" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B228" t="n">
-        <v>585.6400146484375</v>
+        <v>599.1300048828125</v>
       </c>
       <c r="C228" t="n">
-        <v>598.739990234375</v>
+        <v>608.2100219726562</v>
       </c>
       <c r="D228" t="n">
-        <v>585.6199951171875</v>
+        <v>592.030029296875</v>
       </c>
       <c r="E228" t="n">
-        <v>592.0999755859375</v>
+        <v>594.9199829101562</v>
       </c>
       <c r="F228" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B229" t="n">
-        <v>599.1300048828125</v>
+        <v>598</v>
       </c>
       <c r="C229" t="n">
-        <v>608.2100219726562</v>
+        <v>612.4299926757812</v>
       </c>
       <c r="D229" t="n">
-        <v>592.030029296875</v>
+        <v>593.4000244140625</v>
       </c>
       <c r="E229" t="n">
-        <v>594.9199829101562</v>
+        <v>599.1199951171875</v>
       </c>
       <c r="F229" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B230" t="n">
-        <v>598</v>
+        <v>601.0700073242188</v>
       </c>
       <c r="C230" t="n">
-        <v>612.4299926757812</v>
+        <v>604.5</v>
       </c>
       <c r="D230" t="n">
-        <v>593.4000244140625</v>
+        <v>578.2100219726562</v>
       </c>
       <c r="E230" t="n">
-        <v>599.1199951171875</v>
+        <v>578.8499755859375</v>
       </c>
       <c r="F230" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B231" t="n">
-        <v>601.0700073242188</v>
+        <v>580.7100219726562</v>
       </c>
       <c r="C231" t="n">
-        <v>604.5</v>
+        <v>595.8499755859375</v>
       </c>
       <c r="D231" t="n">
-        <v>578.2100219726562</v>
+        <v>579.3900146484375</v>
       </c>
       <c r="E231" t="n">
-        <v>578.8499755859375</v>
+        <v>594.969970703125</v>
       </c>
       <c r="F231" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B232" t="n">
-        <v>580.7100219726562</v>
+        <v>596.97998046875</v>
       </c>
       <c r="C232" t="n">
-        <v>595.8499755859375</v>
+        <v>601.8599853515625</v>
       </c>
       <c r="D232" t="n">
-        <v>579.3900146484375</v>
+        <v>589.2899780273438</v>
       </c>
       <c r="E232" t="n">
-        <v>594.969970703125</v>
+        <v>589.8499755859375</v>
       </c>
       <c r="F232" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B233" t="n">
-        <v>596.97998046875</v>
+        <v>589.75</v>
       </c>
       <c r="C233" t="n">
-        <v>601.8599853515625</v>
+        <v>590.239990234375</v>
       </c>
       <c r="D233" t="n">
-        <v>589.2899780273438</v>
+        <v>564.75</v>
       </c>
       <c r="E233" t="n">
-        <v>589.8499755859375</v>
+        <v>568.969970703125</v>
       </c>
       <c r="F233" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B234" t="n">
-        <v>589.75</v>
+        <v>557.47998046875</v>
       </c>
       <c r="C234" t="n">
-        <v>590.239990234375</v>
+        <v>560.6599731445312</v>
       </c>
       <c r="D234" t="n">
-        <v>564.75</v>
+        <v>543.2100219726562</v>
       </c>
       <c r="E234" t="n">
-        <v>568.969970703125</v>
+        <v>543.6699829101562</v>
       </c>
       <c r="F234" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B235" t="n">
-        <v>557.47998046875</v>
+        <v>541.3400268554688</v>
       </c>
       <c r="C235" t="n">
-        <v>560.6599731445312</v>
+        <v>554.0700073242188</v>
       </c>
       <c r="D235" t="n">
-        <v>543.2100219726562</v>
+        <v>537.27001953125</v>
       </c>
       <c r="E235" t="n">
-        <v>543.6699829101562</v>
+        <v>546.030029296875</v>
       </c>
       <c r="F235" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B236" t="n">
-        <v>541.3400268554688</v>
+        <v>546.9500122070312</v>
       </c>
       <c r="C236" t="n">
-        <v>554.0700073242188</v>
+        <v>549.989990234375</v>
       </c>
       <c r="D236" t="n">
-        <v>537.27001953125</v>
+        <v>539.3099975585938</v>
       </c>
       <c r="E236" t="n">
-        <v>546.030029296875</v>
+        <v>545.8300170898438</v>
       </c>
       <c r="F236" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B237" t="n">
-        <v>546.9500122070312</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="C237" t="n">
-        <v>549.989990234375</v>
+        <v>553.8699951171875</v>
       </c>
       <c r="D237" t="n">
-        <v>539.3099975585938</v>
+        <v>543.22998046875</v>
       </c>
       <c r="E237" t="n">
-        <v>545.8300170898438</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="F237" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B238" t="n">
-        <v>546.8900146484375</v>
+        <v>550.2000122070312</v>
       </c>
       <c r="C238" t="n">
-        <v>553.8699951171875</v>
+        <v>561.4199829101562</v>
       </c>
       <c r="D238" t="n">
-        <v>543.22998046875</v>
+        <v>546.2999877929688</v>
       </c>
       <c r="E238" t="n">
-        <v>549.9000244140625</v>
+        <v>559.02001953125</v>
       </c>
       <c r="F238" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B239" t="n">
-        <v>550.2000122070312</v>
+        <v>563.8800048828125</v>
       </c>
       <c r="C239" t="n">
-        <v>561.4199829101562</v>
+        <v>570.7999877929688</v>
       </c>
       <c r="D239" t="n">
-        <v>546.2999877929688</v>
+        <v>561.4000244140625</v>
       </c>
       <c r="E239" t="n">
-        <v>559.02001953125</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="F239" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B240" t="n">
-        <v>563.8800048828125</v>
+        <v>590.3099975585938</v>
       </c>
       <c r="C240" t="n">
-        <v>570.7999877929688</v>
+        <v>593.3400268554688</v>
       </c>
       <c r="D240" t="n">
-        <v>561.4000244140625</v>
+        <v>561.8800048828125</v>
       </c>
       <c r="E240" t="n">
-        <v>570.0499877929688</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="F240" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B241" t="n">
-        <v>590.3099975585938</v>
+        <v>576.47998046875</v>
       </c>
       <c r="C241" t="n">
-        <v>593.3400268554688</v>
+        <v>588.3900146484375</v>
       </c>
       <c r="D241" t="n">
-        <v>561.8800048828125</v>
+        <v>567.6199951171875</v>
       </c>
       <c r="E241" t="n">
-        <v>576.1400146484375</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="F241" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B242" t="n">
-        <v>576.47998046875</v>
+        <v>571.5499877929688</v>
       </c>
       <c r="C242" t="n">
-        <v>588.3900146484375</v>
+        <v>589.1900024414062</v>
       </c>
       <c r="D242" t="n">
-        <v>567.6199951171875</v>
+        <v>571</v>
       </c>
       <c r="E242" t="n">
-        <v>571.0999755859375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="F242" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B243" t="n">
-        <v>571.5499877929688</v>
+        <v>577.6300048828125</v>
       </c>
       <c r="C243" t="n">
-        <v>589.1900024414062</v>
+        <v>578.6799926757812</v>
       </c>
       <c r="D243" t="n">
-        <v>571</v>
+        <v>569.1400146484375</v>
       </c>
       <c r="E243" t="n">
-        <v>578.02001953125</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="F243" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B244" t="n">
-        <v>577.6300048828125</v>
+        <v>558.3499755859375</v>
       </c>
       <c r="C244" t="n">
-        <v>578.6799926757812</v>
+        <v>584.9500122070312</v>
       </c>
       <c r="D244" t="n">
-        <v>569.1400146484375</v>
+        <v>556.0999755859375</v>
       </c>
       <c r="E244" t="n">
-        <v>572.3400268554688</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="F244" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B245" t="n">
-        <v>558.3499755859375</v>
+        <v>578.7899780273438</v>
       </c>
       <c r="C245" t="n">
-        <v>584.9500122070312</v>
+        <v>600.3800048828125</v>
       </c>
       <c r="D245" t="n">
-        <v>556.0999755859375</v>
+        <v>577</v>
       </c>
       <c r="E245" t="n">
-        <v>578.5399780273438</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="F245" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B246" t="n">
-        <v>578.7899780273438</v>
+        <v>604.489990234375</v>
       </c>
       <c r="C246" t="n">
-        <v>600.3800048828125</v>
+        <v>619.4600219726562</v>
       </c>
       <c r="D246" t="n">
-        <v>577</v>
+        <v>604.3499755859375</v>
       </c>
       <c r="E246" t="n">
-        <v>592.8499755859375</v>
+        <v>610.6799926757812</v>
       </c>
       <c r="F246" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B247" t="n">
-        <v>604.489990234375</v>
+        <v>612.3499755859375</v>
       </c>
       <c r="C247" t="n">
-        <v>619.4600219726562</v>
+        <v>617.4600219726562</v>
       </c>
       <c r="D247" t="n">
-        <v>604.3499755859375</v>
+        <v>605.27001953125</v>
       </c>
       <c r="E247" t="n">
-        <v>610.6799926757812</v>
+        <v>616.77001953125</v>
       </c>
       <c r="F247" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B248" t="n">
-        <v>612.3499755859375</v>
+        <v>616.2100219726562</v>
       </c>
       <c r="C248" t="n">
-        <v>617.4600219726562</v>
+        <v>624.7999877929688</v>
       </c>
       <c r="D248" t="n">
-        <v>605.27001953125</v>
+        <v>609.739990234375</v>
       </c>
       <c r="E248" t="n">
-        <v>616.77001953125</v>
+        <v>613.47998046875</v>
       </c>
       <c r="F248" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B249" t="n">
-        <v>616.2100219726562</v>
+        <v>648.6400146484375</v>
       </c>
       <c r="C249" t="n">
-        <v>624.7999877929688</v>
+        <v>657.8599853515625</v>
       </c>
       <c r="D249" t="n">
-        <v>609.739990234375</v>
+        <v>638.5599975585938</v>
       </c>
       <c r="E249" t="n">
-        <v>613.47998046875</v>
+        <v>653.6900024414062</v>
       </c>
       <c r="F249" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B250" t="n">
-        <v>648.6400146484375</v>
+        <v>653.7100219726562</v>
       </c>
       <c r="C250" t="n">
-        <v>657.8599853515625</v>
+        <v>663.5</v>
       </c>
       <c r="D250" t="n">
-        <v>638.5599975585938</v>
+        <v>642.1400146484375</v>
       </c>
       <c r="E250" t="n">
-        <v>653.6900024414062</v>
+        <v>644.3800048828125</v>
       </c>
       <c r="F250" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B251" t="n">
-        <v>653.7100219726562</v>
+        <v>653.510009765625</v>
       </c>
       <c r="C251" t="n">
-        <v>663.5</v>
+        <v>664.239990234375</v>
       </c>
       <c r="D251" t="n">
-        <v>642.1400146484375</v>
+        <v>646.2000122070312</v>
       </c>
       <c r="E251" t="n">
-        <v>644.3800048828125</v>
+        <v>648.030029296875</v>
       </c>
       <c r="F251" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B252" t="n">
-        <v>653.510009765625</v>
+        <v>657.8300170898438</v>
       </c>
       <c r="C252" t="n">
-        <v>664.239990234375</v>
+        <v>668.5999755859375</v>
       </c>
       <c r="D252" t="n">
-        <v>646.2000122070312</v>
+        <v>649.219970703125</v>
       </c>
       <c r="E252" t="n">
-        <v>648.030029296875</v>
+        <v>665.5999755859375</v>
       </c>
       <c r="F252" t="n">
-        <v>16908400</v>
+        <v>19300300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,34 +10776,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>665.6</v>
+      </c>
+      <c r="D2" t="n">
         <v>648.03</v>
       </c>
-      <c r="D2" t="n">
-        <v>644.38</v>
-      </c>
       <c r="E2" t="n">
-        <v>653.02</v>
+        <v>657.62</v>
       </c>
       <c r="F2" t="n">
-        <v>664.24</v>
+        <v>668.6</v>
       </c>
       <c r="G2" t="n">
-        <v>646.2</v>
+        <v>649.25</v>
       </c>
       <c r="H2" t="n">
-        <v>16862780</v>
+        <v>19270307</v>
       </c>
       <c r="I2" t="n">
-        <v>18264382</v>
+        <v>18281088</v>
       </c>
       <c r="J2" t="n">
-        <v>1650860490752</v>
+        <v>1695620005888</v>
       </c>
       <c r="K2" t="n">
-        <v>24.389538</v>
+        <v>25.050808</v>
       </c>
       <c r="L2" t="n">
-        <v>18.536509</v>
+        <v>19.039085</v>
       </c>
       <c r="M2" t="n">
         <v>26.57</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.321011</v>
+        <v>6.4923916</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1672918466560</v>
+        <v>1717678112768</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-12 21:47:00</t>
+          <t>2026-09-15 14:14:06</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B2" t="n">
-        <v>754.9954213012545</v>
+        <v>777.4419836717854</v>
       </c>
       <c r="C2" t="n">
-        <v>771.5412279036273</v>
+        <v>780.731191338524</v>
       </c>
       <c r="D2" t="n">
-        <v>749.5333431691193</v>
+        <v>763.8066796606671</v>
       </c>
       <c r="E2" t="n">
-        <v>762.2018432617188</v>
+        <v>773.1859130859375</v>
       </c>
       <c r="F2" t="n">
-        <v>10533800</v>
+        <v>9400900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B3" t="n">
-        <v>764.494341124313</v>
+        <v>778.1994163857863</v>
       </c>
       <c r="C3" t="n">
-        <v>778.8074148399552</v>
+        <v>786.2032128794</v>
       </c>
       <c r="D3" t="n">
-        <v>762.6005237676653</v>
+        <v>770.8335437165625</v>
       </c>
       <c r="E3" t="n">
-        <v>776.4551391601562</v>
+        <v>777.7010498046875</v>
       </c>
       <c r="F3" t="n">
-        <v>11782500</v>
+        <v>10955000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B4" t="n">
-        <v>777.4419223006557</v>
+        <v>783.8509325355676</v>
       </c>
       <c r="C4" t="n">
-        <v>780.7311297077449</v>
+        <v>788.2166289656076</v>
       </c>
       <c r="D4" t="n">
-        <v>763.8066193659058</v>
+        <v>766.6772383880447</v>
       </c>
       <c r="E4" t="n">
-        <v>773.1858520507812</v>
+        <v>775.8372192382812</v>
       </c>
       <c r="F4" t="n">
-        <v>9400900</v>
+        <v>23696800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,25 +547,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B5" t="n">
-        <v>778.1994774600552</v>
+        <v>779.8217552362186</v>
       </c>
       <c r="C5" t="n">
-        <v>786.203274581819</v>
+        <v>783.6916948825968</v>
       </c>
       <c r="D5" t="n">
-        <v>770.8336042127465</v>
+        <v>762.4868363426395</v>
       </c>
       <c r="E5" t="n">
-        <v>777.7011108398438</v>
+        <v>763.175048828125</v>
       </c>
       <c r="F5" t="n">
-        <v>10955000</v>
+        <v>11706900</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B6" t="n">
-        <v>783.8508708699721</v>
+        <v>767.2545389947088</v>
       </c>
       <c r="C6" t="n">
-        <v>788.2165669565625</v>
+        <v>768.6010126974617</v>
       </c>
       <c r="D6" t="n">
-        <v>766.6771780735046</v>
+        <v>749.1217058463387</v>
       </c>
       <c r="E6" t="n">
-        <v>775.837158203125</v>
+        <v>753.4404907226562</v>
       </c>
       <c r="F6" t="n">
-        <v>23696800</v>
+        <v>10872600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,25 +599,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B7" t="n">
-        <v>779.8218176027002</v>
+        <v>755.5349308449814</v>
       </c>
       <c r="C7" t="n">
-        <v>783.6917575585782</v>
+        <v>759.1355513505183</v>
       </c>
       <c r="D7" t="n">
-        <v>762.4868973227559</v>
+        <v>750.5778529948334</v>
       </c>
       <c r="E7" t="n">
-        <v>763.1751098632812</v>
+        <v>758.6867065429688</v>
       </c>
       <c r="F7" t="n">
-        <v>11706900</v>
+        <v>8828200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B8" t="n">
-        <v>767.254476840496</v>
+        <v>751.4954858581857</v>
       </c>
       <c r="C8" t="n">
-        <v>768.6009504341728</v>
+        <v>754.8068807440363</v>
       </c>
       <c r="D8" t="n">
-        <v>749.1216451610411</v>
+        <v>742.6185490172081</v>
       </c>
       <c r="E8" t="n">
-        <v>753.4404296875</v>
+        <v>746.9672241210938</v>
       </c>
       <c r="F8" t="n">
-        <v>10872600</v>
+        <v>10591100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B9" t="n">
-        <v>755.5349916265823</v>
+        <v>748.0544659269957</v>
       </c>
       <c r="C9" t="n">
-        <v>759.1356124217834</v>
+        <v>749.9794521140951</v>
       </c>
       <c r="D9" t="n">
-        <v>750.5779133776451</v>
+        <v>735.4372562509625</v>
       </c>
       <c r="E9" t="n">
-        <v>758.686767578125</v>
+        <v>741.8206787109375</v>
       </c>
       <c r="F9" t="n">
-        <v>8828200</v>
+        <v>9696300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>751.4954858581857</v>
+        <v>746.7777648139662</v>
       </c>
       <c r="C10" t="n">
-        <v>754.8068807440363</v>
+        <v>748.832479543402</v>
       </c>
       <c r="D10" t="n">
-        <v>742.6185490172081</v>
+        <v>737.2326433015477</v>
       </c>
       <c r="E10" t="n">
-        <v>746.9672241210938</v>
+        <v>741.4716186523438</v>
       </c>
       <c r="F10" t="n">
-        <v>10591100</v>
+        <v>9246800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>748.0544043789391</v>
+        <v>740.3245554260684</v>
       </c>
       <c r="C11" t="n">
-        <v>749.9793904076555</v>
+        <v>741.0426584785586</v>
       </c>
       <c r="D11" t="n">
-        <v>735.4371957410184</v>
+        <v>724.4159185837501</v>
       </c>
       <c r="E11" t="n">
-        <v>741.8206176757812</v>
+        <v>732.4749755859375</v>
       </c>
       <c r="F11" t="n">
-        <v>9696300</v>
+        <v>16226800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>746.777703342028</v>
+        <v>719.618385039583</v>
       </c>
       <c r="C12" t="n">
-        <v>748.8324179023273</v>
+        <v>719.9774365591268</v>
       </c>
       <c r="D12" t="n">
-        <v>737.2325826153279</v>
+        <v>708.3576941566364</v>
       </c>
       <c r="E12" t="n">
-        <v>741.4715576171875</v>
+        <v>715.4791870117188</v>
       </c>
       <c r="F12" t="n">
-        <v>9246800</v>
+        <v>20419600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>740.3245554260684</v>
+        <v>720.7056259804448</v>
       </c>
       <c r="C13" t="n">
-        <v>741.0426584785586</v>
+        <v>725.8821654223162</v>
       </c>
       <c r="D13" t="n">
-        <v>724.4159185837501</v>
+        <v>716.2771410193245</v>
       </c>
       <c r="E13" t="n">
-        <v>732.4749755859375</v>
+        <v>725.1640014648438</v>
       </c>
       <c r="F13" t="n">
-        <v>16226800</v>
+        <v>11415300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>719.6183236513255</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C14" t="n">
-        <v>719.9773751402398</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D14" t="n">
-        <v>708.357633728991</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E14" t="n">
-        <v>715.4791259765625</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F14" t="n">
-        <v>20419600</v>
+        <v>16154300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B15" t="n">
-        <v>720.7055653205383</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C15" t="n">
-        <v>725.8821043267139</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D15" t="n">
-        <v>716.2770807321521</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E15" t="n">
-        <v>725.1639404296875</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F15" t="n">
-        <v>11415300</v>
+        <v>21654700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B16" t="n">
-        <v>727.7372737109582</v>
+        <v>715.8581417735932</v>
       </c>
       <c r="C16" t="n">
-        <v>729.1037149276121</v>
+        <v>716.6361476056489</v>
       </c>
       <c r="D16" t="n">
-        <v>708.3377167266436</v>
+        <v>703.9192222306009</v>
       </c>
       <c r="E16" t="n">
-        <v>708.7167358398438</v>
+        <v>711.230224609375</v>
       </c>
       <c r="F16" t="n">
-        <v>16154300</v>
+        <v>12062900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B17" t="n">
-        <v>703.3607165744016</v>
+        <v>711.5993392573523</v>
       </c>
       <c r="C17" t="n">
-        <v>715.0203947681905</v>
+        <v>717.783268775081</v>
       </c>
       <c r="D17" t="n">
-        <v>688.718804278428</v>
+        <v>705.9739546774089</v>
       </c>
       <c r="E17" t="n">
-        <v>713.8035278320312</v>
+        <v>715.9779663085938</v>
       </c>
       <c r="F17" t="n">
-        <v>21654700</v>
+        <v>10790600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B18" t="n">
-        <v>715.8581417735932</v>
+        <v>716.4167658258609</v>
       </c>
       <c r="C18" t="n">
-        <v>716.6361476056489</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="D18" t="n">
-        <v>703.9192222306009</v>
+        <v>710.5918883665408</v>
       </c>
       <c r="E18" t="n">
-        <v>711.230224609375</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="F18" t="n">
-        <v>12062900</v>
+        <v>12717200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B19" t="n">
-        <v>711.599278595462</v>
+        <v>729.0239332852144</v>
       </c>
       <c r="C19" t="n">
-        <v>717.7832075860277</v>
+        <v>733.3626856542741</v>
       </c>
       <c r="D19" t="n">
-        <v>705.9738944950672</v>
+        <v>702.6824691715568</v>
       </c>
       <c r="E19" t="n">
-        <v>715.9779052734375</v>
+        <v>703.4703979492188</v>
       </c>
       <c r="F19" t="n">
-        <v>10790600</v>
+        <v>16980100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B20" t="n">
-        <v>716.4167658258609</v>
+        <v>711.1603595995662</v>
       </c>
       <c r="C20" t="n">
-        <v>731.6072387695312</v>
+        <v>718.072374881022</v>
       </c>
       <c r="D20" t="n">
-        <v>710.5918883665408</v>
+        <v>705.8042950194317</v>
       </c>
       <c r="E20" t="n">
-        <v>731.6072387695312</v>
+        <v>713.8433837890625</v>
       </c>
       <c r="F20" t="n">
-        <v>12717200</v>
+        <v>9251800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B21" t="n">
-        <v>729.0239332852144</v>
+        <v>705.9439682909708</v>
       </c>
       <c r="C21" t="n">
-        <v>733.3626856542741</v>
+        <v>713.6937706407739</v>
       </c>
       <c r="D21" t="n">
-        <v>702.6824691715568</v>
+        <v>697.5158763660478</v>
       </c>
       <c r="E21" t="n">
-        <v>703.4703979492188</v>
+        <v>706.8117065429688</v>
       </c>
       <c r="F21" t="n">
-        <v>16980100</v>
+        <v>8829800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B22" t="n">
-        <v>711.1603595995662</v>
+        <v>715.1998794771447</v>
       </c>
       <c r="C22" t="n">
-        <v>718.072374881022</v>
+        <v>722.0221626881838</v>
       </c>
       <c r="D22" t="n">
-        <v>705.8042950194317</v>
+        <v>707.6694770310874</v>
       </c>
       <c r="E22" t="n">
-        <v>713.8433837890625</v>
+        <v>715.6885986328125</v>
       </c>
       <c r="F22" t="n">
-        <v>9251800</v>
+        <v>10246800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B23" t="n">
-        <v>705.9439682909708</v>
+        <v>715.6886043056783</v>
       </c>
       <c r="C23" t="n">
-        <v>713.6937706407739</v>
+        <v>723.6080097298942</v>
       </c>
       <c r="D23" t="n">
-        <v>697.5158763660478</v>
+        <v>702.0540824517458</v>
       </c>
       <c r="E23" t="n">
-        <v>706.8117065429688</v>
+        <v>710.2228393554688</v>
       </c>
       <c r="F23" t="n">
-        <v>8829800</v>
+        <v>9017000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B24" t="n">
-        <v>715.1998794771447</v>
+        <v>705.2458014471516</v>
       </c>
       <c r="C24" t="n">
-        <v>722.0221626881838</v>
+        <v>716.6760344343375</v>
       </c>
       <c r="D24" t="n">
-        <v>707.6694770310874</v>
+        <v>704.2882698394852</v>
       </c>
       <c r="E24" t="n">
-        <v>715.6885986328125</v>
+        <v>715.0602416992188</v>
       </c>
       <c r="F24" t="n">
-        <v>10246800</v>
+        <v>12232400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B25" t="n">
-        <v>715.6886043056783</v>
+        <v>719.3191330444083</v>
       </c>
       <c r="C25" t="n">
-        <v>723.6080097298942</v>
+        <v>731.866515781436</v>
       </c>
       <c r="D25" t="n">
-        <v>702.0540824517458</v>
+        <v>718.3117433877071</v>
       </c>
       <c r="E25" t="n">
-        <v>710.2228393554688</v>
+        <v>730.2706298828125</v>
       </c>
       <c r="F25" t="n">
-        <v>9017000</v>
+        <v>8900200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B26" t="n">
-        <v>705.2458014471516</v>
+        <v>734.1107864324557</v>
       </c>
       <c r="C26" t="n">
-        <v>716.6760344343375</v>
+        <v>736.5843338414116</v>
       </c>
       <c r="D26" t="n">
-        <v>704.2882698394852</v>
+        <v>726.859625303898</v>
       </c>
       <c r="E26" t="n">
-        <v>715.0602416992188</v>
+        <v>731.367919921875</v>
       </c>
       <c r="F26" t="n">
-        <v>12232400</v>
+        <v>7647300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B27" t="n">
-        <v>719.3191931642514</v>
+        <v>731.9264616753367</v>
       </c>
       <c r="C27" t="n">
-        <v>731.8665769499745</v>
+        <v>738.6788588958609</v>
       </c>
       <c r="D27" t="n">
-        <v>718.3118034233538</v>
+        <v>722.1518950553793</v>
       </c>
       <c r="E27" t="n">
-        <v>730.2706909179688</v>
+        <v>731.5075073242188</v>
       </c>
       <c r="F27" t="n">
-        <v>8900200</v>
+        <v>8734500</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B28" t="n">
-        <v>734.1107251683979</v>
+        <v>732.7941435868839</v>
       </c>
       <c r="C28" t="n">
-        <v>736.5842723709278</v>
+        <v>740.4841042897723</v>
       </c>
       <c r="D28" t="n">
-        <v>726.8595646449745</v>
+        <v>731.1982575844598</v>
       </c>
       <c r="E28" t="n">
-        <v>731.3678588867188</v>
+        <v>732.095947265625</v>
       </c>
       <c r="F28" t="n">
-        <v>7647300</v>
+        <v>9856000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B29" t="n">
-        <v>731.9264006052239</v>
+        <v>734.8786455644157</v>
       </c>
       <c r="C29" t="n">
-        <v>738.6787972623451</v>
+        <v>739.2872233202683</v>
       </c>
       <c r="D29" t="n">
-        <v>722.1518348008319</v>
+        <v>729.2533227506186</v>
       </c>
       <c r="E29" t="n">
-        <v>731.5074462890625</v>
+        <v>736.444580078125</v>
       </c>
       <c r="F29" t="n">
-        <v>8734500</v>
+        <v>9151300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B30" t="n">
-        <v>732.7941435868839</v>
+        <v>747.7851152228061</v>
       </c>
       <c r="C30" t="n">
-        <v>740.4841042897723</v>
+        <v>753.7895182960361</v>
       </c>
       <c r="D30" t="n">
-        <v>731.1982575844598</v>
+        <v>746.069606274355</v>
       </c>
       <c r="E30" t="n">
-        <v>732.095947265625</v>
+        <v>748.872314453125</v>
       </c>
       <c r="F30" t="n">
-        <v>9856000</v>
+        <v>11321100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B31" t="n">
-        <v>734.8787064697904</v>
+        <v>750.677577029167</v>
       </c>
       <c r="C31" t="n">
-        <v>739.2872845910176</v>
+        <v>756.4326283200122</v>
       </c>
       <c r="D31" t="n">
-        <v>729.253383189777</v>
+        <v>743.5860359773924</v>
       </c>
       <c r="E31" t="n">
-        <v>736.4446411132812</v>
+        <v>749.4906616210938</v>
       </c>
       <c r="F31" t="n">
-        <v>9151300</v>
+        <v>12193800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B32" t="n">
-        <v>747.7850542762595</v>
+        <v>752.7920587752158</v>
       </c>
       <c r="C32" t="n">
-        <v>753.7894568601143</v>
+        <v>757.1905917498632</v>
       </c>
       <c r="D32" t="n">
-        <v>746.0695454676272</v>
+        <v>740.5838210171188</v>
       </c>
       <c r="E32" t="n">
-        <v>748.8722534179688</v>
+        <v>749.7200317382812</v>
       </c>
       <c r="F32" t="n">
-        <v>11321100</v>
+        <v>26818600</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B33" t="n">
-        <v>750.6776381609803</v>
+        <v>667.414190282622</v>
       </c>
       <c r="C33" t="n">
-        <v>756.4326899204912</v>
+        <v>679.1935516668058</v>
       </c>
       <c r="D33" t="n">
-        <v>743.5860965317024</v>
+        <v>648.4833846789722</v>
       </c>
       <c r="E33" t="n">
-        <v>749.49072265625</v>
+        <v>664.7410888671875</v>
       </c>
       <c r="F33" t="n">
-        <v>12193800</v>
+        <v>88440100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B34" t="n">
-        <v>752.7921200604676</v>
+        <v>672.7603267493847</v>
       </c>
       <c r="C34" t="n">
-        <v>757.1906533932021</v>
+        <v>673.139345897249</v>
       </c>
       <c r="D34" t="n">
-        <v>740.5838813084906</v>
+        <v>643.8953948481166</v>
       </c>
       <c r="E34" t="n">
-        <v>749.7200927734375</v>
+        <v>646.6681518554688</v>
       </c>
       <c r="F34" t="n">
-        <v>26818600</v>
+        <v>56953200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B35" t="n">
-        <v>667.4142515632169</v>
+        <v>654.2982567113449</v>
       </c>
       <c r="C35" t="n">
-        <v>679.1936140289573</v>
+        <v>657.619635334369</v>
       </c>
       <c r="D35" t="n">
-        <v>648.4834442213796</v>
+        <v>634.5296648817072</v>
       </c>
       <c r="E35" t="n">
-        <v>664.7411499023438</v>
+        <v>636.0557250976562</v>
       </c>
       <c r="F35" t="n">
-        <v>88440100</v>
+        <v>33003600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B36" t="n">
-        <v>672.7602632515434</v>
+        <v>626.4107910285981</v>
       </c>
       <c r="C36" t="n">
-        <v>673.1392823636344</v>
+        <v>640.0752642850032</v>
       </c>
       <c r="D36" t="n">
-        <v>643.8953340746643</v>
+        <v>624.3860886703497</v>
       </c>
       <c r="E36" t="n">
-        <v>646.6680908203125</v>
+        <v>625.6926879882812</v>
       </c>
       <c r="F36" t="n">
-        <v>56953200</v>
+        <v>27356600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B37" t="n">
-        <v>654.298319497033</v>
+        <v>630.6697208898194</v>
       </c>
       <c r="C37" t="n">
-        <v>657.6196984387726</v>
+        <v>640.5639703518489</v>
       </c>
       <c r="D37" t="n">
-        <v>634.5297257704245</v>
+        <v>624.9146693781357</v>
       </c>
       <c r="E37" t="n">
-        <v>636.0557861328125</v>
+        <v>634.30029296875</v>
       </c>
       <c r="F37" t="n">
-        <v>33003600</v>
+        <v>20219900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B38" t="n">
-        <v>626.4107910285981</v>
+        <v>634.2005186436334</v>
       </c>
       <c r="C38" t="n">
-        <v>640.0752642850032</v>
+        <v>634.3501538797125</v>
       </c>
       <c r="D38" t="n">
-        <v>624.3860886703497</v>
+        <v>616.3968476378337</v>
       </c>
       <c r="E38" t="n">
-        <v>625.6926879882812</v>
+        <v>617.3344116210938</v>
       </c>
       <c r="F38" t="n">
-        <v>27356600</v>
+        <v>23628800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B39" t="n">
-        <v>630.6697208898194</v>
+        <v>614.8907991985972</v>
       </c>
       <c r="C39" t="n">
-        <v>640.5639703518489</v>
+        <v>620.516183502649</v>
       </c>
       <c r="D39" t="n">
-        <v>624.9146693781357</v>
+        <v>599.6404837711106</v>
       </c>
       <c r="E39" t="n">
-        <v>634.30029296875</v>
+        <v>620.0972900390625</v>
       </c>
       <c r="F39" t="n">
-        <v>20219900</v>
+        <v>29946800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B40" t="n">
-        <v>634.2005186436334</v>
+        <v>629.4529708548182</v>
       </c>
       <c r="C40" t="n">
-        <v>634.3501538797125</v>
+        <v>633.3528014765299</v>
       </c>
       <c r="D40" t="n">
-        <v>616.3968476378337</v>
+        <v>616.5065997528014</v>
       </c>
       <c r="E40" t="n">
-        <v>617.3344116210938</v>
+        <v>630.1212158203125</v>
       </c>
       <c r="F40" t="n">
-        <v>23628800</v>
+        <v>19245000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B41" t="n">
-        <v>614.8907386759073</v>
+        <v>626.3709044869131</v>
       </c>
       <c r="C41" t="n">
-        <v>620.5161224262619</v>
+        <v>627.9268552540688</v>
       </c>
       <c r="D41" t="n">
-        <v>599.6404247494841</v>
+        <v>617.7832543081277</v>
       </c>
       <c r="E41" t="n">
-        <v>620.0972290039062</v>
+        <v>625.4533081054688</v>
       </c>
       <c r="F41" t="n">
-        <v>29946800</v>
+        <v>13302200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B42" t="n">
-        <v>629.4529708548182</v>
+        <v>626.5005716840028</v>
       </c>
       <c r="C42" t="n">
-        <v>633.3528014765299</v>
+        <v>627.3583261459861</v>
       </c>
       <c r="D42" t="n">
-        <v>616.5065997528014</v>
+        <v>606.1934022078184</v>
       </c>
       <c r="E42" t="n">
-        <v>630.1212158203125</v>
+        <v>607.43017578125</v>
       </c>
       <c r="F42" t="n">
-        <v>19245000</v>
+        <v>24493300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B43" t="n">
-        <v>626.3709656116134</v>
+        <v>611.4796659420805</v>
       </c>
       <c r="C43" t="n">
-        <v>627.9269165306073</v>
+        <v>616.0478021853295</v>
       </c>
       <c r="D43" t="n">
-        <v>617.7833145947981</v>
+        <v>601.4357808374693</v>
       </c>
       <c r="E43" t="n">
-        <v>625.453369140625</v>
+        <v>608.3079223632812</v>
       </c>
       <c r="F43" t="n">
-        <v>13302200</v>
+        <v>20973800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B44" t="n">
-        <v>626.5005716840028</v>
+        <v>600.2288811530552</v>
       </c>
       <c r="C44" t="n">
-        <v>627.3583261459861</v>
+        <v>612.088052043071</v>
       </c>
       <c r="D44" t="n">
-        <v>606.1934022078184</v>
+        <v>593.6560102918138</v>
       </c>
       <c r="E44" t="n">
-        <v>607.43017578125</v>
+        <v>607.8790283203125</v>
       </c>
       <c r="F44" t="n">
-        <v>24493300</v>
+        <v>20724100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B45" t="n">
-        <v>611.4796659420805</v>
+        <v>607.4600964135232</v>
       </c>
       <c r="C45" t="n">
-        <v>616.0478021853295</v>
+        <v>610.1032465254069</v>
       </c>
       <c r="D45" t="n">
-        <v>601.4357808374693</v>
+        <v>593.855525554584</v>
       </c>
       <c r="E45" t="n">
-        <v>608.3079223632812</v>
+        <v>600.4483642578125</v>
       </c>
       <c r="F45" t="n">
-        <v>20973800</v>
+        <v>16501300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B46" t="n">
-        <v>600.2288811530552</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C46" t="n">
-        <v>612.088052043071</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D46" t="n">
-        <v>593.6560102918138</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E46" t="n">
-        <v>607.8790283203125</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F46" t="n">
-        <v>20724100</v>
+        <v>25500600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B47" t="n">
-        <v>607.4600346656293</v>
+        <v>592.1798400423816</v>
       </c>
       <c r="C47" t="n">
-        <v>610.1031845088386</v>
+        <v>593.7857099116716</v>
       </c>
       <c r="D47" t="n">
-        <v>593.8554651895852</v>
+        <v>579.7422168855177</v>
       </c>
       <c r="E47" t="n">
-        <v>600.4483032226562</v>
+        <v>588.7886962890625</v>
       </c>
       <c r="F47" t="n">
-        <v>16501300</v>
+        <v>24744700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B48" t="n">
-        <v>590.065358149623</v>
+        <v>601.9344542639864</v>
       </c>
       <c r="C48" t="n">
-        <v>602.0940719298206</v>
+        <v>605.1460720070379</v>
       </c>
       <c r="D48" t="n">
-        <v>582.2656968950795</v>
+        <v>581.8367012414765</v>
       </c>
       <c r="E48" t="n">
-        <v>596.1395874023438</v>
+        <v>587.6217041015625</v>
       </c>
       <c r="F48" t="n">
-        <v>25500600</v>
+        <v>20603000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B49" t="n">
-        <v>592.1797786556917</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C49" t="n">
-        <v>593.7856483585136</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D49" t="n">
-        <v>579.7421567881397</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E49" t="n">
-        <v>588.7886352539062</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F49" t="n">
-        <v>24744700</v>
+        <v>21052600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B50" t="n">
-        <v>601.9344542639864</v>
+        <v>597.1668126146857</v>
       </c>
       <c r="C50" t="n">
-        <v>605.1460720070379</v>
+        <v>615.1002115339802</v>
       </c>
       <c r="D50" t="n">
-        <v>581.8367012414765</v>
+        <v>596.0796743085915</v>
       </c>
       <c r="E50" t="n">
-        <v>587.6217041015625</v>
+        <v>611.4596557617188</v>
       </c>
       <c r="F50" t="n">
-        <v>20603000</v>
+        <v>23554900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B51" t="n">
-        <v>586.9734117815261</v>
+        <v>622.3812488080194</v>
       </c>
       <c r="C51" t="n">
-        <v>596.5684523172222</v>
+        <v>635.3973829418613</v>
       </c>
       <c r="D51" t="n">
-        <v>580.3506215479276</v>
+        <v>616.6960233021972</v>
       </c>
       <c r="E51" t="n">
-        <v>592.70849609375</v>
+        <v>634.5695190429688</v>
       </c>
       <c r="F51" t="n">
-        <v>21052600</v>
+        <v>25213000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B52" t="n">
-        <v>597.1668722231478</v>
+        <v>636.0358029520913</v>
       </c>
       <c r="C52" t="n">
-        <v>615.1002729325323</v>
+        <v>636.7040478933542</v>
       </c>
       <c r="D52" t="n">
-        <v>596.0797338085368</v>
+        <v>629.9915253276793</v>
       </c>
       <c r="E52" t="n">
-        <v>611.459716796875</v>
+        <v>631.9663696289062</v>
       </c>
       <c r="F52" t="n">
-        <v>23554900</v>
+        <v>15209500</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B53" t="n">
-        <v>622.3812488080194</v>
+        <v>634.4299618769652</v>
       </c>
       <c r="C53" t="n">
-        <v>635.3973829418613</v>
+        <v>646.3688812783262</v>
       </c>
       <c r="D53" t="n">
-        <v>616.6960233021972</v>
+        <v>633.8514494094911</v>
       </c>
       <c r="E53" t="n">
-        <v>634.5695190429688</v>
+        <v>646.2691650390625</v>
       </c>
       <c r="F53" t="n">
-        <v>25213000</v>
+        <v>11033200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B54" t="n">
-        <v>636.0358029520913</v>
+        <v>637.8908755177382</v>
       </c>
       <c r="C54" t="n">
-        <v>636.7040478933542</v>
+        <v>643.6459265392308</v>
       </c>
       <c r="D54" t="n">
-        <v>629.9915253276793</v>
+        <v>636.1055410281542</v>
       </c>
       <c r="E54" t="n">
-        <v>631.9663696289062</v>
+        <v>639.2074584960938</v>
       </c>
       <c r="F54" t="n">
-        <v>15209500</v>
+        <v>13029900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B55" t="n">
-        <v>634.4299618769652</v>
+        <v>640.6737247939117</v>
       </c>
       <c r="C55" t="n">
-        <v>646.3688812783262</v>
+        <v>646.1893476978298</v>
       </c>
       <c r="D55" t="n">
-        <v>633.8514494094911</v>
+        <v>636.4147821721649</v>
       </c>
       <c r="E55" t="n">
-        <v>646.2691650390625</v>
+        <v>645.4213256835938</v>
       </c>
       <c r="F55" t="n">
-        <v>11033200</v>
+        <v>11640900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B56" t="n">
-        <v>637.8909364271796</v>
+        <v>642.7383158920676</v>
       </c>
       <c r="C56" t="n">
-        <v>643.6459879981971</v>
+        <v>647.1668005690203</v>
       </c>
       <c r="D56" t="n">
-        <v>636.1056017671217</v>
+        <v>635.8961259576193</v>
       </c>
       <c r="E56" t="n">
-        <v>639.20751953125</v>
+        <v>637.9407958984375</v>
       </c>
       <c r="F56" t="n">
-        <v>13029900</v>
+        <v>11134300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B57" t="n">
-        <v>640.6737247939117</v>
+        <v>674.2463992276428</v>
       </c>
       <c r="C57" t="n">
-        <v>646.1893476978298</v>
+        <v>674.3461154685141</v>
       </c>
       <c r="D57" t="n">
-        <v>636.4147821721649</v>
+        <v>658.3377626918029</v>
       </c>
       <c r="E57" t="n">
-        <v>645.4213256835938</v>
+        <v>659.81396484375</v>
       </c>
       <c r="F57" t="n">
-        <v>11640900</v>
+        <v>29874600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B58" t="n">
-        <v>642.7383158920676</v>
+        <v>662.2775487290173</v>
       </c>
       <c r="C58" t="n">
-        <v>647.1668005690203</v>
+        <v>672.9398207362489</v>
       </c>
       <c r="D58" t="n">
-        <v>635.8961259576193</v>
+        <v>660.6717397649775</v>
       </c>
       <c r="E58" t="n">
-        <v>637.9407958984375</v>
+        <v>671.673095703125</v>
       </c>
       <c r="F58" t="n">
-        <v>11134300</v>
+        <v>21207900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B59" t="n">
-        <v>674.246461597851</v>
+        <v>667.603701448277</v>
       </c>
       <c r="C59" t="n">
-        <v>674.3461778479464</v>
+        <v>674.9545781663558</v>
       </c>
       <c r="D59" t="n">
-        <v>658.3378235904052</v>
+        <v>663.344758713728</v>
       </c>
       <c r="E59" t="n">
-        <v>659.8140258789062</v>
+        <v>665.0702514648438</v>
       </c>
       <c r="F59" t="n">
-        <v>29874600</v>
+        <v>13161000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B60" t="n">
-        <v>662.2775487290173</v>
+        <v>662.0481300460407</v>
       </c>
       <c r="C60" t="n">
-        <v>672.9398207362489</v>
+        <v>662.7562492699393</v>
       </c>
       <c r="D60" t="n">
-        <v>660.6717397649775</v>
+        <v>651.6451938720459</v>
       </c>
       <c r="E60" t="n">
-        <v>671.673095703125</v>
+        <v>655.2557983398438</v>
       </c>
       <c r="F60" t="n">
-        <v>21207900</v>
+        <v>12997100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B61" t="n">
-        <v>667.603701448277</v>
+        <v>648.2640167126568</v>
       </c>
       <c r="C61" t="n">
-        <v>674.9545781663558</v>
+        <v>652.812185461044</v>
       </c>
       <c r="D61" t="n">
-        <v>663.344758713728</v>
+        <v>641.7310198416047</v>
       </c>
       <c r="E61" t="n">
-        <v>665.0702514648438</v>
+        <v>648.4435424804688</v>
       </c>
       <c r="F61" t="n">
-        <v>13161000</v>
+        <v>16910900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B62" t="n">
-        <v>662.0481917138827</v>
+        <v>641.6212380225077</v>
       </c>
       <c r="C62" t="n">
-        <v>662.7563110037405</v>
+        <v>653.5801862453618</v>
       </c>
       <c r="D62" t="n">
-        <v>651.645254570885</v>
+        <v>639.1377070000864</v>
       </c>
       <c r="E62" t="n">
-        <v>655.255859375</v>
+        <v>651.016845703125</v>
       </c>
       <c r="F62" t="n">
-        <v>12997100</v>
+        <v>13056700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B63" t="n">
-        <v>648.2639556943986</v>
+        <v>648.1142734035774</v>
       </c>
       <c r="C63" t="n">
-        <v>652.8121240146866</v>
+        <v>709.1555202318053</v>
       </c>
       <c r="D63" t="n">
-        <v>641.730959438269</v>
+        <v>636.9533001226623</v>
       </c>
       <c r="E63" t="n">
-        <v>648.4434814453125</v>
+        <v>642.5587158203125</v>
       </c>
       <c r="F63" t="n">
-        <v>16910900</v>
+        <v>14016900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,25 +2081,25 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B64" t="n">
-        <v>641.6211778682233</v>
+        <v>644.5502809809109</v>
       </c>
       <c r="C64" t="n">
-        <v>653.5801249698833</v>
+        <v>651.8372704406642</v>
       </c>
       <c r="D64" t="n">
-        <v>639.1376470786419</v>
+        <v>637.5627451568915</v>
       </c>
       <c r="E64" t="n">
-        <v>651.0167846679688</v>
+        <v>646.3570556640625</v>
       </c>
       <c r="F64" t="n">
-        <v>13056700</v>
+        <v>15549100</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B65" t="n">
-        <v>648.1143965293088</v>
+        <v>642.3541401459643</v>
       </c>
       <c r="C65" t="n">
-        <v>709.1556549538686</v>
+        <v>661.3602142938313</v>
       </c>
       <c r="D65" t="n">
-        <v>636.9534211280841</v>
+        <v>642.054686531657</v>
       </c>
       <c r="E65" t="n">
-        <v>642.558837890625</v>
+        <v>655.9798583984375</v>
       </c>
       <c r="F65" t="n">
-        <v>14016900</v>
+        <v>14309100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,25 +2133,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B66" t="n">
-        <v>644.5502809809109</v>
+        <v>654.4426118233187</v>
       </c>
       <c r="C66" t="n">
-        <v>651.8372704406642</v>
+        <v>660.0526000253047</v>
       </c>
       <c r="D66" t="n">
-        <v>637.5627451568915</v>
+        <v>648.0440522221027</v>
       </c>
       <c r="E66" t="n">
-        <v>646.3570556640625</v>
+        <v>648.343505859375</v>
       </c>
       <c r="F66" t="n">
-        <v>15549100</v>
+        <v>15598500</v>
       </c>
       <c r="G66" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B67" t="n">
-        <v>642.3541999133257</v>
+        <v>655.8601356908653</v>
       </c>
       <c r="C67" t="n">
-        <v>661.3602758295988</v>
+        <v>669.366012780715</v>
       </c>
       <c r="D67" t="n">
-        <v>642.054746271156</v>
+        <v>655.2911433094866</v>
       </c>
       <c r="E67" t="n">
-        <v>655.9799194335938</v>
+        <v>663.2669067382812</v>
       </c>
       <c r="F67" t="n">
-        <v>14309100</v>
+        <v>20260300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B68" t="n">
-        <v>654.4426118233187</v>
+        <v>665.2333263832898</v>
       </c>
       <c r="C68" t="n">
-        <v>660.0526000253047</v>
+        <v>669.8051880946751</v>
       </c>
       <c r="D68" t="n">
-        <v>648.0440522221027</v>
+        <v>657.0080086354003</v>
       </c>
       <c r="E68" t="n">
-        <v>648.343505859375</v>
+        <v>657.5969848632812</v>
       </c>
       <c r="F68" t="n">
-        <v>15598500</v>
+        <v>49977100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B69" t="n">
-        <v>655.8600753372949</v>
+        <v>660.4718397886508</v>
       </c>
       <c r="C69" t="n">
-        <v>669.3659511843067</v>
+        <v>672.380589007267</v>
       </c>
       <c r="D69" t="n">
-        <v>655.2910830082761</v>
+        <v>655.4807431709672</v>
       </c>
       <c r="E69" t="n">
-        <v>663.266845703125</v>
+        <v>660.3220825195312</v>
       </c>
       <c r="F69" t="n">
-        <v>20260300</v>
+        <v>15659400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B70" t="n">
-        <v>665.2333263832898</v>
+        <v>658.8746741689592</v>
       </c>
       <c r="C70" t="n">
-        <v>669.8051880946751</v>
+        <v>664.8140915262984</v>
       </c>
       <c r="D70" t="n">
-        <v>657.0080086354003</v>
+        <v>657.0778915122911</v>
       </c>
       <c r="E70" t="n">
-        <v>657.5969848632812</v>
+        <v>663.7559814453125</v>
       </c>
       <c r="F70" t="n">
-        <v>49977100</v>
+        <v>8486800</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B71" t="n">
-        <v>660.4719008376494</v>
+        <v>661.3503688947783</v>
       </c>
       <c r="C71" t="n">
-        <v>672.3806511570199</v>
+        <v>666.9902722948509</v>
       </c>
       <c r="D71" t="n">
-        <v>655.4808037586267</v>
+        <v>661.0209394131572</v>
       </c>
       <c r="E71" t="n">
-        <v>660.3221435546875</v>
+        <v>666.3613891601562</v>
       </c>
       <c r="F71" t="n">
-        <v>15659400</v>
+        <v>5627500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B72" t="n">
-        <v>658.8746741689592</v>
+        <v>666.8704124858896</v>
       </c>
       <c r="C72" t="n">
-        <v>664.8140915262984</v>
+        <v>667.7588423243637</v>
       </c>
       <c r="D72" t="n">
-        <v>657.0778915122911</v>
+        <v>660.1424238558649</v>
       </c>
       <c r="E72" t="n">
-        <v>663.7559814453125</v>
+        <v>662.10888671875</v>
       </c>
       <c r="F72" t="n">
-        <v>8486800</v>
+        <v>7133800</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B73" t="n">
-        <v>661.3503083186049</v>
+        <v>656.8383689858442</v>
       </c>
       <c r="C73" t="n">
-        <v>666.9902112020924</v>
+        <v>659.0743707339258</v>
       </c>
       <c r="D73" t="n">
-        <v>661.0208788671576</v>
+        <v>653.2248195668056</v>
       </c>
       <c r="E73" t="n">
-        <v>666.361328125</v>
+        <v>657.5171508789062</v>
       </c>
       <c r="F73" t="n">
-        <v>5627500</v>
+        <v>8506500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B74" t="n">
-        <v>666.8704739599774</v>
+        <v>657.5171386037911</v>
       </c>
       <c r="C74" t="n">
-        <v>667.7589038803495</v>
+        <v>671.0230153954109</v>
       </c>
       <c r="D74" t="n">
-        <v>660.1424847097468</v>
+        <v>656.6686764849229</v>
       </c>
       <c r="E74" t="n">
-        <v>662.1089477539062</v>
+        <v>664.7642211914062</v>
       </c>
       <c r="F74" t="n">
-        <v>7133800</v>
+        <v>9187500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B75" t="n">
-        <v>656.8383689858442</v>
+        <v>663.5663484641349</v>
       </c>
       <c r="C75" t="n">
-        <v>659.0743707339258</v>
+        <v>663.8159033150052</v>
       </c>
       <c r="D75" t="n">
-        <v>653.2248195668056</v>
+        <v>658.2658058687088</v>
       </c>
       <c r="E75" t="n">
-        <v>657.5171508789062</v>
+        <v>658.9146728515625</v>
       </c>
       <c r="F75" t="n">
-        <v>8506500</v>
+        <v>7940400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B76" t="n">
-        <v>657.5171386037911</v>
+        <v>661.5499631466852</v>
       </c>
       <c r="C76" t="n">
-        <v>671.0230153954109</v>
+        <v>663.2070415689074</v>
       </c>
       <c r="D76" t="n">
-        <v>656.6686764849229</v>
+        <v>642.3542224297569</v>
       </c>
       <c r="E76" t="n">
-        <v>664.7642211914062</v>
+        <v>649.2518920898438</v>
       </c>
       <c r="F76" t="n">
-        <v>9187500</v>
+        <v>13726500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B77" t="n">
-        <v>663.5662869980947</v>
+        <v>649.8508280292294</v>
       </c>
       <c r="C77" t="n">
-        <v>663.8158418258488</v>
+        <v>663.3567049684374</v>
       </c>
       <c r="D77" t="n">
-        <v>658.2657448936569</v>
+        <v>646.5966230035071</v>
       </c>
       <c r="E77" t="n">
-        <v>658.9146118164062</v>
+        <v>657.616943359375</v>
       </c>
       <c r="F77" t="n">
-        <v>7940400</v>
+        <v>12213700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B78" t="n">
-        <v>661.5499009554064</v>
+        <v>658.3956073528642</v>
       </c>
       <c r="C78" t="n">
-        <v>663.2069792218492</v>
+        <v>664.3350252422523</v>
       </c>
       <c r="D78" t="n">
-        <v>642.3541620430398</v>
+        <v>650.7392812609531</v>
       </c>
       <c r="E78" t="n">
-        <v>649.2518310546875</v>
+        <v>659.4437255859375</v>
       </c>
       <c r="F78" t="n">
-        <v>13726500</v>
+        <v>11074400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B79" t="n">
-        <v>649.8508280292294</v>
+        <v>654.4726104611178</v>
       </c>
       <c r="C79" t="n">
-        <v>663.3567049684374</v>
+        <v>657.9763704555172</v>
       </c>
       <c r="D79" t="n">
-        <v>646.5966230035071</v>
+        <v>643.6618768302103</v>
       </c>
       <c r="E79" t="n">
-        <v>657.616943359375</v>
+        <v>647.5349731445312</v>
       </c>
       <c r="F79" t="n">
-        <v>12213700</v>
+        <v>12846300</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B80" t="n">
-        <v>658.3955464147172</v>
+        <v>644.7299347572825</v>
       </c>
       <c r="C80" t="n">
-        <v>664.3349637543794</v>
+        <v>645.9477331499952</v>
       </c>
       <c r="D80" t="n">
-        <v>650.7392210314413</v>
+        <v>634.5879917891143</v>
       </c>
       <c r="E80" t="n">
-        <v>659.4436645507812</v>
+        <v>644.9096069335938</v>
       </c>
       <c r="F80" t="n">
-        <v>11074400</v>
+        <v>11921700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B81" t="n">
-        <v>654.4725487720359</v>
+        <v>644.2906685217797</v>
       </c>
       <c r="C81" t="n">
-        <v>657.9763084361789</v>
+        <v>653.7837438291153</v>
       </c>
       <c r="D81" t="n">
-        <v>643.6618161601232</v>
+        <v>641.7052537227476</v>
       </c>
       <c r="E81" t="n">
-        <v>647.534912109375</v>
+        <v>651.8970947265625</v>
       </c>
       <c r="F81" t="n">
-        <v>12846300</v>
+        <v>11634900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B82" t="n">
-        <v>644.7299347572825</v>
+        <v>651.3681600668523</v>
       </c>
       <c r="C82" t="n">
-        <v>645.9477331499952</v>
+        <v>652.8055375702352</v>
       </c>
       <c r="D82" t="n">
-        <v>634.5879917891143</v>
+        <v>640.0882316599212</v>
       </c>
       <c r="E82" t="n">
-        <v>644.9096069335938</v>
+        <v>640.826904296875</v>
       </c>
       <c r="F82" t="n">
-        <v>11921700</v>
+        <v>14797200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B83" t="n">
-        <v>644.2907288447692</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="C83" t="n">
-        <v>653.7838050409127</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="D83" t="n">
-        <v>641.7053138036724</v>
+        <v>622.9887038024194</v>
       </c>
       <c r="E83" t="n">
-        <v>651.8971557617188</v>
+        <v>629.96630859375</v>
       </c>
       <c r="F83" t="n">
-        <v>11634900</v>
+        <v>18030400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B84" t="n">
-        <v>651.3680980277007</v>
+        <v>625.3844405077801</v>
       </c>
       <c r="C84" t="n">
-        <v>652.8054753941815</v>
+        <v>627.3309804807691</v>
       </c>
       <c r="D84" t="n">
-        <v>640.0881706951194</v>
+        <v>613.7252454803604</v>
       </c>
       <c r="E84" t="n">
-        <v>640.8268432617188</v>
+        <v>614.4240112304688</v>
       </c>
       <c r="F84" t="n">
-        <v>14797200</v>
+        <v>15527900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B85" t="n">
-        <v>641.1263941859123</v>
+        <v>617.378703801015</v>
       </c>
       <c r="C85" t="n">
-        <v>641.1263941859123</v>
+        <v>623.0585745209008</v>
       </c>
       <c r="D85" t="n">
-        <v>622.9887038024194</v>
+        <v>613.1362714280776</v>
       </c>
       <c r="E85" t="n">
-        <v>629.96630859375</v>
+        <v>619.694580078125</v>
       </c>
       <c r="F85" t="n">
-        <v>18030400</v>
+        <v>13076100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B86" t="n">
-        <v>625.3844405077801</v>
+        <v>623.0685636897582</v>
       </c>
       <c r="C86" t="n">
-        <v>627.3309804807691</v>
+        <v>627.9598630097294</v>
       </c>
       <c r="D86" t="n">
-        <v>613.7252454803604</v>
+        <v>618.9758886129073</v>
       </c>
       <c r="E86" t="n">
-        <v>614.4240112304688</v>
+        <v>619.1455688476562</v>
       </c>
       <c r="F86" t="n">
-        <v>15527900</v>
+        <v>17012500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B87" t="n">
-        <v>617.378703801015</v>
+        <v>606.7976262932837</v>
       </c>
       <c r="C87" t="n">
-        <v>623.0585745209008</v>
+        <v>610.3113781504126</v>
       </c>
       <c r="D87" t="n">
-        <v>613.1362714280776</v>
+        <v>598.9316523845154</v>
       </c>
       <c r="E87" t="n">
-        <v>619.694580078125</v>
+        <v>603.0443115234375</v>
       </c>
       <c r="F87" t="n">
-        <v>13076100</v>
+        <v>15169600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B88" t="n">
-        <v>623.0685636897582</v>
+        <v>605.659634898437</v>
       </c>
       <c r="C88" t="n">
-        <v>627.9598630097294</v>
+        <v>617.169133937088</v>
       </c>
       <c r="D88" t="n">
-        <v>618.9758886129073</v>
+        <v>599.0115204374271</v>
       </c>
       <c r="E88" t="n">
-        <v>619.1455688476562</v>
+        <v>611.8685913085938</v>
       </c>
       <c r="F88" t="n">
-        <v>17012500</v>
+        <v>14494700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B89" t="n">
-        <v>606.7976262932837</v>
+        <v>628.2293275614567</v>
       </c>
       <c r="C89" t="n">
-        <v>610.3113781504126</v>
+        <v>659.3937675491238</v>
       </c>
       <c r="D89" t="n">
-        <v>598.9316523845154</v>
+        <v>625.4343255489129</v>
       </c>
       <c r="E89" t="n">
-        <v>603.0443115234375</v>
+        <v>646.476806640625</v>
       </c>
       <c r="F89" t="n">
-        <v>15169600</v>
+        <v>21394700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B90" t="n">
-        <v>605.659634898437</v>
+        <v>643.6219561683764</v>
       </c>
       <c r="C90" t="n">
-        <v>617.169133937088</v>
+        <v>665.3032527677875</v>
       </c>
       <c r="D90" t="n">
-        <v>599.0115204374271</v>
+        <v>643.3025186421843</v>
       </c>
       <c r="E90" t="n">
-        <v>611.8685913085938</v>
+        <v>657.5870361328125</v>
       </c>
       <c r="F90" t="n">
-        <v>14494700</v>
+        <v>22797700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B91" t="n">
-        <v>628.2293275614567</v>
+        <v>663.9456740004919</v>
       </c>
       <c r="C91" t="n">
-        <v>659.3937675491238</v>
+        <v>674.0776252750454</v>
       </c>
       <c r="D91" t="n">
-        <v>625.4343255489129</v>
+        <v>660.1124846991261</v>
       </c>
       <c r="E91" t="n">
-        <v>646.476806640625</v>
+        <v>671.1627807617188</v>
       </c>
       <c r="F91" t="n">
-        <v>21394700</v>
+        <v>16327400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B92" t="n">
-        <v>643.6219561683764</v>
+        <v>673.3888389297905</v>
       </c>
       <c r="C92" t="n">
-        <v>665.3032527677875</v>
+        <v>675.6148486525956</v>
       </c>
       <c r="D92" t="n">
-        <v>643.3025186421843</v>
+        <v>663.4764668627315</v>
       </c>
       <c r="E92" t="n">
-        <v>657.5870361328125</v>
+        <v>671.7716674804688</v>
       </c>
       <c r="F92" t="n">
-        <v>22797700</v>
+        <v>13297400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B93" t="n">
-        <v>663.9456136216552</v>
+        <v>673.2989910894674</v>
       </c>
       <c r="C93" t="n">
-        <v>674.0775639748149</v>
+        <v>676.4733214975852</v>
       </c>
       <c r="D93" t="n">
-        <v>660.1124246688775</v>
+        <v>664.9139236867763</v>
       </c>
       <c r="E93" t="n">
-        <v>671.1627197265625</v>
+        <v>667.5392456054688</v>
       </c>
       <c r="F93" t="n">
-        <v>16327400</v>
+        <v>25709600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B94" t="n">
-        <v>673.3888389297905</v>
+        <v>736.1169233837337</v>
       </c>
       <c r="C94" t="n">
-        <v>675.6148486525956</v>
+        <v>742.6752321400184</v>
       </c>
       <c r="D94" t="n">
-        <v>663.4764668627315</v>
+        <v>711.2812198864386</v>
       </c>
       <c r="E94" t="n">
-        <v>671.7716674804688</v>
+        <v>736.995361328125</v>
       </c>
       <c r="F94" t="n">
-        <v>13297400</v>
+        <v>59852900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B95" t="n">
-        <v>673.2989295276801</v>
+        <v>726.2045952530067</v>
       </c>
       <c r="C95" t="n">
-        <v>676.4732596455591</v>
+        <v>730.8662626744616</v>
       </c>
       <c r="D95" t="n">
-        <v>664.9138628916613</v>
+        <v>712.3193905555435</v>
       </c>
       <c r="E95" t="n">
-        <v>667.5391845703125</v>
+        <v>715.2241821289062</v>
       </c>
       <c r="F95" t="n">
-        <v>25709600</v>
+        <v>23744600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B96" t="n">
-        <v>736.1169233837337</v>
+        <v>713.3275184694113</v>
       </c>
       <c r="C96" t="n">
-        <v>742.6752321400184</v>
+        <v>720.0156002559207</v>
       </c>
       <c r="D96" t="n">
-        <v>711.2812198864386</v>
+        <v>702.2672920108814</v>
       </c>
       <c r="E96" t="n">
-        <v>736.995361328125</v>
+        <v>705.152099609375</v>
       </c>
       <c r="F96" t="n">
-        <v>59852900</v>
+        <v>14365200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B97" t="n">
-        <v>726.2045952530067</v>
+        <v>706.1104025957663</v>
       </c>
       <c r="C97" t="n">
-        <v>730.8662626744616</v>
+        <v>715.7232596178901</v>
       </c>
       <c r="D97" t="n">
-        <v>712.3193905555435</v>
+        <v>685.1877035052055</v>
       </c>
       <c r="E97" t="n">
-        <v>715.2241821289062</v>
+        <v>690.4683227539062</v>
       </c>
       <c r="F97" t="n">
-        <v>23744600</v>
+        <v>13760700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B98" t="n">
-        <v>713.3275184694113</v>
+        <v>686.5053883494637</v>
       </c>
       <c r="C98" t="n">
-        <v>720.0156002559207</v>
+        <v>687.603466213174</v>
       </c>
       <c r="D98" t="n">
-        <v>702.2672920108814</v>
+        <v>666.2715231343633</v>
       </c>
       <c r="E98" t="n">
-        <v>705.152099609375</v>
+        <v>667.7987670898438</v>
       </c>
       <c r="F98" t="n">
-        <v>14365200</v>
+        <v>16882800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B99" t="n">
-        <v>706.1104025957663</v>
+        <v>662.3984025060512</v>
       </c>
       <c r="C99" t="n">
-        <v>715.7232596178901</v>
+        <v>680.2864759062725</v>
       </c>
       <c r="D99" t="n">
-        <v>685.1877035052055</v>
+        <v>652.3363345630947</v>
       </c>
       <c r="E99" t="n">
-        <v>690.4683227539062</v>
+        <v>669.0166015625</v>
       </c>
       <c r="F99" t="n">
-        <v>13760700</v>
+        <v>17131800</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B100" t="n">
-        <v>686.5054510943589</v>
+        <v>664.3050190645899</v>
       </c>
       <c r="C100" t="n">
-        <v>687.6035290584308</v>
+        <v>670.7934451675868</v>
       </c>
       <c r="D100" t="n">
-        <v>666.2715840299333</v>
+        <v>645.3488423980709</v>
       </c>
       <c r="E100" t="n">
-        <v>667.798828125</v>
+        <v>660.2822265625</v>
       </c>
       <c r="F100" t="n">
-        <v>16882800</v>
+        <v>18159300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B101" t="n">
-        <v>662.3984629374214</v>
+        <v>661.9991209626965</v>
       </c>
       <c r="C101" t="n">
-        <v>680.2865379695924</v>
+        <v>682.0932819515241</v>
       </c>
       <c r="D101" t="n">
-        <v>652.3363940764909</v>
+        <v>657.6069922476072</v>
       </c>
       <c r="E101" t="n">
-        <v>669.0166625976562</v>
+        <v>676.0140991210938</v>
       </c>
       <c r="F101" t="n">
-        <v>17131800</v>
+        <v>14837500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B102" t="n">
-        <v>664.3050190645899</v>
+        <v>676.3934502400131</v>
       </c>
       <c r="C102" t="n">
-        <v>670.7934451675868</v>
+        <v>679.4380681924739</v>
       </c>
       <c r="D102" t="n">
-        <v>645.3488423980709</v>
+        <v>668.597359057372</v>
       </c>
       <c r="E102" t="n">
-        <v>660.2822265625</v>
+        <v>669.5256958007812</v>
       </c>
       <c r="F102" t="n">
-        <v>18159300</v>
+        <v>10455800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B103" t="n">
-        <v>661.9991209626965</v>
+        <v>672.7998711552045</v>
       </c>
       <c r="C103" t="n">
-        <v>682.0932819515241</v>
+        <v>678.0605068549233</v>
       </c>
       <c r="D103" t="n">
-        <v>657.6069922476072</v>
+        <v>655.9299390360635</v>
       </c>
       <c r="E103" t="n">
-        <v>676.0140991210938</v>
+        <v>667.4993286132812</v>
       </c>
       <c r="F103" t="n">
-        <v>14837500</v>
+        <v>14323800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B104" t="n">
-        <v>676.39338857878</v>
+        <v>668.7770306530766</v>
       </c>
       <c r="C104" t="n">
-        <v>679.4380062536881</v>
+        <v>674.7963229561075</v>
       </c>
       <c r="D104" t="n">
-        <v>668.5972981068446</v>
+        <v>644.1310518439949</v>
       </c>
       <c r="E104" t="n">
-        <v>669.525634765625</v>
+        <v>648.6529541015625</v>
       </c>
       <c r="F104" t="n">
-        <v>10455800</v>
+        <v>14960100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B105" t="n">
-        <v>672.7998711552045</v>
+        <v>643.9513250294082</v>
       </c>
       <c r="C105" t="n">
-        <v>678.0605068549233</v>
+        <v>650.2700710327099</v>
       </c>
       <c r="D105" t="n">
-        <v>655.9299390360635</v>
+        <v>633.4401061931457</v>
       </c>
       <c r="E105" t="n">
-        <v>667.4993286132812</v>
+        <v>638.630859375</v>
       </c>
       <c r="F105" t="n">
-        <v>14323800</v>
+        <v>12336400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B106" t="n">
-        <v>668.7770306530766</v>
+        <v>638.3612593202278</v>
       </c>
       <c r="C106" t="n">
-        <v>674.7963229561075</v>
+        <v>641.4557148619026</v>
       </c>
       <c r="D106" t="n">
-        <v>644.1310518439949</v>
+        <v>627.6803003409905</v>
       </c>
       <c r="E106" t="n">
-        <v>648.6529541015625</v>
+        <v>638.151611328125</v>
       </c>
       <c r="F106" t="n">
-        <v>14960100</v>
+        <v>12674700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B107" t="n">
-        <v>643.9512634857649</v>
+        <v>632.67143641335</v>
       </c>
       <c r="C107" t="n">
-        <v>650.2700088851722</v>
+        <v>643.8515057528024</v>
       </c>
       <c r="D107" t="n">
-        <v>633.4400456540794</v>
+        <v>627.0315334227189</v>
       </c>
       <c r="E107" t="n">
-        <v>638.6307983398438</v>
+        <v>642.0746459960938</v>
       </c>
       <c r="F107" t="n">
-        <v>12336400</v>
+        <v>14649200</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B108" t="n">
-        <v>638.3613203754355</v>
+        <v>637.432932921519</v>
       </c>
       <c r="C108" t="n">
-        <v>641.4557762130754</v>
+        <v>646.0375787806976</v>
       </c>
       <c r="D108" t="n">
-        <v>627.6803603746322</v>
+        <v>635.5861905818066</v>
       </c>
       <c r="E108" t="n">
-        <v>638.1516723632812</v>
+        <v>643.6318969726562</v>
       </c>
       <c r="F108" t="n">
-        <v>12674700</v>
+        <v>10035700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B109" t="n">
-        <v>632.67143641335</v>
+        <v>638.5509584025834</v>
       </c>
       <c r="C109" t="n">
-        <v>643.8515057528024</v>
+        <v>662.1688021543367</v>
       </c>
       <c r="D109" t="n">
-        <v>627.0315334227189</v>
+        <v>637.6426055733327</v>
       </c>
       <c r="E109" t="n">
-        <v>642.0746459960938</v>
+        <v>654.4924926757812</v>
       </c>
       <c r="F109" t="n">
-        <v>14649200</v>
+        <v>14183500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B110" t="n">
-        <v>637.432932921519</v>
+        <v>651.3780476889771</v>
       </c>
       <c r="C110" t="n">
-        <v>646.0375787806976</v>
+        <v>656.5288937722072</v>
       </c>
       <c r="D110" t="n">
-        <v>635.5861905818066</v>
+        <v>634.8675211939732</v>
       </c>
       <c r="E110" t="n">
-        <v>643.6318969726562</v>
+        <v>636.1152954101562</v>
       </c>
       <c r="F110" t="n">
-        <v>10035700</v>
+        <v>8605900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B111" t="n">
-        <v>638.5510179511008</v>
+        <v>631.9527259539814</v>
       </c>
       <c r="C111" t="n">
-        <v>662.1688639053526</v>
+        <v>639.9683956881865</v>
       </c>
       <c r="D111" t="n">
-        <v>637.642665037141</v>
+        <v>627.8599900449855</v>
       </c>
       <c r="E111" t="n">
-        <v>654.4925537109375</v>
+        <v>638.16162109375</v>
       </c>
       <c r="F111" t="n">
-        <v>14183500</v>
+        <v>10135600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B112" t="n">
-        <v>651.3781101885919</v>
+        <v>641.3859599741169</v>
       </c>
       <c r="C112" t="n">
-        <v>656.5289567660449</v>
+        <v>652.7157261405878</v>
       </c>
       <c r="D112" t="n">
-        <v>634.8675821094057</v>
+        <v>640.9966397738364</v>
       </c>
       <c r="E112" t="n">
-        <v>636.1153564453125</v>
+        <v>652.5260620117188</v>
       </c>
       <c r="F112" t="n">
-        <v>8605900</v>
+        <v>11330700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B113" t="n">
-        <v>631.9527863953055</v>
+        <v>649.3916295582877</v>
       </c>
       <c r="C113" t="n">
-        <v>639.9684568961466</v>
+        <v>659.823034651462</v>
       </c>
       <c r="D113" t="n">
-        <v>627.8600500948714</v>
+        <v>646.3470725216666</v>
       </c>
       <c r="E113" t="n">
-        <v>638.1616821289062</v>
+        <v>655.8401489257812</v>
       </c>
       <c r="F113" t="n">
-        <v>10135600</v>
+        <v>10637700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B114" t="n">
-        <v>641.3858999809694</v>
+        <v>642.3043203814821</v>
       </c>
       <c r="C114" t="n">
-        <v>652.7156650876909</v>
+        <v>648.2836451675449</v>
       </c>
       <c r="D114" t="n">
-        <v>640.9965798171046</v>
+        <v>636.9837936279411</v>
       </c>
       <c r="E114" t="n">
-        <v>652.5260009765625</v>
+        <v>647.02587890625</v>
       </c>
       <c r="F114" t="n">
-        <v>11330700</v>
+        <v>15703000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B115" t="n">
-        <v>649.3916295582877</v>
+        <v>636.0254184162494</v>
       </c>
       <c r="C115" t="n">
-        <v>659.823034651462</v>
+        <v>658.764884603327</v>
       </c>
       <c r="D115" t="n">
-        <v>646.3470725216666</v>
+        <v>633.3701817354564</v>
       </c>
       <c r="E115" t="n">
-        <v>655.8401489257812</v>
+        <v>652.396240234375</v>
       </c>
       <c r="F115" t="n">
-        <v>10637700</v>
+        <v>9816100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B116" t="n">
-        <v>642.3042597917192</v>
+        <v>647.1356255764312</v>
       </c>
       <c r="C116" t="n">
-        <v>648.2835840137412</v>
+        <v>657.866484005116</v>
       </c>
       <c r="D116" t="n">
-        <v>636.9837335400734</v>
+        <v>637.7025010942567</v>
       </c>
       <c r="E116" t="n">
-        <v>647.0258178710938</v>
+        <v>653.91357421875</v>
       </c>
       <c r="F116" t="n">
-        <v>15703000</v>
+        <v>12263800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B117" t="n">
-        <v>636.0254184162494</v>
+        <v>656.7884535878291</v>
       </c>
       <c r="C117" t="n">
-        <v>658.764884603327</v>
+        <v>671.5720803574089</v>
       </c>
       <c r="D117" t="n">
-        <v>633.3701817354564</v>
+        <v>656.4989309709863</v>
       </c>
       <c r="E117" t="n">
-        <v>652.396240234375</v>
+        <v>666.541015625</v>
       </c>
       <c r="F117" t="n">
-        <v>9816100</v>
+        <v>10810100</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B118" t="n">
-        <v>647.1356255764312</v>
+        <v>660.751362594833</v>
       </c>
       <c r="C118" t="n">
-        <v>657.866484005116</v>
+        <v>669.5057662619517</v>
       </c>
       <c r="D118" t="n">
-        <v>637.7025010942567</v>
+        <v>649.1520579976961</v>
       </c>
       <c r="E118" t="n">
-        <v>653.91357421875</v>
+        <v>659.393798828125</v>
       </c>
       <c r="F118" t="n">
-        <v>12263800</v>
+        <v>13341400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B119" t="n">
-        <v>656.7884535878291</v>
+        <v>646.7463568472266</v>
       </c>
       <c r="C119" t="n">
-        <v>671.5720803574089</v>
+        <v>648.3135076492586</v>
       </c>
       <c r="D119" t="n">
-        <v>656.4989309709863</v>
+        <v>634.9773114336934</v>
       </c>
       <c r="E119" t="n">
-        <v>666.541015625</v>
+        <v>643.7117309570312</v>
       </c>
       <c r="F119" t="n">
-        <v>10810100</v>
+        <v>13159400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B120" t="n">
-        <v>660.751362594833</v>
+        <v>633.6497720389343</v>
       </c>
       <c r="C120" t="n">
-        <v>669.5057662619517</v>
+        <v>646.596649067328</v>
       </c>
       <c r="D120" t="n">
-        <v>649.1520579976961</v>
+        <v>625.6640164348609</v>
       </c>
       <c r="E120" t="n">
-        <v>659.393798828125</v>
+        <v>646.2373046875</v>
       </c>
       <c r="F120" t="n">
-        <v>13341400</v>
+        <v>13489700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B121" t="n">
-        <v>646.7463568472266</v>
+        <v>652.3962328583322</v>
       </c>
       <c r="C121" t="n">
-        <v>648.3135076492586</v>
+        <v>659.1242214972237</v>
       </c>
       <c r="D121" t="n">
-        <v>634.9773114336934</v>
+        <v>647.8443550809549</v>
       </c>
       <c r="E121" t="n">
-        <v>643.7117309570312</v>
+        <v>652.9053344726562</v>
       </c>
       <c r="F121" t="n">
-        <v>13159400</v>
+        <v>9859300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B122" t="n">
-        <v>633.6497121926325</v>
+        <v>653.5941111270305</v>
       </c>
       <c r="C122" t="n">
-        <v>646.5965879982328</v>
+        <v>657.9463328691638</v>
       </c>
       <c r="D122" t="n">
-        <v>625.6639573427893</v>
+        <v>647.2054829186618</v>
       </c>
       <c r="E122" t="n">
-        <v>646.2372436523438</v>
+        <v>653.6939086914062</v>
       </c>
       <c r="F122" t="n">
-        <v>13489700</v>
+        <v>8977200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B123" t="n">
-        <v>652.3962938458964</v>
+        <v>647.5948263527883</v>
       </c>
       <c r="C123" t="n">
-        <v>659.1242831137364</v>
+        <v>652.336368433984</v>
       </c>
       <c r="D123" t="n">
-        <v>647.8444156429986</v>
+        <v>635.7659510050273</v>
       </c>
       <c r="E123" t="n">
-        <v>652.9053955078125</v>
+        <v>637.0436401367188</v>
       </c>
       <c r="F123" t="n">
-        <v>9859300</v>
+        <v>11617500</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B124" t="n">
-        <v>653.5941721528687</v>
+        <v>622.7790526456299</v>
       </c>
       <c r="C124" t="n">
-        <v>657.9463943013674</v>
+        <v>628.0496188589474</v>
       </c>
       <c r="D124" t="n">
-        <v>647.2055433479961</v>
+        <v>608.4645611002024</v>
       </c>
       <c r="E124" t="n">
-        <v>653.6939697265625</v>
+        <v>612.6171875</v>
       </c>
       <c r="F124" t="n">
-        <v>8977200</v>
+        <v>18957600</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,25 +3667,25 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B125" t="n">
-        <v>647.5948883988538</v>
+        <v>631.4147932406764</v>
       </c>
       <c r="C125" t="n">
-        <v>652.3364309343367</v>
+        <v>634.1622468505053</v>
       </c>
       <c r="D125" t="n">
-        <v>635.7660119177681</v>
+        <v>622.5230098937741</v>
       </c>
       <c r="E125" t="n">
-        <v>637.043701171875</v>
+        <v>626.8690185546875</v>
       </c>
       <c r="F125" t="n">
-        <v>11617500</v>
+        <v>15134900</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B126" t="n">
-        <v>622.7790526456299</v>
+        <v>627.4085169382369</v>
       </c>
       <c r="C126" t="n">
-        <v>628.0496188589474</v>
+        <v>635.9605885584036</v>
       </c>
       <c r="D126" t="n">
-        <v>608.4645611002024</v>
+        <v>621.1243629754691</v>
       </c>
       <c r="E126" t="n">
-        <v>612.6171875</v>
+        <v>622.0834350585938</v>
       </c>
       <c r="F126" t="n">
-        <v>18957600</v>
+        <v>10348800</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,25 +3719,25 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B127" t="n">
-        <v>631.4147932406764</v>
+        <v>615.7693473594539</v>
       </c>
       <c r="C127" t="n">
-        <v>634.1622468505053</v>
+        <v>622.0735023862151</v>
       </c>
       <c r="D127" t="n">
-        <v>622.5230098937741</v>
+        <v>614.04090772979</v>
       </c>
       <c r="E127" t="n">
-        <v>626.8690185546875</v>
+        <v>615.1099243164062</v>
       </c>
       <c r="F127" t="n">
-        <v>15134900</v>
+        <v>11726300</v>
       </c>
       <c r="G127" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B128" t="n">
-        <v>627.4085169382369</v>
+        <v>611.5832104537112</v>
       </c>
       <c r="C128" t="n">
-        <v>635.9605885584036</v>
+        <v>612.4323990135786</v>
       </c>
       <c r="D128" t="n">
-        <v>621.1243629754691</v>
+        <v>601.7023533616688</v>
       </c>
       <c r="E128" t="n">
-        <v>622.0834350585938</v>
+        <v>606.1382446289062</v>
       </c>
       <c r="F128" t="n">
-        <v>10348800</v>
+        <v>13247700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B129" t="n">
-        <v>615.7693473594539</v>
+        <v>602.9712077810872</v>
       </c>
       <c r="C129" t="n">
-        <v>622.0735023862151</v>
+        <v>603.400802317344</v>
       </c>
       <c r="D129" t="n">
-        <v>614.04090772979</v>
+        <v>586.7062525156723</v>
       </c>
       <c r="E129" t="n">
-        <v>615.1099243164062</v>
+        <v>593.1102905273438</v>
       </c>
       <c r="F129" t="n">
-        <v>11726300</v>
+        <v>21214900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B130" t="n">
-        <v>611.5832104537112</v>
+        <v>605.2290499891692</v>
       </c>
       <c r="C130" t="n">
-        <v>612.4323990135786</v>
+        <v>608.0764476338709</v>
       </c>
       <c r="D130" t="n">
-        <v>601.7023533616688</v>
+        <v>598.4553596033379</v>
       </c>
       <c r="E130" t="n">
-        <v>606.1382446289062</v>
+        <v>603.5006713867188</v>
       </c>
       <c r="F130" t="n">
-        <v>13247700</v>
+        <v>13638000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B131" t="n">
-        <v>602.9712077810872</v>
+        <v>598.5452420228083</v>
       </c>
       <c r="C131" t="n">
-        <v>603.400802317344</v>
+        <v>600.443507118967</v>
       </c>
       <c r="D131" t="n">
-        <v>586.7062525156723</v>
+        <v>590.4527665679026</v>
       </c>
       <c r="E131" t="n">
-        <v>593.1102905273438</v>
+        <v>592.3709716796875</v>
       </c>
       <c r="F131" t="n">
-        <v>21214900</v>
+        <v>10739700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B132" t="n">
-        <v>605.2290499891692</v>
+        <v>598.1855830392399</v>
       </c>
       <c r="C132" t="n">
-        <v>608.0764476338709</v>
+        <v>603.1110107561809</v>
       </c>
       <c r="D132" t="n">
-        <v>598.4553596033379</v>
+        <v>592.8505617950721</v>
       </c>
       <c r="E132" t="n">
-        <v>603.5006713867188</v>
+        <v>594.3391723632812</v>
       </c>
       <c r="F132" t="n">
-        <v>13638000</v>
+        <v>12585000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B133" t="n">
-        <v>598.5452420228083</v>
+        <v>581.9506076701073</v>
       </c>
       <c r="C133" t="n">
-        <v>600.443507118967</v>
+        <v>582.460145169462</v>
       </c>
       <c r="D133" t="n">
-        <v>590.4527665679026</v>
+        <v>542.8468364624507</v>
       </c>
       <c r="E133" t="n">
-        <v>592.3709716796875</v>
+        <v>547.032958984375</v>
       </c>
       <c r="F133" t="n">
-        <v>10739700</v>
+        <v>35780100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B134" t="n">
-        <v>598.1855830392399</v>
+        <v>539.599843303006</v>
       </c>
       <c r="C134" t="n">
-        <v>603.1110107561809</v>
+        <v>543.0966023049141</v>
       </c>
       <c r="D134" t="n">
-        <v>592.8505617950721</v>
+        <v>519.7782492802263</v>
       </c>
       <c r="E134" t="n">
-        <v>594.3391723632812</v>
+        <v>525.233154296875</v>
       </c>
       <c r="F134" t="n">
-        <v>12585000</v>
+        <v>30133000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B135" t="n">
-        <v>581.9506076701073</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="C135" t="n">
-        <v>582.460145169462</v>
+        <v>539.0504095872608</v>
       </c>
       <c r="D135" t="n">
-        <v>542.8468364624507</v>
+        <v>528.0505941707193</v>
       </c>
       <c r="E135" t="n">
-        <v>547.032958984375</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="F135" t="n">
-        <v>35780100</v>
+        <v>22795200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B136" t="n">
-        <v>539.599843303006</v>
+        <v>549.4707059552647</v>
       </c>
       <c r="C136" t="n">
-        <v>543.0966023049141</v>
+        <v>573.1587727471259</v>
       </c>
       <c r="D136" t="n">
-        <v>519.7782492802263</v>
+        <v>546.2637174010383</v>
       </c>
       <c r="E136" t="n">
-        <v>525.233154296875</v>
+        <v>571.6002197265625</v>
       </c>
       <c r="F136" t="n">
-        <v>30133000</v>
+        <v>32898300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>535.8833618164062</v>
+        <v>579.5928556215499</v>
       </c>
       <c r="C137" t="n">
-        <v>539.0504095872608</v>
+        <v>592.0013387220274</v>
       </c>
       <c r="D137" t="n">
-        <v>528.0505941707193</v>
+        <v>573.2887005646345</v>
       </c>
       <c r="E137" t="n">
-        <v>535.8833618164062</v>
+        <v>578.6936645507812</v>
       </c>
       <c r="F137" t="n">
-        <v>22795200</v>
+        <v>23608100</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B138" t="n">
-        <v>549.4707059552647</v>
+        <v>565.5158531822124</v>
       </c>
       <c r="C138" t="n">
-        <v>573.1587727471259</v>
+        <v>577.9643377947169</v>
       </c>
       <c r="D138" t="n">
-        <v>546.2637174010383</v>
+        <v>559.1817578546791</v>
       </c>
       <c r="E138" t="n">
-        <v>571.6002197265625</v>
+        <v>573.9281005859375</v>
       </c>
       <c r="F138" t="n">
-        <v>32898300</v>
+        <v>13518500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B139" t="n">
-        <v>579.5928556215499</v>
+        <v>577.1550997330287</v>
       </c>
       <c r="C139" t="n">
-        <v>592.0013387220274</v>
+        <v>582.2503530791108</v>
       </c>
       <c r="D139" t="n">
-        <v>573.2887005646345</v>
+        <v>571.4703658572956</v>
       </c>
       <c r="E139" t="n">
-        <v>578.6936645507812</v>
+        <v>572.4894409179688</v>
       </c>
       <c r="F139" t="n">
-        <v>23608100</v>
+        <v>9515700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B140" t="n">
-        <v>565.5158531822124</v>
+        <v>571.9498894780604</v>
       </c>
       <c r="C140" t="n">
-        <v>577.9643377947169</v>
+        <v>574.6973431004155</v>
       </c>
       <c r="D140" t="n">
-        <v>559.1817578546791</v>
+        <v>564.2370671243236</v>
       </c>
       <c r="E140" t="n">
-        <v>573.9281005859375</v>
+        <v>574.5175170898438</v>
       </c>
       <c r="F140" t="n">
-        <v>13518500</v>
+        <v>9580800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B141" t="n">
-        <v>577.1550997330287</v>
+        <v>605.4388670235439</v>
       </c>
       <c r="C141" t="n">
-        <v>582.2503530791108</v>
+        <v>629.3667024291958</v>
       </c>
       <c r="D141" t="n">
-        <v>571.4703658572956</v>
+        <v>591.2820049792073</v>
       </c>
       <c r="E141" t="n">
-        <v>572.4894409179688</v>
+        <v>611.8529052734375</v>
       </c>
       <c r="F141" t="n">
-        <v>9515700</v>
+        <v>32036600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B142" t="n">
-        <v>571.9498894780604</v>
+        <v>626.3894374266143</v>
       </c>
       <c r="C142" t="n">
-        <v>574.6973431004155</v>
+        <v>636.9097166035551</v>
       </c>
       <c r="D142" t="n">
-        <v>564.2370671243236</v>
+        <v>622.4231426572783</v>
       </c>
       <c r="E142" t="n">
-        <v>574.5175170898438</v>
+        <v>627.8081665039062</v>
       </c>
       <c r="F142" t="n">
-        <v>9580800</v>
+        <v>19012900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B143" t="n">
-        <v>605.4388670235439</v>
+        <v>633.882449891805</v>
       </c>
       <c r="C143" t="n">
-        <v>629.3667024291958</v>
+        <v>637.9886903650855</v>
       </c>
       <c r="D143" t="n">
-        <v>591.2820049792073</v>
+        <v>623.7518859014353</v>
       </c>
       <c r="E143" t="n">
-        <v>611.8529052734375</v>
+        <v>629.2767333984375</v>
       </c>
       <c r="F143" t="n">
-        <v>32036600</v>
+        <v>13294800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B144" t="n">
-        <v>626.3894374266143</v>
+        <v>628.9171329935918</v>
       </c>
       <c r="C144" t="n">
-        <v>636.9097166035551</v>
+        <v>634.4120404303904</v>
       </c>
       <c r="D144" t="n">
-        <v>622.4231426572783</v>
+        <v>623.8218795800174</v>
       </c>
       <c r="E144" t="n">
-        <v>627.8081665039062</v>
+        <v>633.9425048828125</v>
       </c>
       <c r="F144" t="n">
-        <v>19012900</v>
+        <v>9538900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B145" t="n">
-        <v>633.882449891805</v>
+        <v>642.624350345733</v>
       </c>
       <c r="C145" t="n">
-        <v>637.9886903650855</v>
+        <v>665.6430543798978</v>
       </c>
       <c r="D145" t="n">
-        <v>623.7518859014353</v>
+        <v>638.7779398291946</v>
       </c>
       <c r="E145" t="n">
-        <v>629.2767333984375</v>
+        <v>661.8765258789062</v>
       </c>
       <c r="F145" t="n">
-        <v>13294800</v>
+        <v>17818000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B146" t="n">
-        <v>628.9171329935918</v>
+        <v>666.3824145357423</v>
       </c>
       <c r="C146" t="n">
-        <v>634.4120404303904</v>
+        <v>677.8717665104965</v>
       </c>
       <c r="D146" t="n">
-        <v>623.8218795800174</v>
+        <v>663.6049593103575</v>
       </c>
       <c r="E146" t="n">
-        <v>633.9425048828125</v>
+        <v>670.9581909179688</v>
       </c>
       <c r="F146" t="n">
-        <v>9538900</v>
+        <v>14952600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B147" t="n">
-        <v>642.624350345733</v>
+        <v>675.3640350842893</v>
       </c>
       <c r="C147" t="n">
-        <v>665.6430543798978</v>
+        <v>676.9525896021297</v>
       </c>
       <c r="D147" t="n">
-        <v>638.7779398291946</v>
+        <v>667.131674939706</v>
       </c>
       <c r="E147" t="n">
-        <v>661.8765258789062</v>
+        <v>676.2432250976562</v>
       </c>
       <c r="F147" t="n">
-        <v>17818000</v>
+        <v>9544800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B148" t="n">
-        <v>666.3824145357423</v>
+        <v>677.9716157075654</v>
       </c>
       <c r="C148" t="n">
-        <v>677.8717665104965</v>
+        <v>690.8796961433965</v>
       </c>
       <c r="D148" t="n">
-        <v>663.6049593103575</v>
+        <v>674.5048580761284</v>
       </c>
       <c r="E148" t="n">
-        <v>670.9581909179688</v>
+        <v>687.9124145507812</v>
       </c>
       <c r="F148" t="n">
-        <v>14952600</v>
+        <v>16283500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B149" t="n">
-        <v>675.3640350842893</v>
+        <v>680.7290935491282</v>
       </c>
       <c r="C149" t="n">
-        <v>676.9525896021297</v>
+        <v>682.7472426832454</v>
       </c>
       <c r="D149" t="n">
-        <v>667.131674939706</v>
+        <v>667.381478611767</v>
       </c>
       <c r="E149" t="n">
-        <v>676.2432250976562</v>
+        <v>670.2887573242188</v>
       </c>
       <c r="F149" t="n">
-        <v>9544800</v>
+        <v>12534000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B150" t="n">
-        <v>677.9716157075654</v>
+        <v>670.3786762058809</v>
       </c>
       <c r="C150" t="n">
-        <v>690.8796961433965</v>
+        <v>675.5738733736962</v>
       </c>
       <c r="D150" t="n">
-        <v>674.5048580761284</v>
+        <v>666.7120915784461</v>
       </c>
       <c r="E150" t="n">
-        <v>687.9124145507812</v>
+        <v>668.220703125</v>
       </c>
       <c r="F150" t="n">
-        <v>16283500</v>
+        <v>8660100</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B151" t="n">
-        <v>680.7290935491282</v>
+        <v>673.7355628200382</v>
       </c>
       <c r="C151" t="n">
-        <v>682.7472426832454</v>
+        <v>677.7518600207422</v>
       </c>
       <c r="D151" t="n">
-        <v>667.381478611767</v>
+        <v>669.1298460769134</v>
       </c>
       <c r="E151" t="n">
-        <v>670.2887573242188</v>
+        <v>674.09521484375</v>
       </c>
       <c r="F151" t="n">
-        <v>12534000</v>
+        <v>9215600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B152" t="n">
-        <v>670.3786762058809</v>
+        <v>663.0854475032797</v>
       </c>
       <c r="C152" t="n">
-        <v>675.5738733736962</v>
+        <v>668.9400066983026</v>
       </c>
       <c r="D152" t="n">
-        <v>666.7120915784461</v>
+        <v>652.4452846667049</v>
       </c>
       <c r="E152" t="n">
-        <v>668.220703125</v>
+        <v>658.5396728515625</v>
       </c>
       <c r="F152" t="n">
-        <v>8660100</v>
+        <v>11667000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B153" t="n">
-        <v>673.7355628200382</v>
+        <v>659.7085674039201</v>
       </c>
       <c r="C153" t="n">
-        <v>677.7518600207422</v>
+        <v>680.0396994180859</v>
       </c>
       <c r="D153" t="n">
-        <v>669.1298460769134</v>
+        <v>653.2345872360809</v>
       </c>
       <c r="E153" t="n">
-        <v>674.09521484375</v>
+        <v>674.4049682617188</v>
       </c>
       <c r="F153" t="n">
-        <v>9215600</v>
+        <v>13348300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B154" t="n">
-        <v>663.0854475032797</v>
+        <v>670.3786986745525</v>
       </c>
       <c r="C154" t="n">
-        <v>668.9400066983026</v>
+        <v>681.8680504402118</v>
       </c>
       <c r="D154" t="n">
-        <v>652.4452846667049</v>
+        <v>670.2188736545023</v>
       </c>
       <c r="E154" t="n">
-        <v>658.5396728515625</v>
+        <v>677.9916381835938</v>
       </c>
       <c r="F154" t="n">
-        <v>11667000</v>
+        <v>12805200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B155" t="n">
-        <v>659.7085674039201</v>
+        <v>673.6156618787633</v>
       </c>
       <c r="C155" t="n">
-        <v>680.0396994180859</v>
+        <v>677.5520159823654</v>
       </c>
       <c r="D155" t="n">
-        <v>653.2345872360809</v>
+        <v>665.0136491453696</v>
       </c>
       <c r="E155" t="n">
-        <v>674.4049682617188</v>
+        <v>670.7183837890625</v>
       </c>
       <c r="F155" t="n">
-        <v>13348300</v>
+        <v>10606800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B156" t="n">
-        <v>670.3786986745525</v>
+        <v>668.2905997420939</v>
       </c>
       <c r="C156" t="n">
-        <v>681.8680504402118</v>
+        <v>673.6256820299297</v>
       </c>
       <c r="D156" t="n">
-        <v>670.2188736545023</v>
+        <v>663.1953464496755</v>
       </c>
       <c r="E156" t="n">
-        <v>677.9916381835938</v>
+        <v>668.5004272460938</v>
       </c>
       <c r="F156" t="n">
-        <v>12805200</v>
+        <v>18947500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B157" t="n">
-        <v>673.6156618787633</v>
+        <v>618.7465567527638</v>
       </c>
       <c r="C157" t="n">
-        <v>677.5520159823654</v>
+        <v>620.2751083620838</v>
       </c>
       <c r="D157" t="n">
-        <v>665.0136491453696</v>
+        <v>599.4444385151393</v>
       </c>
       <c r="E157" t="n">
-        <v>670.7183837890625</v>
+        <v>611.3433837890625</v>
       </c>
       <c r="F157" t="n">
-        <v>10606800</v>
+        <v>52765000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B158" t="n">
-        <v>668.2905997420939</v>
+        <v>614.120842749119</v>
       </c>
       <c r="C158" t="n">
-        <v>673.6256820299297</v>
+        <v>618.3069655430758</v>
       </c>
       <c r="D158" t="n">
-        <v>663.1953464496755</v>
+        <v>605.5487701514051</v>
       </c>
       <c r="E158" t="n">
-        <v>668.5004272460938</v>
+        <v>608.1863403320312</v>
       </c>
       <c r="F158" t="n">
-        <v>18947500</v>
+        <v>21404000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="n">
-        <v>618.7465567527638</v>
+        <v>607.3771038685389</v>
       </c>
       <c r="C159" t="n">
-        <v>620.2751083620838</v>
+        <v>613.4314904063681</v>
       </c>
       <c r="D159" t="n">
-        <v>599.4444385151393</v>
+        <v>602.1919069095087</v>
       </c>
       <c r="E159" t="n">
-        <v>611.3433837890625</v>
+        <v>609.8447875976562</v>
       </c>
       <c r="F159" t="n">
-        <v>52765000</v>
+        <v>16203900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B160" t="n">
-        <v>614.120842749119</v>
+        <v>612.7420849871345</v>
       </c>
       <c r="C160" t="n">
-        <v>618.3069655430758</v>
+        <v>613.7811000159977</v>
       </c>
       <c r="D160" t="n">
-        <v>605.5487701514051</v>
+        <v>599.8040642277598</v>
       </c>
       <c r="E160" t="n">
-        <v>608.1863403320312</v>
+        <v>604.3998413085938</v>
       </c>
       <c r="F160" t="n">
-        <v>21404000</v>
+        <v>17171300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B161" t="n">
-        <v>607.3771038685389</v>
+        <v>600.4934370812971</v>
       </c>
       <c r="C161" t="n">
-        <v>613.4314904063681</v>
+        <v>619.3759607512419</v>
       </c>
       <c r="D161" t="n">
-        <v>602.1919069095087</v>
+        <v>597.5461564796674</v>
       </c>
       <c r="E161" t="n">
-        <v>609.8447875976562</v>
+        <v>612.3125</v>
       </c>
       <c r="F161" t="n">
-        <v>16203900</v>
+        <v>19915500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B162" t="n">
-        <v>612.7420849871345</v>
+        <v>614.150739078972</v>
       </c>
       <c r="C162" t="n">
-        <v>613.7811000159977</v>
+        <v>624.4012480600104</v>
       </c>
       <c r="D162" t="n">
-        <v>599.8040642277598</v>
+        <v>612.9718390781961</v>
       </c>
       <c r="E162" t="n">
-        <v>604.3998413085938</v>
+        <v>616.2388305664062</v>
       </c>
       <c r="F162" t="n">
-        <v>17171300</v>
+        <v>12307400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B163" t="n">
-        <v>600.4934370812971</v>
+        <v>614.6303402495529</v>
       </c>
       <c r="C163" t="n">
-        <v>619.3759607512419</v>
+        <v>616.1988937552933</v>
       </c>
       <c r="D163" t="n">
-        <v>597.5461564796674</v>
+        <v>605.4987892063378</v>
       </c>
       <c r="E163" t="n">
-        <v>612.3125</v>
+        <v>609.0654907226562</v>
       </c>
       <c r="F163" t="n">
-        <v>19915500</v>
+        <v>13557000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B164" t="n">
-        <v>614.150739078972</v>
+        <v>604.010215830275</v>
       </c>
       <c r="C164" t="n">
-        <v>624.4012480600104</v>
+        <v>604.3498668649182</v>
       </c>
       <c r="D164" t="n">
-        <v>612.9718390781961</v>
+        <v>597.5262348938886</v>
       </c>
       <c r="E164" t="n">
-        <v>616.2388305664062</v>
+        <v>598.3054809570312</v>
       </c>
       <c r="F164" t="n">
-        <v>12307400</v>
+        <v>15940600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B165" t="n">
-        <v>614.6303402495529</v>
+        <v>594.2692320029287</v>
       </c>
       <c r="C165" t="n">
-        <v>616.1988937552933</v>
+        <v>603.1909559259367</v>
       </c>
       <c r="D165" t="n">
-        <v>605.4987892063378</v>
+        <v>592.0512559095129</v>
       </c>
       <c r="E165" t="n">
-        <v>609.0654907226562</v>
+        <v>602.441650390625</v>
       </c>
       <c r="F165" t="n">
-        <v>13557000</v>
+        <v>11351600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B166" t="n">
-        <v>604.010215830275</v>
+        <v>598.275515544453</v>
       </c>
       <c r="C166" t="n">
-        <v>604.3498668649182</v>
+        <v>619.3260125714435</v>
       </c>
       <c r="D166" t="n">
-        <v>597.5262348938886</v>
+        <v>596.1074810052941</v>
       </c>
       <c r="E166" t="n">
-        <v>598.3054809570312</v>
+        <v>616.0590209960938</v>
       </c>
       <c r="F166" t="n">
-        <v>15940600</v>
+        <v>14634400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B167" t="n">
-        <v>594.2692320029287</v>
+        <v>615.4296182023591</v>
       </c>
       <c r="C167" t="n">
-        <v>603.1909559259367</v>
+        <v>623.152441138389</v>
       </c>
       <c r="D167" t="n">
-        <v>592.0512559095129</v>
+        <v>614.4305441468357</v>
       </c>
       <c r="E167" t="n">
-        <v>602.441650390625</v>
+        <v>617.8573608398438</v>
       </c>
       <c r="F167" t="n">
-        <v>11351600</v>
+        <v>10651200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B168" t="n">
-        <v>598.275515544453</v>
+        <v>613.421486859321</v>
       </c>
       <c r="C168" t="n">
-        <v>619.3260125714435</v>
+        <v>620.6248329546977</v>
       </c>
       <c r="D168" t="n">
-        <v>596.1074810052941</v>
+        <v>608.7458274653094</v>
       </c>
       <c r="E168" t="n">
-        <v>616.0590209960938</v>
+        <v>613.6612548828125</v>
       </c>
       <c r="F168" t="n">
-        <v>14634400</v>
+        <v>13272600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B169" t="n">
-        <v>615.4296182023591</v>
+        <v>608.5459509764945</v>
       </c>
       <c r="C169" t="n">
-        <v>623.152441138389</v>
+        <v>615.0199919776213</v>
       </c>
       <c r="D169" t="n">
-        <v>614.4305441468357</v>
+        <v>603.1309869574205</v>
       </c>
       <c r="E169" t="n">
-        <v>617.8573608398438</v>
+        <v>610.64404296875</v>
       </c>
       <c r="F169" t="n">
-        <v>10651200</v>
+        <v>13772400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B170" t="n">
-        <v>613.421486859321</v>
+        <v>608.3561568042173</v>
       </c>
       <c r="C170" t="n">
-        <v>620.6248329546977</v>
+        <v>613.361527578881</v>
       </c>
       <c r="D170" t="n">
-        <v>608.7458274653094</v>
+        <v>599.9939118379299</v>
       </c>
       <c r="E170" t="n">
-        <v>613.6612548828125</v>
+        <v>602.052001953125</v>
       </c>
       <c r="F170" t="n">
-        <v>13272600</v>
+        <v>11749900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B171" t="n">
-        <v>608.5459509764945</v>
+        <v>600.2037495434126</v>
       </c>
       <c r="C171" t="n">
-        <v>615.0199919776213</v>
+        <v>607.4370360716302</v>
       </c>
       <c r="D171" t="n">
-        <v>603.1309869574205</v>
+        <v>597.2564688338498</v>
       </c>
       <c r="E171" t="n">
-        <v>610.64404296875</v>
+        <v>604.499755859375</v>
       </c>
       <c r="F171" t="n">
-        <v>13772400</v>
+        <v>11329700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B172" t="n">
-        <v>608.3561568042173</v>
+        <v>599.4443949814065</v>
       </c>
       <c r="C172" t="n">
-        <v>613.361527578881</v>
+        <v>609.0354809096541</v>
       </c>
       <c r="D172" t="n">
-        <v>599.9939118379299</v>
+        <v>594.2591985256718</v>
       </c>
       <c r="E172" t="n">
-        <v>602.052001953125</v>
+        <v>606.8175659179688</v>
       </c>
       <c r="F172" t="n">
-        <v>11749900</v>
+        <v>13476100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B173" t="n">
-        <v>600.2037495434126</v>
+        <v>607.3171451453314</v>
       </c>
       <c r="C173" t="n">
-        <v>607.4370360716302</v>
+        <v>614.2407210713809</v>
       </c>
       <c r="D173" t="n">
-        <v>597.2564688338498</v>
+        <v>606.3880135859368</v>
       </c>
       <c r="E173" t="n">
-        <v>604.499755859375</v>
+        <v>609.6949462890625</v>
       </c>
       <c r="F173" t="n">
-        <v>11329700</v>
+        <v>11688600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B174" t="n">
-        <v>599.4443949814065</v>
+        <v>608.3261927003538</v>
       </c>
       <c r="C174" t="n">
-        <v>609.0354809096541</v>
+        <v>613.9009818092591</v>
       </c>
       <c r="D174" t="n">
-        <v>594.2591985256718</v>
+        <v>604.7394901495815</v>
       </c>
       <c r="E174" t="n">
-        <v>606.8175659179688</v>
+        <v>611.7730102539062</v>
       </c>
       <c r="F174" t="n">
-        <v>13476100</v>
+        <v>12234200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B175" t="n">
-        <v>607.3171451453314</v>
+        <v>608.8357727220844</v>
       </c>
       <c r="C175" t="n">
-        <v>614.2407210713809</v>
+        <v>637.908804248614</v>
       </c>
       <c r="D175" t="n">
-        <v>606.3880135859368</v>
+        <v>608.4361186960156</v>
       </c>
       <c r="E175" t="n">
-        <v>609.6949462890625</v>
+        <v>634.6718139648438</v>
       </c>
       <c r="F175" t="n">
-        <v>11688600</v>
+        <v>23143600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B176" t="n">
-        <v>608.3261927003538</v>
+        <v>638.9078448274123</v>
       </c>
       <c r="C176" t="n">
-        <v>613.9009818092591</v>
+        <v>642.4046039468743</v>
       </c>
       <c r="D176" t="n">
-        <v>604.7394901495815</v>
+        <v>628.7272779804616</v>
       </c>
       <c r="E176" t="n">
-        <v>611.7730102539062</v>
+        <v>634.7017211914062</v>
       </c>
       <c r="F176" t="n">
-        <v>12234200</v>
+        <v>16772400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B177" t="n">
-        <v>608.8357727220844</v>
+        <v>632.9133899267435</v>
       </c>
       <c r="C177" t="n">
-        <v>637.908804248614</v>
+        <v>633.9124639439917</v>
       </c>
       <c r="D177" t="n">
-        <v>608.4361186960156</v>
+        <v>622.7727642602187</v>
       </c>
       <c r="E177" t="n">
-        <v>634.6718139648438</v>
+        <v>631.92431640625</v>
       </c>
       <c r="F177" t="n">
-        <v>23143600</v>
+        <v>19806500</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B178" t="n">
-        <v>638.9078448274123</v>
+        <v>629.8162791560948</v>
       </c>
       <c r="C178" t="n">
-        <v>642.4046039468743</v>
+        <v>635.1613007084701</v>
       </c>
       <c r="D178" t="n">
-        <v>628.7272779804616</v>
+        <v>598.9748694014791</v>
       </c>
       <c r="E178" t="n">
-        <v>634.7017211914062</v>
+        <v>599.9139404296875</v>
       </c>
       <c r="F178" t="n">
-        <v>16772400</v>
+        <v>29138800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B179" t="n">
-        <v>632.9133899267435</v>
+        <v>602.6813896226799</v>
       </c>
       <c r="C179" t="n">
-        <v>633.9124639439917</v>
+        <v>608.3161816139932</v>
       </c>
       <c r="D179" t="n">
-        <v>622.7727642602187</v>
+        <v>596.1274666259658</v>
       </c>
       <c r="E179" t="n">
-        <v>631.92431640625</v>
+        <v>597.0765991210938</v>
       </c>
       <c r="F179" t="n">
-        <v>19806500</v>
+        <v>18252000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B180" t="n">
-        <v>629.8162791560948</v>
+        <v>602.4416570391962</v>
       </c>
       <c r="C180" t="n">
-        <v>635.1613007084701</v>
+        <v>623.5720977596394</v>
       </c>
       <c r="D180" t="n">
-        <v>598.9748694014791</v>
+        <v>599.7142043737263</v>
       </c>
       <c r="E180" t="n">
-        <v>599.9139404296875</v>
+        <v>622.4031372070312</v>
       </c>
       <c r="F180" t="n">
-        <v>29138800</v>
+        <v>23020100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B181" t="n">
-        <v>602.6813896226799</v>
+        <v>623.0924785224576</v>
       </c>
       <c r="C181" t="n">
-        <v>608.3161816139932</v>
+        <v>641.8051764288737</v>
       </c>
       <c r="D181" t="n">
-        <v>596.1274666259658</v>
+        <v>621.8536364911718</v>
       </c>
       <c r="E181" t="n">
-        <v>597.0765991210938</v>
+        <v>626.9888916015625</v>
       </c>
       <c r="F181" t="n">
-        <v>18252000</v>
+        <v>21469200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B182" t="n">
-        <v>602.4416570391962</v>
+        <v>622.8827460758752</v>
       </c>
       <c r="C182" t="n">
-        <v>623.5720977596394</v>
+        <v>628.5674800138549</v>
       </c>
       <c r="D182" t="n">
-        <v>599.7142043737263</v>
+        <v>582.3702434655938</v>
       </c>
       <c r="E182" t="n">
-        <v>622.4031372070312</v>
+        <v>592.450927734375</v>
       </c>
       <c r="F182" t="n">
-        <v>23020100</v>
+        <v>30091600</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B183" t="n">
-        <v>623.0924785224576</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="C183" t="n">
-        <v>641.8051764288737</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="D183" t="n">
-        <v>621.8536364911718</v>
+        <v>578.6836307521693</v>
       </c>
       <c r="E183" t="n">
-        <v>626.9888916015625</v>
+        <v>584.8479614257812</v>
       </c>
       <c r="F183" t="n">
-        <v>21469200</v>
+        <v>19512400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B184" t="n">
-        <v>622.8827460758752</v>
+        <v>590.4527436689563</v>
       </c>
       <c r="C184" t="n">
-        <v>628.5674800138549</v>
+        <v>597.0766092757164</v>
       </c>
       <c r="D184" t="n">
-        <v>582.3702434655938</v>
+        <v>580.4720040020986</v>
       </c>
       <c r="E184" t="n">
-        <v>592.450927734375</v>
+        <v>584.0487060546875</v>
       </c>
       <c r="F184" t="n">
-        <v>30091600</v>
+        <v>16977400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B185" t="n">
-        <v>591.4518261333767</v>
+        <v>580.192266144374</v>
       </c>
       <c r="C185" t="n">
-        <v>591.4518261333767</v>
+        <v>590.7724873942649</v>
       </c>
       <c r="D185" t="n">
-        <v>578.6836307521693</v>
+        <v>570.0716409197756</v>
       </c>
       <c r="E185" t="n">
-        <v>584.8479614257812</v>
+        <v>570.4512939453125</v>
       </c>
       <c r="F185" t="n">
-        <v>19512400</v>
+        <v>17064000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B186" t="n">
-        <v>590.4527436689563</v>
+        <v>565.3060574843756</v>
       </c>
       <c r="C186" t="n">
-        <v>597.0766092757164</v>
+        <v>571.6401524850257</v>
       </c>
       <c r="D186" t="n">
-        <v>580.4720040020986</v>
+        <v>556.4942175026772</v>
       </c>
       <c r="E186" t="n">
-        <v>584.0487060546875</v>
+        <v>567.9036254882812</v>
       </c>
       <c r="F186" t="n">
-        <v>16977400</v>
+        <v>17628000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B187" t="n">
-        <v>580.192266144374</v>
+        <v>572.4194595335534</v>
       </c>
       <c r="C187" t="n">
-        <v>590.7724873942649</v>
+        <v>575.5365655300229</v>
       </c>
       <c r="D187" t="n">
-        <v>570.0716409197756</v>
+        <v>560.3806300495169</v>
       </c>
       <c r="E187" t="n">
-        <v>570.4512939453125</v>
+        <v>566.4549560546875</v>
       </c>
       <c r="F187" t="n">
-        <v>17064000</v>
+        <v>14326400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,25 +5305,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B188" t="n">
-        <v>565.3060574843756</v>
+        <v>579.9000244140625</v>
       </c>
       <c r="C188" t="n">
-        <v>571.6401524850257</v>
+        <v>601.27001953125</v>
       </c>
       <c r="D188" t="n">
-        <v>556.4942175026772</v>
+        <v>579.2999877929688</v>
       </c>
       <c r="E188" t="n">
-        <v>567.9036254882812</v>
+        <v>593.47998046875</v>
       </c>
       <c r="F188" t="n">
-        <v>17628000</v>
+        <v>17653300</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B189" t="n">
-        <v>572.4194595335534</v>
+        <v>593.6500244140625</v>
       </c>
       <c r="C189" t="n">
-        <v>575.5365655300229</v>
+        <v>605.8099975585938</v>
       </c>
       <c r="D189" t="n">
-        <v>560.3806300495169</v>
+        <v>592</v>
       </c>
       <c r="E189" t="n">
-        <v>566.4549560546875</v>
+        <v>600.2100219726562</v>
       </c>
       <c r="F189" t="n">
-        <v>14326400</v>
+        <v>11344400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,25 +5357,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B190" t="n">
-        <v>579.9000244140625</v>
+        <v>592</v>
       </c>
       <c r="C190" t="n">
-        <v>601.27001953125</v>
+        <v>593.8099975585938</v>
       </c>
       <c r="D190" t="n">
-        <v>579.2999877929688</v>
+        <v>566.1900024414062</v>
       </c>
       <c r="E190" t="n">
-        <v>593.47998046875</v>
+        <v>567.5800170898438</v>
       </c>
       <c r="F190" t="n">
-        <v>17653300</v>
+        <v>20478300</v>
       </c>
       <c r="G190" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B191" t="n">
-        <v>593.6500244140625</v>
+        <v>572.8200073242188</v>
       </c>
       <c r="C191" t="n">
-        <v>605.8099975585938</v>
+        <v>580.219970703125</v>
       </c>
       <c r="D191" t="n">
-        <v>592</v>
+        <v>563.0999755859375</v>
       </c>
       <c r="E191" t="n">
-        <v>600.2100219726562</v>
+        <v>577.219970703125</v>
       </c>
       <c r="F191" t="n">
-        <v>11344400</v>
+        <v>28824600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B192" t="n">
-        <v>592</v>
+        <v>572.02001953125</v>
       </c>
       <c r="C192" t="n">
-        <v>593.8099975585938</v>
+        <v>575.8099975585938</v>
       </c>
       <c r="D192" t="n">
-        <v>566.1900024414062</v>
+        <v>559.8099975585938</v>
       </c>
       <c r="E192" t="n">
-        <v>567.5800170898438</v>
+        <v>563.8499755859375</v>
       </c>
       <c r="F192" t="n">
-        <v>20478300</v>
+        <v>15405500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B193" t="n">
-        <v>572.8200073242188</v>
+        <v>562.25</v>
       </c>
       <c r="C193" t="n">
-        <v>580.219970703125</v>
+        <v>572.2000122070312</v>
       </c>
       <c r="D193" t="n">
-        <v>563.0999755859375</v>
+        <v>561.02001953125</v>
       </c>
       <c r="E193" t="n">
-        <v>577.219970703125</v>
+        <v>562.2000122070312</v>
       </c>
       <c r="F193" t="n">
-        <v>28824600</v>
+        <v>13103300</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B194" t="n">
-        <v>572.02001953125</v>
+        <v>561.8900146484375</v>
       </c>
       <c r="C194" t="n">
-        <v>575.8099975585938</v>
+        <v>569.0399780273438</v>
       </c>
       <c r="D194" t="n">
-        <v>559.8099975585938</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="E194" t="n">
-        <v>563.8499755859375</v>
+        <v>557.6699829101562</v>
       </c>
       <c r="F194" t="n">
-        <v>15405500</v>
+        <v>13963600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B195" t="n">
-        <v>562.25</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="C195" t="n">
-        <v>572.2000122070312</v>
+        <v>556.3400268554688</v>
       </c>
       <c r="D195" t="n">
-        <v>561.02001953125</v>
+        <v>540.1799926757812</v>
       </c>
       <c r="E195" t="n">
-        <v>562.2000122070312</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="F195" t="n">
-        <v>13103300</v>
+        <v>16968600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B196" t="n">
-        <v>561.8900146484375</v>
+        <v>543.3400268554688</v>
       </c>
       <c r="C196" t="n">
-        <v>569.0399780273438</v>
+        <v>556.8499755859375</v>
       </c>
       <c r="D196" t="n">
-        <v>555.5499877929688</v>
+        <v>540.4000244140625</v>
       </c>
       <c r="E196" t="n">
-        <v>557.6699829101562</v>
+        <v>550.25</v>
       </c>
       <c r="F196" t="n">
-        <v>13963600</v>
+        <v>18867700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B197" t="n">
-        <v>555.5499877929688</v>
+        <v>560</v>
       </c>
       <c r="C197" t="n">
-        <v>556.3400268554688</v>
+        <v>570.9000244140625</v>
       </c>
       <c r="D197" t="n">
-        <v>540.1799926757812</v>
+        <v>558</v>
       </c>
       <c r="E197" t="n">
-        <v>542.8699951171875</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="F197" t="n">
-        <v>16968600</v>
+        <v>15011400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B198" t="n">
-        <v>543.3400268554688</v>
+        <v>560.9400024414062</v>
       </c>
       <c r="C198" t="n">
-        <v>556.8499755859375</v>
+        <v>565.5399780273438</v>
       </c>
       <c r="D198" t="n">
-        <v>540.4000244140625</v>
+        <v>551.4299926757812</v>
       </c>
       <c r="E198" t="n">
-        <v>550.25</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F198" t="n">
-        <v>18867700</v>
+        <v>18111100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B199" t="n">
-        <v>560</v>
+        <v>607.9099731445312</v>
       </c>
       <c r="C199" t="n">
-        <v>570.9000244140625</v>
+        <v>628.280029296875</v>
       </c>
       <c r="D199" t="n">
-        <v>558</v>
+        <v>595.0999755859375</v>
       </c>
       <c r="E199" t="n">
-        <v>562.5999755859375</v>
+        <v>612.9099731445312</v>
       </c>
       <c r="F199" t="n">
-        <v>15011400</v>
+        <v>45536300</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B200" t="n">
-        <v>560.9400024414062</v>
+        <v>607.9000244140625</v>
       </c>
       <c r="C200" t="n">
-        <v>565.5399780273438</v>
+        <v>610</v>
       </c>
       <c r="D200" t="n">
-        <v>551.4299926757812</v>
+        <v>580.4199829101562</v>
       </c>
       <c r="E200" t="n">
-        <v>563.2899780273438</v>
+        <v>582.9000244140625</v>
       </c>
       <c r="F200" t="n">
-        <v>18111100</v>
+        <v>21705900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B201" t="n">
-        <v>607.9099731445312</v>
+        <v>594.8400268554688</v>
       </c>
       <c r="C201" t="n">
-        <v>628.280029296875</v>
+        <v>603.5800170898438</v>
       </c>
       <c r="D201" t="n">
-        <v>595.0999755859375</v>
+        <v>581.760009765625</v>
       </c>
       <c r="E201" t="n">
-        <v>612.9099731445312</v>
+        <v>600.2899780273438</v>
       </c>
       <c r="F201" t="n">
-        <v>45536300</v>
+        <v>17674100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B202" t="n">
-        <v>607.9000244140625</v>
+        <v>607.5900268554688</v>
       </c>
       <c r="C202" t="n">
-        <v>610</v>
+        <v>625.3699951171875</v>
       </c>
       <c r="D202" t="n">
-        <v>580.4199829101562</v>
+        <v>603.6599731445312</v>
       </c>
       <c r="E202" t="n">
-        <v>582.9000244140625</v>
+        <v>615.5800170898438</v>
       </c>
       <c r="F202" t="n">
-        <v>21705900</v>
+        <v>18560800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B203" t="n">
-        <v>594.8400268554688</v>
+        <v>614.3900146484375</v>
       </c>
       <c r="C203" t="n">
-        <v>603.5800170898438</v>
+        <v>616</v>
       </c>
       <c r="D203" t="n">
-        <v>581.760009765625</v>
+        <v>598.010009765625</v>
       </c>
       <c r="E203" t="n">
-        <v>600.2899780273438</v>
+        <v>603.1199951171875</v>
       </c>
       <c r="F203" t="n">
-        <v>17674100</v>
+        <v>13606500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B204" t="n">
-        <v>607.5900268554688</v>
+        <v>583.989990234375</v>
       </c>
       <c r="C204" t="n">
-        <v>625.3699951171875</v>
+        <v>633.27001953125</v>
       </c>
       <c r="D204" t="n">
-        <v>603.6599731445312</v>
+        <v>577.0700073242188</v>
       </c>
       <c r="E204" t="n">
-        <v>615.5800170898438</v>
+        <v>631.47998046875</v>
       </c>
       <c r="F204" t="n">
-        <v>18560800</v>
+        <v>26579700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B205" t="n">
-        <v>614.3900146484375</v>
+        <v>660.3400268554688</v>
       </c>
       <c r="C205" t="n">
-        <v>616</v>
+        <v>677.8599853515625</v>
       </c>
       <c r="D205" t="n">
-        <v>598.010009765625</v>
+        <v>658.010009765625</v>
       </c>
       <c r="E205" t="n">
-        <v>603.1199951171875</v>
+        <v>669.2100219726562</v>
       </c>
       <c r="F205" t="n">
-        <v>13606500</v>
+        <v>40608900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B206" t="n">
-        <v>583.989990234375</v>
+        <v>661.3800048828125</v>
       </c>
       <c r="C206" t="n">
-        <v>633.27001953125</v>
+        <v>676.6199951171875</v>
       </c>
       <c r="D206" t="n">
-        <v>577.0700073242188</v>
+        <v>654.2000122070312</v>
       </c>
       <c r="E206" t="n">
-        <v>631.47998046875</v>
+        <v>656.72998046875</v>
       </c>
       <c r="F206" t="n">
-        <v>26579700</v>
+        <v>19840700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>660.3400268554688</v>
+        <v>652</v>
       </c>
       <c r="C207" t="n">
-        <v>677.8599853515625</v>
+        <v>666.5</v>
       </c>
       <c r="D207" t="n">
-        <v>658.010009765625</v>
+        <v>649.0499877929688</v>
       </c>
       <c r="E207" t="n">
-        <v>669.2100219726562</v>
+        <v>661.0399780273438</v>
       </c>
       <c r="F207" t="n">
-        <v>40608900</v>
+        <v>16748200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>661.3800048828125</v>
+        <v>663.5999755859375</v>
       </c>
       <c r="C208" t="n">
-        <v>676.6199951171875</v>
+        <v>686.0800170898438</v>
       </c>
       <c r="D208" t="n">
-        <v>654.2000122070312</v>
+        <v>656.6599731445312</v>
       </c>
       <c r="E208" t="n">
-        <v>656.72998046875</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="F208" t="n">
-        <v>19840700</v>
+        <v>19003400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>652</v>
+        <v>677.280029296875</v>
       </c>
       <c r="C209" t="n">
-        <v>666.5</v>
+        <v>681.9000244140625</v>
       </c>
       <c r="D209" t="n">
-        <v>649.0499877929688</v>
+        <v>660.1599731445312</v>
       </c>
       <c r="E209" t="n">
-        <v>661.0399780273438</v>
+        <v>664.5399780273438</v>
       </c>
       <c r="F209" t="n">
-        <v>16748200</v>
+        <v>15816000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B210" t="n">
-        <v>663.5999755859375</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C210" t="n">
-        <v>686.0800170898438</v>
+        <v>652.2000122070312</v>
       </c>
       <c r="D210" t="n">
-        <v>656.6599731445312</v>
+        <v>626</v>
       </c>
       <c r="E210" t="n">
-        <v>681.3099975585938</v>
+        <v>646.010009765625</v>
       </c>
       <c r="F210" t="n">
-        <v>19003400</v>
+        <v>22267900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B211" t="n">
-        <v>677.280029296875</v>
+        <v>646.7000122070312</v>
       </c>
       <c r="C211" t="n">
-        <v>681.9000244140625</v>
+        <v>653.2999877929688</v>
       </c>
       <c r="D211" t="n">
-        <v>660.1599731445312</v>
+        <v>636.010009765625</v>
       </c>
       <c r="E211" t="n">
-        <v>664.5399780273438</v>
+        <v>645.8499755859375</v>
       </c>
       <c r="F211" t="n">
-        <v>15816000</v>
+        <v>10225200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B212" t="n">
-        <v>647.7000122070312</v>
+        <v>654.1799926757812</v>
       </c>
       <c r="C212" t="n">
-        <v>652.2000122070312</v>
+        <v>655.8800048828125</v>
       </c>
       <c r="D212" t="n">
-        <v>626</v>
+        <v>643.2000122070312</v>
       </c>
       <c r="E212" t="n">
-        <v>646.010009765625</v>
+        <v>643.8099975585938</v>
       </c>
       <c r="F212" t="n">
-        <v>22267900</v>
+        <v>9140500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B213" t="n">
-        <v>646.7000122070312</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C213" t="n">
-        <v>653.2999877929688</v>
+        <v>649</v>
       </c>
       <c r="D213" t="n">
-        <v>636.010009765625</v>
+        <v>624</v>
       </c>
       <c r="E213" t="n">
-        <v>645.8499755859375</v>
+        <v>627.1699829101562</v>
       </c>
       <c r="F213" t="n">
-        <v>10225200</v>
+        <v>11019600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B214" t="n">
-        <v>654.1799926757812</v>
+        <v>608.4099731445312</v>
       </c>
       <c r="C214" t="n">
-        <v>655.8800048828125</v>
+        <v>614.6500244140625</v>
       </c>
       <c r="D214" t="n">
-        <v>643.2000122070312</v>
+        <v>597.219970703125</v>
       </c>
       <c r="E214" t="n">
-        <v>643.8099975585938</v>
+        <v>606.0999755859375</v>
       </c>
       <c r="F214" t="n">
-        <v>9140500</v>
+        <v>15494800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B215" t="n">
-        <v>647.7000122070312</v>
+        <v>605.2999877929688</v>
       </c>
       <c r="C215" t="n">
-        <v>649</v>
+        <v>609.97998046875</v>
       </c>
       <c r="D215" t="n">
-        <v>624</v>
+        <v>594.4500122070312</v>
       </c>
       <c r="E215" t="n">
-        <v>627.1699829101562</v>
+        <v>595.1900024414062</v>
       </c>
       <c r="F215" t="n">
-        <v>11019600</v>
+        <v>11503500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B216" t="n">
-        <v>608.4099731445312</v>
+        <v>607.219970703125</v>
       </c>
       <c r="C216" t="n">
-        <v>614.6500244140625</v>
+        <v>611.260009765625</v>
       </c>
       <c r="D216" t="n">
-        <v>597.219970703125</v>
+        <v>593.1300048828125</v>
       </c>
       <c r="E216" t="n">
-        <v>606.0999755859375</v>
+        <v>593.8699951171875</v>
       </c>
       <c r="F216" t="n">
-        <v>15494800</v>
+        <v>11195300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B217" t="n">
-        <v>605.2999877929688</v>
+        <v>596.8200073242188</v>
       </c>
       <c r="C217" t="n">
-        <v>609.97998046875</v>
+        <v>601</v>
       </c>
       <c r="D217" t="n">
-        <v>594.4500122070312</v>
+        <v>587</v>
       </c>
       <c r="E217" t="n">
-        <v>595.1900024414062</v>
+        <v>593.4099731445312</v>
       </c>
       <c r="F217" t="n">
-        <v>11503500</v>
+        <v>12009300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B218" t="n">
-        <v>607.219970703125</v>
+        <v>593.25</v>
       </c>
       <c r="C218" t="n">
-        <v>611.260009765625</v>
+        <v>599.969970703125</v>
       </c>
       <c r="D218" t="n">
-        <v>593.1300048828125</v>
+        <v>582.219970703125</v>
       </c>
       <c r="E218" t="n">
-        <v>593.8699951171875</v>
+        <v>585.6099853515625</v>
       </c>
       <c r="F218" t="n">
-        <v>11195300</v>
+        <v>22371100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B219" t="n">
-        <v>596.8200073242188</v>
+        <v>526</v>
       </c>
       <c r="C219" t="n">
-        <v>601</v>
+        <v>539.8800048828125</v>
       </c>
       <c r="D219" t="n">
-        <v>587</v>
+        <v>524.489990234375</v>
       </c>
       <c r="E219" t="n">
-        <v>593.4099731445312</v>
+        <v>539.030029296875</v>
       </c>
       <c r="F219" t="n">
-        <v>12009300</v>
+        <v>42271500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B220" t="n">
-        <v>593.25</v>
+        <v>543.5999755859375</v>
       </c>
       <c r="C220" t="n">
-        <v>599.969970703125</v>
+        <v>558.3300170898438</v>
       </c>
       <c r="D220" t="n">
-        <v>582.219970703125</v>
+        <v>540.219970703125</v>
       </c>
       <c r="E220" t="n">
-        <v>585.6099853515625</v>
+        <v>556.7100219726562</v>
       </c>
       <c r="F220" t="n">
-        <v>22371100</v>
+        <v>24261500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B221" t="n">
-        <v>526</v>
+        <v>562.239990234375</v>
       </c>
       <c r="C221" t="n">
-        <v>539.8800048828125</v>
+        <v>597.52001953125</v>
       </c>
       <c r="D221" t="n">
-        <v>524.489990234375</v>
+        <v>559.3599853515625</v>
       </c>
       <c r="E221" t="n">
-        <v>539.030029296875</v>
+        <v>590.239990234375</v>
       </c>
       <c r="F221" t="n">
-        <v>42271500</v>
+        <v>25938100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B222" t="n">
-        <v>543.5999755859375</v>
+        <v>581.5</v>
       </c>
       <c r="C222" t="n">
-        <v>558.3300170898438</v>
+        <v>592.7899780273438</v>
       </c>
       <c r="D222" t="n">
-        <v>540.219970703125</v>
+        <v>578.25</v>
       </c>
       <c r="E222" t="n">
-        <v>556.7100219726562</v>
+        <v>587.9400024414062</v>
       </c>
       <c r="F222" t="n">
-        <v>24261500</v>
+        <v>17959200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B223" t="n">
-        <v>562.239990234375</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="C223" t="n">
-        <v>597.52001953125</v>
+        <v>601</v>
       </c>
       <c r="D223" t="n">
-        <v>559.3599853515625</v>
+        <v>580.1199951171875</v>
       </c>
       <c r="E223" t="n">
-        <v>590.239990234375</v>
+        <v>588.77001953125</v>
       </c>
       <c r="F223" t="n">
-        <v>25938100</v>
+        <v>14897200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B224" t="n">
-        <v>581.5</v>
+        <v>586.9500122070312</v>
       </c>
       <c r="C224" t="n">
-        <v>592.7899780273438</v>
+        <v>595.3099975585938</v>
       </c>
       <c r="D224" t="n">
-        <v>578.25</v>
+        <v>586</v>
       </c>
       <c r="E224" t="n">
-        <v>587.9400024414062</v>
+        <v>589.9000244140625</v>
       </c>
       <c r="F224" t="n">
-        <v>17959200</v>
+        <v>11811500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B225" t="n">
-        <v>600.4600219726562</v>
+        <v>585.6400146484375</v>
       </c>
       <c r="C225" t="n">
-        <v>601</v>
+        <v>598.739990234375</v>
       </c>
       <c r="D225" t="n">
-        <v>580.1199951171875</v>
+        <v>585.6199951171875</v>
       </c>
       <c r="E225" t="n">
-        <v>588.77001953125</v>
+        <v>592.0999755859375</v>
       </c>
       <c r="F225" t="n">
-        <v>14897200</v>
+        <v>11250300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B226" t="n">
-        <v>586.9500122070312</v>
+        <v>599.1300048828125</v>
       </c>
       <c r="C226" t="n">
-        <v>595.3099975585938</v>
+        <v>608.2100219726562</v>
       </c>
       <c r="D226" t="n">
-        <v>586</v>
+        <v>592.030029296875</v>
       </c>
       <c r="E226" t="n">
-        <v>589.9000244140625</v>
+        <v>594.9199829101562</v>
       </c>
       <c r="F226" t="n">
-        <v>11811500</v>
+        <v>14967300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B227" t="n">
-        <v>585.6400146484375</v>
+        <v>598</v>
       </c>
       <c r="C227" t="n">
-        <v>598.739990234375</v>
+        <v>612.4299926757812</v>
       </c>
       <c r="D227" t="n">
-        <v>585.6199951171875</v>
+        <v>593.4000244140625</v>
       </c>
       <c r="E227" t="n">
-        <v>592.0999755859375</v>
+        <v>599.1199951171875</v>
       </c>
       <c r="F227" t="n">
-        <v>11250300</v>
+        <v>13146900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B228" t="n">
-        <v>599.1300048828125</v>
+        <v>601.0700073242188</v>
       </c>
       <c r="C228" t="n">
-        <v>608.2100219726562</v>
+        <v>604.5</v>
       </c>
       <c r="D228" t="n">
-        <v>592.030029296875</v>
+        <v>578.2100219726562</v>
       </c>
       <c r="E228" t="n">
-        <v>594.9199829101562</v>
+        <v>578.8499755859375</v>
       </c>
       <c r="F228" t="n">
-        <v>14967300</v>
+        <v>16186900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B229" t="n">
-        <v>598</v>
+        <v>580.7100219726562</v>
       </c>
       <c r="C229" t="n">
-        <v>612.4299926757812</v>
+        <v>595.8499755859375</v>
       </c>
       <c r="D229" t="n">
-        <v>593.4000244140625</v>
+        <v>579.3900146484375</v>
       </c>
       <c r="E229" t="n">
-        <v>599.1199951171875</v>
+        <v>594.969970703125</v>
       </c>
       <c r="F229" t="n">
-        <v>13146900</v>
+        <v>11164200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B230" t="n">
-        <v>601.0700073242188</v>
+        <v>596.97998046875</v>
       </c>
       <c r="C230" t="n">
-        <v>604.5</v>
+        <v>601.8599853515625</v>
       </c>
       <c r="D230" t="n">
-        <v>578.2100219726562</v>
+        <v>589.2899780273438</v>
       </c>
       <c r="E230" t="n">
-        <v>578.8499755859375</v>
+        <v>589.8499755859375</v>
       </c>
       <c r="F230" t="n">
-        <v>16186900</v>
+        <v>8758000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B231" t="n">
-        <v>580.7100219726562</v>
+        <v>589.75</v>
       </c>
       <c r="C231" t="n">
-        <v>595.8499755859375</v>
+        <v>590.239990234375</v>
       </c>
       <c r="D231" t="n">
-        <v>579.3900146484375</v>
+        <v>564.75</v>
       </c>
       <c r="E231" t="n">
-        <v>594.969970703125</v>
+        <v>568.969970703125</v>
       </c>
       <c r="F231" t="n">
-        <v>11164200</v>
+        <v>17225600</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B232" t="n">
-        <v>596.97998046875</v>
+        <v>557.47998046875</v>
       </c>
       <c r="C232" t="n">
-        <v>601.8599853515625</v>
+        <v>560.6599731445312</v>
       </c>
       <c r="D232" t="n">
-        <v>589.2899780273438</v>
+        <v>543.2100219726562</v>
       </c>
       <c r="E232" t="n">
-        <v>589.8499755859375</v>
+        <v>543.6699829101562</v>
       </c>
       <c r="F232" t="n">
-        <v>8758000</v>
+        <v>27094900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B233" t="n">
-        <v>589.75</v>
+        <v>541.3400268554688</v>
       </c>
       <c r="C233" t="n">
-        <v>590.239990234375</v>
+        <v>554.0700073242188</v>
       </c>
       <c r="D233" t="n">
-        <v>564.75</v>
+        <v>537.27001953125</v>
       </c>
       <c r="E233" t="n">
-        <v>568.969970703125</v>
+        <v>546.030029296875</v>
       </c>
       <c r="F233" t="n">
-        <v>17225600</v>
+        <v>16971700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B234" t="n">
-        <v>557.47998046875</v>
+        <v>546.9500122070312</v>
       </c>
       <c r="C234" t="n">
-        <v>560.6599731445312</v>
+        <v>549.989990234375</v>
       </c>
       <c r="D234" t="n">
-        <v>543.2100219726562</v>
+        <v>539.3099975585938</v>
       </c>
       <c r="E234" t="n">
-        <v>543.6699829101562</v>
+        <v>545.8300170898438</v>
       </c>
       <c r="F234" t="n">
-        <v>27094900</v>
+        <v>13872200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B235" t="n">
-        <v>541.3400268554688</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="C235" t="n">
-        <v>554.0700073242188</v>
+        <v>553.8699951171875</v>
       </c>
       <c r="D235" t="n">
-        <v>537.27001953125</v>
+        <v>543.22998046875</v>
       </c>
       <c r="E235" t="n">
-        <v>546.030029296875</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="F235" t="n">
-        <v>16971700</v>
+        <v>13848000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B236" t="n">
-        <v>546.9500122070312</v>
+        <v>550.2000122070312</v>
       </c>
       <c r="C236" t="n">
-        <v>549.989990234375</v>
+        <v>561.4199829101562</v>
       </c>
       <c r="D236" t="n">
-        <v>539.3099975585938</v>
+        <v>546.2999877929688</v>
       </c>
       <c r="E236" t="n">
-        <v>545.8300170898438</v>
+        <v>559.02001953125</v>
       </c>
       <c r="F236" t="n">
-        <v>13872200</v>
+        <v>12990600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B237" t="n">
-        <v>546.8900146484375</v>
+        <v>563.8800048828125</v>
       </c>
       <c r="C237" t="n">
-        <v>553.8699951171875</v>
+        <v>570.7999877929688</v>
       </c>
       <c r="D237" t="n">
-        <v>543.22998046875</v>
+        <v>561.4000244140625</v>
       </c>
       <c r="E237" t="n">
-        <v>549.9000244140625</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="F237" t="n">
-        <v>13848000</v>
+        <v>9769100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B238" t="n">
-        <v>550.2000122070312</v>
+        <v>590.3099975585938</v>
       </c>
       <c r="C238" t="n">
-        <v>561.4199829101562</v>
+        <v>593.3400268554688</v>
       </c>
       <c r="D238" t="n">
-        <v>546.2999877929688</v>
+        <v>561.8800048828125</v>
       </c>
       <c r="E238" t="n">
-        <v>559.02001953125</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="F238" t="n">
-        <v>12990600</v>
+        <v>31416300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B239" t="n">
-        <v>563.8800048828125</v>
+        <v>576.47998046875</v>
       </c>
       <c r="C239" t="n">
-        <v>570.7999877929688</v>
+        <v>588.3900146484375</v>
       </c>
       <c r="D239" t="n">
-        <v>561.4000244140625</v>
+        <v>567.6199951171875</v>
       </c>
       <c r="E239" t="n">
-        <v>570.0499877929688</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="F239" t="n">
-        <v>9769100</v>
+        <v>15221400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B240" t="n">
-        <v>590.3099975585938</v>
+        <v>571.5499877929688</v>
       </c>
       <c r="C240" t="n">
-        <v>593.3400268554688</v>
+        <v>589.1900024414062</v>
       </c>
       <c r="D240" t="n">
-        <v>561.8800048828125</v>
+        <v>571</v>
       </c>
       <c r="E240" t="n">
-        <v>576.1400146484375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="F240" t="n">
-        <v>31416300</v>
+        <v>16042400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B241" t="n">
-        <v>576.47998046875</v>
+        <v>577.6300048828125</v>
       </c>
       <c r="C241" t="n">
-        <v>588.3900146484375</v>
+        <v>578.6799926757812</v>
       </c>
       <c r="D241" t="n">
-        <v>567.6199951171875</v>
+        <v>569.1400146484375</v>
       </c>
       <c r="E241" t="n">
-        <v>571.0999755859375</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="F241" t="n">
-        <v>15221400</v>
+        <v>13383800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B242" t="n">
-        <v>571.5499877929688</v>
+        <v>558.3499755859375</v>
       </c>
       <c r="C242" t="n">
-        <v>589.1900024414062</v>
+        <v>584.9500122070312</v>
       </c>
       <c r="D242" t="n">
-        <v>571</v>
+        <v>556.0999755859375</v>
       </c>
       <c r="E242" t="n">
-        <v>578.02001953125</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="F242" t="n">
-        <v>16042400</v>
+        <v>15796900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B243" t="n">
-        <v>577.6300048828125</v>
+        <v>578.7899780273438</v>
       </c>
       <c r="C243" t="n">
-        <v>578.6799926757812</v>
+        <v>600.3800048828125</v>
       </c>
       <c r="D243" t="n">
-        <v>569.1400146484375</v>
+        <v>577</v>
       </c>
       <c r="E243" t="n">
-        <v>572.3400268554688</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="F243" t="n">
-        <v>13383800</v>
+        <v>16552700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B244" t="n">
-        <v>558.3499755859375</v>
+        <v>604.489990234375</v>
       </c>
       <c r="C244" t="n">
-        <v>584.9500122070312</v>
+        <v>619.4600219726562</v>
       </c>
       <c r="D244" t="n">
-        <v>556.0999755859375</v>
+        <v>604.3499755859375</v>
       </c>
       <c r="E244" t="n">
-        <v>578.5399780273438</v>
+        <v>610.6799926757812</v>
       </c>
       <c r="F244" t="n">
-        <v>15796900</v>
+        <v>19737100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B245" t="n">
-        <v>578.7899780273438</v>
+        <v>612.3499755859375</v>
       </c>
       <c r="C245" t="n">
-        <v>600.3800048828125</v>
+        <v>617.4600219726562</v>
       </c>
       <c r="D245" t="n">
-        <v>577</v>
+        <v>605.27001953125</v>
       </c>
       <c r="E245" t="n">
-        <v>592.8499755859375</v>
+        <v>616.77001953125</v>
       </c>
       <c r="F245" t="n">
-        <v>16552700</v>
+        <v>15966200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B246" t="n">
-        <v>604.489990234375</v>
+        <v>616.2100219726562</v>
       </c>
       <c r="C246" t="n">
-        <v>619.4600219726562</v>
+        <v>624.7999877929688</v>
       </c>
       <c r="D246" t="n">
-        <v>604.3499755859375</v>
+        <v>609.739990234375</v>
       </c>
       <c r="E246" t="n">
-        <v>610.6799926757812</v>
+        <v>613.47998046875</v>
       </c>
       <c r="F246" t="n">
-        <v>19737100</v>
+        <v>18909700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B247" t="n">
-        <v>612.3499755859375</v>
+        <v>648.6400146484375</v>
       </c>
       <c r="C247" t="n">
-        <v>617.4600219726562</v>
+        <v>657.8599853515625</v>
       </c>
       <c r="D247" t="n">
-        <v>605.27001953125</v>
+        <v>638.5599975585938</v>
       </c>
       <c r="E247" t="n">
-        <v>616.77001953125</v>
+        <v>653.6900024414062</v>
       </c>
       <c r="F247" t="n">
-        <v>15966200</v>
+        <v>35900700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B248" t="n">
-        <v>616.2100219726562</v>
+        <v>653.7100219726562</v>
       </c>
       <c r="C248" t="n">
-        <v>624.7999877929688</v>
+        <v>663.5</v>
       </c>
       <c r="D248" t="n">
-        <v>609.739990234375</v>
+        <v>642.1400146484375</v>
       </c>
       <c r="E248" t="n">
-        <v>613.47998046875</v>
+        <v>644.3800048828125</v>
       </c>
       <c r="F248" t="n">
-        <v>18909700</v>
+        <v>21531900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B249" t="n">
-        <v>648.6400146484375</v>
+        <v>653.510009765625</v>
       </c>
       <c r="C249" t="n">
-        <v>657.8599853515625</v>
+        <v>664.239990234375</v>
       </c>
       <c r="D249" t="n">
-        <v>638.5599975585938</v>
+        <v>646.2000122070312</v>
       </c>
       <c r="E249" t="n">
-        <v>653.6900024414062</v>
+        <v>648.030029296875</v>
       </c>
       <c r="F249" t="n">
-        <v>35900700</v>
+        <v>16925000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B250" t="n">
-        <v>653.7100219726562</v>
+        <v>657.8300170898438</v>
       </c>
       <c r="C250" t="n">
-        <v>663.5</v>
+        <v>668.5999755859375</v>
       </c>
       <c r="D250" t="n">
-        <v>642.1400146484375</v>
+        <v>649.219970703125</v>
       </c>
       <c r="E250" t="n">
-        <v>644.3800048828125</v>
+        <v>665.5999755859375</v>
       </c>
       <c r="F250" t="n">
-        <v>21531900</v>
+        <v>19332300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B251" t="n">
-        <v>653.510009765625</v>
+        <v>659.2999877929688</v>
       </c>
       <c r="C251" t="n">
-        <v>664.239990234375</v>
+        <v>678.8699951171875</v>
       </c>
       <c r="D251" t="n">
-        <v>646.2000122070312</v>
+        <v>656.2000122070312</v>
       </c>
       <c r="E251" t="n">
-        <v>648.030029296875</v>
+        <v>670.239990234375</v>
       </c>
       <c r="F251" t="n">
-        <v>16925000</v>
+        <v>19502800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,14 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B252" t="n">
-        <v>657.8300170898438</v>
-      </c>
-      <c r="C252" t="n">
-        <v>668.5999755859375</v>
-      </c>
-      <c r="D252" t="n">
-        <v>649.219970703125</v>
-      </c>
-      <c r="E252" t="n">
-        <v>665.5999755859375</v>
-      </c>
+        <v>46281</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>19300300</v>
+        <v>17169529</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,37 +10768,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>665.6</v>
+        <v>673.3099999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>648.03</v>
+        <v>670.24</v>
       </c>
       <c r="E2" t="n">
-        <v>657.62</v>
+        <v>679.75</v>
       </c>
       <c r="F2" t="n">
-        <v>668.6</v>
+        <v>685.3099999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>649.25</v>
+        <v>671.9142000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>19270307</v>
+        <v>17169529</v>
       </c>
       <c r="I2" t="n">
-        <v>18281088</v>
+        <v>18423041</v>
       </c>
       <c r="J2" t="n">
-        <v>1695620005888</v>
+        <v>1715261407232</v>
       </c>
       <c r="K2" t="n">
-        <v>25.050808</v>
+        <v>25.369629</v>
       </c>
       <c r="L2" t="n">
-        <v>19.039085</v>
+        <v>19.259626</v>
       </c>
       <c r="M2" t="n">
-        <v>26.57</v>
+        <v>26.54</v>
       </c>
       <c r="N2" t="n">
         <v>790.8</v>
@@ -10818,7 +10810,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10834,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.4923916</v>
+        <v>6.567597</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10846,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1717678112768</v>
+        <v>1729498578944</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10873,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:14:06</t>
+          <t>2026-09-17 08:09:53</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B2" t="n">
-        <v>777.4419836717854</v>
+        <v>778.1994774600552</v>
       </c>
       <c r="C2" t="n">
-        <v>780.731191338524</v>
+        <v>786.203274581819</v>
       </c>
       <c r="D2" t="n">
-        <v>763.8066796606671</v>
+        <v>770.8336042127465</v>
       </c>
       <c r="E2" t="n">
-        <v>773.1859130859375</v>
+        <v>777.7011108398438</v>
       </c>
       <c r="F2" t="n">
-        <v>9400900</v>
+        <v>10955000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B3" t="n">
-        <v>778.1994163857863</v>
+        <v>783.8508708699721</v>
       </c>
       <c r="C3" t="n">
-        <v>786.2032128794</v>
+        <v>788.2165669565625</v>
       </c>
       <c r="D3" t="n">
-        <v>770.8335437165625</v>
+        <v>766.6771780735046</v>
       </c>
       <c r="E3" t="n">
-        <v>777.7010498046875</v>
+        <v>775.837158203125</v>
       </c>
       <c r="F3" t="n">
-        <v>10955000</v>
+        <v>23696800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,25 +521,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B4" t="n">
-        <v>783.8509325355676</v>
+        <v>779.8217552362186</v>
       </c>
       <c r="C4" t="n">
-        <v>788.2166289656076</v>
+        <v>783.6916948825968</v>
       </c>
       <c r="D4" t="n">
-        <v>766.6772383880447</v>
+        <v>762.4868363426395</v>
       </c>
       <c r="E4" t="n">
-        <v>775.8372192382812</v>
+        <v>763.175048828125</v>
       </c>
       <c r="F4" t="n">
-        <v>23696800</v>
+        <v>11706900</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -547,25 +547,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B5" t="n">
-        <v>779.8217552362186</v>
+        <v>767.2545389947088</v>
       </c>
       <c r="C5" t="n">
-        <v>783.6916948825968</v>
+        <v>768.6010126974617</v>
       </c>
       <c r="D5" t="n">
-        <v>762.4868363426395</v>
+        <v>749.1217058463387</v>
       </c>
       <c r="E5" t="n">
-        <v>763.175048828125</v>
+        <v>753.4404907226562</v>
       </c>
       <c r="F5" t="n">
-        <v>11706900</v>
+        <v>10872600</v>
       </c>
       <c r="G5" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B6" t="n">
-        <v>767.2545389947088</v>
+        <v>755.5349308449814</v>
       </c>
       <c r="C6" t="n">
-        <v>768.6010126974617</v>
+        <v>759.1355513505183</v>
       </c>
       <c r="D6" t="n">
-        <v>749.1217058463387</v>
+        <v>750.5778529948334</v>
       </c>
       <c r="E6" t="n">
-        <v>753.4404907226562</v>
+        <v>758.6867065429688</v>
       </c>
       <c r="F6" t="n">
-        <v>10872600</v>
+        <v>8828200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B7" t="n">
-        <v>755.5349308449814</v>
+        <v>751.4954858581857</v>
       </c>
       <c r="C7" t="n">
-        <v>759.1355513505183</v>
+        <v>754.8068807440363</v>
       </c>
       <c r="D7" t="n">
-        <v>750.5778529948334</v>
+        <v>742.6185490172081</v>
       </c>
       <c r="E7" t="n">
-        <v>758.6867065429688</v>
+        <v>746.9672241210938</v>
       </c>
       <c r="F7" t="n">
-        <v>8828200</v>
+        <v>10591100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B8" t="n">
-        <v>751.4954858581857</v>
+        <v>748.0544659269957</v>
       </c>
       <c r="C8" t="n">
-        <v>754.8068807440363</v>
+        <v>749.9794521140951</v>
       </c>
       <c r="D8" t="n">
-        <v>742.6185490172081</v>
+        <v>735.4372562509625</v>
       </c>
       <c r="E8" t="n">
-        <v>746.9672241210938</v>
+        <v>741.8206787109375</v>
       </c>
       <c r="F8" t="n">
-        <v>10591100</v>
+        <v>9696300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B9" t="n">
-        <v>748.0544659269957</v>
+        <v>746.7777648139662</v>
       </c>
       <c r="C9" t="n">
-        <v>749.9794521140951</v>
+        <v>748.832479543402</v>
       </c>
       <c r="D9" t="n">
-        <v>735.4372562509625</v>
+        <v>737.2326433015477</v>
       </c>
       <c r="E9" t="n">
-        <v>741.8206787109375</v>
+        <v>741.4716186523438</v>
       </c>
       <c r="F9" t="n">
-        <v>9696300</v>
+        <v>9246800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B10" t="n">
-        <v>746.7777648139662</v>
+        <v>740.3245554260684</v>
       </c>
       <c r="C10" t="n">
-        <v>748.832479543402</v>
+        <v>741.0426584785586</v>
       </c>
       <c r="D10" t="n">
-        <v>737.2326433015477</v>
+        <v>724.4159185837501</v>
       </c>
       <c r="E10" t="n">
-        <v>741.4716186523438</v>
+        <v>732.4749755859375</v>
       </c>
       <c r="F10" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B11" t="n">
-        <v>740.3245554260684</v>
+        <v>719.618385039583</v>
       </c>
       <c r="C11" t="n">
-        <v>741.0426584785586</v>
+        <v>719.9774365591268</v>
       </c>
       <c r="D11" t="n">
-        <v>724.4159185837501</v>
+        <v>708.3576941566364</v>
       </c>
       <c r="E11" t="n">
-        <v>732.4749755859375</v>
+        <v>715.4791870117188</v>
       </c>
       <c r="F11" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B12" t="n">
-        <v>719.618385039583</v>
+        <v>720.7056259804448</v>
       </c>
       <c r="C12" t="n">
-        <v>719.9774365591268</v>
+        <v>725.8821654223162</v>
       </c>
       <c r="D12" t="n">
-        <v>708.3576941566364</v>
+        <v>716.2771410193245</v>
       </c>
       <c r="E12" t="n">
-        <v>715.4791870117188</v>
+        <v>725.1640014648438</v>
       </c>
       <c r="F12" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B13" t="n">
-        <v>720.7056259804448</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C13" t="n">
-        <v>725.8821654223162</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D13" t="n">
-        <v>716.2771410193245</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E13" t="n">
-        <v>725.1640014648438</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F13" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B14" t="n">
-        <v>727.7372737109582</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C14" t="n">
-        <v>729.1037149276121</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D14" t="n">
-        <v>708.3377167266436</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E14" t="n">
-        <v>708.7167358398438</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F14" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B15" t="n">
-        <v>703.3607165744016</v>
+        <v>715.8581417735932</v>
       </c>
       <c r="C15" t="n">
-        <v>715.0203947681905</v>
+        <v>716.6361476056489</v>
       </c>
       <c r="D15" t="n">
-        <v>688.718804278428</v>
+        <v>703.9192222306009</v>
       </c>
       <c r="E15" t="n">
-        <v>713.8035278320312</v>
+        <v>711.230224609375</v>
       </c>
       <c r="F15" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B16" t="n">
-        <v>715.8581417735932</v>
+        <v>711.5993392573523</v>
       </c>
       <c r="C16" t="n">
-        <v>716.6361476056489</v>
+        <v>717.783268775081</v>
       </c>
       <c r="D16" t="n">
-        <v>703.9192222306009</v>
+        <v>705.9739546774089</v>
       </c>
       <c r="E16" t="n">
-        <v>711.230224609375</v>
+        <v>715.9779663085938</v>
       </c>
       <c r="F16" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B17" t="n">
-        <v>711.5993392573523</v>
+        <v>716.4167658258609</v>
       </c>
       <c r="C17" t="n">
-        <v>717.783268775081</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="D17" t="n">
-        <v>705.9739546774089</v>
+        <v>710.5918883665408</v>
       </c>
       <c r="E17" t="n">
-        <v>715.9779663085938</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="F17" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B18" t="n">
-        <v>716.4167658258609</v>
+        <v>729.0239332852144</v>
       </c>
       <c r="C18" t="n">
-        <v>731.6072387695312</v>
+        <v>733.3626856542741</v>
       </c>
       <c r="D18" t="n">
-        <v>710.5918883665408</v>
+        <v>702.6824691715568</v>
       </c>
       <c r="E18" t="n">
-        <v>731.6072387695312</v>
+        <v>703.4703979492188</v>
       </c>
       <c r="F18" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B19" t="n">
-        <v>729.0239332852144</v>
+        <v>711.1603595995662</v>
       </c>
       <c r="C19" t="n">
-        <v>733.3626856542741</v>
+        <v>718.072374881022</v>
       </c>
       <c r="D19" t="n">
-        <v>702.6824691715568</v>
+        <v>705.8042950194317</v>
       </c>
       <c r="E19" t="n">
-        <v>703.4703979492188</v>
+        <v>713.8433837890625</v>
       </c>
       <c r="F19" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B20" t="n">
-        <v>711.1603595995662</v>
+        <v>705.9439682909708</v>
       </c>
       <c r="C20" t="n">
-        <v>718.072374881022</v>
+        <v>713.6937706407739</v>
       </c>
       <c r="D20" t="n">
-        <v>705.8042950194317</v>
+        <v>697.5158763660478</v>
       </c>
       <c r="E20" t="n">
-        <v>713.8433837890625</v>
+        <v>706.8117065429688</v>
       </c>
       <c r="F20" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B21" t="n">
-        <v>705.9439682909708</v>
+        <v>715.1998794771447</v>
       </c>
       <c r="C21" t="n">
-        <v>713.6937706407739</v>
+        <v>722.0221626881838</v>
       </c>
       <c r="D21" t="n">
-        <v>697.5158763660478</v>
+        <v>707.6694770310874</v>
       </c>
       <c r="E21" t="n">
-        <v>706.8117065429688</v>
+        <v>715.6885986328125</v>
       </c>
       <c r="F21" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B22" t="n">
-        <v>715.1998794771447</v>
+        <v>715.6886043056783</v>
       </c>
       <c r="C22" t="n">
-        <v>722.0221626881838</v>
+        <v>723.6080097298942</v>
       </c>
       <c r="D22" t="n">
-        <v>707.6694770310874</v>
+        <v>702.0540824517458</v>
       </c>
       <c r="E22" t="n">
-        <v>715.6885986328125</v>
+        <v>710.2228393554688</v>
       </c>
       <c r="F22" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B23" t="n">
-        <v>715.6886043056783</v>
+        <v>705.2458014471516</v>
       </c>
       <c r="C23" t="n">
-        <v>723.6080097298942</v>
+        <v>716.6760344343375</v>
       </c>
       <c r="D23" t="n">
-        <v>702.0540824517458</v>
+        <v>704.2882698394852</v>
       </c>
       <c r="E23" t="n">
-        <v>710.2228393554688</v>
+        <v>715.0602416992188</v>
       </c>
       <c r="F23" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B24" t="n">
-        <v>705.2458014471516</v>
+        <v>719.3191330444083</v>
       </c>
       <c r="C24" t="n">
-        <v>716.6760344343375</v>
+        <v>731.866515781436</v>
       </c>
       <c r="D24" t="n">
-        <v>704.2882698394852</v>
+        <v>718.3117433877071</v>
       </c>
       <c r="E24" t="n">
-        <v>715.0602416992188</v>
+        <v>730.2706298828125</v>
       </c>
       <c r="F24" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B25" t="n">
-        <v>719.3191330444083</v>
+        <v>734.1107864324557</v>
       </c>
       <c r="C25" t="n">
-        <v>731.866515781436</v>
+        <v>736.5843338414116</v>
       </c>
       <c r="D25" t="n">
-        <v>718.3117433877071</v>
+        <v>726.859625303898</v>
       </c>
       <c r="E25" t="n">
-        <v>730.2706298828125</v>
+        <v>731.367919921875</v>
       </c>
       <c r="F25" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B26" t="n">
-        <v>734.1107864324557</v>
+        <v>731.9264616753367</v>
       </c>
       <c r="C26" t="n">
-        <v>736.5843338414116</v>
+        <v>738.6788588958609</v>
       </c>
       <c r="D26" t="n">
-        <v>726.859625303898</v>
+        <v>722.1518950553793</v>
       </c>
       <c r="E26" t="n">
-        <v>731.367919921875</v>
+        <v>731.5075073242188</v>
       </c>
       <c r="F26" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B27" t="n">
-        <v>731.9264616753367</v>
+        <v>732.7941435868839</v>
       </c>
       <c r="C27" t="n">
-        <v>738.6788588958609</v>
+        <v>740.4841042897723</v>
       </c>
       <c r="D27" t="n">
-        <v>722.1518950553793</v>
+        <v>731.1982575844598</v>
       </c>
       <c r="E27" t="n">
-        <v>731.5075073242188</v>
+        <v>732.095947265625</v>
       </c>
       <c r="F27" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B28" t="n">
-        <v>732.7941435868839</v>
+        <v>734.8786455644157</v>
       </c>
       <c r="C28" t="n">
-        <v>740.4841042897723</v>
+        <v>739.2872233202683</v>
       </c>
       <c r="D28" t="n">
-        <v>731.1982575844598</v>
+        <v>729.2533227506186</v>
       </c>
       <c r="E28" t="n">
-        <v>732.095947265625</v>
+        <v>736.444580078125</v>
       </c>
       <c r="F28" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B29" t="n">
-        <v>734.8786455644157</v>
+        <v>747.7851152228061</v>
       </c>
       <c r="C29" t="n">
-        <v>739.2872233202683</v>
+        <v>753.7895182960361</v>
       </c>
       <c r="D29" t="n">
-        <v>729.2533227506186</v>
+        <v>746.069606274355</v>
       </c>
       <c r="E29" t="n">
-        <v>736.444580078125</v>
+        <v>748.872314453125</v>
       </c>
       <c r="F29" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B30" t="n">
-        <v>747.7851152228061</v>
+        <v>750.677577029167</v>
       </c>
       <c r="C30" t="n">
-        <v>753.7895182960361</v>
+        <v>756.4326283200122</v>
       </c>
       <c r="D30" t="n">
-        <v>746.069606274355</v>
+        <v>743.5860359773924</v>
       </c>
       <c r="E30" t="n">
-        <v>748.872314453125</v>
+        <v>749.4906616210938</v>
       </c>
       <c r="F30" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B31" t="n">
-        <v>750.677577029167</v>
+        <v>752.7920587752158</v>
       </c>
       <c r="C31" t="n">
-        <v>756.4326283200122</v>
+        <v>757.1905917498632</v>
       </c>
       <c r="D31" t="n">
-        <v>743.5860359773924</v>
+        <v>740.5838210171188</v>
       </c>
       <c r="E31" t="n">
-        <v>749.4906616210938</v>
+        <v>749.7200317382812</v>
       </c>
       <c r="F31" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B32" t="n">
-        <v>752.7920587752158</v>
+        <v>667.414190282622</v>
       </c>
       <c r="C32" t="n">
-        <v>757.1905917498632</v>
+        <v>679.1935516668058</v>
       </c>
       <c r="D32" t="n">
-        <v>740.5838210171188</v>
+        <v>648.4833846789722</v>
       </c>
       <c r="E32" t="n">
-        <v>749.7200317382812</v>
+        <v>664.7410888671875</v>
       </c>
       <c r="F32" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B33" t="n">
-        <v>667.414190282622</v>
+        <v>672.7603267493847</v>
       </c>
       <c r="C33" t="n">
-        <v>679.1935516668058</v>
+        <v>673.139345897249</v>
       </c>
       <c r="D33" t="n">
-        <v>648.4833846789722</v>
+        <v>643.8953948481166</v>
       </c>
       <c r="E33" t="n">
-        <v>664.7410888671875</v>
+        <v>646.6681518554688</v>
       </c>
       <c r="F33" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B34" t="n">
-        <v>672.7603267493847</v>
+        <v>654.2982567113449</v>
       </c>
       <c r="C34" t="n">
-        <v>673.139345897249</v>
+        <v>657.619635334369</v>
       </c>
       <c r="D34" t="n">
-        <v>643.8953948481166</v>
+        <v>634.5296648817072</v>
       </c>
       <c r="E34" t="n">
-        <v>646.6681518554688</v>
+        <v>636.0557250976562</v>
       </c>
       <c r="F34" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B35" t="n">
-        <v>654.2982567113449</v>
+        <v>626.4107910285981</v>
       </c>
       <c r="C35" t="n">
-        <v>657.619635334369</v>
+        <v>640.0752642850032</v>
       </c>
       <c r="D35" t="n">
-        <v>634.5296648817072</v>
+        <v>624.3860886703497</v>
       </c>
       <c r="E35" t="n">
-        <v>636.0557250976562</v>
+        <v>625.6926879882812</v>
       </c>
       <c r="F35" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B36" t="n">
-        <v>626.4107910285981</v>
+        <v>630.6697208898194</v>
       </c>
       <c r="C36" t="n">
-        <v>640.0752642850032</v>
+        <v>640.5639703518489</v>
       </c>
       <c r="D36" t="n">
-        <v>624.3860886703497</v>
+        <v>624.9146693781357</v>
       </c>
       <c r="E36" t="n">
-        <v>625.6926879882812</v>
+        <v>634.30029296875</v>
       </c>
       <c r="F36" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B37" t="n">
-        <v>630.6697208898194</v>
+        <v>634.2005186436334</v>
       </c>
       <c r="C37" t="n">
-        <v>640.5639703518489</v>
+        <v>634.3501538797125</v>
       </c>
       <c r="D37" t="n">
-        <v>624.9146693781357</v>
+        <v>616.3968476378337</v>
       </c>
       <c r="E37" t="n">
-        <v>634.30029296875</v>
+        <v>617.3344116210938</v>
       </c>
       <c r="F37" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B38" t="n">
-        <v>634.2005186436334</v>
+        <v>614.8907991985972</v>
       </c>
       <c r="C38" t="n">
-        <v>634.3501538797125</v>
+        <v>620.516183502649</v>
       </c>
       <c r="D38" t="n">
-        <v>616.3968476378337</v>
+        <v>599.6404837711106</v>
       </c>
       <c r="E38" t="n">
-        <v>617.3344116210938</v>
+        <v>620.0972900390625</v>
       </c>
       <c r="F38" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B39" t="n">
-        <v>614.8907991985972</v>
+        <v>629.4529708548182</v>
       </c>
       <c r="C39" t="n">
-        <v>620.516183502649</v>
+        <v>633.3528014765299</v>
       </c>
       <c r="D39" t="n">
-        <v>599.6404837711106</v>
+        <v>616.5065997528014</v>
       </c>
       <c r="E39" t="n">
-        <v>620.0972900390625</v>
+        <v>630.1212158203125</v>
       </c>
       <c r="F39" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B40" t="n">
-        <v>629.4529708548182</v>
+        <v>626.3709044869131</v>
       </c>
       <c r="C40" t="n">
-        <v>633.3528014765299</v>
+        <v>627.9268552540688</v>
       </c>
       <c r="D40" t="n">
-        <v>616.5065997528014</v>
+        <v>617.7832543081277</v>
       </c>
       <c r="E40" t="n">
-        <v>630.1212158203125</v>
+        <v>625.4533081054688</v>
       </c>
       <c r="F40" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B41" t="n">
-        <v>626.3709044869131</v>
+        <v>626.5005716840028</v>
       </c>
       <c r="C41" t="n">
-        <v>627.9268552540688</v>
+        <v>627.3583261459861</v>
       </c>
       <c r="D41" t="n">
-        <v>617.7832543081277</v>
+        <v>606.1934022078184</v>
       </c>
       <c r="E41" t="n">
-        <v>625.4533081054688</v>
+        <v>607.43017578125</v>
       </c>
       <c r="F41" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B42" t="n">
-        <v>626.5005716840028</v>
+        <v>611.4796659420805</v>
       </c>
       <c r="C42" t="n">
-        <v>627.3583261459861</v>
+        <v>616.0478021853295</v>
       </c>
       <c r="D42" t="n">
-        <v>606.1934022078184</v>
+        <v>601.4357808374693</v>
       </c>
       <c r="E42" t="n">
-        <v>607.43017578125</v>
+        <v>608.3079223632812</v>
       </c>
       <c r="F42" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B43" t="n">
-        <v>611.4796659420805</v>
+        <v>600.2288811530552</v>
       </c>
       <c r="C43" t="n">
-        <v>616.0478021853295</v>
+        <v>612.088052043071</v>
       </c>
       <c r="D43" t="n">
-        <v>601.4357808374693</v>
+        <v>593.6560102918138</v>
       </c>
       <c r="E43" t="n">
-        <v>608.3079223632812</v>
+        <v>607.8790283203125</v>
       </c>
       <c r="F43" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B44" t="n">
-        <v>600.2288811530552</v>
+        <v>607.4600964135232</v>
       </c>
       <c r="C44" t="n">
-        <v>612.088052043071</v>
+        <v>610.1032465254069</v>
       </c>
       <c r="D44" t="n">
-        <v>593.6560102918138</v>
+        <v>593.855525554584</v>
       </c>
       <c r="E44" t="n">
-        <v>607.8790283203125</v>
+        <v>600.4483642578125</v>
       </c>
       <c r="F44" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B45" t="n">
-        <v>607.4600964135232</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C45" t="n">
-        <v>610.1032465254069</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D45" t="n">
-        <v>593.855525554584</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E45" t="n">
-        <v>600.4483642578125</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F45" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B46" t="n">
-        <v>590.065358149623</v>
+        <v>592.1798400423816</v>
       </c>
       <c r="C46" t="n">
-        <v>602.0940719298206</v>
+        <v>593.7857099116716</v>
       </c>
       <c r="D46" t="n">
-        <v>582.2656968950795</v>
+        <v>579.7422168855177</v>
       </c>
       <c r="E46" t="n">
-        <v>596.1395874023438</v>
+        <v>588.7886962890625</v>
       </c>
       <c r="F46" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B47" t="n">
-        <v>592.1798400423816</v>
+        <v>601.9344542639864</v>
       </c>
       <c r="C47" t="n">
-        <v>593.7857099116716</v>
+        <v>605.1460720070379</v>
       </c>
       <c r="D47" t="n">
-        <v>579.7422168855177</v>
+        <v>581.8367012414765</v>
       </c>
       <c r="E47" t="n">
-        <v>588.7886962890625</v>
+        <v>587.6217041015625</v>
       </c>
       <c r="F47" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B48" t="n">
-        <v>601.9344542639864</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C48" t="n">
-        <v>605.1460720070379</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D48" t="n">
-        <v>581.8367012414765</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E48" t="n">
-        <v>587.6217041015625</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F48" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B49" t="n">
-        <v>586.9734117815261</v>
+        <v>597.1668126146857</v>
       </c>
       <c r="C49" t="n">
-        <v>596.5684523172222</v>
+        <v>615.1002115339802</v>
       </c>
       <c r="D49" t="n">
-        <v>580.3506215479276</v>
+        <v>596.0796743085915</v>
       </c>
       <c r="E49" t="n">
-        <v>592.70849609375</v>
+        <v>611.4596557617188</v>
       </c>
       <c r="F49" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B50" t="n">
-        <v>597.1668126146857</v>
+        <v>622.3812488080194</v>
       </c>
       <c r="C50" t="n">
-        <v>615.1002115339802</v>
+        <v>635.3973829418613</v>
       </c>
       <c r="D50" t="n">
-        <v>596.0796743085915</v>
+        <v>616.6960233021972</v>
       </c>
       <c r="E50" t="n">
-        <v>611.4596557617188</v>
+        <v>634.5695190429688</v>
       </c>
       <c r="F50" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B51" t="n">
-        <v>622.3812488080194</v>
+        <v>636.0358029520913</v>
       </c>
       <c r="C51" t="n">
-        <v>635.3973829418613</v>
+        <v>636.7040478933542</v>
       </c>
       <c r="D51" t="n">
-        <v>616.6960233021972</v>
+        <v>629.9915253276793</v>
       </c>
       <c r="E51" t="n">
-        <v>634.5695190429688</v>
+        <v>631.9663696289062</v>
       </c>
       <c r="F51" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B52" t="n">
-        <v>636.0358029520913</v>
+        <v>634.4299618769652</v>
       </c>
       <c r="C52" t="n">
-        <v>636.7040478933542</v>
+        <v>646.3688812783262</v>
       </c>
       <c r="D52" t="n">
-        <v>629.9915253276793</v>
+        <v>633.8514494094911</v>
       </c>
       <c r="E52" t="n">
-        <v>631.9663696289062</v>
+        <v>646.2691650390625</v>
       </c>
       <c r="F52" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B53" t="n">
-        <v>634.4299618769652</v>
+        <v>637.8908755177382</v>
       </c>
       <c r="C53" t="n">
-        <v>646.3688812783262</v>
+        <v>643.6459265392308</v>
       </c>
       <c r="D53" t="n">
-        <v>633.8514494094911</v>
+        <v>636.1055410281542</v>
       </c>
       <c r="E53" t="n">
-        <v>646.2691650390625</v>
+        <v>639.2074584960938</v>
       </c>
       <c r="F53" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B54" t="n">
-        <v>637.8908755177382</v>
+        <v>640.6737247939117</v>
       </c>
       <c r="C54" t="n">
-        <v>643.6459265392308</v>
+        <v>646.1893476978298</v>
       </c>
       <c r="D54" t="n">
-        <v>636.1055410281542</v>
+        <v>636.4147821721649</v>
       </c>
       <c r="E54" t="n">
-        <v>639.2074584960938</v>
+        <v>645.4213256835938</v>
       </c>
       <c r="F54" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B55" t="n">
-        <v>640.6737247939117</v>
+        <v>642.7383158920676</v>
       </c>
       <c r="C55" t="n">
-        <v>646.1893476978298</v>
+        <v>647.1668005690203</v>
       </c>
       <c r="D55" t="n">
-        <v>636.4147821721649</v>
+        <v>635.8961259576193</v>
       </c>
       <c r="E55" t="n">
-        <v>645.4213256835938</v>
+        <v>637.9407958984375</v>
       </c>
       <c r="F55" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B56" t="n">
-        <v>642.7383158920676</v>
+        <v>674.2463992276428</v>
       </c>
       <c r="C56" t="n">
-        <v>647.1668005690203</v>
+        <v>674.3461154685141</v>
       </c>
       <c r="D56" t="n">
-        <v>635.8961259576193</v>
+        <v>658.3377626918029</v>
       </c>
       <c r="E56" t="n">
-        <v>637.9407958984375</v>
+        <v>659.81396484375</v>
       </c>
       <c r="F56" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B57" t="n">
-        <v>674.2463992276428</v>
+        <v>662.2775487290173</v>
       </c>
       <c r="C57" t="n">
-        <v>674.3461154685141</v>
+        <v>672.9398207362489</v>
       </c>
       <c r="D57" t="n">
-        <v>658.3377626918029</v>
+        <v>660.6717397649775</v>
       </c>
       <c r="E57" t="n">
-        <v>659.81396484375</v>
+        <v>671.673095703125</v>
       </c>
       <c r="F57" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B58" t="n">
-        <v>662.2775487290173</v>
+        <v>667.603701448277</v>
       </c>
       <c r="C58" t="n">
-        <v>672.9398207362489</v>
+        <v>674.9545781663558</v>
       </c>
       <c r="D58" t="n">
-        <v>660.6717397649775</v>
+        <v>663.344758713728</v>
       </c>
       <c r="E58" t="n">
-        <v>671.673095703125</v>
+        <v>665.0702514648438</v>
       </c>
       <c r="F58" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B59" t="n">
-        <v>667.603701448277</v>
+        <v>662.0481300460407</v>
       </c>
       <c r="C59" t="n">
-        <v>674.9545781663558</v>
+        <v>662.7562492699393</v>
       </c>
       <c r="D59" t="n">
-        <v>663.344758713728</v>
+        <v>651.6451938720459</v>
       </c>
       <c r="E59" t="n">
-        <v>665.0702514648438</v>
+        <v>655.2557983398438</v>
       </c>
       <c r="F59" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B60" t="n">
-        <v>662.0481300460407</v>
+        <v>648.2640167126568</v>
       </c>
       <c r="C60" t="n">
-        <v>662.7562492699393</v>
+        <v>652.812185461044</v>
       </c>
       <c r="D60" t="n">
-        <v>651.6451938720459</v>
+        <v>641.7310198416047</v>
       </c>
       <c r="E60" t="n">
-        <v>655.2557983398438</v>
+        <v>648.4435424804688</v>
       </c>
       <c r="F60" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B61" t="n">
-        <v>648.2640167126568</v>
+        <v>641.6212380225077</v>
       </c>
       <c r="C61" t="n">
-        <v>652.812185461044</v>
+        <v>653.5801862453618</v>
       </c>
       <c r="D61" t="n">
-        <v>641.7310198416047</v>
+        <v>639.1377070000864</v>
       </c>
       <c r="E61" t="n">
-        <v>648.4435424804688</v>
+        <v>651.016845703125</v>
       </c>
       <c r="F61" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B62" t="n">
-        <v>641.6212380225077</v>
+        <v>648.1142734035774</v>
       </c>
       <c r="C62" t="n">
-        <v>653.5801862453618</v>
+        <v>709.1555202318053</v>
       </c>
       <c r="D62" t="n">
-        <v>639.1377070000864</v>
+        <v>636.9533001226623</v>
       </c>
       <c r="E62" t="n">
-        <v>651.016845703125</v>
+        <v>642.5587158203125</v>
       </c>
       <c r="F62" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,25 +2055,25 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B63" t="n">
-        <v>648.1142734035774</v>
+        <v>644.5502809809109</v>
       </c>
       <c r="C63" t="n">
-        <v>709.1555202318053</v>
+        <v>651.8372704406642</v>
       </c>
       <c r="D63" t="n">
-        <v>636.9533001226623</v>
+        <v>637.5627451568915</v>
       </c>
       <c r="E63" t="n">
-        <v>642.5587158203125</v>
+        <v>646.3570556640625</v>
       </c>
       <c r="F63" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2081,25 +2081,25 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B64" t="n">
-        <v>644.5502809809109</v>
+        <v>642.3541401459643</v>
       </c>
       <c r="C64" t="n">
-        <v>651.8372704406642</v>
+        <v>661.3602142938313</v>
       </c>
       <c r="D64" t="n">
-        <v>637.5627451568915</v>
+        <v>642.054686531657</v>
       </c>
       <c r="E64" t="n">
-        <v>646.3570556640625</v>
+        <v>655.9798583984375</v>
       </c>
       <c r="F64" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G64" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B65" t="n">
-        <v>642.3541401459643</v>
+        <v>654.4426118233187</v>
       </c>
       <c r="C65" t="n">
-        <v>661.3602142938313</v>
+        <v>660.0526000253047</v>
       </c>
       <c r="D65" t="n">
-        <v>642.054686531657</v>
+        <v>648.0440522221027</v>
       </c>
       <c r="E65" t="n">
-        <v>655.9798583984375</v>
+        <v>648.343505859375</v>
       </c>
       <c r="F65" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B66" t="n">
-        <v>654.4426118233187</v>
+        <v>655.8601356908653</v>
       </c>
       <c r="C66" t="n">
-        <v>660.0526000253047</v>
+        <v>669.366012780715</v>
       </c>
       <c r="D66" t="n">
-        <v>648.0440522221027</v>
+        <v>655.2911433094866</v>
       </c>
       <c r="E66" t="n">
-        <v>648.343505859375</v>
+        <v>663.2669067382812</v>
       </c>
       <c r="F66" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B67" t="n">
-        <v>655.8601356908653</v>
+        <v>665.2333263832898</v>
       </c>
       <c r="C67" t="n">
-        <v>669.366012780715</v>
+        <v>669.8051880946751</v>
       </c>
       <c r="D67" t="n">
-        <v>655.2911433094866</v>
+        <v>657.0080086354003</v>
       </c>
       <c r="E67" t="n">
-        <v>663.2669067382812</v>
+        <v>657.5969848632812</v>
       </c>
       <c r="F67" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B68" t="n">
-        <v>665.2333263832898</v>
+        <v>660.4718397886508</v>
       </c>
       <c r="C68" t="n">
-        <v>669.8051880946751</v>
+        <v>672.380589007267</v>
       </c>
       <c r="D68" t="n">
-        <v>657.0080086354003</v>
+        <v>655.4807431709672</v>
       </c>
       <c r="E68" t="n">
-        <v>657.5969848632812</v>
+        <v>660.3220825195312</v>
       </c>
       <c r="F68" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B69" t="n">
-        <v>660.4718397886508</v>
+        <v>658.8746741689592</v>
       </c>
       <c r="C69" t="n">
-        <v>672.380589007267</v>
+        <v>664.8140915262984</v>
       </c>
       <c r="D69" t="n">
-        <v>655.4807431709672</v>
+        <v>657.0778915122911</v>
       </c>
       <c r="E69" t="n">
-        <v>660.3220825195312</v>
+        <v>663.7559814453125</v>
       </c>
       <c r="F69" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B70" t="n">
-        <v>658.8746741689592</v>
+        <v>661.3503688947783</v>
       </c>
       <c r="C70" t="n">
-        <v>664.8140915262984</v>
+        <v>666.9902722948509</v>
       </c>
       <c r="D70" t="n">
-        <v>657.0778915122911</v>
+        <v>661.0209394131572</v>
       </c>
       <c r="E70" t="n">
-        <v>663.7559814453125</v>
+        <v>666.3613891601562</v>
       </c>
       <c r="F70" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B71" t="n">
-        <v>661.3503688947783</v>
+        <v>666.8704124858896</v>
       </c>
       <c r="C71" t="n">
-        <v>666.9902722948509</v>
+        <v>667.7588423243637</v>
       </c>
       <c r="D71" t="n">
-        <v>661.0209394131572</v>
+        <v>660.1424238558649</v>
       </c>
       <c r="E71" t="n">
-        <v>666.3613891601562</v>
+        <v>662.10888671875</v>
       </c>
       <c r="F71" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B72" t="n">
-        <v>666.8704124858896</v>
+        <v>656.8383689858442</v>
       </c>
       <c r="C72" t="n">
-        <v>667.7588423243637</v>
+        <v>659.0743707339258</v>
       </c>
       <c r="D72" t="n">
-        <v>660.1424238558649</v>
+        <v>653.2248195668056</v>
       </c>
       <c r="E72" t="n">
-        <v>662.10888671875</v>
+        <v>657.5171508789062</v>
       </c>
       <c r="F72" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B73" t="n">
-        <v>656.8383689858442</v>
+        <v>657.5171386037911</v>
       </c>
       <c r="C73" t="n">
-        <v>659.0743707339258</v>
+        <v>671.0230153954109</v>
       </c>
       <c r="D73" t="n">
-        <v>653.2248195668056</v>
+        <v>656.6686764849229</v>
       </c>
       <c r="E73" t="n">
-        <v>657.5171508789062</v>
+        <v>664.7642211914062</v>
       </c>
       <c r="F73" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B74" t="n">
-        <v>657.5171386037911</v>
+        <v>663.5663484641349</v>
       </c>
       <c r="C74" t="n">
-        <v>671.0230153954109</v>
+        <v>663.8159033150052</v>
       </c>
       <c r="D74" t="n">
-        <v>656.6686764849229</v>
+        <v>658.2658058687088</v>
       </c>
       <c r="E74" t="n">
-        <v>664.7642211914062</v>
+        <v>658.9146728515625</v>
       </c>
       <c r="F74" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B75" t="n">
-        <v>663.5663484641349</v>
+        <v>661.5499631466852</v>
       </c>
       <c r="C75" t="n">
-        <v>663.8159033150052</v>
+        <v>663.2070415689074</v>
       </c>
       <c r="D75" t="n">
-        <v>658.2658058687088</v>
+        <v>642.3542224297569</v>
       </c>
       <c r="E75" t="n">
-        <v>658.9146728515625</v>
+        <v>649.2518920898438</v>
       </c>
       <c r="F75" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B76" t="n">
-        <v>661.5499631466852</v>
+        <v>649.8508280292294</v>
       </c>
       <c r="C76" t="n">
-        <v>663.2070415689074</v>
+        <v>663.3567049684374</v>
       </c>
       <c r="D76" t="n">
-        <v>642.3542224297569</v>
+        <v>646.5966230035071</v>
       </c>
       <c r="E76" t="n">
-        <v>649.2518920898438</v>
+        <v>657.616943359375</v>
       </c>
       <c r="F76" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B77" t="n">
-        <v>649.8508280292294</v>
+        <v>658.3956073528642</v>
       </c>
       <c r="C77" t="n">
-        <v>663.3567049684374</v>
+        <v>664.3350252422523</v>
       </c>
       <c r="D77" t="n">
-        <v>646.5966230035071</v>
+        <v>650.7392812609531</v>
       </c>
       <c r="E77" t="n">
-        <v>657.616943359375</v>
+        <v>659.4437255859375</v>
       </c>
       <c r="F77" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B78" t="n">
-        <v>658.3956073528642</v>
+        <v>654.4726104611178</v>
       </c>
       <c r="C78" t="n">
-        <v>664.3350252422523</v>
+        <v>657.9763704555172</v>
       </c>
       <c r="D78" t="n">
-        <v>650.7392812609531</v>
+        <v>643.6618768302103</v>
       </c>
       <c r="E78" t="n">
-        <v>659.4437255859375</v>
+        <v>647.5349731445312</v>
       </c>
       <c r="F78" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B79" t="n">
-        <v>654.4726104611178</v>
+        <v>644.7299347572825</v>
       </c>
       <c r="C79" t="n">
-        <v>657.9763704555172</v>
+        <v>645.9477331499952</v>
       </c>
       <c r="D79" t="n">
-        <v>643.6618768302103</v>
+        <v>634.5879917891143</v>
       </c>
       <c r="E79" t="n">
-        <v>647.5349731445312</v>
+        <v>644.9096069335938</v>
       </c>
       <c r="F79" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B80" t="n">
-        <v>644.7299347572825</v>
+        <v>644.2906685217797</v>
       </c>
       <c r="C80" t="n">
-        <v>645.9477331499952</v>
+        <v>653.7837438291153</v>
       </c>
       <c r="D80" t="n">
-        <v>634.5879917891143</v>
+        <v>641.7052537227476</v>
       </c>
       <c r="E80" t="n">
-        <v>644.9096069335938</v>
+        <v>651.8970947265625</v>
       </c>
       <c r="F80" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B81" t="n">
-        <v>644.2906685217797</v>
+        <v>651.3681600668523</v>
       </c>
       <c r="C81" t="n">
-        <v>653.7837438291153</v>
+        <v>652.8055375702352</v>
       </c>
       <c r="D81" t="n">
-        <v>641.7052537227476</v>
+        <v>640.0882316599212</v>
       </c>
       <c r="E81" t="n">
-        <v>651.8970947265625</v>
+        <v>640.826904296875</v>
       </c>
       <c r="F81" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B82" t="n">
-        <v>651.3681600668523</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="C82" t="n">
-        <v>652.8055375702352</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="D82" t="n">
-        <v>640.0882316599212</v>
+        <v>622.9887038024194</v>
       </c>
       <c r="E82" t="n">
-        <v>640.826904296875</v>
+        <v>629.96630859375</v>
       </c>
       <c r="F82" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B83" t="n">
-        <v>641.1263941859123</v>
+        <v>625.3844405077801</v>
       </c>
       <c r="C83" t="n">
-        <v>641.1263941859123</v>
+        <v>627.3309804807691</v>
       </c>
       <c r="D83" t="n">
-        <v>622.9887038024194</v>
+        <v>613.7252454803604</v>
       </c>
       <c r="E83" t="n">
-        <v>629.96630859375</v>
+        <v>614.4240112304688</v>
       </c>
       <c r="F83" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B84" t="n">
-        <v>625.3844405077801</v>
+        <v>617.378703801015</v>
       </c>
       <c r="C84" t="n">
-        <v>627.3309804807691</v>
+        <v>623.0585745209008</v>
       </c>
       <c r="D84" t="n">
-        <v>613.7252454803604</v>
+        <v>613.1362714280776</v>
       </c>
       <c r="E84" t="n">
-        <v>614.4240112304688</v>
+        <v>619.694580078125</v>
       </c>
       <c r="F84" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B85" t="n">
-        <v>617.378703801015</v>
+        <v>623.0685636897582</v>
       </c>
       <c r="C85" t="n">
-        <v>623.0585745209008</v>
+        <v>627.9598630097294</v>
       </c>
       <c r="D85" t="n">
-        <v>613.1362714280776</v>
+        <v>618.9758886129073</v>
       </c>
       <c r="E85" t="n">
-        <v>619.694580078125</v>
+        <v>619.1455688476562</v>
       </c>
       <c r="F85" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B86" t="n">
-        <v>623.0685636897582</v>
+        <v>606.7976262932837</v>
       </c>
       <c r="C86" t="n">
-        <v>627.9598630097294</v>
+        <v>610.3113781504126</v>
       </c>
       <c r="D86" t="n">
-        <v>618.9758886129073</v>
+        <v>598.9316523845154</v>
       </c>
       <c r="E86" t="n">
-        <v>619.1455688476562</v>
+        <v>603.0443115234375</v>
       </c>
       <c r="F86" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B87" t="n">
-        <v>606.7976262932837</v>
+        <v>605.659634898437</v>
       </c>
       <c r="C87" t="n">
-        <v>610.3113781504126</v>
+        <v>617.169133937088</v>
       </c>
       <c r="D87" t="n">
-        <v>598.9316523845154</v>
+        <v>599.0115204374271</v>
       </c>
       <c r="E87" t="n">
-        <v>603.0443115234375</v>
+        <v>611.8685913085938</v>
       </c>
       <c r="F87" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B88" t="n">
-        <v>605.659634898437</v>
+        <v>628.2293275614567</v>
       </c>
       <c r="C88" t="n">
-        <v>617.169133937088</v>
+        <v>659.3937675491238</v>
       </c>
       <c r="D88" t="n">
-        <v>599.0115204374271</v>
+        <v>625.4343255489129</v>
       </c>
       <c r="E88" t="n">
-        <v>611.8685913085938</v>
+        <v>646.476806640625</v>
       </c>
       <c r="F88" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B89" t="n">
-        <v>628.2293275614567</v>
+        <v>643.6219561683764</v>
       </c>
       <c r="C89" t="n">
-        <v>659.3937675491238</v>
+        <v>665.3032527677875</v>
       </c>
       <c r="D89" t="n">
-        <v>625.4343255489129</v>
+        <v>643.3025186421843</v>
       </c>
       <c r="E89" t="n">
-        <v>646.476806640625</v>
+        <v>657.5870361328125</v>
       </c>
       <c r="F89" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B90" t="n">
-        <v>643.6219561683764</v>
+        <v>663.9456740004919</v>
       </c>
       <c r="C90" t="n">
-        <v>665.3032527677875</v>
+        <v>674.0776252750454</v>
       </c>
       <c r="D90" t="n">
-        <v>643.3025186421843</v>
+        <v>660.1124846991261</v>
       </c>
       <c r="E90" t="n">
-        <v>657.5870361328125</v>
+        <v>671.1627807617188</v>
       </c>
       <c r="F90" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B91" t="n">
-        <v>663.9456740004919</v>
+        <v>673.3888389297905</v>
       </c>
       <c r="C91" t="n">
-        <v>674.0776252750454</v>
+        <v>675.6148486525956</v>
       </c>
       <c r="D91" t="n">
-        <v>660.1124846991261</v>
+        <v>663.4764668627315</v>
       </c>
       <c r="E91" t="n">
-        <v>671.1627807617188</v>
+        <v>671.7716674804688</v>
       </c>
       <c r="F91" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B92" t="n">
-        <v>673.3888389297905</v>
+        <v>673.2989910894674</v>
       </c>
       <c r="C92" t="n">
-        <v>675.6148486525956</v>
+        <v>676.4733214975852</v>
       </c>
       <c r="D92" t="n">
-        <v>663.4764668627315</v>
+        <v>664.9139236867763</v>
       </c>
       <c r="E92" t="n">
-        <v>671.7716674804688</v>
+        <v>667.5392456054688</v>
       </c>
       <c r="F92" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B93" t="n">
-        <v>673.2989910894674</v>
+        <v>736.1169233837337</v>
       </c>
       <c r="C93" t="n">
-        <v>676.4733214975852</v>
+        <v>742.6752321400184</v>
       </c>
       <c r="D93" t="n">
-        <v>664.9139236867763</v>
+        <v>711.2812198864386</v>
       </c>
       <c r="E93" t="n">
-        <v>667.5392456054688</v>
+        <v>736.995361328125</v>
       </c>
       <c r="F93" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B94" t="n">
-        <v>736.1169233837337</v>
+        <v>726.2045952530067</v>
       </c>
       <c r="C94" t="n">
-        <v>742.6752321400184</v>
+        <v>730.8662626744616</v>
       </c>
       <c r="D94" t="n">
-        <v>711.2812198864386</v>
+        <v>712.3193905555435</v>
       </c>
       <c r="E94" t="n">
-        <v>736.995361328125</v>
+        <v>715.2241821289062</v>
       </c>
       <c r="F94" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B95" t="n">
-        <v>726.2045952530067</v>
+        <v>713.3275184694113</v>
       </c>
       <c r="C95" t="n">
-        <v>730.8662626744616</v>
+        <v>720.0156002559207</v>
       </c>
       <c r="D95" t="n">
-        <v>712.3193905555435</v>
+        <v>702.2672920108814</v>
       </c>
       <c r="E95" t="n">
-        <v>715.2241821289062</v>
+        <v>705.152099609375</v>
       </c>
       <c r="F95" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B96" t="n">
-        <v>713.3275184694113</v>
+        <v>706.1104025957663</v>
       </c>
       <c r="C96" t="n">
-        <v>720.0156002559207</v>
+        <v>715.7232596178901</v>
       </c>
       <c r="D96" t="n">
-        <v>702.2672920108814</v>
+        <v>685.1877035052055</v>
       </c>
       <c r="E96" t="n">
-        <v>705.152099609375</v>
+        <v>690.4683227539062</v>
       </c>
       <c r="F96" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B97" t="n">
-        <v>706.1104025957663</v>
+        <v>686.5053883494637</v>
       </c>
       <c r="C97" t="n">
-        <v>715.7232596178901</v>
+        <v>687.603466213174</v>
       </c>
       <c r="D97" t="n">
-        <v>685.1877035052055</v>
+        <v>666.2715231343633</v>
       </c>
       <c r="E97" t="n">
-        <v>690.4683227539062</v>
+        <v>667.7987670898438</v>
       </c>
       <c r="F97" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B98" t="n">
-        <v>686.5053883494637</v>
+        <v>662.3984025060512</v>
       </c>
       <c r="C98" t="n">
-        <v>687.603466213174</v>
+        <v>680.2864759062725</v>
       </c>
       <c r="D98" t="n">
-        <v>666.2715231343633</v>
+        <v>652.3363345630947</v>
       </c>
       <c r="E98" t="n">
-        <v>667.7987670898438</v>
+        <v>669.0166015625</v>
       </c>
       <c r="F98" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B99" t="n">
-        <v>662.3984025060512</v>
+        <v>664.3050190645899</v>
       </c>
       <c r="C99" t="n">
-        <v>680.2864759062725</v>
+        <v>670.7934451675868</v>
       </c>
       <c r="D99" t="n">
-        <v>652.3363345630947</v>
+        <v>645.3488423980709</v>
       </c>
       <c r="E99" t="n">
-        <v>669.0166015625</v>
+        <v>660.2822265625</v>
       </c>
       <c r="F99" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B100" t="n">
-        <v>664.3050190645899</v>
+        <v>661.9991209626965</v>
       </c>
       <c r="C100" t="n">
-        <v>670.7934451675868</v>
+        <v>682.0932819515241</v>
       </c>
       <c r="D100" t="n">
-        <v>645.3488423980709</v>
+        <v>657.6069922476072</v>
       </c>
       <c r="E100" t="n">
-        <v>660.2822265625</v>
+        <v>676.0140991210938</v>
       </c>
       <c r="F100" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B101" t="n">
-        <v>661.9991209626965</v>
+        <v>676.3934502400131</v>
       </c>
       <c r="C101" t="n">
-        <v>682.0932819515241</v>
+        <v>679.4380681924739</v>
       </c>
       <c r="D101" t="n">
-        <v>657.6069922476072</v>
+        <v>668.597359057372</v>
       </c>
       <c r="E101" t="n">
-        <v>676.0140991210938</v>
+        <v>669.5256958007812</v>
       </c>
       <c r="F101" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B102" t="n">
-        <v>676.3934502400131</v>
+        <v>672.7998711552045</v>
       </c>
       <c r="C102" t="n">
-        <v>679.4380681924739</v>
+        <v>678.0605068549233</v>
       </c>
       <c r="D102" t="n">
-        <v>668.597359057372</v>
+        <v>655.9299390360635</v>
       </c>
       <c r="E102" t="n">
-        <v>669.5256958007812</v>
+        <v>667.4993286132812</v>
       </c>
       <c r="F102" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B103" t="n">
-        <v>672.7998711552045</v>
+        <v>668.7770306530766</v>
       </c>
       <c r="C103" t="n">
-        <v>678.0605068549233</v>
+        <v>674.7963229561075</v>
       </c>
       <c r="D103" t="n">
-        <v>655.9299390360635</v>
+        <v>644.1310518439949</v>
       </c>
       <c r="E103" t="n">
-        <v>667.4993286132812</v>
+        <v>648.6529541015625</v>
       </c>
       <c r="F103" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B104" t="n">
-        <v>668.7770306530766</v>
+        <v>643.9513250294082</v>
       </c>
       <c r="C104" t="n">
-        <v>674.7963229561075</v>
+        <v>650.2700710327099</v>
       </c>
       <c r="D104" t="n">
-        <v>644.1310518439949</v>
+        <v>633.4401061931457</v>
       </c>
       <c r="E104" t="n">
-        <v>648.6529541015625</v>
+        <v>638.630859375</v>
       </c>
       <c r="F104" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B105" t="n">
-        <v>643.9513250294082</v>
+        <v>638.3612593202278</v>
       </c>
       <c r="C105" t="n">
-        <v>650.2700710327099</v>
+        <v>641.4557148619026</v>
       </c>
       <c r="D105" t="n">
-        <v>633.4401061931457</v>
+        <v>627.6803003409905</v>
       </c>
       <c r="E105" t="n">
-        <v>638.630859375</v>
+        <v>638.151611328125</v>
       </c>
       <c r="F105" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B106" t="n">
-        <v>638.3612593202278</v>
+        <v>632.67143641335</v>
       </c>
       <c r="C106" t="n">
-        <v>641.4557148619026</v>
+        <v>643.8515057528024</v>
       </c>
       <c r="D106" t="n">
-        <v>627.6803003409905</v>
+        <v>627.0315334227189</v>
       </c>
       <c r="E106" t="n">
-        <v>638.151611328125</v>
+        <v>642.0746459960938</v>
       </c>
       <c r="F106" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B107" t="n">
-        <v>632.67143641335</v>
+        <v>637.432932921519</v>
       </c>
       <c r="C107" t="n">
-        <v>643.8515057528024</v>
+        <v>646.0375787806976</v>
       </c>
       <c r="D107" t="n">
-        <v>627.0315334227189</v>
+        <v>635.5861905818066</v>
       </c>
       <c r="E107" t="n">
-        <v>642.0746459960938</v>
+        <v>643.6318969726562</v>
       </c>
       <c r="F107" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B108" t="n">
-        <v>637.432932921519</v>
+        <v>638.5509584025834</v>
       </c>
       <c r="C108" t="n">
-        <v>646.0375787806976</v>
+        <v>662.1688021543367</v>
       </c>
       <c r="D108" t="n">
-        <v>635.5861905818066</v>
+        <v>637.6426055733327</v>
       </c>
       <c r="E108" t="n">
-        <v>643.6318969726562</v>
+        <v>654.4924926757812</v>
       </c>
       <c r="F108" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B109" t="n">
-        <v>638.5509584025834</v>
+        <v>651.3780476889771</v>
       </c>
       <c r="C109" t="n">
-        <v>662.1688021543367</v>
+        <v>656.5288937722072</v>
       </c>
       <c r="D109" t="n">
-        <v>637.6426055733327</v>
+        <v>634.8675211939732</v>
       </c>
       <c r="E109" t="n">
-        <v>654.4924926757812</v>
+        <v>636.1152954101562</v>
       </c>
       <c r="F109" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B110" t="n">
-        <v>651.3780476889771</v>
+        <v>631.9527259539814</v>
       </c>
       <c r="C110" t="n">
-        <v>656.5288937722072</v>
+        <v>639.9683956881865</v>
       </c>
       <c r="D110" t="n">
-        <v>634.8675211939732</v>
+        <v>627.8599900449855</v>
       </c>
       <c r="E110" t="n">
-        <v>636.1152954101562</v>
+        <v>638.16162109375</v>
       </c>
       <c r="F110" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B111" t="n">
-        <v>631.9527259539814</v>
+        <v>641.3859599741169</v>
       </c>
       <c r="C111" t="n">
-        <v>639.9683956881865</v>
+        <v>652.7157261405878</v>
       </c>
       <c r="D111" t="n">
-        <v>627.8599900449855</v>
+        <v>640.9966397738364</v>
       </c>
       <c r="E111" t="n">
-        <v>638.16162109375</v>
+        <v>652.5260620117188</v>
       </c>
       <c r="F111" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B112" t="n">
-        <v>641.3859599741169</v>
+        <v>649.3916295582877</v>
       </c>
       <c r="C112" t="n">
-        <v>652.7157261405878</v>
+        <v>659.823034651462</v>
       </c>
       <c r="D112" t="n">
-        <v>640.9966397738364</v>
+        <v>646.3470725216666</v>
       </c>
       <c r="E112" t="n">
-        <v>652.5260620117188</v>
+        <v>655.8401489257812</v>
       </c>
       <c r="F112" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B113" t="n">
-        <v>649.3916295582877</v>
+        <v>642.3043203814821</v>
       </c>
       <c r="C113" t="n">
-        <v>659.823034651462</v>
+        <v>648.2836451675449</v>
       </c>
       <c r="D113" t="n">
-        <v>646.3470725216666</v>
+        <v>636.9837936279411</v>
       </c>
       <c r="E113" t="n">
-        <v>655.8401489257812</v>
+        <v>647.02587890625</v>
       </c>
       <c r="F113" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B114" t="n">
-        <v>642.3043203814821</v>
+        <v>636.0254184162494</v>
       </c>
       <c r="C114" t="n">
-        <v>648.2836451675449</v>
+        <v>658.764884603327</v>
       </c>
       <c r="D114" t="n">
-        <v>636.9837936279411</v>
+        <v>633.3701817354564</v>
       </c>
       <c r="E114" t="n">
-        <v>647.02587890625</v>
+        <v>652.396240234375</v>
       </c>
       <c r="F114" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B115" t="n">
-        <v>636.0254184162494</v>
+        <v>647.1356255764312</v>
       </c>
       <c r="C115" t="n">
-        <v>658.764884603327</v>
+        <v>657.866484005116</v>
       </c>
       <c r="D115" t="n">
-        <v>633.3701817354564</v>
+        <v>637.7025010942567</v>
       </c>
       <c r="E115" t="n">
-        <v>652.396240234375</v>
+        <v>653.91357421875</v>
       </c>
       <c r="F115" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B116" t="n">
-        <v>647.1356255764312</v>
+        <v>656.7884535878291</v>
       </c>
       <c r="C116" t="n">
-        <v>657.866484005116</v>
+        <v>671.5720803574089</v>
       </c>
       <c r="D116" t="n">
-        <v>637.7025010942567</v>
+        <v>656.4989309709863</v>
       </c>
       <c r="E116" t="n">
-        <v>653.91357421875</v>
+        <v>666.541015625</v>
       </c>
       <c r="F116" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B117" t="n">
-        <v>656.7884535878291</v>
+        <v>660.751362594833</v>
       </c>
       <c r="C117" t="n">
-        <v>671.5720803574089</v>
+        <v>669.5057662619517</v>
       </c>
       <c r="D117" t="n">
-        <v>656.4989309709863</v>
+        <v>649.1520579976961</v>
       </c>
       <c r="E117" t="n">
-        <v>666.541015625</v>
+        <v>659.393798828125</v>
       </c>
       <c r="F117" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B118" t="n">
-        <v>660.751362594833</v>
+        <v>646.7463568472266</v>
       </c>
       <c r="C118" t="n">
-        <v>669.5057662619517</v>
+        <v>648.3135076492586</v>
       </c>
       <c r="D118" t="n">
-        <v>649.1520579976961</v>
+        <v>634.9773114336934</v>
       </c>
       <c r="E118" t="n">
-        <v>659.393798828125</v>
+        <v>643.7117309570312</v>
       </c>
       <c r="F118" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B119" t="n">
-        <v>646.7463568472266</v>
+        <v>633.6497720389343</v>
       </c>
       <c r="C119" t="n">
-        <v>648.3135076492586</v>
+        <v>646.596649067328</v>
       </c>
       <c r="D119" t="n">
-        <v>634.9773114336934</v>
+        <v>625.6640164348609</v>
       </c>
       <c r="E119" t="n">
-        <v>643.7117309570312</v>
+        <v>646.2373046875</v>
       </c>
       <c r="F119" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B120" t="n">
-        <v>633.6497720389343</v>
+        <v>652.3962328583322</v>
       </c>
       <c r="C120" t="n">
-        <v>646.596649067328</v>
+        <v>659.1242214972237</v>
       </c>
       <c r="D120" t="n">
-        <v>625.6640164348609</v>
+        <v>647.8443550809549</v>
       </c>
       <c r="E120" t="n">
-        <v>646.2373046875</v>
+        <v>652.9053344726562</v>
       </c>
       <c r="F120" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B121" t="n">
-        <v>652.3962328583322</v>
+        <v>653.5941111270305</v>
       </c>
       <c r="C121" t="n">
-        <v>659.1242214972237</v>
+        <v>657.9463328691638</v>
       </c>
       <c r="D121" t="n">
-        <v>647.8443550809549</v>
+        <v>647.2054829186618</v>
       </c>
       <c r="E121" t="n">
-        <v>652.9053344726562</v>
+        <v>653.6939086914062</v>
       </c>
       <c r="F121" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B122" t="n">
-        <v>653.5941111270305</v>
+        <v>647.5948263527883</v>
       </c>
       <c r="C122" t="n">
-        <v>657.9463328691638</v>
+        <v>652.336368433984</v>
       </c>
       <c r="D122" t="n">
-        <v>647.2054829186618</v>
+        <v>635.7659510050273</v>
       </c>
       <c r="E122" t="n">
-        <v>653.6939086914062</v>
+        <v>637.0436401367188</v>
       </c>
       <c r="F122" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B123" t="n">
-        <v>647.5948263527883</v>
+        <v>622.7790526456299</v>
       </c>
       <c r="C123" t="n">
-        <v>652.336368433984</v>
+        <v>628.0496188589474</v>
       </c>
       <c r="D123" t="n">
-        <v>635.7659510050273</v>
+        <v>608.4645611002024</v>
       </c>
       <c r="E123" t="n">
-        <v>637.0436401367188</v>
+        <v>612.6171875</v>
       </c>
       <c r="F123" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B124" t="n">
-        <v>622.7790526456299</v>
+        <v>631.4147932406764</v>
       </c>
       <c r="C124" t="n">
-        <v>628.0496188589474</v>
+        <v>634.1622468505053</v>
       </c>
       <c r="D124" t="n">
-        <v>608.4645611002024</v>
+        <v>622.5230098937741</v>
       </c>
       <c r="E124" t="n">
-        <v>612.6171875</v>
+        <v>626.8690185546875</v>
       </c>
       <c r="F124" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3667,25 +3667,25 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B125" t="n">
-        <v>631.4147932406764</v>
+        <v>627.4085169382369</v>
       </c>
       <c r="C125" t="n">
-        <v>634.1622468505053</v>
+        <v>635.9605885584036</v>
       </c>
       <c r="D125" t="n">
-        <v>622.5230098937741</v>
+        <v>621.1243629754691</v>
       </c>
       <c r="E125" t="n">
-        <v>626.8690185546875</v>
+        <v>622.0834350585938</v>
       </c>
       <c r="F125" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G125" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B126" t="n">
-        <v>627.4085169382369</v>
+        <v>615.7693473594539</v>
       </c>
       <c r="C126" t="n">
-        <v>635.9605885584036</v>
+        <v>622.0735023862151</v>
       </c>
       <c r="D126" t="n">
-        <v>621.1243629754691</v>
+        <v>614.04090772979</v>
       </c>
       <c r="E126" t="n">
-        <v>622.0834350585938</v>
+        <v>615.1099243164062</v>
       </c>
       <c r="F126" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B127" t="n">
-        <v>615.7693473594539</v>
+        <v>611.5832104537112</v>
       </c>
       <c r="C127" t="n">
-        <v>622.0735023862151</v>
+        <v>612.4323990135786</v>
       </c>
       <c r="D127" t="n">
-        <v>614.04090772979</v>
+        <v>601.7023533616688</v>
       </c>
       <c r="E127" t="n">
-        <v>615.1099243164062</v>
+        <v>606.1382446289062</v>
       </c>
       <c r="F127" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B128" t="n">
-        <v>611.5832104537112</v>
+        <v>602.9712077810872</v>
       </c>
       <c r="C128" t="n">
-        <v>612.4323990135786</v>
+        <v>603.400802317344</v>
       </c>
       <c r="D128" t="n">
-        <v>601.7023533616688</v>
+        <v>586.7062525156723</v>
       </c>
       <c r="E128" t="n">
-        <v>606.1382446289062</v>
+        <v>593.1102905273438</v>
       </c>
       <c r="F128" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B129" t="n">
-        <v>602.9712077810872</v>
+        <v>605.2290499891692</v>
       </c>
       <c r="C129" t="n">
-        <v>603.400802317344</v>
+        <v>608.0764476338709</v>
       </c>
       <c r="D129" t="n">
-        <v>586.7062525156723</v>
+        <v>598.4553596033379</v>
       </c>
       <c r="E129" t="n">
-        <v>593.1102905273438</v>
+        <v>603.5006713867188</v>
       </c>
       <c r="F129" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B130" t="n">
-        <v>605.2290499891692</v>
+        <v>598.5452420228083</v>
       </c>
       <c r="C130" t="n">
-        <v>608.0764476338709</v>
+        <v>600.443507118967</v>
       </c>
       <c r="D130" t="n">
-        <v>598.4553596033379</v>
+        <v>590.4527665679026</v>
       </c>
       <c r="E130" t="n">
-        <v>603.5006713867188</v>
+        <v>592.3709716796875</v>
       </c>
       <c r="F130" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B131" t="n">
-        <v>598.5452420228083</v>
+        <v>598.1855830392399</v>
       </c>
       <c r="C131" t="n">
-        <v>600.443507118967</v>
+        <v>603.1110107561809</v>
       </c>
       <c r="D131" t="n">
-        <v>590.4527665679026</v>
+        <v>592.8505617950721</v>
       </c>
       <c r="E131" t="n">
-        <v>592.3709716796875</v>
+        <v>594.3391723632812</v>
       </c>
       <c r="F131" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B132" t="n">
-        <v>598.1855830392399</v>
+        <v>581.9506076701073</v>
       </c>
       <c r="C132" t="n">
-        <v>603.1110107561809</v>
+        <v>582.460145169462</v>
       </c>
       <c r="D132" t="n">
-        <v>592.8505617950721</v>
+        <v>542.8468364624507</v>
       </c>
       <c r="E132" t="n">
-        <v>594.3391723632812</v>
+        <v>547.032958984375</v>
       </c>
       <c r="F132" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B133" t="n">
-        <v>581.9506076701073</v>
+        <v>539.599843303006</v>
       </c>
       <c r="C133" t="n">
-        <v>582.460145169462</v>
+        <v>543.0966023049141</v>
       </c>
       <c r="D133" t="n">
-        <v>542.8468364624507</v>
+        <v>519.7782492802263</v>
       </c>
       <c r="E133" t="n">
-        <v>547.032958984375</v>
+        <v>525.233154296875</v>
       </c>
       <c r="F133" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B134" t="n">
-        <v>539.599843303006</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="C134" t="n">
-        <v>543.0966023049141</v>
+        <v>539.0504095872608</v>
       </c>
       <c r="D134" t="n">
-        <v>519.7782492802263</v>
+        <v>528.0505941707193</v>
       </c>
       <c r="E134" t="n">
-        <v>525.233154296875</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="F134" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B135" t="n">
-        <v>535.8833618164062</v>
+        <v>549.4707059552647</v>
       </c>
       <c r="C135" t="n">
-        <v>539.0504095872608</v>
+        <v>573.1587727471259</v>
       </c>
       <c r="D135" t="n">
-        <v>528.0505941707193</v>
+        <v>546.2637174010383</v>
       </c>
       <c r="E135" t="n">
-        <v>535.8833618164062</v>
+        <v>571.6002197265625</v>
       </c>
       <c r="F135" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B136" t="n">
-        <v>549.4707059552647</v>
+        <v>579.5928556215499</v>
       </c>
       <c r="C136" t="n">
-        <v>573.1587727471259</v>
+        <v>592.0013387220274</v>
       </c>
       <c r="D136" t="n">
-        <v>546.2637174010383</v>
+        <v>573.2887005646345</v>
       </c>
       <c r="E136" t="n">
-        <v>571.6002197265625</v>
+        <v>578.6936645507812</v>
       </c>
       <c r="F136" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B137" t="n">
-        <v>579.5928556215499</v>
+        <v>565.5158531822124</v>
       </c>
       <c r="C137" t="n">
-        <v>592.0013387220274</v>
+        <v>577.9643377947169</v>
       </c>
       <c r="D137" t="n">
-        <v>573.2887005646345</v>
+        <v>559.1817578546791</v>
       </c>
       <c r="E137" t="n">
-        <v>578.6936645507812</v>
+        <v>573.9281005859375</v>
       </c>
       <c r="F137" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B138" t="n">
-        <v>565.5158531822124</v>
+        <v>577.1550997330287</v>
       </c>
       <c r="C138" t="n">
-        <v>577.9643377947169</v>
+        <v>582.2503530791108</v>
       </c>
       <c r="D138" t="n">
-        <v>559.1817578546791</v>
+        <v>571.4703658572956</v>
       </c>
       <c r="E138" t="n">
-        <v>573.9281005859375</v>
+        <v>572.4894409179688</v>
       </c>
       <c r="F138" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B139" t="n">
-        <v>577.1550997330287</v>
+        <v>571.9498894780604</v>
       </c>
       <c r="C139" t="n">
-        <v>582.2503530791108</v>
+        <v>574.6973431004155</v>
       </c>
       <c r="D139" t="n">
-        <v>571.4703658572956</v>
+        <v>564.2370671243236</v>
       </c>
       <c r="E139" t="n">
-        <v>572.4894409179688</v>
+        <v>574.5175170898438</v>
       </c>
       <c r="F139" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B140" t="n">
-        <v>571.9498894780604</v>
+        <v>605.4388670235439</v>
       </c>
       <c r="C140" t="n">
-        <v>574.6973431004155</v>
+        <v>629.3667024291958</v>
       </c>
       <c r="D140" t="n">
-        <v>564.2370671243236</v>
+        <v>591.2820049792073</v>
       </c>
       <c r="E140" t="n">
-        <v>574.5175170898438</v>
+        <v>611.8529052734375</v>
       </c>
       <c r="F140" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B141" t="n">
-        <v>605.4388670235439</v>
+        <v>626.3894374266143</v>
       </c>
       <c r="C141" t="n">
-        <v>629.3667024291958</v>
+        <v>636.9097166035551</v>
       </c>
       <c r="D141" t="n">
-        <v>591.2820049792073</v>
+        <v>622.4231426572783</v>
       </c>
       <c r="E141" t="n">
-        <v>611.8529052734375</v>
+        <v>627.8081665039062</v>
       </c>
       <c r="F141" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B142" t="n">
-        <v>626.3894374266143</v>
+        <v>633.882449891805</v>
       </c>
       <c r="C142" t="n">
-        <v>636.9097166035551</v>
+        <v>637.9886903650855</v>
       </c>
       <c r="D142" t="n">
-        <v>622.4231426572783</v>
+        <v>623.7518859014353</v>
       </c>
       <c r="E142" t="n">
-        <v>627.8081665039062</v>
+        <v>629.2767333984375</v>
       </c>
       <c r="F142" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B143" t="n">
-        <v>633.882449891805</v>
+        <v>628.9171329935918</v>
       </c>
       <c r="C143" t="n">
-        <v>637.9886903650855</v>
+        <v>634.4120404303904</v>
       </c>
       <c r="D143" t="n">
-        <v>623.7518859014353</v>
+        <v>623.8218795800174</v>
       </c>
       <c r="E143" t="n">
-        <v>629.2767333984375</v>
+        <v>633.9425048828125</v>
       </c>
       <c r="F143" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B144" t="n">
-        <v>628.9171329935918</v>
+        <v>642.624350345733</v>
       </c>
       <c r="C144" t="n">
-        <v>634.4120404303904</v>
+        <v>665.6430543798978</v>
       </c>
       <c r="D144" t="n">
-        <v>623.8218795800174</v>
+        <v>638.7779398291946</v>
       </c>
       <c r="E144" t="n">
-        <v>633.9425048828125</v>
+        <v>661.8765258789062</v>
       </c>
       <c r="F144" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B145" t="n">
-        <v>642.624350345733</v>
+        <v>666.3824145357423</v>
       </c>
       <c r="C145" t="n">
-        <v>665.6430543798978</v>
+        <v>677.8717665104965</v>
       </c>
       <c r="D145" t="n">
-        <v>638.7779398291946</v>
+        <v>663.6049593103575</v>
       </c>
       <c r="E145" t="n">
-        <v>661.8765258789062</v>
+        <v>670.9581909179688</v>
       </c>
       <c r="F145" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B146" t="n">
-        <v>666.3824145357423</v>
+        <v>675.3640350842893</v>
       </c>
       <c r="C146" t="n">
-        <v>677.8717665104965</v>
+        <v>676.9525896021297</v>
       </c>
       <c r="D146" t="n">
-        <v>663.6049593103575</v>
+        <v>667.131674939706</v>
       </c>
       <c r="E146" t="n">
-        <v>670.9581909179688</v>
+        <v>676.2432250976562</v>
       </c>
       <c r="F146" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B147" t="n">
-        <v>675.3640350842893</v>
+        <v>677.9716157075654</v>
       </c>
       <c r="C147" t="n">
-        <v>676.9525896021297</v>
+        <v>690.8796961433965</v>
       </c>
       <c r="D147" t="n">
-        <v>667.131674939706</v>
+        <v>674.5048580761284</v>
       </c>
       <c r="E147" t="n">
-        <v>676.2432250976562</v>
+        <v>687.9124145507812</v>
       </c>
       <c r="F147" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B148" t="n">
-        <v>677.9716157075654</v>
+        <v>680.7290935491282</v>
       </c>
       <c r="C148" t="n">
-        <v>690.8796961433965</v>
+        <v>682.7472426832454</v>
       </c>
       <c r="D148" t="n">
-        <v>674.5048580761284</v>
+        <v>667.381478611767</v>
       </c>
       <c r="E148" t="n">
-        <v>687.9124145507812</v>
+        <v>670.2887573242188</v>
       </c>
       <c r="F148" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B149" t="n">
-        <v>680.7290935491282</v>
+        <v>670.3786762058809</v>
       </c>
       <c r="C149" t="n">
-        <v>682.7472426832454</v>
+        <v>675.5738733736962</v>
       </c>
       <c r="D149" t="n">
-        <v>667.381478611767</v>
+        <v>666.7120915784461</v>
       </c>
       <c r="E149" t="n">
-        <v>670.2887573242188</v>
+        <v>668.220703125</v>
       </c>
       <c r="F149" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B150" t="n">
-        <v>670.3786762058809</v>
+        <v>673.7355628200382</v>
       </c>
       <c r="C150" t="n">
-        <v>675.5738733736962</v>
+        <v>677.7518600207422</v>
       </c>
       <c r="D150" t="n">
-        <v>666.7120915784461</v>
+        <v>669.1298460769134</v>
       </c>
       <c r="E150" t="n">
-        <v>668.220703125</v>
+        <v>674.09521484375</v>
       </c>
       <c r="F150" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B151" t="n">
-        <v>673.7355628200382</v>
+        <v>663.0854475032797</v>
       </c>
       <c r="C151" t="n">
-        <v>677.7518600207422</v>
+        <v>668.9400066983026</v>
       </c>
       <c r="D151" t="n">
-        <v>669.1298460769134</v>
+        <v>652.4452846667049</v>
       </c>
       <c r="E151" t="n">
-        <v>674.09521484375</v>
+        <v>658.5396728515625</v>
       </c>
       <c r="F151" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B152" t="n">
-        <v>663.0854475032797</v>
+        <v>659.7085674039201</v>
       </c>
       <c r="C152" t="n">
-        <v>668.9400066983026</v>
+        <v>680.0396994180859</v>
       </c>
       <c r="D152" t="n">
-        <v>652.4452846667049</v>
+        <v>653.2345872360809</v>
       </c>
       <c r="E152" t="n">
-        <v>658.5396728515625</v>
+        <v>674.4049682617188</v>
       </c>
       <c r="F152" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B153" t="n">
-        <v>659.7085674039201</v>
+        <v>670.3786986745525</v>
       </c>
       <c r="C153" t="n">
-        <v>680.0396994180859</v>
+        <v>681.8680504402118</v>
       </c>
       <c r="D153" t="n">
-        <v>653.2345872360809</v>
+        <v>670.2188736545023</v>
       </c>
       <c r="E153" t="n">
-        <v>674.4049682617188</v>
+        <v>677.9916381835938</v>
       </c>
       <c r="F153" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B154" t="n">
-        <v>670.3786986745525</v>
+        <v>673.6156618787633</v>
       </c>
       <c r="C154" t="n">
-        <v>681.8680504402118</v>
+        <v>677.5520159823654</v>
       </c>
       <c r="D154" t="n">
-        <v>670.2188736545023</v>
+        <v>665.0136491453696</v>
       </c>
       <c r="E154" t="n">
-        <v>677.9916381835938</v>
+        <v>670.7183837890625</v>
       </c>
       <c r="F154" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B155" t="n">
-        <v>673.6156618787633</v>
+        <v>668.2905997420939</v>
       </c>
       <c r="C155" t="n">
-        <v>677.5520159823654</v>
+        <v>673.6256820299297</v>
       </c>
       <c r="D155" t="n">
-        <v>665.0136491453696</v>
+        <v>663.1953464496755</v>
       </c>
       <c r="E155" t="n">
-        <v>670.7183837890625</v>
+        <v>668.5004272460938</v>
       </c>
       <c r="F155" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B156" t="n">
-        <v>668.2905997420939</v>
+        <v>618.7465567527638</v>
       </c>
       <c r="C156" t="n">
-        <v>673.6256820299297</v>
+        <v>620.2751083620838</v>
       </c>
       <c r="D156" t="n">
-        <v>663.1953464496755</v>
+        <v>599.4444385151393</v>
       </c>
       <c r="E156" t="n">
-        <v>668.5004272460938</v>
+        <v>611.3433837890625</v>
       </c>
       <c r="F156" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B157" t="n">
-        <v>618.7465567527638</v>
+        <v>614.120842749119</v>
       </c>
       <c r="C157" t="n">
-        <v>620.2751083620838</v>
+        <v>618.3069655430758</v>
       </c>
       <c r="D157" t="n">
-        <v>599.4444385151393</v>
+        <v>605.5487701514051</v>
       </c>
       <c r="E157" t="n">
-        <v>611.3433837890625</v>
+        <v>608.1863403320312</v>
       </c>
       <c r="F157" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B158" t="n">
-        <v>614.120842749119</v>
+        <v>607.3771038685389</v>
       </c>
       <c r="C158" t="n">
-        <v>618.3069655430758</v>
+        <v>613.4314904063681</v>
       </c>
       <c r="D158" t="n">
-        <v>605.5487701514051</v>
+        <v>602.1919069095087</v>
       </c>
       <c r="E158" t="n">
-        <v>608.1863403320312</v>
+        <v>609.8447875976562</v>
       </c>
       <c r="F158" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B159" t="n">
-        <v>607.3771038685389</v>
+        <v>612.7420849871345</v>
       </c>
       <c r="C159" t="n">
-        <v>613.4314904063681</v>
+        <v>613.7811000159977</v>
       </c>
       <c r="D159" t="n">
-        <v>602.1919069095087</v>
+        <v>599.8040642277598</v>
       </c>
       <c r="E159" t="n">
-        <v>609.8447875976562</v>
+        <v>604.3998413085938</v>
       </c>
       <c r="F159" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B160" t="n">
-        <v>612.7420849871345</v>
+        <v>600.4934370812971</v>
       </c>
       <c r="C160" t="n">
-        <v>613.7811000159977</v>
+        <v>619.3759607512419</v>
       </c>
       <c r="D160" t="n">
-        <v>599.8040642277598</v>
+        <v>597.5461564796674</v>
       </c>
       <c r="E160" t="n">
-        <v>604.3998413085938</v>
+        <v>612.3125</v>
       </c>
       <c r="F160" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B161" t="n">
-        <v>600.4934370812971</v>
+        <v>614.150739078972</v>
       </c>
       <c r="C161" t="n">
-        <v>619.3759607512419</v>
+        <v>624.4012480600104</v>
       </c>
       <c r="D161" t="n">
-        <v>597.5461564796674</v>
+        <v>612.9718390781961</v>
       </c>
       <c r="E161" t="n">
-        <v>612.3125</v>
+        <v>616.2388305664062</v>
       </c>
       <c r="F161" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B162" t="n">
-        <v>614.150739078972</v>
+        <v>614.6303402495529</v>
       </c>
       <c r="C162" t="n">
-        <v>624.4012480600104</v>
+        <v>616.1988937552933</v>
       </c>
       <c r="D162" t="n">
-        <v>612.9718390781961</v>
+        <v>605.4987892063378</v>
       </c>
       <c r="E162" t="n">
-        <v>616.2388305664062</v>
+        <v>609.0654907226562</v>
       </c>
       <c r="F162" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B163" t="n">
-        <v>614.6303402495529</v>
+        <v>604.010215830275</v>
       </c>
       <c r="C163" t="n">
-        <v>616.1988937552933</v>
+        <v>604.3498668649182</v>
       </c>
       <c r="D163" t="n">
-        <v>605.4987892063378</v>
+        <v>597.5262348938886</v>
       </c>
       <c r="E163" t="n">
-        <v>609.0654907226562</v>
+        <v>598.3054809570312</v>
       </c>
       <c r="F163" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B164" t="n">
-        <v>604.010215830275</v>
+        <v>594.2692320029287</v>
       </c>
       <c r="C164" t="n">
-        <v>604.3498668649182</v>
+        <v>603.1909559259367</v>
       </c>
       <c r="D164" t="n">
-        <v>597.5262348938886</v>
+        <v>592.0512559095129</v>
       </c>
       <c r="E164" t="n">
-        <v>598.3054809570312</v>
+        <v>602.441650390625</v>
       </c>
       <c r="F164" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B165" t="n">
-        <v>594.2692320029287</v>
+        <v>598.275515544453</v>
       </c>
       <c r="C165" t="n">
-        <v>603.1909559259367</v>
+        <v>619.3260125714435</v>
       </c>
       <c r="D165" t="n">
-        <v>592.0512559095129</v>
+        <v>596.1074810052941</v>
       </c>
       <c r="E165" t="n">
-        <v>602.441650390625</v>
+        <v>616.0590209960938</v>
       </c>
       <c r="F165" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B166" t="n">
-        <v>598.275515544453</v>
+        <v>615.4296182023591</v>
       </c>
       <c r="C166" t="n">
-        <v>619.3260125714435</v>
+        <v>623.152441138389</v>
       </c>
       <c r="D166" t="n">
-        <v>596.1074810052941</v>
+        <v>614.4305441468357</v>
       </c>
       <c r="E166" t="n">
-        <v>616.0590209960938</v>
+        <v>617.8573608398438</v>
       </c>
       <c r="F166" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B167" t="n">
-        <v>615.4296182023591</v>
+        <v>613.421486859321</v>
       </c>
       <c r="C167" t="n">
-        <v>623.152441138389</v>
+        <v>620.6248329546977</v>
       </c>
       <c r="D167" t="n">
-        <v>614.4305441468357</v>
+        <v>608.7458274653094</v>
       </c>
       <c r="E167" t="n">
-        <v>617.8573608398438</v>
+        <v>613.6612548828125</v>
       </c>
       <c r="F167" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B168" t="n">
-        <v>613.421486859321</v>
+        <v>608.5459509764945</v>
       </c>
       <c r="C168" t="n">
-        <v>620.6248329546977</v>
+        <v>615.0199919776213</v>
       </c>
       <c r="D168" t="n">
-        <v>608.7458274653094</v>
+        <v>603.1309869574205</v>
       </c>
       <c r="E168" t="n">
-        <v>613.6612548828125</v>
+        <v>610.64404296875</v>
       </c>
       <c r="F168" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B169" t="n">
-        <v>608.5459509764945</v>
+        <v>608.3561568042173</v>
       </c>
       <c r="C169" t="n">
-        <v>615.0199919776213</v>
+        <v>613.361527578881</v>
       </c>
       <c r="D169" t="n">
-        <v>603.1309869574205</v>
+        <v>599.9939118379299</v>
       </c>
       <c r="E169" t="n">
-        <v>610.64404296875</v>
+        <v>602.052001953125</v>
       </c>
       <c r="F169" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B170" t="n">
-        <v>608.3561568042173</v>
+        <v>600.2037495434126</v>
       </c>
       <c r="C170" t="n">
-        <v>613.361527578881</v>
+        <v>607.4370360716302</v>
       </c>
       <c r="D170" t="n">
-        <v>599.9939118379299</v>
+        <v>597.2564688338498</v>
       </c>
       <c r="E170" t="n">
-        <v>602.052001953125</v>
+        <v>604.499755859375</v>
       </c>
       <c r="F170" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B171" t="n">
-        <v>600.2037495434126</v>
+        <v>599.4443949814065</v>
       </c>
       <c r="C171" t="n">
-        <v>607.4370360716302</v>
+        <v>609.0354809096541</v>
       </c>
       <c r="D171" t="n">
-        <v>597.2564688338498</v>
+        <v>594.2591985256718</v>
       </c>
       <c r="E171" t="n">
-        <v>604.499755859375</v>
+        <v>606.8175659179688</v>
       </c>
       <c r="F171" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B172" t="n">
-        <v>599.4443949814065</v>
+        <v>607.3171451453314</v>
       </c>
       <c r="C172" t="n">
-        <v>609.0354809096541</v>
+        <v>614.2407210713809</v>
       </c>
       <c r="D172" t="n">
-        <v>594.2591985256718</v>
+        <v>606.3880135859368</v>
       </c>
       <c r="E172" t="n">
-        <v>606.8175659179688</v>
+        <v>609.6949462890625</v>
       </c>
       <c r="F172" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B173" t="n">
-        <v>607.3171451453314</v>
+        <v>608.3261927003538</v>
       </c>
       <c r="C173" t="n">
-        <v>614.2407210713809</v>
+        <v>613.9009818092591</v>
       </c>
       <c r="D173" t="n">
-        <v>606.3880135859368</v>
+        <v>604.7394901495815</v>
       </c>
       <c r="E173" t="n">
-        <v>609.6949462890625</v>
+        <v>611.7730102539062</v>
       </c>
       <c r="F173" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B174" t="n">
-        <v>608.3261927003538</v>
+        <v>608.8357727220844</v>
       </c>
       <c r="C174" t="n">
-        <v>613.9009818092591</v>
+        <v>637.908804248614</v>
       </c>
       <c r="D174" t="n">
-        <v>604.7394901495815</v>
+        <v>608.4361186960156</v>
       </c>
       <c r="E174" t="n">
-        <v>611.7730102539062</v>
+        <v>634.6718139648438</v>
       </c>
       <c r="F174" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B175" t="n">
-        <v>608.8357727220844</v>
+        <v>638.9078448274123</v>
       </c>
       <c r="C175" t="n">
-        <v>637.908804248614</v>
+        <v>642.4046039468743</v>
       </c>
       <c r="D175" t="n">
-        <v>608.4361186960156</v>
+        <v>628.7272779804616</v>
       </c>
       <c r="E175" t="n">
-        <v>634.6718139648438</v>
+        <v>634.7017211914062</v>
       </c>
       <c r="F175" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B176" t="n">
-        <v>638.9078448274123</v>
+        <v>632.9133899267435</v>
       </c>
       <c r="C176" t="n">
-        <v>642.4046039468743</v>
+        <v>633.9124639439917</v>
       </c>
       <c r="D176" t="n">
-        <v>628.7272779804616</v>
+        <v>622.7727642602187</v>
       </c>
       <c r="E176" t="n">
-        <v>634.7017211914062</v>
+        <v>631.92431640625</v>
       </c>
       <c r="F176" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B177" t="n">
-        <v>632.9133899267435</v>
+        <v>629.8162791560948</v>
       </c>
       <c r="C177" t="n">
-        <v>633.9124639439917</v>
+        <v>635.1613007084701</v>
       </c>
       <c r="D177" t="n">
-        <v>622.7727642602187</v>
+        <v>598.9748694014791</v>
       </c>
       <c r="E177" t="n">
-        <v>631.92431640625</v>
+        <v>599.9139404296875</v>
       </c>
       <c r="F177" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B178" t="n">
-        <v>629.8162791560948</v>
+        <v>602.6813896226799</v>
       </c>
       <c r="C178" t="n">
-        <v>635.1613007084701</v>
+        <v>608.3161816139932</v>
       </c>
       <c r="D178" t="n">
-        <v>598.9748694014791</v>
+        <v>596.1274666259658</v>
       </c>
       <c r="E178" t="n">
-        <v>599.9139404296875</v>
+        <v>597.0765991210938</v>
       </c>
       <c r="F178" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B179" t="n">
-        <v>602.6813896226799</v>
+        <v>602.4416570391962</v>
       </c>
       <c r="C179" t="n">
-        <v>608.3161816139932</v>
+        <v>623.5720977596394</v>
       </c>
       <c r="D179" t="n">
-        <v>596.1274666259658</v>
+        <v>599.7142043737263</v>
       </c>
       <c r="E179" t="n">
-        <v>597.0765991210938</v>
+        <v>622.4031372070312</v>
       </c>
       <c r="F179" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B180" t="n">
-        <v>602.4416570391962</v>
+        <v>623.0924785224576</v>
       </c>
       <c r="C180" t="n">
-        <v>623.5720977596394</v>
+        <v>641.8051764288737</v>
       </c>
       <c r="D180" t="n">
-        <v>599.7142043737263</v>
+        <v>621.8536364911718</v>
       </c>
       <c r="E180" t="n">
-        <v>622.4031372070312</v>
+        <v>626.9888916015625</v>
       </c>
       <c r="F180" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B181" t="n">
-        <v>623.0924785224576</v>
+        <v>622.8827460758752</v>
       </c>
       <c r="C181" t="n">
-        <v>641.8051764288737</v>
+        <v>628.5674800138549</v>
       </c>
       <c r="D181" t="n">
-        <v>621.8536364911718</v>
+        <v>582.3702434655938</v>
       </c>
       <c r="E181" t="n">
-        <v>626.9888916015625</v>
+        <v>592.450927734375</v>
       </c>
       <c r="F181" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B182" t="n">
-        <v>622.8827460758752</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="C182" t="n">
-        <v>628.5674800138549</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="D182" t="n">
-        <v>582.3702434655938</v>
+        <v>578.6836307521693</v>
       </c>
       <c r="E182" t="n">
-        <v>592.450927734375</v>
+        <v>584.8479614257812</v>
       </c>
       <c r="F182" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B183" t="n">
-        <v>591.4518261333767</v>
+        <v>590.4527436689563</v>
       </c>
       <c r="C183" t="n">
-        <v>591.4518261333767</v>
+        <v>597.0766092757164</v>
       </c>
       <c r="D183" t="n">
-        <v>578.6836307521693</v>
+        <v>580.4720040020986</v>
       </c>
       <c r="E183" t="n">
-        <v>584.8479614257812</v>
+        <v>584.0487060546875</v>
       </c>
       <c r="F183" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B184" t="n">
-        <v>590.4527436689563</v>
+        <v>580.192266144374</v>
       </c>
       <c r="C184" t="n">
-        <v>597.0766092757164</v>
+        <v>590.7724873942649</v>
       </c>
       <c r="D184" t="n">
-        <v>580.4720040020986</v>
+        <v>570.0716409197756</v>
       </c>
       <c r="E184" t="n">
-        <v>584.0487060546875</v>
+        <v>570.4512939453125</v>
       </c>
       <c r="F184" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B185" t="n">
-        <v>580.192266144374</v>
+        <v>565.3060574843756</v>
       </c>
       <c r="C185" t="n">
-        <v>590.7724873942649</v>
+        <v>571.6401524850257</v>
       </c>
       <c r="D185" t="n">
-        <v>570.0716409197756</v>
+        <v>556.4942175026772</v>
       </c>
       <c r="E185" t="n">
-        <v>570.4512939453125</v>
+        <v>567.9036254882812</v>
       </c>
       <c r="F185" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B186" t="n">
-        <v>565.3060574843756</v>
+        <v>572.4194595335534</v>
       </c>
       <c r="C186" t="n">
-        <v>571.6401524850257</v>
+        <v>575.5365655300229</v>
       </c>
       <c r="D186" t="n">
-        <v>556.4942175026772</v>
+        <v>560.3806300495169</v>
       </c>
       <c r="E186" t="n">
-        <v>567.9036254882812</v>
+        <v>566.4549560546875</v>
       </c>
       <c r="F186" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,25 +5279,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B187" t="n">
-        <v>572.4194595335534</v>
+        <v>579.9000244140625</v>
       </c>
       <c r="C187" t="n">
-        <v>575.5365655300229</v>
+        <v>601.27001953125</v>
       </c>
       <c r="D187" t="n">
-        <v>560.3806300495169</v>
+        <v>579.2999877929688</v>
       </c>
       <c r="E187" t="n">
-        <v>566.4549560546875</v>
+        <v>593.47998046875</v>
       </c>
       <c r="F187" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5305,25 +5305,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B188" t="n">
-        <v>579.9000244140625</v>
+        <v>593.6500244140625</v>
       </c>
       <c r="C188" t="n">
-        <v>601.27001953125</v>
+        <v>605.8099975585938</v>
       </c>
       <c r="D188" t="n">
-        <v>579.2999877929688</v>
+        <v>592</v>
       </c>
       <c r="E188" t="n">
-        <v>593.47998046875</v>
+        <v>600.2100219726562</v>
       </c>
       <c r="F188" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G188" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B189" t="n">
-        <v>593.6500244140625</v>
+        <v>592</v>
       </c>
       <c r="C189" t="n">
-        <v>605.8099975585938</v>
+        <v>593.8099975585938</v>
       </c>
       <c r="D189" t="n">
-        <v>592</v>
+        <v>566.1900024414062</v>
       </c>
       <c r="E189" t="n">
-        <v>600.2100219726562</v>
+        <v>567.5800170898438</v>
       </c>
       <c r="F189" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B190" t="n">
-        <v>592</v>
+        <v>572.8200073242188</v>
       </c>
       <c r="C190" t="n">
-        <v>593.8099975585938</v>
+        <v>580.219970703125</v>
       </c>
       <c r="D190" t="n">
-        <v>566.1900024414062</v>
+        <v>563.0999755859375</v>
       </c>
       <c r="E190" t="n">
-        <v>567.5800170898438</v>
+        <v>577.219970703125</v>
       </c>
       <c r="F190" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B191" t="n">
-        <v>572.8200073242188</v>
+        <v>572.02001953125</v>
       </c>
       <c r="C191" t="n">
-        <v>580.219970703125</v>
+        <v>575.8099975585938</v>
       </c>
       <c r="D191" t="n">
-        <v>563.0999755859375</v>
+        <v>559.8099975585938</v>
       </c>
       <c r="E191" t="n">
-        <v>577.219970703125</v>
+        <v>563.8499755859375</v>
       </c>
       <c r="F191" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B192" t="n">
-        <v>572.02001953125</v>
+        <v>562.25</v>
       </c>
       <c r="C192" t="n">
-        <v>575.8099975585938</v>
+        <v>572.2000122070312</v>
       </c>
       <c r="D192" t="n">
-        <v>559.8099975585938</v>
+        <v>561.02001953125</v>
       </c>
       <c r="E192" t="n">
-        <v>563.8499755859375</v>
+        <v>562.2000122070312</v>
       </c>
       <c r="F192" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B193" t="n">
-        <v>562.25</v>
+        <v>561.8900146484375</v>
       </c>
       <c r="C193" t="n">
-        <v>572.2000122070312</v>
+        <v>569.0399780273438</v>
       </c>
       <c r="D193" t="n">
-        <v>561.02001953125</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="E193" t="n">
-        <v>562.2000122070312</v>
+        <v>557.6699829101562</v>
       </c>
       <c r="F193" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B194" t="n">
-        <v>561.8900146484375</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="C194" t="n">
-        <v>569.0399780273438</v>
+        <v>556.3400268554688</v>
       </c>
       <c r="D194" t="n">
-        <v>555.5499877929688</v>
+        <v>540.1799926757812</v>
       </c>
       <c r="E194" t="n">
-        <v>557.6699829101562</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="F194" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B195" t="n">
-        <v>555.5499877929688</v>
+        <v>543.3400268554688</v>
       </c>
       <c r="C195" t="n">
-        <v>556.3400268554688</v>
+        <v>556.8499755859375</v>
       </c>
       <c r="D195" t="n">
-        <v>540.1799926757812</v>
+        <v>540.4000244140625</v>
       </c>
       <c r="E195" t="n">
-        <v>542.8699951171875</v>
+        <v>550.25</v>
       </c>
       <c r="F195" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B196" t="n">
-        <v>543.3400268554688</v>
+        <v>560</v>
       </c>
       <c r="C196" t="n">
-        <v>556.8499755859375</v>
+        <v>570.9000244140625</v>
       </c>
       <c r="D196" t="n">
-        <v>540.4000244140625</v>
+        <v>558</v>
       </c>
       <c r="E196" t="n">
-        <v>550.25</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="F196" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B197" t="n">
-        <v>560</v>
+        <v>560.9400024414062</v>
       </c>
       <c r="C197" t="n">
-        <v>570.9000244140625</v>
+        <v>565.5399780273438</v>
       </c>
       <c r="D197" t="n">
-        <v>558</v>
+        <v>551.4299926757812</v>
       </c>
       <c r="E197" t="n">
-        <v>562.5999755859375</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F197" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B198" t="n">
-        <v>560.9400024414062</v>
+        <v>607.9099731445312</v>
       </c>
       <c r="C198" t="n">
-        <v>565.5399780273438</v>
+        <v>628.280029296875</v>
       </c>
       <c r="D198" t="n">
-        <v>551.4299926757812</v>
+        <v>595.0999755859375</v>
       </c>
       <c r="E198" t="n">
-        <v>563.2899780273438</v>
+        <v>612.9099731445312</v>
       </c>
       <c r="F198" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B199" t="n">
-        <v>607.9099731445312</v>
+        <v>607.9000244140625</v>
       </c>
       <c r="C199" t="n">
-        <v>628.280029296875</v>
+        <v>610</v>
       </c>
       <c r="D199" t="n">
-        <v>595.0999755859375</v>
+        <v>580.4199829101562</v>
       </c>
       <c r="E199" t="n">
-        <v>612.9099731445312</v>
+        <v>582.9000244140625</v>
       </c>
       <c r="F199" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B200" t="n">
-        <v>607.9000244140625</v>
+        <v>594.8400268554688</v>
       </c>
       <c r="C200" t="n">
-        <v>610</v>
+        <v>603.5800170898438</v>
       </c>
       <c r="D200" t="n">
-        <v>580.4199829101562</v>
+        <v>581.760009765625</v>
       </c>
       <c r="E200" t="n">
-        <v>582.9000244140625</v>
+        <v>600.2899780273438</v>
       </c>
       <c r="F200" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B201" t="n">
-        <v>594.8400268554688</v>
+        <v>607.5900268554688</v>
       </c>
       <c r="C201" t="n">
-        <v>603.5800170898438</v>
+        <v>625.3699951171875</v>
       </c>
       <c r="D201" t="n">
-        <v>581.760009765625</v>
+        <v>603.6599731445312</v>
       </c>
       <c r="E201" t="n">
-        <v>600.2899780273438</v>
+        <v>615.5800170898438</v>
       </c>
       <c r="F201" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B202" t="n">
-        <v>607.5900268554688</v>
+        <v>614.3900146484375</v>
       </c>
       <c r="C202" t="n">
-        <v>625.3699951171875</v>
+        <v>616</v>
       </c>
       <c r="D202" t="n">
-        <v>603.6599731445312</v>
+        <v>598.010009765625</v>
       </c>
       <c r="E202" t="n">
-        <v>615.5800170898438</v>
+        <v>603.1199951171875</v>
       </c>
       <c r="F202" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B203" t="n">
-        <v>614.3900146484375</v>
+        <v>583.989990234375</v>
       </c>
       <c r="C203" t="n">
-        <v>616</v>
+        <v>633.27001953125</v>
       </c>
       <c r="D203" t="n">
-        <v>598.010009765625</v>
+        <v>577.0700073242188</v>
       </c>
       <c r="E203" t="n">
-        <v>603.1199951171875</v>
+        <v>631.47998046875</v>
       </c>
       <c r="F203" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B204" t="n">
-        <v>583.989990234375</v>
+        <v>660.3400268554688</v>
       </c>
       <c r="C204" t="n">
-        <v>633.27001953125</v>
+        <v>677.8599853515625</v>
       </c>
       <c r="D204" t="n">
-        <v>577.0700073242188</v>
+        <v>658.010009765625</v>
       </c>
       <c r="E204" t="n">
-        <v>631.47998046875</v>
+        <v>669.2100219726562</v>
       </c>
       <c r="F204" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B205" t="n">
-        <v>660.3400268554688</v>
+        <v>661.3800048828125</v>
       </c>
       <c r="C205" t="n">
-        <v>677.8599853515625</v>
+        <v>676.6199951171875</v>
       </c>
       <c r="D205" t="n">
-        <v>658.010009765625</v>
+        <v>654.2000122070312</v>
       </c>
       <c r="E205" t="n">
-        <v>669.2100219726562</v>
+        <v>656.72998046875</v>
       </c>
       <c r="F205" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>661.3800048828125</v>
+        <v>652</v>
       </c>
       <c r="C206" t="n">
-        <v>676.6199951171875</v>
+        <v>666.5</v>
       </c>
       <c r="D206" t="n">
-        <v>654.2000122070312</v>
+        <v>649.0499877929688</v>
       </c>
       <c r="E206" t="n">
-        <v>656.72998046875</v>
+        <v>661.0399780273438</v>
       </c>
       <c r="F206" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>652</v>
+        <v>663.5999755859375</v>
       </c>
       <c r="C207" t="n">
-        <v>666.5</v>
+        <v>686.0800170898438</v>
       </c>
       <c r="D207" t="n">
-        <v>649.0499877929688</v>
+        <v>656.6599731445312</v>
       </c>
       <c r="E207" t="n">
-        <v>661.0399780273438</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="F207" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B208" t="n">
-        <v>663.5999755859375</v>
+        <v>677.280029296875</v>
       </c>
       <c r="C208" t="n">
-        <v>686.0800170898438</v>
+        <v>681.9000244140625</v>
       </c>
       <c r="D208" t="n">
-        <v>656.6599731445312</v>
+        <v>660.1599731445312</v>
       </c>
       <c r="E208" t="n">
-        <v>681.3099975585938</v>
+        <v>664.5399780273438</v>
       </c>
       <c r="F208" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B209" t="n">
-        <v>677.280029296875</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C209" t="n">
-        <v>681.9000244140625</v>
+        <v>652.2000122070312</v>
       </c>
       <c r="D209" t="n">
-        <v>660.1599731445312</v>
+        <v>626</v>
       </c>
       <c r="E209" t="n">
-        <v>664.5399780273438</v>
+        <v>646.010009765625</v>
       </c>
       <c r="F209" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B210" t="n">
-        <v>647.7000122070312</v>
+        <v>646.7000122070312</v>
       </c>
       <c r="C210" t="n">
-        <v>652.2000122070312</v>
+        <v>653.2999877929688</v>
       </c>
       <c r="D210" t="n">
-        <v>626</v>
+        <v>636.010009765625</v>
       </c>
       <c r="E210" t="n">
-        <v>646.010009765625</v>
+        <v>645.8499755859375</v>
       </c>
       <c r="F210" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B211" t="n">
-        <v>646.7000122070312</v>
+        <v>654.1799926757812</v>
       </c>
       <c r="C211" t="n">
-        <v>653.2999877929688</v>
+        <v>655.8800048828125</v>
       </c>
       <c r="D211" t="n">
-        <v>636.010009765625</v>
+        <v>643.2000122070312</v>
       </c>
       <c r="E211" t="n">
-        <v>645.8499755859375</v>
+        <v>643.8099975585938</v>
       </c>
       <c r="F211" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B212" t="n">
-        <v>654.1799926757812</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C212" t="n">
-        <v>655.8800048828125</v>
+        <v>649</v>
       </c>
       <c r="D212" t="n">
-        <v>643.2000122070312</v>
+        <v>624</v>
       </c>
       <c r="E212" t="n">
-        <v>643.8099975585938</v>
+        <v>627.1699829101562</v>
       </c>
       <c r="F212" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B213" t="n">
-        <v>647.7000122070312</v>
+        <v>608.4099731445312</v>
       </c>
       <c r="C213" t="n">
-        <v>649</v>
+        <v>614.6500244140625</v>
       </c>
       <c r="D213" t="n">
-        <v>624</v>
+        <v>597.219970703125</v>
       </c>
       <c r="E213" t="n">
-        <v>627.1699829101562</v>
+        <v>606.0999755859375</v>
       </c>
       <c r="F213" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B214" t="n">
-        <v>608.4099731445312</v>
+        <v>605.2999877929688</v>
       </c>
       <c r="C214" t="n">
-        <v>614.6500244140625</v>
+        <v>609.97998046875</v>
       </c>
       <c r="D214" t="n">
-        <v>597.219970703125</v>
+        <v>594.4500122070312</v>
       </c>
       <c r="E214" t="n">
-        <v>606.0999755859375</v>
+        <v>595.1900024414062</v>
       </c>
       <c r="F214" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B215" t="n">
-        <v>605.2999877929688</v>
+        <v>607.219970703125</v>
       </c>
       <c r="C215" t="n">
-        <v>609.97998046875</v>
+        <v>611.260009765625</v>
       </c>
       <c r="D215" t="n">
-        <v>594.4500122070312</v>
+        <v>593.1300048828125</v>
       </c>
       <c r="E215" t="n">
-        <v>595.1900024414062</v>
+        <v>593.8699951171875</v>
       </c>
       <c r="F215" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B216" t="n">
-        <v>607.219970703125</v>
+        <v>596.8200073242188</v>
       </c>
       <c r="C216" t="n">
-        <v>611.260009765625</v>
+        <v>601</v>
       </c>
       <c r="D216" t="n">
-        <v>593.1300048828125</v>
+        <v>587</v>
       </c>
       <c r="E216" t="n">
-        <v>593.8699951171875</v>
+        <v>593.4099731445312</v>
       </c>
       <c r="F216" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B217" t="n">
-        <v>596.8200073242188</v>
+        <v>593.25</v>
       </c>
       <c r="C217" t="n">
-        <v>601</v>
+        <v>599.969970703125</v>
       </c>
       <c r="D217" t="n">
-        <v>587</v>
+        <v>582.219970703125</v>
       </c>
       <c r="E217" t="n">
-        <v>593.4099731445312</v>
+        <v>585.6099853515625</v>
       </c>
       <c r="F217" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B218" t="n">
-        <v>593.25</v>
+        <v>526</v>
       </c>
       <c r="C218" t="n">
-        <v>599.969970703125</v>
+        <v>539.8800048828125</v>
       </c>
       <c r="D218" t="n">
-        <v>582.219970703125</v>
+        <v>524.489990234375</v>
       </c>
       <c r="E218" t="n">
-        <v>585.6099853515625</v>
+        <v>539.030029296875</v>
       </c>
       <c r="F218" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B219" t="n">
-        <v>526</v>
+        <v>543.5999755859375</v>
       </c>
       <c r="C219" t="n">
-        <v>539.8800048828125</v>
+        <v>558.3300170898438</v>
       </c>
       <c r="D219" t="n">
-        <v>524.489990234375</v>
+        <v>540.219970703125</v>
       </c>
       <c r="E219" t="n">
-        <v>539.030029296875</v>
+        <v>556.7100219726562</v>
       </c>
       <c r="F219" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B220" t="n">
-        <v>543.5999755859375</v>
+        <v>562.239990234375</v>
       </c>
       <c r="C220" t="n">
-        <v>558.3300170898438</v>
+        <v>597.52001953125</v>
       </c>
       <c r="D220" t="n">
-        <v>540.219970703125</v>
+        <v>559.3599853515625</v>
       </c>
       <c r="E220" t="n">
-        <v>556.7100219726562</v>
+        <v>590.239990234375</v>
       </c>
       <c r="F220" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B221" t="n">
-        <v>562.239990234375</v>
+        <v>581.5</v>
       </c>
       <c r="C221" t="n">
-        <v>597.52001953125</v>
+        <v>592.7899780273438</v>
       </c>
       <c r="D221" t="n">
-        <v>559.3599853515625</v>
+        <v>578.25</v>
       </c>
       <c r="E221" t="n">
-        <v>590.239990234375</v>
+        <v>587.9400024414062</v>
       </c>
       <c r="F221" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B222" t="n">
-        <v>581.5</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="C222" t="n">
-        <v>592.7899780273438</v>
+        <v>601</v>
       </c>
       <c r="D222" t="n">
-        <v>578.25</v>
+        <v>580.1199951171875</v>
       </c>
       <c r="E222" t="n">
-        <v>587.9400024414062</v>
+        <v>588.77001953125</v>
       </c>
       <c r="F222" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B223" t="n">
-        <v>600.4600219726562</v>
+        <v>586.9500122070312</v>
       </c>
       <c r="C223" t="n">
-        <v>601</v>
+        <v>595.3099975585938</v>
       </c>
       <c r="D223" t="n">
-        <v>580.1199951171875</v>
+        <v>586</v>
       </c>
       <c r="E223" t="n">
-        <v>588.77001953125</v>
+        <v>589.9000244140625</v>
       </c>
       <c r="F223" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B224" t="n">
-        <v>586.9500122070312</v>
+        <v>585.6400146484375</v>
       </c>
       <c r="C224" t="n">
-        <v>595.3099975585938</v>
+        <v>598.739990234375</v>
       </c>
       <c r="D224" t="n">
-        <v>586</v>
+        <v>585.6199951171875</v>
       </c>
       <c r="E224" t="n">
-        <v>589.9000244140625</v>
+        <v>592.0999755859375</v>
       </c>
       <c r="F224" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B225" t="n">
-        <v>585.6400146484375</v>
+        <v>599.1300048828125</v>
       </c>
       <c r="C225" t="n">
-        <v>598.739990234375</v>
+        <v>608.2100219726562</v>
       </c>
       <c r="D225" t="n">
-        <v>585.6199951171875</v>
+        <v>592.030029296875</v>
       </c>
       <c r="E225" t="n">
-        <v>592.0999755859375</v>
+        <v>594.9199829101562</v>
       </c>
       <c r="F225" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B226" t="n">
-        <v>599.1300048828125</v>
+        <v>598</v>
       </c>
       <c r="C226" t="n">
-        <v>608.2100219726562</v>
+        <v>612.4299926757812</v>
       </c>
       <c r="D226" t="n">
-        <v>592.030029296875</v>
+        <v>593.4000244140625</v>
       </c>
       <c r="E226" t="n">
-        <v>594.9199829101562</v>
+        <v>599.1199951171875</v>
       </c>
       <c r="F226" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B227" t="n">
-        <v>598</v>
+        <v>601.0700073242188</v>
       </c>
       <c r="C227" t="n">
-        <v>612.4299926757812</v>
+        <v>604.5</v>
       </c>
       <c r="D227" t="n">
-        <v>593.4000244140625</v>
+        <v>578.2100219726562</v>
       </c>
       <c r="E227" t="n">
-        <v>599.1199951171875</v>
+        <v>578.8499755859375</v>
       </c>
       <c r="F227" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B228" t="n">
-        <v>601.0700073242188</v>
+        <v>580.7100219726562</v>
       </c>
       <c r="C228" t="n">
-        <v>604.5</v>
+        <v>595.8499755859375</v>
       </c>
       <c r="D228" t="n">
-        <v>578.2100219726562</v>
+        <v>579.3900146484375</v>
       </c>
       <c r="E228" t="n">
-        <v>578.8499755859375</v>
+        <v>594.969970703125</v>
       </c>
       <c r="F228" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B229" t="n">
-        <v>580.7100219726562</v>
+        <v>596.97998046875</v>
       </c>
       <c r="C229" t="n">
-        <v>595.8499755859375</v>
+        <v>601.8599853515625</v>
       </c>
       <c r="D229" t="n">
-        <v>579.3900146484375</v>
+        <v>589.2899780273438</v>
       </c>
       <c r="E229" t="n">
-        <v>594.969970703125</v>
+        <v>589.8499755859375</v>
       </c>
       <c r="F229" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B230" t="n">
-        <v>596.97998046875</v>
+        <v>589.75</v>
       </c>
       <c r="C230" t="n">
-        <v>601.8599853515625</v>
+        <v>590.239990234375</v>
       </c>
       <c r="D230" t="n">
-        <v>589.2899780273438</v>
+        <v>564.75</v>
       </c>
       <c r="E230" t="n">
-        <v>589.8499755859375</v>
+        <v>568.969970703125</v>
       </c>
       <c r="F230" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B231" t="n">
-        <v>589.75</v>
+        <v>557.47998046875</v>
       </c>
       <c r="C231" t="n">
-        <v>590.239990234375</v>
+        <v>560.6599731445312</v>
       </c>
       <c r="D231" t="n">
-        <v>564.75</v>
+        <v>543.2100219726562</v>
       </c>
       <c r="E231" t="n">
-        <v>568.969970703125</v>
+        <v>543.6699829101562</v>
       </c>
       <c r="F231" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B232" t="n">
-        <v>557.47998046875</v>
+        <v>541.3400268554688</v>
       </c>
       <c r="C232" t="n">
-        <v>560.6599731445312</v>
+        <v>554.0700073242188</v>
       </c>
       <c r="D232" t="n">
-        <v>543.2100219726562</v>
+        <v>537.27001953125</v>
       </c>
       <c r="E232" t="n">
-        <v>543.6699829101562</v>
+        <v>546.030029296875</v>
       </c>
       <c r="F232" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B233" t="n">
-        <v>541.3400268554688</v>
+        <v>546.9500122070312</v>
       </c>
       <c r="C233" t="n">
-        <v>554.0700073242188</v>
+        <v>549.989990234375</v>
       </c>
       <c r="D233" t="n">
-        <v>537.27001953125</v>
+        <v>539.3099975585938</v>
       </c>
       <c r="E233" t="n">
-        <v>546.030029296875</v>
+        <v>545.8300170898438</v>
       </c>
       <c r="F233" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B234" t="n">
-        <v>546.9500122070312</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="C234" t="n">
-        <v>549.989990234375</v>
+        <v>553.8699951171875</v>
       </c>
       <c r="D234" t="n">
-        <v>539.3099975585938</v>
+        <v>543.22998046875</v>
       </c>
       <c r="E234" t="n">
-        <v>545.8300170898438</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="F234" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B235" t="n">
-        <v>546.8900146484375</v>
+        <v>550.2000122070312</v>
       </c>
       <c r="C235" t="n">
-        <v>553.8699951171875</v>
+        <v>561.4199829101562</v>
       </c>
       <c r="D235" t="n">
-        <v>543.22998046875</v>
+        <v>546.2999877929688</v>
       </c>
       <c r="E235" t="n">
-        <v>549.9000244140625</v>
+        <v>559.02001953125</v>
       </c>
       <c r="F235" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B236" t="n">
-        <v>550.2000122070312</v>
+        <v>563.8800048828125</v>
       </c>
       <c r="C236" t="n">
-        <v>561.4199829101562</v>
+        <v>570.7999877929688</v>
       </c>
       <c r="D236" t="n">
-        <v>546.2999877929688</v>
+        <v>561.4000244140625</v>
       </c>
       <c r="E236" t="n">
-        <v>559.02001953125</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="F236" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B237" t="n">
-        <v>563.8800048828125</v>
+        <v>590.3099975585938</v>
       </c>
       <c r="C237" t="n">
-        <v>570.7999877929688</v>
+        <v>593.3400268554688</v>
       </c>
       <c r="D237" t="n">
-        <v>561.4000244140625</v>
+        <v>561.8800048828125</v>
       </c>
       <c r="E237" t="n">
-        <v>570.0499877929688</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="F237" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B238" t="n">
-        <v>590.3099975585938</v>
+        <v>576.47998046875</v>
       </c>
       <c r="C238" t="n">
-        <v>593.3400268554688</v>
+        <v>588.3900146484375</v>
       </c>
       <c r="D238" t="n">
-        <v>561.8800048828125</v>
+        <v>567.6199951171875</v>
       </c>
       <c r="E238" t="n">
-        <v>576.1400146484375</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="F238" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B239" t="n">
-        <v>576.47998046875</v>
+        <v>571.5499877929688</v>
       </c>
       <c r="C239" t="n">
-        <v>588.3900146484375</v>
+        <v>589.1900024414062</v>
       </c>
       <c r="D239" t="n">
-        <v>567.6199951171875</v>
+        <v>571</v>
       </c>
       <c r="E239" t="n">
-        <v>571.0999755859375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="F239" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B240" t="n">
-        <v>571.5499877929688</v>
+        <v>577.6300048828125</v>
       </c>
       <c r="C240" t="n">
-        <v>589.1900024414062</v>
+        <v>578.6799926757812</v>
       </c>
       <c r="D240" t="n">
-        <v>571</v>
+        <v>569.1400146484375</v>
       </c>
       <c r="E240" t="n">
-        <v>578.02001953125</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="F240" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B241" t="n">
-        <v>577.6300048828125</v>
+        <v>558.3499755859375</v>
       </c>
       <c r="C241" t="n">
-        <v>578.6799926757812</v>
+        <v>584.9500122070312</v>
       </c>
       <c r="D241" t="n">
-        <v>569.1400146484375</v>
+        <v>556.0999755859375</v>
       </c>
       <c r="E241" t="n">
-        <v>572.3400268554688</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="F241" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B242" t="n">
-        <v>558.3499755859375</v>
+        <v>578.7899780273438</v>
       </c>
       <c r="C242" t="n">
-        <v>584.9500122070312</v>
+        <v>600.3800048828125</v>
       </c>
       <c r="D242" t="n">
-        <v>556.0999755859375</v>
+        <v>577</v>
       </c>
       <c r="E242" t="n">
-        <v>578.5399780273438</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="F242" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B243" t="n">
-        <v>578.7899780273438</v>
+        <v>604.489990234375</v>
       </c>
       <c r="C243" t="n">
-        <v>600.3800048828125</v>
+        <v>619.4600219726562</v>
       </c>
       <c r="D243" t="n">
-        <v>577</v>
+        <v>604.3499755859375</v>
       </c>
       <c r="E243" t="n">
-        <v>592.8499755859375</v>
+        <v>610.6799926757812</v>
       </c>
       <c r="F243" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B244" t="n">
-        <v>604.489990234375</v>
+        <v>612.3499755859375</v>
       </c>
       <c r="C244" t="n">
-        <v>619.4600219726562</v>
+        <v>617.4600219726562</v>
       </c>
       <c r="D244" t="n">
-        <v>604.3499755859375</v>
+        <v>605.27001953125</v>
       </c>
       <c r="E244" t="n">
-        <v>610.6799926757812</v>
+        <v>616.77001953125</v>
       </c>
       <c r="F244" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B245" t="n">
-        <v>612.3499755859375</v>
+        <v>616.2100219726562</v>
       </c>
       <c r="C245" t="n">
-        <v>617.4600219726562</v>
+        <v>624.7999877929688</v>
       </c>
       <c r="D245" t="n">
-        <v>605.27001953125</v>
+        <v>609.739990234375</v>
       </c>
       <c r="E245" t="n">
-        <v>616.77001953125</v>
+        <v>613.47998046875</v>
       </c>
       <c r="F245" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B246" t="n">
-        <v>616.2100219726562</v>
+        <v>648.6400146484375</v>
       </c>
       <c r="C246" t="n">
-        <v>624.7999877929688</v>
+        <v>657.8599853515625</v>
       </c>
       <c r="D246" t="n">
-        <v>609.739990234375</v>
+        <v>638.5599975585938</v>
       </c>
       <c r="E246" t="n">
-        <v>613.47998046875</v>
+        <v>653.6900024414062</v>
       </c>
       <c r="F246" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B247" t="n">
-        <v>648.6400146484375</v>
+        <v>653.7100219726562</v>
       </c>
       <c r="C247" t="n">
-        <v>657.8599853515625</v>
+        <v>663.5</v>
       </c>
       <c r="D247" t="n">
-        <v>638.5599975585938</v>
+        <v>642.1400146484375</v>
       </c>
       <c r="E247" t="n">
-        <v>653.6900024414062</v>
+        <v>644.3800048828125</v>
       </c>
       <c r="F247" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B248" t="n">
-        <v>653.7100219726562</v>
+        <v>653.510009765625</v>
       </c>
       <c r="C248" t="n">
-        <v>663.5</v>
+        <v>664.239990234375</v>
       </c>
       <c r="D248" t="n">
-        <v>642.1400146484375</v>
+        <v>646.2000122070312</v>
       </c>
       <c r="E248" t="n">
-        <v>644.3800048828125</v>
+        <v>648.030029296875</v>
       </c>
       <c r="F248" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B249" t="n">
-        <v>653.510009765625</v>
+        <v>657.8300170898438</v>
       </c>
       <c r="C249" t="n">
-        <v>664.239990234375</v>
+        <v>668.5999755859375</v>
       </c>
       <c r="D249" t="n">
-        <v>646.2000122070312</v>
+        <v>649.219970703125</v>
       </c>
       <c r="E249" t="n">
-        <v>648.030029296875</v>
+        <v>665.5999755859375</v>
       </c>
       <c r="F249" t="n">
-        <v>16925000</v>
+        <v>19332300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B250" t="n">
-        <v>657.8300170898438</v>
+        <v>659.2999877929688</v>
       </c>
       <c r="C250" t="n">
-        <v>668.5999755859375</v>
+        <v>678.8699951171875</v>
       </c>
       <c r="D250" t="n">
-        <v>649.219970703125</v>
+        <v>656.2000122070312</v>
       </c>
       <c r="E250" t="n">
-        <v>665.5999755859375</v>
+        <v>670.239990234375</v>
       </c>
       <c r="F250" t="n">
-        <v>19332300</v>
+        <v>19502800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B251" t="n">
-        <v>659.2999877929688</v>
+        <v>679.9099731445312</v>
       </c>
       <c r="C251" t="n">
-        <v>678.8699951171875</v>
+        <v>685.3099975585938</v>
       </c>
       <c r="D251" t="n">
-        <v>656.2000122070312</v>
+        <v>671.9099731445312</v>
       </c>
       <c r="E251" t="n">
-        <v>670.239990234375</v>
+        <v>673.3099975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>19502800</v>
+        <v>17217800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46282</v>
+      </c>
+      <c r="B252" t="n">
+        <v>682.4400024414062</v>
+      </c>
+      <c r="C252" t="n">
+        <v>683.2000122070312</v>
+      </c>
+      <c r="D252" t="n">
+        <v>667.0499877929688</v>
+      </c>
+      <c r="E252" t="n">
+        <v>682.3099975585938</v>
+      </c>
       <c r="F252" t="n">
-        <v>17169529</v>
+        <v>15888400</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10768,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>682.3099999999999</v>
+      </c>
+      <c r="D2" t="n">
         <v>673.3099999999999</v>
       </c>
-      <c r="D2" t="n">
-        <v>670.24</v>
-      </c>
       <c r="E2" t="n">
-        <v>679.75</v>
+        <v>682.4400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>685.3099999999999</v>
+        <v>683.2</v>
       </c>
       <c r="G2" t="n">
-        <v>671.9142000000001</v>
+        <v>667.05</v>
       </c>
       <c r="H2" t="n">
-        <v>17169529</v>
+        <v>15740199</v>
       </c>
       <c r="I2" t="n">
-        <v>18423041</v>
+        <v>18199354</v>
       </c>
       <c r="J2" t="n">
-        <v>1715261407232</v>
+        <v>1738188914688</v>
       </c>
       <c r="K2" t="n">
-        <v>25.369629</v>
+        <v>25.383556</v>
       </c>
       <c r="L2" t="n">
-        <v>19.259626</v>
+        <v>19.517067</v>
       </c>
       <c r="M2" t="n">
-        <v>26.54</v>
+        <v>26.88</v>
       </c>
       <c r="N2" t="n">
         <v>790.8</v>
@@ -10834,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.567597</v>
+        <v>6.6553845</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10846,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1729498578944</v>
+        <v>1760247021568</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10873,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-17 08:09:53</t>
+          <t>2026-09-18 13:15:32</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B2" t="n">
-        <v>778.1994774600552</v>
+        <v>783.8508708699721</v>
       </c>
       <c r="C2" t="n">
-        <v>786.203274581819</v>
+        <v>788.2165669565625</v>
       </c>
       <c r="D2" t="n">
-        <v>770.8336042127465</v>
+        <v>766.6771780735046</v>
       </c>
       <c r="E2" t="n">
-        <v>777.7011108398438</v>
+        <v>775.837158203125</v>
       </c>
       <c r="F2" t="n">
-        <v>10955000</v>
+        <v>23696800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,25 +495,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B3" t="n">
-        <v>783.8508708699721</v>
+        <v>779.8218176027002</v>
       </c>
       <c r="C3" t="n">
-        <v>788.2165669565625</v>
+        <v>783.6917575585782</v>
       </c>
       <c r="D3" t="n">
-        <v>766.6771780735046</v>
+        <v>762.4868973227559</v>
       </c>
       <c r="E3" t="n">
-        <v>775.837158203125</v>
+        <v>763.1751098632812</v>
       </c>
       <c r="F3" t="n">
-        <v>23696800</v>
+        <v>11706900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -521,25 +521,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>779.8217552362186</v>
+        <v>767.254476840496</v>
       </c>
       <c r="C4" t="n">
-        <v>783.6916948825968</v>
+        <v>768.6009504341728</v>
       </c>
       <c r="D4" t="n">
-        <v>762.4868363426395</v>
+        <v>749.1216451610411</v>
       </c>
       <c r="E4" t="n">
-        <v>763.175048828125</v>
+        <v>753.4404296875</v>
       </c>
       <c r="F4" t="n">
-        <v>11706900</v>
+        <v>10872600</v>
       </c>
       <c r="G4" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B5" t="n">
-        <v>767.2545389947088</v>
+        <v>755.5349916265823</v>
       </c>
       <c r="C5" t="n">
-        <v>768.6010126974617</v>
+        <v>759.1356124217834</v>
       </c>
       <c r="D5" t="n">
-        <v>749.1217058463387</v>
+        <v>750.5779133776451</v>
       </c>
       <c r="E5" t="n">
-        <v>753.4404907226562</v>
+        <v>758.686767578125</v>
       </c>
       <c r="F5" t="n">
-        <v>10872600</v>
+        <v>8828200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B6" t="n">
-        <v>755.5349308449814</v>
+        <v>751.4954858581857</v>
       </c>
       <c r="C6" t="n">
-        <v>759.1355513505183</v>
+        <v>754.8068807440363</v>
       </c>
       <c r="D6" t="n">
-        <v>750.5778529948334</v>
+        <v>742.6185490172081</v>
       </c>
       <c r="E6" t="n">
-        <v>758.6867065429688</v>
+        <v>746.9672241210938</v>
       </c>
       <c r="F6" t="n">
-        <v>8828200</v>
+        <v>10591100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B7" t="n">
-        <v>751.4954858581857</v>
+        <v>748.0544659269957</v>
       </c>
       <c r="C7" t="n">
-        <v>754.8068807440363</v>
+        <v>749.9794521140951</v>
       </c>
       <c r="D7" t="n">
-        <v>742.6185490172081</v>
+        <v>735.4372562509625</v>
       </c>
       <c r="E7" t="n">
-        <v>746.9672241210938</v>
+        <v>741.8206787109375</v>
       </c>
       <c r="F7" t="n">
-        <v>10591100</v>
+        <v>9696300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B8" t="n">
-        <v>748.0544659269957</v>
+        <v>746.777703342028</v>
       </c>
       <c r="C8" t="n">
-        <v>749.9794521140951</v>
+        <v>748.8324179023273</v>
       </c>
       <c r="D8" t="n">
-        <v>735.4372562509625</v>
+        <v>737.2325826153279</v>
       </c>
       <c r="E8" t="n">
-        <v>741.8206787109375</v>
+        <v>741.4715576171875</v>
       </c>
       <c r="F8" t="n">
-        <v>9696300</v>
+        <v>9246800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B9" t="n">
-        <v>746.7777648139662</v>
+        <v>740.3245554260684</v>
       </c>
       <c r="C9" t="n">
-        <v>748.832479543402</v>
+        <v>741.0426584785586</v>
       </c>
       <c r="D9" t="n">
-        <v>737.2326433015477</v>
+        <v>724.4159185837501</v>
       </c>
       <c r="E9" t="n">
-        <v>741.4716186523438</v>
+        <v>732.4749755859375</v>
       </c>
       <c r="F9" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B10" t="n">
-        <v>740.3245554260684</v>
+        <v>719.6183236513255</v>
       </c>
       <c r="C10" t="n">
-        <v>741.0426584785586</v>
+        <v>719.9773751402398</v>
       </c>
       <c r="D10" t="n">
-        <v>724.4159185837501</v>
+        <v>708.357633728991</v>
       </c>
       <c r="E10" t="n">
-        <v>732.4749755859375</v>
+        <v>715.4791259765625</v>
       </c>
       <c r="F10" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B11" t="n">
-        <v>719.618385039583</v>
+        <v>720.7055653205383</v>
       </c>
       <c r="C11" t="n">
-        <v>719.9774365591268</v>
+        <v>725.8821043267139</v>
       </c>
       <c r="D11" t="n">
-        <v>708.3576941566364</v>
+        <v>716.2770807321521</v>
       </c>
       <c r="E11" t="n">
-        <v>715.4791870117188</v>
+        <v>725.1639404296875</v>
       </c>
       <c r="F11" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B12" t="n">
-        <v>720.7056259804448</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C12" t="n">
-        <v>725.8821654223162</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D12" t="n">
-        <v>716.2771410193245</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E12" t="n">
-        <v>725.1640014648438</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F12" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B13" t="n">
-        <v>727.7372737109582</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C13" t="n">
-        <v>729.1037149276121</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D13" t="n">
-        <v>708.3377167266436</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E13" t="n">
-        <v>708.7167358398438</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F13" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B14" t="n">
-        <v>703.3607165744016</v>
+        <v>715.8581417735932</v>
       </c>
       <c r="C14" t="n">
-        <v>715.0203947681905</v>
+        <v>716.6361476056489</v>
       </c>
       <c r="D14" t="n">
-        <v>688.718804278428</v>
+        <v>703.9192222306009</v>
       </c>
       <c r="E14" t="n">
-        <v>713.8035278320312</v>
+        <v>711.230224609375</v>
       </c>
       <c r="F14" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B15" t="n">
-        <v>715.8581417735932</v>
+        <v>711.599278595462</v>
       </c>
       <c r="C15" t="n">
-        <v>716.6361476056489</v>
+        <v>717.7832075860277</v>
       </c>
       <c r="D15" t="n">
-        <v>703.9192222306009</v>
+        <v>705.9738944950672</v>
       </c>
       <c r="E15" t="n">
-        <v>711.230224609375</v>
+        <v>715.9779052734375</v>
       </c>
       <c r="F15" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B16" t="n">
-        <v>711.5993392573523</v>
+        <v>716.4167658258609</v>
       </c>
       <c r="C16" t="n">
-        <v>717.783268775081</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="D16" t="n">
-        <v>705.9739546774089</v>
+        <v>710.5918883665408</v>
       </c>
       <c r="E16" t="n">
-        <v>715.9779663085938</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="F16" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B17" t="n">
-        <v>716.4167658258609</v>
+        <v>729.0239332852144</v>
       </c>
       <c r="C17" t="n">
-        <v>731.6072387695312</v>
+        <v>733.3626856542741</v>
       </c>
       <c r="D17" t="n">
-        <v>710.5918883665408</v>
+        <v>702.6824691715568</v>
       </c>
       <c r="E17" t="n">
-        <v>731.6072387695312</v>
+        <v>703.4703979492188</v>
       </c>
       <c r="F17" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B18" t="n">
-        <v>729.0239332852144</v>
+        <v>711.1603595995662</v>
       </c>
       <c r="C18" t="n">
-        <v>733.3626856542741</v>
+        <v>718.072374881022</v>
       </c>
       <c r="D18" t="n">
-        <v>702.6824691715568</v>
+        <v>705.8042950194317</v>
       </c>
       <c r="E18" t="n">
-        <v>703.4703979492188</v>
+        <v>713.8433837890625</v>
       </c>
       <c r="F18" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B19" t="n">
-        <v>711.1603595995662</v>
+        <v>705.9439682909708</v>
       </c>
       <c r="C19" t="n">
-        <v>718.072374881022</v>
+        <v>713.6937706407739</v>
       </c>
       <c r="D19" t="n">
-        <v>705.8042950194317</v>
+        <v>697.5158763660478</v>
       </c>
       <c r="E19" t="n">
-        <v>713.8433837890625</v>
+        <v>706.8117065429688</v>
       </c>
       <c r="F19" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B20" t="n">
-        <v>705.9439682909708</v>
+        <v>715.1998794771447</v>
       </c>
       <c r="C20" t="n">
-        <v>713.6937706407739</v>
+        <v>722.0221626881838</v>
       </c>
       <c r="D20" t="n">
-        <v>697.5158763660478</v>
+        <v>707.6694770310874</v>
       </c>
       <c r="E20" t="n">
-        <v>706.8117065429688</v>
+        <v>715.6885986328125</v>
       </c>
       <c r="F20" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B21" t="n">
-        <v>715.1998794771447</v>
+        <v>715.6886043056783</v>
       </c>
       <c r="C21" t="n">
-        <v>722.0221626881838</v>
+        <v>723.6080097298942</v>
       </c>
       <c r="D21" t="n">
-        <v>707.6694770310874</v>
+        <v>702.0540824517458</v>
       </c>
       <c r="E21" t="n">
-        <v>715.6885986328125</v>
+        <v>710.2228393554688</v>
       </c>
       <c r="F21" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B22" t="n">
-        <v>715.6886043056783</v>
+        <v>705.2458014471516</v>
       </c>
       <c r="C22" t="n">
-        <v>723.6080097298942</v>
+        <v>716.6760344343375</v>
       </c>
       <c r="D22" t="n">
-        <v>702.0540824517458</v>
+        <v>704.2882698394852</v>
       </c>
       <c r="E22" t="n">
-        <v>710.2228393554688</v>
+        <v>715.0602416992188</v>
       </c>
       <c r="F22" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B23" t="n">
-        <v>705.2458014471516</v>
+        <v>719.3191931642514</v>
       </c>
       <c r="C23" t="n">
-        <v>716.6760344343375</v>
+        <v>731.8665769499745</v>
       </c>
       <c r="D23" t="n">
-        <v>704.2882698394852</v>
+        <v>718.3118034233538</v>
       </c>
       <c r="E23" t="n">
-        <v>715.0602416992188</v>
+        <v>730.2706909179688</v>
       </c>
       <c r="F23" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B24" t="n">
-        <v>719.3191330444083</v>
+        <v>734.1107251683979</v>
       </c>
       <c r="C24" t="n">
-        <v>731.866515781436</v>
+        <v>736.5842723709278</v>
       </c>
       <c r="D24" t="n">
-        <v>718.3117433877071</v>
+        <v>726.8595646449745</v>
       </c>
       <c r="E24" t="n">
-        <v>730.2706298828125</v>
+        <v>731.3678588867188</v>
       </c>
       <c r="F24" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B25" t="n">
-        <v>734.1107864324557</v>
+        <v>731.9264006052239</v>
       </c>
       <c r="C25" t="n">
-        <v>736.5843338414116</v>
+        <v>738.6787972623451</v>
       </c>
       <c r="D25" t="n">
-        <v>726.859625303898</v>
+        <v>722.1518348008319</v>
       </c>
       <c r="E25" t="n">
-        <v>731.367919921875</v>
+        <v>731.5074462890625</v>
       </c>
       <c r="F25" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B26" t="n">
-        <v>731.9264616753367</v>
+        <v>732.7941435868839</v>
       </c>
       <c r="C26" t="n">
-        <v>738.6788588958609</v>
+        <v>740.4841042897723</v>
       </c>
       <c r="D26" t="n">
-        <v>722.1518950553793</v>
+        <v>731.1982575844598</v>
       </c>
       <c r="E26" t="n">
-        <v>731.5075073242188</v>
+        <v>732.095947265625</v>
       </c>
       <c r="F26" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B27" t="n">
-        <v>732.7941435868839</v>
+        <v>734.8786455644157</v>
       </c>
       <c r="C27" t="n">
-        <v>740.4841042897723</v>
+        <v>739.2872233202683</v>
       </c>
       <c r="D27" t="n">
-        <v>731.1982575844598</v>
+        <v>729.2533227506186</v>
       </c>
       <c r="E27" t="n">
-        <v>732.095947265625</v>
+        <v>736.444580078125</v>
       </c>
       <c r="F27" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B28" t="n">
-        <v>734.8786455644157</v>
+        <v>747.7851152228061</v>
       </c>
       <c r="C28" t="n">
-        <v>739.2872233202683</v>
+        <v>753.7895182960361</v>
       </c>
       <c r="D28" t="n">
-        <v>729.2533227506186</v>
+        <v>746.069606274355</v>
       </c>
       <c r="E28" t="n">
-        <v>736.444580078125</v>
+        <v>748.872314453125</v>
       </c>
       <c r="F28" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B29" t="n">
-        <v>747.7851152228061</v>
+        <v>750.6776381609803</v>
       </c>
       <c r="C29" t="n">
-        <v>753.7895182960361</v>
+        <v>756.4326899204912</v>
       </c>
       <c r="D29" t="n">
-        <v>746.069606274355</v>
+        <v>743.5860965317024</v>
       </c>
       <c r="E29" t="n">
-        <v>748.872314453125</v>
+        <v>749.49072265625</v>
       </c>
       <c r="F29" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B30" t="n">
-        <v>750.677577029167</v>
+        <v>752.7921200604676</v>
       </c>
       <c r="C30" t="n">
-        <v>756.4326283200122</v>
+        <v>757.1906533932021</v>
       </c>
       <c r="D30" t="n">
-        <v>743.5860359773924</v>
+        <v>740.5838813084906</v>
       </c>
       <c r="E30" t="n">
-        <v>749.4906616210938</v>
+        <v>749.7200927734375</v>
       </c>
       <c r="F30" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B31" t="n">
-        <v>752.7920587752158</v>
+        <v>667.414190282622</v>
       </c>
       <c r="C31" t="n">
-        <v>757.1905917498632</v>
+        <v>679.1935516668058</v>
       </c>
       <c r="D31" t="n">
-        <v>740.5838210171188</v>
+        <v>648.4833846789722</v>
       </c>
       <c r="E31" t="n">
-        <v>749.7200317382812</v>
+        <v>664.7410888671875</v>
       </c>
       <c r="F31" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B32" t="n">
-        <v>667.414190282622</v>
+        <v>672.7602632515434</v>
       </c>
       <c r="C32" t="n">
-        <v>679.1935516668058</v>
+        <v>673.1392823636344</v>
       </c>
       <c r="D32" t="n">
-        <v>648.4833846789722</v>
+        <v>643.8953340746643</v>
       </c>
       <c r="E32" t="n">
-        <v>664.7410888671875</v>
+        <v>646.6680908203125</v>
       </c>
       <c r="F32" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B33" t="n">
-        <v>672.7603267493847</v>
+        <v>654.2982567113449</v>
       </c>
       <c r="C33" t="n">
-        <v>673.139345897249</v>
+        <v>657.619635334369</v>
       </c>
       <c r="D33" t="n">
-        <v>643.8953948481166</v>
+        <v>634.5296648817072</v>
       </c>
       <c r="E33" t="n">
-        <v>646.6681518554688</v>
+        <v>636.0557250976562</v>
       </c>
       <c r="F33" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B34" t="n">
-        <v>654.2982567113449</v>
+        <v>626.4107910285981</v>
       </c>
       <c r="C34" t="n">
-        <v>657.619635334369</v>
+        <v>640.0752642850032</v>
       </c>
       <c r="D34" t="n">
-        <v>634.5296648817072</v>
+        <v>624.3860886703497</v>
       </c>
       <c r="E34" t="n">
-        <v>636.0557250976562</v>
+        <v>625.6926879882812</v>
       </c>
       <c r="F34" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B35" t="n">
-        <v>626.4107910285981</v>
+        <v>630.6697208898194</v>
       </c>
       <c r="C35" t="n">
-        <v>640.0752642850032</v>
+        <v>640.5639703518489</v>
       </c>
       <c r="D35" t="n">
-        <v>624.3860886703497</v>
+        <v>624.9146693781357</v>
       </c>
       <c r="E35" t="n">
-        <v>625.6926879882812</v>
+        <v>634.30029296875</v>
       </c>
       <c r="F35" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B36" t="n">
-        <v>630.6697208898194</v>
+        <v>634.2005186436334</v>
       </c>
       <c r="C36" t="n">
-        <v>640.5639703518489</v>
+        <v>634.3501538797125</v>
       </c>
       <c r="D36" t="n">
-        <v>624.9146693781357</v>
+        <v>616.3968476378337</v>
       </c>
       <c r="E36" t="n">
-        <v>634.30029296875</v>
+        <v>617.3344116210938</v>
       </c>
       <c r="F36" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B37" t="n">
-        <v>634.2005186436334</v>
+        <v>614.8907386759073</v>
       </c>
       <c r="C37" t="n">
-        <v>634.3501538797125</v>
+        <v>620.5161224262619</v>
       </c>
       <c r="D37" t="n">
-        <v>616.3968476378337</v>
+        <v>599.6404247494841</v>
       </c>
       <c r="E37" t="n">
-        <v>617.3344116210938</v>
+        <v>620.0972290039062</v>
       </c>
       <c r="F37" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B38" t="n">
-        <v>614.8907991985972</v>
+        <v>629.4529708548182</v>
       </c>
       <c r="C38" t="n">
-        <v>620.516183502649</v>
+        <v>633.3528014765299</v>
       </c>
       <c r="D38" t="n">
-        <v>599.6404837711106</v>
+        <v>616.5065997528014</v>
       </c>
       <c r="E38" t="n">
-        <v>620.0972900390625</v>
+        <v>630.1212158203125</v>
       </c>
       <c r="F38" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B39" t="n">
-        <v>629.4529708548182</v>
+        <v>626.3709044869131</v>
       </c>
       <c r="C39" t="n">
-        <v>633.3528014765299</v>
+        <v>627.9268552540688</v>
       </c>
       <c r="D39" t="n">
-        <v>616.5065997528014</v>
+        <v>617.7832543081277</v>
       </c>
       <c r="E39" t="n">
-        <v>630.1212158203125</v>
+        <v>625.4533081054688</v>
       </c>
       <c r="F39" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B40" t="n">
-        <v>626.3709044869131</v>
+        <v>626.5005716840028</v>
       </c>
       <c r="C40" t="n">
-        <v>627.9268552540688</v>
+        <v>627.3583261459861</v>
       </c>
       <c r="D40" t="n">
-        <v>617.7832543081277</v>
+        <v>606.1934022078184</v>
       </c>
       <c r="E40" t="n">
-        <v>625.4533081054688</v>
+        <v>607.43017578125</v>
       </c>
       <c r="F40" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B41" t="n">
-        <v>626.5005716840028</v>
+        <v>611.4796659420805</v>
       </c>
       <c r="C41" t="n">
-        <v>627.3583261459861</v>
+        <v>616.0478021853295</v>
       </c>
       <c r="D41" t="n">
-        <v>606.1934022078184</v>
+        <v>601.4357808374693</v>
       </c>
       <c r="E41" t="n">
-        <v>607.43017578125</v>
+        <v>608.3079223632812</v>
       </c>
       <c r="F41" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B42" t="n">
-        <v>611.4796659420805</v>
+        <v>600.2288811530552</v>
       </c>
       <c r="C42" t="n">
-        <v>616.0478021853295</v>
+        <v>612.088052043071</v>
       </c>
       <c r="D42" t="n">
-        <v>601.4357808374693</v>
+        <v>593.6560102918138</v>
       </c>
       <c r="E42" t="n">
-        <v>608.3079223632812</v>
+        <v>607.8790283203125</v>
       </c>
       <c r="F42" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B43" t="n">
-        <v>600.2288811530552</v>
+        <v>607.4600964135232</v>
       </c>
       <c r="C43" t="n">
-        <v>612.088052043071</v>
+        <v>610.1032465254069</v>
       </c>
       <c r="D43" t="n">
-        <v>593.6560102918138</v>
+        <v>593.855525554584</v>
       </c>
       <c r="E43" t="n">
-        <v>607.8790283203125</v>
+        <v>600.4483642578125</v>
       </c>
       <c r="F43" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B44" t="n">
-        <v>607.4600964135232</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C44" t="n">
-        <v>610.1032465254069</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D44" t="n">
-        <v>593.855525554584</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E44" t="n">
-        <v>600.4483642578125</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F44" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B45" t="n">
-        <v>590.065358149623</v>
+        <v>592.1797786556917</v>
       </c>
       <c r="C45" t="n">
-        <v>602.0940719298206</v>
+        <v>593.7856483585136</v>
       </c>
       <c r="D45" t="n">
-        <v>582.2656968950795</v>
+        <v>579.7421567881397</v>
       </c>
       <c r="E45" t="n">
-        <v>596.1395874023438</v>
+        <v>588.7886352539062</v>
       </c>
       <c r="F45" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B46" t="n">
-        <v>592.1798400423816</v>
+        <v>601.9344542639864</v>
       </c>
       <c r="C46" t="n">
-        <v>593.7857099116716</v>
+        <v>605.1460720070379</v>
       </c>
       <c r="D46" t="n">
-        <v>579.7422168855177</v>
+        <v>581.8367012414765</v>
       </c>
       <c r="E46" t="n">
-        <v>588.7886962890625</v>
+        <v>587.6217041015625</v>
       </c>
       <c r="F46" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B47" t="n">
-        <v>601.9344542639864</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C47" t="n">
-        <v>605.1460720070379</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D47" t="n">
-        <v>581.8367012414765</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E47" t="n">
-        <v>587.6217041015625</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F47" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B48" t="n">
-        <v>586.9734117815261</v>
+        <v>597.1668126146857</v>
       </c>
       <c r="C48" t="n">
-        <v>596.5684523172222</v>
+        <v>615.1002115339802</v>
       </c>
       <c r="D48" t="n">
-        <v>580.3506215479276</v>
+        <v>596.0796743085915</v>
       </c>
       <c r="E48" t="n">
-        <v>592.70849609375</v>
+        <v>611.4596557617188</v>
       </c>
       <c r="F48" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B49" t="n">
-        <v>597.1668126146857</v>
+        <v>622.3813086708644</v>
       </c>
       <c r="C49" t="n">
-        <v>615.1002115339802</v>
+        <v>635.3974440566444</v>
       </c>
       <c r="D49" t="n">
-        <v>596.0796743085915</v>
+        <v>616.696082618217</v>
       </c>
       <c r="E49" t="n">
-        <v>611.4596557617188</v>
+        <v>634.569580078125</v>
       </c>
       <c r="F49" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B50" t="n">
-        <v>622.3812488080194</v>
+        <v>636.0358029520913</v>
       </c>
       <c r="C50" t="n">
-        <v>635.3973829418613</v>
+        <v>636.7040478933542</v>
       </c>
       <c r="D50" t="n">
-        <v>616.6960233021972</v>
+        <v>629.9915253276793</v>
       </c>
       <c r="E50" t="n">
-        <v>634.5695190429688</v>
+        <v>631.9663696289062</v>
       </c>
       <c r="F50" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B51" t="n">
-        <v>636.0358029520913</v>
+        <v>634.4299618769652</v>
       </c>
       <c r="C51" t="n">
-        <v>636.7040478933542</v>
+        <v>646.3688812783262</v>
       </c>
       <c r="D51" t="n">
-        <v>629.9915253276793</v>
+        <v>633.8514494094911</v>
       </c>
       <c r="E51" t="n">
-        <v>631.9663696289062</v>
+        <v>646.2691650390625</v>
       </c>
       <c r="F51" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B52" t="n">
-        <v>634.4299618769652</v>
+        <v>637.8909364271796</v>
       </c>
       <c r="C52" t="n">
-        <v>646.3688812783262</v>
+        <v>643.6459879981971</v>
       </c>
       <c r="D52" t="n">
-        <v>633.8514494094911</v>
+        <v>636.1056017671217</v>
       </c>
       <c r="E52" t="n">
-        <v>646.2691650390625</v>
+        <v>639.20751953125</v>
       </c>
       <c r="F52" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B53" t="n">
-        <v>637.8908755177382</v>
+        <v>640.6737853801045</v>
       </c>
       <c r="C53" t="n">
-        <v>643.6459265392308</v>
+        <v>646.1894088056151</v>
       </c>
       <c r="D53" t="n">
-        <v>636.1055410281542</v>
+        <v>636.4148423556049</v>
       </c>
       <c r="E53" t="n">
-        <v>639.2074584960938</v>
+        <v>645.42138671875</v>
       </c>
       <c r="F53" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B54" t="n">
-        <v>640.6737247939117</v>
+        <v>642.7383773862279</v>
       </c>
       <c r="C54" t="n">
-        <v>646.1893476978298</v>
+        <v>647.1668624868771</v>
       </c>
       <c r="D54" t="n">
-        <v>636.4147821721649</v>
+        <v>635.8961867971512</v>
       </c>
       <c r="E54" t="n">
-        <v>645.4213256835938</v>
+        <v>637.9408569335938</v>
       </c>
       <c r="F54" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B55" t="n">
-        <v>642.7383158920676</v>
+        <v>674.2463992276428</v>
       </c>
       <c r="C55" t="n">
-        <v>647.1668005690203</v>
+        <v>674.3461154685141</v>
       </c>
       <c r="D55" t="n">
-        <v>635.8961259576193</v>
+        <v>658.3377626918029</v>
       </c>
       <c r="E55" t="n">
-        <v>637.9407958984375</v>
+        <v>659.81396484375</v>
       </c>
       <c r="F55" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B56" t="n">
-        <v>674.2463992276428</v>
+        <v>662.2775487290173</v>
       </c>
       <c r="C56" t="n">
-        <v>674.3461154685141</v>
+        <v>672.9398207362489</v>
       </c>
       <c r="D56" t="n">
-        <v>658.3377626918029</v>
+        <v>660.6717397649775</v>
       </c>
       <c r="E56" t="n">
-        <v>659.81396484375</v>
+        <v>671.673095703125</v>
       </c>
       <c r="F56" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B57" t="n">
-        <v>662.2775487290173</v>
+        <v>667.603701448277</v>
       </c>
       <c r="C57" t="n">
-        <v>672.9398207362489</v>
+        <v>674.9545781663558</v>
       </c>
       <c r="D57" t="n">
-        <v>660.6717397649775</v>
+        <v>663.344758713728</v>
       </c>
       <c r="E57" t="n">
-        <v>671.673095703125</v>
+        <v>665.0702514648438</v>
       </c>
       <c r="F57" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B58" t="n">
-        <v>667.603701448277</v>
+        <v>662.0481300460407</v>
       </c>
       <c r="C58" t="n">
-        <v>674.9545781663558</v>
+        <v>662.7562492699393</v>
       </c>
       <c r="D58" t="n">
-        <v>663.344758713728</v>
+        <v>651.6451938720459</v>
       </c>
       <c r="E58" t="n">
-        <v>665.0702514648438</v>
+        <v>655.2557983398438</v>
       </c>
       <c r="F58" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B59" t="n">
-        <v>662.0481300460407</v>
+        <v>648.2639556943986</v>
       </c>
       <c r="C59" t="n">
-        <v>662.7562492699393</v>
+        <v>652.8121240146866</v>
       </c>
       <c r="D59" t="n">
-        <v>651.6451938720459</v>
+        <v>641.730959438269</v>
       </c>
       <c r="E59" t="n">
-        <v>655.2557983398438</v>
+        <v>648.4434814453125</v>
       </c>
       <c r="F59" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B60" t="n">
-        <v>648.2640167126568</v>
+        <v>641.6212380225077</v>
       </c>
       <c r="C60" t="n">
-        <v>652.812185461044</v>
+        <v>653.5801862453618</v>
       </c>
       <c r="D60" t="n">
-        <v>641.7310198416047</v>
+        <v>639.1377070000864</v>
       </c>
       <c r="E60" t="n">
-        <v>648.4435424804688</v>
+        <v>651.016845703125</v>
       </c>
       <c r="F60" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B61" t="n">
-        <v>641.6212380225077</v>
+        <v>648.1143349664432</v>
       </c>
       <c r="C61" t="n">
-        <v>653.5801862453618</v>
+        <v>709.1555875928369</v>
       </c>
       <c r="D61" t="n">
-        <v>639.1377070000864</v>
+        <v>636.9533606253732</v>
       </c>
       <c r="E61" t="n">
-        <v>651.016845703125</v>
+        <v>642.5587768554688</v>
       </c>
       <c r="F61" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B62" t="n">
-        <v>648.1142734035774</v>
+        <v>644.5502809809109</v>
       </c>
       <c r="C62" t="n">
-        <v>709.1555202318053</v>
+        <v>651.8372704406642</v>
       </c>
       <c r="D62" t="n">
-        <v>636.9533001226623</v>
+        <v>637.5627451568915</v>
       </c>
       <c r="E62" t="n">
-        <v>642.5587158203125</v>
+        <v>646.3570556640625</v>
       </c>
       <c r="F62" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2055,25 +2055,25 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B63" t="n">
-        <v>644.5502809809109</v>
+        <v>642.3541401459643</v>
       </c>
       <c r="C63" t="n">
-        <v>651.8372704406642</v>
+        <v>661.3602142938313</v>
       </c>
       <c r="D63" t="n">
-        <v>637.5627451568915</v>
+        <v>642.054686531657</v>
       </c>
       <c r="E63" t="n">
-        <v>646.3570556640625</v>
+        <v>655.9798583984375</v>
       </c>
       <c r="F63" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G63" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B64" t="n">
-        <v>642.3541401459643</v>
+        <v>654.4426118233187</v>
       </c>
       <c r="C64" t="n">
-        <v>661.3602142938313</v>
+        <v>660.0526000253047</v>
       </c>
       <c r="D64" t="n">
-        <v>642.054686531657</v>
+        <v>648.0440522221027</v>
       </c>
       <c r="E64" t="n">
-        <v>655.9798583984375</v>
+        <v>648.343505859375</v>
       </c>
       <c r="F64" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B65" t="n">
-        <v>654.4426118233187</v>
+        <v>655.8601356908653</v>
       </c>
       <c r="C65" t="n">
-        <v>660.0526000253047</v>
+        <v>669.366012780715</v>
       </c>
       <c r="D65" t="n">
-        <v>648.0440522221027</v>
+        <v>655.2911433094866</v>
       </c>
       <c r="E65" t="n">
-        <v>648.343505859375</v>
+        <v>663.2669067382812</v>
       </c>
       <c r="F65" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B66" t="n">
-        <v>655.8601356908653</v>
+        <v>665.2333263832898</v>
       </c>
       <c r="C66" t="n">
-        <v>669.366012780715</v>
+        <v>669.8051880946751</v>
       </c>
       <c r="D66" t="n">
-        <v>655.2911433094866</v>
+        <v>657.0080086354003</v>
       </c>
       <c r="E66" t="n">
-        <v>663.2669067382812</v>
+        <v>657.5969848632812</v>
       </c>
       <c r="F66" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B67" t="n">
-        <v>665.2333263832898</v>
+        <v>660.4718397886508</v>
       </c>
       <c r="C67" t="n">
-        <v>669.8051880946751</v>
+        <v>672.380589007267</v>
       </c>
       <c r="D67" t="n">
-        <v>657.0080086354003</v>
+        <v>655.4807431709672</v>
       </c>
       <c r="E67" t="n">
-        <v>657.5969848632812</v>
+        <v>660.3220825195312</v>
       </c>
       <c r="F67" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B68" t="n">
-        <v>660.4718397886508</v>
+        <v>658.8746741689592</v>
       </c>
       <c r="C68" t="n">
-        <v>672.380589007267</v>
+        <v>664.8140915262984</v>
       </c>
       <c r="D68" t="n">
-        <v>655.4807431709672</v>
+        <v>657.0778915122911</v>
       </c>
       <c r="E68" t="n">
-        <v>660.3220825195312</v>
+        <v>663.7559814453125</v>
       </c>
       <c r="F68" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B69" t="n">
-        <v>658.8746741689592</v>
+        <v>661.3503688947783</v>
       </c>
       <c r="C69" t="n">
-        <v>664.8140915262984</v>
+        <v>666.9902722948509</v>
       </c>
       <c r="D69" t="n">
-        <v>657.0778915122911</v>
+        <v>661.0209394131572</v>
       </c>
       <c r="E69" t="n">
-        <v>663.7559814453125</v>
+        <v>666.3613891601562</v>
       </c>
       <c r="F69" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B70" t="n">
-        <v>661.3503688947783</v>
+        <v>666.8704124858896</v>
       </c>
       <c r="C70" t="n">
-        <v>666.9902722948509</v>
+        <v>667.7588423243637</v>
       </c>
       <c r="D70" t="n">
-        <v>661.0209394131572</v>
+        <v>660.1424238558649</v>
       </c>
       <c r="E70" t="n">
-        <v>666.3613891601562</v>
+        <v>662.10888671875</v>
       </c>
       <c r="F70" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B71" t="n">
-        <v>666.8704124858896</v>
+        <v>656.8383689858442</v>
       </c>
       <c r="C71" t="n">
-        <v>667.7588423243637</v>
+        <v>659.0743707339258</v>
       </c>
       <c r="D71" t="n">
-        <v>660.1424238558649</v>
+        <v>653.2248195668056</v>
       </c>
       <c r="E71" t="n">
-        <v>662.10888671875</v>
+        <v>657.5171508789062</v>
       </c>
       <c r="F71" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B72" t="n">
-        <v>656.8383689858442</v>
+        <v>657.5171386037911</v>
       </c>
       <c r="C72" t="n">
-        <v>659.0743707339258</v>
+        <v>671.0230153954109</v>
       </c>
       <c r="D72" t="n">
-        <v>653.2248195668056</v>
+        <v>656.6686764849229</v>
       </c>
       <c r="E72" t="n">
-        <v>657.5171508789062</v>
+        <v>664.7642211914062</v>
       </c>
       <c r="F72" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B73" t="n">
-        <v>657.5171386037911</v>
+        <v>663.5663484641349</v>
       </c>
       <c r="C73" t="n">
-        <v>671.0230153954109</v>
+        <v>663.8159033150052</v>
       </c>
       <c r="D73" t="n">
-        <v>656.6686764849229</v>
+        <v>658.2658058687088</v>
       </c>
       <c r="E73" t="n">
-        <v>664.7642211914062</v>
+        <v>658.9146728515625</v>
       </c>
       <c r="F73" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B74" t="n">
-        <v>663.5663484641349</v>
+        <v>661.5499631466852</v>
       </c>
       <c r="C74" t="n">
-        <v>663.8159033150052</v>
+        <v>663.2070415689074</v>
       </c>
       <c r="D74" t="n">
-        <v>658.2658058687088</v>
+        <v>642.3542224297569</v>
       </c>
       <c r="E74" t="n">
-        <v>658.9146728515625</v>
+        <v>649.2518920898438</v>
       </c>
       <c r="F74" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B75" t="n">
-        <v>661.5499631466852</v>
+        <v>649.8508280292294</v>
       </c>
       <c r="C75" t="n">
-        <v>663.2070415689074</v>
+        <v>663.3567049684374</v>
       </c>
       <c r="D75" t="n">
-        <v>642.3542224297569</v>
+        <v>646.5966230035071</v>
       </c>
       <c r="E75" t="n">
-        <v>649.2518920898438</v>
+        <v>657.616943359375</v>
       </c>
       <c r="F75" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B76" t="n">
-        <v>649.8508280292294</v>
+        <v>658.3956073528642</v>
       </c>
       <c r="C76" t="n">
-        <v>663.3567049684374</v>
+        <v>664.3350252422523</v>
       </c>
       <c r="D76" t="n">
-        <v>646.5966230035071</v>
+        <v>650.7392812609531</v>
       </c>
       <c r="E76" t="n">
-        <v>657.616943359375</v>
+        <v>659.4437255859375</v>
       </c>
       <c r="F76" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B77" t="n">
-        <v>658.3956073528642</v>
+        <v>654.4726104611178</v>
       </c>
       <c r="C77" t="n">
-        <v>664.3350252422523</v>
+        <v>657.9763704555172</v>
       </c>
       <c r="D77" t="n">
-        <v>650.7392812609531</v>
+        <v>643.6618768302103</v>
       </c>
       <c r="E77" t="n">
-        <v>659.4437255859375</v>
+        <v>647.5349731445312</v>
       </c>
       <c r="F77" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B78" t="n">
-        <v>654.4726104611178</v>
+        <v>644.7299347572825</v>
       </c>
       <c r="C78" t="n">
-        <v>657.9763704555172</v>
+        <v>645.9477331499952</v>
       </c>
       <c r="D78" t="n">
-        <v>643.6618768302103</v>
+        <v>634.5879917891143</v>
       </c>
       <c r="E78" t="n">
-        <v>647.5349731445312</v>
+        <v>644.9096069335938</v>
       </c>
       <c r="F78" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B79" t="n">
-        <v>644.7299347572825</v>
+        <v>644.2906685217797</v>
       </c>
       <c r="C79" t="n">
-        <v>645.9477331499952</v>
+        <v>653.7837438291153</v>
       </c>
       <c r="D79" t="n">
-        <v>634.5879917891143</v>
+        <v>641.7052537227476</v>
       </c>
       <c r="E79" t="n">
-        <v>644.9096069335938</v>
+        <v>651.8970947265625</v>
       </c>
       <c r="F79" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B80" t="n">
-        <v>644.2906685217797</v>
+        <v>651.3681600668523</v>
       </c>
       <c r="C80" t="n">
-        <v>653.7837438291153</v>
+        <v>652.8055375702352</v>
       </c>
       <c r="D80" t="n">
-        <v>641.7052537227476</v>
+        <v>640.0882316599212</v>
       </c>
       <c r="E80" t="n">
-        <v>651.8970947265625</v>
+        <v>640.826904296875</v>
       </c>
       <c r="F80" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B81" t="n">
-        <v>651.3681600668523</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="C81" t="n">
-        <v>652.8055375702352</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="D81" t="n">
-        <v>640.0882316599212</v>
+        <v>622.9887038024194</v>
       </c>
       <c r="E81" t="n">
-        <v>640.826904296875</v>
+        <v>629.96630859375</v>
       </c>
       <c r="F81" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B82" t="n">
-        <v>641.1263941859123</v>
+        <v>625.3844405077801</v>
       </c>
       <c r="C82" t="n">
-        <v>641.1263941859123</v>
+        <v>627.3309804807691</v>
       </c>
       <c r="D82" t="n">
-        <v>622.9887038024194</v>
+        <v>613.7252454803604</v>
       </c>
       <c r="E82" t="n">
-        <v>629.96630859375</v>
+        <v>614.4240112304688</v>
       </c>
       <c r="F82" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B83" t="n">
-        <v>625.3844405077801</v>
+        <v>617.378703801015</v>
       </c>
       <c r="C83" t="n">
-        <v>627.3309804807691</v>
+        <v>623.0585745209008</v>
       </c>
       <c r="D83" t="n">
-        <v>613.7252454803604</v>
+        <v>613.1362714280776</v>
       </c>
       <c r="E83" t="n">
-        <v>614.4240112304688</v>
+        <v>619.694580078125</v>
       </c>
       <c r="F83" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B84" t="n">
-        <v>617.378703801015</v>
+        <v>623.0685636897582</v>
       </c>
       <c r="C84" t="n">
-        <v>623.0585745209008</v>
+        <v>627.9598630097294</v>
       </c>
       <c r="D84" t="n">
-        <v>613.1362714280776</v>
+        <v>618.9758886129073</v>
       </c>
       <c r="E84" t="n">
-        <v>619.694580078125</v>
+        <v>619.1455688476562</v>
       </c>
       <c r="F84" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B85" t="n">
-        <v>623.0685636897582</v>
+        <v>606.7976262932837</v>
       </c>
       <c r="C85" t="n">
-        <v>627.9598630097294</v>
+        <v>610.3113781504126</v>
       </c>
       <c r="D85" t="n">
-        <v>618.9758886129073</v>
+        <v>598.9316523845154</v>
       </c>
       <c r="E85" t="n">
-        <v>619.1455688476562</v>
+        <v>603.0443115234375</v>
       </c>
       <c r="F85" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B86" t="n">
-        <v>606.7976262932837</v>
+        <v>605.659634898437</v>
       </c>
       <c r="C86" t="n">
-        <v>610.3113781504126</v>
+        <v>617.169133937088</v>
       </c>
       <c r="D86" t="n">
-        <v>598.9316523845154</v>
+        <v>599.0115204374271</v>
       </c>
       <c r="E86" t="n">
-        <v>603.0443115234375</v>
+        <v>611.8685913085938</v>
       </c>
       <c r="F86" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B87" t="n">
-        <v>605.659634898437</v>
+        <v>628.2293275614567</v>
       </c>
       <c r="C87" t="n">
-        <v>617.169133937088</v>
+        <v>659.3937675491238</v>
       </c>
       <c r="D87" t="n">
-        <v>599.0115204374271</v>
+        <v>625.4343255489129</v>
       </c>
       <c r="E87" t="n">
-        <v>611.8685913085938</v>
+        <v>646.476806640625</v>
       </c>
       <c r="F87" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B88" t="n">
-        <v>628.2293275614567</v>
+        <v>643.6219561683764</v>
       </c>
       <c r="C88" t="n">
-        <v>659.3937675491238</v>
+        <v>665.3032527677875</v>
       </c>
       <c r="D88" t="n">
-        <v>625.4343255489129</v>
+        <v>643.3025186421843</v>
       </c>
       <c r="E88" t="n">
-        <v>646.476806640625</v>
+        <v>657.5870361328125</v>
       </c>
       <c r="F88" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B89" t="n">
-        <v>643.6219561683764</v>
+        <v>663.9456740004919</v>
       </c>
       <c r="C89" t="n">
-        <v>665.3032527677875</v>
+        <v>674.0776252750454</v>
       </c>
       <c r="D89" t="n">
-        <v>643.3025186421843</v>
+        <v>660.1124846991261</v>
       </c>
       <c r="E89" t="n">
-        <v>657.5870361328125</v>
+        <v>671.1627807617188</v>
       </c>
       <c r="F89" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B90" t="n">
-        <v>663.9456740004919</v>
+        <v>673.3888389297905</v>
       </c>
       <c r="C90" t="n">
-        <v>674.0776252750454</v>
+        <v>675.6148486525956</v>
       </c>
       <c r="D90" t="n">
-        <v>660.1124846991261</v>
+        <v>663.4764668627315</v>
       </c>
       <c r="E90" t="n">
-        <v>671.1627807617188</v>
+        <v>671.7716674804688</v>
       </c>
       <c r="F90" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B91" t="n">
-        <v>673.3888389297905</v>
+        <v>673.2989910894674</v>
       </c>
       <c r="C91" t="n">
-        <v>675.6148486525956</v>
+        <v>676.4733214975852</v>
       </c>
       <c r="D91" t="n">
-        <v>663.4764668627315</v>
+        <v>664.9139236867763</v>
       </c>
       <c r="E91" t="n">
-        <v>671.7716674804688</v>
+        <v>667.5392456054688</v>
       </c>
       <c r="F91" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B92" t="n">
-        <v>673.2989910894674</v>
+        <v>736.1169233837337</v>
       </c>
       <c r="C92" t="n">
-        <v>676.4733214975852</v>
+        <v>742.6752321400184</v>
       </c>
       <c r="D92" t="n">
-        <v>664.9139236867763</v>
+        <v>711.2812198864386</v>
       </c>
       <c r="E92" t="n">
-        <v>667.5392456054688</v>
+        <v>736.995361328125</v>
       </c>
       <c r="F92" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B93" t="n">
-        <v>736.1169233837337</v>
+        <v>726.2045952530067</v>
       </c>
       <c r="C93" t="n">
-        <v>742.6752321400184</v>
+        <v>730.8662626744616</v>
       </c>
       <c r="D93" t="n">
-        <v>711.2812198864386</v>
+        <v>712.3193905555435</v>
       </c>
       <c r="E93" t="n">
-        <v>736.995361328125</v>
+        <v>715.2241821289062</v>
       </c>
       <c r="F93" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B94" t="n">
-        <v>726.2045952530067</v>
+        <v>713.3275184694113</v>
       </c>
       <c r="C94" t="n">
-        <v>730.8662626744616</v>
+        <v>720.0156002559207</v>
       </c>
       <c r="D94" t="n">
-        <v>712.3193905555435</v>
+        <v>702.2672920108814</v>
       </c>
       <c r="E94" t="n">
-        <v>715.2241821289062</v>
+        <v>705.152099609375</v>
       </c>
       <c r="F94" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B95" t="n">
-        <v>713.3275184694113</v>
+        <v>706.1104025957663</v>
       </c>
       <c r="C95" t="n">
-        <v>720.0156002559207</v>
+        <v>715.7232596178901</v>
       </c>
       <c r="D95" t="n">
-        <v>702.2672920108814</v>
+        <v>685.1877035052055</v>
       </c>
       <c r="E95" t="n">
-        <v>705.152099609375</v>
+        <v>690.4683227539062</v>
       </c>
       <c r="F95" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B96" t="n">
-        <v>706.1104025957663</v>
+        <v>686.5053883494637</v>
       </c>
       <c r="C96" t="n">
-        <v>715.7232596178901</v>
+        <v>687.603466213174</v>
       </c>
       <c r="D96" t="n">
-        <v>685.1877035052055</v>
+        <v>666.2715231343633</v>
       </c>
       <c r="E96" t="n">
-        <v>690.4683227539062</v>
+        <v>667.7987670898438</v>
       </c>
       <c r="F96" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B97" t="n">
-        <v>686.5053883494637</v>
+        <v>662.3984025060512</v>
       </c>
       <c r="C97" t="n">
-        <v>687.603466213174</v>
+        <v>680.2864759062725</v>
       </c>
       <c r="D97" t="n">
-        <v>666.2715231343633</v>
+        <v>652.3363345630947</v>
       </c>
       <c r="E97" t="n">
-        <v>667.7987670898438</v>
+        <v>669.0166015625</v>
       </c>
       <c r="F97" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B98" t="n">
-        <v>662.3984025060512</v>
+        <v>664.3050190645899</v>
       </c>
       <c r="C98" t="n">
-        <v>680.2864759062725</v>
+        <v>670.7934451675868</v>
       </c>
       <c r="D98" t="n">
-        <v>652.3363345630947</v>
+        <v>645.3488423980709</v>
       </c>
       <c r="E98" t="n">
-        <v>669.0166015625</v>
+        <v>660.2822265625</v>
       </c>
       <c r="F98" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B99" t="n">
-        <v>664.3050190645899</v>
+        <v>661.9991209626965</v>
       </c>
       <c r="C99" t="n">
-        <v>670.7934451675868</v>
+        <v>682.0932819515241</v>
       </c>
       <c r="D99" t="n">
-        <v>645.3488423980709</v>
+        <v>657.6069922476072</v>
       </c>
       <c r="E99" t="n">
-        <v>660.2822265625</v>
+        <v>676.0140991210938</v>
       </c>
       <c r="F99" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B100" t="n">
-        <v>661.9991209626965</v>
+        <v>676.3934502400131</v>
       </c>
       <c r="C100" t="n">
-        <v>682.0932819515241</v>
+        <v>679.4380681924739</v>
       </c>
       <c r="D100" t="n">
-        <v>657.6069922476072</v>
+        <v>668.597359057372</v>
       </c>
       <c r="E100" t="n">
-        <v>676.0140991210938</v>
+        <v>669.5256958007812</v>
       </c>
       <c r="F100" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B101" t="n">
-        <v>676.3934502400131</v>
+        <v>672.7998711552045</v>
       </c>
       <c r="C101" t="n">
-        <v>679.4380681924739</v>
+        <v>678.0605068549233</v>
       </c>
       <c r="D101" t="n">
-        <v>668.597359057372</v>
+        <v>655.9299390360635</v>
       </c>
       <c r="E101" t="n">
-        <v>669.5256958007812</v>
+        <v>667.4993286132812</v>
       </c>
       <c r="F101" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B102" t="n">
-        <v>672.7998711552045</v>
+        <v>668.7770306530766</v>
       </c>
       <c r="C102" t="n">
-        <v>678.0605068549233</v>
+        <v>674.7963229561075</v>
       </c>
       <c r="D102" t="n">
-        <v>655.9299390360635</v>
+        <v>644.1310518439949</v>
       </c>
       <c r="E102" t="n">
-        <v>667.4993286132812</v>
+        <v>648.6529541015625</v>
       </c>
       <c r="F102" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B103" t="n">
-        <v>668.7770306530766</v>
+        <v>643.9513250294082</v>
       </c>
       <c r="C103" t="n">
-        <v>674.7963229561075</v>
+        <v>650.2700710327099</v>
       </c>
       <c r="D103" t="n">
-        <v>644.1310518439949</v>
+        <v>633.4401061931457</v>
       </c>
       <c r="E103" t="n">
-        <v>648.6529541015625</v>
+        <v>638.630859375</v>
       </c>
       <c r="F103" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B104" t="n">
-        <v>643.9513250294082</v>
+        <v>638.3612593202278</v>
       </c>
       <c r="C104" t="n">
-        <v>650.2700710327099</v>
+        <v>641.4557148619026</v>
       </c>
       <c r="D104" t="n">
-        <v>633.4401061931457</v>
+        <v>627.6803003409905</v>
       </c>
       <c r="E104" t="n">
-        <v>638.630859375</v>
+        <v>638.151611328125</v>
       </c>
       <c r="F104" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B105" t="n">
-        <v>638.3612593202278</v>
+        <v>632.67143641335</v>
       </c>
       <c r="C105" t="n">
-        <v>641.4557148619026</v>
+        <v>643.8515057528024</v>
       </c>
       <c r="D105" t="n">
-        <v>627.6803003409905</v>
+        <v>627.0315334227189</v>
       </c>
       <c r="E105" t="n">
-        <v>638.151611328125</v>
+        <v>642.0746459960938</v>
       </c>
       <c r="F105" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B106" t="n">
-        <v>632.67143641335</v>
+        <v>637.432932921519</v>
       </c>
       <c r="C106" t="n">
-        <v>643.8515057528024</v>
+        <v>646.0375787806976</v>
       </c>
       <c r="D106" t="n">
-        <v>627.0315334227189</v>
+        <v>635.5861905818066</v>
       </c>
       <c r="E106" t="n">
-        <v>642.0746459960938</v>
+        <v>643.6318969726562</v>
       </c>
       <c r="F106" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B107" t="n">
-        <v>637.432932921519</v>
+        <v>638.5509584025834</v>
       </c>
       <c r="C107" t="n">
-        <v>646.0375787806976</v>
+        <v>662.1688021543367</v>
       </c>
       <c r="D107" t="n">
-        <v>635.5861905818066</v>
+        <v>637.6426055733327</v>
       </c>
       <c r="E107" t="n">
-        <v>643.6318969726562</v>
+        <v>654.4924926757812</v>
       </c>
       <c r="F107" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B108" t="n">
-        <v>638.5509584025834</v>
+        <v>651.3780476889771</v>
       </c>
       <c r="C108" t="n">
-        <v>662.1688021543367</v>
+        <v>656.5288937722072</v>
       </c>
       <c r="D108" t="n">
-        <v>637.6426055733327</v>
+        <v>634.8675211939732</v>
       </c>
       <c r="E108" t="n">
-        <v>654.4924926757812</v>
+        <v>636.1152954101562</v>
       </c>
       <c r="F108" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B109" t="n">
-        <v>651.3780476889771</v>
+        <v>631.9527259539814</v>
       </c>
       <c r="C109" t="n">
-        <v>656.5288937722072</v>
+        <v>639.9683956881865</v>
       </c>
       <c r="D109" t="n">
-        <v>634.8675211939732</v>
+        <v>627.8599900449855</v>
       </c>
       <c r="E109" t="n">
-        <v>636.1152954101562</v>
+        <v>638.16162109375</v>
       </c>
       <c r="F109" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B110" t="n">
-        <v>631.9527259539814</v>
+        <v>641.3859599741169</v>
       </c>
       <c r="C110" t="n">
-        <v>639.9683956881865</v>
+        <v>652.7157261405878</v>
       </c>
       <c r="D110" t="n">
-        <v>627.8599900449855</v>
+        <v>640.9966397738364</v>
       </c>
       <c r="E110" t="n">
-        <v>638.16162109375</v>
+        <v>652.5260620117188</v>
       </c>
       <c r="F110" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B111" t="n">
-        <v>641.3859599741169</v>
+        <v>649.3916295582877</v>
       </c>
       <c r="C111" t="n">
-        <v>652.7157261405878</v>
+        <v>659.823034651462</v>
       </c>
       <c r="D111" t="n">
-        <v>640.9966397738364</v>
+        <v>646.3470725216666</v>
       </c>
       <c r="E111" t="n">
-        <v>652.5260620117188</v>
+        <v>655.8401489257812</v>
       </c>
       <c r="F111" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B112" t="n">
-        <v>649.3916295582877</v>
+        <v>642.3043203814821</v>
       </c>
       <c r="C112" t="n">
-        <v>659.823034651462</v>
+        <v>648.2836451675449</v>
       </c>
       <c r="D112" t="n">
-        <v>646.3470725216666</v>
+        <v>636.9837936279411</v>
       </c>
       <c r="E112" t="n">
-        <v>655.8401489257812</v>
+        <v>647.02587890625</v>
       </c>
       <c r="F112" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B113" t="n">
-        <v>642.3043203814821</v>
+        <v>636.0254184162494</v>
       </c>
       <c r="C113" t="n">
-        <v>648.2836451675449</v>
+        <v>658.764884603327</v>
       </c>
       <c r="D113" t="n">
-        <v>636.9837936279411</v>
+        <v>633.3701817354564</v>
       </c>
       <c r="E113" t="n">
-        <v>647.02587890625</v>
+        <v>652.396240234375</v>
       </c>
       <c r="F113" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B114" t="n">
-        <v>636.0254184162494</v>
+        <v>647.1356255764312</v>
       </c>
       <c r="C114" t="n">
-        <v>658.764884603327</v>
+        <v>657.866484005116</v>
       </c>
       <c r="D114" t="n">
-        <v>633.3701817354564</v>
+        <v>637.7025010942567</v>
       </c>
       <c r="E114" t="n">
-        <v>652.396240234375</v>
+        <v>653.91357421875</v>
       </c>
       <c r="F114" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B115" t="n">
-        <v>647.1356255764312</v>
+        <v>656.7884535878291</v>
       </c>
       <c r="C115" t="n">
-        <v>657.866484005116</v>
+        <v>671.5720803574089</v>
       </c>
       <c r="D115" t="n">
-        <v>637.7025010942567</v>
+        <v>656.4989309709863</v>
       </c>
       <c r="E115" t="n">
-        <v>653.91357421875</v>
+        <v>666.541015625</v>
       </c>
       <c r="F115" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B116" t="n">
-        <v>656.7884535878291</v>
+        <v>660.751362594833</v>
       </c>
       <c r="C116" t="n">
-        <v>671.5720803574089</v>
+        <v>669.5057662619517</v>
       </c>
       <c r="D116" t="n">
-        <v>656.4989309709863</v>
+        <v>649.1520579976961</v>
       </c>
       <c r="E116" t="n">
-        <v>666.541015625</v>
+        <v>659.393798828125</v>
       </c>
       <c r="F116" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B117" t="n">
-        <v>660.751362594833</v>
+        <v>646.7463568472266</v>
       </c>
       <c r="C117" t="n">
-        <v>669.5057662619517</v>
+        <v>648.3135076492586</v>
       </c>
       <c r="D117" t="n">
-        <v>649.1520579976961</v>
+        <v>634.9773114336934</v>
       </c>
       <c r="E117" t="n">
-        <v>659.393798828125</v>
+        <v>643.7117309570312</v>
       </c>
       <c r="F117" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B118" t="n">
-        <v>646.7463568472266</v>
+        <v>633.6497720389343</v>
       </c>
       <c r="C118" t="n">
-        <v>648.3135076492586</v>
+        <v>646.596649067328</v>
       </c>
       <c r="D118" t="n">
-        <v>634.9773114336934</v>
+        <v>625.6640164348609</v>
       </c>
       <c r="E118" t="n">
-        <v>643.7117309570312</v>
+        <v>646.2373046875</v>
       </c>
       <c r="F118" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B119" t="n">
-        <v>633.6497720389343</v>
+        <v>652.3962328583322</v>
       </c>
       <c r="C119" t="n">
-        <v>646.596649067328</v>
+        <v>659.1242214972237</v>
       </c>
       <c r="D119" t="n">
-        <v>625.6640164348609</v>
+        <v>647.8443550809549</v>
       </c>
       <c r="E119" t="n">
-        <v>646.2373046875</v>
+        <v>652.9053344726562</v>
       </c>
       <c r="F119" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B120" t="n">
-        <v>652.3962328583322</v>
+        <v>653.5941111270305</v>
       </c>
       <c r="C120" t="n">
-        <v>659.1242214972237</v>
+        <v>657.9463328691638</v>
       </c>
       <c r="D120" t="n">
-        <v>647.8443550809549</v>
+        <v>647.2054829186618</v>
       </c>
       <c r="E120" t="n">
-        <v>652.9053344726562</v>
+        <v>653.6939086914062</v>
       </c>
       <c r="F120" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B121" t="n">
-        <v>653.5941111270305</v>
+        <v>647.5948263527883</v>
       </c>
       <c r="C121" t="n">
-        <v>657.9463328691638</v>
+        <v>652.336368433984</v>
       </c>
       <c r="D121" t="n">
-        <v>647.2054829186618</v>
+        <v>635.7659510050273</v>
       </c>
       <c r="E121" t="n">
-        <v>653.6939086914062</v>
+        <v>637.0436401367188</v>
       </c>
       <c r="F121" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B122" t="n">
-        <v>647.5948263527883</v>
+        <v>622.7790526456299</v>
       </c>
       <c r="C122" t="n">
-        <v>652.336368433984</v>
+        <v>628.0496188589474</v>
       </c>
       <c r="D122" t="n">
-        <v>635.7659510050273</v>
+        <v>608.4645611002024</v>
       </c>
       <c r="E122" t="n">
-        <v>637.0436401367188</v>
+        <v>612.6171875</v>
       </c>
       <c r="F122" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,25 +3615,25 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B123" t="n">
-        <v>622.7790526456299</v>
+        <v>631.4147932406764</v>
       </c>
       <c r="C123" t="n">
-        <v>628.0496188589474</v>
+        <v>634.1622468505053</v>
       </c>
       <c r="D123" t="n">
-        <v>608.4645611002024</v>
+        <v>622.5230098937741</v>
       </c>
       <c r="E123" t="n">
-        <v>612.6171875</v>
+        <v>626.8690185546875</v>
       </c>
       <c r="F123" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B124" t="n">
-        <v>631.4147932406764</v>
+        <v>627.4085169382369</v>
       </c>
       <c r="C124" t="n">
-        <v>634.1622468505053</v>
+        <v>635.9605885584036</v>
       </c>
       <c r="D124" t="n">
-        <v>622.5230098937741</v>
+        <v>621.1243629754691</v>
       </c>
       <c r="E124" t="n">
-        <v>626.8690185546875</v>
+        <v>622.0834350585938</v>
       </c>
       <c r="F124" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G124" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B125" t="n">
-        <v>627.4085169382369</v>
+        <v>615.7693473594539</v>
       </c>
       <c r="C125" t="n">
-        <v>635.9605885584036</v>
+        <v>622.0735023862151</v>
       </c>
       <c r="D125" t="n">
-        <v>621.1243629754691</v>
+        <v>614.04090772979</v>
       </c>
       <c r="E125" t="n">
-        <v>622.0834350585938</v>
+        <v>615.1099243164062</v>
       </c>
       <c r="F125" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B126" t="n">
-        <v>615.7693473594539</v>
+        <v>611.5832104537112</v>
       </c>
       <c r="C126" t="n">
-        <v>622.0735023862151</v>
+        <v>612.4323990135786</v>
       </c>
       <c r="D126" t="n">
-        <v>614.04090772979</v>
+        <v>601.7023533616688</v>
       </c>
       <c r="E126" t="n">
-        <v>615.1099243164062</v>
+        <v>606.1382446289062</v>
       </c>
       <c r="F126" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B127" t="n">
-        <v>611.5832104537112</v>
+        <v>602.9712077810872</v>
       </c>
       <c r="C127" t="n">
-        <v>612.4323990135786</v>
+        <v>603.400802317344</v>
       </c>
       <c r="D127" t="n">
-        <v>601.7023533616688</v>
+        <v>586.7062525156723</v>
       </c>
       <c r="E127" t="n">
-        <v>606.1382446289062</v>
+        <v>593.1102905273438</v>
       </c>
       <c r="F127" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B128" t="n">
-        <v>602.9712077810872</v>
+        <v>605.2290499891692</v>
       </c>
       <c r="C128" t="n">
-        <v>603.400802317344</v>
+        <v>608.0764476338709</v>
       </c>
       <c r="D128" t="n">
-        <v>586.7062525156723</v>
+        <v>598.4553596033379</v>
       </c>
       <c r="E128" t="n">
-        <v>593.1102905273438</v>
+        <v>603.5006713867188</v>
       </c>
       <c r="F128" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B129" t="n">
-        <v>605.2290499891692</v>
+        <v>598.5452420228083</v>
       </c>
       <c r="C129" t="n">
-        <v>608.0764476338709</v>
+        <v>600.443507118967</v>
       </c>
       <c r="D129" t="n">
-        <v>598.4553596033379</v>
+        <v>590.4527665679026</v>
       </c>
       <c r="E129" t="n">
-        <v>603.5006713867188</v>
+        <v>592.3709716796875</v>
       </c>
       <c r="F129" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B130" t="n">
-        <v>598.5452420228083</v>
+        <v>598.1855830392399</v>
       </c>
       <c r="C130" t="n">
-        <v>600.443507118967</v>
+        <v>603.1110107561809</v>
       </c>
       <c r="D130" t="n">
-        <v>590.4527665679026</v>
+        <v>592.8505617950721</v>
       </c>
       <c r="E130" t="n">
-        <v>592.3709716796875</v>
+        <v>594.3391723632812</v>
       </c>
       <c r="F130" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B131" t="n">
-        <v>598.1855830392399</v>
+        <v>581.9506076701073</v>
       </c>
       <c r="C131" t="n">
-        <v>603.1110107561809</v>
+        <v>582.460145169462</v>
       </c>
       <c r="D131" t="n">
-        <v>592.8505617950721</v>
+        <v>542.8468364624507</v>
       </c>
       <c r="E131" t="n">
-        <v>594.3391723632812</v>
+        <v>547.032958984375</v>
       </c>
       <c r="F131" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B132" t="n">
-        <v>581.9506076701073</v>
+        <v>539.599843303006</v>
       </c>
       <c r="C132" t="n">
-        <v>582.460145169462</v>
+        <v>543.0966023049141</v>
       </c>
       <c r="D132" t="n">
-        <v>542.8468364624507</v>
+        <v>519.7782492802263</v>
       </c>
       <c r="E132" t="n">
-        <v>547.032958984375</v>
+        <v>525.233154296875</v>
       </c>
       <c r="F132" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B133" t="n">
-        <v>539.599843303006</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="C133" t="n">
-        <v>543.0966023049141</v>
+        <v>539.0504095872608</v>
       </c>
       <c r="D133" t="n">
-        <v>519.7782492802263</v>
+        <v>528.0505941707193</v>
       </c>
       <c r="E133" t="n">
-        <v>525.233154296875</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="F133" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B134" t="n">
-        <v>535.8833618164062</v>
+        <v>549.4707059552647</v>
       </c>
       <c r="C134" t="n">
-        <v>539.0504095872608</v>
+        <v>573.1587727471259</v>
       </c>
       <c r="D134" t="n">
-        <v>528.0505941707193</v>
+        <v>546.2637174010383</v>
       </c>
       <c r="E134" t="n">
-        <v>535.8833618164062</v>
+        <v>571.6002197265625</v>
       </c>
       <c r="F134" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B135" t="n">
-        <v>549.4707059552647</v>
+        <v>579.5928556215499</v>
       </c>
       <c r="C135" t="n">
-        <v>573.1587727471259</v>
+        <v>592.0013387220274</v>
       </c>
       <c r="D135" t="n">
-        <v>546.2637174010383</v>
+        <v>573.2887005646345</v>
       </c>
       <c r="E135" t="n">
-        <v>571.6002197265625</v>
+        <v>578.6936645507812</v>
       </c>
       <c r="F135" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B136" t="n">
-        <v>579.5928556215499</v>
+        <v>565.5158531822124</v>
       </c>
       <c r="C136" t="n">
-        <v>592.0013387220274</v>
+        <v>577.9643377947169</v>
       </c>
       <c r="D136" t="n">
-        <v>573.2887005646345</v>
+        <v>559.1817578546791</v>
       </c>
       <c r="E136" t="n">
-        <v>578.6936645507812</v>
+        <v>573.9281005859375</v>
       </c>
       <c r="F136" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B137" t="n">
-        <v>565.5158531822124</v>
+        <v>577.1550997330287</v>
       </c>
       <c r="C137" t="n">
-        <v>577.9643377947169</v>
+        <v>582.2503530791108</v>
       </c>
       <c r="D137" t="n">
-        <v>559.1817578546791</v>
+        <v>571.4703658572956</v>
       </c>
       <c r="E137" t="n">
-        <v>573.9281005859375</v>
+        <v>572.4894409179688</v>
       </c>
       <c r="F137" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B138" t="n">
-        <v>577.1550997330287</v>
+        <v>571.9498894780604</v>
       </c>
       <c r="C138" t="n">
-        <v>582.2503530791108</v>
+        <v>574.6973431004155</v>
       </c>
       <c r="D138" t="n">
-        <v>571.4703658572956</v>
+        <v>564.2370671243236</v>
       </c>
       <c r="E138" t="n">
-        <v>572.4894409179688</v>
+        <v>574.5175170898438</v>
       </c>
       <c r="F138" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B139" t="n">
-        <v>571.9498894780604</v>
+        <v>605.4388670235439</v>
       </c>
       <c r="C139" t="n">
-        <v>574.6973431004155</v>
+        <v>629.3667024291958</v>
       </c>
       <c r="D139" t="n">
-        <v>564.2370671243236</v>
+        <v>591.2820049792073</v>
       </c>
       <c r="E139" t="n">
-        <v>574.5175170898438</v>
+        <v>611.8529052734375</v>
       </c>
       <c r="F139" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B140" t="n">
-        <v>605.4388670235439</v>
+        <v>626.3894374266143</v>
       </c>
       <c r="C140" t="n">
-        <v>629.3667024291958</v>
+        <v>636.9097166035551</v>
       </c>
       <c r="D140" t="n">
-        <v>591.2820049792073</v>
+        <v>622.4231426572783</v>
       </c>
       <c r="E140" t="n">
-        <v>611.8529052734375</v>
+        <v>627.8081665039062</v>
       </c>
       <c r="F140" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B141" t="n">
-        <v>626.3894374266143</v>
+        <v>633.882449891805</v>
       </c>
       <c r="C141" t="n">
-        <v>636.9097166035551</v>
+        <v>637.9886903650855</v>
       </c>
       <c r="D141" t="n">
-        <v>622.4231426572783</v>
+        <v>623.7518859014353</v>
       </c>
       <c r="E141" t="n">
-        <v>627.8081665039062</v>
+        <v>629.2767333984375</v>
       </c>
       <c r="F141" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B142" t="n">
-        <v>633.882449891805</v>
+        <v>628.9171329935918</v>
       </c>
       <c r="C142" t="n">
-        <v>637.9886903650855</v>
+        <v>634.4120404303904</v>
       </c>
       <c r="D142" t="n">
-        <v>623.7518859014353</v>
+        <v>623.8218795800174</v>
       </c>
       <c r="E142" t="n">
-        <v>629.2767333984375</v>
+        <v>633.9425048828125</v>
       </c>
       <c r="F142" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B143" t="n">
-        <v>628.9171329935918</v>
+        <v>642.624350345733</v>
       </c>
       <c r="C143" t="n">
-        <v>634.4120404303904</v>
+        <v>665.6430543798978</v>
       </c>
       <c r="D143" t="n">
-        <v>623.8218795800174</v>
+        <v>638.7779398291946</v>
       </c>
       <c r="E143" t="n">
-        <v>633.9425048828125</v>
+        <v>661.8765258789062</v>
       </c>
       <c r="F143" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B144" t="n">
-        <v>642.624350345733</v>
+        <v>666.3824145357423</v>
       </c>
       <c r="C144" t="n">
-        <v>665.6430543798978</v>
+        <v>677.8717665104965</v>
       </c>
       <c r="D144" t="n">
-        <v>638.7779398291946</v>
+        <v>663.6049593103575</v>
       </c>
       <c r="E144" t="n">
-        <v>661.8765258789062</v>
+        <v>670.9581909179688</v>
       </c>
       <c r="F144" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B145" t="n">
-        <v>666.3824145357423</v>
+        <v>675.3640350842893</v>
       </c>
       <c r="C145" t="n">
-        <v>677.8717665104965</v>
+        <v>676.9525896021297</v>
       </c>
       <c r="D145" t="n">
-        <v>663.6049593103575</v>
+        <v>667.131674939706</v>
       </c>
       <c r="E145" t="n">
-        <v>670.9581909179688</v>
+        <v>676.2432250976562</v>
       </c>
       <c r="F145" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B146" t="n">
-        <v>675.3640350842893</v>
+        <v>677.9716157075654</v>
       </c>
       <c r="C146" t="n">
-        <v>676.9525896021297</v>
+        <v>690.8796961433965</v>
       </c>
       <c r="D146" t="n">
-        <v>667.131674939706</v>
+        <v>674.5048580761284</v>
       </c>
       <c r="E146" t="n">
-        <v>676.2432250976562</v>
+        <v>687.9124145507812</v>
       </c>
       <c r="F146" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B147" t="n">
-        <v>677.9716157075654</v>
+        <v>680.7290935491282</v>
       </c>
       <c r="C147" t="n">
-        <v>690.8796961433965</v>
+        <v>682.7472426832454</v>
       </c>
       <c r="D147" t="n">
-        <v>674.5048580761284</v>
+        <v>667.381478611767</v>
       </c>
       <c r="E147" t="n">
-        <v>687.9124145507812</v>
+        <v>670.2887573242188</v>
       </c>
       <c r="F147" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B148" t="n">
-        <v>680.7290935491282</v>
+        <v>670.3786762058809</v>
       </c>
       <c r="C148" t="n">
-        <v>682.7472426832454</v>
+        <v>675.5738733736962</v>
       </c>
       <c r="D148" t="n">
-        <v>667.381478611767</v>
+        <v>666.7120915784461</v>
       </c>
       <c r="E148" t="n">
-        <v>670.2887573242188</v>
+        <v>668.220703125</v>
       </c>
       <c r="F148" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B149" t="n">
-        <v>670.3786762058809</v>
+        <v>673.7355628200382</v>
       </c>
       <c r="C149" t="n">
-        <v>675.5738733736962</v>
+        <v>677.7518600207422</v>
       </c>
       <c r="D149" t="n">
-        <v>666.7120915784461</v>
+        <v>669.1298460769134</v>
       </c>
       <c r="E149" t="n">
-        <v>668.220703125</v>
+        <v>674.09521484375</v>
       </c>
       <c r="F149" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B150" t="n">
-        <v>673.7355628200382</v>
+        <v>663.0854475032797</v>
       </c>
       <c r="C150" t="n">
-        <v>677.7518600207422</v>
+        <v>668.9400066983026</v>
       </c>
       <c r="D150" t="n">
-        <v>669.1298460769134</v>
+        <v>652.4452846667049</v>
       </c>
       <c r="E150" t="n">
-        <v>674.09521484375</v>
+        <v>658.5396728515625</v>
       </c>
       <c r="F150" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B151" t="n">
-        <v>663.0854475032797</v>
+        <v>659.7085674039201</v>
       </c>
       <c r="C151" t="n">
-        <v>668.9400066983026</v>
+        <v>680.0396994180859</v>
       </c>
       <c r="D151" t="n">
-        <v>652.4452846667049</v>
+        <v>653.2345872360809</v>
       </c>
       <c r="E151" t="n">
-        <v>658.5396728515625</v>
+        <v>674.4049682617188</v>
       </c>
       <c r="F151" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B152" t="n">
-        <v>659.7085674039201</v>
+        <v>670.3786986745525</v>
       </c>
       <c r="C152" t="n">
-        <v>680.0396994180859</v>
+        <v>681.8680504402118</v>
       </c>
       <c r="D152" t="n">
-        <v>653.2345872360809</v>
+        <v>670.2188736545023</v>
       </c>
       <c r="E152" t="n">
-        <v>674.4049682617188</v>
+        <v>677.9916381835938</v>
       </c>
       <c r="F152" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B153" t="n">
-        <v>670.3786986745525</v>
+        <v>673.6156618787633</v>
       </c>
       <c r="C153" t="n">
-        <v>681.8680504402118</v>
+        <v>677.5520159823654</v>
       </c>
       <c r="D153" t="n">
-        <v>670.2188736545023</v>
+        <v>665.0136491453696</v>
       </c>
       <c r="E153" t="n">
-        <v>677.9916381835938</v>
+        <v>670.7183837890625</v>
       </c>
       <c r="F153" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B154" t="n">
-        <v>673.6156618787633</v>
+        <v>668.2905997420939</v>
       </c>
       <c r="C154" t="n">
-        <v>677.5520159823654</v>
+        <v>673.6256820299297</v>
       </c>
       <c r="D154" t="n">
-        <v>665.0136491453696</v>
+        <v>663.1953464496755</v>
       </c>
       <c r="E154" t="n">
-        <v>670.7183837890625</v>
+        <v>668.5004272460938</v>
       </c>
       <c r="F154" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B155" t="n">
-        <v>668.2905997420939</v>
+        <v>618.7465567527638</v>
       </c>
       <c r="C155" t="n">
-        <v>673.6256820299297</v>
+        <v>620.2751083620838</v>
       </c>
       <c r="D155" t="n">
-        <v>663.1953464496755</v>
+        <v>599.4444385151393</v>
       </c>
       <c r="E155" t="n">
-        <v>668.5004272460938</v>
+        <v>611.3433837890625</v>
       </c>
       <c r="F155" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B156" t="n">
-        <v>618.7465567527638</v>
+        <v>614.120842749119</v>
       </c>
       <c r="C156" t="n">
-        <v>620.2751083620838</v>
+        <v>618.3069655430758</v>
       </c>
       <c r="D156" t="n">
-        <v>599.4444385151393</v>
+        <v>605.5487701514051</v>
       </c>
       <c r="E156" t="n">
-        <v>611.3433837890625</v>
+        <v>608.1863403320312</v>
       </c>
       <c r="F156" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B157" t="n">
-        <v>614.120842749119</v>
+        <v>607.3771038685389</v>
       </c>
       <c r="C157" t="n">
-        <v>618.3069655430758</v>
+        <v>613.4314904063681</v>
       </c>
       <c r="D157" t="n">
-        <v>605.5487701514051</v>
+        <v>602.1919069095087</v>
       </c>
       <c r="E157" t="n">
-        <v>608.1863403320312</v>
+        <v>609.8447875976562</v>
       </c>
       <c r="F157" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B158" t="n">
-        <v>607.3771038685389</v>
+        <v>612.7420849871345</v>
       </c>
       <c r="C158" t="n">
-        <v>613.4314904063681</v>
+        <v>613.7811000159977</v>
       </c>
       <c r="D158" t="n">
-        <v>602.1919069095087</v>
+        <v>599.8040642277598</v>
       </c>
       <c r="E158" t="n">
-        <v>609.8447875976562</v>
+        <v>604.3998413085938</v>
       </c>
       <c r="F158" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B159" t="n">
-        <v>612.7420849871345</v>
+        <v>600.4934370812971</v>
       </c>
       <c r="C159" t="n">
-        <v>613.7811000159977</v>
+        <v>619.3759607512419</v>
       </c>
       <c r="D159" t="n">
-        <v>599.8040642277598</v>
+        <v>597.5461564796674</v>
       </c>
       <c r="E159" t="n">
-        <v>604.3998413085938</v>
+        <v>612.3125</v>
       </c>
       <c r="F159" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B160" t="n">
-        <v>600.4934370812971</v>
+        <v>614.150739078972</v>
       </c>
       <c r="C160" t="n">
-        <v>619.3759607512419</v>
+        <v>624.4012480600104</v>
       </c>
       <c r="D160" t="n">
-        <v>597.5461564796674</v>
+        <v>612.9718390781961</v>
       </c>
       <c r="E160" t="n">
-        <v>612.3125</v>
+        <v>616.2388305664062</v>
       </c>
       <c r="F160" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B161" t="n">
-        <v>614.150739078972</v>
+        <v>614.6303402495529</v>
       </c>
       <c r="C161" t="n">
-        <v>624.4012480600104</v>
+        <v>616.1988937552933</v>
       </c>
       <c r="D161" t="n">
-        <v>612.9718390781961</v>
+        <v>605.4987892063378</v>
       </c>
       <c r="E161" t="n">
-        <v>616.2388305664062</v>
+        <v>609.0654907226562</v>
       </c>
       <c r="F161" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="n">
-        <v>614.6303402495529</v>
+        <v>604.010215830275</v>
       </c>
       <c r="C162" t="n">
-        <v>616.1988937552933</v>
+        <v>604.3498668649182</v>
       </c>
       <c r="D162" t="n">
-        <v>605.4987892063378</v>
+        <v>597.5262348938886</v>
       </c>
       <c r="E162" t="n">
-        <v>609.0654907226562</v>
+        <v>598.3054809570312</v>
       </c>
       <c r="F162" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="n">
-        <v>604.010215830275</v>
+        <v>594.2692320029287</v>
       </c>
       <c r="C163" t="n">
-        <v>604.3498668649182</v>
+        <v>603.1909559259367</v>
       </c>
       <c r="D163" t="n">
-        <v>597.5262348938886</v>
+        <v>592.0512559095129</v>
       </c>
       <c r="E163" t="n">
-        <v>598.3054809570312</v>
+        <v>602.441650390625</v>
       </c>
       <c r="F163" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="n">
-        <v>594.2692320029287</v>
+        <v>598.275515544453</v>
       </c>
       <c r="C164" t="n">
-        <v>603.1909559259367</v>
+        <v>619.3260125714435</v>
       </c>
       <c r="D164" t="n">
-        <v>592.0512559095129</v>
+        <v>596.1074810052941</v>
       </c>
       <c r="E164" t="n">
-        <v>602.441650390625</v>
+        <v>616.0590209960938</v>
       </c>
       <c r="F164" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="n">
-        <v>598.275515544453</v>
+        <v>615.4296182023591</v>
       </c>
       <c r="C165" t="n">
-        <v>619.3260125714435</v>
+        <v>623.152441138389</v>
       </c>
       <c r="D165" t="n">
-        <v>596.1074810052941</v>
+        <v>614.4305441468357</v>
       </c>
       <c r="E165" t="n">
-        <v>616.0590209960938</v>
+        <v>617.8573608398438</v>
       </c>
       <c r="F165" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="n">
-        <v>615.4296182023591</v>
+        <v>613.421486859321</v>
       </c>
       <c r="C166" t="n">
-        <v>623.152441138389</v>
+        <v>620.6248329546977</v>
       </c>
       <c r="D166" t="n">
-        <v>614.4305441468357</v>
+        <v>608.7458274653094</v>
       </c>
       <c r="E166" t="n">
-        <v>617.8573608398438</v>
+        <v>613.6612548828125</v>
       </c>
       <c r="F166" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="n">
-        <v>613.421486859321</v>
+        <v>608.5459509764945</v>
       </c>
       <c r="C167" t="n">
-        <v>620.6248329546977</v>
+        <v>615.0199919776213</v>
       </c>
       <c r="D167" t="n">
-        <v>608.7458274653094</v>
+        <v>603.1309869574205</v>
       </c>
       <c r="E167" t="n">
-        <v>613.6612548828125</v>
+        <v>610.64404296875</v>
       </c>
       <c r="F167" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="n">
-        <v>608.5459509764945</v>
+        <v>608.3561568042173</v>
       </c>
       <c r="C168" t="n">
-        <v>615.0199919776213</v>
+        <v>613.361527578881</v>
       </c>
       <c r="D168" t="n">
-        <v>603.1309869574205</v>
+        <v>599.9939118379299</v>
       </c>
       <c r="E168" t="n">
-        <v>610.64404296875</v>
+        <v>602.052001953125</v>
       </c>
       <c r="F168" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="n">
-        <v>608.3561568042173</v>
+        <v>600.2037495434126</v>
       </c>
       <c r="C169" t="n">
-        <v>613.361527578881</v>
+        <v>607.4370360716302</v>
       </c>
       <c r="D169" t="n">
-        <v>599.9939118379299</v>
+        <v>597.2564688338498</v>
       </c>
       <c r="E169" t="n">
-        <v>602.052001953125</v>
+        <v>604.499755859375</v>
       </c>
       <c r="F169" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="n">
-        <v>600.2037495434126</v>
+        <v>599.4443949814065</v>
       </c>
       <c r="C170" t="n">
-        <v>607.4370360716302</v>
+        <v>609.0354809096541</v>
       </c>
       <c r="D170" t="n">
-        <v>597.2564688338498</v>
+        <v>594.2591985256718</v>
       </c>
       <c r="E170" t="n">
-        <v>604.499755859375</v>
+        <v>606.8175659179688</v>
       </c>
       <c r="F170" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="n">
-        <v>599.4443949814065</v>
+        <v>607.3171451453314</v>
       </c>
       <c r="C171" t="n">
-        <v>609.0354809096541</v>
+        <v>614.2407210713809</v>
       </c>
       <c r="D171" t="n">
-        <v>594.2591985256718</v>
+        <v>606.3880135859368</v>
       </c>
       <c r="E171" t="n">
-        <v>606.8175659179688</v>
+        <v>609.6949462890625</v>
       </c>
       <c r="F171" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B172" t="n">
-        <v>607.3171451453314</v>
+        <v>608.3261927003538</v>
       </c>
       <c r="C172" t="n">
-        <v>614.2407210713809</v>
+        <v>613.9009818092591</v>
       </c>
       <c r="D172" t="n">
-        <v>606.3880135859368</v>
+        <v>604.7394901495815</v>
       </c>
       <c r="E172" t="n">
-        <v>609.6949462890625</v>
+        <v>611.7730102539062</v>
       </c>
       <c r="F172" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B173" t="n">
-        <v>608.3261927003538</v>
+        <v>608.8357727220844</v>
       </c>
       <c r="C173" t="n">
-        <v>613.9009818092591</v>
+        <v>637.908804248614</v>
       </c>
       <c r="D173" t="n">
-        <v>604.7394901495815</v>
+        <v>608.4361186960156</v>
       </c>
       <c r="E173" t="n">
-        <v>611.7730102539062</v>
+        <v>634.6718139648438</v>
       </c>
       <c r="F173" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B174" t="n">
-        <v>608.8357727220844</v>
+        <v>638.9078448274123</v>
       </c>
       <c r="C174" t="n">
-        <v>637.908804248614</v>
+        <v>642.4046039468743</v>
       </c>
       <c r="D174" t="n">
-        <v>608.4361186960156</v>
+        <v>628.7272779804616</v>
       </c>
       <c r="E174" t="n">
-        <v>634.6718139648438</v>
+        <v>634.7017211914062</v>
       </c>
       <c r="F174" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B175" t="n">
-        <v>638.9078448274123</v>
+        <v>632.9133899267435</v>
       </c>
       <c r="C175" t="n">
-        <v>642.4046039468743</v>
+        <v>633.9124639439917</v>
       </c>
       <c r="D175" t="n">
-        <v>628.7272779804616</v>
+        <v>622.7727642602187</v>
       </c>
       <c r="E175" t="n">
-        <v>634.7017211914062</v>
+        <v>631.92431640625</v>
       </c>
       <c r="F175" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B176" t="n">
-        <v>632.9133899267435</v>
+        <v>629.8162791560948</v>
       </c>
       <c r="C176" t="n">
-        <v>633.9124639439917</v>
+        <v>635.1613007084701</v>
       </c>
       <c r="D176" t="n">
-        <v>622.7727642602187</v>
+        <v>598.9748694014791</v>
       </c>
       <c r="E176" t="n">
-        <v>631.92431640625</v>
+        <v>599.9139404296875</v>
       </c>
       <c r="F176" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B177" t="n">
-        <v>629.8162791560948</v>
+        <v>602.6813896226799</v>
       </c>
       <c r="C177" t="n">
-        <v>635.1613007084701</v>
+        <v>608.3161816139932</v>
       </c>
       <c r="D177" t="n">
-        <v>598.9748694014791</v>
+        <v>596.1274666259658</v>
       </c>
       <c r="E177" t="n">
-        <v>599.9139404296875</v>
+        <v>597.0765991210938</v>
       </c>
       <c r="F177" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B178" t="n">
-        <v>602.6813896226799</v>
+        <v>602.4416570391962</v>
       </c>
       <c r="C178" t="n">
-        <v>608.3161816139932</v>
+        <v>623.5720977596394</v>
       </c>
       <c r="D178" t="n">
-        <v>596.1274666259658</v>
+        <v>599.7142043737263</v>
       </c>
       <c r="E178" t="n">
-        <v>597.0765991210938</v>
+        <v>622.4031372070312</v>
       </c>
       <c r="F178" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B179" t="n">
-        <v>602.4416570391962</v>
+        <v>623.0924785224576</v>
       </c>
       <c r="C179" t="n">
-        <v>623.5720977596394</v>
+        <v>641.8051764288737</v>
       </c>
       <c r="D179" t="n">
-        <v>599.7142043737263</v>
+        <v>621.8536364911718</v>
       </c>
       <c r="E179" t="n">
-        <v>622.4031372070312</v>
+        <v>626.9888916015625</v>
       </c>
       <c r="F179" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B180" t="n">
-        <v>623.0924785224576</v>
+        <v>622.8827460758752</v>
       </c>
       <c r="C180" t="n">
-        <v>641.8051764288737</v>
+        <v>628.5674800138549</v>
       </c>
       <c r="D180" t="n">
-        <v>621.8536364911718</v>
+        <v>582.3702434655938</v>
       </c>
       <c r="E180" t="n">
-        <v>626.9888916015625</v>
+        <v>592.450927734375</v>
       </c>
       <c r="F180" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B181" t="n">
-        <v>622.8827460758752</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="C181" t="n">
-        <v>628.5674800138549</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="D181" t="n">
-        <v>582.3702434655938</v>
+        <v>578.6836307521693</v>
       </c>
       <c r="E181" t="n">
-        <v>592.450927734375</v>
+        <v>584.8479614257812</v>
       </c>
       <c r="F181" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B182" t="n">
-        <v>591.4518261333767</v>
+        <v>590.4527436689563</v>
       </c>
       <c r="C182" t="n">
-        <v>591.4518261333767</v>
+        <v>597.0766092757164</v>
       </c>
       <c r="D182" t="n">
-        <v>578.6836307521693</v>
+        <v>580.4720040020986</v>
       </c>
       <c r="E182" t="n">
-        <v>584.8479614257812</v>
+        <v>584.0487060546875</v>
       </c>
       <c r="F182" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B183" t="n">
-        <v>590.4527436689563</v>
+        <v>580.192266144374</v>
       </c>
       <c r="C183" t="n">
-        <v>597.0766092757164</v>
+        <v>590.7724873942649</v>
       </c>
       <c r="D183" t="n">
-        <v>580.4720040020986</v>
+        <v>570.0716409197756</v>
       </c>
       <c r="E183" t="n">
-        <v>584.0487060546875</v>
+        <v>570.4512939453125</v>
       </c>
       <c r="F183" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B184" t="n">
-        <v>580.192266144374</v>
+        <v>565.3060574843756</v>
       </c>
       <c r="C184" t="n">
-        <v>590.7724873942649</v>
+        <v>571.6401524850257</v>
       </c>
       <c r="D184" t="n">
-        <v>570.0716409197756</v>
+        <v>556.4942175026772</v>
       </c>
       <c r="E184" t="n">
-        <v>570.4512939453125</v>
+        <v>567.9036254882812</v>
       </c>
       <c r="F184" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B185" t="n">
-        <v>565.3060574843756</v>
+        <v>572.4194595335534</v>
       </c>
       <c r="C185" t="n">
-        <v>571.6401524850257</v>
+        <v>575.5365655300229</v>
       </c>
       <c r="D185" t="n">
-        <v>556.4942175026772</v>
+        <v>560.3806300495169</v>
       </c>
       <c r="E185" t="n">
-        <v>567.9036254882812</v>
+        <v>566.4549560546875</v>
       </c>
       <c r="F185" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B186" t="n">
-        <v>572.4194595335534</v>
+        <v>579.9000244140625</v>
       </c>
       <c r="C186" t="n">
-        <v>575.5365655300229</v>
+        <v>601.27001953125</v>
       </c>
       <c r="D186" t="n">
-        <v>560.3806300495169</v>
+        <v>579.2999877929688</v>
       </c>
       <c r="E186" t="n">
-        <v>566.4549560546875</v>
+        <v>593.47998046875</v>
       </c>
       <c r="F186" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5279,25 +5279,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B187" t="n">
-        <v>579.9000244140625</v>
+        <v>593.6500244140625</v>
       </c>
       <c r="C187" t="n">
-        <v>601.27001953125</v>
+        <v>605.8099975585938</v>
       </c>
       <c r="D187" t="n">
-        <v>579.2999877929688</v>
+        <v>592</v>
       </c>
       <c r="E187" t="n">
-        <v>593.47998046875</v>
+        <v>600.2100219726562</v>
       </c>
       <c r="F187" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G187" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B188" t="n">
-        <v>593.6500244140625</v>
+        <v>592</v>
       </c>
       <c r="C188" t="n">
-        <v>605.8099975585938</v>
+        <v>593.8099975585938</v>
       </c>
       <c r="D188" t="n">
-        <v>592</v>
+        <v>566.1900024414062</v>
       </c>
       <c r="E188" t="n">
-        <v>600.2100219726562</v>
+        <v>567.5800170898438</v>
       </c>
       <c r="F188" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B189" t="n">
-        <v>592</v>
+        <v>572.8200073242188</v>
       </c>
       <c r="C189" t="n">
-        <v>593.8099975585938</v>
+        <v>580.219970703125</v>
       </c>
       <c r="D189" t="n">
-        <v>566.1900024414062</v>
+        <v>563.0999755859375</v>
       </c>
       <c r="E189" t="n">
-        <v>567.5800170898438</v>
+        <v>577.219970703125</v>
       </c>
       <c r="F189" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B190" t="n">
-        <v>572.8200073242188</v>
+        <v>572.02001953125</v>
       </c>
       <c r="C190" t="n">
-        <v>580.219970703125</v>
+        <v>575.8099975585938</v>
       </c>
       <c r="D190" t="n">
-        <v>563.0999755859375</v>
+        <v>559.8099975585938</v>
       </c>
       <c r="E190" t="n">
-        <v>577.219970703125</v>
+        <v>563.8499755859375</v>
       </c>
       <c r="F190" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B191" t="n">
-        <v>572.02001953125</v>
+        <v>562.25</v>
       </c>
       <c r="C191" t="n">
-        <v>575.8099975585938</v>
+        <v>572.2000122070312</v>
       </c>
       <c r="D191" t="n">
-        <v>559.8099975585938</v>
+        <v>561.02001953125</v>
       </c>
       <c r="E191" t="n">
-        <v>563.8499755859375</v>
+        <v>562.2000122070312</v>
       </c>
       <c r="F191" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B192" t="n">
-        <v>562.25</v>
+        <v>561.8900146484375</v>
       </c>
       <c r="C192" t="n">
-        <v>572.2000122070312</v>
+        <v>569.0399780273438</v>
       </c>
       <c r="D192" t="n">
-        <v>561.02001953125</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="E192" t="n">
-        <v>562.2000122070312</v>
+        <v>557.6699829101562</v>
       </c>
       <c r="F192" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B193" t="n">
-        <v>561.8900146484375</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="C193" t="n">
-        <v>569.0399780273438</v>
+        <v>556.3400268554688</v>
       </c>
       <c r="D193" t="n">
-        <v>555.5499877929688</v>
+        <v>540.1799926757812</v>
       </c>
       <c r="E193" t="n">
-        <v>557.6699829101562</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="F193" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B194" t="n">
-        <v>555.5499877929688</v>
+        <v>543.3400268554688</v>
       </c>
       <c r="C194" t="n">
-        <v>556.3400268554688</v>
+        <v>556.8499755859375</v>
       </c>
       <c r="D194" t="n">
-        <v>540.1799926757812</v>
+        <v>540.4000244140625</v>
       </c>
       <c r="E194" t="n">
-        <v>542.8699951171875</v>
+        <v>550.25</v>
       </c>
       <c r="F194" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B195" t="n">
-        <v>543.3400268554688</v>
+        <v>560</v>
       </c>
       <c r="C195" t="n">
-        <v>556.8499755859375</v>
+        <v>570.9000244140625</v>
       </c>
       <c r="D195" t="n">
-        <v>540.4000244140625</v>
+        <v>558</v>
       </c>
       <c r="E195" t="n">
-        <v>550.25</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="F195" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B196" t="n">
-        <v>560</v>
+        <v>560.9400024414062</v>
       </c>
       <c r="C196" t="n">
-        <v>570.9000244140625</v>
+        <v>565.5399780273438</v>
       </c>
       <c r="D196" t="n">
-        <v>558</v>
+        <v>551.4299926757812</v>
       </c>
       <c r="E196" t="n">
-        <v>562.5999755859375</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F196" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B197" t="n">
-        <v>560.9400024414062</v>
+        <v>607.9099731445312</v>
       </c>
       <c r="C197" t="n">
-        <v>565.5399780273438</v>
+        <v>628.280029296875</v>
       </c>
       <c r="D197" t="n">
-        <v>551.4299926757812</v>
+        <v>595.0999755859375</v>
       </c>
       <c r="E197" t="n">
-        <v>563.2899780273438</v>
+        <v>612.9099731445312</v>
       </c>
       <c r="F197" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B198" t="n">
-        <v>607.9099731445312</v>
+        <v>607.9000244140625</v>
       </c>
       <c r="C198" t="n">
-        <v>628.280029296875</v>
+        <v>610</v>
       </c>
       <c r="D198" t="n">
-        <v>595.0999755859375</v>
+        <v>580.4199829101562</v>
       </c>
       <c r="E198" t="n">
-        <v>612.9099731445312</v>
+        <v>582.9000244140625</v>
       </c>
       <c r="F198" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B199" t="n">
-        <v>607.9000244140625</v>
+        <v>594.8400268554688</v>
       </c>
       <c r="C199" t="n">
-        <v>610</v>
+        <v>603.5800170898438</v>
       </c>
       <c r="D199" t="n">
-        <v>580.4199829101562</v>
+        <v>581.760009765625</v>
       </c>
       <c r="E199" t="n">
-        <v>582.9000244140625</v>
+        <v>600.2899780273438</v>
       </c>
       <c r="F199" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B200" t="n">
-        <v>594.8400268554688</v>
+        <v>607.5900268554688</v>
       </c>
       <c r="C200" t="n">
-        <v>603.5800170898438</v>
+        <v>625.3699951171875</v>
       </c>
       <c r="D200" t="n">
-        <v>581.760009765625</v>
+        <v>603.6599731445312</v>
       </c>
       <c r="E200" t="n">
-        <v>600.2899780273438</v>
+        <v>615.5800170898438</v>
       </c>
       <c r="F200" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B201" t="n">
-        <v>607.5900268554688</v>
+        <v>614.3900146484375</v>
       </c>
       <c r="C201" t="n">
-        <v>625.3699951171875</v>
+        <v>616</v>
       </c>
       <c r="D201" t="n">
-        <v>603.6599731445312</v>
+        <v>598.010009765625</v>
       </c>
       <c r="E201" t="n">
-        <v>615.5800170898438</v>
+        <v>603.1199951171875</v>
       </c>
       <c r="F201" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B202" t="n">
-        <v>614.3900146484375</v>
+        <v>583.989990234375</v>
       </c>
       <c r="C202" t="n">
-        <v>616</v>
+        <v>633.27001953125</v>
       </c>
       <c r="D202" t="n">
-        <v>598.010009765625</v>
+        <v>577.0700073242188</v>
       </c>
       <c r="E202" t="n">
-        <v>603.1199951171875</v>
+        <v>631.47998046875</v>
       </c>
       <c r="F202" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B203" t="n">
-        <v>583.989990234375</v>
+        <v>660.3400268554688</v>
       </c>
       <c r="C203" t="n">
-        <v>633.27001953125</v>
+        <v>677.8599853515625</v>
       </c>
       <c r="D203" t="n">
-        <v>577.0700073242188</v>
+        <v>658.010009765625</v>
       </c>
       <c r="E203" t="n">
-        <v>631.47998046875</v>
+        <v>669.2100219726562</v>
       </c>
       <c r="F203" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B204" t="n">
-        <v>660.3400268554688</v>
+        <v>661.3800048828125</v>
       </c>
       <c r="C204" t="n">
-        <v>677.8599853515625</v>
+        <v>676.6199951171875</v>
       </c>
       <c r="D204" t="n">
-        <v>658.010009765625</v>
+        <v>654.2000122070312</v>
       </c>
       <c r="E204" t="n">
-        <v>669.2100219726562</v>
+        <v>656.72998046875</v>
       </c>
       <c r="F204" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>661.3800048828125</v>
+        <v>652</v>
       </c>
       <c r="C205" t="n">
-        <v>676.6199951171875</v>
+        <v>666.5</v>
       </c>
       <c r="D205" t="n">
-        <v>654.2000122070312</v>
+        <v>649.0499877929688</v>
       </c>
       <c r="E205" t="n">
-        <v>656.72998046875</v>
+        <v>661.0399780273438</v>
       </c>
       <c r="F205" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>652</v>
+        <v>663.5999755859375</v>
       </c>
       <c r="C206" t="n">
-        <v>666.5</v>
+        <v>686.0800170898438</v>
       </c>
       <c r="D206" t="n">
-        <v>649.0499877929688</v>
+        <v>656.6599731445312</v>
       </c>
       <c r="E206" t="n">
-        <v>661.0399780273438</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="F206" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>663.5999755859375</v>
+        <v>677.280029296875</v>
       </c>
       <c r="C207" t="n">
-        <v>686.0800170898438</v>
+        <v>681.9000244140625</v>
       </c>
       <c r="D207" t="n">
-        <v>656.6599731445312</v>
+        <v>660.1599731445312</v>
       </c>
       <c r="E207" t="n">
-        <v>681.3099975585938</v>
+        <v>664.5399780273438</v>
       </c>
       <c r="F207" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B208" t="n">
-        <v>677.280029296875</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C208" t="n">
-        <v>681.9000244140625</v>
+        <v>652.2000122070312</v>
       </c>
       <c r="D208" t="n">
-        <v>660.1599731445312</v>
+        <v>626</v>
       </c>
       <c r="E208" t="n">
-        <v>664.5399780273438</v>
+        <v>646.010009765625</v>
       </c>
       <c r="F208" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B209" t="n">
-        <v>647.7000122070312</v>
+        <v>646.7000122070312</v>
       </c>
       <c r="C209" t="n">
-        <v>652.2000122070312</v>
+        <v>653.2999877929688</v>
       </c>
       <c r="D209" t="n">
-        <v>626</v>
+        <v>636.010009765625</v>
       </c>
       <c r="E209" t="n">
-        <v>646.010009765625</v>
+        <v>645.8499755859375</v>
       </c>
       <c r="F209" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B210" t="n">
-        <v>646.7000122070312</v>
+        <v>654.1799926757812</v>
       </c>
       <c r="C210" t="n">
-        <v>653.2999877929688</v>
+        <v>655.8800048828125</v>
       </c>
       <c r="D210" t="n">
-        <v>636.010009765625</v>
+        <v>643.2000122070312</v>
       </c>
       <c r="E210" t="n">
-        <v>645.8499755859375</v>
+        <v>643.8099975585938</v>
       </c>
       <c r="F210" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B211" t="n">
-        <v>654.1799926757812</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C211" t="n">
-        <v>655.8800048828125</v>
+        <v>649</v>
       </c>
       <c r="D211" t="n">
-        <v>643.2000122070312</v>
+        <v>624</v>
       </c>
       <c r="E211" t="n">
-        <v>643.8099975585938</v>
+        <v>627.1699829101562</v>
       </c>
       <c r="F211" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B212" t="n">
-        <v>647.7000122070312</v>
+        <v>608.4099731445312</v>
       </c>
       <c r="C212" t="n">
-        <v>649</v>
+        <v>614.6500244140625</v>
       </c>
       <c r="D212" t="n">
-        <v>624</v>
+        <v>597.219970703125</v>
       </c>
       <c r="E212" t="n">
-        <v>627.1699829101562</v>
+        <v>606.0999755859375</v>
       </c>
       <c r="F212" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B213" t="n">
-        <v>608.4099731445312</v>
+        <v>605.2999877929688</v>
       </c>
       <c r="C213" t="n">
-        <v>614.6500244140625</v>
+        <v>609.97998046875</v>
       </c>
       <c r="D213" t="n">
-        <v>597.219970703125</v>
+        <v>594.4500122070312</v>
       </c>
       <c r="E213" t="n">
-        <v>606.0999755859375</v>
+        <v>595.1900024414062</v>
       </c>
       <c r="F213" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B214" t="n">
-        <v>605.2999877929688</v>
+        <v>607.219970703125</v>
       </c>
       <c r="C214" t="n">
-        <v>609.97998046875</v>
+        <v>611.260009765625</v>
       </c>
       <c r="D214" t="n">
-        <v>594.4500122070312</v>
+        <v>593.1300048828125</v>
       </c>
       <c r="E214" t="n">
-        <v>595.1900024414062</v>
+        <v>593.8699951171875</v>
       </c>
       <c r="F214" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B215" t="n">
-        <v>607.219970703125</v>
+        <v>596.8200073242188</v>
       </c>
       <c r="C215" t="n">
-        <v>611.260009765625</v>
+        <v>601</v>
       </c>
       <c r="D215" t="n">
-        <v>593.1300048828125</v>
+        <v>587</v>
       </c>
       <c r="E215" t="n">
-        <v>593.8699951171875</v>
+        <v>593.4099731445312</v>
       </c>
       <c r="F215" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B216" t="n">
-        <v>596.8200073242188</v>
+        <v>593.25</v>
       </c>
       <c r="C216" t="n">
-        <v>601</v>
+        <v>599.969970703125</v>
       </c>
       <c r="D216" t="n">
-        <v>587</v>
+        <v>582.219970703125</v>
       </c>
       <c r="E216" t="n">
-        <v>593.4099731445312</v>
+        <v>585.6099853515625</v>
       </c>
       <c r="F216" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B217" t="n">
-        <v>593.25</v>
+        <v>526</v>
       </c>
       <c r="C217" t="n">
-        <v>599.969970703125</v>
+        <v>539.8800048828125</v>
       </c>
       <c r="D217" t="n">
-        <v>582.219970703125</v>
+        <v>524.489990234375</v>
       </c>
       <c r="E217" t="n">
-        <v>585.6099853515625</v>
+        <v>539.030029296875</v>
       </c>
       <c r="F217" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B218" t="n">
-        <v>526</v>
+        <v>543.5999755859375</v>
       </c>
       <c r="C218" t="n">
-        <v>539.8800048828125</v>
+        <v>558.3300170898438</v>
       </c>
       <c r="D218" t="n">
-        <v>524.489990234375</v>
+        <v>540.219970703125</v>
       </c>
       <c r="E218" t="n">
-        <v>539.030029296875</v>
+        <v>556.7100219726562</v>
       </c>
       <c r="F218" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B219" t="n">
-        <v>543.5999755859375</v>
+        <v>562.239990234375</v>
       </c>
       <c r="C219" t="n">
-        <v>558.3300170898438</v>
+        <v>597.52001953125</v>
       </c>
       <c r="D219" t="n">
-        <v>540.219970703125</v>
+        <v>559.3599853515625</v>
       </c>
       <c r="E219" t="n">
-        <v>556.7100219726562</v>
+        <v>590.239990234375</v>
       </c>
       <c r="F219" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B220" t="n">
-        <v>562.239990234375</v>
+        <v>581.5</v>
       </c>
       <c r="C220" t="n">
-        <v>597.52001953125</v>
+        <v>592.7899780273438</v>
       </c>
       <c r="D220" t="n">
-        <v>559.3599853515625</v>
+        <v>578.25</v>
       </c>
       <c r="E220" t="n">
-        <v>590.239990234375</v>
+        <v>587.9400024414062</v>
       </c>
       <c r="F220" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B221" t="n">
-        <v>581.5</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="C221" t="n">
-        <v>592.7899780273438</v>
+        <v>601</v>
       </c>
       <c r="D221" t="n">
-        <v>578.25</v>
+        <v>580.1199951171875</v>
       </c>
       <c r="E221" t="n">
-        <v>587.9400024414062</v>
+        <v>588.77001953125</v>
       </c>
       <c r="F221" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B222" t="n">
-        <v>600.4600219726562</v>
+        <v>586.9500122070312</v>
       </c>
       <c r="C222" t="n">
-        <v>601</v>
+        <v>595.3099975585938</v>
       </c>
       <c r="D222" t="n">
-        <v>580.1199951171875</v>
+        <v>586</v>
       </c>
       <c r="E222" t="n">
-        <v>588.77001953125</v>
+        <v>589.9000244140625</v>
       </c>
       <c r="F222" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B223" t="n">
-        <v>586.9500122070312</v>
+        <v>585.6400146484375</v>
       </c>
       <c r="C223" t="n">
-        <v>595.3099975585938</v>
+        <v>598.739990234375</v>
       </c>
       <c r="D223" t="n">
-        <v>586</v>
+        <v>585.6199951171875</v>
       </c>
       <c r="E223" t="n">
-        <v>589.9000244140625</v>
+        <v>592.0999755859375</v>
       </c>
       <c r="F223" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B224" t="n">
-        <v>585.6400146484375</v>
+        <v>599.1300048828125</v>
       </c>
       <c r="C224" t="n">
-        <v>598.739990234375</v>
+        <v>608.2100219726562</v>
       </c>
       <c r="D224" t="n">
-        <v>585.6199951171875</v>
+        <v>592.030029296875</v>
       </c>
       <c r="E224" t="n">
-        <v>592.0999755859375</v>
+        <v>594.9199829101562</v>
       </c>
       <c r="F224" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B225" t="n">
-        <v>599.1300048828125</v>
+        <v>598</v>
       </c>
       <c r="C225" t="n">
-        <v>608.2100219726562</v>
+        <v>612.4299926757812</v>
       </c>
       <c r="D225" t="n">
-        <v>592.030029296875</v>
+        <v>593.4000244140625</v>
       </c>
       <c r="E225" t="n">
-        <v>594.9199829101562</v>
+        <v>599.1199951171875</v>
       </c>
       <c r="F225" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B226" t="n">
-        <v>598</v>
+        <v>601.0700073242188</v>
       </c>
       <c r="C226" t="n">
-        <v>612.4299926757812</v>
+        <v>604.5</v>
       </c>
       <c r="D226" t="n">
-        <v>593.4000244140625</v>
+        <v>578.2100219726562</v>
       </c>
       <c r="E226" t="n">
-        <v>599.1199951171875</v>
+        <v>578.8499755859375</v>
       </c>
       <c r="F226" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B227" t="n">
-        <v>601.0700073242188</v>
+        <v>580.7100219726562</v>
       </c>
       <c r="C227" t="n">
-        <v>604.5</v>
+        <v>595.8499755859375</v>
       </c>
       <c r="D227" t="n">
-        <v>578.2100219726562</v>
+        <v>579.3900146484375</v>
       </c>
       <c r="E227" t="n">
-        <v>578.8499755859375</v>
+        <v>594.969970703125</v>
       </c>
       <c r="F227" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B228" t="n">
-        <v>580.7100219726562</v>
+        <v>596.97998046875</v>
       </c>
       <c r="C228" t="n">
-        <v>595.8499755859375</v>
+        <v>601.8599853515625</v>
       </c>
       <c r="D228" t="n">
-        <v>579.3900146484375</v>
+        <v>589.2899780273438</v>
       </c>
       <c r="E228" t="n">
-        <v>594.969970703125</v>
+        <v>589.8499755859375</v>
       </c>
       <c r="F228" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B229" t="n">
-        <v>596.97998046875</v>
+        <v>589.75</v>
       </c>
       <c r="C229" t="n">
-        <v>601.8599853515625</v>
+        <v>590.239990234375</v>
       </c>
       <c r="D229" t="n">
-        <v>589.2899780273438</v>
+        <v>564.75</v>
       </c>
       <c r="E229" t="n">
-        <v>589.8499755859375</v>
+        <v>568.969970703125</v>
       </c>
       <c r="F229" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B230" t="n">
-        <v>589.75</v>
+        <v>557.47998046875</v>
       </c>
       <c r="C230" t="n">
-        <v>590.239990234375</v>
+        <v>560.6599731445312</v>
       </c>
       <c r="D230" t="n">
-        <v>564.75</v>
+        <v>543.2100219726562</v>
       </c>
       <c r="E230" t="n">
-        <v>568.969970703125</v>
+        <v>543.6699829101562</v>
       </c>
       <c r="F230" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B231" t="n">
-        <v>557.47998046875</v>
+        <v>541.3400268554688</v>
       </c>
       <c r="C231" t="n">
-        <v>560.6599731445312</v>
+        <v>554.0700073242188</v>
       </c>
       <c r="D231" t="n">
-        <v>543.2100219726562</v>
+        <v>537.27001953125</v>
       </c>
       <c r="E231" t="n">
-        <v>543.6699829101562</v>
+        <v>546.030029296875</v>
       </c>
       <c r="F231" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B232" t="n">
-        <v>541.3400268554688</v>
+        <v>546.9500122070312</v>
       </c>
       <c r="C232" t="n">
-        <v>554.0700073242188</v>
+        <v>549.989990234375</v>
       </c>
       <c r="D232" t="n">
-        <v>537.27001953125</v>
+        <v>539.3099975585938</v>
       </c>
       <c r="E232" t="n">
-        <v>546.030029296875</v>
+        <v>545.8300170898438</v>
       </c>
       <c r="F232" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B233" t="n">
-        <v>546.9500122070312</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="C233" t="n">
-        <v>549.989990234375</v>
+        <v>553.8699951171875</v>
       </c>
       <c r="D233" t="n">
-        <v>539.3099975585938</v>
+        <v>543.22998046875</v>
       </c>
       <c r="E233" t="n">
-        <v>545.8300170898438</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="F233" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B234" t="n">
-        <v>546.8900146484375</v>
+        <v>550.2000122070312</v>
       </c>
       <c r="C234" t="n">
-        <v>553.8699951171875</v>
+        <v>561.4199829101562</v>
       </c>
       <c r="D234" t="n">
-        <v>543.22998046875</v>
+        <v>546.2999877929688</v>
       </c>
       <c r="E234" t="n">
-        <v>549.9000244140625</v>
+        <v>559.02001953125</v>
       </c>
       <c r="F234" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B235" t="n">
-        <v>550.2000122070312</v>
+        <v>563.8800048828125</v>
       </c>
       <c r="C235" t="n">
-        <v>561.4199829101562</v>
+        <v>570.7999877929688</v>
       </c>
       <c r="D235" t="n">
-        <v>546.2999877929688</v>
+        <v>561.4000244140625</v>
       </c>
       <c r="E235" t="n">
-        <v>559.02001953125</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="F235" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B236" t="n">
-        <v>563.8800048828125</v>
+        <v>590.3099975585938</v>
       </c>
       <c r="C236" t="n">
-        <v>570.7999877929688</v>
+        <v>593.3400268554688</v>
       </c>
       <c r="D236" t="n">
-        <v>561.4000244140625</v>
+        <v>561.8800048828125</v>
       </c>
       <c r="E236" t="n">
-        <v>570.0499877929688</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="F236" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B237" t="n">
-        <v>590.3099975585938</v>
+        <v>576.47998046875</v>
       </c>
       <c r="C237" t="n">
-        <v>593.3400268554688</v>
+        <v>588.3900146484375</v>
       </c>
       <c r="D237" t="n">
-        <v>561.8800048828125</v>
+        <v>567.6199951171875</v>
       </c>
       <c r="E237" t="n">
-        <v>576.1400146484375</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="F237" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B238" t="n">
-        <v>576.47998046875</v>
+        <v>571.5499877929688</v>
       </c>
       <c r="C238" t="n">
-        <v>588.3900146484375</v>
+        <v>589.1900024414062</v>
       </c>
       <c r="D238" t="n">
-        <v>567.6199951171875</v>
+        <v>571</v>
       </c>
       <c r="E238" t="n">
-        <v>571.0999755859375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="F238" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B239" t="n">
-        <v>571.5499877929688</v>
+        <v>577.6300048828125</v>
       </c>
       <c r="C239" t="n">
-        <v>589.1900024414062</v>
+        <v>578.6799926757812</v>
       </c>
       <c r="D239" t="n">
-        <v>571</v>
+        <v>569.1400146484375</v>
       </c>
       <c r="E239" t="n">
-        <v>578.02001953125</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="F239" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B240" t="n">
-        <v>577.6300048828125</v>
+        <v>558.3499755859375</v>
       </c>
       <c r="C240" t="n">
-        <v>578.6799926757812</v>
+        <v>584.9500122070312</v>
       </c>
       <c r="D240" t="n">
-        <v>569.1400146484375</v>
+        <v>556.0999755859375</v>
       </c>
       <c r="E240" t="n">
-        <v>572.3400268554688</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="F240" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B241" t="n">
-        <v>558.3499755859375</v>
+        <v>578.7899780273438</v>
       </c>
       <c r="C241" t="n">
-        <v>584.9500122070312</v>
+        <v>600.3800048828125</v>
       </c>
       <c r="D241" t="n">
-        <v>556.0999755859375</v>
+        <v>577</v>
       </c>
       <c r="E241" t="n">
-        <v>578.5399780273438</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="F241" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B242" t="n">
-        <v>578.7899780273438</v>
+        <v>604.489990234375</v>
       </c>
       <c r="C242" t="n">
-        <v>600.3800048828125</v>
+        <v>619.4600219726562</v>
       </c>
       <c r="D242" t="n">
-        <v>577</v>
+        <v>604.3499755859375</v>
       </c>
       <c r="E242" t="n">
-        <v>592.8499755859375</v>
+        <v>610.6799926757812</v>
       </c>
       <c r="F242" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B243" t="n">
-        <v>604.489990234375</v>
+        <v>612.3499755859375</v>
       </c>
       <c r="C243" t="n">
-        <v>619.4600219726562</v>
+        <v>617.4600219726562</v>
       </c>
       <c r="D243" t="n">
-        <v>604.3499755859375</v>
+        <v>605.27001953125</v>
       </c>
       <c r="E243" t="n">
-        <v>610.6799926757812</v>
+        <v>616.77001953125</v>
       </c>
       <c r="F243" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B244" t="n">
-        <v>612.3499755859375</v>
+        <v>616.2100219726562</v>
       </c>
       <c r="C244" t="n">
-        <v>617.4600219726562</v>
+        <v>624.7999877929688</v>
       </c>
       <c r="D244" t="n">
-        <v>605.27001953125</v>
+        <v>609.739990234375</v>
       </c>
       <c r="E244" t="n">
-        <v>616.77001953125</v>
+        <v>613.47998046875</v>
       </c>
       <c r="F244" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B245" t="n">
-        <v>616.2100219726562</v>
+        <v>648.6400146484375</v>
       </c>
       <c r="C245" t="n">
-        <v>624.7999877929688</v>
+        <v>657.8599853515625</v>
       </c>
       <c r="D245" t="n">
-        <v>609.739990234375</v>
+        <v>638.5599975585938</v>
       </c>
       <c r="E245" t="n">
-        <v>613.47998046875</v>
+        <v>653.6900024414062</v>
       </c>
       <c r="F245" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B246" t="n">
-        <v>648.6400146484375</v>
+        <v>653.7100219726562</v>
       </c>
       <c r="C246" t="n">
-        <v>657.8599853515625</v>
+        <v>663.5</v>
       </c>
       <c r="D246" t="n">
-        <v>638.5599975585938</v>
+        <v>642.1400146484375</v>
       </c>
       <c r="E246" t="n">
-        <v>653.6900024414062</v>
+        <v>644.3800048828125</v>
       </c>
       <c r="F246" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B247" t="n">
-        <v>653.7100219726562</v>
+        <v>653.510009765625</v>
       </c>
       <c r="C247" t="n">
-        <v>663.5</v>
+        <v>664.239990234375</v>
       </c>
       <c r="D247" t="n">
-        <v>642.1400146484375</v>
+        <v>646.2000122070312</v>
       </c>
       <c r="E247" t="n">
-        <v>644.3800048828125</v>
+        <v>648.030029296875</v>
       </c>
       <c r="F247" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B248" t="n">
-        <v>653.510009765625</v>
+        <v>657.8300170898438</v>
       </c>
       <c r="C248" t="n">
-        <v>664.239990234375</v>
+        <v>668.5999755859375</v>
       </c>
       <c r="D248" t="n">
-        <v>646.2000122070312</v>
+        <v>649.219970703125</v>
       </c>
       <c r="E248" t="n">
-        <v>648.030029296875</v>
+        <v>665.5999755859375</v>
       </c>
       <c r="F248" t="n">
-        <v>16925000</v>
+        <v>19332300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B249" t="n">
-        <v>657.8300170898438</v>
+        <v>659.2999877929688</v>
       </c>
       <c r="C249" t="n">
-        <v>668.5999755859375</v>
+        <v>678.8699951171875</v>
       </c>
       <c r="D249" t="n">
-        <v>649.219970703125</v>
+        <v>656.2000122070312</v>
       </c>
       <c r="E249" t="n">
-        <v>665.5999755859375</v>
+        <v>670.239990234375</v>
       </c>
       <c r="F249" t="n">
-        <v>19332300</v>
+        <v>19502800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B250" t="n">
-        <v>659.2999877929688</v>
+        <v>679.9099731445312</v>
       </c>
       <c r="C250" t="n">
-        <v>678.8699951171875</v>
+        <v>685.3099975585938</v>
       </c>
       <c r="D250" t="n">
-        <v>656.2000122070312</v>
+        <v>671.9099731445312</v>
       </c>
       <c r="E250" t="n">
-        <v>670.239990234375</v>
+        <v>673.3099975585938</v>
       </c>
       <c r="F250" t="n">
-        <v>19502800</v>
+        <v>17217800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B251" t="n">
-        <v>679.9099731445312</v>
+        <v>682.4400024414062</v>
       </c>
       <c r="C251" t="n">
-        <v>685.3099975585938</v>
+        <v>683.2000122070312</v>
       </c>
       <c r="D251" t="n">
-        <v>671.9099731445312</v>
+        <v>667.0499877929688</v>
       </c>
       <c r="E251" t="n">
-        <v>673.3099975585938</v>
+        <v>682.3099975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>17217800</v>
+        <v>15928000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B252" t="n">
-        <v>682.4400024414062</v>
+        <v>688.6199951171875</v>
       </c>
       <c r="C252" t="n">
-        <v>683.2000122070312</v>
+        <v>690.1500244140625</v>
       </c>
       <c r="D252" t="n">
-        <v>667.0499877929688</v>
+        <v>660.7999877929688</v>
       </c>
       <c r="E252" t="n">
-        <v>682.3099975585938</v>
+        <v>665.75</v>
       </c>
       <c r="F252" t="n">
-        <v>15888400</v>
+        <v>27548000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>665.75</v>
+      </c>
+      <c r="D2" t="n">
         <v>682.3099999999999</v>
       </c>
-      <c r="D2" t="n">
-        <v>673.3099999999999</v>
-      </c>
       <c r="E2" t="n">
-        <v>682.4400000000001</v>
+        <v>686.8200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>683.2</v>
+        <v>690.15</v>
       </c>
       <c r="G2" t="n">
-        <v>667.05</v>
+        <v>660.8</v>
       </c>
       <c r="H2" t="n">
-        <v>15740199</v>
+        <v>27394770</v>
       </c>
       <c r="I2" t="n">
-        <v>18199354</v>
+        <v>18162719</v>
       </c>
       <c r="J2" t="n">
-        <v>1738188914688</v>
+        <v>1696002211840</v>
       </c>
       <c r="K2" t="n">
-        <v>25.383556</v>
+        <v>25.704634</v>
       </c>
       <c r="L2" t="n">
-        <v>19.517067</v>
+        <v>19.043377</v>
       </c>
       <c r="M2" t="n">
-        <v>26.88</v>
+        <v>25.9</v>
       </c>
       <c r="N2" t="n">
-        <v>790.8</v>
+        <v>785.73</v>
       </c>
       <c r="O2" t="n">
         <v>520.26</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.6553845</v>
+        <v>6.493855</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1760247021568</v>
+        <v>1718060318720</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:15:32</t>
+          <t>2026-09-19 15:21:17</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45919</v>
+        <v>45925</v>
       </c>
       <c r="B2" t="n">
-        <v>783.8508708699721</v>
+        <v>750.9028646268723</v>
       </c>
       <c r="C2" t="n">
-        <v>788.2165669565625</v>
+        <v>754.2116481824468</v>
       </c>
       <c r="D2" t="n">
-        <v>766.6771780735046</v>
+        <v>742.0329280425029</v>
       </c>
       <c r="E2" t="n">
-        <v>775.837158203125</v>
+        <v>746.378173828125</v>
       </c>
       <c r="F2" t="n">
-        <v>23696800</v>
+        <v>10591100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,25 +495,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="B3" t="n">
-        <v>779.8218176027002</v>
+        <v>747.4645893513656</v>
       </c>
       <c r="C3" t="n">
-        <v>783.6917575585782</v>
+        <v>749.3880575951708</v>
       </c>
       <c r="D3" t="n">
-        <v>762.4868973227559</v>
+        <v>734.8573289461095</v>
       </c>
       <c r="E3" t="n">
-        <v>763.1751098632812</v>
+        <v>741.2357177734375</v>
       </c>
       <c r="F3" t="n">
-        <v>11706900</v>
+        <v>9696300</v>
       </c>
       <c r="G3" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45923</v>
+        <v>45929</v>
       </c>
       <c r="B4" t="n">
-        <v>767.254476840496</v>
+        <v>746.1888021735474</v>
       </c>
       <c r="C4" t="n">
-        <v>768.6009504341728</v>
+        <v>748.2418964072087</v>
       </c>
       <c r="D4" t="n">
-        <v>749.1216451610411</v>
+        <v>736.6512086302703</v>
       </c>
       <c r="E4" t="n">
-        <v>753.4404296875</v>
+        <v>740.8868408203125</v>
       </c>
       <c r="F4" t="n">
-        <v>10872600</v>
+        <v>9246800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="B5" t="n">
-        <v>755.5349916265823</v>
+        <v>739.7407284541446</v>
       </c>
       <c r="C5" t="n">
-        <v>759.1356124217834</v>
+        <v>740.4582652037509</v>
       </c>
       <c r="D5" t="n">
-        <v>750.5779133776451</v>
+        <v>723.8446373138524</v>
       </c>
       <c r="E5" t="n">
-        <v>758.686767578125</v>
+        <v>731.8973388671875</v>
       </c>
       <c r="F5" t="n">
-        <v>8828200</v>
+        <v>16226800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="B6" t="n">
-        <v>751.4954858581857</v>
+        <v>719.0508505989554</v>
       </c>
       <c r="C6" t="n">
-        <v>754.8068807440363</v>
+        <v>719.4096189488256</v>
       </c>
       <c r="D6" t="n">
-        <v>742.6185490172081</v>
+        <v>707.7990405756898</v>
       </c>
       <c r="E6" t="n">
-        <v>746.9672241210938</v>
+        <v>714.9149169921875</v>
       </c>
       <c r="F6" t="n">
-        <v>10591100</v>
+        <v>20419600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
       <c r="B7" t="n">
-        <v>748.0544659269957</v>
+        <v>720.1372426569798</v>
       </c>
       <c r="C7" t="n">
-        <v>749.9794521140951</v>
+        <v>725.309699629413</v>
       </c>
       <c r="D7" t="n">
-        <v>735.4372562509625</v>
+        <v>715.7122502133443</v>
       </c>
       <c r="E7" t="n">
-        <v>741.8206787109375</v>
+        <v>724.5921020507812</v>
       </c>
       <c r="F7" t="n">
-        <v>9696300</v>
+        <v>11415300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45929</v>
+        <v>45933</v>
       </c>
       <c r="B8" t="n">
-        <v>746.777703342028</v>
+        <v>727.1633750572937</v>
       </c>
       <c r="C8" t="n">
-        <v>748.8324179023273</v>
+        <v>728.5287386889415</v>
       </c>
       <c r="D8" t="n">
-        <v>737.2325826153279</v>
+        <v>707.7791166979599</v>
       </c>
       <c r="E8" t="n">
-        <v>741.4715576171875</v>
+        <v>708.1578369140625</v>
       </c>
       <c r="F8" t="n">
-        <v>9246800</v>
+        <v>16154300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45930</v>
+        <v>45936</v>
       </c>
       <c r="B9" t="n">
-        <v>740.3245554260684</v>
+        <v>702.8060849901855</v>
       </c>
       <c r="C9" t="n">
-        <v>741.0426584785586</v>
+        <v>714.456569002901</v>
       </c>
       <c r="D9" t="n">
-        <v>724.4159185837501</v>
+        <v>688.1757185011091</v>
       </c>
       <c r="E9" t="n">
-        <v>732.4749755859375</v>
+        <v>713.2406616210938</v>
       </c>
       <c r="F9" t="n">
-        <v>16226800</v>
+        <v>21654700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="B10" t="n">
-        <v>719.6183236513255</v>
+        <v>715.2936403041813</v>
       </c>
       <c r="C10" t="n">
-        <v>719.9773751402398</v>
+        <v>716.0710326272052</v>
       </c>
       <c r="D10" t="n">
-        <v>708.357633728991</v>
+        <v>703.3641353885179</v>
       </c>
       <c r="E10" t="n">
-        <v>715.4791259765625</v>
+        <v>710.6693725585938</v>
       </c>
       <c r="F10" t="n">
-        <v>20419600</v>
+        <v>12062900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45932</v>
+        <v>45938</v>
       </c>
       <c r="B11" t="n">
-        <v>720.7055653205383</v>
+        <v>711.0381561100638</v>
       </c>
       <c r="C11" t="n">
-        <v>725.8821043267139</v>
+        <v>717.2172088427283</v>
       </c>
       <c r="D11" t="n">
-        <v>716.2770807321521</v>
+        <v>705.4172078341599</v>
       </c>
       <c r="E11" t="n">
-        <v>725.1639404296875</v>
+        <v>715.413330078125</v>
       </c>
       <c r="F11" t="n">
-        <v>11415300</v>
+        <v>10790600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45933</v>
+        <v>45939</v>
       </c>
       <c r="B12" t="n">
-        <v>727.7372737109582</v>
+        <v>715.8518398810967</v>
       </c>
       <c r="C12" t="n">
-        <v>729.1037149276121</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="D12" t="n">
-        <v>708.3377167266436</v>
+        <v>710.0315555923428</v>
       </c>
       <c r="E12" t="n">
-        <v>708.7167358398438</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="F12" t="n">
-        <v>16154300</v>
+        <v>12717200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B13" t="n">
-        <v>703.3607165744016</v>
+        <v>728.4490335307075</v>
       </c>
       <c r="C13" t="n">
-        <v>715.0203947681905</v>
+        <v>732.784364410351</v>
       </c>
       <c r="D13" t="n">
-        <v>688.718804278428</v>
+        <v>702.1283419878271</v>
       </c>
       <c r="E13" t="n">
-        <v>713.8035278320312</v>
+        <v>702.9156494140625</v>
       </c>
       <c r="F13" t="n">
-        <v>21654700</v>
+        <v>16980100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="B14" t="n">
-        <v>715.8581417735932</v>
+        <v>710.5995481500918</v>
       </c>
       <c r="C14" t="n">
-        <v>716.6361476056489</v>
+        <v>717.5061127097006</v>
       </c>
       <c r="D14" t="n">
-        <v>703.9192222306009</v>
+        <v>705.2477072901073</v>
       </c>
       <c r="E14" t="n">
-        <v>711.230224609375</v>
+        <v>713.2804565429688</v>
       </c>
       <c r="F14" t="n">
-        <v>12062900</v>
+        <v>9251800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45938</v>
+        <v>45944</v>
       </c>
       <c r="B15" t="n">
-        <v>711.599278595462</v>
+        <v>705.3872795195668</v>
       </c>
       <c r="C15" t="n">
-        <v>717.7832075860277</v>
+        <v>713.1309705798873</v>
       </c>
       <c r="D15" t="n">
-        <v>705.9738944950672</v>
+        <v>696.9658337653736</v>
       </c>
       <c r="E15" t="n">
-        <v>715.9779052734375</v>
+        <v>706.2543334960938</v>
       </c>
       <c r="F15" t="n">
-        <v>10790600</v>
+        <v>8829800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45939</v>
+        <v>45945</v>
       </c>
       <c r="B16" t="n">
-        <v>716.4167658258609</v>
+        <v>714.6358727912688</v>
       </c>
       <c r="C16" t="n">
-        <v>731.6072387695312</v>
+        <v>721.4527759491865</v>
       </c>
       <c r="D16" t="n">
-        <v>710.5918883665408</v>
+        <v>707.1114088212217</v>
       </c>
       <c r="E16" t="n">
-        <v>731.6072387695312</v>
+        <v>715.1242065429688</v>
       </c>
       <c r="F16" t="n">
-        <v>12717200</v>
+        <v>10246800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="B17" t="n">
-        <v>729.0239332852144</v>
+        <v>715.1242355877501</v>
       </c>
       <c r="C17" t="n">
-        <v>733.3626856542741</v>
+        <v>723.0373960268438</v>
       </c>
       <c r="D17" t="n">
-        <v>702.6824691715568</v>
+        <v>701.5004654735715</v>
       </c>
       <c r="E17" t="n">
-        <v>703.4703979492188</v>
+        <v>709.6627807617188</v>
       </c>
       <c r="F17" t="n">
-        <v>16980100</v>
+        <v>9017000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45943</v>
+        <v>45947</v>
       </c>
       <c r="B18" t="n">
-        <v>711.1603595995662</v>
+        <v>704.6896374063629</v>
       </c>
       <c r="C18" t="n">
-        <v>718.072374881022</v>
+        <v>716.1108563950927</v>
       </c>
       <c r="D18" t="n">
-        <v>705.8042950194317</v>
+        <v>703.7328609179003</v>
       </c>
       <c r="E18" t="n">
-        <v>713.8433837890625</v>
+        <v>714.496337890625</v>
       </c>
       <c r="F18" t="n">
-        <v>9251800</v>
+        <v>12232400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="B19" t="n">
-        <v>705.9439682909708</v>
+        <v>718.7519624447335</v>
       </c>
       <c r="C19" t="n">
-        <v>713.6937706407739</v>
+        <v>731.2894517891565</v>
       </c>
       <c r="D19" t="n">
-        <v>697.5158763660478</v>
+        <v>717.7453670972193</v>
       </c>
       <c r="E19" t="n">
-        <v>706.8117065429688</v>
+        <v>729.69482421875</v>
       </c>
       <c r="F19" t="n">
-        <v>8829800</v>
+        <v>8900200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="B20" t="n">
-        <v>715.1998794771447</v>
+        <v>733.5318410857864</v>
       </c>
       <c r="C20" t="n">
-        <v>722.0221626881838</v>
+        <v>736.0034377690635</v>
       </c>
       <c r="D20" t="n">
-        <v>707.6694770310874</v>
+        <v>726.2863984755653</v>
       </c>
       <c r="E20" t="n">
-        <v>715.6885986328125</v>
+        <v>730.7911376953125</v>
       </c>
       <c r="F20" t="n">
-        <v>10246800</v>
+        <v>7647300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="B21" t="n">
-        <v>715.6886043056783</v>
+        <v>731.3492269695964</v>
       </c>
       <c r="C21" t="n">
-        <v>723.6080097298942</v>
+        <v>738.0962989037338</v>
       </c>
       <c r="D21" t="n">
-        <v>702.0540824517458</v>
+        <v>721.5823690736463</v>
       </c>
       <c r="E21" t="n">
-        <v>710.2228393554688</v>
+        <v>730.9306030273438</v>
       </c>
       <c r="F21" t="n">
-        <v>9017000</v>
+        <v>8734500</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="B22" t="n">
-        <v>705.2458014471516</v>
+        <v>732.2162614456487</v>
       </c>
       <c r="C22" t="n">
-        <v>716.6760344343375</v>
+        <v>739.900157838395</v>
       </c>
       <c r="D22" t="n">
-        <v>704.2882698394852</v>
+        <v>730.6216339604061</v>
       </c>
       <c r="E22" t="n">
-        <v>715.0602416992188</v>
+        <v>731.5186157226562</v>
       </c>
       <c r="F22" t="n">
-        <v>12232400</v>
+        <v>9856000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="B23" t="n">
-        <v>719.3191931642514</v>
+        <v>734.2991309259364</v>
       </c>
       <c r="C23" t="n">
-        <v>731.8665769499745</v>
+        <v>738.704232141329</v>
       </c>
       <c r="D23" t="n">
-        <v>718.3118034233538</v>
+        <v>728.6782441600997</v>
       </c>
       <c r="E23" t="n">
-        <v>730.2706909179688</v>
+        <v>735.8638305664062</v>
       </c>
       <c r="F23" t="n">
-        <v>8900200</v>
+        <v>9151300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="B24" t="n">
-        <v>734.1107251683979</v>
+        <v>747.195457385242</v>
       </c>
       <c r="C24" t="n">
-        <v>736.5842723709278</v>
+        <v>753.1951257515892</v>
       </c>
       <c r="D24" t="n">
-        <v>726.8595646449745</v>
+        <v>745.4813011827554</v>
       </c>
       <c r="E24" t="n">
-        <v>731.3678588867188</v>
+        <v>748.2817993164062</v>
       </c>
       <c r="F24" t="n">
-        <v>7647300</v>
+        <v>11321100</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45952</v>
+        <v>45958</v>
       </c>
       <c r="B25" t="n">
-        <v>731.9264006052239</v>
+        <v>750.0856988126538</v>
       </c>
       <c r="C25" t="n">
-        <v>738.6787972623451</v>
+        <v>755.8362124836232</v>
       </c>
       <c r="D25" t="n">
-        <v>722.1518348008319</v>
+        <v>742.9997491476457</v>
       </c>
       <c r="E25" t="n">
-        <v>731.5074462890625</v>
+        <v>748.8997192382812</v>
       </c>
       <c r="F25" t="n">
-        <v>8734500</v>
+        <v>12193800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45953</v>
+        <v>45959</v>
       </c>
       <c r="B26" t="n">
-        <v>732.7941435868839</v>
+        <v>752.1985111114485</v>
       </c>
       <c r="C26" t="n">
-        <v>740.4841042897723</v>
+        <v>756.5935760115584</v>
       </c>
       <c r="D26" t="n">
-        <v>731.1982575844598</v>
+        <v>739.9998990805568</v>
       </c>
       <c r="E26" t="n">
-        <v>732.095947265625</v>
+        <v>749.12890625</v>
       </c>
       <c r="F26" t="n">
-        <v>9856000</v>
+        <v>26818600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45954</v>
+        <v>45960</v>
       </c>
       <c r="B27" t="n">
-        <v>734.8786455644157</v>
+        <v>666.8879125335289</v>
       </c>
       <c r="C27" t="n">
-        <v>739.2872233202683</v>
+        <v>678.6579855089774</v>
       </c>
       <c r="D27" t="n">
-        <v>729.2533227506186</v>
+        <v>647.9720344844721</v>
       </c>
       <c r="E27" t="n">
-        <v>736.444580078125</v>
+        <v>664.2169189453125</v>
       </c>
       <c r="F27" t="n">
-        <v>9151300</v>
+        <v>88440100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="B28" t="n">
-        <v>747.7851152228061</v>
+        <v>672.2297387877188</v>
       </c>
       <c r="C28" t="n">
-        <v>753.7895182960361</v>
+        <v>672.6084590133829</v>
       </c>
       <c r="D28" t="n">
-        <v>746.069606274355</v>
+        <v>643.3875718813117</v>
       </c>
       <c r="E28" t="n">
-        <v>748.872314453125</v>
+        <v>646.1581420898438</v>
       </c>
       <c r="F28" t="n">
-        <v>11321100</v>
+        <v>56953200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45958</v>
+        <v>45964</v>
       </c>
       <c r="B29" t="n">
-        <v>750.6776381609803</v>
+        <v>653.7822839270266</v>
       </c>
       <c r="C29" t="n">
-        <v>756.4326899204912</v>
+        <v>657.1010433454932</v>
       </c>
       <c r="D29" t="n">
-        <v>743.5860965317024</v>
+        <v>634.0292814028221</v>
       </c>
       <c r="E29" t="n">
-        <v>749.49072265625</v>
+        <v>635.5541381835938</v>
       </c>
       <c r="F29" t="n">
-        <v>12193800</v>
+        <v>33003600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="B30" t="n">
-        <v>752.7921200604676</v>
+        <v>625.9168165443936</v>
       </c>
       <c r="C30" t="n">
-        <v>757.1906533932021</v>
+        <v>639.5705142822006</v>
       </c>
       <c r="D30" t="n">
-        <v>740.5838813084906</v>
+        <v>623.8937108241939</v>
       </c>
       <c r="E30" t="n">
-        <v>749.7200927734375</v>
+        <v>625.1992797851562</v>
       </c>
       <c r="F30" t="n">
-        <v>26818600</v>
+        <v>27356600</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45960</v>
+        <v>45966</v>
       </c>
       <c r="B31" t="n">
-        <v>667.414190282622</v>
+        <v>630.1724007040705</v>
       </c>
       <c r="C31" t="n">
-        <v>679.1935516668058</v>
+        <v>640.0588479681868</v>
       </c>
       <c r="D31" t="n">
-        <v>648.4833846789722</v>
+        <v>624.4218873891514</v>
       </c>
       <c r="E31" t="n">
-        <v>664.7410888671875</v>
+        <v>633.8001098632812</v>
       </c>
       <c r="F31" t="n">
-        <v>88440100</v>
+        <v>20219900</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45961</v>
+        <v>45967</v>
       </c>
       <c r="B32" t="n">
-        <v>672.7602632515434</v>
+        <v>633.7004019945108</v>
       </c>
       <c r="C32" t="n">
-        <v>673.1392823636344</v>
+        <v>633.8499192315176</v>
       </c>
       <c r="D32" t="n">
-        <v>643.8953340746643</v>
+        <v>615.9107705740217</v>
       </c>
       <c r="E32" t="n">
-        <v>646.6680908203125</v>
+        <v>616.8475952148438</v>
       </c>
       <c r="F32" t="n">
-        <v>56953200</v>
+        <v>23628800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="B33" t="n">
-        <v>654.2982567113449</v>
+        <v>614.4058308842617</v>
       </c>
       <c r="C33" t="n">
-        <v>657.619635334369</v>
+        <v>620.0267784116583</v>
       </c>
       <c r="D33" t="n">
-        <v>634.5296648817072</v>
+        <v>599.1675434782962</v>
       </c>
       <c r="E33" t="n">
-        <v>636.0557250976562</v>
+        <v>619.6082153320312</v>
       </c>
       <c r="F33" t="n">
-        <v>33003600</v>
+        <v>29946800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45965</v>
+        <v>45971</v>
       </c>
       <c r="B34" t="n">
-        <v>626.4107910285981</v>
+        <v>628.9566105977867</v>
       </c>
       <c r="C34" t="n">
-        <v>640.0752642850032</v>
+        <v>632.8533659763596</v>
       </c>
       <c r="D34" t="n">
-        <v>624.3860886703497</v>
+        <v>616.0204484619443</v>
       </c>
       <c r="E34" t="n">
-        <v>625.6926879882812</v>
+        <v>629.6243286132812</v>
       </c>
       <c r="F34" t="n">
-        <v>27356600</v>
+        <v>19245000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45966</v>
+        <v>45972</v>
       </c>
       <c r="B35" t="n">
-        <v>630.6697208898194</v>
+        <v>625.8769557835792</v>
       </c>
       <c r="C35" t="n">
-        <v>640.5639703518489</v>
+        <v>627.431679546322</v>
       </c>
       <c r="D35" t="n">
-        <v>624.9146693781357</v>
+        <v>617.29607772438</v>
       </c>
       <c r="E35" t="n">
-        <v>634.30029296875</v>
+        <v>624.9600830078125</v>
       </c>
       <c r="F35" t="n">
-        <v>20219900</v>
+        <v>13302200</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45967</v>
+        <v>45973</v>
       </c>
       <c r="B36" t="n">
-        <v>634.2005186436334</v>
+        <v>626.0065293511232</v>
       </c>
       <c r="C36" t="n">
-        <v>634.3501538797125</v>
+        <v>626.8636074098682</v>
       </c>
       <c r="D36" t="n">
-        <v>616.3968476378337</v>
+        <v>605.7153735895874</v>
       </c>
       <c r="E36" t="n">
-        <v>617.3344116210938</v>
+        <v>606.951171875</v>
       </c>
       <c r="F36" t="n">
-        <v>23628800</v>
+        <v>24493300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45968</v>
+        <v>45974</v>
       </c>
       <c r="B37" t="n">
-        <v>614.8907386759073</v>
+        <v>610.9974896015757</v>
       </c>
       <c r="C37" t="n">
-        <v>620.5161224262619</v>
+        <v>615.5620236854409</v>
       </c>
       <c r="D37" t="n">
-        <v>599.6404247494841</v>
+        <v>600.9615245048305</v>
       </c>
       <c r="E37" t="n">
-        <v>620.0972290039062</v>
+        <v>607.8282470703125</v>
       </c>
       <c r="F37" t="n">
-        <v>29946800</v>
+        <v>20973800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="B38" t="n">
-        <v>629.4529708548182</v>
+        <v>599.7555439005879</v>
       </c>
       <c r="C38" t="n">
-        <v>633.3528014765299</v>
+        <v>611.6053627125183</v>
       </c>
       <c r="D38" t="n">
-        <v>616.5065997528014</v>
+        <v>593.1878563697925</v>
       </c>
       <c r="E38" t="n">
-        <v>630.1212158203125</v>
+        <v>607.399658203125</v>
       </c>
       <c r="F38" t="n">
-        <v>19245000</v>
+        <v>20724100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="B39" t="n">
-        <v>626.3709044869131</v>
+        <v>606.9810562524968</v>
       </c>
       <c r="C39" t="n">
-        <v>627.9268552540688</v>
+        <v>609.6221219886945</v>
       </c>
       <c r="D39" t="n">
-        <v>617.7832543081277</v>
+        <v>593.3872138938384</v>
       </c>
       <c r="E39" t="n">
-        <v>625.4533081054688</v>
+        <v>599.974853515625</v>
       </c>
       <c r="F39" t="n">
-        <v>13302200</v>
+        <v>16501300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45973</v>
+        <v>45979</v>
       </c>
       <c r="B40" t="n">
-        <v>626.5005716840028</v>
+        <v>589.6000552799869</v>
       </c>
       <c r="C40" t="n">
-        <v>627.3583261459861</v>
+        <v>601.6192836786712</v>
       </c>
       <c r="D40" t="n">
-        <v>606.1934022078184</v>
+        <v>581.8065445386262</v>
       </c>
       <c r="E40" t="n">
-        <v>607.43017578125</v>
+        <v>595.6694946289062</v>
       </c>
       <c r="F40" t="n">
-        <v>24493300</v>
+        <v>25500600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="B41" t="n">
-        <v>611.4796659420805</v>
+        <v>591.7128101062766</v>
       </c>
       <c r="C41" t="n">
-        <v>616.0478021853295</v>
+        <v>593.3174134864839</v>
       </c>
       <c r="D41" t="n">
-        <v>601.4357808374693</v>
+        <v>579.2849960343485</v>
       </c>
       <c r="E41" t="n">
-        <v>608.3079223632812</v>
+        <v>588.3243408203125</v>
       </c>
       <c r="F41" t="n">
-        <v>20973800</v>
+        <v>24744700</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="B42" t="n">
-        <v>600.2288811530552</v>
+        <v>601.4597887996167</v>
       </c>
       <c r="C42" t="n">
-        <v>612.088052043071</v>
+        <v>604.6688739678727</v>
       </c>
       <c r="D42" t="n">
-        <v>593.6560102918138</v>
+        <v>581.3778841958236</v>
       </c>
       <c r="E42" t="n">
-        <v>607.8790283203125</v>
+        <v>587.1583251953125</v>
       </c>
       <c r="F42" t="n">
-        <v>20724100</v>
+        <v>20603000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="B43" t="n">
-        <v>607.4600964135232</v>
+        <v>586.5105272163902</v>
       </c>
       <c r="C43" t="n">
-        <v>610.1032465254069</v>
+        <v>596.0980011467227</v>
       </c>
       <c r="D43" t="n">
-        <v>593.855525554584</v>
+        <v>579.8929596850738</v>
       </c>
       <c r="E43" t="n">
-        <v>600.4483642578125</v>
+        <v>592.2410888671875</v>
       </c>
       <c r="F43" t="n">
-        <v>16501300</v>
+        <v>21052600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45979</v>
+        <v>45985</v>
       </c>
       <c r="B44" t="n">
-        <v>590.065358149623</v>
+        <v>596.6959057641074</v>
       </c>
       <c r="C44" t="n">
-        <v>602.0940719298206</v>
+        <v>614.6151629725317</v>
       </c>
       <c r="D44" t="n">
-        <v>582.2656968950795</v>
+        <v>595.609624740878</v>
       </c>
       <c r="E44" t="n">
-        <v>596.1395874023438</v>
+        <v>610.9774780273438</v>
       </c>
       <c r="F44" t="n">
-        <v>25500600</v>
+        <v>23554900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45980</v>
+        <v>45986</v>
       </c>
       <c r="B45" t="n">
-        <v>592.1797786556917</v>
+        <v>621.8904932046078</v>
       </c>
       <c r="C45" t="n">
-        <v>593.7856483585136</v>
+        <v>634.8963639496133</v>
       </c>
       <c r="D45" t="n">
-        <v>579.7421567881397</v>
+        <v>616.209750572071</v>
       </c>
       <c r="E45" t="n">
-        <v>588.7886352539062</v>
+        <v>634.0691528320312</v>
       </c>
       <c r="F45" t="n">
-        <v>24744700</v>
+        <v>25213000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="B46" t="n">
-        <v>601.9344542639864</v>
+        <v>635.5342418532664</v>
       </c>
       <c r="C46" t="n">
-        <v>605.1460720070379</v>
+        <v>636.2019598341516</v>
       </c>
       <c r="D46" t="n">
-        <v>581.8367012414765</v>
+        <v>629.4947305871518</v>
       </c>
       <c r="E46" t="n">
-        <v>587.6217041015625</v>
+        <v>631.468017578125</v>
       </c>
       <c r="F46" t="n">
-        <v>20603000</v>
+        <v>15209500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B47" t="n">
-        <v>586.9734117815261</v>
+        <v>633.9296546389559</v>
       </c>
       <c r="C47" t="n">
-        <v>596.5684523172222</v>
+        <v>645.8591590880771</v>
       </c>
       <c r="D47" t="n">
-        <v>580.3506215479276</v>
+        <v>633.3515983825566</v>
       </c>
       <c r="E47" t="n">
-        <v>592.70849609375</v>
+        <v>645.759521484375</v>
       </c>
       <c r="F47" t="n">
-        <v>21052600</v>
+        <v>11033200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="B48" t="n">
-        <v>597.1668126146857</v>
+        <v>637.3878853503733</v>
       </c>
       <c r="C48" t="n">
-        <v>615.1002115339802</v>
+        <v>643.1383983949365</v>
       </c>
       <c r="D48" t="n">
-        <v>596.0796743085915</v>
+        <v>635.6039586340122</v>
       </c>
       <c r="E48" t="n">
-        <v>611.4596557617188</v>
+        <v>638.7034301757812</v>
       </c>
       <c r="F48" t="n">
-        <v>23554900</v>
+        <v>13029900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="B49" t="n">
-        <v>622.3813086708644</v>
+        <v>640.1685571180485</v>
       </c>
       <c r="C49" t="n">
-        <v>635.3974440566444</v>
+        <v>645.6798309839221</v>
       </c>
       <c r="D49" t="n">
-        <v>616.696082618217</v>
+        <v>635.9129726489192</v>
       </c>
       <c r="E49" t="n">
-        <v>634.569580078125</v>
+        <v>644.9124145507812</v>
       </c>
       <c r="F49" t="n">
-        <v>25213000</v>
+        <v>11640900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B50" t="n">
-        <v>636.0358029520913</v>
+        <v>642.2315425173783</v>
       </c>
       <c r="C50" t="n">
-        <v>636.7040478933542</v>
+        <v>646.6565355118391</v>
       </c>
       <c r="D50" t="n">
-        <v>629.9915253276793</v>
+        <v>635.394747375177</v>
       </c>
       <c r="E50" t="n">
-        <v>631.9663696289062</v>
+        <v>637.4378051757812</v>
       </c>
       <c r="F50" t="n">
-        <v>15209500</v>
+        <v>11134300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="B51" t="n">
-        <v>634.4299618769652</v>
+        <v>673.7146932031604</v>
       </c>
       <c r="C51" t="n">
-        <v>646.3688812783262</v>
+        <v>673.8143308084973</v>
       </c>
       <c r="D51" t="n">
-        <v>633.8514494094911</v>
+        <v>657.8186021075292</v>
       </c>
       <c r="E51" t="n">
-        <v>646.2691650390625</v>
+        <v>659.2936401367188</v>
       </c>
       <c r="F51" t="n">
-        <v>11033200</v>
+        <v>29874600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="B52" t="n">
-        <v>637.8909364271796</v>
+        <v>661.7552947151958</v>
       </c>
       <c r="C52" t="n">
-        <v>643.6459879981971</v>
+        <v>672.4091587454953</v>
       </c>
       <c r="D52" t="n">
-        <v>636.1056017671217</v>
+        <v>660.1507520483126</v>
       </c>
       <c r="E52" t="n">
-        <v>639.20751953125</v>
+        <v>671.1434326171875</v>
       </c>
       <c r="F52" t="n">
-        <v>13029900</v>
+        <v>21207900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="B53" t="n">
-        <v>640.6737853801045</v>
+        <v>667.0772284693074</v>
       </c>
       <c r="C53" t="n">
-        <v>646.1894088056151</v>
+        <v>674.4223082782987</v>
       </c>
       <c r="D53" t="n">
-        <v>636.4148423556049</v>
+        <v>662.8216443414645</v>
       </c>
       <c r="E53" t="n">
-        <v>645.42138671875</v>
+        <v>664.5457763671875</v>
       </c>
       <c r="F53" t="n">
-        <v>11640900</v>
+        <v>13161000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="B54" t="n">
-        <v>642.7383773862279</v>
+        <v>661.5260500954003</v>
       </c>
       <c r="C54" t="n">
-        <v>647.1668624868771</v>
+        <v>662.2336109084633</v>
       </c>
       <c r="D54" t="n">
-        <v>635.8961867971512</v>
+        <v>651.1313175008097</v>
       </c>
       <c r="E54" t="n">
-        <v>637.9408569335938</v>
+        <v>654.7390747070312</v>
       </c>
       <c r="F54" t="n">
-        <v>11134300</v>
+        <v>12997100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="B55" t="n">
-        <v>674.2463992276428</v>
+        <v>647.7527447265774</v>
       </c>
       <c r="C55" t="n">
-        <v>674.3461154685141</v>
+        <v>652.2973264314004</v>
       </c>
       <c r="D55" t="n">
-        <v>658.3377626918029</v>
+        <v>641.2249002906431</v>
       </c>
       <c r="E55" t="n">
-        <v>659.81396484375</v>
+        <v>647.93212890625</v>
       </c>
       <c r="F55" t="n">
-        <v>29874600</v>
+        <v>16910900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="B56" t="n">
-        <v>662.2775487290173</v>
+        <v>641.1152803360264</v>
       </c>
       <c r="C56" t="n">
-        <v>672.9398207362489</v>
+        <v>653.0647981949571</v>
       </c>
       <c r="D56" t="n">
-        <v>660.6717397649775</v>
+        <v>638.6337077300913</v>
       </c>
       <c r="E56" t="n">
-        <v>671.673095703125</v>
+        <v>650.5034790039062</v>
       </c>
       <c r="F56" t="n">
-        <v>21207900</v>
+        <v>13056700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="B57" t="n">
-        <v>667.603701448277</v>
+        <v>647.603240055161</v>
       </c>
       <c r="C57" t="n">
-        <v>674.9545781663558</v>
+        <v>708.5963563082138</v>
       </c>
       <c r="D57" t="n">
-        <v>663.344758713728</v>
+        <v>636.4510671197735</v>
       </c>
       <c r="E57" t="n">
-        <v>665.0702514648438</v>
+        <v>642.0520629882812</v>
       </c>
       <c r="F57" t="n">
-        <v>13161000</v>
+        <v>14016900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,25 +1925,25 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="B58" t="n">
-        <v>662.0481300460407</v>
+        <v>644.0420011784053</v>
       </c>
       <c r="C58" t="n">
-        <v>662.7562492699393</v>
+        <v>651.3232442601446</v>
       </c>
       <c r="D58" t="n">
-        <v>651.6451938720459</v>
+        <v>637.0599755890928</v>
       </c>
       <c r="E58" t="n">
-        <v>655.2557983398438</v>
+        <v>645.8473510742188</v>
       </c>
       <c r="F58" t="n">
-        <v>12997100</v>
+        <v>15549100</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="B59" t="n">
-        <v>648.2639556943986</v>
+        <v>641.8476117575357</v>
       </c>
       <c r="C59" t="n">
-        <v>652.8121240146866</v>
+        <v>660.8386986647098</v>
       </c>
       <c r="D59" t="n">
-        <v>641.730959438269</v>
+        <v>641.5483942773906</v>
       </c>
       <c r="E59" t="n">
-        <v>648.4434814453125</v>
+        <v>655.4625854492188</v>
       </c>
       <c r="F59" t="n">
-        <v>16910900</v>
+        <v>14309100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="B60" t="n">
-        <v>641.6212380225077</v>
+        <v>653.9265104909302</v>
       </c>
       <c r="C60" t="n">
-        <v>653.5801862453618</v>
+        <v>659.5320745885969</v>
       </c>
       <c r="D60" t="n">
-        <v>639.1377070000864</v>
+        <v>647.5329968709444</v>
       </c>
       <c r="E60" t="n">
-        <v>651.016845703125</v>
+        <v>647.8322143554688</v>
       </c>
       <c r="F60" t="n">
-        <v>13056700</v>
+        <v>15598500</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46003</v>
+        <v>46009</v>
       </c>
       <c r="B61" t="n">
-        <v>648.1143349664432</v>
+        <v>655.3429659472675</v>
       </c>
       <c r="C61" t="n">
-        <v>709.1555875928369</v>
+        <v>668.8381931582612</v>
       </c>
       <c r="D61" t="n">
-        <v>636.9533606253732</v>
+        <v>654.774422237226</v>
       </c>
       <c r="E61" t="n">
-        <v>642.5587768554688</v>
+        <v>662.743896484375</v>
       </c>
       <c r="F61" t="n">
-        <v>14016900</v>
+        <v>20260300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,25 +2029,25 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="B62" t="n">
-        <v>644.5502809809109</v>
+        <v>664.7087499822148</v>
       </c>
       <c r="C62" t="n">
-        <v>651.8372704406642</v>
+        <v>669.2770065062657</v>
       </c>
       <c r="D62" t="n">
-        <v>637.5627451568915</v>
+        <v>656.4899183910027</v>
       </c>
       <c r="E62" t="n">
-        <v>646.3570556640625</v>
+        <v>657.0784301757812</v>
       </c>
       <c r="F62" t="n">
-        <v>15549100</v>
+        <v>49977100</v>
       </c>
       <c r="G62" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="B63" t="n">
-        <v>642.3541401459643</v>
+        <v>659.9510307809619</v>
       </c>
       <c r="C63" t="n">
-        <v>661.3602142938313</v>
+        <v>671.850389464676</v>
       </c>
       <c r="D63" t="n">
-        <v>642.054686531657</v>
+        <v>654.9638698467097</v>
       </c>
       <c r="E63" t="n">
-        <v>655.9798583984375</v>
+        <v>659.8013916015625</v>
       </c>
       <c r="F63" t="n">
-        <v>14309100</v>
+        <v>15659400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="B64" t="n">
-        <v>654.4426118233187</v>
+        <v>658.3550860644432</v>
       </c>
       <c r="C64" t="n">
-        <v>660.0526000253047</v>
+        <v>664.2898196014329</v>
       </c>
       <c r="D64" t="n">
-        <v>648.0440522221027</v>
+        <v>656.5597203493141</v>
       </c>
       <c r="E64" t="n">
-        <v>648.343505859375</v>
+        <v>663.2325439453125</v>
       </c>
       <c r="F64" t="n">
-        <v>15598500</v>
+        <v>8486800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46009</v>
+        <v>46015</v>
       </c>
       <c r="B65" t="n">
-        <v>655.8601356908653</v>
+        <v>660.8288686174008</v>
       </c>
       <c r="C65" t="n">
-        <v>669.366012780715</v>
+        <v>666.4643247360839</v>
       </c>
       <c r="D65" t="n">
-        <v>655.2911433094866</v>
+        <v>660.4996989036335</v>
       </c>
       <c r="E65" t="n">
-        <v>663.2669067382812</v>
+        <v>665.8359375</v>
       </c>
       <c r="F65" t="n">
-        <v>20260300</v>
+        <v>5627500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c r="B66" t="n">
-        <v>665.2333263832898</v>
+        <v>666.3445631389869</v>
       </c>
       <c r="C66" t="n">
-        <v>669.8051880946751</v>
+        <v>667.2322924211887</v>
       </c>
       <c r="D66" t="n">
-        <v>657.0080086354003</v>
+        <v>659.6218797502219</v>
       </c>
       <c r="E66" t="n">
-        <v>657.5969848632812</v>
+        <v>661.5867919921875</v>
       </c>
       <c r="F66" t="n">
-        <v>49977100</v>
+        <v>7133800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="B67" t="n">
-        <v>660.4718397886508</v>
+        <v>656.3204105957403</v>
       </c>
       <c r="C67" t="n">
-        <v>672.380589007267</v>
+        <v>658.5546491157273</v>
       </c>
       <c r="D67" t="n">
-        <v>655.4807431709672</v>
+        <v>652.7097106878265</v>
       </c>
       <c r="E67" t="n">
-        <v>660.3220825195312</v>
+        <v>656.9986572265625</v>
       </c>
       <c r="F67" t="n">
-        <v>15659400</v>
+        <v>8506500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="B68" t="n">
-        <v>658.8746741689592</v>
+        <v>656.9986226731097</v>
       </c>
       <c r="C68" t="n">
-        <v>664.8140915262984</v>
+        <v>670.4938487731155</v>
       </c>
       <c r="D68" t="n">
-        <v>657.0778915122911</v>
+        <v>656.1508296487782</v>
       </c>
       <c r="E68" t="n">
-        <v>663.7559814453125</v>
+        <v>664.239990234375</v>
       </c>
       <c r="F68" t="n">
-        <v>8486800</v>
+        <v>9187500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B69" t="n">
-        <v>661.3503688947783</v>
+        <v>663.0430880640301</v>
       </c>
       <c r="C69" t="n">
-        <v>666.9902722948509</v>
+        <v>663.2924461264837</v>
       </c>
       <c r="D69" t="n">
-        <v>661.0209394131572</v>
+        <v>657.7467252526537</v>
       </c>
       <c r="E69" t="n">
-        <v>666.3613891601562</v>
+        <v>658.3950805664062</v>
       </c>
       <c r="F69" t="n">
-        <v>5627500</v>
+        <v>7940400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46017</v>
+        <v>46024</v>
       </c>
       <c r="B70" t="n">
-        <v>666.8704124858896</v>
+        <v>661.0283027009447</v>
       </c>
       <c r="C70" t="n">
-        <v>667.7588423243637</v>
+        <v>662.6840744459444</v>
       </c>
       <c r="D70" t="n">
-        <v>660.1424238558649</v>
+        <v>641.8476986467276</v>
       </c>
       <c r="E70" t="n">
-        <v>662.10888671875</v>
+        <v>648.7399291992188</v>
       </c>
       <c r="F70" t="n">
-        <v>7133800</v>
+        <v>13726500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="B71" t="n">
-        <v>656.8383689858442</v>
+        <v>649.3383972038786</v>
       </c>
       <c r="C71" t="n">
-        <v>659.0743707339258</v>
+        <v>662.8336242718107</v>
       </c>
       <c r="D71" t="n">
-        <v>653.2248195668056</v>
+        <v>646.086758236235</v>
       </c>
       <c r="E71" t="n">
-        <v>657.5171508789062</v>
+        <v>657.098388671875</v>
       </c>
       <c r="F71" t="n">
-        <v>8506500</v>
+        <v>12213700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="B72" t="n">
-        <v>657.5171386037911</v>
+        <v>657.8764143393763</v>
       </c>
       <c r="C72" t="n">
-        <v>671.0230153954109</v>
+        <v>663.8111485640529</v>
       </c>
       <c r="D72" t="n">
-        <v>656.6686764849229</v>
+        <v>650.2261258196658</v>
       </c>
       <c r="E72" t="n">
-        <v>664.7642211914062</v>
+        <v>658.9237060546875</v>
       </c>
       <c r="F72" t="n">
-        <v>9187500</v>
+        <v>11074400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B73" t="n">
-        <v>663.5663484641349</v>
+        <v>653.9565196013041</v>
       </c>
       <c r="C73" t="n">
-        <v>663.8159033150052</v>
+        <v>657.4575166710536</v>
       </c>
       <c r="D73" t="n">
-        <v>658.2658058687088</v>
+        <v>643.1543108814861</v>
       </c>
       <c r="E73" t="n">
-        <v>658.9146728515625</v>
+        <v>647.0243530273438</v>
       </c>
       <c r="F73" t="n">
-        <v>7940400</v>
+        <v>12846300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="B74" t="n">
-        <v>661.5499631466852</v>
+        <v>644.2215315163064</v>
       </c>
       <c r="C74" t="n">
-        <v>663.2070415689074</v>
+        <v>645.4383696113561</v>
       </c>
       <c r="D74" t="n">
-        <v>642.3542224297569</v>
+        <v>634.0875860000896</v>
       </c>
       <c r="E74" t="n">
-        <v>649.2518920898438</v>
+        <v>644.4010620117188</v>
       </c>
       <c r="F74" t="n">
-        <v>13726500</v>
+        <v>11921700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B75" t="n">
-        <v>649.8508280292294</v>
+        <v>643.7826283039087</v>
       </c>
       <c r="C75" t="n">
-        <v>663.3567049684374</v>
+        <v>653.2682180705046</v>
       </c>
       <c r="D75" t="n">
-        <v>646.5966230035071</v>
+        <v>641.1992521727667</v>
       </c>
       <c r="E75" t="n">
-        <v>657.616943359375</v>
+        <v>651.383056640625</v>
       </c>
       <c r="F75" t="n">
-        <v>12213700</v>
+        <v>11634900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46028</v>
+        <v>46034</v>
       </c>
       <c r="B76" t="n">
-        <v>658.3956073528642</v>
+        <v>650.8545379312607</v>
       </c>
       <c r="C76" t="n">
-        <v>664.3350252422523</v>
+        <v>652.2907820220081</v>
       </c>
       <c r="D76" t="n">
-        <v>650.7392812609531</v>
+        <v>639.5835040655014</v>
       </c>
       <c r="E76" t="n">
-        <v>659.4437255859375</v>
+        <v>640.3215942382812</v>
       </c>
       <c r="F76" t="n">
-        <v>11074400</v>
+        <v>14797200</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B77" t="n">
-        <v>654.4726104611178</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="C77" t="n">
-        <v>657.9763704555172</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="D77" t="n">
-        <v>643.6618768302103</v>
+        <v>622.4974409136</v>
       </c>
       <c r="E77" t="n">
-        <v>647.5349731445312</v>
+        <v>629.4695434570312</v>
       </c>
       <c r="F77" t="n">
-        <v>12846300</v>
+        <v>18030400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="B78" t="n">
-        <v>644.7299347572825</v>
+        <v>624.8913007155408</v>
       </c>
       <c r="C78" t="n">
-        <v>645.9477331499952</v>
+        <v>626.836305766559</v>
       </c>
       <c r="D78" t="n">
-        <v>634.5879917891143</v>
+        <v>613.2412994138377</v>
       </c>
       <c r="E78" t="n">
-        <v>644.9096069335938</v>
+        <v>613.9395141601562</v>
       </c>
       <c r="F78" t="n">
-        <v>11921700</v>
+        <v>15527900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="B79" t="n">
-        <v>644.2906685217797</v>
+        <v>616.8918824768537</v>
       </c>
       <c r="C79" t="n">
-        <v>653.7837438291153</v>
+        <v>622.567274451088</v>
       </c>
       <c r="D79" t="n">
-        <v>641.7052537227476</v>
+        <v>612.6527953870184</v>
       </c>
       <c r="E79" t="n">
-        <v>651.8970947265625</v>
+        <v>619.2059326171875</v>
       </c>
       <c r="F79" t="n">
-        <v>11634900</v>
+        <v>13076100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="B80" t="n">
-        <v>651.3681600668523</v>
+        <v>622.5772500418334</v>
       </c>
       <c r="C80" t="n">
-        <v>652.8055375702352</v>
+        <v>627.4646923832119</v>
       </c>
       <c r="D80" t="n">
-        <v>640.0882316599212</v>
+        <v>618.4878021974878</v>
       </c>
       <c r="E80" t="n">
-        <v>640.826904296875</v>
+        <v>618.6573486328125</v>
       </c>
       <c r="F80" t="n">
-        <v>14797200</v>
+        <v>17012500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B81" t="n">
-        <v>641.1263941859123</v>
+        <v>606.3191417499893</v>
       </c>
       <c r="C81" t="n">
-        <v>641.1263941859123</v>
+        <v>609.8301228712422</v>
       </c>
       <c r="D81" t="n">
-        <v>622.9887038024194</v>
+        <v>598.4593704807342</v>
       </c>
       <c r="E81" t="n">
-        <v>629.96630859375</v>
+        <v>602.5687866210938</v>
       </c>
       <c r="F81" t="n">
-        <v>18030400</v>
+        <v>15169600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B82" t="n">
-        <v>625.3844405077801</v>
+        <v>605.1820479992876</v>
       </c>
       <c r="C82" t="n">
-        <v>627.3309804807691</v>
+        <v>616.6824713366042</v>
       </c>
       <c r="D82" t="n">
-        <v>613.7252454803604</v>
+        <v>598.5391758430108</v>
       </c>
       <c r="E82" t="n">
-        <v>614.4240112304688</v>
+        <v>611.3861083984375</v>
       </c>
       <c r="F82" t="n">
-        <v>15527900</v>
+        <v>14494700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B83" t="n">
-        <v>617.378703801015</v>
+        <v>627.7339506004921</v>
       </c>
       <c r="C83" t="n">
-        <v>623.0585745209008</v>
+        <v>658.8738165275513</v>
       </c>
       <c r="D83" t="n">
-        <v>613.1362714280776</v>
+        <v>624.9411525277235</v>
       </c>
       <c r="E83" t="n">
-        <v>619.694580078125</v>
+        <v>645.967041015625</v>
       </c>
       <c r="F83" t="n">
-        <v>13076100</v>
+        <v>21394700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B84" t="n">
-        <v>623.0685636897582</v>
+        <v>643.1144139511335</v>
       </c>
       <c r="C84" t="n">
-        <v>627.9598630097294</v>
+        <v>664.7786132883346</v>
       </c>
       <c r="D84" t="n">
-        <v>618.9758886129073</v>
+        <v>642.7952283244125</v>
       </c>
       <c r="E84" t="n">
-        <v>619.1455688476562</v>
+        <v>657.0684814453125</v>
       </c>
       <c r="F84" t="n">
-        <v>17012500</v>
+        <v>22797700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B85" t="n">
-        <v>606.7976262932837</v>
+        <v>663.4221291072672</v>
       </c>
       <c r="C85" t="n">
-        <v>610.3113781504126</v>
+        <v>673.5460909761269</v>
       </c>
       <c r="D85" t="n">
-        <v>598.9316523845154</v>
+        <v>659.5919624126628</v>
       </c>
       <c r="E85" t="n">
-        <v>603.0443115234375</v>
+        <v>670.633544921875</v>
       </c>
       <c r="F85" t="n">
-        <v>15169600</v>
+        <v>16327400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="B86" t="n">
-        <v>605.659634898437</v>
+        <v>672.8578395915863</v>
       </c>
       <c r="C86" t="n">
-        <v>617.169133937088</v>
+        <v>675.0820939991542</v>
       </c>
       <c r="D86" t="n">
-        <v>599.0115204374271</v>
+        <v>662.9532839044604</v>
       </c>
       <c r="E86" t="n">
-        <v>611.8685913085938</v>
+        <v>671.241943359375</v>
       </c>
       <c r="F86" t="n">
-        <v>14494700</v>
+        <v>13297400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B87" t="n">
-        <v>628.2293275614567</v>
+        <v>672.768020673078</v>
       </c>
       <c r="C87" t="n">
-        <v>659.3937675491238</v>
+        <v>675.9398477720257</v>
       </c>
       <c r="D87" t="n">
-        <v>625.4343255489129</v>
+        <v>664.3895658196245</v>
       </c>
       <c r="E87" t="n">
-        <v>646.476806640625</v>
+        <v>667.0128173828125</v>
       </c>
       <c r="F87" t="n">
-        <v>21394700</v>
+        <v>25709600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="B88" t="n">
-        <v>643.6219561683764</v>
+        <v>735.536439340887</v>
       </c>
       <c r="C88" t="n">
-        <v>665.3032527677875</v>
+        <v>742.0895763731422</v>
       </c>
       <c r="D88" t="n">
-        <v>643.3025186421843</v>
+        <v>710.7203206800697</v>
       </c>
       <c r="E88" t="n">
-        <v>657.5870361328125</v>
+        <v>736.4141845703125</v>
       </c>
       <c r="F88" t="n">
-        <v>22797700</v>
+        <v>59852900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B89" t="n">
-        <v>663.9456740004919</v>
+        <v>725.6319102189462</v>
       </c>
       <c r="C89" t="n">
-        <v>674.0776252750454</v>
+        <v>730.2899014488934</v>
       </c>
       <c r="D89" t="n">
-        <v>660.1124846991261</v>
+        <v>711.7576553956329</v>
       </c>
       <c r="E89" t="n">
-        <v>671.1627807617188</v>
+        <v>714.66015625</v>
       </c>
       <c r="F89" t="n">
-        <v>16327400</v>
+        <v>23744600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B90" t="n">
-        <v>673.3888389297905</v>
+        <v>712.7649799285471</v>
       </c>
       <c r="C90" t="n">
-        <v>675.6148486525956</v>
+        <v>719.4477874144414</v>
       </c>
       <c r="D90" t="n">
-        <v>663.4764668627315</v>
+        <v>701.7134756957726</v>
       </c>
       <c r="E90" t="n">
-        <v>671.7716674804688</v>
+        <v>704.5960083007812</v>
       </c>
       <c r="F90" t="n">
-        <v>13297400</v>
+        <v>14365200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="B91" t="n">
-        <v>673.2989910894674</v>
+        <v>705.5535728195721</v>
       </c>
       <c r="C91" t="n">
-        <v>676.4733214975852</v>
+        <v>715.1588492636382</v>
       </c>
       <c r="D91" t="n">
-        <v>664.9139236867763</v>
+        <v>684.6473731061755</v>
       </c>
       <c r="E91" t="n">
-        <v>667.5392456054688</v>
+        <v>689.923828125</v>
       </c>
       <c r="F91" t="n">
-        <v>25709600</v>
+        <v>13760700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="B92" t="n">
-        <v>736.1169233837337</v>
+        <v>685.964025393825</v>
       </c>
       <c r="C92" t="n">
-        <v>742.6752321400184</v>
+        <v>687.0612373376343</v>
       </c>
       <c r="D92" t="n">
-        <v>711.2812198864386</v>
+        <v>665.7461161570209</v>
       </c>
       <c r="E92" t="n">
-        <v>736.995361328125</v>
+        <v>667.2721557617188</v>
       </c>
       <c r="F92" t="n">
-        <v>59852900</v>
+        <v>16882800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="B93" t="n">
-        <v>726.2045952530067</v>
+        <v>661.876033741038</v>
       </c>
       <c r="C93" t="n">
-        <v>730.8662626744616</v>
+        <v>679.7500005691794</v>
       </c>
       <c r="D93" t="n">
-        <v>712.3193905555435</v>
+        <v>651.8219007658969</v>
       </c>
       <c r="E93" t="n">
-        <v>715.2241821289062</v>
+        <v>668.489013671875</v>
       </c>
       <c r="F93" t="n">
-        <v>23744600</v>
+        <v>17131800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="B94" t="n">
-        <v>713.3275184694113</v>
+        <v>663.7811558190369</v>
       </c>
       <c r="C94" t="n">
-        <v>720.0156002559207</v>
+        <v>670.2644652243433</v>
       </c>
       <c r="D94" t="n">
-        <v>702.2672920108814</v>
+        <v>644.8399277739295</v>
       </c>
       <c r="E94" t="n">
-        <v>705.152099609375</v>
+        <v>659.7615356445312</v>
       </c>
       <c r="F94" t="n">
-        <v>14365200</v>
+        <v>18159300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46056</v>
+        <v>46062</v>
       </c>
       <c r="B95" t="n">
-        <v>706.1104025957663</v>
+        <v>661.4770916291903</v>
       </c>
       <c r="C95" t="n">
-        <v>715.7232596178901</v>
+        <v>681.5554070660584</v>
       </c>
       <c r="D95" t="n">
-        <v>685.1877035052055</v>
+        <v>657.0884263930592</v>
       </c>
       <c r="E95" t="n">
-        <v>690.4683227539062</v>
+        <v>675.4810180664062</v>
       </c>
       <c r="F95" t="n">
-        <v>13760700</v>
+        <v>14837500</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="B96" t="n">
-        <v>686.5053883494637</v>
+        <v>675.8600805746455</v>
       </c>
       <c r="C96" t="n">
-        <v>687.603466213174</v>
+        <v>678.9022976953746</v>
       </c>
       <c r="D96" t="n">
-        <v>666.2715231343633</v>
+        <v>668.0701369952135</v>
       </c>
       <c r="E96" t="n">
-        <v>667.7987670898438</v>
+        <v>668.9977416992188</v>
       </c>
       <c r="F96" t="n">
-        <v>16882800</v>
+        <v>10455800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="B97" t="n">
-        <v>662.3984025060512</v>
+        <v>672.2693241407737</v>
       </c>
       <c r="C97" t="n">
-        <v>680.2864759062725</v>
+        <v>677.5258114827353</v>
       </c>
       <c r="D97" t="n">
-        <v>652.3363345630947</v>
+        <v>655.4126950742984</v>
       </c>
       <c r="E97" t="n">
-        <v>669.0166015625</v>
+        <v>666.9729614257812</v>
       </c>
       <c r="F97" t="n">
-        <v>17131800</v>
+        <v>14323800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="B98" t="n">
-        <v>664.3050190645899</v>
+        <v>668.2496249159107</v>
       </c>
       <c r="C98" t="n">
-        <v>670.7934451675868</v>
+        <v>674.2641703314905</v>
       </c>
       <c r="D98" t="n">
-        <v>645.3488423980709</v>
+        <v>643.6230822268304</v>
       </c>
       <c r="E98" t="n">
-        <v>660.2822265625</v>
+        <v>648.1414184570312</v>
       </c>
       <c r="F98" t="n">
-        <v>18159300</v>
+        <v>14960100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="B99" t="n">
-        <v>661.9991209626965</v>
+        <v>643.4435284294337</v>
       </c>
       <c r="C99" t="n">
-        <v>682.0932819515241</v>
+        <v>649.7572916993954</v>
       </c>
       <c r="D99" t="n">
-        <v>657.6069922476072</v>
+        <v>632.9405983581432</v>
       </c>
       <c r="E99" t="n">
-        <v>676.0140991210938</v>
+        <v>638.1272583007812</v>
       </c>
       <c r="F99" t="n">
-        <v>14837500</v>
+        <v>12336400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46063</v>
+        <v>46070</v>
       </c>
       <c r="B100" t="n">
-        <v>676.3934502400131</v>
+        <v>637.8578591323172</v>
       </c>
       <c r="C100" t="n">
-        <v>679.4380681924739</v>
+        <v>640.9498744421038</v>
       </c>
       <c r="D100" t="n">
-        <v>668.597359057372</v>
+        <v>627.1853229648948</v>
       </c>
       <c r="E100" t="n">
-        <v>669.5256958007812</v>
+        <v>637.6483764648438</v>
       </c>
       <c r="F100" t="n">
-        <v>10455800</v>
+        <v>12674700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B101" t="n">
-        <v>672.7998711552045</v>
+        <v>632.1725042393389</v>
       </c>
       <c r="C101" t="n">
-        <v>678.0605068549233</v>
+        <v>643.3437568439427</v>
       </c>
       <c r="D101" t="n">
-        <v>655.9299390360635</v>
+        <v>626.5370489428796</v>
       </c>
       <c r="E101" t="n">
-        <v>667.4993286132812</v>
+        <v>641.5682983398438</v>
       </c>
       <c r="F101" t="n">
-        <v>14323800</v>
+        <v>14649200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B102" t="n">
-        <v>668.7770306530766</v>
+        <v>636.9302530675583</v>
       </c>
       <c r="C102" t="n">
-        <v>674.7963229561075</v>
+        <v>645.5281132997313</v>
       </c>
       <c r="D102" t="n">
-        <v>644.1310518439949</v>
+        <v>635.0849670695593</v>
       </c>
       <c r="E102" t="n">
-        <v>648.6529541015625</v>
+        <v>643.1243286132812</v>
       </c>
       <c r="F102" t="n">
-        <v>14960100</v>
+        <v>10035700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B103" t="n">
-        <v>643.9513250294082</v>
+        <v>638.0474161403351</v>
       </c>
       <c r="C103" t="n">
-        <v>650.2700710327099</v>
+        <v>661.6466355641227</v>
       </c>
       <c r="D103" t="n">
-        <v>633.4401061931457</v>
+        <v>637.1397796110642</v>
       </c>
       <c r="E103" t="n">
-        <v>638.630859375</v>
+        <v>653.9763793945312</v>
       </c>
       <c r="F103" t="n">
-        <v>12336400</v>
+        <v>14183500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="B104" t="n">
-        <v>638.3612593202278</v>
+        <v>650.8643633551039</v>
       </c>
       <c r="C104" t="n">
-        <v>641.4557148619026</v>
+        <v>656.0111474209717</v>
       </c>
       <c r="D104" t="n">
-        <v>627.6803003409905</v>
+        <v>634.3668572540702</v>
       </c>
       <c r="E104" t="n">
-        <v>638.151611328125</v>
+        <v>635.6136474609375</v>
       </c>
       <c r="F104" t="n">
-        <v>12674700</v>
+        <v>8605900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
       <c r="B105" t="n">
-        <v>632.67143641335</v>
+        <v>631.4543872367445</v>
       </c>
       <c r="C105" t="n">
-        <v>643.8515057528024</v>
+        <v>639.4637360573605</v>
       </c>
       <c r="D105" t="n">
-        <v>627.0315334227189</v>
+        <v>627.364878734925</v>
       </c>
       <c r="E105" t="n">
-        <v>642.0746459960938</v>
+        <v>637.6583862304688</v>
       </c>
       <c r="F105" t="n">
-        <v>14649200</v>
+        <v>10135600</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46072</v>
+        <v>46078</v>
       </c>
       <c r="B106" t="n">
-        <v>637.432932921519</v>
+        <v>640.8801577475739</v>
       </c>
       <c r="C106" t="n">
-        <v>646.0375787806976</v>
+        <v>652.2009891675571</v>
       </c>
       <c r="D106" t="n">
-        <v>635.5861905818066</v>
+        <v>640.4911445683953</v>
       </c>
       <c r="E106" t="n">
-        <v>643.6318969726562</v>
+        <v>652.011474609375</v>
       </c>
       <c r="F106" t="n">
-        <v>10035700</v>
+        <v>11330700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46073</v>
+        <v>46079</v>
       </c>
       <c r="B107" t="n">
-        <v>638.5509584025834</v>
+        <v>648.8795635426123</v>
       </c>
       <c r="C107" t="n">
-        <v>662.1688021543367</v>
+        <v>659.3027431401059</v>
       </c>
       <c r="D107" t="n">
-        <v>637.6426055733327</v>
+        <v>645.8374072363367</v>
       </c>
       <c r="E107" t="n">
-        <v>654.4924926757812</v>
+        <v>655.322998046875</v>
       </c>
       <c r="F107" t="n">
-        <v>14183500</v>
+        <v>10637700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="B108" t="n">
-        <v>651.3780476889771</v>
+        <v>641.7977899641362</v>
       </c>
       <c r="C108" t="n">
-        <v>656.5288937722072</v>
+        <v>647.7723993687464</v>
       </c>
       <c r="D108" t="n">
-        <v>634.8675211939732</v>
+        <v>636.4814590544522</v>
       </c>
       <c r="E108" t="n">
-        <v>636.1152954101562</v>
+        <v>646.515625</v>
       </c>
       <c r="F108" t="n">
-        <v>8605900</v>
+        <v>15703000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="B109" t="n">
-        <v>631.9527259539814</v>
+        <v>635.5238627543893</v>
       </c>
       <c r="C109" t="n">
-        <v>639.9683956881865</v>
+        <v>658.2453970983619</v>
       </c>
       <c r="D109" t="n">
-        <v>627.8599900449855</v>
+        <v>632.870719934867</v>
       </c>
       <c r="E109" t="n">
-        <v>638.16162109375</v>
+        <v>651.8817749023438</v>
       </c>
       <c r="F109" t="n">
-        <v>10135600</v>
+        <v>9816100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="B110" t="n">
-        <v>641.3859599741169</v>
+        <v>646.6252847330551</v>
       </c>
       <c r="C110" t="n">
-        <v>652.7157261405878</v>
+        <v>657.3476806461185</v>
       </c>
       <c r="D110" t="n">
-        <v>640.9966397738364</v>
+        <v>637.199599354082</v>
       </c>
       <c r="E110" t="n">
-        <v>652.5260620117188</v>
+        <v>653.3978881835938</v>
       </c>
       <c r="F110" t="n">
-        <v>11330700</v>
+        <v>12263800</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="B111" t="n">
-        <v>649.3916295582877</v>
+        <v>656.2705097002453</v>
       </c>
       <c r="C111" t="n">
-        <v>659.823034651462</v>
+        <v>671.0424780902056</v>
       </c>
       <c r="D111" t="n">
-        <v>646.3470725216666</v>
+        <v>655.9812154011644</v>
       </c>
       <c r="E111" t="n">
-        <v>655.8401489257812</v>
+        <v>666.015380859375</v>
       </c>
       <c r="F111" t="n">
-        <v>10637700</v>
+        <v>10810100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="B112" t="n">
-        <v>642.3043203814821</v>
+        <v>660.2303336051802</v>
       </c>
       <c r="C112" t="n">
-        <v>648.2836451675449</v>
+        <v>668.9778340733714</v>
       </c>
       <c r="D112" t="n">
-        <v>636.9837936279411</v>
+        <v>648.6401755256248</v>
       </c>
       <c r="E112" t="n">
-        <v>647.02587890625</v>
+        <v>658.8738403320312</v>
       </c>
       <c r="F112" t="n">
-        <v>15703000</v>
+        <v>13341400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="B113" t="n">
-        <v>636.0254184162494</v>
+        <v>646.2363343546218</v>
       </c>
       <c r="C113" t="n">
-        <v>658.764884603327</v>
+        <v>647.8022493056128</v>
       </c>
       <c r="D113" t="n">
-        <v>633.3701817354564</v>
+        <v>634.4765699796501</v>
       </c>
       <c r="E113" t="n">
-        <v>652.396240234375</v>
+        <v>643.2041015625</v>
       </c>
       <c r="F113" t="n">
-        <v>9816100</v>
+        <v>13159400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="B114" t="n">
-        <v>647.1356255764312</v>
+        <v>633.1501152642575</v>
       </c>
       <c r="C114" t="n">
-        <v>657.866484005116</v>
+        <v>646.0867831911829</v>
       </c>
       <c r="D114" t="n">
-        <v>637.7025010942567</v>
+        <v>625.1706567300553</v>
       </c>
       <c r="E114" t="n">
-        <v>653.91357421875</v>
+        <v>645.7277221679688</v>
       </c>
       <c r="F114" t="n">
-        <v>12263800</v>
+        <v>13489700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="B115" t="n">
-        <v>656.7884535878291</v>
+        <v>651.881802754218</v>
       </c>
       <c r="C115" t="n">
-        <v>671.5720803574089</v>
+        <v>658.6044862124207</v>
       </c>
       <c r="D115" t="n">
-        <v>656.4989309709863</v>
+        <v>647.3335142418318</v>
       </c>
       <c r="E115" t="n">
-        <v>666.541015625</v>
+        <v>652.3905029296875</v>
       </c>
       <c r="F115" t="n">
-        <v>10810100</v>
+        <v>9859300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B116" t="n">
-        <v>660.751362594833</v>
+        <v>653.0786868976891</v>
       </c>
       <c r="C116" t="n">
-        <v>669.5057662619517</v>
+        <v>657.4274764783338</v>
       </c>
       <c r="D116" t="n">
-        <v>649.1520579976961</v>
+        <v>646.695096760678</v>
       </c>
       <c r="E116" t="n">
-        <v>659.393798828125</v>
+        <v>653.1784057617188</v>
       </c>
       <c r="F116" t="n">
-        <v>13341400</v>
+        <v>8977200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="B117" t="n">
-        <v>646.7463568472266</v>
+        <v>647.084125187776</v>
       </c>
       <c r="C117" t="n">
-        <v>648.3135076492586</v>
+        <v>651.8219280311547</v>
       </c>
       <c r="D117" t="n">
-        <v>634.9773114336934</v>
+        <v>635.2645782351397</v>
       </c>
       <c r="E117" t="n">
-        <v>643.7117309570312</v>
+        <v>636.541259765625</v>
       </c>
       <c r="F117" t="n">
-        <v>13159400</v>
+        <v>11617500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="B118" t="n">
-        <v>633.6497720389343</v>
+        <v>622.2879460132801</v>
       </c>
       <c r="C118" t="n">
-        <v>646.596649067328</v>
+        <v>627.554356001348</v>
       </c>
       <c r="D118" t="n">
-        <v>625.6640164348609</v>
+        <v>607.9847424867846</v>
       </c>
       <c r="E118" t="n">
-        <v>646.2373046875</v>
+        <v>612.1340942382812</v>
       </c>
       <c r="F118" t="n">
-        <v>13489700</v>
+        <v>18957600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,25 +3511,25 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="B119" t="n">
-        <v>652.3962328583322</v>
+        <v>630.9168848948667</v>
       </c>
       <c r="C119" t="n">
-        <v>659.1242214972237</v>
+        <v>633.6621719731276</v>
       </c>
       <c r="D119" t="n">
-        <v>647.8443550809549</v>
+        <v>622.0321132511823</v>
       </c>
       <c r="E119" t="n">
-        <v>652.9053344726562</v>
+        <v>626.3746948242188</v>
       </c>
       <c r="F119" t="n">
-        <v>9859300</v>
+        <v>15134900</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46092</v>
+        <v>46098</v>
       </c>
       <c r="B120" t="n">
-        <v>653.5941111270305</v>
+        <v>626.9137783313067</v>
       </c>
       <c r="C120" t="n">
-        <v>657.9463328691638</v>
+        <v>635.4591062750881</v>
       </c>
       <c r="D120" t="n">
-        <v>647.2054829186618</v>
+        <v>620.634579694285</v>
       </c>
       <c r="E120" t="n">
-        <v>653.6939086914062</v>
+        <v>621.5928955078125</v>
       </c>
       <c r="F120" t="n">
-        <v>8977200</v>
+        <v>10348800</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46093</v>
+        <v>46099</v>
       </c>
       <c r="B121" t="n">
-        <v>647.5948263527883</v>
+        <v>615.2837809831337</v>
       </c>
       <c r="C121" t="n">
-        <v>652.336368433984</v>
+        <v>621.5829648535273</v>
       </c>
       <c r="D121" t="n">
-        <v>635.7659510050273</v>
+        <v>613.5567043186309</v>
       </c>
       <c r="E121" t="n">
-        <v>637.0436401367188</v>
+        <v>614.6248779296875</v>
       </c>
       <c r="F121" t="n">
-        <v>11617500</v>
+        <v>11726300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B122" t="n">
-        <v>622.7790526456299</v>
+        <v>611.1009505532863</v>
       </c>
       <c r="C122" t="n">
-        <v>628.0496188589474</v>
+        <v>611.9494694911245</v>
       </c>
       <c r="D122" t="n">
-        <v>608.4645611002024</v>
+        <v>601.2278849458298</v>
       </c>
       <c r="E122" t="n">
-        <v>612.6171875</v>
+        <v>605.6602783203125</v>
       </c>
       <c r="F122" t="n">
-        <v>18957600</v>
+        <v>13247700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,25 +3615,25 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="B123" t="n">
-        <v>631.4147932406764</v>
+        <v>602.4957192983555</v>
       </c>
       <c r="C123" t="n">
-        <v>634.1622468505053</v>
+        <v>602.9249750667714</v>
       </c>
       <c r="D123" t="n">
-        <v>622.5230098937741</v>
+        <v>586.2435901825164</v>
       </c>
       <c r="E123" t="n">
-        <v>626.8690185546875</v>
+        <v>592.642578125</v>
       </c>
       <c r="F123" t="n">
-        <v>15134900</v>
+        <v>21214900</v>
       </c>
       <c r="G123" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="B124" t="n">
-        <v>627.4085169382369</v>
+        <v>604.7517959610541</v>
       </c>
       <c r="C124" t="n">
-        <v>635.9605885584036</v>
+        <v>607.5969482872343</v>
       </c>
       <c r="D124" t="n">
-        <v>621.1243629754691</v>
+        <v>597.9834469761715</v>
       </c>
       <c r="E124" t="n">
-        <v>622.0834350585938</v>
+        <v>603.0247802734375</v>
       </c>
       <c r="F124" t="n">
-        <v>10348800</v>
+        <v>13638000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="B125" t="n">
-        <v>615.7693473594539</v>
+        <v>598.0732713770465</v>
       </c>
       <c r="C125" t="n">
-        <v>622.0735023862151</v>
+        <v>599.9700396349708</v>
       </c>
       <c r="D125" t="n">
-        <v>614.04090772979</v>
+        <v>589.9871770786485</v>
       </c>
       <c r="E125" t="n">
-        <v>615.1099243164062</v>
+        <v>591.9038696289062</v>
       </c>
       <c r="F125" t="n">
-        <v>11726300</v>
+        <v>10739700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="B126" t="n">
-        <v>611.5832104537112</v>
+        <v>597.7138608396341</v>
       </c>
       <c r="C126" t="n">
-        <v>612.4323990135786</v>
+        <v>602.6354044215132</v>
       </c>
       <c r="D126" t="n">
-        <v>601.7023533616688</v>
+        <v>592.3830467312241</v>
       </c>
       <c r="E126" t="n">
-        <v>606.1382446289062</v>
+        <v>593.8704833984375</v>
       </c>
       <c r="F126" t="n">
-        <v>13247700</v>
+        <v>12585000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="B127" t="n">
-        <v>602.9712077810872</v>
+        <v>581.4916747262954</v>
       </c>
       <c r="C127" t="n">
-        <v>603.400802317344</v>
+        <v>582.0008103985165</v>
       </c>
       <c r="D127" t="n">
-        <v>586.7062525156723</v>
+        <v>542.4187412024525</v>
       </c>
       <c r="E127" t="n">
-        <v>593.1102905273438</v>
+        <v>546.6015625</v>
       </c>
       <c r="F127" t="n">
-        <v>21214900</v>
+        <v>35780100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="B128" t="n">
-        <v>605.2290499891692</v>
+        <v>539.1743295527585</v>
       </c>
       <c r="C128" t="n">
-        <v>608.0764476338709</v>
+        <v>542.6683311056884</v>
       </c>
       <c r="D128" t="n">
-        <v>598.4553596033379</v>
+        <v>519.368366299545</v>
       </c>
       <c r="E128" t="n">
-        <v>603.5006713867188</v>
+        <v>524.8189697265625</v>
       </c>
       <c r="F128" t="n">
-        <v>13638000</v>
+        <v>30133000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="B129" t="n">
-        <v>598.5452420228083</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="C129" t="n">
-        <v>600.443507118967</v>
+        <v>538.6253045735799</v>
       </c>
       <c r="D129" t="n">
-        <v>590.4527665679026</v>
+        <v>527.6341638126921</v>
       </c>
       <c r="E129" t="n">
-        <v>592.3709716796875</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="F129" t="n">
-        <v>10739700</v>
+        <v>22795200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="B130" t="n">
-        <v>598.1855830392399</v>
+        <v>549.0374119135495</v>
       </c>
       <c r="C130" t="n">
-        <v>603.1110107561809</v>
+        <v>572.7067990959439</v>
       </c>
       <c r="D130" t="n">
-        <v>592.8505617950721</v>
+        <v>545.8329522821889</v>
       </c>
       <c r="E130" t="n">
-        <v>594.3391723632812</v>
+        <v>571.1494750976562</v>
       </c>
       <c r="F130" t="n">
-        <v>12585000</v>
+        <v>32898300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B131" t="n">
-        <v>581.9506076701073</v>
+        <v>579.1357866530213</v>
       </c>
       <c r="C131" t="n">
-        <v>582.460145169462</v>
+        <v>591.5344843799961</v>
       </c>
       <c r="D131" t="n">
-        <v>542.8468364624507</v>
+        <v>572.8366030750008</v>
       </c>
       <c r="E131" t="n">
-        <v>547.032958984375</v>
+        <v>578.2373046875</v>
       </c>
       <c r="F131" t="n">
-        <v>35780100</v>
+        <v>23608100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="B132" t="n">
-        <v>539.599843303006</v>
+        <v>565.0699110449033</v>
       </c>
       <c r="C132" t="n">
-        <v>543.0966023049141</v>
+        <v>577.5085793033603</v>
       </c>
       <c r="D132" t="n">
-        <v>519.7782492802263</v>
+        <v>558.7408105198895</v>
       </c>
       <c r="E132" t="n">
-        <v>525.233154296875</v>
+        <v>573.4755249023438</v>
       </c>
       <c r="F132" t="n">
-        <v>30133000</v>
+        <v>13518500</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="B133" t="n">
-        <v>535.8833618164062</v>
+        <v>576.6999432469056</v>
       </c>
       <c r="C133" t="n">
-        <v>539.0504095872608</v>
+        <v>581.7911783704857</v>
       </c>
       <c r="D133" t="n">
-        <v>528.0505941707193</v>
+        <v>571.0196924702504</v>
       </c>
       <c r="E133" t="n">
-        <v>535.8833618164062</v>
+        <v>572.0379638671875</v>
       </c>
       <c r="F133" t="n">
-        <v>22795200</v>
+        <v>9515700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="B134" t="n">
-        <v>549.4707059552647</v>
+        <v>571.4988503418972</v>
       </c>
       <c r="C134" t="n">
-        <v>573.1587727471259</v>
+        <v>574.2441373249518</v>
       </c>
       <c r="D134" t="n">
-        <v>546.2637174010383</v>
+        <v>563.7921103124964</v>
       </c>
       <c r="E134" t="n">
-        <v>571.6002197265625</v>
+        <v>574.064453125</v>
       </c>
       <c r="F134" t="n">
-        <v>32898300</v>
+        <v>9580800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B135" t="n">
-        <v>579.5928556215499</v>
+        <v>604.9614419693103</v>
       </c>
       <c r="C135" t="n">
-        <v>592.0013387220274</v>
+        <v>628.8704088339113</v>
       </c>
       <c r="D135" t="n">
-        <v>573.2887005646345</v>
+        <v>590.8157434643455</v>
       </c>
       <c r="E135" t="n">
-        <v>578.6936645507812</v>
+        <v>611.3704223632812</v>
       </c>
       <c r="F135" t="n">
-        <v>23608100</v>
+        <v>32036600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="B136" t="n">
-        <v>565.5158531822124</v>
+        <v>625.8955000086161</v>
       </c>
       <c r="C136" t="n">
-        <v>577.9643377947169</v>
+        <v>636.4074834525468</v>
       </c>
       <c r="D136" t="n">
-        <v>559.1817578546791</v>
+        <v>621.9323328485281</v>
       </c>
       <c r="E136" t="n">
-        <v>573.9281005859375</v>
+        <v>627.3131103515625</v>
       </c>
       <c r="F136" t="n">
-        <v>13518500</v>
+        <v>19012900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="B137" t="n">
-        <v>577.1550997330287</v>
+        <v>633.3826022362973</v>
       </c>
       <c r="C137" t="n">
-        <v>582.2503530791108</v>
+        <v>637.4856047359222</v>
       </c>
       <c r="D137" t="n">
-        <v>571.4703658572956</v>
+        <v>623.2600266965629</v>
       </c>
       <c r="E137" t="n">
-        <v>572.4894409179688</v>
+        <v>628.780517578125</v>
       </c>
       <c r="F137" t="n">
-        <v>9515700</v>
+        <v>13294800</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="B138" t="n">
-        <v>571.9498894780604</v>
+        <v>628.4212176827168</v>
       </c>
       <c r="C138" t="n">
-        <v>574.6973431004155</v>
+        <v>633.9117922613585</v>
       </c>
       <c r="D138" t="n">
-        <v>564.2370671243236</v>
+        <v>623.3299819911093</v>
       </c>
       <c r="E138" t="n">
-        <v>574.5175170898438</v>
+        <v>633.442626953125</v>
       </c>
       <c r="F138" t="n">
-        <v>9580800</v>
+        <v>9538900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="B139" t="n">
-        <v>605.4388670235439</v>
+        <v>642.117619704398</v>
       </c>
       <c r="C139" t="n">
-        <v>629.3667024291958</v>
+        <v>665.1181727259973</v>
       </c>
       <c r="D139" t="n">
-        <v>591.2820049792073</v>
+        <v>638.2742422102883</v>
       </c>
       <c r="E139" t="n">
-        <v>611.8529052734375</v>
+        <v>661.3546142578125</v>
       </c>
       <c r="F139" t="n">
-        <v>32036600</v>
+        <v>17818000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="B140" t="n">
-        <v>626.3894374266143</v>
+        <v>665.856909197143</v>
       </c>
       <c r="C140" t="n">
-        <v>636.9097166035551</v>
+        <v>677.3372007350248</v>
       </c>
       <c r="D140" t="n">
-        <v>622.4231426572783</v>
+        <v>663.081644256971</v>
       </c>
       <c r="E140" t="n">
-        <v>627.8081665039062</v>
+        <v>670.4290771484375</v>
       </c>
       <c r="F140" t="n">
-        <v>19012900</v>
+        <v>14952600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B141" t="n">
-        <v>633.882449891805</v>
+        <v>674.831464225754</v>
       </c>
       <c r="C141" t="n">
-        <v>637.9886903650855</v>
+        <v>676.4187660594131</v>
       </c>
       <c r="D141" t="n">
-        <v>623.7518859014353</v>
+        <v>666.605595861725</v>
       </c>
       <c r="E141" t="n">
-        <v>629.2767333984375</v>
+        <v>675.7099609375</v>
       </c>
       <c r="F141" t="n">
-        <v>13294800</v>
+        <v>9544800</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="B142" t="n">
-        <v>628.9171329935918</v>
+        <v>677.4369744478516</v>
       </c>
       <c r="C142" t="n">
-        <v>634.4120404303904</v>
+        <v>690.3348757077041</v>
       </c>
       <c r="D142" t="n">
-        <v>623.8218795800174</v>
+        <v>673.9729506648888</v>
       </c>
       <c r="E142" t="n">
-        <v>633.9425048828125</v>
+        <v>687.3699340820312</v>
       </c>
       <c r="F142" t="n">
-        <v>9538900</v>
+        <v>16283500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="B143" t="n">
-        <v>642.624350345733</v>
+        <v>680.192296240317</v>
       </c>
       <c r="C143" t="n">
-        <v>665.6430543798978</v>
+        <v>682.2088539380842</v>
       </c>
       <c r="D143" t="n">
-        <v>638.7779398291946</v>
+        <v>666.8552067290691</v>
       </c>
       <c r="E143" t="n">
-        <v>661.8765258789062</v>
+        <v>669.7601928710938</v>
       </c>
       <c r="F143" t="n">
-        <v>17818000</v>
+        <v>12534000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B144" t="n">
-        <v>666.3824145357423</v>
+        <v>669.8500580611455</v>
       </c>
       <c r="C144" t="n">
-        <v>677.8717665104965</v>
+        <v>675.0411586256739</v>
       </c>
       <c r="D144" t="n">
-        <v>663.6049593103575</v>
+        <v>666.1863646700106</v>
       </c>
       <c r="E144" t="n">
-        <v>670.9581909179688</v>
+        <v>667.6937866210938</v>
       </c>
       <c r="F144" t="n">
-        <v>14952600</v>
+        <v>8660100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="B145" t="n">
-        <v>675.3640350842893</v>
+        <v>673.2042912464699</v>
       </c>
       <c r="C145" t="n">
-        <v>676.9525896021297</v>
+        <v>677.2174214115423</v>
       </c>
       <c r="D145" t="n">
-        <v>667.131674939706</v>
+        <v>668.6022063234784</v>
       </c>
       <c r="E145" t="n">
-        <v>676.2432250976562</v>
+        <v>673.5636596679688</v>
       </c>
       <c r="F145" t="n">
-        <v>9544800</v>
+        <v>9215600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B146" t="n">
-        <v>677.9716157075654</v>
+        <v>662.562575853328</v>
       </c>
       <c r="C146" t="n">
-        <v>690.8796961433965</v>
+        <v>668.4125184743669</v>
       </c>
       <c r="D146" t="n">
-        <v>674.5048580761284</v>
+        <v>651.9308032468797</v>
       </c>
       <c r="E146" t="n">
-        <v>687.9124145507812</v>
+        <v>658.0203857421875</v>
       </c>
       <c r="F146" t="n">
-        <v>16283500</v>
+        <v>11667000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="B147" t="n">
-        <v>680.7290935491282</v>
+        <v>659.1883568751083</v>
       </c>
       <c r="C147" t="n">
-        <v>682.7472426832454</v>
+        <v>679.5034568571632</v>
       </c>
       <c r="D147" t="n">
-        <v>667.381478611767</v>
+        <v>652.719481738207</v>
       </c>
       <c r="E147" t="n">
-        <v>670.2887573242188</v>
+        <v>673.8731689453125</v>
       </c>
       <c r="F147" t="n">
-        <v>12534000</v>
+        <v>13348300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B148" t="n">
-        <v>670.3786762058809</v>
+        <v>669.8500343121515</v>
       </c>
       <c r="C148" t="n">
-        <v>675.5738733736962</v>
+        <v>681.330325511242</v>
       </c>
       <c r="D148" t="n">
-        <v>666.7120915784461</v>
+        <v>669.6903353309991</v>
       </c>
       <c r="E148" t="n">
-        <v>668.220703125</v>
+        <v>677.4569702148438</v>
       </c>
       <c r="F148" t="n">
-        <v>8660100</v>
+        <v>12805200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B149" t="n">
-        <v>673.7355628200382</v>
+        <v>673.0844464119266</v>
       </c>
       <c r="C149" t="n">
-        <v>677.7518600207422</v>
+        <v>677.0176962940845</v>
       </c>
       <c r="D149" t="n">
-        <v>669.1298460769134</v>
+        <v>664.489217253305</v>
       </c>
       <c r="E149" t="n">
-        <v>674.09521484375</v>
+        <v>670.189453125</v>
       </c>
       <c r="F149" t="n">
-        <v>9215600</v>
+        <v>10606800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="B150" t="n">
-        <v>663.0854475032797</v>
+        <v>667.7636045616339</v>
       </c>
       <c r="C150" t="n">
-        <v>668.9400066983026</v>
+        <v>673.0944797535534</v>
       </c>
       <c r="D150" t="n">
-        <v>652.4452846667049</v>
+        <v>662.6723692427279</v>
       </c>
       <c r="E150" t="n">
-        <v>658.5396728515625</v>
+        <v>667.9732666015625</v>
       </c>
       <c r="F150" t="n">
-        <v>11667000</v>
+        <v>18947500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="B151" t="n">
-        <v>659.7085674039201</v>
+        <v>618.2586017744245</v>
       </c>
       <c r="C151" t="n">
-        <v>680.0396994180859</v>
+        <v>619.7859479396749</v>
       </c>
       <c r="D151" t="n">
-        <v>653.2345872360809</v>
+        <v>598.9717055442339</v>
       </c>
       <c r="E151" t="n">
-        <v>674.4049682617188</v>
+        <v>610.8612670898438</v>
       </c>
       <c r="F151" t="n">
-        <v>13348300</v>
+        <v>52765000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="B152" t="n">
-        <v>670.3786986745525</v>
+        <v>613.6365485572411</v>
       </c>
       <c r="C152" t="n">
-        <v>681.8680504402118</v>
+        <v>617.8193701850194</v>
       </c>
       <c r="D152" t="n">
-        <v>670.2188736545023</v>
+        <v>605.0712358749745</v>
       </c>
       <c r="E152" t="n">
-        <v>677.9916381835938</v>
+        <v>607.7067260742188</v>
       </c>
       <c r="F152" t="n">
-        <v>12805200</v>
+        <v>21404000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B153" t="n">
-        <v>673.6156618787633</v>
+        <v>606.8981537761392</v>
       </c>
       <c r="C153" t="n">
-        <v>677.5520159823654</v>
+        <v>612.9477660987843</v>
       </c>
       <c r="D153" t="n">
-        <v>665.0136491453696</v>
+        <v>601.7170456287333</v>
       </c>
       <c r="E153" t="n">
-        <v>670.7183837890625</v>
+        <v>609.3638916015625</v>
       </c>
       <c r="F153" t="n">
-        <v>10606800</v>
+        <v>16203900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="B154" t="n">
-        <v>668.2905997420939</v>
+        <v>612.2588828439087</v>
       </c>
       <c r="C154" t="n">
-        <v>673.6256820299297</v>
+        <v>613.2970785161436</v>
       </c>
       <c r="D154" t="n">
-        <v>663.1953464496755</v>
+        <v>599.3310648754198</v>
       </c>
       <c r="E154" t="n">
-        <v>668.5004272460938</v>
+        <v>603.9232177734375</v>
       </c>
       <c r="F154" t="n">
-        <v>18947500</v>
+        <v>17171300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="B155" t="n">
-        <v>618.7465567527638</v>
+        <v>600.0199080772063</v>
       </c>
       <c r="C155" t="n">
-        <v>620.2751083620838</v>
+        <v>618.8875416216711</v>
       </c>
       <c r="D155" t="n">
-        <v>599.4444385151393</v>
+        <v>597.0749516023062</v>
       </c>
       <c r="E155" t="n">
-        <v>611.3433837890625</v>
+        <v>611.8296508789062</v>
       </c>
       <c r="F155" t="n">
-        <v>52765000</v>
+        <v>19915500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B156" t="n">
-        <v>614.120842749119</v>
+        <v>613.6664238202088</v>
       </c>
       <c r="C156" t="n">
-        <v>618.3069655430758</v>
+        <v>623.9088493168618</v>
       </c>
       <c r="D156" t="n">
-        <v>605.5487701514051</v>
+        <v>612.4884534922683</v>
       </c>
       <c r="E156" t="n">
-        <v>608.1863403320312</v>
+        <v>615.7528686523438</v>
       </c>
       <c r="F156" t="n">
-        <v>21404000</v>
+        <v>12307400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="n">
-        <v>607.3771038685389</v>
+        <v>614.1456663784968</v>
       </c>
       <c r="C157" t="n">
-        <v>613.4314904063681</v>
+        <v>615.7129829832094</v>
       </c>
       <c r="D157" t="n">
-        <v>602.1919069095087</v>
+        <v>605.0213161255829</v>
       </c>
       <c r="E157" t="n">
-        <v>609.8447875976562</v>
+        <v>608.585205078125</v>
       </c>
       <c r="F157" t="n">
-        <v>16203900</v>
+        <v>13557000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B158" t="n">
-        <v>612.7420849871345</v>
+        <v>603.533915527778</v>
       </c>
       <c r="C158" t="n">
-        <v>613.7811000159977</v>
+        <v>603.8732987260729</v>
       </c>
       <c r="D158" t="n">
-        <v>599.8040642277598</v>
+        <v>597.0550476209405</v>
       </c>
       <c r="E158" t="n">
-        <v>604.3998413085938</v>
+        <v>597.8336791992188</v>
       </c>
       <c r="F158" t="n">
-        <v>17171300</v>
+        <v>15940600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="B159" t="n">
-        <v>600.4934370812971</v>
+        <v>593.8006394881057</v>
       </c>
       <c r="C159" t="n">
-        <v>619.3759607512419</v>
+        <v>602.7153284632744</v>
       </c>
       <c r="D159" t="n">
-        <v>597.5461564796674</v>
+        <v>591.5844123107358</v>
       </c>
       <c r="E159" t="n">
-        <v>612.3125</v>
+        <v>601.9666137695312</v>
       </c>
       <c r="F159" t="n">
-        <v>19915500</v>
+        <v>11351600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="B160" t="n">
-        <v>614.150739078972</v>
+        <v>597.8037594995824</v>
       </c>
       <c r="C160" t="n">
-        <v>624.4012480600104</v>
+        <v>618.837657653709</v>
       </c>
       <c r="D160" t="n">
-        <v>612.9718390781961</v>
+        <v>595.6374345129168</v>
       </c>
       <c r="E160" t="n">
-        <v>616.2388305664062</v>
+        <v>615.5732421875</v>
       </c>
       <c r="F160" t="n">
-        <v>12307400</v>
+        <v>14634400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B161" t="n">
-        <v>614.6303402495529</v>
+        <v>614.944289073115</v>
       </c>
       <c r="C161" t="n">
-        <v>616.1988937552933</v>
+        <v>622.6610217742586</v>
       </c>
       <c r="D161" t="n">
-        <v>605.4987892063378</v>
+        <v>613.9460028895547</v>
       </c>
       <c r="E161" t="n">
-        <v>609.0654907226562</v>
+        <v>617.3701171875</v>
       </c>
       <c r="F161" t="n">
-        <v>13557000</v>
+        <v>10651200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B162" t="n">
-        <v>604.010215830275</v>
+        <v>612.9377892034477</v>
       </c>
       <c r="C162" t="n">
-        <v>604.3498668649182</v>
+        <v>620.135455286475</v>
       </c>
       <c r="D162" t="n">
-        <v>597.5262348938886</v>
+        <v>608.2658166797805</v>
       </c>
       <c r="E162" t="n">
-        <v>598.3054809570312</v>
+        <v>613.1773681640625</v>
       </c>
       <c r="F162" t="n">
-        <v>15940600</v>
+        <v>13272600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B163" t="n">
-        <v>594.2692320029287</v>
+        <v>608.0660990208263</v>
       </c>
       <c r="C163" t="n">
-        <v>603.1909559259367</v>
+        <v>614.5350350972873</v>
       </c>
       <c r="D163" t="n">
-        <v>592.0512559095129</v>
+        <v>602.6554048207697</v>
       </c>
       <c r="E163" t="n">
-        <v>602.441650390625</v>
+        <v>610.1625366210938</v>
       </c>
       <c r="F163" t="n">
-        <v>11351600</v>
+        <v>13772400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B164" t="n">
-        <v>598.275515544453</v>
+        <v>607.8764543920544</v>
       </c>
       <c r="C164" t="n">
-        <v>619.3260125714435</v>
+        <v>612.8778783201094</v>
       </c>
       <c r="D164" t="n">
-        <v>596.1074810052941</v>
+        <v>599.5208032426234</v>
       </c>
       <c r="E164" t="n">
-        <v>616.0590209960938</v>
+        <v>601.5772705078125</v>
       </c>
       <c r="F164" t="n">
-        <v>14634400</v>
+        <v>11749900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B165" t="n">
-        <v>615.4296182023591</v>
+        <v>599.7304526335664</v>
       </c>
       <c r="C165" t="n">
-        <v>623.152441138389</v>
+        <v>606.9580352784536</v>
       </c>
       <c r="D165" t="n">
-        <v>614.4305441468357</v>
+        <v>596.7854960328639</v>
       </c>
       <c r="E165" t="n">
-        <v>617.8573608398438</v>
+        <v>604.0230712890625</v>
       </c>
       <c r="F165" t="n">
-        <v>10651200</v>
+        <v>11329700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B166" t="n">
-        <v>613.421486859321</v>
+        <v>598.9716935873996</v>
       </c>
       <c r="C166" t="n">
-        <v>620.6248329546977</v>
+        <v>608.5552163125774</v>
       </c>
       <c r="D166" t="n">
-        <v>608.7458274653094</v>
+        <v>593.7905860006466</v>
       </c>
       <c r="E166" t="n">
-        <v>613.6612548828125</v>
+        <v>606.3390502929688</v>
       </c>
       <c r="F166" t="n">
-        <v>13272600</v>
+        <v>13476100</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B167" t="n">
-        <v>608.5459509764945</v>
+        <v>606.838246230648</v>
       </c>
       <c r="C167" t="n">
-        <v>615.0199919776213</v>
+        <v>613.7563625825306</v>
       </c>
       <c r="D167" t="n">
-        <v>603.1309869574205</v>
+        <v>605.9098473363839</v>
       </c>
       <c r="E167" t="n">
-        <v>610.64404296875</v>
+        <v>609.2141723632812</v>
       </c>
       <c r="F167" t="n">
-        <v>13772400</v>
+        <v>11688600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B168" t="n">
-        <v>608.3561568042173</v>
+        <v>607.8464888599174</v>
       </c>
       <c r="C168" t="n">
-        <v>613.361527578881</v>
+        <v>613.4168818935308</v>
       </c>
       <c r="D168" t="n">
-        <v>599.9939118379299</v>
+        <v>604.2626146519137</v>
       </c>
       <c r="E168" t="n">
-        <v>602.052001953125</v>
+        <v>611.2905883789062</v>
       </c>
       <c r="F168" t="n">
-        <v>11749900</v>
+        <v>12234200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B169" t="n">
-        <v>600.2037495434126</v>
+        <v>608.3556581766634</v>
       </c>
       <c r="C169" t="n">
-        <v>607.4370360716302</v>
+        <v>637.4057633477772</v>
       </c>
       <c r="D169" t="n">
-        <v>597.2564688338498</v>
+        <v>607.9563193089997</v>
       </c>
       <c r="E169" t="n">
-        <v>604.499755859375</v>
+        <v>634.1713256835938</v>
       </c>
       <c r="F169" t="n">
-        <v>11329700</v>
+        <v>23143600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B170" t="n">
-        <v>599.4443949814065</v>
+        <v>638.4040398455469</v>
       </c>
       <c r="C170" t="n">
-        <v>609.0354809096541</v>
+        <v>641.8980416273442</v>
       </c>
       <c r="D170" t="n">
-        <v>594.2591985256718</v>
+        <v>628.2315007921775</v>
       </c>
       <c r="E170" t="n">
-        <v>606.8175659179688</v>
+        <v>634.2012329101562</v>
       </c>
       <c r="F170" t="n">
-        <v>13476100</v>
+        <v>16772400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B171" t="n">
-        <v>607.3171451453314</v>
+        <v>632.4143189973911</v>
       </c>
       <c r="C171" t="n">
-        <v>614.2407210713809</v>
+        <v>633.4126052152244</v>
       </c>
       <c r="D171" t="n">
-        <v>606.3880135859368</v>
+        <v>622.281689514161</v>
       </c>
       <c r="E171" t="n">
-        <v>609.6949462890625</v>
+        <v>631.426025390625</v>
       </c>
       <c r="F171" t="n">
-        <v>11688600</v>
+        <v>19806500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="B172" t="n">
-        <v>608.3261927003538</v>
+        <v>629.3196151062037</v>
       </c>
       <c r="C172" t="n">
-        <v>613.9009818092591</v>
+        <v>634.6604216515384</v>
       </c>
       <c r="D172" t="n">
-        <v>604.7394901495815</v>
+        <v>598.5025264432778</v>
       </c>
       <c r="E172" t="n">
-        <v>611.7730102539062</v>
+        <v>599.4408569335938</v>
       </c>
       <c r="F172" t="n">
-        <v>12234200</v>
+        <v>29138800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="B173" t="n">
-        <v>608.8357727220844</v>
+        <v>602.2061447656582</v>
       </c>
       <c r="C173" t="n">
-        <v>637.908804248614</v>
+        <v>607.8364934375654</v>
       </c>
       <c r="D173" t="n">
-        <v>608.4361186960156</v>
+        <v>595.6573898697867</v>
       </c>
       <c r="E173" t="n">
-        <v>634.6718139648438</v>
+        <v>596.6057739257812</v>
       </c>
       <c r="F173" t="n">
-        <v>23143600</v>
+        <v>18252000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="n">
-        <v>638.9078448274123</v>
+        <v>601.9666135784172</v>
       </c>
       <c r="C174" t="n">
-        <v>642.4046039468743</v>
+        <v>623.0803923074952</v>
       </c>
       <c r="D174" t="n">
-        <v>628.7272779804616</v>
+        <v>599.2413115918356</v>
       </c>
       <c r="E174" t="n">
-        <v>634.7017211914062</v>
+        <v>621.912353515625</v>
       </c>
       <c r="F174" t="n">
-        <v>16772400</v>
+        <v>23020100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="n">
-        <v>632.9133899267435</v>
+        <v>622.601105447702</v>
       </c>
       <c r="C175" t="n">
-        <v>633.9124639439917</v>
+        <v>641.2990464500883</v>
       </c>
       <c r="D175" t="n">
-        <v>622.7727642602187</v>
+        <v>621.3632403719068</v>
       </c>
       <c r="E175" t="n">
-        <v>631.92431640625</v>
+        <v>626.4944458007812</v>
       </c>
       <c r="F175" t="n">
-        <v>19806500</v>
+        <v>21469200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B176" t="n">
-        <v>629.8162791560948</v>
+        <v>622.3915867034917</v>
       </c>
       <c r="C176" t="n">
-        <v>635.1613007084701</v>
+        <v>628.0718380797523</v>
       </c>
       <c r="D176" t="n">
-        <v>598.9748694014791</v>
+        <v>581.9110292634388</v>
       </c>
       <c r="E176" t="n">
-        <v>599.9139404296875</v>
+        <v>591.9837646484375</v>
       </c>
       <c r="F176" t="n">
-        <v>29138800</v>
+        <v>30091600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="B177" t="n">
-        <v>602.6813896226799</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="C177" t="n">
-        <v>608.3161816139932</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="D177" t="n">
-        <v>596.1274666259658</v>
+        <v>578.2273099921849</v>
       </c>
       <c r="E177" t="n">
-        <v>597.0765991210938</v>
+        <v>584.3867797851562</v>
       </c>
       <c r="F177" t="n">
-        <v>18252000</v>
+        <v>19512400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B178" t="n">
-        <v>602.4416570391962</v>
+        <v>589.9871222602228</v>
       </c>
       <c r="C178" t="n">
-        <v>623.5720977596394</v>
+        <v>596.6057643945405</v>
       </c>
       <c r="D178" t="n">
-        <v>599.7142043737263</v>
+        <v>580.0142532419713</v>
       </c>
       <c r="E178" t="n">
-        <v>622.4031372070312</v>
+        <v>583.588134765625</v>
       </c>
       <c r="F178" t="n">
-        <v>23020100</v>
+        <v>16977400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B179" t="n">
-        <v>623.0924785224576</v>
+        <v>579.7347558037309</v>
       </c>
       <c r="C179" t="n">
-        <v>641.8051764288737</v>
+        <v>590.3066340250939</v>
       </c>
       <c r="D179" t="n">
-        <v>621.8536364911718</v>
+        <v>569.6221111934292</v>
       </c>
       <c r="E179" t="n">
-        <v>626.9888916015625</v>
+        <v>570.00146484375</v>
       </c>
       <c r="F179" t="n">
-        <v>21469200</v>
+        <v>17064000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B180" t="n">
-        <v>622.8827460758752</v>
+        <v>564.8602908302337</v>
       </c>
       <c r="C180" t="n">
-        <v>628.5674800138549</v>
+        <v>571.1893911411966</v>
       </c>
       <c r="D180" t="n">
-        <v>582.3702434655938</v>
+        <v>556.0553993401948</v>
       </c>
       <c r="E180" t="n">
-        <v>592.450927734375</v>
+        <v>567.455810546875</v>
       </c>
       <c r="F180" t="n">
-        <v>30091600</v>
+        <v>17628000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="B181" t="n">
-        <v>591.4518261333767</v>
+        <v>571.9680395129554</v>
       </c>
       <c r="C181" t="n">
-        <v>591.4518261333767</v>
+        <v>575.0826873049916</v>
       </c>
       <c r="D181" t="n">
-        <v>578.6836307521693</v>
+        <v>559.938704060897</v>
       </c>
       <c r="E181" t="n">
-        <v>584.8479614257812</v>
+        <v>566.0082397460938</v>
       </c>
       <c r="F181" t="n">
-        <v>19512400</v>
+        <v>14326400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,25 +5149,25 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="B182" t="n">
-        <v>590.4527436689563</v>
+        <v>579.4427159724761</v>
       </c>
       <c r="C182" t="n">
-        <v>597.0766092757164</v>
+        <v>600.795858737961</v>
       </c>
       <c r="D182" t="n">
-        <v>580.4720040020986</v>
+        <v>578.8431525395191</v>
       </c>
       <c r="E182" t="n">
-        <v>584.0487060546875</v>
+        <v>593.011962890625</v>
       </c>
       <c r="F182" t="n">
-        <v>16977400</v>
+        <v>17653300</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="B183" t="n">
-        <v>580.192266144374</v>
+        <v>593.1818700134238</v>
       </c>
       <c r="C183" t="n">
-        <v>590.7724873942649</v>
+        <v>605.3322537623429</v>
       </c>
       <c r="D183" t="n">
-        <v>570.0716409197756</v>
+        <v>591.5331468141493</v>
       </c>
       <c r="E183" t="n">
-        <v>570.4512939453125</v>
+        <v>599.7366943359375</v>
       </c>
       <c r="F183" t="n">
-        <v>17064000</v>
+        <v>11344400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="B184" t="n">
-        <v>565.3060574843756</v>
+        <v>591.5331725816898</v>
       </c>
       <c r="C184" t="n">
-        <v>571.6401524850257</v>
+        <v>593.3417428489197</v>
       </c>
       <c r="D184" t="n">
-        <v>556.4942175026772</v>
+        <v>565.7435277503374</v>
       </c>
       <c r="E184" t="n">
-        <v>567.9036254882812</v>
+        <v>567.1324462890625</v>
       </c>
       <c r="F184" t="n">
-        <v>17628000</v>
+        <v>20478300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="B185" t="n">
-        <v>572.4194595335534</v>
+        <v>572.3682769745303</v>
       </c>
       <c r="C185" t="n">
-        <v>575.5365655300229</v>
+        <v>579.7624046842873</v>
       </c>
       <c r="D185" t="n">
-        <v>560.3806300495169</v>
+        <v>562.6559105294999</v>
       </c>
       <c r="E185" t="n">
-        <v>566.4549560546875</v>
+        <v>576.7647705078125</v>
       </c>
       <c r="F185" t="n">
-        <v>14326400</v>
+        <v>28824600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,25 +5253,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B186" t="n">
-        <v>579.9000244140625</v>
+        <v>571.5689356803741</v>
       </c>
       <c r="C186" t="n">
-        <v>601.27001953125</v>
+        <v>575.3559250048318</v>
       </c>
       <c r="D186" t="n">
-        <v>579.2999877929688</v>
+        <v>559.3685422933314</v>
       </c>
       <c r="E186" t="n">
-        <v>593.47998046875</v>
+        <v>563.4053344726562</v>
       </c>
       <c r="F186" t="n">
-        <v>17653300</v>
+        <v>15405500</v>
       </c>
       <c r="G186" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B187" t="n">
-        <v>593.6500244140625</v>
+        <v>561.8066012038755</v>
       </c>
       <c r="C187" t="n">
-        <v>605.8099975585938</v>
+        <v>571.7487666818112</v>
       </c>
       <c r="D187" t="n">
-        <v>592</v>
+        <v>560.5775907162</v>
       </c>
       <c r="E187" t="n">
-        <v>600.2100219726562</v>
+        <v>561.7566528320312</v>
       </c>
       <c r="F187" t="n">
-        <v>11344400</v>
+        <v>13103300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B188" t="n">
-        <v>592</v>
+        <v>561.4469285838474</v>
       </c>
       <c r="C188" t="n">
-        <v>593.8099975585938</v>
+        <v>568.591253761232</v>
       </c>
       <c r="D188" t="n">
-        <v>566.1900024414062</v>
+        <v>555.1119012433646</v>
       </c>
       <c r="E188" t="n">
-        <v>567.5800170898438</v>
+        <v>557.230224609375</v>
       </c>
       <c r="F188" t="n">
-        <v>20478300</v>
+        <v>13963600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B189" t="n">
-        <v>572.8200073242188</v>
+        <v>555.1118879211193</v>
       </c>
       <c r="C189" t="n">
-        <v>580.219970703125</v>
+        <v>555.9013039685537</v>
       </c>
       <c r="D189" t="n">
-        <v>563.0999755859375</v>
+        <v>539.7540133926082</v>
       </c>
       <c r="E189" t="n">
-        <v>577.219970703125</v>
+        <v>542.44189453125</v>
       </c>
       <c r="F189" t="n">
-        <v>28824600</v>
+        <v>16968600</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="B190" t="n">
-        <v>572.02001953125</v>
+        <v>542.9115767800729</v>
       </c>
       <c r="C190" t="n">
-        <v>575.8099975585938</v>
+        <v>556.4108722579447</v>
       </c>
       <c r="D190" t="n">
-        <v>559.8099975585938</v>
+        <v>539.9738926737891</v>
       </c>
       <c r="E190" t="n">
-        <v>563.8499755859375</v>
+        <v>549.8161010742188</v>
       </c>
       <c r="F190" t="n">
-        <v>15405500</v>
+        <v>18867700</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="B191" t="n">
-        <v>562.25</v>
+        <v>559.5583857816937</v>
       </c>
       <c r="C191" t="n">
-        <v>572.2000122070312</v>
+        <v>570.4498144711828</v>
       </c>
       <c r="D191" t="n">
-        <v>561.02001953125</v>
+        <v>557.5599629753306</v>
       </c>
       <c r="E191" t="n">
-        <v>562.2000122070312</v>
+        <v>562.1563110351562</v>
       </c>
       <c r="F191" t="n">
-        <v>13103300</v>
+        <v>15011400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="B192" t="n">
-        <v>561.8900146484375</v>
+        <v>560.4976417791106</v>
       </c>
       <c r="C192" t="n">
-        <v>569.0399780273438</v>
+        <v>565.0939897966132</v>
       </c>
       <c r="D192" t="n">
-        <v>555.5499877929688</v>
+        <v>550.9951316644288</v>
       </c>
       <c r="E192" t="n">
-        <v>557.6699829101562</v>
+        <v>562.8457641601562</v>
       </c>
       <c r="F192" t="n">
-        <v>13963600</v>
+        <v>18111100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="B193" t="n">
-        <v>555.5499877929688</v>
+        <v>607.4305787144307</v>
       </c>
       <c r="C193" t="n">
-        <v>556.3400268554688</v>
+        <v>627.784571153574</v>
       </c>
       <c r="D193" t="n">
-        <v>540.1799926757812</v>
+        <v>594.6306830487989</v>
       </c>
       <c r="E193" t="n">
-        <v>542.8699951171875</v>
+        <v>612.4266357421875</v>
       </c>
       <c r="F193" t="n">
-        <v>16968600</v>
+        <v>45536300</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46199</v>
+        <v>46205</v>
       </c>
       <c r="B194" t="n">
-        <v>543.3400268554688</v>
+        <v>607.4206544757068</v>
       </c>
       <c r="C194" t="n">
-        <v>556.8499755859375</v>
+        <v>609.5189740900589</v>
       </c>
       <c r="D194" t="n">
-        <v>540.4000244140625</v>
+        <v>579.9622828274885</v>
       </c>
       <c r="E194" t="n">
-        <v>550.25</v>
+        <v>582.4403686523438</v>
       </c>
       <c r="F194" t="n">
-        <v>18867700</v>
+        <v>21705900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B195" t="n">
-        <v>560</v>
+        <v>594.3709360150443</v>
       </c>
       <c r="C195" t="n">
-        <v>570.9000244140625</v>
+        <v>603.1040338931904</v>
       </c>
       <c r="D195" t="n">
-        <v>558</v>
+        <v>581.301233826573</v>
       </c>
       <c r="E195" t="n">
-        <v>562.5999755859375</v>
+        <v>599.8165893554688</v>
       </c>
       <c r="F195" t="n">
-        <v>15011400</v>
+        <v>17674100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B196" t="n">
-        <v>560.9400024414062</v>
+        <v>607.1109147253509</v>
       </c>
       <c r="C196" t="n">
-        <v>565.5399780273438</v>
+        <v>624.8768626804635</v>
       </c>
       <c r="D196" t="n">
-        <v>551.4299926757812</v>
+        <v>603.1839600389557</v>
       </c>
       <c r="E196" t="n">
-        <v>563.2899780273438</v>
+        <v>615.0946044921875</v>
       </c>
       <c r="F196" t="n">
-        <v>18111100</v>
+        <v>18560800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B197" t="n">
-        <v>607.9099731445312</v>
+        <v>613.9055418180343</v>
       </c>
       <c r="C197" t="n">
-        <v>628.280029296875</v>
+        <v>615.5142576272189</v>
       </c>
       <c r="D197" t="n">
-        <v>595.0999755859375</v>
+        <v>597.5384532703483</v>
       </c>
       <c r="E197" t="n">
-        <v>612.9099731445312</v>
+        <v>602.6444091796875</v>
       </c>
       <c r="F197" t="n">
-        <v>45536300</v>
+        <v>13606500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B198" t="n">
-        <v>607.9000244140625</v>
+        <v>583.529455055522</v>
       </c>
       <c r="C198" t="n">
-        <v>610</v>
+        <v>632.77062206454</v>
       </c>
       <c r="D198" t="n">
-        <v>580.4199829101562</v>
+        <v>576.6149292518581</v>
       </c>
       <c r="E198" t="n">
-        <v>582.9000244140625</v>
+        <v>630.9819946289062</v>
       </c>
       <c r="F198" t="n">
-        <v>21705900</v>
+        <v>26579700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B199" t="n">
-        <v>594.8400268554688</v>
+        <v>659.8193113874754</v>
       </c>
       <c r="C199" t="n">
-        <v>603.5800170898438</v>
+        <v>677.3254544051542</v>
       </c>
       <c r="D199" t="n">
-        <v>581.760009765625</v>
+        <v>657.491131647921</v>
       </c>
       <c r="E199" t="n">
-        <v>600.2899780273438</v>
+        <v>668.6823120117188</v>
       </c>
       <c r="F199" t="n">
-        <v>17674100</v>
+        <v>40608900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B200" t="n">
-        <v>607.5900268554688</v>
+        <v>660.858454671636</v>
       </c>
       <c r="C200" t="n">
-        <v>625.3699951171875</v>
+        <v>676.0864269737083</v>
       </c>
       <c r="D200" t="n">
-        <v>603.6599731445312</v>
+        <v>653.6841239854351</v>
       </c>
       <c r="E200" t="n">
-        <v>615.5800170898438</v>
+        <v>656.2120971679688</v>
       </c>
       <c r="F200" t="n">
-        <v>18560800</v>
+        <v>19840700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>614.3900146484375</v>
+        <v>651.4858277274717</v>
       </c>
       <c r="C201" t="n">
-        <v>616</v>
+        <v>665.9743929146624</v>
       </c>
       <c r="D201" t="n">
-        <v>598.010009765625</v>
+        <v>648.5381419230179</v>
       </c>
       <c r="E201" t="n">
-        <v>603.1199951171875</v>
+        <v>660.5186767578125</v>
       </c>
       <c r="F201" t="n">
-        <v>13606500</v>
+        <v>16748200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>583.989990234375</v>
+        <v>663.0767089741589</v>
       </c>
       <c r="C202" t="n">
-        <v>633.27001953125</v>
+        <v>685.5390243545221</v>
       </c>
       <c r="D202" t="n">
-        <v>577.0700073242188</v>
+        <v>656.1421789132482</v>
       </c>
       <c r="E202" t="n">
-        <v>631.47998046875</v>
+        <v>680.7727661132812</v>
       </c>
       <c r="F202" t="n">
-        <v>26579700</v>
+        <v>19003400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>660.3400268554688</v>
+        <v>676.7459348014426</v>
       </c>
       <c r="C203" t="n">
-        <v>677.8599853515625</v>
+        <v>681.3622866487058</v>
       </c>
       <c r="D203" t="n">
-        <v>658.010009765625</v>
+        <v>659.6393793096187</v>
       </c>
       <c r="E203" t="n">
-        <v>669.2100219726562</v>
+        <v>664.0159301757812</v>
       </c>
       <c r="F203" t="n">
-        <v>40608900</v>
+        <v>15816000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B204" t="n">
-        <v>661.3800048828125</v>
+        <v>647.1892801723585</v>
       </c>
       <c r="C204" t="n">
-        <v>676.6199951171875</v>
+        <v>651.68573177941</v>
       </c>
       <c r="D204" t="n">
-        <v>654.2000122070312</v>
+        <v>625.5063791142821</v>
       </c>
       <c r="E204" t="n">
-        <v>656.72998046875</v>
+        <v>645.5006103515625</v>
       </c>
       <c r="F204" t="n">
-        <v>19840700</v>
+        <v>22267900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B205" t="n">
-        <v>652</v>
+        <v>646.1900645769782</v>
       </c>
       <c r="C205" t="n">
-        <v>666.5</v>
+        <v>652.7848358303891</v>
       </c>
       <c r="D205" t="n">
-        <v>649.0499877929688</v>
+        <v>635.5084916103011</v>
       </c>
       <c r="E205" t="n">
-        <v>661.0399780273438</v>
+        <v>645.3406982421875</v>
       </c>
       <c r="F205" t="n">
-        <v>16748200</v>
+        <v>10225200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B206" t="n">
-        <v>663.5999755859375</v>
+        <v>653.664124760039</v>
       </c>
       <c r="C206" t="n">
-        <v>686.0800170898438</v>
+        <v>655.3627963853286</v>
       </c>
       <c r="D206" t="n">
-        <v>656.6599731445312</v>
+        <v>642.6928027946103</v>
       </c>
       <c r="E206" t="n">
-        <v>681.3099975585938</v>
+        <v>643.3023071289062</v>
       </c>
       <c r="F206" t="n">
-        <v>19003400</v>
+        <v>9140500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="B207" t="n">
-        <v>677.280029296875</v>
+        <v>647.189254956408</v>
       </c>
       <c r="C207" t="n">
-        <v>681.9000244140625</v>
+        <v>648.4882176170956</v>
       </c>
       <c r="D207" t="n">
-        <v>660.1599731445312</v>
+        <v>623.5079318845419</v>
       </c>
       <c r="E207" t="n">
-        <v>664.5399780273438</v>
+        <v>626.6754150390625</v>
       </c>
       <c r="F207" t="n">
-        <v>15816000</v>
+        <v>11019600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B208" t="n">
-        <v>647.7000122070312</v>
+        <v>607.9301851876114</v>
       </c>
       <c r="C208" t="n">
-        <v>652.2000122070312</v>
+        <v>614.1653155952538</v>
       </c>
       <c r="D208" t="n">
-        <v>626</v>
+        <v>596.7490071058414</v>
       </c>
       <c r="E208" t="n">
-        <v>646.010009765625</v>
+        <v>605.6220092773438</v>
       </c>
       <c r="F208" t="n">
-        <v>22267900</v>
+        <v>15494800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B209" t="n">
-        <v>646.7000122070312</v>
+        <v>604.8226548171024</v>
       </c>
       <c r="C209" t="n">
-        <v>653.2999877929688</v>
+        <v>609.4989569016461</v>
       </c>
       <c r="D209" t="n">
-        <v>636.010009765625</v>
+        <v>593.9812354037057</v>
       </c>
       <c r="E209" t="n">
-        <v>645.8499755859375</v>
+        <v>594.7206420898438</v>
       </c>
       <c r="F209" t="n">
-        <v>10225200</v>
+        <v>11503500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B210" t="n">
-        <v>654.1799926757812</v>
+        <v>606.7411202287035</v>
       </c>
       <c r="C210" t="n">
-        <v>655.8800048828125</v>
+        <v>610.7779733376527</v>
       </c>
       <c r="D210" t="n">
-        <v>643.2000122070312</v>
+        <v>592.6622656813121</v>
       </c>
       <c r="E210" t="n">
-        <v>643.8099975585938</v>
+        <v>593.4016723632812</v>
       </c>
       <c r="F210" t="n">
-        <v>9140500</v>
+        <v>11195300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B211" t="n">
-        <v>647.7000122070312</v>
+        <v>596.3493616660036</v>
       </c>
       <c r="C211" t="n">
-        <v>649</v>
+        <v>600.5260580457825</v>
       </c>
       <c r="D211" t="n">
-        <v>624</v>
+        <v>586.5370982909723</v>
       </c>
       <c r="E211" t="n">
-        <v>627.1699829101562</v>
+        <v>592.9420166015625</v>
       </c>
       <c r="F211" t="n">
-        <v>11019600</v>
+        <v>12009300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="B212" t="n">
-        <v>608.4099731445312</v>
+        <v>592.7821833537371</v>
       </c>
       <c r="C212" t="n">
-        <v>614.6500244140625</v>
+        <v>599.4968549179539</v>
       </c>
       <c r="D212" t="n">
-        <v>597.219970703125</v>
+        <v>581.7608519604674</v>
       </c>
       <c r="E212" t="n">
-        <v>606.0999755859375</v>
+        <v>585.148193359375</v>
       </c>
       <c r="F212" t="n">
-        <v>15494800</v>
+        <v>22371100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B213" t="n">
-        <v>605.2999877929688</v>
+        <v>525.58522592167</v>
       </c>
       <c r="C213" t="n">
-        <v>609.97998046875</v>
+        <v>539.4542858116451</v>
       </c>
       <c r="D213" t="n">
-        <v>594.4500122070312</v>
+        <v>524.0764068649972</v>
       </c>
       <c r="E213" t="n">
-        <v>595.1900024414062</v>
+        <v>538.60498046875</v>
       </c>
       <c r="F213" t="n">
-        <v>11503500</v>
+        <v>42271500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B214" t="n">
-        <v>607.219970703125</v>
+        <v>543.171288392182</v>
       </c>
       <c r="C214" t="n">
-        <v>611.260009765625</v>
+        <v>557.8897136701136</v>
       </c>
       <c r="D214" t="n">
-        <v>593.1300048828125</v>
+        <v>539.7939490076644</v>
       </c>
       <c r="E214" t="n">
-        <v>593.8699951171875</v>
+        <v>556.27099609375</v>
       </c>
       <c r="F214" t="n">
-        <v>11195300</v>
+        <v>24261500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B215" t="n">
-        <v>596.8200073242188</v>
+        <v>561.7966164985271</v>
       </c>
       <c r="C215" t="n">
-        <v>601</v>
+        <v>597.0488245114987</v>
       </c>
       <c r="D215" t="n">
-        <v>587</v>
+        <v>558.9188827428958</v>
       </c>
       <c r="E215" t="n">
-        <v>593.4099731445312</v>
+        <v>589.7745361328125</v>
       </c>
       <c r="F215" t="n">
-        <v>12009300</v>
+        <v>25938100</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B216" t="n">
-        <v>593.25</v>
+        <v>581.0414552494501</v>
       </c>
       <c r="C216" t="n">
-        <v>599.969970703125</v>
+        <v>592.32253050782</v>
       </c>
       <c r="D216" t="n">
-        <v>582.219970703125</v>
+        <v>577.794018053301</v>
       </c>
       <c r="E216" t="n">
-        <v>585.6099853515625</v>
+        <v>587.4763793945312</v>
       </c>
       <c r="F216" t="n">
-        <v>22371100</v>
+        <v>17959200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B217" t="n">
-        <v>526</v>
+        <v>599.9865089938204</v>
       </c>
       <c r="C217" t="n">
-        <v>539.8800048828125</v>
+        <v>600.5260612032997</v>
       </c>
       <c r="D217" t="n">
-        <v>524.489990234375</v>
+        <v>579.6625219517506</v>
       </c>
       <c r="E217" t="n">
-        <v>539.030029296875</v>
+        <v>588.3057250976562</v>
       </c>
       <c r="F217" t="n">
-        <v>42271500</v>
+        <v>14897200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B218" t="n">
-        <v>543.5999755859375</v>
+        <v>586.487189429669</v>
       </c>
       <c r="C218" t="n">
-        <v>558.3300170898438</v>
+        <v>594.8405827519979</v>
       </c>
       <c r="D218" t="n">
-        <v>540.219970703125</v>
+        <v>585.5379263278069</v>
       </c>
       <c r="E218" t="n">
-        <v>556.7100219726562</v>
+        <v>589.4348754882812</v>
       </c>
       <c r="F218" t="n">
-        <v>24261500</v>
+        <v>11811500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B219" t="n">
-        <v>562.239990234375</v>
+        <v>585.1781899072663</v>
       </c>
       <c r="C219" t="n">
-        <v>597.52001953125</v>
+        <v>598.2678350979388</v>
       </c>
       <c r="D219" t="n">
-        <v>559.3599853515625</v>
+        <v>585.1581861630435</v>
       </c>
       <c r="E219" t="n">
-        <v>590.239990234375</v>
+        <v>591.633056640625</v>
       </c>
       <c r="F219" t="n">
-        <v>25938100</v>
+        <v>11250300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B220" t="n">
-        <v>581.5</v>
+        <v>598.657568915248</v>
       </c>
       <c r="C220" t="n">
-        <v>592.7899780273438</v>
+        <v>607.7304260788247</v>
       </c>
       <c r="D220" t="n">
-        <v>578.25</v>
+        <v>591.5631919202813</v>
       </c>
       <c r="E220" t="n">
-        <v>587.9400024414062</v>
+        <v>594.4508666992188</v>
       </c>
       <c r="F220" t="n">
-        <v>17959200</v>
+        <v>14967300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B221" t="n">
-        <v>600.4600219726562</v>
+        <v>597.5284100969216</v>
       </c>
       <c r="C221" t="n">
-        <v>601</v>
+        <v>611.9470231090784</v>
       </c>
       <c r="D221" t="n">
-        <v>580.1199951171875</v>
+        <v>592.9320621063698</v>
       </c>
       <c r="E221" t="n">
-        <v>588.77001953125</v>
+        <v>598.6475219726562</v>
       </c>
       <c r="F221" t="n">
-        <v>14897200</v>
+        <v>13146900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B222" t="n">
-        <v>586.9500122070312</v>
+        <v>600.5960026412422</v>
       </c>
       <c r="C222" t="n">
-        <v>595.3099975585938</v>
+        <v>604.023290419805</v>
       </c>
       <c r="D222" t="n">
-        <v>586</v>
+        <v>577.7540447074138</v>
       </c>
       <c r="E222" t="n">
-        <v>589.9000244140625</v>
+        <v>578.3934936523438</v>
       </c>
       <c r="F222" t="n">
-        <v>11811500</v>
+        <v>16186900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B223" t="n">
-        <v>585.6400146484375</v>
+        <v>580.2520897369063</v>
       </c>
       <c r="C223" t="n">
-        <v>598.739990234375</v>
+        <v>595.3801043917661</v>
       </c>
       <c r="D223" t="n">
-        <v>585.6199951171875</v>
+        <v>578.9331233348041</v>
       </c>
       <c r="E223" t="n">
-        <v>592.0999755859375</v>
+        <v>594.5007934570312</v>
       </c>
       <c r="F223" t="n">
-        <v>11250300</v>
+        <v>11164200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B224" t="n">
-        <v>599.1300048828125</v>
+        <v>596.5092089028919</v>
       </c>
       <c r="C224" t="n">
-        <v>608.2100219726562</v>
+        <v>601.3853654698224</v>
       </c>
       <c r="D224" t="n">
-        <v>592.030029296875</v>
+        <v>588.8252707092146</v>
       </c>
       <c r="E224" t="n">
-        <v>594.9199829101562</v>
+        <v>589.3848266601562</v>
       </c>
       <c r="F224" t="n">
-        <v>14967300</v>
+        <v>8758000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B225" t="n">
-        <v>598</v>
+        <v>589.2849441761664</v>
       </c>
       <c r="C225" t="n">
-        <v>612.4299926757812</v>
+        <v>589.774548021712</v>
       </c>
       <c r="D225" t="n">
-        <v>593.4000244140625</v>
+        <v>564.3046582848494</v>
       </c>
       <c r="E225" t="n">
-        <v>599.1199951171875</v>
+        <v>568.5213012695312</v>
       </c>
       <c r="F225" t="n">
-        <v>13146900</v>
+        <v>17225600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B226" t="n">
-        <v>601.0700073242188</v>
+        <v>557.0403796583744</v>
       </c>
       <c r="C226" t="n">
-        <v>604.5</v>
+        <v>560.2178647510921</v>
       </c>
       <c r="D226" t="n">
-        <v>578.2100219726562</v>
+        <v>542.7816737373303</v>
       </c>
       <c r="E226" t="n">
-        <v>578.8499755859375</v>
+        <v>543.2412719726562</v>
       </c>
       <c r="F226" t="n">
-        <v>16186900</v>
+        <v>27094900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B227" t="n">
-        <v>580.7100219726562</v>
+        <v>540.9131223962278</v>
       </c>
       <c r="C227" t="n">
-        <v>595.8499755859375</v>
+        <v>553.6330639150415</v>
       </c>
       <c r="D227" t="n">
-        <v>579.3900146484375</v>
+        <v>536.8463247077087</v>
       </c>
       <c r="E227" t="n">
-        <v>594.969970703125</v>
+        <v>545.5994262695312</v>
       </c>
       <c r="F227" t="n">
-        <v>11164200</v>
+        <v>16971700</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B228" t="n">
-        <v>596.97998046875</v>
+        <v>546.5187091013889</v>
       </c>
       <c r="C228" t="n">
-        <v>601.8599853515625</v>
+        <v>549.5562899225255</v>
       </c>
       <c r="D228" t="n">
-        <v>589.2899780273438</v>
+        <v>538.8847190657524</v>
       </c>
       <c r="E228" t="n">
-        <v>589.8499755859375</v>
+        <v>545.3995971679688</v>
       </c>
       <c r="F228" t="n">
-        <v>8758000</v>
+        <v>13872200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B229" t="n">
-        <v>589.75</v>
+        <v>546.4587335768297</v>
       </c>
       <c r="C229" t="n">
-        <v>590.239990234375</v>
+        <v>553.4332095869578</v>
       </c>
       <c r="D229" t="n">
-        <v>564.75</v>
+        <v>542.8015857242297</v>
       </c>
       <c r="E229" t="n">
-        <v>568.969970703125</v>
+        <v>549.4663696289062</v>
       </c>
       <c r="F229" t="n">
-        <v>17225600</v>
+        <v>13848000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B230" t="n">
-        <v>557.47998046875</v>
+        <v>549.7661710202622</v>
       </c>
       <c r="C230" t="n">
-        <v>560.6599731445312</v>
+        <v>560.9772946036173</v>
       </c>
       <c r="D230" t="n">
-        <v>543.2100219726562</v>
+        <v>545.8692218355393</v>
       </c>
       <c r="E230" t="n">
-        <v>543.6699829101562</v>
+        <v>558.5792236328125</v>
       </c>
       <c r="F230" t="n">
-        <v>27094900</v>
+        <v>12990600</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B231" t="n">
-        <v>541.3400268554688</v>
+        <v>563.4353464162</v>
       </c>
       <c r="C231" t="n">
-        <v>554.0700073242188</v>
+        <v>570.3498724402046</v>
       </c>
       <c r="D231" t="n">
-        <v>537.27001953125</v>
+        <v>560.9573215839381</v>
       </c>
       <c r="E231" t="n">
-        <v>546.030029296875</v>
+        <v>569.6004638671875</v>
       </c>
       <c r="F231" t="n">
-        <v>16971700</v>
+        <v>9769100</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B232" t="n">
-        <v>546.9500122070312</v>
+        <v>589.8444773654404</v>
       </c>
       <c r="C232" t="n">
-        <v>549.989990234375</v>
+        <v>592.8721171723366</v>
       </c>
       <c r="D232" t="n">
-        <v>539.3099975585938</v>
+        <v>561.4369046651577</v>
       </c>
       <c r="E232" t="n">
-        <v>545.8300170898438</v>
+        <v>575.6856689453125</v>
       </c>
       <c r="F232" t="n">
-        <v>13872200</v>
+        <v>31416300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B233" t="n">
-        <v>546.8900146484375</v>
+        <v>576.0253592943615</v>
       </c>
       <c r="C233" t="n">
-        <v>553.8699951171875</v>
+        <v>587.9260010338789</v>
       </c>
       <c r="D233" t="n">
-        <v>543.22998046875</v>
+        <v>567.1723610665189</v>
       </c>
       <c r="E233" t="n">
-        <v>549.9000244140625</v>
+        <v>570.6495971679688</v>
       </c>
       <c r="F233" t="n">
-        <v>13848000</v>
+        <v>15221400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B234" t="n">
-        <v>550.2000122070312</v>
+        <v>571.0992793335739</v>
       </c>
       <c r="C234" t="n">
-        <v>561.4199829101562</v>
+        <v>588.7253835559844</v>
       </c>
       <c r="D234" t="n">
-        <v>546.2999877929688</v>
+        <v>570.5497252457161</v>
       </c>
       <c r="E234" t="n">
-        <v>559.02001953125</v>
+        <v>577.564208984375</v>
       </c>
       <c r="F234" t="n">
-        <v>12990600</v>
+        <v>16042400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B235" t="n">
-        <v>563.8800048828125</v>
+        <v>577.1744781551006</v>
       </c>
       <c r="C235" t="n">
-        <v>570.7999877929688</v>
+        <v>578.2236379136884</v>
       </c>
       <c r="D235" t="n">
-        <v>561.4000244140625</v>
+        <v>568.6911832402849</v>
       </c>
       <c r="E235" t="n">
-        <v>570.0499877929688</v>
+        <v>571.888671875</v>
       </c>
       <c r="F235" t="n">
-        <v>9769100</v>
+        <v>13383800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B236" t="n">
-        <v>590.3099975585938</v>
+        <v>557.9096596695957</v>
       </c>
       <c r="C236" t="n">
-        <v>593.3400268554688</v>
+        <v>584.4887194481862</v>
       </c>
       <c r="D236" t="n">
-        <v>561.8800048828125</v>
+        <v>555.6614340241316</v>
       </c>
       <c r="E236" t="n">
-        <v>576.1400146484375</v>
+        <v>578.083740234375</v>
       </c>
       <c r="F236" t="n">
-        <v>31416300</v>
+        <v>15796900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B237" t="n">
-        <v>576.47998046875</v>
+        <v>578.3335366296732</v>
       </c>
       <c r="C237" t="n">
-        <v>588.3900146484375</v>
+        <v>599.9065373056851</v>
       </c>
       <c r="D237" t="n">
-        <v>567.6199951171875</v>
+        <v>576.5449702025707</v>
       </c>
       <c r="E237" t="n">
-        <v>571.0999755859375</v>
+        <v>592.3824462890625</v>
       </c>
       <c r="F237" t="n">
-        <v>15221400</v>
+        <v>16552700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B238" t="n">
-        <v>571.5499877929688</v>
+        <v>604.0133041368691</v>
       </c>
       <c r="C238" t="n">
-        <v>589.1900024414062</v>
+        <v>618.9715308723809</v>
       </c>
       <c r="D238" t="n">
-        <v>571</v>
+        <v>603.8733999005765</v>
       </c>
       <c r="E238" t="n">
-        <v>578.02001953125</v>
+        <v>610.1984252929688</v>
       </c>
       <c r="F238" t="n">
-        <v>16042400</v>
+        <v>19737100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B239" t="n">
-        <v>577.6300048828125</v>
+        <v>611.8670721034152</v>
       </c>
       <c r="C239" t="n">
-        <v>578.6799926757812</v>
+        <v>616.9730886717387</v>
       </c>
       <c r="D239" t="n">
-        <v>569.1400146484375</v>
+        <v>604.7926993516937</v>
       </c>
       <c r="E239" t="n">
-        <v>572.3400268554688</v>
+        <v>616.2836303710938</v>
       </c>
       <c r="F239" t="n">
-        <v>13383800</v>
+        <v>15966200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B240" t="n">
-        <v>558.3499755859375</v>
+        <v>615.7241045276966</v>
       </c>
       <c r="C240" t="n">
-        <v>584.9500122070312</v>
+        <v>624.3072966603136</v>
       </c>
       <c r="D240" t="n">
-        <v>556.0999755859375</v>
+        <v>609.2591747857786</v>
       </c>
       <c r="E240" t="n">
-        <v>578.5399780273438</v>
+        <v>612.9962158203125</v>
       </c>
       <c r="F240" t="n">
-        <v>15796900</v>
+        <v>18909700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B241" t="n">
-        <v>578.7899780273438</v>
+        <v>648.1284941622514</v>
       </c>
       <c r="C241" t="n">
-        <v>600.3800048828125</v>
+        <v>657.3411939542544</v>
       </c>
       <c r="D241" t="n">
-        <v>577</v>
+        <v>638.056426220049</v>
       </c>
       <c r="E241" t="n">
-        <v>592.8499755859375</v>
+        <v>653.1744995117188</v>
       </c>
       <c r="F241" t="n">
-        <v>16552700</v>
+        <v>35900700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B242" t="n">
-        <v>604.489990234375</v>
+        <v>653.1945472302951</v>
       </c>
       <c r="C242" t="n">
-        <v>619.4600219726562</v>
+        <v>662.9768054946985</v>
       </c>
       <c r="D242" t="n">
-        <v>604.3499755859375</v>
+        <v>641.6336632885306</v>
       </c>
       <c r="E242" t="n">
-        <v>610.6799926757812</v>
+        <v>643.8718872070312</v>
       </c>
       <c r="F242" t="n">
-        <v>19737100</v>
+        <v>21531900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B243" t="n">
-        <v>612.3499755859375</v>
+        <v>652.9947023490145</v>
       </c>
       <c r="C243" t="n">
-        <v>617.4600219726562</v>
+        <v>663.716221985592</v>
       </c>
       <c r="D243" t="n">
-        <v>605.27001953125</v>
+        <v>645.6904688887529</v>
       </c>
       <c r="E243" t="n">
-        <v>616.77001953125</v>
+        <v>647.51904296875</v>
       </c>
       <c r="F243" t="n">
-        <v>15966200</v>
+        <v>16925000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B244" t="n">
-        <v>616.2100219726562</v>
+        <v>657.311302577125</v>
       </c>
       <c r="C244" t="n">
-        <v>624.7999877929688</v>
+        <v>668.072768706455</v>
       </c>
       <c r="D244" t="n">
-        <v>609.739990234375</v>
+        <v>648.708045415434</v>
       </c>
       <c r="E244" t="n">
-        <v>613.47998046875</v>
+        <v>665.0751342773438</v>
       </c>
       <c r="F244" t="n">
-        <v>18909700</v>
+        <v>19332300</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B245" t="n">
-        <v>648.6400146484375</v>
+        <v>658.7801108800835</v>
       </c>
       <c r="C245" t="n">
-        <v>657.8599853515625</v>
+        <v>678.3346866933342</v>
       </c>
       <c r="D245" t="n">
-        <v>638.5599975585938</v>
+        <v>655.6825797136325</v>
       </c>
       <c r="E245" t="n">
-        <v>653.6900024414062</v>
+        <v>669.7114868164062</v>
       </c>
       <c r="F245" t="n">
-        <v>35900700</v>
+        <v>19502800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B246" t="n">
-        <v>653.7100219726562</v>
+        <v>679.3738238485387</v>
       </c>
       <c r="C246" t="n">
-        <v>663.5</v>
+        <v>684.7695900234191</v>
       </c>
       <c r="D246" t="n">
-        <v>642.1400146484375</v>
+        <v>671.3801323225093</v>
       </c>
       <c r="E246" t="n">
-        <v>644.3800048828125</v>
+        <v>672.779052734375</v>
       </c>
       <c r="F246" t="n">
-        <v>21531900</v>
+        <v>17217800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B247" t="n">
-        <v>653.510009765625</v>
+        <v>681.9018750257407</v>
       </c>
       <c r="C247" t="n">
-        <v>664.239990234375</v>
+        <v>682.6612854975235</v>
       </c>
       <c r="D247" t="n">
-        <v>646.2000122070312</v>
+        <v>666.5239959332205</v>
       </c>
       <c r="E247" t="n">
-        <v>648.030029296875</v>
+        <v>681.77197265625</v>
       </c>
       <c r="F247" t="n">
-        <v>16925000</v>
+        <v>15928000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B248" t="n">
-        <v>657.8300170898438</v>
+        <v>688.0769980771287</v>
       </c>
       <c r="C248" t="n">
-        <v>668.5999755859375</v>
+        <v>689.6058209010791</v>
       </c>
       <c r="D248" t="n">
-        <v>649.219970703125</v>
+        <v>660.278927643704</v>
       </c>
       <c r="E248" t="n">
-        <v>665.5999755859375</v>
+        <v>665.2250366210938</v>
       </c>
       <c r="F248" t="n">
-        <v>19332300</v>
+        <v>27596400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,25 +6891,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B249" t="n">
-        <v>659.2999877929688</v>
+        <v>680.2999877929688</v>
       </c>
       <c r="C249" t="n">
-        <v>678.8699951171875</v>
+        <v>753</v>
       </c>
       <c r="D249" t="n">
-        <v>656.2000122070312</v>
+        <v>679.5999755859375</v>
       </c>
       <c r="E249" t="n">
-        <v>670.239990234375</v>
+        <v>741.25</v>
       </c>
       <c r="F249" t="n">
-        <v>19502800</v>
+        <v>48720500</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B250" t="n">
-        <v>679.9099731445312</v>
+        <v>731.4000244140625</v>
       </c>
       <c r="C250" t="n">
-        <v>685.3099975585938</v>
+        <v>757.27001953125</v>
       </c>
       <c r="D250" t="n">
-        <v>671.9099731445312</v>
+        <v>730</v>
       </c>
       <c r="E250" t="n">
-        <v>673.3099975585938</v>
+        <v>736.5999755859375</v>
       </c>
       <c r="F250" t="n">
-        <v>17217800</v>
+        <v>28122100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B251" t="n">
-        <v>682.4400024414062</v>
+        <v>747.5999755859375</v>
       </c>
       <c r="C251" t="n">
-        <v>683.2000122070312</v>
+        <v>763.9000244140625</v>
       </c>
       <c r="D251" t="n">
-        <v>667.0499877929688</v>
+        <v>739.510009765625</v>
       </c>
       <c r="E251" t="n">
-        <v>682.3099975585938</v>
+        <v>744.0999755859375</v>
       </c>
       <c r="F251" t="n">
-        <v>15928000</v>
+        <v>30829200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B252" t="n">
-        <v>688.6199951171875</v>
+        <v>744.3599853515625</v>
       </c>
       <c r="C252" t="n">
-        <v>690.1500244140625</v>
+        <v>779.8200073242188</v>
       </c>
       <c r="D252" t="n">
-        <v>660.7999877929688</v>
+        <v>743.010009765625</v>
       </c>
       <c r="E252" t="n">
-        <v>665.75</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="F252" t="n">
-        <v>27548000</v>
+        <v>34744400</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>665.75</v>
+        <v>777.59</v>
       </c>
       <c r="D2" t="n">
-        <v>682.3099999999999</v>
+        <v>744.1</v>
       </c>
       <c r="E2" t="n">
-        <v>686.8200000000001</v>
+        <v>744.35</v>
       </c>
       <c r="F2" t="n">
-        <v>690.15</v>
+        <v>779.8192</v>
       </c>
       <c r="G2" t="n">
-        <v>660.8</v>
+        <v>743.006</v>
       </c>
       <c r="H2" t="n">
-        <v>27394770</v>
+        <v>34646511</v>
       </c>
       <c r="I2" t="n">
-        <v>18162719</v>
+        <v>19629526</v>
       </c>
       <c r="J2" t="n">
-        <v>1696002211840</v>
+        <v>1980915384320</v>
       </c>
       <c r="K2" t="n">
-        <v>25.704634</v>
+        <v>28.011168</v>
       </c>
       <c r="L2" t="n">
-        <v>19.043377</v>
+        <v>22.262783</v>
       </c>
       <c r="M2" t="n">
-        <v>25.9</v>
+        <v>27.76</v>
       </c>
       <c r="N2" t="n">
-        <v>785.73</v>
+        <v>779.8200000000001</v>
       </c>
       <c r="O2" t="n">
         <v>520.26</v>
@@ -10818,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.493855</v>
+        <v>7.5847645</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1718060318720</v>
+        <v>2002973360128</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:17</t>
+          <t>2026-09-25 14:29:04</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B2" t="n">
-        <v>750.9028646268723</v>
+        <v>747.4645278033088</v>
       </c>
       <c r="C2" t="n">
-        <v>754.2116481824468</v>
+        <v>749.387995888731</v>
       </c>
       <c r="D2" t="n">
-        <v>742.0329280425029</v>
+        <v>734.8572684361654</v>
       </c>
       <c r="E2" t="n">
-        <v>746.378173828125</v>
+        <v>741.2356567382812</v>
       </c>
       <c r="F2" t="n">
-        <v>10591100</v>
+        <v>9696300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B3" t="n">
-        <v>747.4645893513656</v>
+        <v>746.188925117424</v>
       </c>
       <c r="C3" t="n">
-        <v>749.3880575951708</v>
+        <v>748.242019689358</v>
       </c>
       <c r="D3" t="n">
-        <v>734.8573289461095</v>
+        <v>736.6513300027099</v>
       </c>
       <c r="E3" t="n">
-        <v>741.2357177734375</v>
+        <v>740.886962890625</v>
       </c>
       <c r="F3" t="n">
-        <v>9696300</v>
+        <v>9246800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>746.1888021735474</v>
+        <v>739.7407284541446</v>
       </c>
       <c r="C4" t="n">
-        <v>748.2418964072087</v>
+        <v>740.4582652037509</v>
       </c>
       <c r="D4" t="n">
-        <v>736.6512086302703</v>
+        <v>723.8446373138524</v>
       </c>
       <c r="E4" t="n">
-        <v>740.8868408203125</v>
+        <v>731.8973388671875</v>
       </c>
       <c r="F4" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>739.7407284541446</v>
+        <v>719.050911987213</v>
       </c>
       <c r="C5" t="n">
-        <v>740.4582652037509</v>
+        <v>719.4096803677126</v>
       </c>
       <c r="D5" t="n">
-        <v>723.8446373138524</v>
+        <v>707.7991010033351</v>
       </c>
       <c r="E5" t="n">
-        <v>731.8973388671875</v>
+        <v>714.9149780273438</v>
       </c>
       <c r="F5" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>719.0508505989554</v>
+        <v>720.1373033168862</v>
       </c>
       <c r="C6" t="n">
-        <v>719.4096189488256</v>
+        <v>725.3097607250153</v>
       </c>
       <c r="D6" t="n">
-        <v>707.7990405756898</v>
+        <v>715.7123105005168</v>
       </c>
       <c r="E6" t="n">
-        <v>714.9149169921875</v>
+        <v>724.5921630859375</v>
       </c>
       <c r="F6" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>720.1372426569798</v>
+        <v>727.1634377305112</v>
       </c>
       <c r="C7" t="n">
-        <v>725.309699629413</v>
+        <v>728.528801479838</v>
       </c>
       <c r="D7" t="n">
-        <v>715.7122502133443</v>
+        <v>707.7791777004747</v>
       </c>
       <c r="E7" t="n">
-        <v>724.5921020507812</v>
+        <v>708.1578979492188</v>
       </c>
       <c r="F7" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B8" t="n">
-        <v>727.1633750572937</v>
+        <v>702.8060849901855</v>
       </c>
       <c r="C8" t="n">
-        <v>728.5287386889415</v>
+        <v>714.456569002901</v>
       </c>
       <c r="D8" t="n">
-        <v>707.7791166979599</v>
+        <v>688.1757185011091</v>
       </c>
       <c r="E8" t="n">
-        <v>708.1578369140625</v>
+        <v>713.2406616210938</v>
       </c>
       <c r="F8" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B9" t="n">
-        <v>702.8060849901855</v>
+        <v>715.2937017364883</v>
       </c>
       <c r="C9" t="n">
-        <v>714.456569002901</v>
+        <v>716.0710941262779</v>
       </c>
       <c r="D9" t="n">
-        <v>688.1757185011091</v>
+        <v>703.3641957962709</v>
       </c>
       <c r="E9" t="n">
-        <v>713.2406616210938</v>
+        <v>710.66943359375</v>
       </c>
       <c r="F9" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B10" t="n">
-        <v>715.2936403041813</v>
+        <v>711.0380347862832</v>
       </c>
       <c r="C10" t="n">
-        <v>716.0710326272052</v>
+        <v>717.2170864646216</v>
       </c>
       <c r="D10" t="n">
-        <v>703.3641353885179</v>
+        <v>705.4170874694764</v>
       </c>
       <c r="E10" t="n">
-        <v>710.6693725585938</v>
+        <v>715.4132080078125</v>
       </c>
       <c r="F10" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B11" t="n">
-        <v>711.0381561100638</v>
+        <v>715.8517801132227</v>
       </c>
       <c r="C11" t="n">
-        <v>717.2172088427283</v>
+        <v>731.0302734375</v>
       </c>
       <c r="D11" t="n">
-        <v>705.4172078341599</v>
+        <v>710.0314963104157</v>
       </c>
       <c r="E11" t="n">
-        <v>715.413330078125</v>
+        <v>731.0302734375</v>
       </c>
       <c r="F11" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B12" t="n">
-        <v>715.8518398810967</v>
+        <v>728.4490335307075</v>
       </c>
       <c r="C12" t="n">
-        <v>731.0303344726562</v>
+        <v>732.784364410351</v>
       </c>
       <c r="D12" t="n">
-        <v>710.0315555923428</v>
+        <v>702.1283419878271</v>
       </c>
       <c r="E12" t="n">
-        <v>731.0303344726562</v>
+        <v>702.9156494140625</v>
       </c>
       <c r="F12" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B13" t="n">
-        <v>728.4490335307075</v>
+        <v>710.5996089558437</v>
       </c>
       <c r="C13" t="n">
-        <v>732.784364410351</v>
+        <v>717.5061741064447</v>
       </c>
       <c r="D13" t="n">
-        <v>702.1283419878271</v>
+        <v>705.2477676379041</v>
       </c>
       <c r="E13" t="n">
-        <v>702.9156494140625</v>
+        <v>713.280517578125</v>
       </c>
       <c r="F13" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B14" t="n">
-        <v>710.5995481500918</v>
+        <v>705.3873404797914</v>
       </c>
       <c r="C14" t="n">
-        <v>717.5061127097006</v>
+        <v>713.1310322093289</v>
       </c>
       <c r="D14" t="n">
-        <v>705.2477072901073</v>
+        <v>696.9658939978091</v>
       </c>
       <c r="E14" t="n">
-        <v>713.2804565429688</v>
+        <v>706.25439453125</v>
       </c>
       <c r="F14" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B15" t="n">
-        <v>705.3872795195668</v>
+        <v>714.6358727912688</v>
       </c>
       <c r="C15" t="n">
-        <v>713.1309705798873</v>
+        <v>721.4527759491865</v>
       </c>
       <c r="D15" t="n">
-        <v>696.9658337653736</v>
+        <v>707.1114088212217</v>
       </c>
       <c r="E15" t="n">
-        <v>706.2543334960938</v>
+        <v>715.1242065429688</v>
       </c>
       <c r="F15" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B16" t="n">
-        <v>714.6358727912688</v>
+        <v>715.1242355877501</v>
       </c>
       <c r="C16" t="n">
-        <v>721.4527759491865</v>
+        <v>723.0373960268438</v>
       </c>
       <c r="D16" t="n">
-        <v>707.1114088212217</v>
+        <v>701.5004654735715</v>
       </c>
       <c r="E16" t="n">
-        <v>715.1242065429688</v>
+        <v>709.6627807617188</v>
       </c>
       <c r="F16" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B17" t="n">
-        <v>715.1242355877501</v>
+        <v>704.6896374063629</v>
       </c>
       <c r="C17" t="n">
-        <v>723.0373960268438</v>
+        <v>716.1108563950927</v>
       </c>
       <c r="D17" t="n">
-        <v>701.5004654735715</v>
+        <v>703.7328609179003</v>
       </c>
       <c r="E17" t="n">
-        <v>709.6627807617188</v>
+        <v>714.496337890625</v>
       </c>
       <c r="F17" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B18" t="n">
-        <v>704.6896374063629</v>
+        <v>718.7519624447335</v>
       </c>
       <c r="C18" t="n">
-        <v>716.1108563950927</v>
+        <v>731.2894517891565</v>
       </c>
       <c r="D18" t="n">
-        <v>703.7328609179003</v>
+        <v>717.7453670972193</v>
       </c>
       <c r="E18" t="n">
-        <v>714.496337890625</v>
+        <v>729.69482421875</v>
       </c>
       <c r="F18" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B19" t="n">
-        <v>718.7519624447335</v>
+        <v>733.5318410857864</v>
       </c>
       <c r="C19" t="n">
-        <v>731.2894517891565</v>
+        <v>736.0034377690635</v>
       </c>
       <c r="D19" t="n">
-        <v>717.7453670972193</v>
+        <v>726.2863984755653</v>
       </c>
       <c r="E19" t="n">
-        <v>729.69482421875</v>
+        <v>730.7911376953125</v>
       </c>
       <c r="F19" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B20" t="n">
-        <v>733.5318410857864</v>
+        <v>731.3492880397093</v>
       </c>
       <c r="C20" t="n">
-        <v>736.0034377690635</v>
+        <v>738.0963605372498</v>
       </c>
       <c r="D20" t="n">
-        <v>726.2863984755653</v>
+        <v>721.5824293281937</v>
       </c>
       <c r="E20" t="n">
-        <v>730.7911376953125</v>
+        <v>730.9306640625</v>
       </c>
       <c r="F20" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B21" t="n">
-        <v>731.3492269695964</v>
+        <v>732.2163225390138</v>
       </c>
       <c r="C21" t="n">
-        <v>738.0962989037338</v>
+        <v>739.9002195728755</v>
       </c>
       <c r="D21" t="n">
-        <v>721.5823690736463</v>
+        <v>730.6216949207216</v>
       </c>
       <c r="E21" t="n">
-        <v>730.9306030273438</v>
+        <v>731.5186767578125</v>
       </c>
       <c r="F21" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B22" t="n">
-        <v>732.2162614456487</v>
+        <v>734.2991918313108</v>
       </c>
       <c r="C22" t="n">
-        <v>739.900157838395</v>
+        <v>738.7042934120783</v>
       </c>
       <c r="D22" t="n">
-        <v>730.6216339604061</v>
+        <v>728.6783045992579</v>
       </c>
       <c r="E22" t="n">
-        <v>731.5186157226562</v>
+        <v>735.8638916015625</v>
       </c>
       <c r="F22" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B23" t="n">
-        <v>734.2991309259364</v>
+        <v>747.195457385242</v>
       </c>
       <c r="C23" t="n">
-        <v>738.704232141329</v>
+        <v>753.1951257515892</v>
       </c>
       <c r="D23" t="n">
-        <v>728.6782441600997</v>
+        <v>745.4813011827554</v>
       </c>
       <c r="E23" t="n">
-        <v>735.8638305664062</v>
+        <v>748.2817993164062</v>
       </c>
       <c r="F23" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B24" t="n">
-        <v>747.195457385242</v>
+        <v>750.0856988126538</v>
       </c>
       <c r="C24" t="n">
-        <v>753.1951257515892</v>
+        <v>755.8362124836232</v>
       </c>
       <c r="D24" t="n">
-        <v>745.4813011827554</v>
+        <v>742.9997491476457</v>
       </c>
       <c r="E24" t="n">
-        <v>748.2817993164062</v>
+        <v>748.8997192382812</v>
       </c>
       <c r="F24" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B25" t="n">
-        <v>750.0856988126538</v>
+        <v>752.1985723967003</v>
       </c>
       <c r="C25" t="n">
-        <v>755.8362124836232</v>
+        <v>756.5936376548974</v>
       </c>
       <c r="D25" t="n">
-        <v>742.9997491476457</v>
+        <v>739.9999593719286</v>
       </c>
       <c r="E25" t="n">
-        <v>748.8997192382812</v>
+        <v>749.1289672851562</v>
       </c>
       <c r="F25" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B26" t="n">
-        <v>752.1985111114485</v>
+        <v>666.8879125335289</v>
       </c>
       <c r="C26" t="n">
-        <v>756.5935760115584</v>
+        <v>678.6579855089774</v>
       </c>
       <c r="D26" t="n">
-        <v>739.9998990805568</v>
+        <v>647.9720344844721</v>
       </c>
       <c r="E26" t="n">
-        <v>749.12890625</v>
+        <v>664.2169189453125</v>
       </c>
       <c r="F26" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B27" t="n">
-        <v>666.8879125335289</v>
+        <v>672.22980228556</v>
       </c>
       <c r="C27" t="n">
-        <v>678.6579855089774</v>
+        <v>672.6085225469975</v>
       </c>
       <c r="D27" t="n">
-        <v>647.9720344844721</v>
+        <v>643.3876326547638</v>
       </c>
       <c r="E27" t="n">
-        <v>664.2169189453125</v>
+        <v>646.158203125</v>
       </c>
       <c r="F27" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B28" t="n">
-        <v>672.2297387877188</v>
+        <v>653.7823467127146</v>
       </c>
       <c r="C28" t="n">
-        <v>672.6084590133829</v>
+        <v>657.1011064498967</v>
       </c>
       <c r="D28" t="n">
-        <v>643.3875718813117</v>
+        <v>634.0293422915395</v>
       </c>
       <c r="E28" t="n">
-        <v>646.1581420898438</v>
+        <v>635.55419921875</v>
       </c>
       <c r="F28" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B29" t="n">
-        <v>653.7822839270266</v>
+        <v>625.9168165443936</v>
       </c>
       <c r="C29" t="n">
-        <v>657.1010433454932</v>
+        <v>639.5705142822006</v>
       </c>
       <c r="D29" t="n">
-        <v>634.0292814028221</v>
+        <v>623.8937108241939</v>
       </c>
       <c r="E29" t="n">
-        <v>635.5541381835938</v>
+        <v>625.1992797851562</v>
       </c>
       <c r="F29" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B30" t="n">
-        <v>625.9168165443936</v>
+        <v>630.1724613898772</v>
       </c>
       <c r="C30" t="n">
-        <v>639.5705142822006</v>
+        <v>640.0589096060615</v>
       </c>
       <c r="D30" t="n">
-        <v>623.8937108241939</v>
+        <v>624.4219475211817</v>
       </c>
       <c r="E30" t="n">
-        <v>625.1992797851562</v>
+        <v>633.8001708984375</v>
       </c>
       <c r="F30" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B31" t="n">
-        <v>630.1724007040705</v>
+        <v>633.7004019945108</v>
       </c>
       <c r="C31" t="n">
-        <v>640.0588479681868</v>
+        <v>633.8499192315176</v>
       </c>
       <c r="D31" t="n">
-        <v>624.4218873891514</v>
+        <v>615.9107705740217</v>
       </c>
       <c r="E31" t="n">
-        <v>633.8001098632812</v>
+        <v>616.8475952148438</v>
       </c>
       <c r="F31" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B32" t="n">
-        <v>633.7004019945108</v>
+        <v>614.4058308842617</v>
       </c>
       <c r="C32" t="n">
-        <v>633.8499192315176</v>
+        <v>620.0267784116583</v>
       </c>
       <c r="D32" t="n">
-        <v>615.9107705740217</v>
+        <v>599.1675434782962</v>
       </c>
       <c r="E32" t="n">
-        <v>616.8475952148438</v>
+        <v>619.6082153320312</v>
       </c>
       <c r="F32" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B33" t="n">
-        <v>614.4058308842617</v>
+        <v>628.9565496273584</v>
       </c>
       <c r="C33" t="n">
-        <v>620.0267784116583</v>
+        <v>632.8533046281837</v>
       </c>
       <c r="D33" t="n">
-        <v>599.1675434782962</v>
+        <v>616.0203887455347</v>
       </c>
       <c r="E33" t="n">
-        <v>619.6082153320312</v>
+        <v>629.624267578125</v>
       </c>
       <c r="F33" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B34" t="n">
-        <v>628.9566105977867</v>
+        <v>625.8769557835792</v>
       </c>
       <c r="C34" t="n">
-        <v>632.8533659763596</v>
+        <v>627.431679546322</v>
       </c>
       <c r="D34" t="n">
-        <v>616.0204484619443</v>
+        <v>617.29607772438</v>
       </c>
       <c r="E34" t="n">
-        <v>629.6243286132812</v>
+        <v>624.9600830078125</v>
       </c>
       <c r="F34" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B35" t="n">
-        <v>625.8769557835792</v>
+        <v>626.0064663997556</v>
       </c>
       <c r="C35" t="n">
-        <v>627.431679546322</v>
+        <v>626.8635443723126</v>
       </c>
       <c r="D35" t="n">
-        <v>617.29607772438</v>
+        <v>605.7153126787034</v>
       </c>
       <c r="E35" t="n">
-        <v>624.9600830078125</v>
+        <v>606.9511108398438</v>
       </c>
       <c r="F35" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B36" t="n">
-        <v>626.0065293511232</v>
+        <v>610.9974282481795</v>
       </c>
       <c r="C36" t="n">
-        <v>626.8636074098682</v>
+        <v>615.5619618736964</v>
       </c>
       <c r="D36" t="n">
-        <v>605.7153735895874</v>
+        <v>600.9614641591972</v>
       </c>
       <c r="E36" t="n">
-        <v>606.951171875</v>
+        <v>607.8281860351562</v>
       </c>
       <c r="F36" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B37" t="n">
-        <v>610.9974896015757</v>
+        <v>599.7556041676178</v>
       </c>
       <c r="C37" t="n">
-        <v>615.5620236854409</v>
+        <v>611.6054241702889</v>
       </c>
       <c r="D37" t="n">
-        <v>600.9615245048305</v>
+        <v>593.1879159768617</v>
       </c>
       <c r="E37" t="n">
-        <v>607.8282470703125</v>
+        <v>607.3997192382812</v>
       </c>
       <c r="F37" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B38" t="n">
-        <v>599.7555439005879</v>
+        <v>606.980994504603</v>
       </c>
       <c r="C38" t="n">
-        <v>611.6053627125183</v>
+        <v>609.6220599721263</v>
       </c>
       <c r="D38" t="n">
-        <v>593.1878563697925</v>
+        <v>593.3871535288397</v>
       </c>
       <c r="E38" t="n">
-        <v>607.399658203125</v>
+        <v>599.9747924804688</v>
       </c>
       <c r="F38" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B39" t="n">
-        <v>606.9810562524968</v>
+        <v>589.5999948667346</v>
       </c>
       <c r="C39" t="n">
-        <v>609.6221219886945</v>
+        <v>601.619222033871</v>
       </c>
       <c r="D39" t="n">
-        <v>593.3872138938384</v>
+        <v>581.8064849239344</v>
       </c>
       <c r="E39" t="n">
-        <v>599.974853515625</v>
+        <v>595.66943359375</v>
       </c>
       <c r="F39" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B40" t="n">
-        <v>589.6000552799869</v>
+        <v>591.7128101062766</v>
       </c>
       <c r="C40" t="n">
-        <v>601.6192836786712</v>
+        <v>593.3174134864839</v>
       </c>
       <c r="D40" t="n">
-        <v>581.8065445386262</v>
+        <v>579.2849960343485</v>
       </c>
       <c r="E40" t="n">
-        <v>595.6694946289062</v>
+        <v>588.3243408203125</v>
       </c>
       <c r="F40" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B41" t="n">
-        <v>591.7128101062766</v>
+        <v>601.4598513214113</v>
       </c>
       <c r="C41" t="n">
-        <v>593.3174134864839</v>
+        <v>604.668936823252</v>
       </c>
       <c r="D41" t="n">
-        <v>579.2849960343485</v>
+        <v>581.3779446301025</v>
       </c>
       <c r="E41" t="n">
-        <v>588.3243408203125</v>
+        <v>587.1583862304688</v>
       </c>
       <c r="F41" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B42" t="n">
-        <v>601.4597887996167</v>
+        <v>586.5105272163902</v>
       </c>
       <c r="C42" t="n">
-        <v>604.6688739678727</v>
+        <v>596.0980011467227</v>
       </c>
       <c r="D42" t="n">
-        <v>581.3778841958236</v>
+        <v>579.8929596850738</v>
       </c>
       <c r="E42" t="n">
-        <v>587.1583251953125</v>
+        <v>592.2410888671875</v>
       </c>
       <c r="F42" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B43" t="n">
-        <v>586.5105272163902</v>
+        <v>596.6959057641074</v>
       </c>
       <c r="C43" t="n">
-        <v>596.0980011467227</v>
+        <v>614.6151629725317</v>
       </c>
       <c r="D43" t="n">
-        <v>579.8929596850738</v>
+        <v>595.609624740878</v>
       </c>
       <c r="E43" t="n">
-        <v>592.2410888671875</v>
+        <v>610.9774780273438</v>
       </c>
       <c r="F43" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B44" t="n">
-        <v>596.6959057641074</v>
+        <v>621.8904932046078</v>
       </c>
       <c r="C44" t="n">
-        <v>614.6151629725317</v>
+        <v>634.8963639496133</v>
       </c>
       <c r="D44" t="n">
-        <v>595.609624740878</v>
+        <v>616.209750572071</v>
       </c>
       <c r="E44" t="n">
-        <v>610.9774780273438</v>
+        <v>634.0691528320312</v>
       </c>
       <c r="F44" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B45" t="n">
-        <v>621.8904932046078</v>
+        <v>635.5342418532664</v>
       </c>
       <c r="C45" t="n">
-        <v>634.8963639496133</v>
+        <v>636.2019598341516</v>
       </c>
       <c r="D45" t="n">
-        <v>616.209750572071</v>
+        <v>629.4947305871518</v>
       </c>
       <c r="E45" t="n">
-        <v>634.0691528320312</v>
+        <v>631.468017578125</v>
       </c>
       <c r="F45" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B46" t="n">
-        <v>635.5342418532664</v>
+        <v>633.9297145559904</v>
       </c>
       <c r="C46" t="n">
-        <v>636.2019598341516</v>
+        <v>645.8592201326509</v>
       </c>
       <c r="D46" t="n">
-        <v>629.4947305871518</v>
+        <v>633.351658244955</v>
       </c>
       <c r="E46" t="n">
-        <v>631.468017578125</v>
+        <v>645.7595825195312</v>
       </c>
       <c r="F46" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B47" t="n">
-        <v>633.9296546389559</v>
+        <v>637.3878853503733</v>
       </c>
       <c r="C47" t="n">
-        <v>645.8591590880771</v>
+        <v>643.1383983949365</v>
       </c>
       <c r="D47" t="n">
-        <v>633.3515983825566</v>
+        <v>635.6039586340122</v>
       </c>
       <c r="E47" t="n">
-        <v>645.759521484375</v>
+        <v>638.7034301757812</v>
       </c>
       <c r="F47" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B48" t="n">
-        <v>637.3878853503733</v>
+        <v>640.1684965318557</v>
       </c>
       <c r="C48" t="n">
-        <v>643.1383983949365</v>
+        <v>645.6797698761368</v>
       </c>
       <c r="D48" t="n">
-        <v>635.6039586340122</v>
+        <v>635.9129124654792</v>
       </c>
       <c r="E48" t="n">
-        <v>638.7034301757812</v>
+        <v>644.912353515625</v>
       </c>
       <c r="F48" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B49" t="n">
-        <v>640.1685571180485</v>
+        <v>642.2314810232181</v>
       </c>
       <c r="C49" t="n">
-        <v>645.6798309839221</v>
+        <v>646.6564735939825</v>
       </c>
       <c r="D49" t="n">
-        <v>635.9129726489192</v>
+        <v>635.3946865356451</v>
       </c>
       <c r="E49" t="n">
-        <v>644.9124145507812</v>
+        <v>637.437744140625</v>
       </c>
       <c r="F49" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B50" t="n">
-        <v>642.2315425173783</v>
+        <v>673.7146932031604</v>
       </c>
       <c r="C50" t="n">
-        <v>646.6565355118391</v>
+        <v>673.8143308084973</v>
       </c>
       <c r="D50" t="n">
-        <v>635.394747375177</v>
+        <v>657.8186021075292</v>
       </c>
       <c r="E50" t="n">
-        <v>637.4378051757812</v>
+        <v>659.2936401367188</v>
       </c>
       <c r="F50" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B51" t="n">
-        <v>673.7146932031604</v>
+        <v>661.7553548965755</v>
       </c>
       <c r="C51" t="n">
-        <v>673.8143308084973</v>
+        <v>672.4092198957593</v>
       </c>
       <c r="D51" t="n">
-        <v>657.8186021075292</v>
+        <v>660.1508120837719</v>
       </c>
       <c r="E51" t="n">
-        <v>659.2936401367188</v>
+        <v>671.1434936523438</v>
       </c>
       <c r="F51" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B52" t="n">
-        <v>661.7552947151958</v>
+        <v>667.0772284693074</v>
       </c>
       <c r="C52" t="n">
-        <v>672.4091587454953</v>
+        <v>674.4223082782987</v>
       </c>
       <c r="D52" t="n">
-        <v>660.1507520483126</v>
+        <v>662.8216443414645</v>
       </c>
       <c r="E52" t="n">
-        <v>671.1434326171875</v>
+        <v>664.5457763671875</v>
       </c>
       <c r="F52" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B53" t="n">
-        <v>667.0772284693074</v>
+        <v>661.5260500954003</v>
       </c>
       <c r="C53" t="n">
-        <v>674.4223082782987</v>
+        <v>662.2336109084633</v>
       </c>
       <c r="D53" t="n">
-        <v>662.8216443414645</v>
+        <v>651.1313175008097</v>
       </c>
       <c r="E53" t="n">
-        <v>664.5457763671875</v>
+        <v>654.7390747070312</v>
       </c>
       <c r="F53" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B54" t="n">
-        <v>661.5260500954003</v>
+        <v>647.7528057448357</v>
       </c>
       <c r="C54" t="n">
-        <v>662.2336109084633</v>
+        <v>652.297387877758</v>
       </c>
       <c r="D54" t="n">
-        <v>651.1313175008097</v>
+        <v>641.2249606939789</v>
       </c>
       <c r="E54" t="n">
-        <v>654.7390747070312</v>
+        <v>647.9321899414062</v>
       </c>
       <c r="F54" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B55" t="n">
-        <v>647.7527447265774</v>
+        <v>641.1152803360264</v>
       </c>
       <c r="C55" t="n">
-        <v>652.2973264314004</v>
+        <v>653.0647981949571</v>
       </c>
       <c r="D55" t="n">
-        <v>641.2249002906431</v>
+        <v>638.6337077300913</v>
       </c>
       <c r="E55" t="n">
-        <v>647.93212890625</v>
+        <v>650.5034790039062</v>
       </c>
       <c r="F55" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B56" t="n">
-        <v>641.1152803360264</v>
+        <v>647.6033016180266</v>
       </c>
       <c r="C56" t="n">
-        <v>653.0647981949571</v>
+        <v>708.5964236692454</v>
       </c>
       <c r="D56" t="n">
-        <v>638.6337077300913</v>
+        <v>636.4511276224844</v>
       </c>
       <c r="E56" t="n">
-        <v>650.5034790039062</v>
+        <v>642.0521240234375</v>
       </c>
       <c r="F56" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B57" t="n">
-        <v>647.603240055161</v>
+        <v>644.0420011784053</v>
       </c>
       <c r="C57" t="n">
-        <v>708.5963563082138</v>
+        <v>651.3232442601446</v>
       </c>
       <c r="D57" t="n">
-        <v>636.4510671197735</v>
+        <v>637.0599755890928</v>
       </c>
       <c r="E57" t="n">
-        <v>642.0520629882812</v>
+        <v>645.8473510742188</v>
       </c>
       <c r="F57" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,25 +1925,25 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B58" t="n">
-        <v>644.0420011784053</v>
+        <v>641.8476715248971</v>
       </c>
       <c r="C58" t="n">
-        <v>651.3232442601446</v>
+        <v>660.8387602004772</v>
       </c>
       <c r="D58" t="n">
-        <v>637.0599755890928</v>
+        <v>641.5484540168895</v>
       </c>
       <c r="E58" t="n">
-        <v>645.8473510742188</v>
+        <v>655.462646484375</v>
       </c>
       <c r="F58" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G58" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B59" t="n">
-        <v>641.8476117575357</v>
+        <v>653.9265721002572</v>
       </c>
       <c r="C59" t="n">
-        <v>660.8386986647098</v>
+        <v>659.5321367260491</v>
       </c>
       <c r="D59" t="n">
-        <v>641.5483942773906</v>
+        <v>647.5330578779101</v>
       </c>
       <c r="E59" t="n">
-        <v>655.4625854492188</v>
+        <v>647.832275390625</v>
       </c>
       <c r="F59" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B60" t="n">
-        <v>653.9265104909302</v>
+        <v>655.3429055936973</v>
       </c>
       <c r="C60" t="n">
-        <v>659.5320745885969</v>
+        <v>668.8381315618529</v>
       </c>
       <c r="D60" t="n">
-        <v>647.5329968709444</v>
+        <v>654.7743619360156</v>
       </c>
       <c r="E60" t="n">
-        <v>647.8322143554688</v>
+        <v>662.7438354492188</v>
       </c>
       <c r="F60" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B61" t="n">
-        <v>655.3429659472675</v>
+        <v>664.7087499822148</v>
       </c>
       <c r="C61" t="n">
-        <v>668.8381931582612</v>
+        <v>669.2770065062657</v>
       </c>
       <c r="D61" t="n">
-        <v>654.774422237226</v>
+        <v>656.4899183910027</v>
       </c>
       <c r="E61" t="n">
-        <v>662.743896484375</v>
+        <v>657.0784301757812</v>
       </c>
       <c r="F61" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B62" t="n">
-        <v>664.7087499822148</v>
+        <v>659.9510918299604</v>
       </c>
       <c r="C62" t="n">
-        <v>669.2770065062657</v>
+        <v>671.8504516144289</v>
       </c>
       <c r="D62" t="n">
-        <v>656.4899183910027</v>
+        <v>654.9639304343692</v>
       </c>
       <c r="E62" t="n">
-        <v>657.0784301757812</v>
+        <v>659.8014526367188</v>
       </c>
       <c r="F62" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B63" t="n">
-        <v>659.9510307809619</v>
+        <v>658.3550860644432</v>
       </c>
       <c r="C63" t="n">
-        <v>671.850389464676</v>
+        <v>664.2898196014329</v>
       </c>
       <c r="D63" t="n">
-        <v>654.9638698467097</v>
+        <v>656.5597203493141</v>
       </c>
       <c r="E63" t="n">
-        <v>659.8013916015625</v>
+        <v>663.2325439453125</v>
       </c>
       <c r="F63" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B64" t="n">
-        <v>658.3550860644432</v>
+        <v>660.8288080412273</v>
       </c>
       <c r="C64" t="n">
-        <v>664.2898196014329</v>
+        <v>666.4642636433252</v>
       </c>
       <c r="D64" t="n">
-        <v>656.5597203493141</v>
+        <v>660.499638357634</v>
       </c>
       <c r="E64" t="n">
-        <v>663.2325439453125</v>
+        <v>665.8358764648438</v>
       </c>
       <c r="F64" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B65" t="n">
-        <v>660.8288686174008</v>
+        <v>666.3446246130748</v>
       </c>
       <c r="C65" t="n">
-        <v>666.4643247360839</v>
+        <v>667.2323539771746</v>
       </c>
       <c r="D65" t="n">
-        <v>660.4996989036335</v>
+        <v>659.6219406041037</v>
       </c>
       <c r="E65" t="n">
-        <v>665.8359375</v>
+        <v>661.5868530273438</v>
       </c>
       <c r="F65" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B66" t="n">
-        <v>666.3445631389869</v>
+        <v>656.3204105957403</v>
       </c>
       <c r="C66" t="n">
-        <v>667.2322924211887</v>
+        <v>658.5546491157273</v>
       </c>
       <c r="D66" t="n">
-        <v>659.6218797502219</v>
+        <v>652.7097106878265</v>
       </c>
       <c r="E66" t="n">
-        <v>661.5867919921875</v>
+        <v>656.9986572265625</v>
       </c>
       <c r="F66" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B67" t="n">
-        <v>656.3204105957403</v>
+        <v>656.9986226731097</v>
       </c>
       <c r="C67" t="n">
-        <v>658.5546491157273</v>
+        <v>670.4938487731155</v>
       </c>
       <c r="D67" t="n">
-        <v>652.7097106878265</v>
+        <v>656.1508296487782</v>
       </c>
       <c r="E67" t="n">
-        <v>656.9986572265625</v>
+        <v>664.239990234375</v>
       </c>
       <c r="F67" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B68" t="n">
-        <v>656.9986226731097</v>
+        <v>663.0430265979899</v>
       </c>
       <c r="C68" t="n">
-        <v>670.4938487731155</v>
+        <v>663.2923846373272</v>
       </c>
       <c r="D68" t="n">
-        <v>656.1508296487782</v>
+        <v>657.7466642776019</v>
       </c>
       <c r="E68" t="n">
-        <v>664.239990234375</v>
+        <v>658.39501953125</v>
       </c>
       <c r="F68" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B69" t="n">
-        <v>663.0430880640301</v>
+        <v>661.0282405096659</v>
       </c>
       <c r="C69" t="n">
-        <v>663.2924461264837</v>
+        <v>662.6840120988863</v>
       </c>
       <c r="D69" t="n">
-        <v>657.7467252526537</v>
+        <v>641.8476382600104</v>
       </c>
       <c r="E69" t="n">
-        <v>658.3950805664062</v>
+        <v>648.7398681640625</v>
       </c>
       <c r="F69" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B70" t="n">
-        <v>661.0283027009447</v>
+        <v>649.3383972038786</v>
       </c>
       <c r="C70" t="n">
-        <v>662.6840744459444</v>
+        <v>662.8336242718107</v>
       </c>
       <c r="D70" t="n">
-        <v>641.8476986467276</v>
+        <v>646.086758236235</v>
       </c>
       <c r="E70" t="n">
-        <v>648.7399291992188</v>
+        <v>657.098388671875</v>
       </c>
       <c r="F70" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B71" t="n">
-        <v>649.3383972038786</v>
+        <v>657.8763534012292</v>
       </c>
       <c r="C71" t="n">
-        <v>662.8336242718107</v>
+        <v>663.8110870761799</v>
       </c>
       <c r="D71" t="n">
-        <v>646.086758236235</v>
+        <v>650.2260655901538</v>
       </c>
       <c r="E71" t="n">
-        <v>657.098388671875</v>
+        <v>658.9236450195312</v>
       </c>
       <c r="F71" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B72" t="n">
-        <v>657.8764143393763</v>
+        <v>653.956457912222</v>
       </c>
       <c r="C72" t="n">
-        <v>663.8111485640529</v>
+        <v>657.4574546517152</v>
       </c>
       <c r="D72" t="n">
-        <v>650.2261258196658</v>
+        <v>643.154250211399</v>
       </c>
       <c r="E72" t="n">
-        <v>658.9237060546875</v>
+        <v>647.0242919921875</v>
       </c>
       <c r="F72" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B73" t="n">
-        <v>653.9565196013041</v>
+        <v>644.2215315163064</v>
       </c>
       <c r="C73" t="n">
-        <v>657.4575166710536</v>
+        <v>645.4383696113561</v>
       </c>
       <c r="D73" t="n">
-        <v>643.1543108814861</v>
+        <v>634.0875860000896</v>
       </c>
       <c r="E73" t="n">
-        <v>647.0243530273438</v>
+        <v>644.4010620117188</v>
       </c>
       <c r="F73" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B74" t="n">
-        <v>644.2215315163064</v>
+        <v>643.7826886268982</v>
       </c>
       <c r="C74" t="n">
-        <v>645.4383696113561</v>
+        <v>653.2682792823022</v>
       </c>
       <c r="D74" t="n">
-        <v>634.0875860000896</v>
+        <v>641.1993122536916</v>
       </c>
       <c r="E74" t="n">
-        <v>644.4010620117188</v>
+        <v>651.3831176757812</v>
       </c>
       <c r="F74" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B75" t="n">
-        <v>643.7826283039087</v>
+        <v>650.8544758921091</v>
       </c>
       <c r="C75" t="n">
-        <v>653.2682180705046</v>
+        <v>652.2907198459545</v>
       </c>
       <c r="D75" t="n">
-        <v>641.1992521727667</v>
+        <v>639.5834431006995</v>
       </c>
       <c r="E75" t="n">
-        <v>651.383056640625</v>
+        <v>640.321533203125</v>
       </c>
       <c r="F75" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B76" t="n">
-        <v>650.8545379312607</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="C76" t="n">
-        <v>652.2907820220081</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="D76" t="n">
-        <v>639.5835040655014</v>
+        <v>622.4974409136</v>
       </c>
       <c r="E76" t="n">
-        <v>640.3215942382812</v>
+        <v>629.4695434570312</v>
       </c>
       <c r="F76" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B77" t="n">
-        <v>640.6208286715078</v>
+        <v>624.8912385916063</v>
       </c>
       <c r="C77" t="n">
-        <v>640.6208286715078</v>
+        <v>626.8362434492608</v>
       </c>
       <c r="D77" t="n">
-        <v>622.4974409136</v>
+        <v>613.241238448095</v>
       </c>
       <c r="E77" t="n">
-        <v>629.4695434570312</v>
+        <v>613.939453125</v>
       </c>
       <c r="F77" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B78" t="n">
-        <v>624.8913007155408</v>
+        <v>616.8918216697934</v>
       </c>
       <c r="C78" t="n">
-        <v>626.836305766559</v>
+        <v>622.5672130846042</v>
       </c>
       <c r="D78" t="n">
-        <v>613.2412994138377</v>
+        <v>612.6527349978052</v>
       </c>
       <c r="E78" t="n">
-        <v>613.9395141601562</v>
+        <v>619.2058715820312</v>
       </c>
       <c r="F78" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B79" t="n">
-        <v>616.8918824768537</v>
+        <v>622.5772500418334</v>
       </c>
       <c r="C79" t="n">
-        <v>622.567274451088</v>
+        <v>627.4646923832119</v>
       </c>
       <c r="D79" t="n">
-        <v>612.6527953870184</v>
+        <v>618.4878021974878</v>
       </c>
       <c r="E79" t="n">
-        <v>619.2059326171875</v>
+        <v>618.6573486328125</v>
       </c>
       <c r="F79" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B80" t="n">
-        <v>622.5772500418334</v>
+        <v>606.3190803349536</v>
       </c>
       <c r="C80" t="n">
-        <v>627.4646923832119</v>
+        <v>609.8300611005736</v>
       </c>
       <c r="D80" t="n">
-        <v>618.4878021974878</v>
+        <v>598.4593098618273</v>
       </c>
       <c r="E80" t="n">
-        <v>618.6573486328125</v>
+        <v>602.5687255859375</v>
       </c>
       <c r="F80" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B81" t="n">
-        <v>606.3191417499893</v>
+        <v>605.1819875834877</v>
       </c>
       <c r="C81" t="n">
-        <v>609.8301228712422</v>
+        <v>616.682409772708</v>
       </c>
       <c r="D81" t="n">
-        <v>598.4593704807342</v>
+        <v>598.5391160903739</v>
       </c>
       <c r="E81" t="n">
-        <v>602.5687866210938</v>
+        <v>611.3860473632812</v>
       </c>
       <c r="F81" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B82" t="n">
-        <v>605.1820479992876</v>
+        <v>627.7339506004921</v>
       </c>
       <c r="C82" t="n">
-        <v>616.6824713366042</v>
+        <v>658.8738165275513</v>
       </c>
       <c r="D82" t="n">
-        <v>598.5391758430108</v>
+        <v>624.9411525277235</v>
       </c>
       <c r="E82" t="n">
-        <v>611.3861083984375</v>
+        <v>645.967041015625</v>
       </c>
       <c r="F82" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B83" t="n">
-        <v>627.7339506004921</v>
+        <v>643.114354212172</v>
       </c>
       <c r="C83" t="n">
-        <v>658.8738165275513</v>
+        <v>664.7785515369834</v>
       </c>
       <c r="D83" t="n">
-        <v>624.9411525277235</v>
+        <v>642.7951686151001</v>
       </c>
       <c r="E83" t="n">
-        <v>645.967041015625</v>
+        <v>657.0684204101562</v>
       </c>
       <c r="F83" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B84" t="n">
-        <v>643.1144139511335</v>
+        <v>663.4220687284304</v>
       </c>
       <c r="C84" t="n">
-        <v>664.7786132883346</v>
+        <v>673.5460296758964</v>
       </c>
       <c r="D84" t="n">
-        <v>642.7952283244125</v>
+        <v>659.5919023824141</v>
       </c>
       <c r="E84" t="n">
-        <v>657.0684814453125</v>
+        <v>670.6334838867188</v>
       </c>
       <c r="F84" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B85" t="n">
-        <v>663.4221291072672</v>
+        <v>672.8578395915863</v>
       </c>
       <c r="C85" t="n">
-        <v>673.5460909761269</v>
+        <v>675.0820939991542</v>
       </c>
       <c r="D85" t="n">
-        <v>659.5919624126628</v>
+        <v>662.9532839044604</v>
       </c>
       <c r="E85" t="n">
-        <v>670.633544921875</v>
+        <v>671.241943359375</v>
       </c>
       <c r="F85" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B86" t="n">
-        <v>672.8578395915863</v>
+        <v>672.7679591112906</v>
       </c>
       <c r="C86" t="n">
-        <v>675.0820939991542</v>
+        <v>675.9397859199995</v>
       </c>
       <c r="D86" t="n">
-        <v>662.9532839044604</v>
+        <v>664.3895050245095</v>
       </c>
       <c r="E86" t="n">
-        <v>671.241943359375</v>
+        <v>667.0127563476562</v>
       </c>
       <c r="F86" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B87" t="n">
-        <v>672.768020673078</v>
+        <v>735.536439340887</v>
       </c>
       <c r="C87" t="n">
-        <v>675.9398477720257</v>
+        <v>742.0895763731422</v>
       </c>
       <c r="D87" t="n">
-        <v>664.3895658196245</v>
+        <v>710.7203206800697</v>
       </c>
       <c r="E87" t="n">
-        <v>667.0128173828125</v>
+        <v>736.4141845703125</v>
       </c>
       <c r="F87" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B88" t="n">
-        <v>735.536439340887</v>
+        <v>725.6319721911391</v>
       </c>
       <c r="C88" t="n">
-        <v>742.0895763731422</v>
+        <v>730.2899638188994</v>
       </c>
       <c r="D88" t="n">
-        <v>710.7203206800697</v>
+        <v>711.7577161829028</v>
       </c>
       <c r="E88" t="n">
-        <v>736.4141845703125</v>
+        <v>714.6602172851562</v>
       </c>
       <c r="F88" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B89" t="n">
-        <v>725.6319102189462</v>
+        <v>712.7650416713351</v>
       </c>
       <c r="C89" t="n">
-        <v>730.2899014488934</v>
+        <v>719.4478497361232</v>
       </c>
       <c r="D89" t="n">
-        <v>711.7576553956329</v>
+        <v>701.7135364812315</v>
       </c>
       <c r="E89" t="n">
-        <v>714.66015625</v>
+        <v>704.5960693359375</v>
       </c>
       <c r="F89" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B90" t="n">
-        <v>712.7649799285471</v>
+        <v>705.5536352374374</v>
       </c>
       <c r="C90" t="n">
-        <v>719.4477874144414</v>
+        <v>715.1589125312489</v>
       </c>
       <c r="D90" t="n">
-        <v>701.7134756957726</v>
+        <v>684.6474336745422</v>
       </c>
       <c r="E90" t="n">
-        <v>704.5960083007812</v>
+        <v>689.9238891601562</v>
       </c>
       <c r="F90" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B91" t="n">
-        <v>705.5535728195721</v>
+        <v>685.964025393825</v>
       </c>
       <c r="C91" t="n">
-        <v>715.1588492636382</v>
+        <v>687.0612373376343</v>
       </c>
       <c r="D91" t="n">
-        <v>684.6473731061755</v>
+        <v>665.7461161570209</v>
       </c>
       <c r="E91" t="n">
-        <v>689.923828125</v>
+        <v>667.2721557617188</v>
       </c>
       <c r="F91" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B92" t="n">
-        <v>685.964025393825</v>
+        <v>661.8760941724082</v>
       </c>
       <c r="C92" t="n">
-        <v>687.0612373376343</v>
+        <v>679.7500626324993</v>
       </c>
       <c r="D92" t="n">
-        <v>665.7461161570209</v>
+        <v>651.8219602792932</v>
       </c>
       <c r="E92" t="n">
-        <v>667.2721557617188</v>
+        <v>668.4890747070312</v>
       </c>
       <c r="F92" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B93" t="n">
-        <v>661.876033741038</v>
+        <v>663.7811558190369</v>
       </c>
       <c r="C93" t="n">
-        <v>679.7500005691794</v>
+        <v>670.2644652243433</v>
       </c>
       <c r="D93" t="n">
-        <v>651.8219007658969</v>
+        <v>644.8399277739295</v>
       </c>
       <c r="E93" t="n">
-        <v>668.489013671875</v>
+        <v>659.7615356445312</v>
       </c>
       <c r="F93" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B94" t="n">
-        <v>663.7811558190369</v>
+        <v>661.4770916291903</v>
       </c>
       <c r="C94" t="n">
-        <v>670.2644652243433</v>
+        <v>681.5554070660584</v>
       </c>
       <c r="D94" t="n">
-        <v>644.8399277739295</v>
+        <v>657.0884263930592</v>
       </c>
       <c r="E94" t="n">
-        <v>659.7615356445312</v>
+        <v>675.4810180664062</v>
       </c>
       <c r="F94" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B95" t="n">
-        <v>661.4770916291903</v>
+        <v>675.8600189134125</v>
       </c>
       <c r="C95" t="n">
-        <v>681.5554070660584</v>
+        <v>678.9022357565889</v>
       </c>
       <c r="D95" t="n">
-        <v>657.0884263930592</v>
+        <v>668.0700760446862</v>
       </c>
       <c r="E95" t="n">
-        <v>675.4810180664062</v>
+        <v>668.9976806640625</v>
       </c>
       <c r="F95" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B96" t="n">
-        <v>675.8600805746455</v>
+        <v>672.2693241407737</v>
       </c>
       <c r="C96" t="n">
-        <v>678.9022976953746</v>
+        <v>677.5258114827353</v>
       </c>
       <c r="D96" t="n">
-        <v>668.0701369952135</v>
+        <v>655.4126950742984</v>
       </c>
       <c r="E96" t="n">
-        <v>668.9977416992188</v>
+        <v>666.9729614257812</v>
       </c>
       <c r="F96" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B97" t="n">
-        <v>672.2693241407737</v>
+        <v>668.2496878446467</v>
       </c>
       <c r="C97" t="n">
-        <v>677.5258114827353</v>
+        <v>674.2642338266133</v>
       </c>
       <c r="D97" t="n">
-        <v>655.4126950742984</v>
+        <v>643.6231428364971</v>
       </c>
       <c r="E97" t="n">
-        <v>666.9729614257812</v>
+        <v>648.1414794921875</v>
       </c>
       <c r="F97" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B98" t="n">
-        <v>668.2496249159107</v>
+        <v>643.4434668857905</v>
       </c>
       <c r="C98" t="n">
-        <v>674.2641703314905</v>
+        <v>649.7572295518577</v>
       </c>
       <c r="D98" t="n">
-        <v>643.6230822268304</v>
+        <v>632.9405378190771</v>
       </c>
       <c r="E98" t="n">
-        <v>648.1414184570312</v>
+        <v>638.127197265625</v>
       </c>
       <c r="F98" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B99" t="n">
-        <v>643.4435284294337</v>
+        <v>637.8578591323172</v>
       </c>
       <c r="C99" t="n">
-        <v>649.7572916993954</v>
+        <v>640.9498744421038</v>
       </c>
       <c r="D99" t="n">
-        <v>632.9405983581432</v>
+        <v>627.1853229648948</v>
       </c>
       <c r="E99" t="n">
-        <v>638.1272583007812</v>
+        <v>637.6483764648438</v>
       </c>
       <c r="F99" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B100" t="n">
-        <v>637.8578591323172</v>
+        <v>632.1725643806327</v>
       </c>
       <c r="C100" t="n">
-        <v>640.9498744421038</v>
+        <v>643.3438180480059</v>
       </c>
       <c r="D100" t="n">
-        <v>627.1853229648948</v>
+        <v>626.5371085480483</v>
       </c>
       <c r="E100" t="n">
-        <v>637.6483764648438</v>
+        <v>641.568359375</v>
       </c>
       <c r="F100" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B101" t="n">
-        <v>632.1725042393389</v>
+        <v>636.9303135148713</v>
       </c>
       <c r="C101" t="n">
-        <v>643.3437568439427</v>
+        <v>645.5281745630167</v>
       </c>
       <c r="D101" t="n">
-        <v>626.5370489428796</v>
+        <v>635.085027341747</v>
       </c>
       <c r="E101" t="n">
-        <v>641.5682983398438</v>
+        <v>643.1243896484375</v>
       </c>
       <c r="F101" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B102" t="n">
-        <v>636.9302530675583</v>
+        <v>638.0474161403351</v>
       </c>
       <c r="C102" t="n">
-        <v>645.5281132997313</v>
+        <v>661.6466355641227</v>
       </c>
       <c r="D102" t="n">
-        <v>635.0849670695593</v>
+        <v>637.1397796110642</v>
       </c>
       <c r="E102" t="n">
-        <v>643.1243286132812</v>
+        <v>653.9763793945312</v>
       </c>
       <c r="F102" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B103" t="n">
-        <v>638.0474161403351</v>
+        <v>650.8644258547187</v>
       </c>
       <c r="C103" t="n">
-        <v>661.6466355641227</v>
+        <v>656.0112104148094</v>
       </c>
       <c r="D103" t="n">
-        <v>637.1397796110642</v>
+        <v>634.3669181695027</v>
       </c>
       <c r="E103" t="n">
-        <v>653.9763793945312</v>
+        <v>635.6137084960938</v>
       </c>
       <c r="F103" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B104" t="n">
-        <v>650.8643633551039</v>
+        <v>631.4543872367445</v>
       </c>
       <c r="C104" t="n">
-        <v>656.0111474209717</v>
+        <v>639.4637360573605</v>
       </c>
       <c r="D104" t="n">
-        <v>634.3668572540702</v>
+        <v>627.364878734925</v>
       </c>
       <c r="E104" t="n">
-        <v>635.6136474609375</v>
+        <v>637.6583862304688</v>
       </c>
       <c r="F104" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B105" t="n">
-        <v>631.4543872367445</v>
+        <v>640.8801577475739</v>
       </c>
       <c r="C105" t="n">
-        <v>639.4637360573605</v>
+        <v>652.2009891675571</v>
       </c>
       <c r="D105" t="n">
-        <v>627.364878734925</v>
+        <v>640.4911445683953</v>
       </c>
       <c r="E105" t="n">
-        <v>637.6583862304688</v>
+        <v>652.011474609375</v>
       </c>
       <c r="F105" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B106" t="n">
-        <v>640.8801577475739</v>
+        <v>648.8795635426123</v>
       </c>
       <c r="C106" t="n">
-        <v>652.2009891675571</v>
+        <v>659.3027431401059</v>
       </c>
       <c r="D106" t="n">
-        <v>640.4911445683953</v>
+        <v>645.8374072363367</v>
       </c>
       <c r="E106" t="n">
-        <v>652.011474609375</v>
+        <v>655.322998046875</v>
       </c>
       <c r="F106" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B107" t="n">
-        <v>648.8795635426123</v>
+        <v>641.7977899641362</v>
       </c>
       <c r="C107" t="n">
-        <v>659.3027431401059</v>
+        <v>647.7723993687464</v>
       </c>
       <c r="D107" t="n">
-        <v>645.8374072363367</v>
+        <v>636.4814590544522</v>
       </c>
       <c r="E107" t="n">
-        <v>655.322998046875</v>
+        <v>646.515625</v>
       </c>
       <c r="F107" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B108" t="n">
-        <v>641.7977899641362</v>
+        <v>635.5238627543893</v>
       </c>
       <c r="C108" t="n">
-        <v>647.7723993687464</v>
+        <v>658.2453970983619</v>
       </c>
       <c r="D108" t="n">
-        <v>636.4814590544522</v>
+        <v>632.870719934867</v>
       </c>
       <c r="E108" t="n">
-        <v>646.515625</v>
+        <v>651.8817749023438</v>
       </c>
       <c r="F108" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B109" t="n">
-        <v>635.5238627543893</v>
+        <v>646.6253451355694</v>
       </c>
       <c r="C109" t="n">
-        <v>658.2453970983619</v>
+        <v>657.3477420502325</v>
       </c>
       <c r="D109" t="n">
-        <v>632.870719934867</v>
+        <v>637.1996588761248</v>
       </c>
       <c r="E109" t="n">
-        <v>651.8817749023438</v>
+        <v>653.39794921875</v>
       </c>
       <c r="F109" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B110" t="n">
-        <v>646.6252847330551</v>
+        <v>656.2705097002453</v>
       </c>
       <c r="C110" t="n">
-        <v>657.3476806461185</v>
+        <v>671.0424780902056</v>
       </c>
       <c r="D110" t="n">
-        <v>637.199599354082</v>
+        <v>655.9812154011644</v>
       </c>
       <c r="E110" t="n">
-        <v>653.3978881835938</v>
+        <v>666.015380859375</v>
       </c>
       <c r="F110" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B111" t="n">
-        <v>656.2705097002453</v>
+        <v>660.2303336051802</v>
       </c>
       <c r="C111" t="n">
-        <v>671.0424780902056</v>
+        <v>668.9778340733714</v>
       </c>
       <c r="D111" t="n">
-        <v>655.9812154011644</v>
+        <v>648.6401755256248</v>
       </c>
       <c r="E111" t="n">
-        <v>666.015380859375</v>
+        <v>658.8738403320312</v>
       </c>
       <c r="F111" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B112" t="n">
-        <v>660.2303336051802</v>
+        <v>646.2363956775138</v>
       </c>
       <c r="C112" t="n">
-        <v>668.9778340733714</v>
+        <v>647.8023107770981</v>
       </c>
       <c r="D112" t="n">
-        <v>648.6401755256248</v>
+        <v>634.4766301866302</v>
       </c>
       <c r="E112" t="n">
-        <v>658.8738403320312</v>
+        <v>643.2041625976562</v>
       </c>
       <c r="F112" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B113" t="n">
-        <v>646.2363343546218</v>
+        <v>633.1500554179556</v>
       </c>
       <c r="C113" t="n">
-        <v>647.8022493056128</v>
+        <v>646.0867221220876</v>
       </c>
       <c r="D113" t="n">
-        <v>634.4765699796501</v>
+        <v>625.1705976379839</v>
       </c>
       <c r="E113" t="n">
-        <v>643.2041015625</v>
+        <v>645.7276611328125</v>
       </c>
       <c r="F113" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B114" t="n">
-        <v>633.1501152642575</v>
+        <v>651.881802754218</v>
       </c>
       <c r="C114" t="n">
-        <v>646.0867831911829</v>
+        <v>658.6044862124207</v>
       </c>
       <c r="D114" t="n">
-        <v>625.1706567300553</v>
+        <v>647.3335142418318</v>
       </c>
       <c r="E114" t="n">
-        <v>645.7277221679688</v>
+        <v>652.3905029296875</v>
       </c>
       <c r="F114" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B115" t="n">
-        <v>651.881802754218</v>
+        <v>653.0787479235273</v>
       </c>
       <c r="C115" t="n">
-        <v>658.6044862124207</v>
+        <v>657.4275379105374</v>
       </c>
       <c r="D115" t="n">
-        <v>647.3335142418318</v>
+        <v>646.6951571900124</v>
       </c>
       <c r="E115" t="n">
-        <v>652.3905029296875</v>
+        <v>653.178466796875</v>
       </c>
       <c r="F115" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B116" t="n">
-        <v>653.0786868976891</v>
+        <v>647.0841872338415</v>
       </c>
       <c r="C116" t="n">
-        <v>657.4274764783338</v>
+        <v>651.8219905315074</v>
       </c>
       <c r="D116" t="n">
-        <v>646.695096760678</v>
+        <v>635.2646391478804</v>
       </c>
       <c r="E116" t="n">
-        <v>653.1784057617188</v>
+        <v>636.5413208007812</v>
       </c>
       <c r="F116" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B117" t="n">
-        <v>647.084125187776</v>
+        <v>622.2880080608647</v>
       </c>
       <c r="C117" t="n">
-        <v>651.8219280311547</v>
+        <v>627.55441857404</v>
       </c>
       <c r="D117" t="n">
-        <v>635.2645782351397</v>
+        <v>607.9848031082139</v>
       </c>
       <c r="E117" t="n">
-        <v>636.541259765625</v>
+        <v>612.1341552734375</v>
       </c>
       <c r="F117" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,25 +3485,25 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B118" t="n">
-        <v>622.2879460132801</v>
+        <v>630.9168848948667</v>
       </c>
       <c r="C118" t="n">
-        <v>627.554356001348</v>
+        <v>633.6621719731276</v>
       </c>
       <c r="D118" t="n">
-        <v>607.9847424867846</v>
+        <v>622.0321132511823</v>
       </c>
       <c r="E118" t="n">
-        <v>612.1340942382812</v>
+        <v>626.3746948242188</v>
       </c>
       <c r="F118" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3511,25 +3511,25 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B119" t="n">
-        <v>630.9168848948667</v>
+        <v>626.9137167736849</v>
       </c>
       <c r="C119" t="n">
-        <v>633.6621719731276</v>
+        <v>635.4590438783874</v>
       </c>
       <c r="D119" t="n">
-        <v>622.0321132511823</v>
+        <v>620.6345187532272</v>
       </c>
       <c r="E119" t="n">
-        <v>626.3746948242188</v>
+        <v>621.5928344726562</v>
       </c>
       <c r="F119" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G119" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B120" t="n">
-        <v>626.9137783313067</v>
+        <v>615.2837198825454</v>
       </c>
       <c r="C120" t="n">
-        <v>635.4591062750881</v>
+        <v>621.5829031274002</v>
       </c>
       <c r="D120" t="n">
-        <v>620.634579694285</v>
+        <v>613.5566433895493</v>
       </c>
       <c r="E120" t="n">
-        <v>621.5928955078125</v>
+        <v>614.6248168945312</v>
       </c>
       <c r="F120" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B121" t="n">
-        <v>615.2837809831337</v>
+        <v>611.1008889698486</v>
       </c>
       <c r="C121" t="n">
-        <v>621.5829648535273</v>
+        <v>611.9494078221777</v>
       </c>
       <c r="D121" t="n">
-        <v>613.5567043186309</v>
+        <v>601.2278243573462</v>
       </c>
       <c r="E121" t="n">
-        <v>614.6248779296875</v>
+        <v>605.6602172851562</v>
       </c>
       <c r="F121" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B122" t="n">
-        <v>611.1009505532863</v>
+        <v>602.4957192983555</v>
       </c>
       <c r="C122" t="n">
-        <v>611.9494694911245</v>
+        <v>602.9249750667714</v>
       </c>
       <c r="D122" t="n">
-        <v>601.2278849458298</v>
+        <v>586.2435901825164</v>
       </c>
       <c r="E122" t="n">
-        <v>605.6602783203125</v>
+        <v>592.642578125</v>
       </c>
       <c r="F122" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B123" t="n">
-        <v>602.4957192983555</v>
+        <v>604.7517959610541</v>
       </c>
       <c r="C123" t="n">
-        <v>602.9249750667714</v>
+        <v>607.5969482872343</v>
       </c>
       <c r="D123" t="n">
-        <v>586.2435901825164</v>
+        <v>597.9834469761715</v>
       </c>
       <c r="E123" t="n">
-        <v>592.642578125</v>
+        <v>603.0247802734375</v>
       </c>
       <c r="F123" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B124" t="n">
-        <v>604.7517959610541</v>
+        <v>598.0732713770465</v>
       </c>
       <c r="C124" t="n">
-        <v>607.5969482872343</v>
+        <v>599.9700396349708</v>
       </c>
       <c r="D124" t="n">
-        <v>597.9834469761715</v>
+        <v>589.9871770786485</v>
       </c>
       <c r="E124" t="n">
-        <v>603.0247802734375</v>
+        <v>591.9038696289062</v>
       </c>
       <c r="F124" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B125" t="n">
-        <v>598.0732713770465</v>
+        <v>597.7138608396341</v>
       </c>
       <c r="C125" t="n">
-        <v>599.9700396349708</v>
+        <v>602.6354044215132</v>
       </c>
       <c r="D125" t="n">
-        <v>589.9871770786485</v>
+        <v>592.3830467312241</v>
       </c>
       <c r="E125" t="n">
-        <v>591.9038696289062</v>
+        <v>593.8704833984375</v>
       </c>
       <c r="F125" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B126" t="n">
-        <v>597.7138608396341</v>
+        <v>581.4917396573854</v>
       </c>
       <c r="C126" t="n">
-        <v>602.6354044215132</v>
+        <v>582.0008753864581</v>
       </c>
       <c r="D126" t="n">
-        <v>592.3830467312241</v>
+        <v>542.4188017705425</v>
       </c>
       <c r="E126" t="n">
-        <v>593.8704833984375</v>
+        <v>546.6016235351562</v>
       </c>
       <c r="F126" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B127" t="n">
-        <v>581.4916747262954</v>
+        <v>539.1743922574078</v>
       </c>
       <c r="C127" t="n">
-        <v>582.0008103985165</v>
+        <v>542.6683942166816</v>
       </c>
       <c r="D127" t="n">
-        <v>542.4187412024525</v>
+        <v>519.3684267008094</v>
       </c>
       <c r="E127" t="n">
-        <v>546.6015625</v>
+        <v>524.8190307617188</v>
       </c>
       <c r="F127" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B128" t="n">
-        <v>539.1743295527585</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="C128" t="n">
-        <v>542.6683311056884</v>
+        <v>538.6253045735799</v>
       </c>
       <c r="D128" t="n">
-        <v>519.368366299545</v>
+        <v>527.6341638126921</v>
       </c>
       <c r="E128" t="n">
-        <v>524.8189697265625</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="F128" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B129" t="n">
-        <v>535.4607543945312</v>
+        <v>549.0374119135495</v>
       </c>
       <c r="C129" t="n">
-        <v>538.6253045735799</v>
+        <v>572.7067990959439</v>
       </c>
       <c r="D129" t="n">
-        <v>527.6341638126921</v>
+        <v>545.8329522821889</v>
       </c>
       <c r="E129" t="n">
-        <v>535.4607543945312</v>
+        <v>571.1494750976562</v>
       </c>
       <c r="F129" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B130" t="n">
-        <v>549.0374119135495</v>
+        <v>579.135725523027</v>
       </c>
       <c r="C130" t="n">
-        <v>572.7067990959439</v>
+        <v>591.5344219412718</v>
       </c>
       <c r="D130" t="n">
-        <v>545.8329522821889</v>
+        <v>572.8365426099092</v>
       </c>
       <c r="E130" t="n">
-        <v>571.1494750976562</v>
+        <v>578.2372436523438</v>
       </c>
       <c r="F130" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B131" t="n">
-        <v>579.1357866530213</v>
+        <v>565.0699110449033</v>
       </c>
       <c r="C131" t="n">
-        <v>591.5344843799961</v>
+        <v>577.5085793033603</v>
       </c>
       <c r="D131" t="n">
-        <v>572.8366030750008</v>
+        <v>558.7408105198895</v>
       </c>
       <c r="E131" t="n">
-        <v>578.2373046875</v>
+        <v>573.4755249023438</v>
       </c>
       <c r="F131" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B132" t="n">
-        <v>565.0699110449033</v>
+        <v>576.7000047794845</v>
       </c>
       <c r="C132" t="n">
-        <v>577.5085793033603</v>
+        <v>581.7912404462878</v>
       </c>
       <c r="D132" t="n">
-        <v>558.7408105198895</v>
+        <v>571.0197533967594</v>
       </c>
       <c r="E132" t="n">
-        <v>573.4755249023438</v>
+        <v>572.0380249023438</v>
       </c>
       <c r="F132" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B133" t="n">
-        <v>576.6999432469056</v>
+        <v>571.4988503418972</v>
       </c>
       <c r="C133" t="n">
-        <v>581.7911783704857</v>
+        <v>574.2441373249518</v>
       </c>
       <c r="D133" t="n">
-        <v>571.0196924702504</v>
+        <v>563.7921103124964</v>
       </c>
       <c r="E133" t="n">
-        <v>572.0379638671875</v>
+        <v>574.064453125</v>
       </c>
       <c r="F133" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B134" t="n">
-        <v>571.4988503418972</v>
+        <v>604.9614419693103</v>
       </c>
       <c r="C134" t="n">
-        <v>574.2441373249518</v>
+        <v>628.8704088339113</v>
       </c>
       <c r="D134" t="n">
-        <v>563.7921103124964</v>
+        <v>590.8157434643455</v>
       </c>
       <c r="E134" t="n">
-        <v>574.064453125</v>
+        <v>611.3704223632812</v>
       </c>
       <c r="F134" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B135" t="n">
-        <v>604.9614419693103</v>
+        <v>625.8954391113879</v>
       </c>
       <c r="C135" t="n">
-        <v>628.8704088339113</v>
+        <v>636.4074215325429</v>
       </c>
       <c r="D135" t="n">
-        <v>590.8157434643455</v>
+        <v>621.9322723369008</v>
       </c>
       <c r="E135" t="n">
-        <v>611.3704223632812</v>
+        <v>627.3130493164062</v>
       </c>
       <c r="F135" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B136" t="n">
-        <v>625.8955000086161</v>
+        <v>633.3826022362973</v>
       </c>
       <c r="C136" t="n">
-        <v>636.4074834525468</v>
+        <v>637.4856047359222</v>
       </c>
       <c r="D136" t="n">
-        <v>621.9323328485281</v>
+        <v>623.2600266965629</v>
       </c>
       <c r="E136" t="n">
-        <v>627.3131103515625</v>
+        <v>628.780517578125</v>
       </c>
       <c r="F136" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B137" t="n">
-        <v>633.3826022362973</v>
+        <v>628.4211571313969</v>
       </c>
       <c r="C137" t="n">
-        <v>637.4856047359222</v>
+        <v>633.911731180996</v>
       </c>
       <c r="D137" t="n">
-        <v>623.2600266965629</v>
+        <v>623.3299219303536</v>
       </c>
       <c r="E137" t="n">
-        <v>628.780517578125</v>
+        <v>633.4425659179688</v>
       </c>
       <c r="F137" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B138" t="n">
-        <v>628.4212176827168</v>
+        <v>642.117619704398</v>
       </c>
       <c r="C138" t="n">
-        <v>633.9117922613585</v>
+        <v>665.1181727259973</v>
       </c>
       <c r="D138" t="n">
-        <v>623.3299819911093</v>
+        <v>638.2742422102883</v>
       </c>
       <c r="E138" t="n">
-        <v>633.442626953125</v>
+        <v>661.3546142578125</v>
       </c>
       <c r="F138" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B139" t="n">
-        <v>642.117619704398</v>
+        <v>665.856909197143</v>
       </c>
       <c r="C139" t="n">
-        <v>665.1181727259973</v>
+        <v>677.3372007350248</v>
       </c>
       <c r="D139" t="n">
-        <v>638.2742422102883</v>
+        <v>663.081644256971</v>
       </c>
       <c r="E139" t="n">
-        <v>661.3546142578125</v>
+        <v>670.4290771484375</v>
       </c>
       <c r="F139" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B140" t="n">
-        <v>665.856909197143</v>
+        <v>674.831464225754</v>
       </c>
       <c r="C140" t="n">
-        <v>677.3372007350248</v>
+        <v>676.4187660594131</v>
       </c>
       <c r="D140" t="n">
-        <v>663.081644256971</v>
+        <v>666.605595861725</v>
       </c>
       <c r="E140" t="n">
-        <v>670.4290771484375</v>
+        <v>675.7099609375</v>
       </c>
       <c r="F140" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B141" t="n">
-        <v>674.831464225754</v>
+        <v>677.4369744478516</v>
       </c>
       <c r="C141" t="n">
-        <v>676.4187660594131</v>
+        <v>690.3348757077041</v>
       </c>
       <c r="D141" t="n">
-        <v>666.605595861725</v>
+        <v>673.9729506648888</v>
       </c>
       <c r="E141" t="n">
-        <v>675.7099609375</v>
+        <v>687.3699340820312</v>
       </c>
       <c r="F141" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B142" t="n">
-        <v>677.4369744478516</v>
+        <v>680.192296240317</v>
       </c>
       <c r="C142" t="n">
-        <v>690.3348757077041</v>
+        <v>682.2088539380842</v>
       </c>
       <c r="D142" t="n">
-        <v>673.9729506648888</v>
+        <v>666.8552067290691</v>
       </c>
       <c r="E142" t="n">
-        <v>687.3699340820312</v>
+        <v>669.7601928710938</v>
       </c>
       <c r="F142" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B143" t="n">
-        <v>680.192296240317</v>
+        <v>669.8500580611455</v>
       </c>
       <c r="C143" t="n">
-        <v>682.2088539380842</v>
+        <v>675.0411586256739</v>
       </c>
       <c r="D143" t="n">
-        <v>666.8552067290691</v>
+        <v>666.1863646700106</v>
       </c>
       <c r="E143" t="n">
-        <v>669.7601928710938</v>
+        <v>667.6937866210938</v>
       </c>
       <c r="F143" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B144" t="n">
-        <v>669.8500580611455</v>
+        <v>673.2042912464699</v>
       </c>
       <c r="C144" t="n">
-        <v>675.0411586256739</v>
+        <v>677.2174214115423</v>
       </c>
       <c r="D144" t="n">
-        <v>666.1863646700106</v>
+        <v>668.6022063234784</v>
       </c>
       <c r="E144" t="n">
-        <v>667.6937866210938</v>
+        <v>673.5636596679688</v>
       </c>
       <c r="F144" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B145" t="n">
-        <v>673.2042912464699</v>
+        <v>662.562575853328</v>
       </c>
       <c r="C145" t="n">
-        <v>677.2174214115423</v>
+        <v>668.4125184743669</v>
       </c>
       <c r="D145" t="n">
-        <v>668.6022063234784</v>
+        <v>651.9308032468797</v>
       </c>
       <c r="E145" t="n">
-        <v>673.5636596679688</v>
+        <v>658.0203857421875</v>
       </c>
       <c r="F145" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B146" t="n">
-        <v>662.562575853328</v>
+        <v>659.1883568751083</v>
       </c>
       <c r="C146" t="n">
-        <v>668.4125184743669</v>
+        <v>679.5034568571632</v>
       </c>
       <c r="D146" t="n">
-        <v>651.9308032468797</v>
+        <v>652.719481738207</v>
       </c>
       <c r="E146" t="n">
-        <v>658.0203857421875</v>
+        <v>673.8731689453125</v>
       </c>
       <c r="F146" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B147" t="n">
-        <v>659.1883568751083</v>
+        <v>669.8500343121515</v>
       </c>
       <c r="C147" t="n">
-        <v>679.5034568571632</v>
+        <v>681.330325511242</v>
       </c>
       <c r="D147" t="n">
-        <v>652.719481738207</v>
+        <v>669.6903353309991</v>
       </c>
       <c r="E147" t="n">
-        <v>673.8731689453125</v>
+        <v>677.4569702148438</v>
       </c>
       <c r="F147" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B148" t="n">
-        <v>669.8500343121515</v>
+        <v>673.0844464119266</v>
       </c>
       <c r="C148" t="n">
-        <v>681.330325511242</v>
+        <v>677.0176962940845</v>
       </c>
       <c r="D148" t="n">
-        <v>669.6903353309991</v>
+        <v>664.489217253305</v>
       </c>
       <c r="E148" t="n">
-        <v>677.4569702148438</v>
+        <v>670.189453125</v>
       </c>
       <c r="F148" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B149" t="n">
-        <v>673.0844464119266</v>
+        <v>667.7636045616339</v>
       </c>
       <c r="C149" t="n">
-        <v>677.0176962940845</v>
+        <v>673.0944797535534</v>
       </c>
       <c r="D149" t="n">
-        <v>664.489217253305</v>
+        <v>662.6723692427279</v>
       </c>
       <c r="E149" t="n">
-        <v>670.189453125</v>
+        <v>667.9732666015625</v>
       </c>
       <c r="F149" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B150" t="n">
-        <v>667.7636045616339</v>
+        <v>618.2586017744245</v>
       </c>
       <c r="C150" t="n">
-        <v>673.0944797535534</v>
+        <v>619.7859479396749</v>
       </c>
       <c r="D150" t="n">
-        <v>662.6723692427279</v>
+        <v>598.9717055442339</v>
       </c>
       <c r="E150" t="n">
-        <v>667.9732666015625</v>
+        <v>610.8612670898438</v>
       </c>
       <c r="F150" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B151" t="n">
-        <v>618.2586017744245</v>
+        <v>613.6365485572411</v>
       </c>
       <c r="C151" t="n">
-        <v>619.7859479396749</v>
+        <v>617.8193701850194</v>
       </c>
       <c r="D151" t="n">
-        <v>598.9717055442339</v>
+        <v>605.0712358749745</v>
       </c>
       <c r="E151" t="n">
-        <v>610.8612670898438</v>
+        <v>607.7067260742188</v>
       </c>
       <c r="F151" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B152" t="n">
-        <v>613.6365485572411</v>
+        <v>606.8981537761392</v>
       </c>
       <c r="C152" t="n">
-        <v>617.8193701850194</v>
+        <v>612.9477660987843</v>
       </c>
       <c r="D152" t="n">
-        <v>605.0712358749745</v>
+        <v>601.7170456287333</v>
       </c>
       <c r="E152" t="n">
-        <v>607.7067260742188</v>
+        <v>609.3638916015625</v>
       </c>
       <c r="F152" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B153" t="n">
-        <v>606.8981537761392</v>
+        <v>612.2588828439087</v>
       </c>
       <c r="C153" t="n">
-        <v>612.9477660987843</v>
+        <v>613.2970785161436</v>
       </c>
       <c r="D153" t="n">
-        <v>601.7170456287333</v>
+        <v>599.3310648754198</v>
       </c>
       <c r="E153" t="n">
-        <v>609.3638916015625</v>
+        <v>603.9232177734375</v>
       </c>
       <c r="F153" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B154" t="n">
-        <v>612.2588828439087</v>
+        <v>600.0199080772063</v>
       </c>
       <c r="C154" t="n">
-        <v>613.2970785161436</v>
+        <v>618.8875416216711</v>
       </c>
       <c r="D154" t="n">
-        <v>599.3310648754198</v>
+        <v>597.0749516023062</v>
       </c>
       <c r="E154" t="n">
-        <v>603.9232177734375</v>
+        <v>611.8296508789062</v>
       </c>
       <c r="F154" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B155" t="n">
-        <v>600.0199080772063</v>
+        <v>613.6664846485507</v>
       </c>
       <c r="C155" t="n">
-        <v>618.8875416216711</v>
+        <v>623.9089111604618</v>
       </c>
       <c r="D155" t="n">
-        <v>597.0749516023062</v>
+        <v>612.4885142038465</v>
       </c>
       <c r="E155" t="n">
-        <v>611.8296508789062</v>
+        <v>615.7529296875</v>
       </c>
       <c r="F155" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B156" t="n">
-        <v>613.6664238202088</v>
+        <v>614.145727971313</v>
       </c>
       <c r="C156" t="n">
-        <v>623.9088493168618</v>
+        <v>615.7130447332122</v>
       </c>
       <c r="D156" t="n">
-        <v>612.4884534922683</v>
+        <v>605.0213768033159</v>
       </c>
       <c r="E156" t="n">
-        <v>615.7528686523438</v>
+        <v>608.5852661132812</v>
       </c>
       <c r="F156" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B157" t="n">
-        <v>614.1456663784968</v>
+        <v>603.533915527778</v>
       </c>
       <c r="C157" t="n">
-        <v>615.7129829832094</v>
+        <v>603.8732987260729</v>
       </c>
       <c r="D157" t="n">
-        <v>605.0213161255829</v>
+        <v>597.0550476209405</v>
       </c>
       <c r="E157" t="n">
-        <v>608.585205078125</v>
+        <v>597.8336791992188</v>
       </c>
       <c r="F157" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B158" t="n">
-        <v>603.533915527778</v>
+        <v>593.8005792809215</v>
       </c>
       <c r="C158" t="n">
-        <v>603.8732987260729</v>
+        <v>602.7152673522038</v>
       </c>
       <c r="D158" t="n">
-        <v>597.0550476209405</v>
+        <v>591.5843523282613</v>
       </c>
       <c r="E158" t="n">
-        <v>597.8336791992188</v>
+        <v>601.966552734375</v>
       </c>
       <c r="F158" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B159" t="n">
-        <v>593.8006394881057</v>
+        <v>597.8037594995824</v>
       </c>
       <c r="C159" t="n">
-        <v>602.7153284632744</v>
+        <v>618.837657653709</v>
       </c>
       <c r="D159" t="n">
-        <v>591.5844123107358</v>
+        <v>595.6374345129168</v>
       </c>
       <c r="E159" t="n">
-        <v>601.9666137695312</v>
+        <v>615.5732421875</v>
       </c>
       <c r="F159" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B160" t="n">
-        <v>597.8037594995824</v>
+        <v>614.944289073115</v>
       </c>
       <c r="C160" t="n">
-        <v>618.837657653709</v>
+        <v>622.6610217742586</v>
       </c>
       <c r="D160" t="n">
-        <v>595.6374345129168</v>
+        <v>613.9460028895547</v>
       </c>
       <c r="E160" t="n">
-        <v>615.5732421875</v>
+        <v>617.3701171875</v>
       </c>
       <c r="F160" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B161" t="n">
-        <v>614.944289073115</v>
+        <v>612.9377281921389</v>
       </c>
       <c r="C161" t="n">
-        <v>622.6610217742586</v>
+        <v>620.1353935587166</v>
       </c>
       <c r="D161" t="n">
-        <v>613.9460028895547</v>
+        <v>608.2657561335159</v>
       </c>
       <c r="E161" t="n">
-        <v>617.3701171875</v>
+        <v>613.1773071289062</v>
       </c>
       <c r="F161" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B162" t="n">
-        <v>612.9377892034477</v>
+        <v>608.0660990208263</v>
       </c>
       <c r="C162" t="n">
-        <v>620.135455286475</v>
+        <v>614.5350350972873</v>
       </c>
       <c r="D162" t="n">
-        <v>608.2658166797805</v>
+        <v>602.6554048207697</v>
       </c>
       <c r="E162" t="n">
-        <v>613.1773681640625</v>
+        <v>610.1625366210938</v>
       </c>
       <c r="F162" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B163" t="n">
-        <v>608.0660990208263</v>
+        <v>607.8763927177921</v>
       </c>
       <c r="C163" t="n">
-        <v>614.5350350972873</v>
+        <v>612.8778161384099</v>
       </c>
       <c r="D163" t="n">
-        <v>602.6554048207697</v>
+        <v>599.5207424161133</v>
       </c>
       <c r="E163" t="n">
-        <v>610.1625366210938</v>
+        <v>601.5772094726562</v>
       </c>
       <c r="F163" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B164" t="n">
-        <v>607.8764543920544</v>
+        <v>599.7304526335664</v>
       </c>
       <c r="C164" t="n">
-        <v>612.8778783201094</v>
+        <v>606.9580352784536</v>
       </c>
       <c r="D164" t="n">
-        <v>599.5208032426234</v>
+        <v>596.7854960328639</v>
       </c>
       <c r="E164" t="n">
-        <v>601.5772705078125</v>
+        <v>604.0230712890625</v>
       </c>
       <c r="F164" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B165" t="n">
-        <v>599.7304526335664</v>
+        <v>598.9717538809448</v>
       </c>
       <c r="C165" t="n">
-        <v>606.9580352784536</v>
+        <v>608.5552775708169</v>
       </c>
       <c r="D165" t="n">
-        <v>596.7854960328639</v>
+        <v>593.7906457726523</v>
       </c>
       <c r="E165" t="n">
-        <v>604.0230712890625</v>
+        <v>606.339111328125</v>
       </c>
       <c r="F165" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B166" t="n">
-        <v>598.9716935873996</v>
+        <v>606.8381854335279</v>
       </c>
       <c r="C166" t="n">
-        <v>608.5552163125774</v>
+        <v>613.7563010923075</v>
       </c>
       <c r="D166" t="n">
-        <v>593.7905860006466</v>
+        <v>605.9097866322771</v>
       </c>
       <c r="E166" t="n">
-        <v>606.3390502929688</v>
+        <v>609.214111328125</v>
       </c>
       <c r="F166" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B167" t="n">
-        <v>606.838246230648</v>
+        <v>607.8465495511928</v>
       </c>
       <c r="C167" t="n">
-        <v>613.7563625825306</v>
+        <v>613.4169431409898</v>
       </c>
       <c r="D167" t="n">
-        <v>605.9098473363839</v>
+        <v>604.2626749853522</v>
       </c>
       <c r="E167" t="n">
-        <v>609.2141723632812</v>
+        <v>611.2906494140625</v>
       </c>
       <c r="F167" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B168" t="n">
-        <v>607.8464888599174</v>
+        <v>608.3555996261091</v>
       </c>
       <c r="C168" t="n">
-        <v>613.4168818935308</v>
+        <v>637.4057020013258</v>
       </c>
       <c r="D168" t="n">
-        <v>604.2626146519137</v>
+        <v>607.9562607968793</v>
       </c>
       <c r="E168" t="n">
-        <v>611.2905883789062</v>
+        <v>634.1712646484375</v>
       </c>
       <c r="F168" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B169" t="n">
-        <v>608.3556581766634</v>
+        <v>638.4040398455469</v>
       </c>
       <c r="C169" t="n">
-        <v>637.4057633477772</v>
+        <v>641.8980416273442</v>
       </c>
       <c r="D169" t="n">
-        <v>607.9563193089997</v>
+        <v>628.2315007921775</v>
       </c>
       <c r="E169" t="n">
-        <v>634.1713256835938</v>
+        <v>634.2012329101562</v>
       </c>
       <c r="F169" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B170" t="n">
-        <v>638.4040398455469</v>
+        <v>632.4143189973911</v>
       </c>
       <c r="C170" t="n">
-        <v>641.8980416273442</v>
+        <v>633.4126052152244</v>
       </c>
       <c r="D170" t="n">
-        <v>628.2315007921775</v>
+        <v>622.281689514161</v>
       </c>
       <c r="E170" t="n">
-        <v>634.2012329101562</v>
+        <v>631.426025390625</v>
       </c>
       <c r="F170" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B171" t="n">
-        <v>632.4143189973911</v>
+        <v>629.3196791836195</v>
       </c>
       <c r="C171" t="n">
-        <v>633.4126052152244</v>
+        <v>634.6604862727559</v>
       </c>
       <c r="D171" t="n">
-        <v>622.281689514161</v>
+        <v>598.5025873828931</v>
       </c>
       <c r="E171" t="n">
-        <v>631.426025390625</v>
+        <v>599.44091796875</v>
       </c>
       <c r="F171" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B172" t="n">
-        <v>629.3196151062037</v>
+        <v>602.2062063737548</v>
       </c>
       <c r="C172" t="n">
-        <v>634.6604216515384</v>
+        <v>607.8365556216692</v>
       </c>
       <c r="D172" t="n">
-        <v>598.5025264432778</v>
+        <v>595.6574508079194</v>
       </c>
       <c r="E172" t="n">
-        <v>599.4408569335938</v>
+        <v>596.6058349609375</v>
       </c>
       <c r="F172" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B173" t="n">
-        <v>602.2061447656582</v>
+        <v>601.9665545007575</v>
       </c>
       <c r="C173" t="n">
-        <v>607.8364934375654</v>
+        <v>623.0803311577063</v>
       </c>
       <c r="D173" t="n">
-        <v>595.6573898697867</v>
+        <v>599.2412527816401</v>
       </c>
       <c r="E173" t="n">
-        <v>596.6057739257812</v>
+        <v>621.9122924804688</v>
       </c>
       <c r="F173" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B174" t="n">
-        <v>601.9666135784172</v>
+        <v>622.6011661035562</v>
       </c>
       <c r="C174" t="n">
-        <v>623.0803923074952</v>
+        <v>641.2991089275577</v>
       </c>
       <c r="D174" t="n">
-        <v>599.2413115918356</v>
+        <v>621.3633009071642</v>
       </c>
       <c r="E174" t="n">
-        <v>621.912353515625</v>
+        <v>626.4945068359375</v>
       </c>
       <c r="F174" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B175" t="n">
-        <v>622.601105447702</v>
+        <v>622.3915225332053</v>
       </c>
       <c r="C175" t="n">
-        <v>641.2990464500883</v>
+        <v>628.0717733238163</v>
       </c>
       <c r="D175" t="n">
-        <v>621.3632403719068</v>
+        <v>581.9109692668093</v>
       </c>
       <c r="E175" t="n">
-        <v>626.4944458007812</v>
+        <v>591.9837036132812</v>
       </c>
       <c r="F175" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B176" t="n">
-        <v>622.3915867034917</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="C176" t="n">
-        <v>628.0718380797523</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="D176" t="n">
-        <v>581.9110292634388</v>
+        <v>578.2273099921849</v>
       </c>
       <c r="E176" t="n">
-        <v>591.9837646484375</v>
+        <v>584.3867797851562</v>
       </c>
       <c r="F176" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B177" t="n">
-        <v>590.9854370177134</v>
+        <v>589.9871222602228</v>
       </c>
       <c r="C177" t="n">
-        <v>590.9854370177134</v>
+        <v>596.6057643945405</v>
       </c>
       <c r="D177" t="n">
-        <v>578.2273099921849</v>
+        <v>580.0142532419713</v>
       </c>
       <c r="E177" t="n">
-        <v>584.3867797851562</v>
+        <v>583.588134765625</v>
       </c>
       <c r="F177" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B178" t="n">
-        <v>589.9871222602228</v>
+        <v>579.7347558037309</v>
       </c>
       <c r="C178" t="n">
-        <v>596.6057643945405</v>
+        <v>590.3066340250939</v>
       </c>
       <c r="D178" t="n">
-        <v>580.0142532419713</v>
+        <v>569.6221111934292</v>
       </c>
       <c r="E178" t="n">
-        <v>583.588134765625</v>
+        <v>570.00146484375</v>
       </c>
       <c r="F178" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B179" t="n">
-        <v>579.7347558037309</v>
+        <v>564.8602908302337</v>
       </c>
       <c r="C179" t="n">
-        <v>590.3066340250939</v>
+        <v>571.1893911411966</v>
       </c>
       <c r="D179" t="n">
-        <v>569.6221111934292</v>
+        <v>556.0553993401948</v>
       </c>
       <c r="E179" t="n">
-        <v>570.00146484375</v>
+        <v>567.455810546875</v>
       </c>
       <c r="F179" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B180" t="n">
-        <v>564.8602908302337</v>
+        <v>571.968101190783</v>
       </c>
       <c r="C180" t="n">
-        <v>571.1893911411966</v>
+        <v>575.0827493186854</v>
       </c>
       <c r="D180" t="n">
-        <v>556.0553993401948</v>
+        <v>559.9387644415484</v>
       </c>
       <c r="E180" t="n">
-        <v>567.455810546875</v>
+        <v>566.00830078125</v>
       </c>
       <c r="F180" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,25 +5123,25 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B181" t="n">
-        <v>571.9680395129554</v>
+        <v>579.4427159724761</v>
       </c>
       <c r="C181" t="n">
-        <v>575.0826873049916</v>
+        <v>600.795858737961</v>
       </c>
       <c r="D181" t="n">
-        <v>559.938704060897</v>
+        <v>578.8431525395191</v>
       </c>
       <c r="E181" t="n">
-        <v>566.0082397460938</v>
+        <v>593.011962890625</v>
       </c>
       <c r="F181" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5149,25 +5149,25 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B182" t="n">
-        <v>579.4427159724761</v>
+        <v>593.1818700134238</v>
       </c>
       <c r="C182" t="n">
-        <v>600.795858737961</v>
+        <v>605.3322537623429</v>
       </c>
       <c r="D182" t="n">
-        <v>578.8431525395191</v>
+        <v>591.5331468141493</v>
       </c>
       <c r="E182" t="n">
-        <v>593.011962890625</v>
+        <v>599.7366943359375</v>
       </c>
       <c r="F182" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G182" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B183" t="n">
-        <v>593.1818700134238</v>
+        <v>591.5331725816898</v>
       </c>
       <c r="C183" t="n">
-        <v>605.3322537623429</v>
+        <v>593.3417428489197</v>
       </c>
       <c r="D183" t="n">
-        <v>591.5331468141493</v>
+        <v>565.7435277503374</v>
       </c>
       <c r="E183" t="n">
-        <v>599.7366943359375</v>
+        <v>567.1324462890625</v>
       </c>
       <c r="F183" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B184" t="n">
-        <v>591.5331725816898</v>
+        <v>572.3682769745303</v>
       </c>
       <c r="C184" t="n">
-        <v>593.3417428489197</v>
+        <v>579.7624046842873</v>
       </c>
       <c r="D184" t="n">
-        <v>565.7435277503374</v>
+        <v>562.6559105294999</v>
       </c>
       <c r="E184" t="n">
-        <v>567.1324462890625</v>
+        <v>576.7647705078125</v>
       </c>
       <c r="F184" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B185" t="n">
-        <v>572.3682769745303</v>
+        <v>571.5689356803741</v>
       </c>
       <c r="C185" t="n">
-        <v>579.7624046842873</v>
+        <v>575.3559250048318</v>
       </c>
       <c r="D185" t="n">
-        <v>562.6559105294999</v>
+        <v>559.3685422933314</v>
       </c>
       <c r="E185" t="n">
-        <v>576.7647705078125</v>
+        <v>563.4053344726562</v>
       </c>
       <c r="F185" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B186" t="n">
-        <v>571.5689356803741</v>
+        <v>561.8066012038755</v>
       </c>
       <c r="C186" t="n">
-        <v>575.3559250048318</v>
+        <v>571.7487666818112</v>
       </c>
       <c r="D186" t="n">
-        <v>559.3685422933314</v>
+        <v>560.5775907162</v>
       </c>
       <c r="E186" t="n">
-        <v>563.4053344726562</v>
+        <v>561.7566528320312</v>
       </c>
       <c r="F186" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B187" t="n">
-        <v>561.8066012038755</v>
+        <v>561.4469285838474</v>
       </c>
       <c r="C187" t="n">
-        <v>571.7487666818112</v>
+        <v>568.591253761232</v>
       </c>
       <c r="D187" t="n">
-        <v>560.5775907162</v>
+        <v>555.1119012433646</v>
       </c>
       <c r="E187" t="n">
-        <v>561.7566528320312</v>
+        <v>557.230224609375</v>
       </c>
       <c r="F187" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B188" t="n">
-        <v>561.4469285838474</v>
+        <v>555.1118879211193</v>
       </c>
       <c r="C188" t="n">
-        <v>568.591253761232</v>
+        <v>555.9013039685537</v>
       </c>
       <c r="D188" t="n">
-        <v>555.1119012433646</v>
+        <v>539.7540133926082</v>
       </c>
       <c r="E188" t="n">
-        <v>557.230224609375</v>
+        <v>542.44189453125</v>
       </c>
       <c r="F188" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B189" t="n">
-        <v>555.1118879211193</v>
+        <v>542.9115767800729</v>
       </c>
       <c r="C189" t="n">
-        <v>555.9013039685537</v>
+        <v>556.4108722579447</v>
       </c>
       <c r="D189" t="n">
-        <v>539.7540133926082</v>
+        <v>539.9738926737891</v>
       </c>
       <c r="E189" t="n">
-        <v>542.44189453125</v>
+        <v>549.8161010742188</v>
       </c>
       <c r="F189" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B190" t="n">
-        <v>542.9115767800729</v>
+        <v>559.5583857816937</v>
       </c>
       <c r="C190" t="n">
-        <v>556.4108722579447</v>
+        <v>570.4498144711828</v>
       </c>
       <c r="D190" t="n">
-        <v>539.9738926737891</v>
+        <v>557.5599629753306</v>
       </c>
       <c r="E190" t="n">
-        <v>549.8161010742188</v>
+        <v>562.1563110351562</v>
       </c>
       <c r="F190" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B191" t="n">
-        <v>559.5583857816937</v>
+        <v>560.4976417791106</v>
       </c>
       <c r="C191" t="n">
-        <v>570.4498144711828</v>
+        <v>565.0939897966132</v>
       </c>
       <c r="D191" t="n">
-        <v>557.5599629753306</v>
+        <v>550.9951316644288</v>
       </c>
       <c r="E191" t="n">
-        <v>562.1563110351562</v>
+        <v>562.8457641601562</v>
       </c>
       <c r="F191" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B192" t="n">
-        <v>560.4976417791106</v>
+        <v>607.4305787144307</v>
       </c>
       <c r="C192" t="n">
-        <v>565.0939897966132</v>
+        <v>627.784571153574</v>
       </c>
       <c r="D192" t="n">
-        <v>550.9951316644288</v>
+        <v>594.6306830487989</v>
       </c>
       <c r="E192" t="n">
-        <v>562.8457641601562</v>
+        <v>612.4266357421875</v>
       </c>
       <c r="F192" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B193" t="n">
-        <v>607.4305787144307</v>
+        <v>607.4206544757068</v>
       </c>
       <c r="C193" t="n">
-        <v>627.784571153574</v>
+        <v>609.5189740900589</v>
       </c>
       <c r="D193" t="n">
-        <v>594.6306830487989</v>
+        <v>579.9622828274885</v>
       </c>
       <c r="E193" t="n">
-        <v>612.4266357421875</v>
+        <v>582.4403686523438</v>
       </c>
       <c r="F193" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B194" t="n">
-        <v>607.4206544757068</v>
+        <v>594.3709360150443</v>
       </c>
       <c r="C194" t="n">
-        <v>609.5189740900589</v>
+        <v>603.1040338931904</v>
       </c>
       <c r="D194" t="n">
-        <v>579.9622828274885</v>
+        <v>581.301233826573</v>
       </c>
       <c r="E194" t="n">
-        <v>582.4403686523438</v>
+        <v>599.8165893554688</v>
       </c>
       <c r="F194" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B195" t="n">
-        <v>594.3709360150443</v>
+        <v>607.1109147253509</v>
       </c>
       <c r="C195" t="n">
-        <v>603.1040338931904</v>
+        <v>624.8768626804635</v>
       </c>
       <c r="D195" t="n">
-        <v>581.301233826573</v>
+        <v>603.1839600389557</v>
       </c>
       <c r="E195" t="n">
-        <v>599.8165893554688</v>
+        <v>615.0946044921875</v>
       </c>
       <c r="F195" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B196" t="n">
-        <v>607.1109147253509</v>
+        <v>613.9055418180343</v>
       </c>
       <c r="C196" t="n">
-        <v>624.8768626804635</v>
+        <v>615.5142576272189</v>
       </c>
       <c r="D196" t="n">
-        <v>603.1839600389557</v>
+        <v>597.5384532703483</v>
       </c>
       <c r="E196" t="n">
-        <v>615.0946044921875</v>
+        <v>602.6444091796875</v>
       </c>
       <c r="F196" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B197" t="n">
-        <v>613.9055418180343</v>
+        <v>583.529455055522</v>
       </c>
       <c r="C197" t="n">
-        <v>615.5142576272189</v>
+        <v>632.77062206454</v>
       </c>
       <c r="D197" t="n">
-        <v>597.5384532703483</v>
+        <v>576.6149292518581</v>
       </c>
       <c r="E197" t="n">
-        <v>602.6444091796875</v>
+        <v>630.9819946289062</v>
       </c>
       <c r="F197" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B198" t="n">
-        <v>583.529455055522</v>
+        <v>659.8193113874754</v>
       </c>
       <c r="C198" t="n">
-        <v>632.77062206454</v>
+        <v>677.3254544051542</v>
       </c>
       <c r="D198" t="n">
-        <v>576.6149292518581</v>
+        <v>657.491131647921</v>
       </c>
       <c r="E198" t="n">
-        <v>630.9819946289062</v>
+        <v>668.6823120117188</v>
       </c>
       <c r="F198" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B199" t="n">
-        <v>659.8193113874754</v>
+        <v>660.858454671636</v>
       </c>
       <c r="C199" t="n">
-        <v>677.3254544051542</v>
+        <v>676.0864269737083</v>
       </c>
       <c r="D199" t="n">
-        <v>657.491131647921</v>
+        <v>653.6841239854351</v>
       </c>
       <c r="E199" t="n">
-        <v>668.6823120117188</v>
+        <v>656.2120971679688</v>
       </c>
       <c r="F199" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>660.858454671636</v>
+        <v>651.4858277274717</v>
       </c>
       <c r="C200" t="n">
-        <v>676.0864269737083</v>
+        <v>665.9743929146624</v>
       </c>
       <c r="D200" t="n">
-        <v>653.6841239854351</v>
+        <v>648.5381419230179</v>
       </c>
       <c r="E200" t="n">
-        <v>656.2120971679688</v>
+        <v>660.5186767578125</v>
       </c>
       <c r="F200" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>651.4858277274717</v>
+        <v>663.0767089741589</v>
       </c>
       <c r="C201" t="n">
-        <v>665.9743929146624</v>
+        <v>685.5390243545221</v>
       </c>
       <c r="D201" t="n">
-        <v>648.5381419230179</v>
+        <v>656.1421789132482</v>
       </c>
       <c r="E201" t="n">
-        <v>660.5186767578125</v>
+        <v>680.7727661132812</v>
       </c>
       <c r="F201" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>663.0767089741589</v>
+        <v>676.7459348014426</v>
       </c>
       <c r="C202" t="n">
-        <v>685.5390243545221</v>
+        <v>681.3622866487058</v>
       </c>
       <c r="D202" t="n">
-        <v>656.1421789132482</v>
+        <v>659.6393793096187</v>
       </c>
       <c r="E202" t="n">
-        <v>680.7727661132812</v>
+        <v>664.0159301757812</v>
       </c>
       <c r="F202" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B203" t="n">
-        <v>676.7459348014426</v>
+        <v>647.1892801723585</v>
       </c>
       <c r="C203" t="n">
-        <v>681.3622866487058</v>
+        <v>651.68573177941</v>
       </c>
       <c r="D203" t="n">
-        <v>659.6393793096187</v>
+        <v>625.5063791142821</v>
       </c>
       <c r="E203" t="n">
-        <v>664.0159301757812</v>
+        <v>645.5006103515625</v>
       </c>
       <c r="F203" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B204" t="n">
-        <v>647.1892801723585</v>
+        <v>646.1900645769782</v>
       </c>
       <c r="C204" t="n">
-        <v>651.68573177941</v>
+        <v>652.7848358303891</v>
       </c>
       <c r="D204" t="n">
-        <v>625.5063791142821</v>
+        <v>635.5084916103011</v>
       </c>
       <c r="E204" t="n">
-        <v>645.5006103515625</v>
+        <v>645.3406982421875</v>
       </c>
       <c r="F204" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B205" t="n">
-        <v>646.1900645769782</v>
+        <v>653.664124760039</v>
       </c>
       <c r="C205" t="n">
-        <v>652.7848358303891</v>
+        <v>655.3627963853286</v>
       </c>
       <c r="D205" t="n">
-        <v>635.5084916103011</v>
+        <v>642.6928027946103</v>
       </c>
       <c r="E205" t="n">
-        <v>645.3406982421875</v>
+        <v>643.3023071289062</v>
       </c>
       <c r="F205" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B206" t="n">
-        <v>653.664124760039</v>
+        <v>647.189254956408</v>
       </c>
       <c r="C206" t="n">
-        <v>655.3627963853286</v>
+        <v>648.4882176170956</v>
       </c>
       <c r="D206" t="n">
-        <v>642.6928027946103</v>
+        <v>623.5079318845419</v>
       </c>
       <c r="E206" t="n">
-        <v>643.3023071289062</v>
+        <v>626.6754150390625</v>
       </c>
       <c r="F206" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B207" t="n">
-        <v>647.189254956408</v>
+        <v>607.9301851876114</v>
       </c>
       <c r="C207" t="n">
-        <v>648.4882176170956</v>
+        <v>614.1653155952538</v>
       </c>
       <c r="D207" t="n">
-        <v>623.5079318845419</v>
+        <v>596.7490071058414</v>
       </c>
       <c r="E207" t="n">
-        <v>626.6754150390625</v>
+        <v>605.6220092773438</v>
       </c>
       <c r="F207" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B208" t="n">
-        <v>607.9301851876114</v>
+        <v>604.8226548171024</v>
       </c>
       <c r="C208" t="n">
-        <v>614.1653155952538</v>
+        <v>609.4989569016461</v>
       </c>
       <c r="D208" t="n">
-        <v>596.7490071058414</v>
+        <v>593.9812354037057</v>
       </c>
       <c r="E208" t="n">
-        <v>605.6220092773438</v>
+        <v>594.7206420898438</v>
       </c>
       <c r="F208" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B209" t="n">
-        <v>604.8226548171024</v>
+        <v>606.7411202287035</v>
       </c>
       <c r="C209" t="n">
-        <v>609.4989569016461</v>
+        <v>610.7779733376527</v>
       </c>
       <c r="D209" t="n">
-        <v>593.9812354037057</v>
+        <v>592.6622656813121</v>
       </c>
       <c r="E209" t="n">
-        <v>594.7206420898438</v>
+        <v>593.4016723632812</v>
       </c>
       <c r="F209" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B210" t="n">
-        <v>606.7411202287035</v>
+        <v>596.3493616660036</v>
       </c>
       <c r="C210" t="n">
-        <v>610.7779733376527</v>
+        <v>600.5260580457825</v>
       </c>
       <c r="D210" t="n">
-        <v>592.6622656813121</v>
+        <v>586.5370982909723</v>
       </c>
       <c r="E210" t="n">
-        <v>593.4016723632812</v>
+        <v>592.9420166015625</v>
       </c>
       <c r="F210" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B211" t="n">
-        <v>596.3493616660036</v>
+        <v>592.7821833537371</v>
       </c>
       <c r="C211" t="n">
-        <v>600.5260580457825</v>
+        <v>599.4968549179539</v>
       </c>
       <c r="D211" t="n">
-        <v>586.5370982909723</v>
+        <v>581.7608519604674</v>
       </c>
       <c r="E211" t="n">
-        <v>592.9420166015625</v>
+        <v>585.148193359375</v>
       </c>
       <c r="F211" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B212" t="n">
-        <v>592.7821833537371</v>
+        <v>525.58522592167</v>
       </c>
       <c r="C212" t="n">
-        <v>599.4968549179539</v>
+        <v>539.4542858116451</v>
       </c>
       <c r="D212" t="n">
-        <v>581.7608519604674</v>
+        <v>524.0764068649972</v>
       </c>
       <c r="E212" t="n">
-        <v>585.148193359375</v>
+        <v>538.60498046875</v>
       </c>
       <c r="F212" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B213" t="n">
-        <v>525.58522592167</v>
+        <v>543.171288392182</v>
       </c>
       <c r="C213" t="n">
-        <v>539.4542858116451</v>
+        <v>557.8897136701136</v>
       </c>
       <c r="D213" t="n">
-        <v>524.0764068649972</v>
+        <v>539.7939490076644</v>
       </c>
       <c r="E213" t="n">
-        <v>538.60498046875</v>
+        <v>556.27099609375</v>
       </c>
       <c r="F213" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B214" t="n">
-        <v>543.171288392182</v>
+        <v>561.7966164985271</v>
       </c>
       <c r="C214" t="n">
-        <v>557.8897136701136</v>
+        <v>597.0488245114987</v>
       </c>
       <c r="D214" t="n">
-        <v>539.7939490076644</v>
+        <v>558.9188827428958</v>
       </c>
       <c r="E214" t="n">
-        <v>556.27099609375</v>
+        <v>589.7745361328125</v>
       </c>
       <c r="F214" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B215" t="n">
-        <v>561.7966164985271</v>
+        <v>581.0414552494501</v>
       </c>
       <c r="C215" t="n">
-        <v>597.0488245114987</v>
+        <v>592.32253050782</v>
       </c>
       <c r="D215" t="n">
-        <v>558.9188827428958</v>
+        <v>577.794018053301</v>
       </c>
       <c r="E215" t="n">
-        <v>589.7745361328125</v>
+        <v>587.4763793945312</v>
       </c>
       <c r="F215" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B216" t="n">
-        <v>581.0414552494501</v>
+        <v>599.9865089938204</v>
       </c>
       <c r="C216" t="n">
-        <v>592.32253050782</v>
+        <v>600.5260612032997</v>
       </c>
       <c r="D216" t="n">
-        <v>577.794018053301</v>
+        <v>579.6625219517506</v>
       </c>
       <c r="E216" t="n">
-        <v>587.4763793945312</v>
+        <v>588.3057250976562</v>
       </c>
       <c r="F216" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B217" t="n">
-        <v>599.9865089938204</v>
+        <v>586.487189429669</v>
       </c>
       <c r="C217" t="n">
-        <v>600.5260612032997</v>
+        <v>594.8405827519979</v>
       </c>
       <c r="D217" t="n">
-        <v>579.6625219517506</v>
+        <v>585.5379263278069</v>
       </c>
       <c r="E217" t="n">
-        <v>588.3057250976562</v>
+        <v>589.4348754882812</v>
       </c>
       <c r="F217" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B218" t="n">
-        <v>586.487189429669</v>
+        <v>585.1781899072663</v>
       </c>
       <c r="C218" t="n">
-        <v>594.8405827519979</v>
+        <v>598.2678350979388</v>
       </c>
       <c r="D218" t="n">
-        <v>585.5379263278069</v>
+        <v>585.1581861630435</v>
       </c>
       <c r="E218" t="n">
-        <v>589.4348754882812</v>
+        <v>591.633056640625</v>
       </c>
       <c r="F218" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B219" t="n">
-        <v>585.1781899072663</v>
+        <v>598.657568915248</v>
       </c>
       <c r="C219" t="n">
-        <v>598.2678350979388</v>
+        <v>607.7304260788247</v>
       </c>
       <c r="D219" t="n">
-        <v>585.1581861630435</v>
+        <v>591.5631919202813</v>
       </c>
       <c r="E219" t="n">
-        <v>591.633056640625</v>
+        <v>594.4508666992188</v>
       </c>
       <c r="F219" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B220" t="n">
-        <v>598.657568915248</v>
+        <v>597.5284100969216</v>
       </c>
       <c r="C220" t="n">
-        <v>607.7304260788247</v>
+        <v>611.9470231090784</v>
       </c>
       <c r="D220" t="n">
-        <v>591.5631919202813</v>
+        <v>592.9320621063698</v>
       </c>
       <c r="E220" t="n">
-        <v>594.4508666992188</v>
+        <v>598.6475219726562</v>
       </c>
       <c r="F220" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B221" t="n">
-        <v>597.5284100969216</v>
+        <v>600.5960026412422</v>
       </c>
       <c r="C221" t="n">
-        <v>611.9470231090784</v>
+        <v>604.023290419805</v>
       </c>
       <c r="D221" t="n">
-        <v>592.9320621063698</v>
+        <v>577.7540447074138</v>
       </c>
       <c r="E221" t="n">
-        <v>598.6475219726562</v>
+        <v>578.3934936523438</v>
       </c>
       <c r="F221" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B222" t="n">
-        <v>600.5960026412422</v>
+        <v>580.2520897369063</v>
       </c>
       <c r="C222" t="n">
-        <v>604.023290419805</v>
+        <v>595.3801043917661</v>
       </c>
       <c r="D222" t="n">
-        <v>577.7540447074138</v>
+        <v>578.9331233348041</v>
       </c>
       <c r="E222" t="n">
-        <v>578.3934936523438</v>
+        <v>594.5007934570312</v>
       </c>
       <c r="F222" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B223" t="n">
-        <v>580.2520897369063</v>
+        <v>596.5092089028919</v>
       </c>
       <c r="C223" t="n">
-        <v>595.3801043917661</v>
+        <v>601.3853654698224</v>
       </c>
       <c r="D223" t="n">
-        <v>578.9331233348041</v>
+        <v>588.8252707092146</v>
       </c>
       <c r="E223" t="n">
-        <v>594.5007934570312</v>
+        <v>589.3848266601562</v>
       </c>
       <c r="F223" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B224" t="n">
-        <v>596.5092089028919</v>
+        <v>589.2849441761664</v>
       </c>
       <c r="C224" t="n">
-        <v>601.3853654698224</v>
+        <v>589.774548021712</v>
       </c>
       <c r="D224" t="n">
-        <v>588.8252707092146</v>
+        <v>564.3046582848494</v>
       </c>
       <c r="E224" t="n">
-        <v>589.3848266601562</v>
+        <v>568.5213012695312</v>
       </c>
       <c r="F224" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B225" t="n">
-        <v>589.2849441761664</v>
+        <v>557.0403796583744</v>
       </c>
       <c r="C225" t="n">
-        <v>589.774548021712</v>
+        <v>560.2178647510921</v>
       </c>
       <c r="D225" t="n">
-        <v>564.3046582848494</v>
+        <v>542.7816737373303</v>
       </c>
       <c r="E225" t="n">
-        <v>568.5213012695312</v>
+        <v>543.2412719726562</v>
       </c>
       <c r="F225" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B226" t="n">
-        <v>557.0403796583744</v>
+        <v>540.9131223962278</v>
       </c>
       <c r="C226" t="n">
-        <v>560.2178647510921</v>
+        <v>553.6330639150415</v>
       </c>
       <c r="D226" t="n">
-        <v>542.7816737373303</v>
+        <v>536.8463247077087</v>
       </c>
       <c r="E226" t="n">
-        <v>543.2412719726562</v>
+        <v>545.5994262695312</v>
       </c>
       <c r="F226" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B227" t="n">
-        <v>540.9131223962278</v>
+        <v>546.5187091013889</v>
       </c>
       <c r="C227" t="n">
-        <v>553.6330639150415</v>
+        <v>549.5562899225255</v>
       </c>
       <c r="D227" t="n">
-        <v>536.8463247077087</v>
+        <v>538.8847190657524</v>
       </c>
       <c r="E227" t="n">
-        <v>545.5994262695312</v>
+        <v>545.3995971679688</v>
       </c>
       <c r="F227" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B228" t="n">
-        <v>546.5187091013889</v>
+        <v>546.4587335768297</v>
       </c>
       <c r="C228" t="n">
-        <v>549.5562899225255</v>
+        <v>553.4332095869578</v>
       </c>
       <c r="D228" t="n">
-        <v>538.8847190657524</v>
+        <v>542.8015857242297</v>
       </c>
       <c r="E228" t="n">
-        <v>545.3995971679688</v>
+        <v>549.4663696289062</v>
       </c>
       <c r="F228" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B229" t="n">
-        <v>546.4587335768297</v>
+        <v>549.7661710202622</v>
       </c>
       <c r="C229" t="n">
-        <v>553.4332095869578</v>
+        <v>560.9772946036173</v>
       </c>
       <c r="D229" t="n">
-        <v>542.8015857242297</v>
+        <v>545.8692218355393</v>
       </c>
       <c r="E229" t="n">
-        <v>549.4663696289062</v>
+        <v>558.5792236328125</v>
       </c>
       <c r="F229" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B230" t="n">
-        <v>549.7661710202622</v>
+        <v>563.4353464162</v>
       </c>
       <c r="C230" t="n">
-        <v>560.9772946036173</v>
+        <v>570.3498724402046</v>
       </c>
       <c r="D230" t="n">
-        <v>545.8692218355393</v>
+        <v>560.9573215839381</v>
       </c>
       <c r="E230" t="n">
-        <v>558.5792236328125</v>
+        <v>569.6004638671875</v>
       </c>
       <c r="F230" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B231" t="n">
-        <v>563.4353464162</v>
+        <v>589.8444773654404</v>
       </c>
       <c r="C231" t="n">
-        <v>570.3498724402046</v>
+        <v>592.8721171723366</v>
       </c>
       <c r="D231" t="n">
-        <v>560.9573215839381</v>
+        <v>561.4369046651577</v>
       </c>
       <c r="E231" t="n">
-        <v>569.6004638671875</v>
+        <v>575.6856689453125</v>
       </c>
       <c r="F231" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B232" t="n">
-        <v>589.8444773654404</v>
+        <v>576.0253592943615</v>
       </c>
       <c r="C232" t="n">
-        <v>592.8721171723366</v>
+        <v>587.9260010338789</v>
       </c>
       <c r="D232" t="n">
-        <v>561.4369046651577</v>
+        <v>567.1723610665189</v>
       </c>
       <c r="E232" t="n">
-        <v>575.6856689453125</v>
+        <v>570.6495971679688</v>
       </c>
       <c r="F232" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B233" t="n">
-        <v>576.0253592943615</v>
+        <v>571.0992793335739</v>
       </c>
       <c r="C233" t="n">
-        <v>587.9260010338789</v>
+        <v>588.7253835559844</v>
       </c>
       <c r="D233" t="n">
-        <v>567.1723610665189</v>
+        <v>570.5497252457161</v>
       </c>
       <c r="E233" t="n">
-        <v>570.6495971679688</v>
+        <v>577.564208984375</v>
       </c>
       <c r="F233" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B234" t="n">
-        <v>571.0992793335739</v>
+        <v>577.1744781551006</v>
       </c>
       <c r="C234" t="n">
-        <v>588.7253835559844</v>
+        <v>578.2236379136884</v>
       </c>
       <c r="D234" t="n">
-        <v>570.5497252457161</v>
+        <v>568.6911832402849</v>
       </c>
       <c r="E234" t="n">
-        <v>577.564208984375</v>
+        <v>571.888671875</v>
       </c>
       <c r="F234" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B235" t="n">
-        <v>577.1744781551006</v>
+        <v>557.9096596695957</v>
       </c>
       <c r="C235" t="n">
-        <v>578.2236379136884</v>
+        <v>584.4887194481862</v>
       </c>
       <c r="D235" t="n">
-        <v>568.6911832402849</v>
+        <v>555.6614340241316</v>
       </c>
       <c r="E235" t="n">
-        <v>571.888671875</v>
+        <v>578.083740234375</v>
       </c>
       <c r="F235" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B236" t="n">
-        <v>557.9096596695957</v>
+        <v>578.3335366296732</v>
       </c>
       <c r="C236" t="n">
-        <v>584.4887194481862</v>
+        <v>599.9065373056851</v>
       </c>
       <c r="D236" t="n">
-        <v>555.6614340241316</v>
+        <v>576.5449702025707</v>
       </c>
       <c r="E236" t="n">
-        <v>578.083740234375</v>
+        <v>592.3824462890625</v>
       </c>
       <c r="F236" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B237" t="n">
-        <v>578.3335366296732</v>
+        <v>604.0133041368691</v>
       </c>
       <c r="C237" t="n">
-        <v>599.9065373056851</v>
+        <v>618.9715308723809</v>
       </c>
       <c r="D237" t="n">
-        <v>576.5449702025707</v>
+        <v>603.8733999005765</v>
       </c>
       <c r="E237" t="n">
-        <v>592.3824462890625</v>
+        <v>610.1984252929688</v>
       </c>
       <c r="F237" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B238" t="n">
-        <v>604.0133041368691</v>
+        <v>611.8670721034152</v>
       </c>
       <c r="C238" t="n">
-        <v>618.9715308723809</v>
+        <v>616.9730886717387</v>
       </c>
       <c r="D238" t="n">
-        <v>603.8733999005765</v>
+        <v>604.7926993516937</v>
       </c>
       <c r="E238" t="n">
-        <v>610.1984252929688</v>
+        <v>616.2836303710938</v>
       </c>
       <c r="F238" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B239" t="n">
-        <v>611.8670721034152</v>
+        <v>615.7241045276966</v>
       </c>
       <c r="C239" t="n">
-        <v>616.9730886717387</v>
+        <v>624.3072966603136</v>
       </c>
       <c r="D239" t="n">
-        <v>604.7926993516937</v>
+        <v>609.2591747857786</v>
       </c>
       <c r="E239" t="n">
-        <v>616.2836303710938</v>
+        <v>612.9962158203125</v>
       </c>
       <c r="F239" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B240" t="n">
-        <v>615.7241045276966</v>
+        <v>648.1284941622514</v>
       </c>
       <c r="C240" t="n">
-        <v>624.3072966603136</v>
+        <v>657.3411939542544</v>
       </c>
       <c r="D240" t="n">
-        <v>609.2591747857786</v>
+        <v>638.056426220049</v>
       </c>
       <c r="E240" t="n">
-        <v>612.9962158203125</v>
+        <v>653.1744995117188</v>
       </c>
       <c r="F240" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B241" t="n">
-        <v>648.1284941622514</v>
+        <v>653.1945472302951</v>
       </c>
       <c r="C241" t="n">
-        <v>657.3411939542544</v>
+        <v>662.9768054946985</v>
       </c>
       <c r="D241" t="n">
-        <v>638.056426220049</v>
+        <v>641.6336632885306</v>
       </c>
       <c r="E241" t="n">
-        <v>653.1744995117188</v>
+        <v>643.8718872070312</v>
       </c>
       <c r="F241" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B242" t="n">
-        <v>653.1945472302951</v>
+        <v>652.9947023490145</v>
       </c>
       <c r="C242" t="n">
-        <v>662.9768054946985</v>
+        <v>663.716221985592</v>
       </c>
       <c r="D242" t="n">
-        <v>641.6336632885306</v>
+        <v>645.6904688887529</v>
       </c>
       <c r="E242" t="n">
-        <v>643.8718872070312</v>
+        <v>647.51904296875</v>
       </c>
       <c r="F242" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B243" t="n">
-        <v>652.9947023490145</v>
+        <v>657.311302577125</v>
       </c>
       <c r="C243" t="n">
-        <v>663.716221985592</v>
+        <v>668.072768706455</v>
       </c>
       <c r="D243" t="n">
-        <v>645.6904688887529</v>
+        <v>648.708045415434</v>
       </c>
       <c r="E243" t="n">
-        <v>647.51904296875</v>
+        <v>665.0751342773438</v>
       </c>
       <c r="F243" t="n">
-        <v>16925000</v>
+        <v>19332300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B244" t="n">
-        <v>657.311302577125</v>
+        <v>658.7801108800835</v>
       </c>
       <c r="C244" t="n">
-        <v>668.072768706455</v>
+        <v>678.3346866933342</v>
       </c>
       <c r="D244" t="n">
-        <v>648.708045415434</v>
+        <v>655.6825797136325</v>
       </c>
       <c r="E244" t="n">
-        <v>665.0751342773438</v>
+        <v>669.7114868164062</v>
       </c>
       <c r="F244" t="n">
-        <v>19332300</v>
+        <v>19502800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B245" t="n">
-        <v>658.7801108800835</v>
+        <v>679.3738238485387</v>
       </c>
       <c r="C245" t="n">
-        <v>678.3346866933342</v>
+        <v>684.7695900234191</v>
       </c>
       <c r="D245" t="n">
-        <v>655.6825797136325</v>
+        <v>671.3801323225093</v>
       </c>
       <c r="E245" t="n">
-        <v>669.7114868164062</v>
+        <v>672.779052734375</v>
       </c>
       <c r="F245" t="n">
-        <v>19502800</v>
+        <v>17217800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B246" t="n">
-        <v>679.3738238485387</v>
+        <v>681.9018750257407</v>
       </c>
       <c r="C246" t="n">
-        <v>684.7695900234191</v>
+        <v>682.6612854975235</v>
       </c>
       <c r="D246" t="n">
-        <v>671.3801323225093</v>
+        <v>666.5239959332205</v>
       </c>
       <c r="E246" t="n">
-        <v>672.779052734375</v>
+        <v>681.77197265625</v>
       </c>
       <c r="F246" t="n">
-        <v>17217800</v>
+        <v>15928000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B247" t="n">
-        <v>681.9018750257407</v>
+        <v>688.0769980771287</v>
       </c>
       <c r="C247" t="n">
-        <v>682.6612854975235</v>
+        <v>689.6058209010791</v>
       </c>
       <c r="D247" t="n">
-        <v>666.5239959332205</v>
+        <v>660.278927643704</v>
       </c>
       <c r="E247" t="n">
-        <v>681.77197265625</v>
+        <v>665.2250366210938</v>
       </c>
       <c r="F247" t="n">
-        <v>15928000</v>
+        <v>27596400</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B248" t="n">
-        <v>688.0769980771287</v>
+        <v>680.2999877929688</v>
       </c>
       <c r="C248" t="n">
-        <v>689.6058209010791</v>
+        <v>753</v>
       </c>
       <c r="D248" t="n">
-        <v>660.278927643704</v>
+        <v>679.5999755859375</v>
       </c>
       <c r="E248" t="n">
-        <v>665.2250366210938</v>
+        <v>741.25</v>
       </c>
       <c r="F248" t="n">
-        <v>27596400</v>
+        <v>48720500</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,25 +6891,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B249" t="n">
-        <v>680.2999877929688</v>
+        <v>731.4000244140625</v>
       </c>
       <c r="C249" t="n">
-        <v>753</v>
+        <v>757.27001953125</v>
       </c>
       <c r="D249" t="n">
-        <v>679.5999755859375</v>
+        <v>730</v>
       </c>
       <c r="E249" t="n">
-        <v>741.25</v>
+        <v>736.5999755859375</v>
       </c>
       <c r="F249" t="n">
-        <v>48720500</v>
+        <v>28122100</v>
       </c>
       <c r="G249" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B250" t="n">
-        <v>731.4000244140625</v>
+        <v>747.5999755859375</v>
       </c>
       <c r="C250" t="n">
-        <v>757.27001953125</v>
+        <v>763.9000244140625</v>
       </c>
       <c r="D250" t="n">
-        <v>730</v>
+        <v>739.510009765625</v>
       </c>
       <c r="E250" t="n">
-        <v>736.5999755859375</v>
+        <v>744.0999755859375</v>
       </c>
       <c r="F250" t="n">
-        <v>28122100</v>
+        <v>30829200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B251" t="n">
-        <v>747.5999755859375</v>
+        <v>744.3599853515625</v>
       </c>
       <c r="C251" t="n">
-        <v>763.9000244140625</v>
+        <v>779.8200073242188</v>
       </c>
       <c r="D251" t="n">
-        <v>739.510009765625</v>
+        <v>743.010009765625</v>
       </c>
       <c r="E251" t="n">
-        <v>744.0999755859375</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="F251" t="n">
-        <v>30829200</v>
+        <v>34808500</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B252" t="n">
-        <v>744.3599853515625</v>
+        <v>768.8499755859375</v>
       </c>
       <c r="C252" t="n">
-        <v>779.8200073242188</v>
+        <v>769.5700073242188</v>
       </c>
       <c r="D252" t="n">
-        <v>743.010009765625</v>
+        <v>746.5399780273438</v>
       </c>
       <c r="E252" t="n">
-        <v>777.5900268554688</v>
+        <v>751.6599731445312</v>
       </c>
       <c r="F252" t="n">
-        <v>34744400</v>
+        <v>25753100</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>751.66</v>
+      </c>
+      <c r="D2" t="n">
         <v>777.59</v>
       </c>
-      <c r="D2" t="n">
-        <v>744.1</v>
-      </c>
       <c r="E2" t="n">
-        <v>744.35</v>
+        <v>768.845</v>
       </c>
       <c r="F2" t="n">
-        <v>779.8192</v>
+        <v>769.5700000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>743.006</v>
+        <v>746.5405</v>
       </c>
       <c r="H2" t="n">
-        <v>34646511</v>
+        <v>25649562</v>
       </c>
       <c r="I2" t="n">
-        <v>19629526</v>
+        <v>19642848</v>
       </c>
       <c r="J2" t="n">
-        <v>1980915384320</v>
+        <v>1914858373120</v>
       </c>
       <c r="K2" t="n">
-        <v>28.011168</v>
+        <v>28.343136</v>
       </c>
       <c r="L2" t="n">
-        <v>22.262783</v>
+        <v>21.496538</v>
       </c>
       <c r="M2" t="n">
-        <v>27.76</v>
+        <v>26.52</v>
       </c>
       <c r="N2" t="n">
         <v>779.8200000000001</v>
@@ -10818,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.5847645</v>
+        <v>7.3318377</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>2002973360128</v>
+        <v>1936916480000</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:29:04</t>
+          <t>2026-09-26 14:49:37</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>747.4645278033088</v>
+        <v>746.1888636454856</v>
       </c>
       <c r="C2" t="n">
-        <v>749.387995888731</v>
+        <v>748.2419580482833</v>
       </c>
       <c r="D2" t="n">
-        <v>734.8572684361654</v>
+        <v>736.65126931649</v>
       </c>
       <c r="E2" t="n">
-        <v>741.2356567382812</v>
+        <v>740.8869018554688</v>
       </c>
       <c r="F2" t="n">
-        <v>9696300</v>
+        <v>9246800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>746.188925117424</v>
+        <v>739.7407284541446</v>
       </c>
       <c r="C3" t="n">
-        <v>748.242019689358</v>
+        <v>740.4582652037509</v>
       </c>
       <c r="D3" t="n">
-        <v>736.6513300027099</v>
+        <v>723.8446373138524</v>
       </c>
       <c r="E3" t="n">
-        <v>740.886962890625</v>
+        <v>731.8973388671875</v>
       </c>
       <c r="F3" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>739.7407284541446</v>
+        <v>719.0509733754704</v>
       </c>
       <c r="C4" t="n">
-        <v>740.4582652037509</v>
+        <v>719.4097417865995</v>
       </c>
       <c r="D4" t="n">
-        <v>723.8446373138524</v>
+        <v>707.7991614309803</v>
       </c>
       <c r="E4" t="n">
-        <v>731.8973388671875</v>
+        <v>714.9150390625</v>
       </c>
       <c r="F4" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>719.050911987213</v>
+        <v>720.1372426569798</v>
       </c>
       <c r="C5" t="n">
-        <v>719.4096803677126</v>
+        <v>725.309699629413</v>
       </c>
       <c r="D5" t="n">
-        <v>707.7991010033351</v>
+        <v>715.7122502133443</v>
       </c>
       <c r="E5" t="n">
-        <v>714.9149780273438</v>
+        <v>724.5921020507812</v>
       </c>
       <c r="F5" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>720.1373033168862</v>
+        <v>727.1633750572937</v>
       </c>
       <c r="C6" t="n">
-        <v>725.3097607250153</v>
+        <v>728.5287386889415</v>
       </c>
       <c r="D6" t="n">
-        <v>715.7123105005168</v>
+        <v>707.7791166979599</v>
       </c>
       <c r="E6" t="n">
-        <v>724.5921630859375</v>
+        <v>708.1578369140625</v>
       </c>
       <c r="F6" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>727.1634377305112</v>
+        <v>702.8060248479621</v>
       </c>
       <c r="C7" t="n">
-        <v>728.528801479838</v>
+        <v>714.4565078636942</v>
       </c>
       <c r="D7" t="n">
-        <v>707.7791777004747</v>
+        <v>688.1756596108709</v>
       </c>
       <c r="E7" t="n">
-        <v>708.1578979492188</v>
+        <v>713.2406005859375</v>
       </c>
       <c r="F7" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>702.8060849901855</v>
+        <v>715.2936403041813</v>
       </c>
       <c r="C8" t="n">
-        <v>714.456569002901</v>
+        <v>716.0710326272052</v>
       </c>
       <c r="D8" t="n">
-        <v>688.1757185011091</v>
+        <v>703.3641353885179</v>
       </c>
       <c r="E8" t="n">
-        <v>713.2406616210938</v>
+        <v>710.6693725585938</v>
       </c>
       <c r="F8" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>715.2937017364883</v>
+        <v>711.0380954481734</v>
       </c>
       <c r="C9" t="n">
-        <v>716.0710941262779</v>
+        <v>717.2171476536749</v>
       </c>
       <c r="D9" t="n">
-        <v>703.3641957962709</v>
+        <v>705.4171476518181</v>
       </c>
       <c r="E9" t="n">
-        <v>710.66943359375</v>
+        <v>715.4132690429688</v>
       </c>
       <c r="F9" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>711.0380347862832</v>
+        <v>715.8518398810967</v>
       </c>
       <c r="C10" t="n">
-        <v>717.2170864646216</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="D10" t="n">
-        <v>705.4170874694764</v>
+        <v>710.0315555923428</v>
       </c>
       <c r="E10" t="n">
-        <v>715.4132080078125</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="F10" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>715.8517801132227</v>
+        <v>728.4490335307075</v>
       </c>
       <c r="C11" t="n">
-        <v>731.0302734375</v>
+        <v>732.784364410351</v>
       </c>
       <c r="D11" t="n">
-        <v>710.0314963104157</v>
+        <v>702.1283419878271</v>
       </c>
       <c r="E11" t="n">
-        <v>731.0302734375</v>
+        <v>702.9156494140625</v>
       </c>
       <c r="F11" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>728.4490335307075</v>
+        <v>710.5996089558437</v>
       </c>
       <c r="C12" t="n">
-        <v>732.784364410351</v>
+        <v>717.5061741064447</v>
       </c>
       <c r="D12" t="n">
-        <v>702.1283419878271</v>
+        <v>705.2477676379041</v>
       </c>
       <c r="E12" t="n">
-        <v>702.9156494140625</v>
+        <v>713.280517578125</v>
       </c>
       <c r="F12" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>710.5996089558437</v>
+        <v>705.3873404797914</v>
       </c>
       <c r="C13" t="n">
-        <v>717.5061741064447</v>
+        <v>713.1310322093289</v>
       </c>
       <c r="D13" t="n">
-        <v>705.2477676379041</v>
+        <v>696.9658939978091</v>
       </c>
       <c r="E13" t="n">
-        <v>713.280517578125</v>
+        <v>706.25439453125</v>
       </c>
       <c r="F13" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>705.3873404797914</v>
+        <v>714.6358727912688</v>
       </c>
       <c r="C14" t="n">
-        <v>713.1310322093289</v>
+        <v>721.4527759491865</v>
       </c>
       <c r="D14" t="n">
-        <v>696.9658939978091</v>
+        <v>707.1114088212217</v>
       </c>
       <c r="E14" t="n">
-        <v>706.25439453125</v>
+        <v>715.1242065429688</v>
       </c>
       <c r="F14" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>714.6358727912688</v>
+        <v>715.1241740828767</v>
       </c>
       <c r="C15" t="n">
-        <v>721.4527759491865</v>
+        <v>723.0373338413923</v>
       </c>
       <c r="D15" t="n">
-        <v>707.1114088212217</v>
+        <v>701.5004051404221</v>
       </c>
       <c r="E15" t="n">
-        <v>715.1242065429688</v>
+        <v>709.6627197265625</v>
       </c>
       <c r="F15" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>715.1242355877501</v>
+        <v>704.6896976037913</v>
       </c>
       <c r="C16" t="n">
-        <v>723.0373960268438</v>
+        <v>716.1109175681677</v>
       </c>
       <c r="D16" t="n">
-        <v>701.5004654735715</v>
+        <v>703.732921033597</v>
       </c>
       <c r="E16" t="n">
-        <v>709.6627807617188</v>
+        <v>714.4963989257812</v>
       </c>
       <c r="F16" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>704.6896374063629</v>
+        <v>718.7519023248905</v>
       </c>
       <c r="C17" t="n">
-        <v>716.1108563950927</v>
+        <v>731.289390620618</v>
       </c>
       <c r="D17" t="n">
-        <v>703.7328609179003</v>
+        <v>717.7453070615727</v>
       </c>
       <c r="E17" t="n">
-        <v>714.496337890625</v>
+        <v>729.6947631835938</v>
       </c>
       <c r="F17" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>718.7519624447335</v>
+        <v>733.5318410857864</v>
       </c>
       <c r="C18" t="n">
-        <v>731.2894517891565</v>
+        <v>736.0034377690635</v>
       </c>
       <c r="D18" t="n">
-        <v>717.7453670972193</v>
+        <v>726.2863984755653</v>
       </c>
       <c r="E18" t="n">
-        <v>729.69482421875</v>
+        <v>730.7911376953125</v>
       </c>
       <c r="F18" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>733.5318410857864</v>
+        <v>731.3492269695964</v>
       </c>
       <c r="C19" t="n">
-        <v>736.0034377690635</v>
+        <v>738.0962989037338</v>
       </c>
       <c r="D19" t="n">
-        <v>726.2863984755653</v>
+        <v>721.5823690736463</v>
       </c>
       <c r="E19" t="n">
-        <v>730.7911376953125</v>
+        <v>730.9306030273438</v>
       </c>
       <c r="F19" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>731.3492880397093</v>
+        <v>732.2163225390138</v>
       </c>
       <c r="C20" t="n">
-        <v>738.0963605372498</v>
+        <v>739.9002195728755</v>
       </c>
       <c r="D20" t="n">
-        <v>721.5824293281937</v>
+        <v>730.6216949207216</v>
       </c>
       <c r="E20" t="n">
-        <v>730.9306640625</v>
+        <v>731.5186767578125</v>
       </c>
       <c r="F20" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>732.2163225390138</v>
+        <v>734.2991309259364</v>
       </c>
       <c r="C21" t="n">
-        <v>739.9002195728755</v>
+        <v>738.704232141329</v>
       </c>
       <c r="D21" t="n">
-        <v>730.6216949207216</v>
+        <v>728.6782441600997</v>
       </c>
       <c r="E21" t="n">
-        <v>731.5186767578125</v>
+        <v>735.8638305664062</v>
       </c>
       <c r="F21" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>734.2991918313108</v>
+        <v>747.195457385242</v>
       </c>
       <c r="C22" t="n">
-        <v>738.7042934120783</v>
+        <v>753.1951257515892</v>
       </c>
       <c r="D22" t="n">
-        <v>728.6783045992579</v>
+        <v>745.4813011827554</v>
       </c>
       <c r="E22" t="n">
-        <v>735.8638916015625</v>
+        <v>748.2817993164062</v>
       </c>
       <c r="F22" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>747.195457385242</v>
+        <v>750.0856988126538</v>
       </c>
       <c r="C23" t="n">
-        <v>753.1951257515892</v>
+        <v>755.8362124836232</v>
       </c>
       <c r="D23" t="n">
-        <v>745.4813011827554</v>
+        <v>742.9997491476457</v>
       </c>
       <c r="E23" t="n">
-        <v>748.2817993164062</v>
+        <v>748.8997192382812</v>
       </c>
       <c r="F23" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>750.0856988126538</v>
+        <v>752.1985111114485</v>
       </c>
       <c r="C24" t="n">
-        <v>755.8362124836232</v>
+        <v>756.5935760115584</v>
       </c>
       <c r="D24" t="n">
-        <v>742.9997491476457</v>
+        <v>739.9998990805568</v>
       </c>
       <c r="E24" t="n">
-        <v>748.8997192382812</v>
+        <v>749.12890625</v>
       </c>
       <c r="F24" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>752.1985723967003</v>
+        <v>666.8879125335289</v>
       </c>
       <c r="C25" t="n">
-        <v>756.5936376548974</v>
+        <v>678.6579855089774</v>
       </c>
       <c r="D25" t="n">
-        <v>739.9999593719286</v>
+        <v>647.9720344844721</v>
       </c>
       <c r="E25" t="n">
-        <v>749.1289672851562</v>
+        <v>664.2169189453125</v>
       </c>
       <c r="F25" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>666.8879125335289</v>
+        <v>672.2297387877188</v>
       </c>
       <c r="C26" t="n">
-        <v>678.6579855089774</v>
+        <v>672.6084590133829</v>
       </c>
       <c r="D26" t="n">
-        <v>647.9720344844721</v>
+        <v>643.3875718813117</v>
       </c>
       <c r="E26" t="n">
-        <v>664.2169189453125</v>
+        <v>646.1581420898438</v>
       </c>
       <c r="F26" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>672.22980228556</v>
+        <v>653.7823467127146</v>
       </c>
       <c r="C27" t="n">
-        <v>672.6085225469975</v>
+        <v>657.1011064498967</v>
       </c>
       <c r="D27" t="n">
-        <v>643.3876326547638</v>
+        <v>634.0293422915395</v>
       </c>
       <c r="E27" t="n">
-        <v>646.158203125</v>
+        <v>635.55419921875</v>
       </c>
       <c r="F27" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>653.7823467127146</v>
+        <v>625.9168776495994</v>
       </c>
       <c r="C28" t="n">
-        <v>657.1011064498967</v>
+        <v>639.5705767203505</v>
       </c>
       <c r="D28" t="n">
-        <v>634.0293422915395</v>
+        <v>623.8937717318939</v>
       </c>
       <c r="E28" t="n">
-        <v>635.55419921875</v>
+        <v>625.1993408203125</v>
       </c>
       <c r="F28" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>625.9168165443936</v>
+        <v>630.1724007040705</v>
       </c>
       <c r="C29" t="n">
-        <v>639.5705142822006</v>
+        <v>640.0588479681868</v>
       </c>
       <c r="D29" t="n">
-        <v>623.8937108241939</v>
+        <v>624.4218873891514</v>
       </c>
       <c r="E29" t="n">
-        <v>625.1992797851562</v>
+        <v>633.8001098632812</v>
       </c>
       <c r="F29" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>630.1724613898772</v>
+        <v>633.7004019945108</v>
       </c>
       <c r="C30" t="n">
-        <v>640.0589096060615</v>
+        <v>633.8499192315176</v>
       </c>
       <c r="D30" t="n">
-        <v>624.4219475211817</v>
+        <v>615.9107705740217</v>
       </c>
       <c r="E30" t="n">
-        <v>633.8001708984375</v>
+        <v>616.8475952148438</v>
       </c>
       <c r="F30" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>633.7004019945108</v>
+        <v>614.4058914069517</v>
       </c>
       <c r="C31" t="n">
-        <v>633.8499192315176</v>
+        <v>620.0268394880455</v>
       </c>
       <c r="D31" t="n">
-        <v>615.9107705740217</v>
+        <v>599.1676024999227</v>
       </c>
       <c r="E31" t="n">
-        <v>616.8475952148438</v>
+        <v>619.6082763671875</v>
       </c>
       <c r="F31" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>614.4058308842617</v>
+        <v>628.9565496273584</v>
       </c>
       <c r="C32" t="n">
-        <v>620.0267784116583</v>
+        <v>632.8533046281837</v>
       </c>
       <c r="D32" t="n">
-        <v>599.1675434782962</v>
+        <v>616.0203887455347</v>
       </c>
       <c r="E32" t="n">
-        <v>619.6082153320312</v>
+        <v>629.624267578125</v>
       </c>
       <c r="F32" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>628.9565496273584</v>
+        <v>625.8770169082796</v>
       </c>
       <c r="C33" t="n">
-        <v>632.8533046281837</v>
+        <v>627.4317408228605</v>
       </c>
       <c r="D33" t="n">
-        <v>616.0203887455347</v>
+        <v>617.2961380110504</v>
       </c>
       <c r="E33" t="n">
-        <v>629.624267578125</v>
+        <v>624.9601440429688</v>
       </c>
       <c r="F33" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>625.8769557835792</v>
+        <v>626.0065923024907</v>
       </c>
       <c r="C34" t="n">
-        <v>627.431679546322</v>
+        <v>626.8636704474237</v>
       </c>
       <c r="D34" t="n">
-        <v>617.29607772438</v>
+        <v>605.7154345004715</v>
       </c>
       <c r="E34" t="n">
-        <v>624.9600830078125</v>
+        <v>606.9512329101562</v>
       </c>
       <c r="F34" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>626.0064663997556</v>
+        <v>610.9974282481795</v>
       </c>
       <c r="C35" t="n">
-        <v>626.8635443723126</v>
+        <v>615.5619618736964</v>
       </c>
       <c r="D35" t="n">
-        <v>605.7153126787034</v>
+        <v>600.9614641591972</v>
       </c>
       <c r="E35" t="n">
-        <v>606.9511108398438</v>
+        <v>607.8281860351562</v>
       </c>
       <c r="F35" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>610.9974282481795</v>
+        <v>599.7556041676178</v>
       </c>
       <c r="C36" t="n">
-        <v>615.5619618736964</v>
+        <v>611.6054241702889</v>
       </c>
       <c r="D36" t="n">
-        <v>600.9614641591972</v>
+        <v>593.1879159768617</v>
       </c>
       <c r="E36" t="n">
-        <v>607.8281860351562</v>
+        <v>607.3997192382812</v>
       </c>
       <c r="F36" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>599.7556041676178</v>
+        <v>606.9810562524968</v>
       </c>
       <c r="C37" t="n">
-        <v>611.6054241702889</v>
+        <v>609.6221219886945</v>
       </c>
       <c r="D37" t="n">
-        <v>593.1879159768617</v>
+        <v>593.3872138938384</v>
       </c>
       <c r="E37" t="n">
-        <v>607.3997192382812</v>
+        <v>599.974853515625</v>
       </c>
       <c r="F37" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>606.980994504603</v>
+        <v>589.5999948667346</v>
       </c>
       <c r="C38" t="n">
-        <v>609.6220599721263</v>
+        <v>601.619222033871</v>
       </c>
       <c r="D38" t="n">
-        <v>593.3871535288397</v>
+        <v>581.8064849239344</v>
       </c>
       <c r="E38" t="n">
-        <v>599.9747924804688</v>
+        <v>595.66943359375</v>
       </c>
       <c r="F38" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>589.5999948667346</v>
+        <v>591.7128714929664</v>
       </c>
       <c r="C39" t="n">
-        <v>601.619222033871</v>
+        <v>593.3174750396417</v>
       </c>
       <c r="D39" t="n">
-        <v>581.8064849239344</v>
+        <v>579.2850561317264</v>
       </c>
       <c r="E39" t="n">
-        <v>595.66943359375</v>
+        <v>588.3244018554688</v>
       </c>
       <c r="F39" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>591.7128101062766</v>
+        <v>601.4598513214113</v>
       </c>
       <c r="C40" t="n">
-        <v>593.3174134864839</v>
+        <v>604.668936823252</v>
       </c>
       <c r="D40" t="n">
-        <v>579.2849960343485</v>
+        <v>581.3779446301025</v>
       </c>
       <c r="E40" t="n">
-        <v>588.3243408203125</v>
+        <v>587.1583862304688</v>
       </c>
       <c r="F40" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>601.4598513214113</v>
+        <v>586.5104667718139</v>
       </c>
       <c r="C41" t="n">
-        <v>604.668936823252</v>
+        <v>596.097939714081</v>
       </c>
       <c r="D41" t="n">
-        <v>581.3779446301025</v>
+        <v>579.8928999224906</v>
       </c>
       <c r="E41" t="n">
-        <v>587.1583862304688</v>
+        <v>592.2410278320312</v>
       </c>
       <c r="F41" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>586.5105272163902</v>
+        <v>596.6959653725695</v>
       </c>
       <c r="C42" t="n">
-        <v>596.0980011467227</v>
+        <v>614.6152243710839</v>
       </c>
       <c r="D42" t="n">
-        <v>579.8929596850738</v>
+        <v>595.6096842408232</v>
       </c>
       <c r="E42" t="n">
-        <v>592.2410888671875</v>
+        <v>610.9775390625</v>
       </c>
       <c r="F42" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>596.6959057641074</v>
+        <v>621.8904932046078</v>
       </c>
       <c r="C43" t="n">
-        <v>614.6151629725317</v>
+        <v>634.8963639496133</v>
       </c>
       <c r="D43" t="n">
-        <v>595.609624740878</v>
+        <v>616.209750572071</v>
       </c>
       <c r="E43" t="n">
-        <v>610.9774780273438</v>
+        <v>634.0691528320312</v>
       </c>
       <c r="F43" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>621.8904932046078</v>
+        <v>635.5342418532664</v>
       </c>
       <c r="C44" t="n">
-        <v>634.8963639496133</v>
+        <v>636.2019598341516</v>
       </c>
       <c r="D44" t="n">
-        <v>616.209750572071</v>
+        <v>629.4947305871518</v>
       </c>
       <c r="E44" t="n">
-        <v>634.0691528320312</v>
+        <v>631.468017578125</v>
       </c>
       <c r="F44" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>635.5342418532664</v>
+        <v>633.9296546389559</v>
       </c>
       <c r="C45" t="n">
-        <v>636.2019598341516</v>
+        <v>645.8591590880771</v>
       </c>
       <c r="D45" t="n">
-        <v>629.4947305871518</v>
+        <v>633.3515983825566</v>
       </c>
       <c r="E45" t="n">
-        <v>631.468017578125</v>
+        <v>645.759521484375</v>
       </c>
       <c r="F45" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>633.9297145559904</v>
+        <v>637.3879462598147</v>
       </c>
       <c r="C46" t="n">
-        <v>645.8592201326509</v>
+        <v>643.138459853903</v>
       </c>
       <c r="D46" t="n">
-        <v>633.351658244955</v>
+        <v>635.6040193729798</v>
       </c>
       <c r="E46" t="n">
-        <v>645.7595825195312</v>
+        <v>638.7034912109375</v>
       </c>
       <c r="F46" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>637.3878853503733</v>
+        <v>640.1684359456628</v>
       </c>
       <c r="C47" t="n">
-        <v>643.1383983949365</v>
+        <v>645.6797087683515</v>
       </c>
       <c r="D47" t="n">
-        <v>635.6039586340122</v>
+        <v>635.9128522820391</v>
       </c>
       <c r="E47" t="n">
-        <v>638.7034301757812</v>
+        <v>644.9122924804688</v>
       </c>
       <c r="F47" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>640.1684965318557</v>
+        <v>642.2314810232181</v>
       </c>
       <c r="C48" t="n">
-        <v>645.6797698761368</v>
+        <v>646.6564735939825</v>
       </c>
       <c r="D48" t="n">
-        <v>635.9129124654792</v>
+        <v>635.3946865356451</v>
       </c>
       <c r="E48" t="n">
-        <v>644.912353515625</v>
+        <v>637.437744140625</v>
       </c>
       <c r="F48" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>642.2314810232181</v>
+        <v>673.7146932031604</v>
       </c>
       <c r="C49" t="n">
-        <v>646.6564735939825</v>
+        <v>673.8143308084973</v>
       </c>
       <c r="D49" t="n">
-        <v>635.3946865356451</v>
+        <v>657.8186021075292</v>
       </c>
       <c r="E49" t="n">
-        <v>637.437744140625</v>
+        <v>659.2936401367188</v>
       </c>
       <c r="F49" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>673.7146932031604</v>
+        <v>661.7552947151958</v>
       </c>
       <c r="C50" t="n">
-        <v>673.8143308084973</v>
+        <v>672.4091587454953</v>
       </c>
       <c r="D50" t="n">
-        <v>657.8186021075292</v>
+        <v>660.1507520483126</v>
       </c>
       <c r="E50" t="n">
-        <v>659.2936401367188</v>
+        <v>671.1434326171875</v>
       </c>
       <c r="F50" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>661.7553548965755</v>
+        <v>667.0772284693074</v>
       </c>
       <c r="C51" t="n">
-        <v>672.4092198957593</v>
+        <v>674.4223082782987</v>
       </c>
       <c r="D51" t="n">
-        <v>660.1508120837719</v>
+        <v>662.8216443414645</v>
       </c>
       <c r="E51" t="n">
-        <v>671.1434936523438</v>
+        <v>664.5457763671875</v>
       </c>
       <c r="F51" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>667.0772284693074</v>
+        <v>661.5260500954003</v>
       </c>
       <c r="C52" t="n">
-        <v>674.4223082782987</v>
+        <v>662.2336109084633</v>
       </c>
       <c r="D52" t="n">
-        <v>662.8216443414645</v>
+        <v>651.1313175008097</v>
       </c>
       <c r="E52" t="n">
-        <v>664.5457763671875</v>
+        <v>654.7390747070312</v>
       </c>
       <c r="F52" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>661.5260500954003</v>
+        <v>647.7527447265774</v>
       </c>
       <c r="C53" t="n">
-        <v>662.2336109084633</v>
+        <v>652.2973264314004</v>
       </c>
       <c r="D53" t="n">
-        <v>651.1313175008097</v>
+        <v>641.2249002906431</v>
       </c>
       <c r="E53" t="n">
-        <v>654.7390747070312</v>
+        <v>647.93212890625</v>
       </c>
       <c r="F53" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>647.7528057448357</v>
+        <v>641.1152803360264</v>
       </c>
       <c r="C54" t="n">
-        <v>652.297387877758</v>
+        <v>653.0647981949571</v>
       </c>
       <c r="D54" t="n">
-        <v>641.2249606939789</v>
+        <v>638.6337077300913</v>
       </c>
       <c r="E54" t="n">
-        <v>647.9321899414062</v>
+        <v>650.5034790039062</v>
       </c>
       <c r="F54" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>641.1152803360264</v>
+        <v>647.6033016180266</v>
       </c>
       <c r="C55" t="n">
-        <v>653.0647981949571</v>
+        <v>708.5964236692454</v>
       </c>
       <c r="D55" t="n">
-        <v>638.6337077300913</v>
+        <v>636.4511276224844</v>
       </c>
       <c r="E55" t="n">
-        <v>650.5034790039062</v>
+        <v>642.0521240234375</v>
       </c>
       <c r="F55" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>647.6033016180266</v>
+        <v>644.0420011784053</v>
       </c>
       <c r="C56" t="n">
-        <v>708.5964236692454</v>
+        <v>651.3232442601446</v>
       </c>
       <c r="D56" t="n">
-        <v>636.4511276224844</v>
+        <v>637.0599755890928</v>
       </c>
       <c r="E56" t="n">
-        <v>642.0521240234375</v>
+        <v>645.8473510742188</v>
       </c>
       <c r="F56" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>644.0420011784053</v>
+        <v>641.8476715248971</v>
       </c>
       <c r="C57" t="n">
-        <v>651.3232442601446</v>
+        <v>660.8387602004772</v>
       </c>
       <c r="D57" t="n">
-        <v>637.0599755890928</v>
+        <v>641.5484540168895</v>
       </c>
       <c r="E57" t="n">
-        <v>645.8473510742188</v>
+        <v>655.462646484375</v>
       </c>
       <c r="F57" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G57" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>641.8476715248971</v>
+        <v>653.9265104909302</v>
       </c>
       <c r="C58" t="n">
-        <v>660.8387602004772</v>
+        <v>659.5320745885969</v>
       </c>
       <c r="D58" t="n">
-        <v>641.5484540168895</v>
+        <v>647.5329968709444</v>
       </c>
       <c r="E58" t="n">
-        <v>655.462646484375</v>
+        <v>647.8322143554688</v>
       </c>
       <c r="F58" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>653.9265721002572</v>
+        <v>655.3429055936973</v>
       </c>
       <c r="C59" t="n">
-        <v>659.5321367260491</v>
+        <v>668.8381315618529</v>
       </c>
       <c r="D59" t="n">
-        <v>647.5330578779101</v>
+        <v>654.7743619360156</v>
       </c>
       <c r="E59" t="n">
-        <v>647.832275390625</v>
+        <v>662.7438354492188</v>
       </c>
       <c r="F59" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>655.3429055936973</v>
+        <v>664.7087499822148</v>
       </c>
       <c r="C60" t="n">
-        <v>668.8381315618529</v>
+        <v>669.2770065062657</v>
       </c>
       <c r="D60" t="n">
-        <v>654.7743619360156</v>
+        <v>656.4899183910027</v>
       </c>
       <c r="E60" t="n">
-        <v>662.7438354492188</v>
+        <v>657.0784301757812</v>
       </c>
       <c r="F60" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>664.7087499822148</v>
+        <v>659.9510918299604</v>
       </c>
       <c r="C61" t="n">
-        <v>669.2770065062657</v>
+        <v>671.8504516144289</v>
       </c>
       <c r="D61" t="n">
-        <v>656.4899183910027</v>
+        <v>654.9639304343692</v>
       </c>
       <c r="E61" t="n">
-        <v>657.0784301757812</v>
+        <v>659.8014526367188</v>
       </c>
       <c r="F61" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>659.9510918299604</v>
+        <v>658.3550860644432</v>
       </c>
       <c r="C62" t="n">
-        <v>671.8504516144289</v>
+        <v>664.2898196014329</v>
       </c>
       <c r="D62" t="n">
-        <v>654.9639304343692</v>
+        <v>656.5597203493141</v>
       </c>
       <c r="E62" t="n">
-        <v>659.8014526367188</v>
+        <v>663.2325439453125</v>
       </c>
       <c r="F62" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>658.3550860644432</v>
+        <v>660.8288080412273</v>
       </c>
       <c r="C63" t="n">
-        <v>664.2898196014329</v>
+        <v>666.4642636433252</v>
       </c>
       <c r="D63" t="n">
-        <v>656.5597203493141</v>
+        <v>660.499638357634</v>
       </c>
       <c r="E63" t="n">
-        <v>663.2325439453125</v>
+        <v>665.8358764648438</v>
       </c>
       <c r="F63" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>660.8288080412273</v>
+        <v>666.3446246130748</v>
       </c>
       <c r="C64" t="n">
-        <v>666.4642636433252</v>
+        <v>667.2323539771746</v>
       </c>
       <c r="D64" t="n">
-        <v>660.499638357634</v>
+        <v>659.6219406041037</v>
       </c>
       <c r="E64" t="n">
-        <v>665.8358764648438</v>
+        <v>661.5868530273438</v>
       </c>
       <c r="F64" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>666.3446246130748</v>
+        <v>656.3204105957403</v>
       </c>
       <c r="C65" t="n">
-        <v>667.2323539771746</v>
+        <v>658.5546491157273</v>
       </c>
       <c r="D65" t="n">
-        <v>659.6219406041037</v>
+        <v>652.7097106878265</v>
       </c>
       <c r="E65" t="n">
-        <v>661.5868530273438</v>
+        <v>656.9986572265625</v>
       </c>
       <c r="F65" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>656.3204105957403</v>
+        <v>656.9986226731097</v>
       </c>
       <c r="C66" t="n">
-        <v>658.5546491157273</v>
+        <v>670.4938487731155</v>
       </c>
       <c r="D66" t="n">
-        <v>652.7097106878265</v>
+        <v>656.1508296487782</v>
       </c>
       <c r="E66" t="n">
-        <v>656.9986572265625</v>
+        <v>664.239990234375</v>
       </c>
       <c r="F66" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>656.9986226731097</v>
+        <v>663.0430265979899</v>
       </c>
       <c r="C67" t="n">
-        <v>670.4938487731155</v>
+        <v>663.2923846373272</v>
       </c>
       <c r="D67" t="n">
-        <v>656.1508296487782</v>
+        <v>657.7466642776019</v>
       </c>
       <c r="E67" t="n">
-        <v>664.239990234375</v>
+        <v>658.39501953125</v>
       </c>
       <c r="F67" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>663.0430265979899</v>
+        <v>661.0282405096659</v>
       </c>
       <c r="C68" t="n">
-        <v>663.2923846373272</v>
+        <v>662.6840120988863</v>
       </c>
       <c r="D68" t="n">
-        <v>657.7466642776019</v>
+        <v>641.8476382600104</v>
       </c>
       <c r="E68" t="n">
-        <v>658.39501953125</v>
+        <v>648.7398681640625</v>
       </c>
       <c r="F68" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>661.0282405096659</v>
+        <v>649.3383972038786</v>
       </c>
       <c r="C69" t="n">
-        <v>662.6840120988863</v>
+        <v>662.8336242718107</v>
       </c>
       <c r="D69" t="n">
-        <v>641.8476382600104</v>
+        <v>646.086758236235</v>
       </c>
       <c r="E69" t="n">
-        <v>648.7398681640625</v>
+        <v>657.098388671875</v>
       </c>
       <c r="F69" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>649.3383972038786</v>
+        <v>657.8763534012292</v>
       </c>
       <c r="C70" t="n">
-        <v>662.8336242718107</v>
+        <v>663.8110870761799</v>
       </c>
       <c r="D70" t="n">
-        <v>646.086758236235</v>
+        <v>650.2260655901538</v>
       </c>
       <c r="E70" t="n">
-        <v>657.098388671875</v>
+        <v>658.9236450195312</v>
       </c>
       <c r="F70" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>657.8763534012292</v>
+        <v>653.956457912222</v>
       </c>
       <c r="C71" t="n">
-        <v>663.8110870761799</v>
+        <v>657.4574546517152</v>
       </c>
       <c r="D71" t="n">
-        <v>650.2260655901538</v>
+        <v>643.154250211399</v>
       </c>
       <c r="E71" t="n">
-        <v>658.9236450195312</v>
+        <v>647.0242919921875</v>
       </c>
       <c r="F71" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>653.956457912222</v>
+        <v>644.2215315163064</v>
       </c>
       <c r="C72" t="n">
-        <v>657.4574546517152</v>
+        <v>645.4383696113561</v>
       </c>
       <c r="D72" t="n">
-        <v>643.154250211399</v>
+        <v>634.0875860000896</v>
       </c>
       <c r="E72" t="n">
-        <v>647.0242919921875</v>
+        <v>644.4010620117188</v>
       </c>
       <c r="F72" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>644.2215315163064</v>
+        <v>643.7826886268982</v>
       </c>
       <c r="C73" t="n">
-        <v>645.4383696113561</v>
+        <v>653.2682792823022</v>
       </c>
       <c r="D73" t="n">
-        <v>634.0875860000896</v>
+        <v>641.1993122536916</v>
       </c>
       <c r="E73" t="n">
-        <v>644.4010620117188</v>
+        <v>651.3831176757812</v>
       </c>
       <c r="F73" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>643.7826886268982</v>
+        <v>650.8544758921091</v>
       </c>
       <c r="C74" t="n">
-        <v>653.2682792823022</v>
+        <v>652.2907198459545</v>
       </c>
       <c r="D74" t="n">
-        <v>641.1993122536916</v>
+        <v>639.5834431006995</v>
       </c>
       <c r="E74" t="n">
-        <v>651.3831176757812</v>
+        <v>640.321533203125</v>
       </c>
       <c r="F74" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>650.8544758921091</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="C75" t="n">
-        <v>652.2907198459545</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="D75" t="n">
-        <v>639.5834431006995</v>
+        <v>622.4974409136</v>
       </c>
       <c r="E75" t="n">
-        <v>640.321533203125</v>
+        <v>629.4695434570312</v>
       </c>
       <c r="F75" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>640.6208286715078</v>
+        <v>624.8913007155408</v>
       </c>
       <c r="C76" t="n">
-        <v>640.6208286715078</v>
+        <v>626.836305766559</v>
       </c>
       <c r="D76" t="n">
-        <v>622.4974409136</v>
+        <v>613.2412994138377</v>
       </c>
       <c r="E76" t="n">
-        <v>629.4695434570312</v>
+        <v>613.9395141601562</v>
       </c>
       <c r="F76" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>624.8912385916063</v>
+        <v>616.8918824768537</v>
       </c>
       <c r="C77" t="n">
-        <v>626.8362434492608</v>
+        <v>622.567274451088</v>
       </c>
       <c r="D77" t="n">
-        <v>613.241238448095</v>
+        <v>612.6527953870184</v>
       </c>
       <c r="E77" t="n">
-        <v>613.939453125</v>
+        <v>619.2059326171875</v>
       </c>
       <c r="F77" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>616.8918216697934</v>
+        <v>622.5772500418334</v>
       </c>
       <c r="C78" t="n">
-        <v>622.5672130846042</v>
+        <v>627.4646923832119</v>
       </c>
       <c r="D78" t="n">
-        <v>612.6527349978052</v>
+        <v>618.4878021974878</v>
       </c>
       <c r="E78" t="n">
-        <v>619.2058715820312</v>
+        <v>618.6573486328125</v>
       </c>
       <c r="F78" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>622.5772500418334</v>
+        <v>606.3191417499893</v>
       </c>
       <c r="C79" t="n">
-        <v>627.4646923832119</v>
+        <v>609.8301228712422</v>
       </c>
       <c r="D79" t="n">
-        <v>618.4878021974878</v>
+        <v>598.4593704807342</v>
       </c>
       <c r="E79" t="n">
-        <v>618.6573486328125</v>
+        <v>602.5687866210938</v>
       </c>
       <c r="F79" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>606.3190803349536</v>
+        <v>605.1820479992876</v>
       </c>
       <c r="C80" t="n">
-        <v>609.8300611005736</v>
+        <v>616.6824713366042</v>
       </c>
       <c r="D80" t="n">
-        <v>598.4593098618273</v>
+        <v>598.5391758430108</v>
       </c>
       <c r="E80" t="n">
-        <v>602.5687255859375</v>
+        <v>611.3861083984375</v>
       </c>
       <c r="F80" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>605.1819875834877</v>
+        <v>627.7339506004921</v>
       </c>
       <c r="C81" t="n">
-        <v>616.682409772708</v>
+        <v>658.8738165275513</v>
       </c>
       <c r="D81" t="n">
-        <v>598.5391160903739</v>
+        <v>624.9411525277235</v>
       </c>
       <c r="E81" t="n">
-        <v>611.3860473632812</v>
+        <v>645.967041015625</v>
       </c>
       <c r="F81" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>627.7339506004921</v>
+        <v>643.1144139511335</v>
       </c>
       <c r="C82" t="n">
-        <v>658.8738165275513</v>
+        <v>664.7786132883346</v>
       </c>
       <c r="D82" t="n">
-        <v>624.9411525277235</v>
+        <v>642.7952283244125</v>
       </c>
       <c r="E82" t="n">
-        <v>645.967041015625</v>
+        <v>657.0684814453125</v>
       </c>
       <c r="F82" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>643.114354212172</v>
+        <v>663.4220687284304</v>
       </c>
       <c r="C83" t="n">
-        <v>664.7785515369834</v>
+        <v>673.5460296758964</v>
       </c>
       <c r="D83" t="n">
-        <v>642.7951686151001</v>
+        <v>659.5919023824141</v>
       </c>
       <c r="E83" t="n">
-        <v>657.0684204101562</v>
+        <v>670.6334838867188</v>
       </c>
       <c r="F83" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>663.4220687284304</v>
+        <v>672.8578395915863</v>
       </c>
       <c r="C84" t="n">
-        <v>673.5460296758964</v>
+        <v>675.0820939991542</v>
       </c>
       <c r="D84" t="n">
-        <v>659.5919023824141</v>
+        <v>662.9532839044604</v>
       </c>
       <c r="E84" t="n">
-        <v>670.6334838867188</v>
+        <v>671.241943359375</v>
       </c>
       <c r="F84" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>672.8578395915863</v>
+        <v>672.7679591112906</v>
       </c>
       <c r="C85" t="n">
-        <v>675.0820939991542</v>
+        <v>675.9397859199995</v>
       </c>
       <c r="D85" t="n">
-        <v>662.9532839044604</v>
+        <v>664.3895050245095</v>
       </c>
       <c r="E85" t="n">
-        <v>671.241943359375</v>
+        <v>667.0127563476562</v>
       </c>
       <c r="F85" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>672.7679591112906</v>
+        <v>735.536439340887</v>
       </c>
       <c r="C86" t="n">
-        <v>675.9397859199995</v>
+        <v>742.0895763731422</v>
       </c>
       <c r="D86" t="n">
-        <v>664.3895050245095</v>
+        <v>710.7203206800697</v>
       </c>
       <c r="E86" t="n">
-        <v>667.0127563476562</v>
+        <v>736.4141845703125</v>
       </c>
       <c r="F86" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>735.536439340887</v>
+        <v>725.6319102189462</v>
       </c>
       <c r="C87" t="n">
-        <v>742.0895763731422</v>
+        <v>730.2899014488934</v>
       </c>
       <c r="D87" t="n">
-        <v>710.7203206800697</v>
+        <v>711.7576553956329</v>
       </c>
       <c r="E87" t="n">
-        <v>736.4141845703125</v>
+        <v>714.66015625</v>
       </c>
       <c r="F87" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>725.6319721911391</v>
+        <v>712.7649799285471</v>
       </c>
       <c r="C88" t="n">
-        <v>730.2899638188994</v>
+        <v>719.4477874144414</v>
       </c>
       <c r="D88" t="n">
-        <v>711.7577161829028</v>
+        <v>701.7134756957726</v>
       </c>
       <c r="E88" t="n">
-        <v>714.6602172851562</v>
+        <v>704.5960083007812</v>
       </c>
       <c r="F88" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>712.7650416713351</v>
+        <v>705.5535728195721</v>
       </c>
       <c r="C89" t="n">
-        <v>719.4478497361232</v>
+        <v>715.1588492636382</v>
       </c>
       <c r="D89" t="n">
-        <v>701.7135364812315</v>
+        <v>684.6473731061755</v>
       </c>
       <c r="E89" t="n">
-        <v>704.5960693359375</v>
+        <v>689.923828125</v>
       </c>
       <c r="F89" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>705.5536352374374</v>
+        <v>685.9640881387202</v>
       </c>
       <c r="C90" t="n">
-        <v>715.1589125312489</v>
+        <v>687.0613001828912</v>
       </c>
       <c r="D90" t="n">
-        <v>684.6474336745422</v>
+        <v>665.7461770525908</v>
       </c>
       <c r="E90" t="n">
-        <v>689.9238891601562</v>
+        <v>667.272216796875</v>
       </c>
       <c r="F90" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>685.964025393825</v>
+        <v>661.8760941724082</v>
       </c>
       <c r="C91" t="n">
-        <v>687.0612373376343</v>
+        <v>679.7500626324993</v>
       </c>
       <c r="D91" t="n">
-        <v>665.7461161570209</v>
+        <v>651.8219602792932</v>
       </c>
       <c r="E91" t="n">
-        <v>667.2721557617188</v>
+        <v>668.4890747070312</v>
       </c>
       <c r="F91" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>661.8760941724082</v>
+        <v>663.7811558190369</v>
       </c>
       <c r="C92" t="n">
-        <v>679.7500626324993</v>
+        <v>670.2644652243433</v>
       </c>
       <c r="D92" t="n">
-        <v>651.8219602792932</v>
+        <v>644.8399277739295</v>
       </c>
       <c r="E92" t="n">
-        <v>668.4890747070312</v>
+        <v>659.7615356445312</v>
       </c>
       <c r="F92" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>663.7811558190369</v>
+        <v>661.4770916291903</v>
       </c>
       <c r="C93" t="n">
-        <v>670.2644652243433</v>
+        <v>681.5554070660584</v>
       </c>
       <c r="D93" t="n">
-        <v>644.8399277739295</v>
+        <v>657.0884263930592</v>
       </c>
       <c r="E93" t="n">
-        <v>659.7615356445312</v>
+        <v>675.4810180664062</v>
       </c>
       <c r="F93" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>661.4770916291903</v>
+        <v>675.8600189134125</v>
       </c>
       <c r="C94" t="n">
-        <v>681.5554070660584</v>
+        <v>678.9022357565889</v>
       </c>
       <c r="D94" t="n">
-        <v>657.0884263930592</v>
+        <v>668.0700760446862</v>
       </c>
       <c r="E94" t="n">
-        <v>675.4810180664062</v>
+        <v>668.9976806640625</v>
       </c>
       <c r="F94" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>675.8600189134125</v>
+        <v>672.2693241407737</v>
       </c>
       <c r="C95" t="n">
-        <v>678.9022357565889</v>
+        <v>677.5258114827353</v>
       </c>
       <c r="D95" t="n">
-        <v>668.0700760446862</v>
+        <v>655.4126950742984</v>
       </c>
       <c r="E95" t="n">
-        <v>668.9976806640625</v>
+        <v>666.9729614257812</v>
       </c>
       <c r="F95" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>672.2693241407737</v>
+        <v>668.2496249159107</v>
       </c>
       <c r="C96" t="n">
-        <v>677.5258114827353</v>
+        <v>674.2641703314905</v>
       </c>
       <c r="D96" t="n">
-        <v>655.4126950742984</v>
+        <v>643.6230822268304</v>
       </c>
       <c r="E96" t="n">
-        <v>666.9729614257812</v>
+        <v>648.1414184570312</v>
       </c>
       <c r="F96" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>668.2496878446467</v>
+        <v>643.4434668857905</v>
       </c>
       <c r="C97" t="n">
-        <v>674.2642338266133</v>
+        <v>649.7572295518577</v>
       </c>
       <c r="D97" t="n">
-        <v>643.6231428364971</v>
+        <v>632.9405378190771</v>
       </c>
       <c r="E97" t="n">
-        <v>648.1414794921875</v>
+        <v>638.127197265625</v>
       </c>
       <c r="F97" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>643.4434668857905</v>
+        <v>637.8579201875249</v>
       </c>
       <c r="C98" t="n">
-        <v>649.7572295518577</v>
+        <v>640.9499357932766</v>
       </c>
       <c r="D98" t="n">
-        <v>632.9405378190771</v>
+        <v>627.1853829985365</v>
       </c>
       <c r="E98" t="n">
-        <v>638.127197265625</v>
+        <v>637.6484375</v>
       </c>
       <c r="F98" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>637.8578591323172</v>
+        <v>632.1725042393389</v>
       </c>
       <c r="C99" t="n">
-        <v>640.9498744421038</v>
+        <v>643.3437568439427</v>
       </c>
       <c r="D99" t="n">
-        <v>627.1853229648948</v>
+        <v>626.5370489428796</v>
       </c>
       <c r="E99" t="n">
-        <v>637.6483764648438</v>
+        <v>641.5682983398438</v>
       </c>
       <c r="F99" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>632.1725643806327</v>
+        <v>636.9302530675583</v>
       </c>
       <c r="C100" t="n">
-        <v>643.3438180480059</v>
+        <v>645.5281132997313</v>
       </c>
       <c r="D100" t="n">
-        <v>626.5371085480483</v>
+        <v>635.0849670695593</v>
       </c>
       <c r="E100" t="n">
-        <v>641.568359375</v>
+        <v>643.1243286132812</v>
       </c>
       <c r="F100" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>636.9303135148713</v>
+        <v>638.0474756888525</v>
       </c>
       <c r="C101" t="n">
-        <v>645.5281745630167</v>
+        <v>661.6466973151385</v>
       </c>
       <c r="D101" t="n">
-        <v>635.085027341747</v>
+        <v>637.1398390748724</v>
       </c>
       <c r="E101" t="n">
-        <v>643.1243896484375</v>
+        <v>653.9764404296875</v>
       </c>
       <c r="F101" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>638.0474161403351</v>
+        <v>650.8644258547187</v>
       </c>
       <c r="C102" t="n">
-        <v>661.6466355641227</v>
+        <v>656.0112104148094</v>
       </c>
       <c r="D102" t="n">
-        <v>637.1397796110642</v>
+        <v>634.3669181695027</v>
       </c>
       <c r="E102" t="n">
-        <v>653.9763793945312</v>
+        <v>635.6137084960938</v>
       </c>
       <c r="F102" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>650.8644258547187</v>
+        <v>631.4544476780686</v>
       </c>
       <c r="C103" t="n">
-        <v>656.0112104148094</v>
+        <v>639.4637972653206</v>
       </c>
       <c r="D103" t="n">
-        <v>634.3669181695027</v>
+        <v>627.364938784811</v>
       </c>
       <c r="E103" t="n">
-        <v>635.6137084960938</v>
+        <v>637.658447265625</v>
       </c>
       <c r="F103" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>631.4543872367445</v>
+        <v>640.8800977544264</v>
       </c>
       <c r="C104" t="n">
-        <v>639.4637360573605</v>
+        <v>652.2009281146602</v>
       </c>
       <c r="D104" t="n">
-        <v>627.364878734925</v>
+        <v>640.4910846116635</v>
       </c>
       <c r="E104" t="n">
-        <v>637.6583862304688</v>
+        <v>652.0114135742188</v>
       </c>
       <c r="F104" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>640.8801577475739</v>
+        <v>648.8795635426123</v>
       </c>
       <c r="C105" t="n">
-        <v>652.2009891675571</v>
+        <v>659.3027431401059</v>
       </c>
       <c r="D105" t="n">
-        <v>640.4911445683953</v>
+        <v>645.8374072363367</v>
       </c>
       <c r="E105" t="n">
-        <v>652.011474609375</v>
+        <v>655.322998046875</v>
       </c>
       <c r="F105" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>648.8795635426123</v>
+        <v>641.7977293743734</v>
       </c>
       <c r="C106" t="n">
-        <v>659.3027431401059</v>
+        <v>647.7723382149427</v>
       </c>
       <c r="D106" t="n">
-        <v>645.8374072363367</v>
+        <v>636.4813989665846</v>
       </c>
       <c r="E106" t="n">
-        <v>655.322998046875</v>
+        <v>646.5155639648438</v>
       </c>
       <c r="F106" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>641.7977899641362</v>
+        <v>635.5238627543893</v>
       </c>
       <c r="C107" t="n">
-        <v>647.7723993687464</v>
+        <v>658.2453970983619</v>
       </c>
       <c r="D107" t="n">
-        <v>636.4814590544522</v>
+        <v>632.870719934867</v>
       </c>
       <c r="E107" t="n">
-        <v>646.515625</v>
+        <v>651.8817749023438</v>
       </c>
       <c r="F107" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>635.5238627543893</v>
+        <v>646.6252847330551</v>
       </c>
       <c r="C108" t="n">
-        <v>658.2453970983619</v>
+        <v>657.3476806461185</v>
       </c>
       <c r="D108" t="n">
-        <v>632.870719934867</v>
+        <v>637.199599354082</v>
       </c>
       <c r="E108" t="n">
-        <v>651.8817749023438</v>
+        <v>653.3978881835938</v>
       </c>
       <c r="F108" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>646.6253451355694</v>
+        <v>656.2705097002453</v>
       </c>
       <c r="C109" t="n">
-        <v>657.3477420502325</v>
+        <v>671.0424780902056</v>
       </c>
       <c r="D109" t="n">
-        <v>637.1996588761248</v>
+        <v>655.9812154011644</v>
       </c>
       <c r="E109" t="n">
-        <v>653.39794921875</v>
+        <v>666.015380859375</v>
       </c>
       <c r="F109" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>656.2705097002453</v>
+        <v>660.2303336051802</v>
       </c>
       <c r="C110" t="n">
-        <v>671.0424780902056</v>
+        <v>668.9778340733714</v>
       </c>
       <c r="D110" t="n">
-        <v>655.9812154011644</v>
+        <v>648.6401755256248</v>
       </c>
       <c r="E110" t="n">
-        <v>666.015380859375</v>
+        <v>658.8738403320312</v>
       </c>
       <c r="F110" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>660.2303336051802</v>
+        <v>646.2363343546218</v>
       </c>
       <c r="C111" t="n">
-        <v>668.9778340733714</v>
+        <v>647.8022493056128</v>
       </c>
       <c r="D111" t="n">
-        <v>648.6401755256248</v>
+        <v>634.4765699796501</v>
       </c>
       <c r="E111" t="n">
-        <v>658.8738403320312</v>
+        <v>643.2041015625</v>
       </c>
       <c r="F111" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>646.2363956775138</v>
+        <v>633.1500554179556</v>
       </c>
       <c r="C112" t="n">
-        <v>647.8023107770981</v>
+        <v>646.0867221220876</v>
       </c>
       <c r="D112" t="n">
-        <v>634.4766301866302</v>
+        <v>625.1705976379839</v>
       </c>
       <c r="E112" t="n">
-        <v>643.2041625976562</v>
+        <v>645.7276611328125</v>
       </c>
       <c r="F112" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>633.1500554179556</v>
+        <v>651.8818637417822</v>
       </c>
       <c r="C113" t="n">
-        <v>646.0867221220876</v>
+        <v>658.6045478289335</v>
       </c>
       <c r="D113" t="n">
-        <v>625.1705976379839</v>
+        <v>647.3335748038755</v>
       </c>
       <c r="E113" t="n">
-        <v>645.7276611328125</v>
+        <v>652.3905639648438</v>
       </c>
       <c r="F113" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>651.881802754218</v>
+        <v>653.0787479235273</v>
       </c>
       <c r="C114" t="n">
-        <v>658.6044862124207</v>
+        <v>657.4275379105374</v>
       </c>
       <c r="D114" t="n">
-        <v>647.3335142418318</v>
+        <v>646.6951571900124</v>
       </c>
       <c r="E114" t="n">
-        <v>652.3905029296875</v>
+        <v>653.178466796875</v>
       </c>
       <c r="F114" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>653.0787479235273</v>
+        <v>647.0841872338415</v>
       </c>
       <c r="C115" t="n">
-        <v>657.4275379105374</v>
+        <v>651.8219905315074</v>
       </c>
       <c r="D115" t="n">
-        <v>646.6951571900124</v>
+        <v>635.2646391478804</v>
       </c>
       <c r="E115" t="n">
-        <v>653.178466796875</v>
+        <v>636.5413208007812</v>
       </c>
       <c r="F115" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>647.0841872338415</v>
+        <v>622.2879460132801</v>
       </c>
       <c r="C116" t="n">
-        <v>651.8219905315074</v>
+        <v>627.554356001348</v>
       </c>
       <c r="D116" t="n">
-        <v>635.2646391478804</v>
+        <v>607.9847424867846</v>
       </c>
       <c r="E116" t="n">
-        <v>636.5413208007812</v>
+        <v>612.1340942382812</v>
       </c>
       <c r="F116" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,25 +3459,25 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>622.2880080608647</v>
+        <v>630.9168848948667</v>
       </c>
       <c r="C117" t="n">
-        <v>627.55441857404</v>
+        <v>633.6621719731276</v>
       </c>
       <c r="D117" t="n">
-        <v>607.9848031082139</v>
+        <v>622.0321132511823</v>
       </c>
       <c r="E117" t="n">
-        <v>612.1341552734375</v>
+        <v>626.3746948242188</v>
       </c>
       <c r="F117" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3485,25 +3485,25 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>630.9168848948667</v>
+        <v>626.9137783313067</v>
       </c>
       <c r="C118" t="n">
-        <v>633.6621719731276</v>
+        <v>635.4591062750881</v>
       </c>
       <c r="D118" t="n">
-        <v>622.0321132511823</v>
+        <v>620.634579694285</v>
       </c>
       <c r="E118" t="n">
-        <v>626.3746948242188</v>
+        <v>621.5928955078125</v>
       </c>
       <c r="F118" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G118" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>626.9137167736849</v>
+        <v>615.2837809831337</v>
       </c>
       <c r="C119" t="n">
-        <v>635.4590438783874</v>
+        <v>621.5829648535273</v>
       </c>
       <c r="D119" t="n">
-        <v>620.6345187532272</v>
+        <v>613.5567043186309</v>
       </c>
       <c r="E119" t="n">
-        <v>621.5928344726562</v>
+        <v>614.6248779296875</v>
       </c>
       <c r="F119" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>615.2837198825454</v>
+        <v>611.1009505532863</v>
       </c>
       <c r="C120" t="n">
-        <v>621.5829031274002</v>
+        <v>611.9494694911245</v>
       </c>
       <c r="D120" t="n">
-        <v>613.5566433895493</v>
+        <v>601.2278849458298</v>
       </c>
       <c r="E120" t="n">
-        <v>614.6248168945312</v>
+        <v>605.6602783203125</v>
       </c>
       <c r="F120" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>611.1008889698486</v>
+        <v>602.4957192983555</v>
       </c>
       <c r="C121" t="n">
-        <v>611.9494078221777</v>
+        <v>602.9249750667714</v>
       </c>
       <c r="D121" t="n">
-        <v>601.2278243573462</v>
+        <v>586.2435901825164</v>
       </c>
       <c r="E121" t="n">
-        <v>605.6602172851562</v>
+        <v>592.642578125</v>
       </c>
       <c r="F121" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>602.4957192983555</v>
+        <v>604.7517959610541</v>
       </c>
       <c r="C122" t="n">
-        <v>602.9249750667714</v>
+        <v>607.5969482872343</v>
       </c>
       <c r="D122" t="n">
-        <v>586.2435901825164</v>
+        <v>597.9834469761715</v>
       </c>
       <c r="E122" t="n">
-        <v>592.642578125</v>
+        <v>603.0247802734375</v>
       </c>
       <c r="F122" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>604.7517959610541</v>
+        <v>598.0732713770465</v>
       </c>
       <c r="C123" t="n">
-        <v>607.5969482872343</v>
+        <v>599.9700396349708</v>
       </c>
       <c r="D123" t="n">
-        <v>597.9834469761715</v>
+        <v>589.9871770786485</v>
       </c>
       <c r="E123" t="n">
-        <v>603.0247802734375</v>
+        <v>591.9038696289062</v>
       </c>
       <c r="F123" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>598.0732713770465</v>
+        <v>597.7138608396341</v>
       </c>
       <c r="C124" t="n">
-        <v>599.9700396349708</v>
+        <v>602.6354044215132</v>
       </c>
       <c r="D124" t="n">
-        <v>589.9871770786485</v>
+        <v>592.3830467312241</v>
       </c>
       <c r="E124" t="n">
-        <v>591.9038696289062</v>
+        <v>593.8704833984375</v>
       </c>
       <c r="F124" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B125" t="n">
-        <v>597.7138608396341</v>
+        <v>581.4916747262954</v>
       </c>
       <c r="C125" t="n">
-        <v>602.6354044215132</v>
+        <v>582.0008103985165</v>
       </c>
       <c r="D125" t="n">
-        <v>592.3830467312241</v>
+        <v>542.4187412024525</v>
       </c>
       <c r="E125" t="n">
-        <v>593.8704833984375</v>
+        <v>546.6015625</v>
       </c>
       <c r="F125" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B126" t="n">
-        <v>581.4917396573854</v>
+        <v>539.1743295527585</v>
       </c>
       <c r="C126" t="n">
-        <v>582.0008753864581</v>
+        <v>542.6683311056884</v>
       </c>
       <c r="D126" t="n">
-        <v>542.4188017705425</v>
+        <v>519.368366299545</v>
       </c>
       <c r="E126" t="n">
-        <v>546.6016235351562</v>
+        <v>524.8189697265625</v>
       </c>
       <c r="F126" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B127" t="n">
-        <v>539.1743922574078</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="C127" t="n">
-        <v>542.6683942166816</v>
+        <v>538.6253045735799</v>
       </c>
       <c r="D127" t="n">
-        <v>519.3684267008094</v>
+        <v>527.6341638126921</v>
       </c>
       <c r="E127" t="n">
-        <v>524.8190307617188</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="F127" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B128" t="n">
-        <v>535.4607543945312</v>
+        <v>549.0374119135495</v>
       </c>
       <c r="C128" t="n">
-        <v>538.6253045735799</v>
+        <v>572.7067990959439</v>
       </c>
       <c r="D128" t="n">
-        <v>527.6341638126921</v>
+        <v>545.8329522821889</v>
       </c>
       <c r="E128" t="n">
-        <v>535.4607543945312</v>
+        <v>571.1494750976562</v>
       </c>
       <c r="F128" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B129" t="n">
-        <v>549.0374119135495</v>
+        <v>579.1357866530213</v>
       </c>
       <c r="C129" t="n">
-        <v>572.7067990959439</v>
+        <v>591.5344843799961</v>
       </c>
       <c r="D129" t="n">
-        <v>545.8329522821889</v>
+        <v>572.8366030750008</v>
       </c>
       <c r="E129" t="n">
-        <v>571.1494750976562</v>
+        <v>578.2373046875</v>
       </c>
       <c r="F129" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B130" t="n">
-        <v>579.135725523027</v>
+        <v>565.0699110449033</v>
       </c>
       <c r="C130" t="n">
-        <v>591.5344219412718</v>
+        <v>577.5085793033603</v>
       </c>
       <c r="D130" t="n">
-        <v>572.8365426099092</v>
+        <v>558.7408105198895</v>
       </c>
       <c r="E130" t="n">
-        <v>578.2372436523438</v>
+        <v>573.4755249023438</v>
       </c>
       <c r="F130" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B131" t="n">
-        <v>565.0699110449033</v>
+        <v>576.6999432469056</v>
       </c>
       <c r="C131" t="n">
-        <v>577.5085793033603</v>
+        <v>581.7911783704857</v>
       </c>
       <c r="D131" t="n">
-        <v>558.7408105198895</v>
+        <v>571.0196924702504</v>
       </c>
       <c r="E131" t="n">
-        <v>573.4755249023438</v>
+        <v>572.0379638671875</v>
       </c>
       <c r="F131" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B132" t="n">
-        <v>576.7000047794845</v>
+        <v>571.4988503418972</v>
       </c>
       <c r="C132" t="n">
-        <v>581.7912404462878</v>
+        <v>574.2441373249518</v>
       </c>
       <c r="D132" t="n">
-        <v>571.0197533967594</v>
+        <v>563.7921103124964</v>
       </c>
       <c r="E132" t="n">
-        <v>572.0380249023438</v>
+        <v>574.064453125</v>
       </c>
       <c r="F132" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B133" t="n">
-        <v>571.4988503418972</v>
+        <v>604.9614419693103</v>
       </c>
       <c r="C133" t="n">
-        <v>574.2441373249518</v>
+        <v>628.8704088339113</v>
       </c>
       <c r="D133" t="n">
-        <v>563.7921103124964</v>
+        <v>590.8157434643455</v>
       </c>
       <c r="E133" t="n">
-        <v>574.064453125</v>
+        <v>611.3704223632812</v>
       </c>
       <c r="F133" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B134" t="n">
-        <v>604.9614419693103</v>
+        <v>625.8955000086161</v>
       </c>
       <c r="C134" t="n">
-        <v>628.8704088339113</v>
+        <v>636.4074834525468</v>
       </c>
       <c r="D134" t="n">
-        <v>590.8157434643455</v>
+        <v>621.9323328485281</v>
       </c>
       <c r="E134" t="n">
-        <v>611.3704223632812</v>
+        <v>627.3131103515625</v>
       </c>
       <c r="F134" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B135" t="n">
-        <v>625.8954391113879</v>
+        <v>633.3826022362973</v>
       </c>
       <c r="C135" t="n">
-        <v>636.4074215325429</v>
+        <v>637.4856047359222</v>
       </c>
       <c r="D135" t="n">
-        <v>621.9322723369008</v>
+        <v>623.2600266965629</v>
       </c>
       <c r="E135" t="n">
-        <v>627.3130493164062</v>
+        <v>628.780517578125</v>
       </c>
       <c r="F135" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B136" t="n">
-        <v>633.3826022362973</v>
+        <v>628.4212176827168</v>
       </c>
       <c r="C136" t="n">
-        <v>637.4856047359222</v>
+        <v>633.9117922613585</v>
       </c>
       <c r="D136" t="n">
-        <v>623.2600266965629</v>
+        <v>623.3299819911093</v>
       </c>
       <c r="E136" t="n">
-        <v>628.780517578125</v>
+        <v>633.442626953125</v>
       </c>
       <c r="F136" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B137" t="n">
-        <v>628.4211571313969</v>
+        <v>642.117619704398</v>
       </c>
       <c r="C137" t="n">
-        <v>633.911731180996</v>
+        <v>665.1181727259973</v>
       </c>
       <c r="D137" t="n">
-        <v>623.3299219303536</v>
+        <v>638.2742422102883</v>
       </c>
       <c r="E137" t="n">
-        <v>633.4425659179688</v>
+        <v>661.3546142578125</v>
       </c>
       <c r="F137" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B138" t="n">
-        <v>642.117619704398</v>
+        <v>665.856909197143</v>
       </c>
       <c r="C138" t="n">
-        <v>665.1181727259973</v>
+        <v>677.3372007350248</v>
       </c>
       <c r="D138" t="n">
-        <v>638.2742422102883</v>
+        <v>663.081644256971</v>
       </c>
       <c r="E138" t="n">
-        <v>661.3546142578125</v>
+        <v>670.4290771484375</v>
       </c>
       <c r="F138" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B139" t="n">
-        <v>665.856909197143</v>
+        <v>674.831464225754</v>
       </c>
       <c r="C139" t="n">
-        <v>677.3372007350248</v>
+        <v>676.4187660594131</v>
       </c>
       <c r="D139" t="n">
-        <v>663.081644256971</v>
+        <v>666.605595861725</v>
       </c>
       <c r="E139" t="n">
-        <v>670.4290771484375</v>
+        <v>675.7099609375</v>
       </c>
       <c r="F139" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B140" t="n">
-        <v>674.831464225754</v>
+        <v>677.4369744478516</v>
       </c>
       <c r="C140" t="n">
-        <v>676.4187660594131</v>
+        <v>690.3348757077041</v>
       </c>
       <c r="D140" t="n">
-        <v>666.605595861725</v>
+        <v>673.9729506648888</v>
       </c>
       <c r="E140" t="n">
-        <v>675.7099609375</v>
+        <v>687.3699340820312</v>
       </c>
       <c r="F140" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B141" t="n">
-        <v>677.4369744478516</v>
+        <v>680.192296240317</v>
       </c>
       <c r="C141" t="n">
-        <v>690.3348757077041</v>
+        <v>682.2088539380842</v>
       </c>
       <c r="D141" t="n">
-        <v>673.9729506648888</v>
+        <v>666.8552067290691</v>
       </c>
       <c r="E141" t="n">
-        <v>687.3699340820312</v>
+        <v>669.7601928710938</v>
       </c>
       <c r="F141" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B142" t="n">
-        <v>680.192296240317</v>
+        <v>669.8500580611455</v>
       </c>
       <c r="C142" t="n">
-        <v>682.2088539380842</v>
+        <v>675.0411586256739</v>
       </c>
       <c r="D142" t="n">
-        <v>666.8552067290691</v>
+        <v>666.1863646700106</v>
       </c>
       <c r="E142" t="n">
-        <v>669.7601928710938</v>
+        <v>667.6937866210938</v>
       </c>
       <c r="F142" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B143" t="n">
-        <v>669.8500580611455</v>
+        <v>673.2042912464699</v>
       </c>
       <c r="C143" t="n">
-        <v>675.0411586256739</v>
+        <v>677.2174214115423</v>
       </c>
       <c r="D143" t="n">
-        <v>666.1863646700106</v>
+        <v>668.6022063234784</v>
       </c>
       <c r="E143" t="n">
-        <v>667.6937866210938</v>
+        <v>673.5636596679688</v>
       </c>
       <c r="F143" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B144" t="n">
-        <v>673.2042912464699</v>
+        <v>662.562575853328</v>
       </c>
       <c r="C144" t="n">
-        <v>677.2174214115423</v>
+        <v>668.4125184743669</v>
       </c>
       <c r="D144" t="n">
-        <v>668.6022063234784</v>
+        <v>651.9308032468797</v>
       </c>
       <c r="E144" t="n">
-        <v>673.5636596679688</v>
+        <v>658.0203857421875</v>
       </c>
       <c r="F144" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B145" t="n">
-        <v>662.562575853328</v>
+        <v>659.1883568751083</v>
       </c>
       <c r="C145" t="n">
-        <v>668.4125184743669</v>
+        <v>679.5034568571632</v>
       </c>
       <c r="D145" t="n">
-        <v>651.9308032468797</v>
+        <v>652.719481738207</v>
       </c>
       <c r="E145" t="n">
-        <v>658.0203857421875</v>
+        <v>673.8731689453125</v>
       </c>
       <c r="F145" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B146" t="n">
-        <v>659.1883568751083</v>
+        <v>669.8500343121515</v>
       </c>
       <c r="C146" t="n">
-        <v>679.5034568571632</v>
+        <v>681.330325511242</v>
       </c>
       <c r="D146" t="n">
-        <v>652.719481738207</v>
+        <v>669.6903353309991</v>
       </c>
       <c r="E146" t="n">
-        <v>673.8731689453125</v>
+        <v>677.4569702148438</v>
       </c>
       <c r="F146" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B147" t="n">
-        <v>669.8500343121515</v>
+        <v>673.0844464119266</v>
       </c>
       <c r="C147" t="n">
-        <v>681.330325511242</v>
+        <v>677.0176962940845</v>
       </c>
       <c r="D147" t="n">
-        <v>669.6903353309991</v>
+        <v>664.489217253305</v>
       </c>
       <c r="E147" t="n">
-        <v>677.4569702148438</v>
+        <v>670.189453125</v>
       </c>
       <c r="F147" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B148" t="n">
-        <v>673.0844464119266</v>
+        <v>667.7636045616339</v>
       </c>
       <c r="C148" t="n">
-        <v>677.0176962940845</v>
+        <v>673.0944797535534</v>
       </c>
       <c r="D148" t="n">
-        <v>664.489217253305</v>
+        <v>662.6723692427279</v>
       </c>
       <c r="E148" t="n">
-        <v>670.189453125</v>
+        <v>667.9732666015625</v>
       </c>
       <c r="F148" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B149" t="n">
-        <v>667.7636045616339</v>
+        <v>618.2586017744245</v>
       </c>
       <c r="C149" t="n">
-        <v>673.0944797535534</v>
+        <v>619.7859479396749</v>
       </c>
       <c r="D149" t="n">
-        <v>662.6723692427279</v>
+        <v>598.9717055442339</v>
       </c>
       <c r="E149" t="n">
-        <v>667.9732666015625</v>
+        <v>610.8612670898438</v>
       </c>
       <c r="F149" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B150" t="n">
-        <v>618.2586017744245</v>
+        <v>613.6365485572411</v>
       </c>
       <c r="C150" t="n">
-        <v>619.7859479396749</v>
+        <v>617.8193701850194</v>
       </c>
       <c r="D150" t="n">
-        <v>598.9717055442339</v>
+        <v>605.0712358749745</v>
       </c>
       <c r="E150" t="n">
-        <v>610.8612670898438</v>
+        <v>607.7067260742188</v>
       </c>
       <c r="F150" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B151" t="n">
-        <v>613.6365485572411</v>
+        <v>606.8981537761392</v>
       </c>
       <c r="C151" t="n">
-        <v>617.8193701850194</v>
+        <v>612.9477660987843</v>
       </c>
       <c r="D151" t="n">
-        <v>605.0712358749745</v>
+        <v>601.7170456287333</v>
       </c>
       <c r="E151" t="n">
-        <v>607.7067260742188</v>
+        <v>609.3638916015625</v>
       </c>
       <c r="F151" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B152" t="n">
-        <v>606.8981537761392</v>
+        <v>612.2588828439087</v>
       </c>
       <c r="C152" t="n">
-        <v>612.9477660987843</v>
+        <v>613.2970785161436</v>
       </c>
       <c r="D152" t="n">
-        <v>601.7170456287333</v>
+        <v>599.3310648754198</v>
       </c>
       <c r="E152" t="n">
-        <v>609.3638916015625</v>
+        <v>603.9232177734375</v>
       </c>
       <c r="F152" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B153" t="n">
-        <v>612.2588828439087</v>
+        <v>600.0199080772063</v>
       </c>
       <c r="C153" t="n">
-        <v>613.2970785161436</v>
+        <v>618.8875416216711</v>
       </c>
       <c r="D153" t="n">
-        <v>599.3310648754198</v>
+        <v>597.0749516023062</v>
       </c>
       <c r="E153" t="n">
-        <v>603.9232177734375</v>
+        <v>611.8296508789062</v>
       </c>
       <c r="F153" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B154" t="n">
-        <v>600.0199080772063</v>
+        <v>613.6664238202088</v>
       </c>
       <c r="C154" t="n">
-        <v>618.8875416216711</v>
+        <v>623.9088493168618</v>
       </c>
       <c r="D154" t="n">
-        <v>597.0749516023062</v>
+        <v>612.4884534922683</v>
       </c>
       <c r="E154" t="n">
-        <v>611.8296508789062</v>
+        <v>615.7528686523438</v>
       </c>
       <c r="F154" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B155" t="n">
-        <v>613.6664846485507</v>
+        <v>614.1456663784968</v>
       </c>
       <c r="C155" t="n">
-        <v>623.9089111604618</v>
+        <v>615.7129829832094</v>
       </c>
       <c r="D155" t="n">
-        <v>612.4885142038465</v>
+        <v>605.0213161255829</v>
       </c>
       <c r="E155" t="n">
-        <v>615.7529296875</v>
+        <v>608.585205078125</v>
       </c>
       <c r="F155" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B156" t="n">
-        <v>614.145727971313</v>
+        <v>603.533915527778</v>
       </c>
       <c r="C156" t="n">
-        <v>615.7130447332122</v>
+        <v>603.8732987260729</v>
       </c>
       <c r="D156" t="n">
-        <v>605.0213768033159</v>
+        <v>597.0550476209405</v>
       </c>
       <c r="E156" t="n">
-        <v>608.5852661132812</v>
+        <v>597.8336791992188</v>
       </c>
       <c r="F156" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B157" t="n">
-        <v>603.533915527778</v>
+        <v>593.8006394881057</v>
       </c>
       <c r="C157" t="n">
-        <v>603.8732987260729</v>
+        <v>602.7153284632744</v>
       </c>
       <c r="D157" t="n">
-        <v>597.0550476209405</v>
+        <v>591.5844123107358</v>
       </c>
       <c r="E157" t="n">
-        <v>597.8336791992188</v>
+        <v>601.9666137695312</v>
       </c>
       <c r="F157" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B158" t="n">
-        <v>593.8005792809215</v>
+        <v>597.8037594995824</v>
       </c>
       <c r="C158" t="n">
-        <v>602.7152673522038</v>
+        <v>618.837657653709</v>
       </c>
       <c r="D158" t="n">
-        <v>591.5843523282613</v>
+        <v>595.6374345129168</v>
       </c>
       <c r="E158" t="n">
-        <v>601.966552734375</v>
+        <v>615.5732421875</v>
       </c>
       <c r="F158" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B159" t="n">
-        <v>597.8037594995824</v>
+        <v>614.944289073115</v>
       </c>
       <c r="C159" t="n">
-        <v>618.837657653709</v>
+        <v>622.6610217742586</v>
       </c>
       <c r="D159" t="n">
-        <v>595.6374345129168</v>
+        <v>613.9460028895547</v>
       </c>
       <c r="E159" t="n">
-        <v>615.5732421875</v>
+        <v>617.3701171875</v>
       </c>
       <c r="F159" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B160" t="n">
-        <v>614.944289073115</v>
+        <v>612.9377892034477</v>
       </c>
       <c r="C160" t="n">
-        <v>622.6610217742586</v>
+        <v>620.135455286475</v>
       </c>
       <c r="D160" t="n">
-        <v>613.9460028895547</v>
+        <v>608.2658166797805</v>
       </c>
       <c r="E160" t="n">
-        <v>617.3701171875</v>
+        <v>613.1773681640625</v>
       </c>
       <c r="F160" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B161" t="n">
-        <v>612.9377281921389</v>
+        <v>608.0660990208263</v>
       </c>
       <c r="C161" t="n">
-        <v>620.1353935587166</v>
+        <v>614.5350350972873</v>
       </c>
       <c r="D161" t="n">
-        <v>608.2657561335159</v>
+        <v>602.6554048207697</v>
       </c>
       <c r="E161" t="n">
-        <v>613.1773071289062</v>
+        <v>610.1625366210938</v>
       </c>
       <c r="F161" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B162" t="n">
-        <v>608.0660990208263</v>
+        <v>607.8764543920544</v>
       </c>
       <c r="C162" t="n">
-        <v>614.5350350972873</v>
+        <v>612.8778783201094</v>
       </c>
       <c r="D162" t="n">
-        <v>602.6554048207697</v>
+        <v>599.5208032426234</v>
       </c>
       <c r="E162" t="n">
-        <v>610.1625366210938</v>
+        <v>601.5772705078125</v>
       </c>
       <c r="F162" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B163" t="n">
-        <v>607.8763927177921</v>
+        <v>599.7304526335664</v>
       </c>
       <c r="C163" t="n">
-        <v>612.8778161384099</v>
+        <v>606.9580352784536</v>
       </c>
       <c r="D163" t="n">
-        <v>599.5207424161133</v>
+        <v>596.7854960328639</v>
       </c>
       <c r="E163" t="n">
-        <v>601.5772094726562</v>
+        <v>604.0230712890625</v>
       </c>
       <c r="F163" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B164" t="n">
-        <v>599.7304526335664</v>
+        <v>598.9716935873996</v>
       </c>
       <c r="C164" t="n">
-        <v>606.9580352784536</v>
+        <v>608.5552163125774</v>
       </c>
       <c r="D164" t="n">
-        <v>596.7854960328639</v>
+        <v>593.7905860006466</v>
       </c>
       <c r="E164" t="n">
-        <v>604.0230712890625</v>
+        <v>606.3390502929688</v>
       </c>
       <c r="F164" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B165" t="n">
-        <v>598.9717538809448</v>
+        <v>606.838246230648</v>
       </c>
       <c r="C165" t="n">
-        <v>608.5552775708169</v>
+        <v>613.7563625825306</v>
       </c>
       <c r="D165" t="n">
-        <v>593.7906457726523</v>
+        <v>605.9098473363839</v>
       </c>
       <c r="E165" t="n">
-        <v>606.339111328125</v>
+        <v>609.2141723632812</v>
       </c>
       <c r="F165" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B166" t="n">
-        <v>606.8381854335279</v>
+        <v>607.8464888599174</v>
       </c>
       <c r="C166" t="n">
-        <v>613.7563010923075</v>
+        <v>613.4168818935308</v>
       </c>
       <c r="D166" t="n">
-        <v>605.9097866322771</v>
+        <v>604.2626146519137</v>
       </c>
       <c r="E166" t="n">
-        <v>609.214111328125</v>
+        <v>611.2905883789062</v>
       </c>
       <c r="F166" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B167" t="n">
-        <v>607.8465495511928</v>
+        <v>608.3556581766634</v>
       </c>
       <c r="C167" t="n">
-        <v>613.4169431409898</v>
+        <v>637.4057633477772</v>
       </c>
       <c r="D167" t="n">
-        <v>604.2626749853522</v>
+        <v>607.9563193089997</v>
       </c>
       <c r="E167" t="n">
-        <v>611.2906494140625</v>
+        <v>634.1713256835938</v>
       </c>
       <c r="F167" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B168" t="n">
-        <v>608.3555996261091</v>
+        <v>638.4040398455469</v>
       </c>
       <c r="C168" t="n">
-        <v>637.4057020013258</v>
+        <v>641.8980416273442</v>
       </c>
       <c r="D168" t="n">
-        <v>607.9562607968793</v>
+        <v>628.2315007921775</v>
       </c>
       <c r="E168" t="n">
-        <v>634.1712646484375</v>
+        <v>634.2012329101562</v>
       </c>
       <c r="F168" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B169" t="n">
-        <v>638.4040398455469</v>
+        <v>632.4143189973911</v>
       </c>
       <c r="C169" t="n">
-        <v>641.8980416273442</v>
+        <v>633.4126052152244</v>
       </c>
       <c r="D169" t="n">
-        <v>628.2315007921775</v>
+        <v>622.281689514161</v>
       </c>
       <c r="E169" t="n">
-        <v>634.2012329101562</v>
+        <v>631.426025390625</v>
       </c>
       <c r="F169" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B170" t="n">
-        <v>632.4143189973911</v>
+        <v>629.3196151062037</v>
       </c>
       <c r="C170" t="n">
-        <v>633.4126052152244</v>
+        <v>634.6604216515384</v>
       </c>
       <c r="D170" t="n">
-        <v>622.281689514161</v>
+        <v>598.5025264432778</v>
       </c>
       <c r="E170" t="n">
-        <v>631.426025390625</v>
+        <v>599.4408569335938</v>
       </c>
       <c r="F170" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B171" t="n">
-        <v>629.3196791836195</v>
+        <v>602.2061447656582</v>
       </c>
       <c r="C171" t="n">
-        <v>634.6604862727559</v>
+        <v>607.8364934375654</v>
       </c>
       <c r="D171" t="n">
-        <v>598.5025873828931</v>
+        <v>595.6573898697867</v>
       </c>
       <c r="E171" t="n">
-        <v>599.44091796875</v>
+        <v>596.6057739257812</v>
       </c>
       <c r="F171" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="n">
-        <v>602.2062063737548</v>
+        <v>601.9666135784172</v>
       </c>
       <c r="C172" t="n">
-        <v>607.8365556216692</v>
+        <v>623.0803923074952</v>
       </c>
       <c r="D172" t="n">
-        <v>595.6574508079194</v>
+        <v>599.2413115918356</v>
       </c>
       <c r="E172" t="n">
-        <v>596.6058349609375</v>
+        <v>621.912353515625</v>
       </c>
       <c r="F172" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B173" t="n">
-        <v>601.9665545007575</v>
+        <v>622.601105447702</v>
       </c>
       <c r="C173" t="n">
-        <v>623.0803311577063</v>
+        <v>641.2990464500883</v>
       </c>
       <c r="D173" t="n">
-        <v>599.2412527816401</v>
+        <v>621.3632403719068</v>
       </c>
       <c r="E173" t="n">
-        <v>621.9122924804688</v>
+        <v>626.4944458007812</v>
       </c>
       <c r="F173" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B174" t="n">
-        <v>622.6011661035562</v>
+        <v>622.3915867034917</v>
       </c>
       <c r="C174" t="n">
-        <v>641.2991089275577</v>
+        <v>628.0718380797523</v>
       </c>
       <c r="D174" t="n">
-        <v>621.3633009071642</v>
+        <v>581.9110292634388</v>
       </c>
       <c r="E174" t="n">
-        <v>626.4945068359375</v>
+        <v>591.9837646484375</v>
       </c>
       <c r="F174" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B175" t="n">
-        <v>622.3915225332053</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="C175" t="n">
-        <v>628.0717733238163</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="D175" t="n">
-        <v>581.9109692668093</v>
+        <v>578.2273099921849</v>
       </c>
       <c r="E175" t="n">
-        <v>591.9837036132812</v>
+        <v>584.3867797851562</v>
       </c>
       <c r="F175" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B176" t="n">
-        <v>590.9854370177134</v>
+        <v>589.9871222602228</v>
       </c>
       <c r="C176" t="n">
-        <v>590.9854370177134</v>
+        <v>596.6057643945405</v>
       </c>
       <c r="D176" t="n">
-        <v>578.2273099921849</v>
+        <v>580.0142532419713</v>
       </c>
       <c r="E176" t="n">
-        <v>584.3867797851562</v>
+        <v>583.588134765625</v>
       </c>
       <c r="F176" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B177" t="n">
-        <v>589.9871222602228</v>
+        <v>579.7347558037309</v>
       </c>
       <c r="C177" t="n">
-        <v>596.6057643945405</v>
+        <v>590.3066340250939</v>
       </c>
       <c r="D177" t="n">
-        <v>580.0142532419713</v>
+        <v>569.6221111934292</v>
       </c>
       <c r="E177" t="n">
-        <v>583.588134765625</v>
+        <v>570.00146484375</v>
       </c>
       <c r="F177" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B178" t="n">
-        <v>579.7347558037309</v>
+        <v>564.8602908302337</v>
       </c>
       <c r="C178" t="n">
-        <v>590.3066340250939</v>
+        <v>571.1893911411966</v>
       </c>
       <c r="D178" t="n">
-        <v>569.6221111934292</v>
+        <v>556.0553993401948</v>
       </c>
       <c r="E178" t="n">
-        <v>570.00146484375</v>
+        <v>567.455810546875</v>
       </c>
       <c r="F178" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B179" t="n">
-        <v>564.8602908302337</v>
+        <v>571.9680395129554</v>
       </c>
       <c r="C179" t="n">
-        <v>571.1893911411966</v>
+        <v>575.0826873049916</v>
       </c>
       <c r="D179" t="n">
-        <v>556.0553993401948</v>
+        <v>559.938704060897</v>
       </c>
       <c r="E179" t="n">
-        <v>567.455810546875</v>
+        <v>566.0082397460938</v>
       </c>
       <c r="F179" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B180" t="n">
-        <v>571.968101190783</v>
+        <v>579.4427159724761</v>
       </c>
       <c r="C180" t="n">
-        <v>575.0827493186854</v>
+        <v>600.795858737961</v>
       </c>
       <c r="D180" t="n">
-        <v>559.9387644415484</v>
+        <v>578.8431525395191</v>
       </c>
       <c r="E180" t="n">
-        <v>566.00830078125</v>
+        <v>593.011962890625</v>
       </c>
       <c r="F180" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,25 +5123,25 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B181" t="n">
-        <v>579.4427159724761</v>
+        <v>593.1818700134238</v>
       </c>
       <c r="C181" t="n">
-        <v>600.795858737961</v>
+        <v>605.3322537623429</v>
       </c>
       <c r="D181" t="n">
-        <v>578.8431525395191</v>
+        <v>591.5331468141493</v>
       </c>
       <c r="E181" t="n">
-        <v>593.011962890625</v>
+        <v>599.7366943359375</v>
       </c>
       <c r="F181" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G181" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B182" t="n">
-        <v>593.1818700134238</v>
+        <v>591.5331725816898</v>
       </c>
       <c r="C182" t="n">
-        <v>605.3322537623429</v>
+        <v>593.3417428489197</v>
       </c>
       <c r="D182" t="n">
-        <v>591.5331468141493</v>
+        <v>565.7435277503374</v>
       </c>
       <c r="E182" t="n">
-        <v>599.7366943359375</v>
+        <v>567.1324462890625</v>
       </c>
       <c r="F182" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B183" t="n">
-        <v>591.5331725816898</v>
+        <v>572.3682769745303</v>
       </c>
       <c r="C183" t="n">
-        <v>593.3417428489197</v>
+        <v>579.7624046842873</v>
       </c>
       <c r="D183" t="n">
-        <v>565.7435277503374</v>
+        <v>562.6559105294999</v>
       </c>
       <c r="E183" t="n">
-        <v>567.1324462890625</v>
+        <v>576.7647705078125</v>
       </c>
       <c r="F183" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B184" t="n">
-        <v>572.3682769745303</v>
+        <v>571.5689356803741</v>
       </c>
       <c r="C184" t="n">
-        <v>579.7624046842873</v>
+        <v>575.3559250048318</v>
       </c>
       <c r="D184" t="n">
-        <v>562.6559105294999</v>
+        <v>559.3685422933314</v>
       </c>
       <c r="E184" t="n">
-        <v>576.7647705078125</v>
+        <v>563.4053344726562</v>
       </c>
       <c r="F184" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B185" t="n">
-        <v>571.5689356803741</v>
+        <v>561.8066012038755</v>
       </c>
       <c r="C185" t="n">
-        <v>575.3559250048318</v>
+        <v>571.7487666818112</v>
       </c>
       <c r="D185" t="n">
-        <v>559.3685422933314</v>
+        <v>560.5775907162</v>
       </c>
       <c r="E185" t="n">
-        <v>563.4053344726562</v>
+        <v>561.7566528320312</v>
       </c>
       <c r="F185" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B186" t="n">
-        <v>561.8066012038755</v>
+        <v>561.4469285838474</v>
       </c>
       <c r="C186" t="n">
-        <v>571.7487666818112</v>
+        <v>568.591253761232</v>
       </c>
       <c r="D186" t="n">
-        <v>560.5775907162</v>
+        <v>555.1119012433646</v>
       </c>
       <c r="E186" t="n">
-        <v>561.7566528320312</v>
+        <v>557.230224609375</v>
       </c>
       <c r="F186" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B187" t="n">
-        <v>561.4469285838474</v>
+        <v>555.1118879211193</v>
       </c>
       <c r="C187" t="n">
-        <v>568.591253761232</v>
+        <v>555.9013039685537</v>
       </c>
       <c r="D187" t="n">
-        <v>555.1119012433646</v>
+        <v>539.7540133926082</v>
       </c>
       <c r="E187" t="n">
-        <v>557.230224609375</v>
+        <v>542.44189453125</v>
       </c>
       <c r="F187" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B188" t="n">
-        <v>555.1118879211193</v>
+        <v>542.9115767800729</v>
       </c>
       <c r="C188" t="n">
-        <v>555.9013039685537</v>
+        <v>556.4108722579447</v>
       </c>
       <c r="D188" t="n">
-        <v>539.7540133926082</v>
+        <v>539.9738926737891</v>
       </c>
       <c r="E188" t="n">
-        <v>542.44189453125</v>
+        <v>549.8161010742188</v>
       </c>
       <c r="F188" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B189" t="n">
-        <v>542.9115767800729</v>
+        <v>559.5583857816937</v>
       </c>
       <c r="C189" t="n">
-        <v>556.4108722579447</v>
+        <v>570.4498144711828</v>
       </c>
       <c r="D189" t="n">
-        <v>539.9738926737891</v>
+        <v>557.5599629753306</v>
       </c>
       <c r="E189" t="n">
-        <v>549.8161010742188</v>
+        <v>562.1563110351562</v>
       </c>
       <c r="F189" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B190" t="n">
-        <v>559.5583857816937</v>
+        <v>560.4976417791106</v>
       </c>
       <c r="C190" t="n">
-        <v>570.4498144711828</v>
+        <v>565.0939897966132</v>
       </c>
       <c r="D190" t="n">
-        <v>557.5599629753306</v>
+        <v>550.9951316644288</v>
       </c>
       <c r="E190" t="n">
-        <v>562.1563110351562</v>
+        <v>562.8457641601562</v>
       </c>
       <c r="F190" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B191" t="n">
-        <v>560.4976417791106</v>
+        <v>607.4305787144307</v>
       </c>
       <c r="C191" t="n">
-        <v>565.0939897966132</v>
+        <v>627.784571153574</v>
       </c>
       <c r="D191" t="n">
-        <v>550.9951316644288</v>
+        <v>594.6306830487989</v>
       </c>
       <c r="E191" t="n">
-        <v>562.8457641601562</v>
+        <v>612.4266357421875</v>
       </c>
       <c r="F191" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B192" t="n">
-        <v>607.4305787144307</v>
+        <v>607.4206544757068</v>
       </c>
       <c r="C192" t="n">
-        <v>627.784571153574</v>
+        <v>609.5189740900589</v>
       </c>
       <c r="D192" t="n">
-        <v>594.6306830487989</v>
+        <v>579.9622828274885</v>
       </c>
       <c r="E192" t="n">
-        <v>612.4266357421875</v>
+        <v>582.4403686523438</v>
       </c>
       <c r="F192" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B193" t="n">
-        <v>607.4206544757068</v>
+        <v>594.3709360150443</v>
       </c>
       <c r="C193" t="n">
-        <v>609.5189740900589</v>
+        <v>603.1040338931904</v>
       </c>
       <c r="D193" t="n">
-        <v>579.9622828274885</v>
+        <v>581.301233826573</v>
       </c>
       <c r="E193" t="n">
-        <v>582.4403686523438</v>
+        <v>599.8165893554688</v>
       </c>
       <c r="F193" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B194" t="n">
-        <v>594.3709360150443</v>
+        <v>607.1109147253509</v>
       </c>
       <c r="C194" t="n">
-        <v>603.1040338931904</v>
+        <v>624.8768626804635</v>
       </c>
       <c r="D194" t="n">
-        <v>581.301233826573</v>
+        <v>603.1839600389557</v>
       </c>
       <c r="E194" t="n">
-        <v>599.8165893554688</v>
+        <v>615.0946044921875</v>
       </c>
       <c r="F194" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B195" t="n">
-        <v>607.1109147253509</v>
+        <v>613.9055418180343</v>
       </c>
       <c r="C195" t="n">
-        <v>624.8768626804635</v>
+        <v>615.5142576272189</v>
       </c>
       <c r="D195" t="n">
-        <v>603.1839600389557</v>
+        <v>597.5384532703483</v>
       </c>
       <c r="E195" t="n">
-        <v>615.0946044921875</v>
+        <v>602.6444091796875</v>
       </c>
       <c r="F195" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B196" t="n">
-        <v>613.9055418180343</v>
+        <v>583.529455055522</v>
       </c>
       <c r="C196" t="n">
-        <v>615.5142576272189</v>
+        <v>632.77062206454</v>
       </c>
       <c r="D196" t="n">
-        <v>597.5384532703483</v>
+        <v>576.6149292518581</v>
       </c>
       <c r="E196" t="n">
-        <v>602.6444091796875</v>
+        <v>630.9819946289062</v>
       </c>
       <c r="F196" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B197" t="n">
-        <v>583.529455055522</v>
+        <v>659.8193113874754</v>
       </c>
       <c r="C197" t="n">
-        <v>632.77062206454</v>
+        <v>677.3254544051542</v>
       </c>
       <c r="D197" t="n">
-        <v>576.6149292518581</v>
+        <v>657.491131647921</v>
       </c>
       <c r="E197" t="n">
-        <v>630.9819946289062</v>
+        <v>668.6823120117188</v>
       </c>
       <c r="F197" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B198" t="n">
-        <v>659.8193113874754</v>
+        <v>660.858454671636</v>
       </c>
       <c r="C198" t="n">
-        <v>677.3254544051542</v>
+        <v>676.0864269737083</v>
       </c>
       <c r="D198" t="n">
-        <v>657.491131647921</v>
+        <v>653.6841239854351</v>
       </c>
       <c r="E198" t="n">
-        <v>668.6823120117188</v>
+        <v>656.2120971679688</v>
       </c>
       <c r="F198" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>660.858454671636</v>
+        <v>651.4858277274717</v>
       </c>
       <c r="C199" t="n">
-        <v>676.0864269737083</v>
+        <v>665.9743929146624</v>
       </c>
       <c r="D199" t="n">
-        <v>653.6841239854351</v>
+        <v>648.5381419230179</v>
       </c>
       <c r="E199" t="n">
-        <v>656.2120971679688</v>
+        <v>660.5186767578125</v>
       </c>
       <c r="F199" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>651.4858277274717</v>
+        <v>663.0767089741589</v>
       </c>
       <c r="C200" t="n">
-        <v>665.9743929146624</v>
+        <v>685.5390243545221</v>
       </c>
       <c r="D200" t="n">
-        <v>648.5381419230179</v>
+        <v>656.1421789132482</v>
       </c>
       <c r="E200" t="n">
-        <v>660.5186767578125</v>
+        <v>680.7727661132812</v>
       </c>
       <c r="F200" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>663.0767089741589</v>
+        <v>676.7459348014426</v>
       </c>
       <c r="C201" t="n">
-        <v>685.5390243545221</v>
+        <v>681.3622866487058</v>
       </c>
       <c r="D201" t="n">
-        <v>656.1421789132482</v>
+        <v>659.6393793096187</v>
       </c>
       <c r="E201" t="n">
-        <v>680.7727661132812</v>
+        <v>664.0159301757812</v>
       </c>
       <c r="F201" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B202" t="n">
-        <v>676.7459348014426</v>
+        <v>647.1892801723585</v>
       </c>
       <c r="C202" t="n">
-        <v>681.3622866487058</v>
+        <v>651.68573177941</v>
       </c>
       <c r="D202" t="n">
-        <v>659.6393793096187</v>
+        <v>625.5063791142821</v>
       </c>
       <c r="E202" t="n">
-        <v>664.0159301757812</v>
+        <v>645.5006103515625</v>
       </c>
       <c r="F202" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B203" t="n">
-        <v>647.1892801723585</v>
+        <v>646.1900645769782</v>
       </c>
       <c r="C203" t="n">
-        <v>651.68573177941</v>
+        <v>652.7848358303891</v>
       </c>
       <c r="D203" t="n">
-        <v>625.5063791142821</v>
+        <v>635.5084916103011</v>
       </c>
       <c r="E203" t="n">
-        <v>645.5006103515625</v>
+        <v>645.3406982421875</v>
       </c>
       <c r="F203" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B204" t="n">
-        <v>646.1900645769782</v>
+        <v>653.664124760039</v>
       </c>
       <c r="C204" t="n">
-        <v>652.7848358303891</v>
+        <v>655.3627963853286</v>
       </c>
       <c r="D204" t="n">
-        <v>635.5084916103011</v>
+        <v>642.6928027946103</v>
       </c>
       <c r="E204" t="n">
-        <v>645.3406982421875</v>
+        <v>643.3023071289062</v>
       </c>
       <c r="F204" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B205" t="n">
-        <v>653.664124760039</v>
+        <v>647.189254956408</v>
       </c>
       <c r="C205" t="n">
-        <v>655.3627963853286</v>
+        <v>648.4882176170956</v>
       </c>
       <c r="D205" t="n">
-        <v>642.6928027946103</v>
+        <v>623.5079318845419</v>
       </c>
       <c r="E205" t="n">
-        <v>643.3023071289062</v>
+        <v>626.6754150390625</v>
       </c>
       <c r="F205" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B206" t="n">
-        <v>647.189254956408</v>
+        <v>607.9301851876114</v>
       </c>
       <c r="C206" t="n">
-        <v>648.4882176170956</v>
+        <v>614.1653155952538</v>
       </c>
       <c r="D206" t="n">
-        <v>623.5079318845419</v>
+        <v>596.7490071058414</v>
       </c>
       <c r="E206" t="n">
-        <v>626.6754150390625</v>
+        <v>605.6220092773438</v>
       </c>
       <c r="F206" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B207" t="n">
-        <v>607.9301851876114</v>
+        <v>604.8226548171024</v>
       </c>
       <c r="C207" t="n">
-        <v>614.1653155952538</v>
+        <v>609.4989569016461</v>
       </c>
       <c r="D207" t="n">
-        <v>596.7490071058414</v>
+        <v>593.9812354037057</v>
       </c>
       <c r="E207" t="n">
-        <v>605.6220092773438</v>
+        <v>594.7206420898438</v>
       </c>
       <c r="F207" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B208" t="n">
-        <v>604.8226548171024</v>
+        <v>606.7411202287035</v>
       </c>
       <c r="C208" t="n">
-        <v>609.4989569016461</v>
+        <v>610.7779733376527</v>
       </c>
       <c r="D208" t="n">
-        <v>593.9812354037057</v>
+        <v>592.6622656813121</v>
       </c>
       <c r="E208" t="n">
-        <v>594.7206420898438</v>
+        <v>593.4016723632812</v>
       </c>
       <c r="F208" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B209" t="n">
-        <v>606.7411202287035</v>
+        <v>596.3493616660036</v>
       </c>
       <c r="C209" t="n">
-        <v>610.7779733376527</v>
+        <v>600.5260580457825</v>
       </c>
       <c r="D209" t="n">
-        <v>592.6622656813121</v>
+        <v>586.5370982909723</v>
       </c>
       <c r="E209" t="n">
-        <v>593.4016723632812</v>
+        <v>592.9420166015625</v>
       </c>
       <c r="F209" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B210" t="n">
-        <v>596.3493616660036</v>
+        <v>592.7821833537371</v>
       </c>
       <c r="C210" t="n">
-        <v>600.5260580457825</v>
+        <v>599.4968549179539</v>
       </c>
       <c r="D210" t="n">
-        <v>586.5370982909723</v>
+        <v>581.7608519604674</v>
       </c>
       <c r="E210" t="n">
-        <v>592.9420166015625</v>
+        <v>585.148193359375</v>
       </c>
       <c r="F210" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B211" t="n">
-        <v>592.7821833537371</v>
+        <v>525.58522592167</v>
       </c>
       <c r="C211" t="n">
-        <v>599.4968549179539</v>
+        <v>539.4542858116451</v>
       </c>
       <c r="D211" t="n">
-        <v>581.7608519604674</v>
+        <v>524.0764068649972</v>
       </c>
       <c r="E211" t="n">
-        <v>585.148193359375</v>
+        <v>538.60498046875</v>
       </c>
       <c r="F211" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B212" t="n">
-        <v>525.58522592167</v>
+        <v>543.171288392182</v>
       </c>
       <c r="C212" t="n">
-        <v>539.4542858116451</v>
+        <v>557.8897136701136</v>
       </c>
       <c r="D212" t="n">
-        <v>524.0764068649972</v>
+        <v>539.7939490076644</v>
       </c>
       <c r="E212" t="n">
-        <v>538.60498046875</v>
+        <v>556.27099609375</v>
       </c>
       <c r="F212" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B213" t="n">
-        <v>543.171288392182</v>
+        <v>561.7966164985271</v>
       </c>
       <c r="C213" t="n">
-        <v>557.8897136701136</v>
+        <v>597.0488245114987</v>
       </c>
       <c r="D213" t="n">
-        <v>539.7939490076644</v>
+        <v>558.9188827428958</v>
       </c>
       <c r="E213" t="n">
-        <v>556.27099609375</v>
+        <v>589.7745361328125</v>
       </c>
       <c r="F213" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B214" t="n">
-        <v>561.7966164985271</v>
+        <v>581.0414552494501</v>
       </c>
       <c r="C214" t="n">
-        <v>597.0488245114987</v>
+        <v>592.32253050782</v>
       </c>
       <c r="D214" t="n">
-        <v>558.9188827428958</v>
+        <v>577.794018053301</v>
       </c>
       <c r="E214" t="n">
-        <v>589.7745361328125</v>
+        <v>587.4763793945312</v>
       </c>
       <c r="F214" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B215" t="n">
-        <v>581.0414552494501</v>
+        <v>599.9865089938204</v>
       </c>
       <c r="C215" t="n">
-        <v>592.32253050782</v>
+        <v>600.5260612032997</v>
       </c>
       <c r="D215" t="n">
-        <v>577.794018053301</v>
+        <v>579.6625219517506</v>
       </c>
       <c r="E215" t="n">
-        <v>587.4763793945312</v>
+        <v>588.3057250976562</v>
       </c>
       <c r="F215" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B216" t="n">
-        <v>599.9865089938204</v>
+        <v>586.487189429669</v>
       </c>
       <c r="C216" t="n">
-        <v>600.5260612032997</v>
+        <v>594.8405827519979</v>
       </c>
       <c r="D216" t="n">
-        <v>579.6625219517506</v>
+        <v>585.5379263278069</v>
       </c>
       <c r="E216" t="n">
-        <v>588.3057250976562</v>
+        <v>589.4348754882812</v>
       </c>
       <c r="F216" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B217" t="n">
-        <v>586.487189429669</v>
+        <v>585.1781899072663</v>
       </c>
       <c r="C217" t="n">
-        <v>594.8405827519979</v>
+        <v>598.2678350979388</v>
       </c>
       <c r="D217" t="n">
-        <v>585.5379263278069</v>
+        <v>585.1581861630435</v>
       </c>
       <c r="E217" t="n">
-        <v>589.4348754882812</v>
+        <v>591.633056640625</v>
       </c>
       <c r="F217" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B218" t="n">
-        <v>585.1781899072663</v>
+        <v>598.657568915248</v>
       </c>
       <c r="C218" t="n">
-        <v>598.2678350979388</v>
+        <v>607.7304260788247</v>
       </c>
       <c r="D218" t="n">
-        <v>585.1581861630435</v>
+        <v>591.5631919202813</v>
       </c>
       <c r="E218" t="n">
-        <v>591.633056640625</v>
+        <v>594.4508666992188</v>
       </c>
       <c r="F218" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B219" t="n">
-        <v>598.657568915248</v>
+        <v>597.5284100969216</v>
       </c>
       <c r="C219" t="n">
-        <v>607.7304260788247</v>
+        <v>611.9470231090784</v>
       </c>
       <c r="D219" t="n">
-        <v>591.5631919202813</v>
+        <v>592.9320621063698</v>
       </c>
       <c r="E219" t="n">
-        <v>594.4508666992188</v>
+        <v>598.6475219726562</v>
       </c>
       <c r="F219" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B220" t="n">
-        <v>597.5284100969216</v>
+        <v>600.5960026412422</v>
       </c>
       <c r="C220" t="n">
-        <v>611.9470231090784</v>
+        <v>604.023290419805</v>
       </c>
       <c r="D220" t="n">
-        <v>592.9320621063698</v>
+        <v>577.7540447074138</v>
       </c>
       <c r="E220" t="n">
-        <v>598.6475219726562</v>
+        <v>578.3934936523438</v>
       </c>
       <c r="F220" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B221" t="n">
-        <v>600.5960026412422</v>
+        <v>580.2520897369063</v>
       </c>
       <c r="C221" t="n">
-        <v>604.023290419805</v>
+        <v>595.3801043917661</v>
       </c>
       <c r="D221" t="n">
-        <v>577.7540447074138</v>
+        <v>578.9331233348041</v>
       </c>
       <c r="E221" t="n">
-        <v>578.3934936523438</v>
+        <v>594.5007934570312</v>
       </c>
       <c r="F221" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B222" t="n">
-        <v>580.2520897369063</v>
+        <v>596.5092089028919</v>
       </c>
       <c r="C222" t="n">
-        <v>595.3801043917661</v>
+        <v>601.3853654698224</v>
       </c>
       <c r="D222" t="n">
-        <v>578.9331233348041</v>
+        <v>588.8252707092146</v>
       </c>
       <c r="E222" t="n">
-        <v>594.5007934570312</v>
+        <v>589.3848266601562</v>
       </c>
       <c r="F222" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B223" t="n">
-        <v>596.5092089028919</v>
+        <v>589.2849441761664</v>
       </c>
       <c r="C223" t="n">
-        <v>601.3853654698224</v>
+        <v>589.774548021712</v>
       </c>
       <c r="D223" t="n">
-        <v>588.8252707092146</v>
+        <v>564.3046582848494</v>
       </c>
       <c r="E223" t="n">
-        <v>589.3848266601562</v>
+        <v>568.5213012695312</v>
       </c>
       <c r="F223" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B224" t="n">
-        <v>589.2849441761664</v>
+        <v>557.0403796583744</v>
       </c>
       <c r="C224" t="n">
-        <v>589.774548021712</v>
+        <v>560.2178647510921</v>
       </c>
       <c r="D224" t="n">
-        <v>564.3046582848494</v>
+        <v>542.7816737373303</v>
       </c>
       <c r="E224" t="n">
-        <v>568.5213012695312</v>
+        <v>543.2412719726562</v>
       </c>
       <c r="F224" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B225" t="n">
-        <v>557.0403796583744</v>
+        <v>540.9131223962278</v>
       </c>
       <c r="C225" t="n">
-        <v>560.2178647510921</v>
+        <v>553.6330639150415</v>
       </c>
       <c r="D225" t="n">
-        <v>542.7816737373303</v>
+        <v>536.8463247077087</v>
       </c>
       <c r="E225" t="n">
-        <v>543.2412719726562</v>
+        <v>545.5994262695312</v>
       </c>
       <c r="F225" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B226" t="n">
-        <v>540.9131223962278</v>
+        <v>546.5187091013889</v>
       </c>
       <c r="C226" t="n">
-        <v>553.6330639150415</v>
+        <v>549.5562899225255</v>
       </c>
       <c r="D226" t="n">
-        <v>536.8463247077087</v>
+        <v>538.8847190657524</v>
       </c>
       <c r="E226" t="n">
-        <v>545.5994262695312</v>
+        <v>545.3995971679688</v>
       </c>
       <c r="F226" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B227" t="n">
-        <v>546.5187091013889</v>
+        <v>546.4587335768297</v>
       </c>
       <c r="C227" t="n">
-        <v>549.5562899225255</v>
+        <v>553.4332095869578</v>
       </c>
       <c r="D227" t="n">
-        <v>538.8847190657524</v>
+        <v>542.8015857242297</v>
       </c>
       <c r="E227" t="n">
-        <v>545.3995971679688</v>
+        <v>549.4663696289062</v>
       </c>
       <c r="F227" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B228" t="n">
-        <v>546.4587335768297</v>
+        <v>549.7661710202622</v>
       </c>
       <c r="C228" t="n">
-        <v>553.4332095869578</v>
+        <v>560.9772946036173</v>
       </c>
       <c r="D228" t="n">
-        <v>542.8015857242297</v>
+        <v>545.8692218355393</v>
       </c>
       <c r="E228" t="n">
-        <v>549.4663696289062</v>
+        <v>558.5792236328125</v>
       </c>
       <c r="F228" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B229" t="n">
-        <v>549.7661710202622</v>
+        <v>563.4353464162</v>
       </c>
       <c r="C229" t="n">
-        <v>560.9772946036173</v>
+        <v>570.3498724402046</v>
       </c>
       <c r="D229" t="n">
-        <v>545.8692218355393</v>
+        <v>560.9573215839381</v>
       </c>
       <c r="E229" t="n">
-        <v>558.5792236328125</v>
+        <v>569.6004638671875</v>
       </c>
       <c r="F229" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B230" t="n">
-        <v>563.4353464162</v>
+        <v>589.8444773654404</v>
       </c>
       <c r="C230" t="n">
-        <v>570.3498724402046</v>
+        <v>592.8721171723366</v>
       </c>
       <c r="D230" t="n">
-        <v>560.9573215839381</v>
+        <v>561.4369046651577</v>
       </c>
       <c r="E230" t="n">
-        <v>569.6004638671875</v>
+        <v>575.6856689453125</v>
       </c>
       <c r="F230" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B231" t="n">
-        <v>589.8444773654404</v>
+        <v>576.0253592943615</v>
       </c>
       <c r="C231" t="n">
-        <v>592.8721171723366</v>
+        <v>587.9260010338789</v>
       </c>
       <c r="D231" t="n">
-        <v>561.4369046651577</v>
+        <v>567.1723610665189</v>
       </c>
       <c r="E231" t="n">
-        <v>575.6856689453125</v>
+        <v>570.6495971679688</v>
       </c>
       <c r="F231" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B232" t="n">
-        <v>576.0253592943615</v>
+        <v>571.0992793335739</v>
       </c>
       <c r="C232" t="n">
-        <v>587.9260010338789</v>
+        <v>588.7253835559844</v>
       </c>
       <c r="D232" t="n">
-        <v>567.1723610665189</v>
+        <v>570.5497252457161</v>
       </c>
       <c r="E232" t="n">
-        <v>570.6495971679688</v>
+        <v>577.564208984375</v>
       </c>
       <c r="F232" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B233" t="n">
-        <v>571.0992793335739</v>
+        <v>577.1744781551006</v>
       </c>
       <c r="C233" t="n">
-        <v>588.7253835559844</v>
+        <v>578.2236379136884</v>
       </c>
       <c r="D233" t="n">
-        <v>570.5497252457161</v>
+        <v>568.6911832402849</v>
       </c>
       <c r="E233" t="n">
-        <v>577.564208984375</v>
+        <v>571.888671875</v>
       </c>
       <c r="F233" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B234" t="n">
-        <v>577.1744781551006</v>
+        <v>557.9096596695957</v>
       </c>
       <c r="C234" t="n">
-        <v>578.2236379136884</v>
+        <v>584.4887194481862</v>
       </c>
       <c r="D234" t="n">
-        <v>568.6911832402849</v>
+        <v>555.6614340241316</v>
       </c>
       <c r="E234" t="n">
-        <v>571.888671875</v>
+        <v>578.083740234375</v>
       </c>
       <c r="F234" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B235" t="n">
-        <v>557.9096596695957</v>
+        <v>578.3335366296732</v>
       </c>
       <c r="C235" t="n">
-        <v>584.4887194481862</v>
+        <v>599.9065373056851</v>
       </c>
       <c r="D235" t="n">
-        <v>555.6614340241316</v>
+        <v>576.5449702025707</v>
       </c>
       <c r="E235" t="n">
-        <v>578.083740234375</v>
+        <v>592.3824462890625</v>
       </c>
       <c r="F235" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B236" t="n">
-        <v>578.3335366296732</v>
+        <v>604.0133041368691</v>
       </c>
       <c r="C236" t="n">
-        <v>599.9065373056851</v>
+        <v>618.9715308723809</v>
       </c>
       <c r="D236" t="n">
-        <v>576.5449702025707</v>
+        <v>603.8733999005765</v>
       </c>
       <c r="E236" t="n">
-        <v>592.3824462890625</v>
+        <v>610.1984252929688</v>
       </c>
       <c r="F236" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B237" t="n">
-        <v>604.0133041368691</v>
+        <v>611.8670721034152</v>
       </c>
       <c r="C237" t="n">
-        <v>618.9715308723809</v>
+        <v>616.9730886717387</v>
       </c>
       <c r="D237" t="n">
-        <v>603.8733999005765</v>
+        <v>604.7926993516937</v>
       </c>
       <c r="E237" t="n">
-        <v>610.1984252929688</v>
+        <v>616.2836303710938</v>
       </c>
       <c r="F237" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B238" t="n">
-        <v>611.8670721034152</v>
+        <v>615.7241045276966</v>
       </c>
       <c r="C238" t="n">
-        <v>616.9730886717387</v>
+        <v>624.3072966603136</v>
       </c>
       <c r="D238" t="n">
-        <v>604.7926993516937</v>
+        <v>609.2591747857786</v>
       </c>
       <c r="E238" t="n">
-        <v>616.2836303710938</v>
+        <v>612.9962158203125</v>
       </c>
       <c r="F238" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B239" t="n">
-        <v>615.7241045276966</v>
+        <v>648.1284941622514</v>
       </c>
       <c r="C239" t="n">
-        <v>624.3072966603136</v>
+        <v>657.3411939542544</v>
       </c>
       <c r="D239" t="n">
-        <v>609.2591747857786</v>
+        <v>638.056426220049</v>
       </c>
       <c r="E239" t="n">
-        <v>612.9962158203125</v>
+        <v>653.1744995117188</v>
       </c>
       <c r="F239" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B240" t="n">
-        <v>648.1284941622514</v>
+        <v>653.1945472302951</v>
       </c>
       <c r="C240" t="n">
-        <v>657.3411939542544</v>
+        <v>662.9768054946985</v>
       </c>
       <c r="D240" t="n">
-        <v>638.056426220049</v>
+        <v>641.6336632885306</v>
       </c>
       <c r="E240" t="n">
-        <v>653.1744995117188</v>
+        <v>643.8718872070312</v>
       </c>
       <c r="F240" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B241" t="n">
-        <v>653.1945472302951</v>
+        <v>652.9947023490145</v>
       </c>
       <c r="C241" t="n">
-        <v>662.9768054946985</v>
+        <v>663.716221985592</v>
       </c>
       <c r="D241" t="n">
-        <v>641.6336632885306</v>
+        <v>645.6904688887529</v>
       </c>
       <c r="E241" t="n">
-        <v>643.8718872070312</v>
+        <v>647.51904296875</v>
       </c>
       <c r="F241" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B242" t="n">
-        <v>652.9947023490145</v>
+        <v>657.311302577125</v>
       </c>
       <c r="C242" t="n">
-        <v>663.716221985592</v>
+        <v>668.072768706455</v>
       </c>
       <c r="D242" t="n">
-        <v>645.6904688887529</v>
+        <v>648.708045415434</v>
       </c>
       <c r="E242" t="n">
-        <v>647.51904296875</v>
+        <v>665.0751342773438</v>
       </c>
       <c r="F242" t="n">
-        <v>16925000</v>
+        <v>19332300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B243" t="n">
-        <v>657.311302577125</v>
+        <v>658.7801108800835</v>
       </c>
       <c r="C243" t="n">
-        <v>668.072768706455</v>
+        <v>678.3346866933342</v>
       </c>
       <c r="D243" t="n">
-        <v>648.708045415434</v>
+        <v>655.6825797136325</v>
       </c>
       <c r="E243" t="n">
-        <v>665.0751342773438</v>
+        <v>669.7114868164062</v>
       </c>
       <c r="F243" t="n">
-        <v>19332300</v>
+        <v>19502800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B244" t="n">
-        <v>658.7801108800835</v>
+        <v>679.3738238485387</v>
       </c>
       <c r="C244" t="n">
-        <v>678.3346866933342</v>
+        <v>684.7695900234191</v>
       </c>
       <c r="D244" t="n">
-        <v>655.6825797136325</v>
+        <v>671.3801323225093</v>
       </c>
       <c r="E244" t="n">
-        <v>669.7114868164062</v>
+        <v>672.779052734375</v>
       </c>
       <c r="F244" t="n">
-        <v>19502800</v>
+        <v>17217800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B245" t="n">
-        <v>679.3738238485387</v>
+        <v>681.9018750257407</v>
       </c>
       <c r="C245" t="n">
-        <v>684.7695900234191</v>
+        <v>682.6612854975235</v>
       </c>
       <c r="D245" t="n">
-        <v>671.3801323225093</v>
+        <v>666.5239959332205</v>
       </c>
       <c r="E245" t="n">
-        <v>672.779052734375</v>
+        <v>681.77197265625</v>
       </c>
       <c r="F245" t="n">
-        <v>17217800</v>
+        <v>15928000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B246" t="n">
-        <v>681.9018750257407</v>
+        <v>688.0769980771287</v>
       </c>
       <c r="C246" t="n">
-        <v>682.6612854975235</v>
+        <v>689.6058209010791</v>
       </c>
       <c r="D246" t="n">
-        <v>666.5239959332205</v>
+        <v>660.278927643704</v>
       </c>
       <c r="E246" t="n">
-        <v>681.77197265625</v>
+        <v>665.2250366210938</v>
       </c>
       <c r="F246" t="n">
-        <v>15928000</v>
+        <v>27596400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,25 +6839,25 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B247" t="n">
-        <v>688.0769980771287</v>
+        <v>680.2999877929688</v>
       </c>
       <c r="C247" t="n">
-        <v>689.6058209010791</v>
+        <v>753</v>
       </c>
       <c r="D247" t="n">
-        <v>660.278927643704</v>
+        <v>679.5999755859375</v>
       </c>
       <c r="E247" t="n">
-        <v>665.2250366210938</v>
+        <v>741.25</v>
       </c>
       <c r="F247" t="n">
-        <v>27596400</v>
+        <v>48720500</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -6865,25 +6865,25 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B248" t="n">
-        <v>680.2999877929688</v>
+        <v>731.4000244140625</v>
       </c>
       <c r="C248" t="n">
-        <v>753</v>
+        <v>757.27001953125</v>
       </c>
       <c r="D248" t="n">
-        <v>679.5999755859375</v>
+        <v>730</v>
       </c>
       <c r="E248" t="n">
-        <v>741.25</v>
+        <v>736.5999755859375</v>
       </c>
       <c r="F248" t="n">
-        <v>48720500</v>
+        <v>28122100</v>
       </c>
       <c r="G248" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B249" t="n">
-        <v>731.4000244140625</v>
+        <v>747.5999755859375</v>
       </c>
       <c r="C249" t="n">
-        <v>757.27001953125</v>
+        <v>763.9000244140625</v>
       </c>
       <c r="D249" t="n">
-        <v>730</v>
+        <v>739.510009765625</v>
       </c>
       <c r="E249" t="n">
-        <v>736.5999755859375</v>
+        <v>744.0999755859375</v>
       </c>
       <c r="F249" t="n">
-        <v>28122100</v>
+        <v>30829200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B250" t="n">
-        <v>747.5999755859375</v>
+        <v>744.3599853515625</v>
       </c>
       <c r="C250" t="n">
-        <v>763.9000244140625</v>
+        <v>779.8200073242188</v>
       </c>
       <c r="D250" t="n">
-        <v>739.510009765625</v>
+        <v>743.010009765625</v>
       </c>
       <c r="E250" t="n">
-        <v>744.0999755859375</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="F250" t="n">
-        <v>30829200</v>
+        <v>34808500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B251" t="n">
-        <v>744.3599853515625</v>
+        <v>768.8499755859375</v>
       </c>
       <c r="C251" t="n">
-        <v>779.8200073242188</v>
+        <v>769.5700073242188</v>
       </c>
       <c r="D251" t="n">
-        <v>743.010009765625</v>
+        <v>746.5399780273438</v>
       </c>
       <c r="E251" t="n">
-        <v>777.5900268554688</v>
+        <v>751.6599731445312</v>
       </c>
       <c r="F251" t="n">
-        <v>34808500</v>
+        <v>25826700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B252" t="n">
-        <v>768.8499755859375</v>
+        <v>750.0399780273438</v>
       </c>
       <c r="C252" t="n">
-        <v>769.5700073242188</v>
+        <v>750.5800170898438</v>
       </c>
       <c r="D252" t="n">
-        <v>746.5399780273438</v>
+        <v>713.1900024414062</v>
       </c>
       <c r="E252" t="n">
-        <v>751.6599731445312</v>
+        <v>715.6199951171875</v>
       </c>
       <c r="F252" t="n">
-        <v>25753100</v>
+        <v>27713500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>715.62</v>
+      </c>
+      <c r="D2" t="n">
         <v>751.66</v>
       </c>
-      <c r="D2" t="n">
-        <v>777.59</v>
-      </c>
       <c r="E2" t="n">
-        <v>768.845</v>
+        <v>750.425</v>
       </c>
       <c r="F2" t="n">
-        <v>769.5700000000001</v>
+        <v>750.576</v>
       </c>
       <c r="G2" t="n">
-        <v>746.5405</v>
+        <v>713.1900000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>25649562</v>
+        <v>27629348</v>
       </c>
       <c r="I2" t="n">
-        <v>19642848</v>
+        <v>19942625</v>
       </c>
       <c r="J2" t="n">
-        <v>1914858373120</v>
+        <v>1823046369280</v>
       </c>
       <c r="K2" t="n">
-        <v>28.343136</v>
+        <v>28.330166</v>
       </c>
       <c r="L2" t="n">
-        <v>21.496538</v>
+        <v>20.547644</v>
       </c>
       <c r="M2" t="n">
-        <v>26.52</v>
+        <v>25.26</v>
       </c>
       <c r="N2" t="n">
         <v>779.8200000000001</v>
@@ -10818,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.3318377</v>
+        <v>6.9802966</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1936916480000</v>
+        <v>1845104345088</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:37</t>
+          <t>2026-09-29 13:24:32</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B2" t="n">
-        <v>746.1888636454856</v>
+        <v>739.740790143385</v>
       </c>
       <c r="C2" t="n">
-        <v>748.2419580482833</v>
+        <v>740.4583269528289</v>
       </c>
       <c r="D2" t="n">
-        <v>736.65126931649</v>
+        <v>723.8446976774693</v>
       </c>
       <c r="E2" t="n">
-        <v>740.8869018554688</v>
+        <v>731.8973999023438</v>
       </c>
       <c r="F2" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B3" t="n">
-        <v>739.7407284541446</v>
+        <v>719.050911987213</v>
       </c>
       <c r="C3" t="n">
-        <v>740.4582652037509</v>
+        <v>719.4096803677126</v>
       </c>
       <c r="D3" t="n">
-        <v>723.8446373138524</v>
+        <v>707.7991010033351</v>
       </c>
       <c r="E3" t="n">
-        <v>731.8973388671875</v>
+        <v>714.9149780273438</v>
       </c>
       <c r="F3" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B4" t="n">
-        <v>719.0509733754704</v>
+        <v>720.1372426569798</v>
       </c>
       <c r="C4" t="n">
-        <v>719.4097417865995</v>
+        <v>725.309699629413</v>
       </c>
       <c r="D4" t="n">
-        <v>707.7991614309803</v>
+        <v>715.7122502133443</v>
       </c>
       <c r="E4" t="n">
-        <v>714.9150390625</v>
+        <v>724.5921020507812</v>
       </c>
       <c r="F4" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B5" t="n">
-        <v>720.1372426569798</v>
+        <v>727.1634377305112</v>
       </c>
       <c r="C5" t="n">
-        <v>725.309699629413</v>
+        <v>728.528801479838</v>
       </c>
       <c r="D5" t="n">
-        <v>715.7122502133443</v>
+        <v>707.7791777004747</v>
       </c>
       <c r="E5" t="n">
-        <v>724.5921020507812</v>
+        <v>708.1578979492188</v>
       </c>
       <c r="F5" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B6" t="n">
-        <v>727.1633750572937</v>
+        <v>702.8060248479621</v>
       </c>
       <c r="C6" t="n">
-        <v>728.5287386889415</v>
+        <v>714.4565078636942</v>
       </c>
       <c r="D6" t="n">
-        <v>707.7791166979599</v>
+        <v>688.1756596108709</v>
       </c>
       <c r="E6" t="n">
-        <v>708.1578369140625</v>
+        <v>713.2406005859375</v>
       </c>
       <c r="F6" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B7" t="n">
-        <v>702.8060248479621</v>
+        <v>715.2937017364883</v>
       </c>
       <c r="C7" t="n">
-        <v>714.4565078636942</v>
+        <v>716.0710941262779</v>
       </c>
       <c r="D7" t="n">
-        <v>688.1756596108709</v>
+        <v>703.3641957962709</v>
       </c>
       <c r="E7" t="n">
-        <v>713.2406005859375</v>
+        <v>710.66943359375</v>
       </c>
       <c r="F7" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B8" t="n">
-        <v>715.2936403041813</v>
+        <v>711.0380954481734</v>
       </c>
       <c r="C8" t="n">
-        <v>716.0710326272052</v>
+        <v>717.2171476536749</v>
       </c>
       <c r="D8" t="n">
-        <v>703.3641353885179</v>
+        <v>705.4171476518181</v>
       </c>
       <c r="E8" t="n">
-        <v>710.6693725585938</v>
+        <v>715.4132690429688</v>
       </c>
       <c r="F8" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B9" t="n">
-        <v>711.0380954481734</v>
+        <v>715.8517801132227</v>
       </c>
       <c r="C9" t="n">
-        <v>717.2171476536749</v>
+        <v>731.0302734375</v>
       </c>
       <c r="D9" t="n">
-        <v>705.4171476518181</v>
+        <v>710.0314963104157</v>
       </c>
       <c r="E9" t="n">
-        <v>715.4132690429688</v>
+        <v>731.0302734375</v>
       </c>
       <c r="F9" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B10" t="n">
-        <v>715.8518398810967</v>
+        <v>728.4490335307075</v>
       </c>
       <c r="C10" t="n">
-        <v>731.0303344726562</v>
+        <v>732.784364410351</v>
       </c>
       <c r="D10" t="n">
-        <v>710.0315555923428</v>
+        <v>702.1283419878271</v>
       </c>
       <c r="E10" t="n">
-        <v>731.0303344726562</v>
+        <v>702.9156494140625</v>
       </c>
       <c r="F10" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B11" t="n">
-        <v>728.4490335307075</v>
+        <v>710.5996089558437</v>
       </c>
       <c r="C11" t="n">
-        <v>732.784364410351</v>
+        <v>717.5061741064447</v>
       </c>
       <c r="D11" t="n">
-        <v>702.1283419878271</v>
+        <v>705.2477676379041</v>
       </c>
       <c r="E11" t="n">
-        <v>702.9156494140625</v>
+        <v>713.280517578125</v>
       </c>
       <c r="F11" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B12" t="n">
-        <v>710.5996089558437</v>
+        <v>705.3873404797914</v>
       </c>
       <c r="C12" t="n">
-        <v>717.5061741064447</v>
+        <v>713.1310322093289</v>
       </c>
       <c r="D12" t="n">
-        <v>705.2477676379041</v>
+        <v>696.9658939978091</v>
       </c>
       <c r="E12" t="n">
-        <v>713.280517578125</v>
+        <v>706.25439453125</v>
       </c>
       <c r="F12" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B13" t="n">
-        <v>705.3873404797914</v>
+        <v>714.6359337847463</v>
       </c>
       <c r="C13" t="n">
-        <v>713.1310322093289</v>
+        <v>721.4528375244799</v>
       </c>
       <c r="D13" t="n">
-        <v>696.9658939978091</v>
+        <v>707.1114691724935</v>
       </c>
       <c r="E13" t="n">
-        <v>706.25439453125</v>
+        <v>715.124267578125</v>
       </c>
       <c r="F13" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B14" t="n">
-        <v>714.6358727912688</v>
+        <v>715.1242970926235</v>
       </c>
       <c r="C14" t="n">
-        <v>721.4527759491865</v>
+        <v>723.0374582122953</v>
       </c>
       <c r="D14" t="n">
-        <v>707.1114088212217</v>
+        <v>701.5005258067208</v>
       </c>
       <c r="E14" t="n">
-        <v>715.1242065429688</v>
+        <v>709.662841796875</v>
       </c>
       <c r="F14" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B15" t="n">
-        <v>715.1241740828767</v>
+        <v>704.6896374063629</v>
       </c>
       <c r="C15" t="n">
-        <v>723.0373338413923</v>
+        <v>716.1108563950927</v>
       </c>
       <c r="D15" t="n">
-        <v>701.5004051404221</v>
+        <v>703.7328609179003</v>
       </c>
       <c r="E15" t="n">
-        <v>709.6627197265625</v>
+        <v>714.496337890625</v>
       </c>
       <c r="F15" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B16" t="n">
-        <v>704.6896976037913</v>
+        <v>718.7519624447335</v>
       </c>
       <c r="C16" t="n">
-        <v>716.1109175681677</v>
+        <v>731.2894517891565</v>
       </c>
       <c r="D16" t="n">
-        <v>703.732921033597</v>
+        <v>717.7453670972193</v>
       </c>
       <c r="E16" t="n">
-        <v>714.4963989257812</v>
+        <v>729.69482421875</v>
       </c>
       <c r="F16" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B17" t="n">
-        <v>718.7519023248905</v>
+        <v>733.5318410857864</v>
       </c>
       <c r="C17" t="n">
-        <v>731.289390620618</v>
+        <v>736.0034377690635</v>
       </c>
       <c r="D17" t="n">
-        <v>717.7453070615727</v>
+        <v>726.2863984755653</v>
       </c>
       <c r="E17" t="n">
-        <v>729.6947631835938</v>
+        <v>730.7911376953125</v>
       </c>
       <c r="F17" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B18" t="n">
-        <v>733.5318410857864</v>
+        <v>731.3492269695964</v>
       </c>
       <c r="C18" t="n">
-        <v>736.0034377690635</v>
+        <v>738.0962989037338</v>
       </c>
       <c r="D18" t="n">
-        <v>726.2863984755653</v>
+        <v>721.5823690736463</v>
       </c>
       <c r="E18" t="n">
-        <v>730.7911376953125</v>
+        <v>730.9306030273438</v>
       </c>
       <c r="F18" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B19" t="n">
-        <v>731.3492269695964</v>
+        <v>732.2163225390138</v>
       </c>
       <c r="C19" t="n">
-        <v>738.0962989037338</v>
+        <v>739.9002195728755</v>
       </c>
       <c r="D19" t="n">
-        <v>721.5823690736463</v>
+        <v>730.6216949207216</v>
       </c>
       <c r="E19" t="n">
-        <v>730.9306030273438</v>
+        <v>731.5186767578125</v>
       </c>
       <c r="F19" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B20" t="n">
-        <v>732.2163225390138</v>
+        <v>734.2991918313108</v>
       </c>
       <c r="C20" t="n">
-        <v>739.9002195728755</v>
+        <v>738.7042934120783</v>
       </c>
       <c r="D20" t="n">
-        <v>730.6216949207216</v>
+        <v>728.6783045992579</v>
       </c>
       <c r="E20" t="n">
-        <v>731.5186767578125</v>
+        <v>735.8638916015625</v>
       </c>
       <c r="F20" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B21" t="n">
-        <v>734.2991309259364</v>
+        <v>747.1953964386955</v>
       </c>
       <c r="C21" t="n">
-        <v>738.704232141329</v>
+        <v>753.1950643156673</v>
       </c>
       <c r="D21" t="n">
-        <v>728.6782441600997</v>
+        <v>745.4812403760276</v>
       </c>
       <c r="E21" t="n">
-        <v>735.8638305664062</v>
+        <v>748.28173828125</v>
       </c>
       <c r="F21" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B22" t="n">
-        <v>747.195457385242</v>
+        <v>750.0856376808406</v>
       </c>
       <c r="C22" t="n">
-        <v>753.1951257515892</v>
+        <v>755.8361508831443</v>
       </c>
       <c r="D22" t="n">
-        <v>745.4813011827554</v>
+        <v>742.9996885933356</v>
       </c>
       <c r="E22" t="n">
-        <v>748.2817993164062</v>
+        <v>748.899658203125</v>
       </c>
       <c r="F22" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B23" t="n">
-        <v>750.0856988126538</v>
+        <v>752.1985111114485</v>
       </c>
       <c r="C23" t="n">
-        <v>755.8362124836232</v>
+        <v>756.5935760115584</v>
       </c>
       <c r="D23" t="n">
-        <v>742.9997491476457</v>
+        <v>739.9998990805568</v>
       </c>
       <c r="E23" t="n">
-        <v>748.8997192382812</v>
+        <v>749.12890625</v>
       </c>
       <c r="F23" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B24" t="n">
-        <v>752.1985111114485</v>
+        <v>666.8879125335289</v>
       </c>
       <c r="C24" t="n">
-        <v>756.5935760115584</v>
+        <v>678.6579855089774</v>
       </c>
       <c r="D24" t="n">
-        <v>739.9998990805568</v>
+        <v>647.9720344844721</v>
       </c>
       <c r="E24" t="n">
-        <v>749.12890625</v>
+        <v>664.2169189453125</v>
       </c>
       <c r="F24" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B25" t="n">
-        <v>666.8879125335289</v>
+        <v>672.22980228556</v>
       </c>
       <c r="C25" t="n">
-        <v>678.6579855089774</v>
+        <v>672.6085225469975</v>
       </c>
       <c r="D25" t="n">
-        <v>647.9720344844721</v>
+        <v>643.3876326547638</v>
       </c>
       <c r="E25" t="n">
-        <v>664.2169189453125</v>
+        <v>646.158203125</v>
       </c>
       <c r="F25" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B26" t="n">
-        <v>672.2297387877188</v>
+        <v>653.7823467127146</v>
       </c>
       <c r="C26" t="n">
-        <v>672.6084590133829</v>
+        <v>657.1011064498967</v>
       </c>
       <c r="D26" t="n">
-        <v>643.3875718813117</v>
+        <v>634.0293422915395</v>
       </c>
       <c r="E26" t="n">
-        <v>646.1581420898438</v>
+        <v>635.55419921875</v>
       </c>
       <c r="F26" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B27" t="n">
-        <v>653.7823467127146</v>
+        <v>625.9168165443936</v>
       </c>
       <c r="C27" t="n">
-        <v>657.1011064498967</v>
+        <v>639.5705142822006</v>
       </c>
       <c r="D27" t="n">
-        <v>634.0293422915395</v>
+        <v>623.8937108241939</v>
       </c>
       <c r="E27" t="n">
-        <v>635.55419921875</v>
+        <v>625.1992797851562</v>
       </c>
       <c r="F27" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B28" t="n">
-        <v>625.9168776495994</v>
+        <v>630.1724007040705</v>
       </c>
       <c r="C28" t="n">
-        <v>639.5705767203505</v>
+        <v>640.0588479681868</v>
       </c>
       <c r="D28" t="n">
-        <v>623.8937717318939</v>
+        <v>624.4218873891514</v>
       </c>
       <c r="E28" t="n">
-        <v>625.1993408203125</v>
+        <v>633.8001098632812</v>
       </c>
       <c r="F28" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B29" t="n">
-        <v>630.1724007040705</v>
+        <v>633.7004019945108</v>
       </c>
       <c r="C29" t="n">
-        <v>640.0588479681868</v>
+        <v>633.8499192315176</v>
       </c>
       <c r="D29" t="n">
-        <v>624.4218873891514</v>
+        <v>615.9107705740217</v>
       </c>
       <c r="E29" t="n">
-        <v>633.8001098632812</v>
+        <v>616.8475952148438</v>
       </c>
       <c r="F29" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B30" t="n">
-        <v>633.7004019945108</v>
+        <v>614.4058308842617</v>
       </c>
       <c r="C30" t="n">
-        <v>633.8499192315176</v>
+        <v>620.0267784116583</v>
       </c>
       <c r="D30" t="n">
-        <v>615.9107705740217</v>
+        <v>599.1675434782962</v>
       </c>
       <c r="E30" t="n">
-        <v>616.8475952148438</v>
+        <v>619.6082153320312</v>
       </c>
       <c r="F30" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B31" t="n">
-        <v>614.4058914069517</v>
+        <v>628.9565496273584</v>
       </c>
       <c r="C31" t="n">
-        <v>620.0268394880455</v>
+        <v>632.8533046281837</v>
       </c>
       <c r="D31" t="n">
-        <v>599.1676024999227</v>
+        <v>616.0203887455347</v>
       </c>
       <c r="E31" t="n">
-        <v>619.6082763671875</v>
+        <v>629.624267578125</v>
       </c>
       <c r="F31" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B32" t="n">
-        <v>628.9565496273584</v>
+        <v>625.8770169082796</v>
       </c>
       <c r="C32" t="n">
-        <v>632.8533046281837</v>
+        <v>627.4317408228605</v>
       </c>
       <c r="D32" t="n">
-        <v>616.0203887455347</v>
+        <v>617.2961380110504</v>
       </c>
       <c r="E32" t="n">
-        <v>629.624267578125</v>
+        <v>624.9601440429688</v>
       </c>
       <c r="F32" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B33" t="n">
-        <v>625.8770169082796</v>
+        <v>626.0065293511232</v>
       </c>
       <c r="C33" t="n">
-        <v>627.4317408228605</v>
+        <v>626.8636074098682</v>
       </c>
       <c r="D33" t="n">
-        <v>617.2961380110504</v>
+        <v>605.7153735895874</v>
       </c>
       <c r="E33" t="n">
-        <v>624.9601440429688</v>
+        <v>606.951171875</v>
       </c>
       <c r="F33" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B34" t="n">
-        <v>626.0065923024907</v>
+        <v>610.9974896015757</v>
       </c>
       <c r="C34" t="n">
-        <v>626.8636704474237</v>
+        <v>615.5620236854409</v>
       </c>
       <c r="D34" t="n">
-        <v>605.7154345004715</v>
+        <v>600.9615245048305</v>
       </c>
       <c r="E34" t="n">
-        <v>606.9512329101562</v>
+        <v>607.8282470703125</v>
       </c>
       <c r="F34" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B35" t="n">
-        <v>610.9974282481795</v>
+        <v>599.7556041676178</v>
       </c>
       <c r="C35" t="n">
-        <v>615.5619618736964</v>
+        <v>611.6054241702889</v>
       </c>
       <c r="D35" t="n">
-        <v>600.9614641591972</v>
+        <v>593.1879159768617</v>
       </c>
       <c r="E35" t="n">
-        <v>607.8281860351562</v>
+        <v>607.3997192382812</v>
       </c>
       <c r="F35" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B36" t="n">
-        <v>599.7556041676178</v>
+        <v>606.980994504603</v>
       </c>
       <c r="C36" t="n">
-        <v>611.6054241702889</v>
+        <v>609.6220599721263</v>
       </c>
       <c r="D36" t="n">
-        <v>593.1879159768617</v>
+        <v>593.3871535288397</v>
       </c>
       <c r="E36" t="n">
-        <v>607.3997192382812</v>
+        <v>599.9747924804688</v>
       </c>
       <c r="F36" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B37" t="n">
-        <v>606.9810562524968</v>
+        <v>589.5999948667346</v>
       </c>
       <c r="C37" t="n">
-        <v>609.6221219886945</v>
+        <v>601.619222033871</v>
       </c>
       <c r="D37" t="n">
-        <v>593.3872138938384</v>
+        <v>581.8064849239344</v>
       </c>
       <c r="E37" t="n">
-        <v>599.974853515625</v>
+        <v>595.66943359375</v>
       </c>
       <c r="F37" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B38" t="n">
-        <v>589.5999948667346</v>
+        <v>591.7128101062766</v>
       </c>
       <c r="C38" t="n">
-        <v>601.619222033871</v>
+        <v>593.3174134864839</v>
       </c>
       <c r="D38" t="n">
-        <v>581.8064849239344</v>
+        <v>579.2849960343485</v>
       </c>
       <c r="E38" t="n">
-        <v>595.66943359375</v>
+        <v>588.3243408203125</v>
       </c>
       <c r="F38" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B39" t="n">
-        <v>591.7128714929664</v>
+        <v>601.4597887996167</v>
       </c>
       <c r="C39" t="n">
-        <v>593.3174750396417</v>
+        <v>604.6688739678727</v>
       </c>
       <c r="D39" t="n">
-        <v>579.2850561317264</v>
+        <v>581.3778841958236</v>
       </c>
       <c r="E39" t="n">
-        <v>588.3244018554688</v>
+        <v>587.1583251953125</v>
       </c>
       <c r="F39" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B40" t="n">
-        <v>601.4598513214113</v>
+        <v>586.5105876609664</v>
       </c>
       <c r="C40" t="n">
-        <v>604.668936823252</v>
+        <v>596.0980625793645</v>
       </c>
       <c r="D40" t="n">
-        <v>581.3779446301025</v>
+        <v>579.8930194476571</v>
       </c>
       <c r="E40" t="n">
-        <v>587.1583862304688</v>
+        <v>592.2411499023438</v>
       </c>
       <c r="F40" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B41" t="n">
-        <v>586.5104667718139</v>
+        <v>596.6959057641074</v>
       </c>
       <c r="C41" t="n">
-        <v>596.097939714081</v>
+        <v>614.6151629725317</v>
       </c>
       <c r="D41" t="n">
-        <v>579.8928999224906</v>
+        <v>595.609624740878</v>
       </c>
       <c r="E41" t="n">
-        <v>592.2410278320312</v>
+        <v>610.9774780273438</v>
       </c>
       <c r="F41" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B42" t="n">
-        <v>596.6959653725695</v>
+        <v>621.8904932046078</v>
       </c>
       <c r="C42" t="n">
-        <v>614.6152243710839</v>
+        <v>634.8963639496133</v>
       </c>
       <c r="D42" t="n">
-        <v>595.6096842408232</v>
+        <v>616.209750572071</v>
       </c>
       <c r="E42" t="n">
-        <v>610.9775390625</v>
+        <v>634.0691528320312</v>
       </c>
       <c r="F42" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B43" t="n">
-        <v>621.8904932046078</v>
+        <v>635.5341804250853</v>
       </c>
       <c r="C43" t="n">
-        <v>634.8963639496133</v>
+        <v>636.2018983414315</v>
       </c>
       <c r="D43" t="n">
-        <v>616.209750572071</v>
+        <v>629.4946697427255</v>
       </c>
       <c r="E43" t="n">
-        <v>634.0691528320312</v>
+        <v>631.4679565429688</v>
       </c>
       <c r="F43" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B44" t="n">
-        <v>635.5342418532664</v>
+        <v>633.9296546389559</v>
       </c>
       <c r="C44" t="n">
-        <v>636.2019598341516</v>
+        <v>645.8591590880771</v>
       </c>
       <c r="D44" t="n">
-        <v>629.4947305871518</v>
+        <v>633.3515983825566</v>
       </c>
       <c r="E44" t="n">
-        <v>631.468017578125</v>
+        <v>645.759521484375</v>
       </c>
       <c r="F44" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B45" t="n">
-        <v>633.9296546389559</v>
+        <v>637.3878853503733</v>
       </c>
       <c r="C45" t="n">
-        <v>645.8591590880771</v>
+        <v>643.1383983949365</v>
       </c>
       <c r="D45" t="n">
-        <v>633.3515983825566</v>
+        <v>635.6039586340122</v>
       </c>
       <c r="E45" t="n">
-        <v>645.759521484375</v>
+        <v>638.7034301757812</v>
       </c>
       <c r="F45" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B46" t="n">
-        <v>637.3879462598147</v>
+        <v>640.1684965318557</v>
       </c>
       <c r="C46" t="n">
-        <v>643.138459853903</v>
+        <v>645.6797698761368</v>
       </c>
       <c r="D46" t="n">
-        <v>635.6040193729798</v>
+        <v>635.9129124654792</v>
       </c>
       <c r="E46" t="n">
-        <v>638.7034912109375</v>
+        <v>644.912353515625</v>
       </c>
       <c r="F46" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B47" t="n">
-        <v>640.1684359456628</v>
+        <v>642.2314810232181</v>
       </c>
       <c r="C47" t="n">
-        <v>645.6797087683515</v>
+        <v>646.6564735939825</v>
       </c>
       <c r="D47" t="n">
-        <v>635.9128522820391</v>
+        <v>635.3946865356451</v>
       </c>
       <c r="E47" t="n">
-        <v>644.9122924804688</v>
+        <v>637.437744140625</v>
       </c>
       <c r="F47" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B48" t="n">
-        <v>642.2314810232181</v>
+        <v>673.7147555733686</v>
       </c>
       <c r="C48" t="n">
-        <v>646.6564735939825</v>
+        <v>673.8143931879296</v>
       </c>
       <c r="D48" t="n">
-        <v>635.3946865356451</v>
+        <v>657.8186630061315</v>
       </c>
       <c r="E48" t="n">
-        <v>637.437744140625</v>
+        <v>659.293701171875</v>
       </c>
       <c r="F48" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B49" t="n">
-        <v>673.7146932031604</v>
+        <v>661.7553548965755</v>
       </c>
       <c r="C49" t="n">
-        <v>673.8143308084973</v>
+        <v>672.4092198957593</v>
       </c>
       <c r="D49" t="n">
-        <v>657.8186021075292</v>
+        <v>660.1508120837719</v>
       </c>
       <c r="E49" t="n">
-        <v>659.2936401367188</v>
+        <v>671.1434936523438</v>
       </c>
       <c r="F49" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B50" t="n">
-        <v>661.7552947151958</v>
+        <v>667.0772284693074</v>
       </c>
       <c r="C50" t="n">
-        <v>672.4091587454953</v>
+        <v>674.4223082782987</v>
       </c>
       <c r="D50" t="n">
-        <v>660.1507520483126</v>
+        <v>662.8216443414645</v>
       </c>
       <c r="E50" t="n">
-        <v>671.1434326171875</v>
+        <v>664.5457763671875</v>
       </c>
       <c r="F50" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B51" t="n">
-        <v>667.0772284693074</v>
+        <v>661.5261117632423</v>
       </c>
       <c r="C51" t="n">
-        <v>674.4223082782987</v>
+        <v>662.2336726422647</v>
       </c>
       <c r="D51" t="n">
-        <v>662.8216443414645</v>
+        <v>651.1313781996487</v>
       </c>
       <c r="E51" t="n">
-        <v>664.5457763671875</v>
+        <v>654.7391357421875</v>
       </c>
       <c r="F51" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B52" t="n">
-        <v>661.5260500954003</v>
+        <v>647.7528057448357</v>
       </c>
       <c r="C52" t="n">
-        <v>662.2336109084633</v>
+        <v>652.297387877758</v>
       </c>
       <c r="D52" t="n">
-        <v>651.1313175008097</v>
+        <v>641.2249606939789</v>
       </c>
       <c r="E52" t="n">
-        <v>654.7390747070312</v>
+        <v>647.9321899414062</v>
       </c>
       <c r="F52" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B53" t="n">
-        <v>647.7527447265774</v>
+        <v>641.1152803360264</v>
       </c>
       <c r="C53" t="n">
-        <v>652.2973264314004</v>
+        <v>653.0647981949571</v>
       </c>
       <c r="D53" t="n">
-        <v>641.2249002906431</v>
+        <v>638.6337077300913</v>
       </c>
       <c r="E53" t="n">
-        <v>647.93212890625</v>
+        <v>650.5034790039062</v>
       </c>
       <c r="F53" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B54" t="n">
-        <v>641.1152803360264</v>
+        <v>647.603240055161</v>
       </c>
       <c r="C54" t="n">
-        <v>653.0647981949571</v>
+        <v>708.5963563082138</v>
       </c>
       <c r="D54" t="n">
-        <v>638.6337077300913</v>
+        <v>636.4510671197735</v>
       </c>
       <c r="E54" t="n">
-        <v>650.5034790039062</v>
+        <v>642.0520629882812</v>
       </c>
       <c r="F54" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,25 +1847,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B55" t="n">
-        <v>647.6033016180266</v>
+        <v>644.0420011784053</v>
       </c>
       <c r="C55" t="n">
-        <v>708.5964236692454</v>
+        <v>651.3232442601446</v>
       </c>
       <c r="D55" t="n">
-        <v>636.4511276224844</v>
+        <v>637.0599755890928</v>
       </c>
       <c r="E55" t="n">
-        <v>642.0521240234375</v>
+        <v>645.8473510742188</v>
       </c>
       <c r="F55" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B56" t="n">
-        <v>644.0420011784053</v>
+        <v>641.8476715248971</v>
       </c>
       <c r="C56" t="n">
-        <v>651.3232442601446</v>
+        <v>660.8387602004772</v>
       </c>
       <c r="D56" t="n">
-        <v>637.0599755890928</v>
+        <v>641.5484540168895</v>
       </c>
       <c r="E56" t="n">
-        <v>645.8473510742188</v>
+        <v>655.462646484375</v>
       </c>
       <c r="F56" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G56" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B57" t="n">
-        <v>641.8476715248971</v>
+        <v>653.9265721002572</v>
       </c>
       <c r="C57" t="n">
-        <v>660.8387602004772</v>
+        <v>659.5321367260491</v>
       </c>
       <c r="D57" t="n">
-        <v>641.5484540168895</v>
+        <v>647.5330578779101</v>
       </c>
       <c r="E57" t="n">
-        <v>655.462646484375</v>
+        <v>647.832275390625</v>
       </c>
       <c r="F57" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B58" t="n">
-        <v>653.9265104909302</v>
+        <v>655.3429055936973</v>
       </c>
       <c r="C58" t="n">
-        <v>659.5320745885969</v>
+        <v>668.8381315618529</v>
       </c>
       <c r="D58" t="n">
-        <v>647.5329968709444</v>
+        <v>654.7743619360156</v>
       </c>
       <c r="E58" t="n">
-        <v>647.8322143554688</v>
+        <v>662.7438354492188</v>
       </c>
       <c r="F58" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B59" t="n">
-        <v>655.3429055936973</v>
+        <v>664.7087499822148</v>
       </c>
       <c r="C59" t="n">
-        <v>668.8381315618529</v>
+        <v>669.2770065062657</v>
       </c>
       <c r="D59" t="n">
-        <v>654.7743619360156</v>
+        <v>656.4899183910027</v>
       </c>
       <c r="E59" t="n">
-        <v>662.7438354492188</v>
+        <v>657.0784301757812</v>
       </c>
       <c r="F59" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B60" t="n">
-        <v>664.7087499822148</v>
+        <v>659.9510307809619</v>
       </c>
       <c r="C60" t="n">
-        <v>669.2770065062657</v>
+        <v>671.850389464676</v>
       </c>
       <c r="D60" t="n">
-        <v>656.4899183910027</v>
+        <v>654.9638698467097</v>
       </c>
       <c r="E60" t="n">
-        <v>657.0784301757812</v>
+        <v>659.8013916015625</v>
       </c>
       <c r="F60" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B61" t="n">
-        <v>659.9510918299604</v>
+        <v>658.3551466507428</v>
       </c>
       <c r="C61" t="n">
-        <v>671.8504516144289</v>
+        <v>664.2898807338869</v>
       </c>
       <c r="D61" t="n">
-        <v>654.9639304343692</v>
+        <v>656.559780770392</v>
       </c>
       <c r="E61" t="n">
-        <v>659.8014526367188</v>
+        <v>663.2326049804688</v>
       </c>
       <c r="F61" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B62" t="n">
-        <v>658.3550860644432</v>
+        <v>660.8287474650539</v>
       </c>
       <c r="C62" t="n">
-        <v>664.2898196014329</v>
+        <v>666.4642025505667</v>
       </c>
       <c r="D62" t="n">
-        <v>656.5597203493141</v>
+        <v>660.4995778116346</v>
       </c>
       <c r="E62" t="n">
-        <v>663.2325439453125</v>
+        <v>665.8358154296875</v>
       </c>
       <c r="F62" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B63" t="n">
-        <v>660.8288080412273</v>
+        <v>666.3445631389869</v>
       </c>
       <c r="C63" t="n">
-        <v>666.4642636433252</v>
+        <v>667.2322924211887</v>
       </c>
       <c r="D63" t="n">
-        <v>660.499638357634</v>
+        <v>659.6218797502219</v>
       </c>
       <c r="E63" t="n">
-        <v>665.8358764648438</v>
+        <v>661.5867919921875</v>
       </c>
       <c r="F63" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B64" t="n">
-        <v>666.3446246130748</v>
+        <v>656.3204105957403</v>
       </c>
       <c r="C64" t="n">
-        <v>667.2323539771746</v>
+        <v>658.5546491157273</v>
       </c>
       <c r="D64" t="n">
-        <v>659.6219406041037</v>
+        <v>652.7097106878265</v>
       </c>
       <c r="E64" t="n">
-        <v>661.5868530273438</v>
+        <v>656.9986572265625</v>
       </c>
       <c r="F64" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B65" t="n">
-        <v>656.3204105957403</v>
+        <v>656.9986830428769</v>
       </c>
       <c r="C65" t="n">
-        <v>658.5546491157273</v>
+        <v>670.4939103829213</v>
       </c>
       <c r="D65" t="n">
-        <v>652.7097106878265</v>
+        <v>656.1508899406441</v>
       </c>
       <c r="E65" t="n">
-        <v>656.9986572265625</v>
+        <v>664.2400512695312</v>
       </c>
       <c r="F65" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B66" t="n">
-        <v>656.9986226731097</v>
+        <v>663.0430880640301</v>
       </c>
       <c r="C66" t="n">
-        <v>670.4938487731155</v>
+        <v>663.2924461264837</v>
       </c>
       <c r="D66" t="n">
-        <v>656.1508296487782</v>
+        <v>657.7467252526537</v>
       </c>
       <c r="E66" t="n">
-        <v>664.239990234375</v>
+        <v>658.3950805664062</v>
       </c>
       <c r="F66" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B67" t="n">
-        <v>663.0430265979899</v>
+        <v>661.0282405096659</v>
       </c>
       <c r="C67" t="n">
-        <v>663.2923846373272</v>
+        <v>662.6840120988863</v>
       </c>
       <c r="D67" t="n">
-        <v>657.7466642776019</v>
+        <v>641.8476382600104</v>
       </c>
       <c r="E67" t="n">
-        <v>658.39501953125</v>
+        <v>648.7398681640625</v>
       </c>
       <c r="F67" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B68" t="n">
-        <v>661.0282405096659</v>
+        <v>649.338336889516</v>
       </c>
       <c r="C68" t="n">
-        <v>662.6840120988863</v>
+        <v>662.8335627039321</v>
       </c>
       <c r="D68" t="n">
-        <v>641.8476382600104</v>
+        <v>646.0866982239037</v>
       </c>
       <c r="E68" t="n">
-        <v>648.7398681640625</v>
+        <v>657.0983276367188</v>
       </c>
       <c r="F68" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B69" t="n">
-        <v>649.3383972038786</v>
+        <v>657.8763534012292</v>
       </c>
       <c r="C69" t="n">
-        <v>662.8336242718107</v>
+        <v>663.8110870761799</v>
       </c>
       <c r="D69" t="n">
-        <v>646.086758236235</v>
+        <v>650.2260655901538</v>
       </c>
       <c r="E69" t="n">
-        <v>657.098388671875</v>
+        <v>658.9236450195312</v>
       </c>
       <c r="F69" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B70" t="n">
-        <v>657.8763534012292</v>
+        <v>653.956457912222</v>
       </c>
       <c r="C70" t="n">
-        <v>663.8110870761799</v>
+        <v>657.4574546517152</v>
       </c>
       <c r="D70" t="n">
-        <v>650.2260655901538</v>
+        <v>643.154250211399</v>
       </c>
       <c r="E70" t="n">
-        <v>658.9236450195312</v>
+        <v>647.0242919921875</v>
       </c>
       <c r="F70" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B71" t="n">
-        <v>653.956457912222</v>
+        <v>644.2215315163064</v>
       </c>
       <c r="C71" t="n">
-        <v>657.4574546517152</v>
+        <v>645.4383696113561</v>
       </c>
       <c r="D71" t="n">
-        <v>643.154250211399</v>
+        <v>634.0875860000896</v>
       </c>
       <c r="E71" t="n">
-        <v>647.0242919921875</v>
+        <v>644.4010620117188</v>
       </c>
       <c r="F71" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B72" t="n">
-        <v>644.2215315163064</v>
+        <v>643.7826886268982</v>
       </c>
       <c r="C72" t="n">
-        <v>645.4383696113561</v>
+        <v>653.2682792823022</v>
       </c>
       <c r="D72" t="n">
-        <v>634.0875860000896</v>
+        <v>641.1993122536916</v>
       </c>
       <c r="E72" t="n">
-        <v>644.4010620117188</v>
+        <v>651.3831176757812</v>
       </c>
       <c r="F72" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B73" t="n">
-        <v>643.7826886268982</v>
+        <v>650.8544758921091</v>
       </c>
       <c r="C73" t="n">
-        <v>653.2682792823022</v>
+        <v>652.2907198459545</v>
       </c>
       <c r="D73" t="n">
-        <v>641.1993122536916</v>
+        <v>639.5834431006995</v>
       </c>
       <c r="E73" t="n">
-        <v>651.3831176757812</v>
+        <v>640.321533203125</v>
       </c>
       <c r="F73" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B74" t="n">
-        <v>650.8544758921091</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="C74" t="n">
-        <v>652.2907198459545</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="D74" t="n">
-        <v>639.5834431006995</v>
+        <v>622.4974409136</v>
       </c>
       <c r="E74" t="n">
-        <v>640.321533203125</v>
+        <v>629.4695434570312</v>
       </c>
       <c r="F74" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B75" t="n">
-        <v>640.6208286715078</v>
+        <v>624.8913007155408</v>
       </c>
       <c r="C75" t="n">
-        <v>640.6208286715078</v>
+        <v>626.836305766559</v>
       </c>
       <c r="D75" t="n">
-        <v>622.4974409136</v>
+        <v>613.2412994138377</v>
       </c>
       <c r="E75" t="n">
-        <v>629.4695434570312</v>
+        <v>613.9395141601562</v>
       </c>
       <c r="F75" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B76" t="n">
-        <v>624.8913007155408</v>
+        <v>616.8918216697934</v>
       </c>
       <c r="C76" t="n">
-        <v>626.836305766559</v>
+        <v>622.5672130846042</v>
       </c>
       <c r="D76" t="n">
-        <v>613.2412994138377</v>
+        <v>612.6527349978052</v>
       </c>
       <c r="E76" t="n">
-        <v>613.9395141601562</v>
+        <v>619.2058715820312</v>
       </c>
       <c r="F76" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B77" t="n">
-        <v>616.8918824768537</v>
+        <v>622.5772500418334</v>
       </c>
       <c r="C77" t="n">
-        <v>622.567274451088</v>
+        <v>627.4646923832119</v>
       </c>
       <c r="D77" t="n">
-        <v>612.6527953870184</v>
+        <v>618.4878021974878</v>
       </c>
       <c r="E77" t="n">
-        <v>619.2059326171875</v>
+        <v>618.6573486328125</v>
       </c>
       <c r="F77" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B78" t="n">
-        <v>622.5772500418334</v>
+        <v>606.3191417499893</v>
       </c>
       <c r="C78" t="n">
-        <v>627.4646923832119</v>
+        <v>609.8301228712422</v>
       </c>
       <c r="D78" t="n">
-        <v>618.4878021974878</v>
+        <v>598.4593704807342</v>
       </c>
       <c r="E78" t="n">
-        <v>618.6573486328125</v>
+        <v>602.5687866210938</v>
       </c>
       <c r="F78" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B79" t="n">
-        <v>606.3191417499893</v>
+        <v>605.1820479992876</v>
       </c>
       <c r="C79" t="n">
-        <v>609.8301228712422</v>
+        <v>616.6824713366042</v>
       </c>
       <c r="D79" t="n">
-        <v>598.4593704807342</v>
+        <v>598.5391758430108</v>
       </c>
       <c r="E79" t="n">
-        <v>602.5687866210938</v>
+        <v>611.3861083984375</v>
       </c>
       <c r="F79" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B80" t="n">
-        <v>605.1820479992876</v>
+        <v>627.7339506004921</v>
       </c>
       <c r="C80" t="n">
-        <v>616.6824713366042</v>
+        <v>658.8738165275513</v>
       </c>
       <c r="D80" t="n">
-        <v>598.5391758430108</v>
+        <v>624.9411525277235</v>
       </c>
       <c r="E80" t="n">
-        <v>611.3861083984375</v>
+        <v>645.967041015625</v>
       </c>
       <c r="F80" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B81" t="n">
-        <v>627.7339506004921</v>
+        <v>643.114354212172</v>
       </c>
       <c r="C81" t="n">
-        <v>658.8738165275513</v>
+        <v>664.7785515369834</v>
       </c>
       <c r="D81" t="n">
-        <v>624.9411525277235</v>
+        <v>642.7951686151001</v>
       </c>
       <c r="E81" t="n">
-        <v>645.967041015625</v>
+        <v>657.0684204101562</v>
       </c>
       <c r="F81" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B82" t="n">
-        <v>643.1144139511335</v>
+        <v>663.4220687284304</v>
       </c>
       <c r="C82" t="n">
-        <v>664.7786132883346</v>
+        <v>673.5460296758964</v>
       </c>
       <c r="D82" t="n">
-        <v>642.7952283244125</v>
+        <v>659.5919023824141</v>
       </c>
       <c r="E82" t="n">
-        <v>657.0684814453125</v>
+        <v>670.6334838867188</v>
       </c>
       <c r="F82" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B83" t="n">
-        <v>663.4220687284304</v>
+        <v>672.8577784094987</v>
       </c>
       <c r="C83" t="n">
-        <v>673.5460296758964</v>
+        <v>675.082032614818</v>
       </c>
       <c r="D83" t="n">
-        <v>659.5919023824141</v>
+        <v>662.9532236229811</v>
       </c>
       <c r="E83" t="n">
-        <v>670.6334838867188</v>
+        <v>671.2418823242188</v>
       </c>
       <c r="F83" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B84" t="n">
-        <v>672.8578395915863</v>
+        <v>672.768020673078</v>
       </c>
       <c r="C84" t="n">
-        <v>675.0820939991542</v>
+        <v>675.9398477720257</v>
       </c>
       <c r="D84" t="n">
-        <v>662.9532839044604</v>
+        <v>664.3895658196245</v>
       </c>
       <c r="E84" t="n">
-        <v>671.241943359375</v>
+        <v>667.0128173828125</v>
       </c>
       <c r="F84" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B85" t="n">
-        <v>672.7679591112906</v>
+        <v>735.536439340887</v>
       </c>
       <c r="C85" t="n">
-        <v>675.9397859199995</v>
+        <v>742.0895763731422</v>
       </c>
       <c r="D85" t="n">
-        <v>664.3895050245095</v>
+        <v>710.7203206800697</v>
       </c>
       <c r="E85" t="n">
-        <v>667.0127563476562</v>
+        <v>736.4141845703125</v>
       </c>
       <c r="F85" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B86" t="n">
-        <v>735.536439340887</v>
+        <v>725.6319721911391</v>
       </c>
       <c r="C86" t="n">
-        <v>742.0895763731422</v>
+        <v>730.2899638188994</v>
       </c>
       <c r="D86" t="n">
-        <v>710.7203206800697</v>
+        <v>711.7577161829028</v>
       </c>
       <c r="E86" t="n">
-        <v>736.4141845703125</v>
+        <v>714.6602172851562</v>
       </c>
       <c r="F86" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B87" t="n">
-        <v>725.6319102189462</v>
+        <v>712.7650416713351</v>
       </c>
       <c r="C87" t="n">
-        <v>730.2899014488934</v>
+        <v>719.4478497361232</v>
       </c>
       <c r="D87" t="n">
-        <v>711.7576553956329</v>
+        <v>701.7135364812315</v>
       </c>
       <c r="E87" t="n">
-        <v>714.66015625</v>
+        <v>704.5960693359375</v>
       </c>
       <c r="F87" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B88" t="n">
-        <v>712.7649799285471</v>
+        <v>705.5536352374374</v>
       </c>
       <c r="C88" t="n">
-        <v>719.4477874144414</v>
+        <v>715.1589125312489</v>
       </c>
       <c r="D88" t="n">
-        <v>701.7134756957726</v>
+        <v>684.6474336745422</v>
       </c>
       <c r="E88" t="n">
-        <v>704.5960083007812</v>
+        <v>689.9238891601562</v>
       </c>
       <c r="F88" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B89" t="n">
-        <v>705.5535728195721</v>
+        <v>685.964025393825</v>
       </c>
       <c r="C89" t="n">
-        <v>715.1588492636382</v>
+        <v>687.0612373376343</v>
       </c>
       <c r="D89" t="n">
-        <v>684.6473731061755</v>
+        <v>665.7461161570209</v>
       </c>
       <c r="E89" t="n">
-        <v>689.923828125</v>
+        <v>667.2721557617188</v>
       </c>
       <c r="F89" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B90" t="n">
-        <v>685.9640881387202</v>
+        <v>661.8760941724082</v>
       </c>
       <c r="C90" t="n">
-        <v>687.0613001828912</v>
+        <v>679.7500626324993</v>
       </c>
       <c r="D90" t="n">
-        <v>665.7461770525908</v>
+        <v>651.8219602792932</v>
       </c>
       <c r="E90" t="n">
-        <v>667.272216796875</v>
+        <v>668.4890747070312</v>
       </c>
       <c r="F90" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B91" t="n">
-        <v>661.8760941724082</v>
+        <v>663.781217226052</v>
       </c>
       <c r="C91" t="n">
-        <v>679.7500626324993</v>
+        <v>670.2645272311354</v>
       </c>
       <c r="D91" t="n">
-        <v>651.8219602792932</v>
+        <v>644.8399874286738</v>
       </c>
       <c r="E91" t="n">
-        <v>668.4890747070312</v>
+        <v>659.7615966796875</v>
       </c>
       <c r="F91" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B92" t="n">
-        <v>663.7811558190369</v>
+        <v>661.4770916291903</v>
       </c>
       <c r="C92" t="n">
-        <v>670.2644652243433</v>
+        <v>681.5554070660584</v>
       </c>
       <c r="D92" t="n">
-        <v>644.8399277739295</v>
+        <v>657.0884263930592</v>
       </c>
       <c r="E92" t="n">
-        <v>659.7615356445312</v>
+        <v>675.4810180664062</v>
       </c>
       <c r="F92" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B93" t="n">
-        <v>661.4770916291903</v>
+        <v>675.8600189134125</v>
       </c>
       <c r="C93" t="n">
-        <v>681.5554070660584</v>
+        <v>678.9022357565889</v>
       </c>
       <c r="D93" t="n">
-        <v>657.0884263930592</v>
+        <v>668.0700760446862</v>
       </c>
       <c r="E93" t="n">
-        <v>675.4810180664062</v>
+        <v>668.9976806640625</v>
       </c>
       <c r="F93" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B94" t="n">
-        <v>675.8600189134125</v>
+        <v>672.2693241407737</v>
       </c>
       <c r="C94" t="n">
-        <v>678.9022357565889</v>
+        <v>677.5258114827353</v>
       </c>
       <c r="D94" t="n">
-        <v>668.0700760446862</v>
+        <v>655.4126950742984</v>
       </c>
       <c r="E94" t="n">
-        <v>668.9976806640625</v>
+        <v>666.9729614257812</v>
       </c>
       <c r="F94" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B95" t="n">
-        <v>672.2693241407737</v>
+        <v>668.2496878446467</v>
       </c>
       <c r="C95" t="n">
-        <v>677.5258114827353</v>
+        <v>674.2642338266133</v>
       </c>
       <c r="D95" t="n">
-        <v>655.4126950742984</v>
+        <v>643.6231428364971</v>
       </c>
       <c r="E95" t="n">
-        <v>666.9729614257812</v>
+        <v>648.1414794921875</v>
       </c>
       <c r="F95" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B96" t="n">
-        <v>668.2496249159107</v>
+        <v>643.4434668857905</v>
       </c>
       <c r="C96" t="n">
-        <v>674.2641703314905</v>
+        <v>649.7572295518577</v>
       </c>
       <c r="D96" t="n">
-        <v>643.6230822268304</v>
+        <v>632.9405378190771</v>
       </c>
       <c r="E96" t="n">
-        <v>648.1414184570312</v>
+        <v>638.127197265625</v>
       </c>
       <c r="F96" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B97" t="n">
-        <v>643.4434668857905</v>
+        <v>637.8578591323172</v>
       </c>
       <c r="C97" t="n">
-        <v>649.7572295518577</v>
+        <v>640.9498744421038</v>
       </c>
       <c r="D97" t="n">
-        <v>632.9405378190771</v>
+        <v>627.1853229648948</v>
       </c>
       <c r="E97" t="n">
-        <v>638.127197265625</v>
+        <v>637.6483764648438</v>
       </c>
       <c r="F97" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B98" t="n">
-        <v>637.8579201875249</v>
+        <v>632.1725643806327</v>
       </c>
       <c r="C98" t="n">
-        <v>640.9499357932766</v>
+        <v>643.3438180480059</v>
       </c>
       <c r="D98" t="n">
-        <v>627.1853829985365</v>
+        <v>626.5371085480483</v>
       </c>
       <c r="E98" t="n">
-        <v>637.6484375</v>
+        <v>641.568359375</v>
       </c>
       <c r="F98" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B99" t="n">
-        <v>632.1725042393389</v>
+        <v>636.9302530675583</v>
       </c>
       <c r="C99" t="n">
-        <v>643.3437568439427</v>
+        <v>645.5281132997313</v>
       </c>
       <c r="D99" t="n">
-        <v>626.5370489428796</v>
+        <v>635.0849670695593</v>
       </c>
       <c r="E99" t="n">
-        <v>641.5682983398438</v>
+        <v>643.1243286132812</v>
       </c>
       <c r="F99" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B100" t="n">
-        <v>636.9302530675583</v>
+        <v>638.0474161403351</v>
       </c>
       <c r="C100" t="n">
-        <v>645.5281132997313</v>
+        <v>661.6466355641227</v>
       </c>
       <c r="D100" t="n">
-        <v>635.0849670695593</v>
+        <v>637.1397796110642</v>
       </c>
       <c r="E100" t="n">
-        <v>643.1243286132812</v>
+        <v>653.9763793945312</v>
       </c>
       <c r="F100" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B101" t="n">
-        <v>638.0474756888525</v>
+        <v>650.8644258547187</v>
       </c>
       <c r="C101" t="n">
-        <v>661.6466973151385</v>
+        <v>656.0112104148094</v>
       </c>
       <c r="D101" t="n">
-        <v>637.1398390748724</v>
+        <v>634.3669181695027</v>
       </c>
       <c r="E101" t="n">
-        <v>653.9764404296875</v>
+        <v>635.6137084960938</v>
       </c>
       <c r="F101" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B102" t="n">
-        <v>650.8644258547187</v>
+        <v>631.4543872367445</v>
       </c>
       <c r="C102" t="n">
-        <v>656.0112104148094</v>
+        <v>639.4637360573605</v>
       </c>
       <c r="D102" t="n">
-        <v>634.3669181695027</v>
+        <v>627.364878734925</v>
       </c>
       <c r="E102" t="n">
-        <v>635.6137084960938</v>
+        <v>637.6583862304688</v>
       </c>
       <c r="F102" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B103" t="n">
-        <v>631.4544476780686</v>
+        <v>640.8800977544264</v>
       </c>
       <c r="C103" t="n">
-        <v>639.4637972653206</v>
+        <v>652.2009281146602</v>
       </c>
       <c r="D103" t="n">
-        <v>627.364938784811</v>
+        <v>640.4910846116635</v>
       </c>
       <c r="E103" t="n">
-        <v>637.658447265625</v>
+        <v>652.0114135742188</v>
       </c>
       <c r="F103" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B104" t="n">
-        <v>640.8800977544264</v>
+        <v>648.8795031075816</v>
       </c>
       <c r="C104" t="n">
-        <v>652.2009281146602</v>
+        <v>659.3026817342861</v>
       </c>
       <c r="D104" t="n">
-        <v>640.4910846116635</v>
+        <v>645.837347084645</v>
       </c>
       <c r="E104" t="n">
-        <v>652.0114135742188</v>
+        <v>655.3229370117188</v>
       </c>
       <c r="F104" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B105" t="n">
-        <v>648.8795635426123</v>
+        <v>641.7978505538991</v>
       </c>
       <c r="C105" t="n">
-        <v>659.3027431401059</v>
+        <v>647.7724605225501</v>
       </c>
       <c r="D105" t="n">
-        <v>645.8374072363367</v>
+        <v>636.4815191423199</v>
       </c>
       <c r="E105" t="n">
-        <v>655.322998046875</v>
+        <v>646.5156860351562</v>
       </c>
       <c r="F105" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B106" t="n">
-        <v>641.7977293743734</v>
+        <v>635.5238627543893</v>
       </c>
       <c r="C106" t="n">
-        <v>647.7723382149427</v>
+        <v>658.2453970983619</v>
       </c>
       <c r="D106" t="n">
-        <v>636.4813989665846</v>
+        <v>632.870719934867</v>
       </c>
       <c r="E106" t="n">
-        <v>646.5155639648438</v>
+        <v>651.8817749023438</v>
       </c>
       <c r="F106" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B107" t="n">
-        <v>635.5238627543893</v>
+        <v>646.6252847330551</v>
       </c>
       <c r="C107" t="n">
-        <v>658.2453970983619</v>
+        <v>657.3476806461185</v>
       </c>
       <c r="D107" t="n">
-        <v>632.870719934867</v>
+        <v>637.199599354082</v>
       </c>
       <c r="E107" t="n">
-        <v>651.8817749023438</v>
+        <v>653.3978881835938</v>
       </c>
       <c r="F107" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B108" t="n">
-        <v>646.6252847330551</v>
+        <v>656.2705698423595</v>
       </c>
       <c r="C108" t="n">
-        <v>657.3476806461185</v>
+        <v>671.0425395860565</v>
       </c>
       <c r="D108" t="n">
-        <v>637.199599354082</v>
+        <v>655.981275516767</v>
       </c>
       <c r="E108" t="n">
-        <v>653.3978881835938</v>
+        <v>666.0154418945312</v>
       </c>
       <c r="F108" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B109" t="n">
-        <v>656.2705097002453</v>
+        <v>660.2302724443645</v>
       </c>
       <c r="C109" t="n">
-        <v>671.0424780902056</v>
+        <v>668.9777721022258</v>
       </c>
       <c r="D109" t="n">
-        <v>655.9812154011644</v>
+        <v>648.6401154384699</v>
       </c>
       <c r="E109" t="n">
-        <v>666.015380859375</v>
+        <v>658.873779296875</v>
       </c>
       <c r="F109" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B110" t="n">
-        <v>660.2303336051802</v>
+        <v>646.2363343546218</v>
       </c>
       <c r="C110" t="n">
-        <v>668.9778340733714</v>
+        <v>647.8022493056128</v>
       </c>
       <c r="D110" t="n">
-        <v>648.6401755256248</v>
+        <v>634.4765699796501</v>
       </c>
       <c r="E110" t="n">
-        <v>658.8738403320312</v>
+        <v>643.2041015625</v>
       </c>
       <c r="F110" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B111" t="n">
-        <v>646.2363343546218</v>
+        <v>633.1501152642575</v>
       </c>
       <c r="C111" t="n">
-        <v>647.8022493056128</v>
+        <v>646.0867831911829</v>
       </c>
       <c r="D111" t="n">
-        <v>634.4765699796501</v>
+        <v>625.1706567300553</v>
       </c>
       <c r="E111" t="n">
-        <v>643.2041015625</v>
+        <v>645.7277221679688</v>
       </c>
       <c r="F111" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B112" t="n">
-        <v>633.1500554179556</v>
+        <v>651.8817417666538</v>
       </c>
       <c r="C112" t="n">
-        <v>646.0867221220876</v>
+        <v>658.6044245959081</v>
       </c>
       <c r="D112" t="n">
-        <v>625.1705976379839</v>
+        <v>647.333453679788</v>
       </c>
       <c r="E112" t="n">
-        <v>645.7276611328125</v>
+        <v>652.3904418945312</v>
       </c>
       <c r="F112" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B113" t="n">
-        <v>651.8818637417822</v>
+        <v>653.0787479235273</v>
       </c>
       <c r="C113" t="n">
-        <v>658.6045478289335</v>
+        <v>657.4275379105374</v>
       </c>
       <c r="D113" t="n">
-        <v>647.3335748038755</v>
+        <v>646.6951571900124</v>
       </c>
       <c r="E113" t="n">
-        <v>652.3905639648438</v>
+        <v>653.178466796875</v>
       </c>
       <c r="F113" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B114" t="n">
-        <v>653.0787479235273</v>
+        <v>647.0841872338415</v>
       </c>
       <c r="C114" t="n">
-        <v>657.4275379105374</v>
+        <v>651.8219905315074</v>
       </c>
       <c r="D114" t="n">
-        <v>646.6951571900124</v>
+        <v>635.2646391478804</v>
       </c>
       <c r="E114" t="n">
-        <v>653.178466796875</v>
+        <v>636.5413208007812</v>
       </c>
       <c r="F114" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B115" t="n">
-        <v>647.0841872338415</v>
+        <v>622.2880080608647</v>
       </c>
       <c r="C115" t="n">
-        <v>651.8219905315074</v>
+        <v>627.55441857404</v>
       </c>
       <c r="D115" t="n">
-        <v>635.2646391478804</v>
+        <v>607.9848031082139</v>
       </c>
       <c r="E115" t="n">
-        <v>636.5413208007812</v>
+        <v>612.1341552734375</v>
       </c>
       <c r="F115" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,25 +3433,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B116" t="n">
-        <v>622.2879460132801</v>
+        <v>630.9168848948667</v>
       </c>
       <c r="C116" t="n">
-        <v>627.554356001348</v>
+        <v>633.6621719731276</v>
       </c>
       <c r="D116" t="n">
-        <v>607.9847424867846</v>
+        <v>622.0321132511823</v>
       </c>
       <c r="E116" t="n">
-        <v>612.1340942382812</v>
+        <v>626.3746948242188</v>
       </c>
       <c r="F116" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3459,25 +3459,25 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B117" t="n">
-        <v>630.9168848948667</v>
+        <v>626.9137167736849</v>
       </c>
       <c r="C117" t="n">
-        <v>633.6621719731276</v>
+        <v>635.4590438783874</v>
       </c>
       <c r="D117" t="n">
-        <v>622.0321132511823</v>
+        <v>620.6345187532272</v>
       </c>
       <c r="E117" t="n">
-        <v>626.3746948242188</v>
+        <v>621.5928344726562</v>
       </c>
       <c r="F117" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G117" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B118" t="n">
-        <v>626.9137783313067</v>
+        <v>615.2837198825454</v>
       </c>
       <c r="C118" t="n">
-        <v>635.4591062750881</v>
+        <v>621.5829031274002</v>
       </c>
       <c r="D118" t="n">
-        <v>620.634579694285</v>
+        <v>613.5566433895493</v>
       </c>
       <c r="E118" t="n">
-        <v>621.5928955078125</v>
+        <v>614.6248168945312</v>
       </c>
       <c r="F118" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B119" t="n">
-        <v>615.2837809831337</v>
+        <v>611.1008889698486</v>
       </c>
       <c r="C119" t="n">
-        <v>621.5829648535273</v>
+        <v>611.9494078221777</v>
       </c>
       <c r="D119" t="n">
-        <v>613.5567043186309</v>
+        <v>601.2278243573462</v>
       </c>
       <c r="E119" t="n">
-        <v>614.6248779296875</v>
+        <v>605.6602172851562</v>
       </c>
       <c r="F119" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B120" t="n">
-        <v>611.1009505532863</v>
+        <v>602.4957192983555</v>
       </c>
       <c r="C120" t="n">
-        <v>611.9494694911245</v>
+        <v>602.9249750667714</v>
       </c>
       <c r="D120" t="n">
-        <v>601.2278849458298</v>
+        <v>586.2435901825164</v>
       </c>
       <c r="E120" t="n">
-        <v>605.6602783203125</v>
+        <v>592.642578125</v>
       </c>
       <c r="F120" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B121" t="n">
-        <v>602.4957192983555</v>
+        <v>604.7517959610541</v>
       </c>
       <c r="C121" t="n">
-        <v>602.9249750667714</v>
+        <v>607.5969482872343</v>
       </c>
       <c r="D121" t="n">
-        <v>586.2435901825164</v>
+        <v>597.9834469761715</v>
       </c>
       <c r="E121" t="n">
-        <v>592.642578125</v>
+        <v>603.0247802734375</v>
       </c>
       <c r="F121" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B122" t="n">
-        <v>604.7517959610541</v>
+        <v>598.0732713770465</v>
       </c>
       <c r="C122" t="n">
-        <v>607.5969482872343</v>
+        <v>599.9700396349708</v>
       </c>
       <c r="D122" t="n">
-        <v>597.9834469761715</v>
+        <v>589.9871770786485</v>
       </c>
       <c r="E122" t="n">
-        <v>603.0247802734375</v>
+        <v>591.9038696289062</v>
       </c>
       <c r="F122" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B123" t="n">
-        <v>598.0732713770465</v>
+        <v>597.7138608396341</v>
       </c>
       <c r="C123" t="n">
-        <v>599.9700396349708</v>
+        <v>602.6354044215132</v>
       </c>
       <c r="D123" t="n">
-        <v>589.9871770786485</v>
+        <v>592.3830467312241</v>
       </c>
       <c r="E123" t="n">
-        <v>591.9038696289062</v>
+        <v>593.8704833984375</v>
       </c>
       <c r="F123" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B124" t="n">
-        <v>597.7138608396341</v>
+        <v>581.4917396573854</v>
       </c>
       <c r="C124" t="n">
-        <v>602.6354044215132</v>
+        <v>582.0008753864581</v>
       </c>
       <c r="D124" t="n">
-        <v>592.3830467312241</v>
+        <v>542.4188017705425</v>
       </c>
       <c r="E124" t="n">
-        <v>593.8704833984375</v>
+        <v>546.6016235351562</v>
       </c>
       <c r="F124" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B125" t="n">
-        <v>581.4916747262954</v>
+        <v>539.1743922574078</v>
       </c>
       <c r="C125" t="n">
-        <v>582.0008103985165</v>
+        <v>542.6683942166816</v>
       </c>
       <c r="D125" t="n">
-        <v>542.4187412024525</v>
+        <v>519.3684267008094</v>
       </c>
       <c r="E125" t="n">
-        <v>546.6015625</v>
+        <v>524.8190307617188</v>
       </c>
       <c r="F125" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B126" t="n">
-        <v>539.1743295527585</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="C126" t="n">
-        <v>542.6683311056884</v>
+        <v>538.6253045735799</v>
       </c>
       <c r="D126" t="n">
-        <v>519.368366299545</v>
+        <v>527.6341638126921</v>
       </c>
       <c r="E126" t="n">
-        <v>524.8189697265625</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="F126" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B127" t="n">
-        <v>535.4607543945312</v>
+        <v>549.0374119135495</v>
       </c>
       <c r="C127" t="n">
-        <v>538.6253045735799</v>
+        <v>572.7067990959439</v>
       </c>
       <c r="D127" t="n">
-        <v>527.6341638126921</v>
+        <v>545.8329522821889</v>
       </c>
       <c r="E127" t="n">
-        <v>535.4607543945312</v>
+        <v>571.1494750976562</v>
       </c>
       <c r="F127" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B128" t="n">
-        <v>549.0374119135495</v>
+        <v>579.135725523027</v>
       </c>
       <c r="C128" t="n">
-        <v>572.7067990959439</v>
+        <v>591.5344219412718</v>
       </c>
       <c r="D128" t="n">
-        <v>545.8329522821889</v>
+        <v>572.8365426099092</v>
       </c>
       <c r="E128" t="n">
-        <v>571.1494750976562</v>
+        <v>578.2372436523438</v>
       </c>
       <c r="F128" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B129" t="n">
-        <v>579.1357866530213</v>
+        <v>565.0699110449033</v>
       </c>
       <c r="C129" t="n">
-        <v>591.5344843799961</v>
+        <v>577.5085793033603</v>
       </c>
       <c r="D129" t="n">
-        <v>572.8366030750008</v>
+        <v>558.7408105198895</v>
       </c>
       <c r="E129" t="n">
-        <v>578.2373046875</v>
+        <v>573.4755249023438</v>
       </c>
       <c r="F129" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B130" t="n">
-        <v>565.0699110449033</v>
+        <v>576.7000047794845</v>
       </c>
       <c r="C130" t="n">
-        <v>577.5085793033603</v>
+        <v>581.7912404462878</v>
       </c>
       <c r="D130" t="n">
-        <v>558.7408105198895</v>
+        <v>571.0197533967594</v>
       </c>
       <c r="E130" t="n">
-        <v>573.4755249023438</v>
+        <v>572.0380249023438</v>
       </c>
       <c r="F130" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B131" t="n">
-        <v>576.6999432469056</v>
+        <v>571.4988503418972</v>
       </c>
       <c r="C131" t="n">
-        <v>581.7911783704857</v>
+        <v>574.2441373249518</v>
       </c>
       <c r="D131" t="n">
-        <v>571.0196924702504</v>
+        <v>563.7921103124964</v>
       </c>
       <c r="E131" t="n">
-        <v>572.0379638671875</v>
+        <v>574.064453125</v>
       </c>
       <c r="F131" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B132" t="n">
-        <v>571.4988503418972</v>
+        <v>604.9614419693103</v>
       </c>
       <c r="C132" t="n">
-        <v>574.2441373249518</v>
+        <v>628.8704088339113</v>
       </c>
       <c r="D132" t="n">
-        <v>563.7921103124964</v>
+        <v>590.8157434643455</v>
       </c>
       <c r="E132" t="n">
-        <v>574.064453125</v>
+        <v>611.3704223632812</v>
       </c>
       <c r="F132" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B133" t="n">
-        <v>604.9614419693103</v>
+        <v>625.8954391113879</v>
       </c>
       <c r="C133" t="n">
-        <v>628.8704088339113</v>
+        <v>636.4074215325429</v>
       </c>
       <c r="D133" t="n">
-        <v>590.8157434643455</v>
+        <v>621.9322723369008</v>
       </c>
       <c r="E133" t="n">
-        <v>611.3704223632812</v>
+        <v>627.3130493164062</v>
       </c>
       <c r="F133" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B134" t="n">
-        <v>625.8955000086161</v>
+        <v>633.3826022362973</v>
       </c>
       <c r="C134" t="n">
-        <v>636.4074834525468</v>
+        <v>637.4856047359222</v>
       </c>
       <c r="D134" t="n">
-        <v>621.9323328485281</v>
+        <v>623.2600266965629</v>
       </c>
       <c r="E134" t="n">
-        <v>627.3131103515625</v>
+        <v>628.780517578125</v>
       </c>
       <c r="F134" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B135" t="n">
-        <v>633.3826022362973</v>
+        <v>628.4211571313969</v>
       </c>
       <c r="C135" t="n">
-        <v>637.4856047359222</v>
+        <v>633.911731180996</v>
       </c>
       <c r="D135" t="n">
-        <v>623.2600266965629</v>
+        <v>623.3299219303536</v>
       </c>
       <c r="E135" t="n">
-        <v>628.780517578125</v>
+        <v>633.4425659179688</v>
       </c>
       <c r="F135" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B136" t="n">
-        <v>628.4212176827168</v>
+        <v>642.117619704398</v>
       </c>
       <c r="C136" t="n">
-        <v>633.9117922613585</v>
+        <v>665.1181727259973</v>
       </c>
       <c r="D136" t="n">
-        <v>623.3299819911093</v>
+        <v>638.2742422102883</v>
       </c>
       <c r="E136" t="n">
-        <v>633.442626953125</v>
+        <v>661.3546142578125</v>
       </c>
       <c r="F136" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B137" t="n">
-        <v>642.117619704398</v>
+        <v>665.856909197143</v>
       </c>
       <c r="C137" t="n">
-        <v>665.1181727259973</v>
+        <v>677.3372007350248</v>
       </c>
       <c r="D137" t="n">
-        <v>638.2742422102883</v>
+        <v>663.081644256971</v>
       </c>
       <c r="E137" t="n">
-        <v>661.3546142578125</v>
+        <v>670.4290771484375</v>
       </c>
       <c r="F137" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B138" t="n">
-        <v>665.856909197143</v>
+        <v>674.831464225754</v>
       </c>
       <c r="C138" t="n">
-        <v>677.3372007350248</v>
+        <v>676.4187660594131</v>
       </c>
       <c r="D138" t="n">
-        <v>663.081644256971</v>
+        <v>666.605595861725</v>
       </c>
       <c r="E138" t="n">
-        <v>670.4290771484375</v>
+        <v>675.7099609375</v>
       </c>
       <c r="F138" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B139" t="n">
-        <v>674.831464225754</v>
+        <v>677.4369744478516</v>
       </c>
       <c r="C139" t="n">
-        <v>676.4187660594131</v>
+        <v>690.3348757077041</v>
       </c>
       <c r="D139" t="n">
-        <v>666.605595861725</v>
+        <v>673.9729506648888</v>
       </c>
       <c r="E139" t="n">
-        <v>675.7099609375</v>
+        <v>687.3699340820312</v>
       </c>
       <c r="F139" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B140" t="n">
-        <v>677.4369744478516</v>
+        <v>680.192296240317</v>
       </c>
       <c r="C140" t="n">
-        <v>690.3348757077041</v>
+        <v>682.2088539380842</v>
       </c>
       <c r="D140" t="n">
-        <v>673.9729506648888</v>
+        <v>666.8552067290691</v>
       </c>
       <c r="E140" t="n">
-        <v>687.3699340820312</v>
+        <v>669.7601928710938</v>
       </c>
       <c r="F140" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B141" t="n">
-        <v>680.192296240317</v>
+        <v>669.8500580611455</v>
       </c>
       <c r="C141" t="n">
-        <v>682.2088539380842</v>
+        <v>675.0411586256739</v>
       </c>
       <c r="D141" t="n">
-        <v>666.8552067290691</v>
+        <v>666.1863646700106</v>
       </c>
       <c r="E141" t="n">
-        <v>669.7601928710938</v>
+        <v>667.6937866210938</v>
       </c>
       <c r="F141" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B142" t="n">
-        <v>669.8500580611455</v>
+        <v>673.2042912464699</v>
       </c>
       <c r="C142" t="n">
-        <v>675.0411586256739</v>
+        <v>677.2174214115423</v>
       </c>
       <c r="D142" t="n">
-        <v>666.1863646700106</v>
+        <v>668.6022063234784</v>
       </c>
       <c r="E142" t="n">
-        <v>667.6937866210938</v>
+        <v>673.5636596679688</v>
       </c>
       <c r="F142" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B143" t="n">
-        <v>673.2042912464699</v>
+        <v>662.562575853328</v>
       </c>
       <c r="C143" t="n">
-        <v>677.2174214115423</v>
+        <v>668.4125184743669</v>
       </c>
       <c r="D143" t="n">
-        <v>668.6022063234784</v>
+        <v>651.9308032468797</v>
       </c>
       <c r="E143" t="n">
-        <v>673.5636596679688</v>
+        <v>658.0203857421875</v>
       </c>
       <c r="F143" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B144" t="n">
-        <v>662.562575853328</v>
+        <v>659.1883568751083</v>
       </c>
       <c r="C144" t="n">
-        <v>668.4125184743669</v>
+        <v>679.5034568571632</v>
       </c>
       <c r="D144" t="n">
-        <v>651.9308032468797</v>
+        <v>652.719481738207</v>
       </c>
       <c r="E144" t="n">
-        <v>658.0203857421875</v>
+        <v>673.8731689453125</v>
       </c>
       <c r="F144" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B145" t="n">
-        <v>659.1883568751083</v>
+        <v>669.8500343121515</v>
       </c>
       <c r="C145" t="n">
-        <v>679.5034568571632</v>
+        <v>681.330325511242</v>
       </c>
       <c r="D145" t="n">
-        <v>652.719481738207</v>
+        <v>669.6903353309991</v>
       </c>
       <c r="E145" t="n">
-        <v>673.8731689453125</v>
+        <v>677.4569702148438</v>
       </c>
       <c r="F145" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B146" t="n">
-        <v>669.8500343121515</v>
+        <v>673.0844464119266</v>
       </c>
       <c r="C146" t="n">
-        <v>681.330325511242</v>
+        <v>677.0176962940845</v>
       </c>
       <c r="D146" t="n">
-        <v>669.6903353309991</v>
+        <v>664.489217253305</v>
       </c>
       <c r="E146" t="n">
-        <v>677.4569702148438</v>
+        <v>670.189453125</v>
       </c>
       <c r="F146" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B147" t="n">
-        <v>673.0844464119266</v>
+        <v>667.7636045616339</v>
       </c>
       <c r="C147" t="n">
-        <v>677.0176962940845</v>
+        <v>673.0944797535534</v>
       </c>
       <c r="D147" t="n">
-        <v>664.489217253305</v>
+        <v>662.6723692427279</v>
       </c>
       <c r="E147" t="n">
-        <v>670.189453125</v>
+        <v>667.9732666015625</v>
       </c>
       <c r="F147" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B148" t="n">
-        <v>667.7636045616339</v>
+        <v>618.2586017744245</v>
       </c>
       <c r="C148" t="n">
-        <v>673.0944797535534</v>
+        <v>619.7859479396749</v>
       </c>
       <c r="D148" t="n">
-        <v>662.6723692427279</v>
+        <v>598.9717055442339</v>
       </c>
       <c r="E148" t="n">
-        <v>667.9732666015625</v>
+        <v>610.8612670898438</v>
       </c>
       <c r="F148" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B149" t="n">
-        <v>618.2586017744245</v>
+        <v>613.6365485572411</v>
       </c>
       <c r="C149" t="n">
-        <v>619.7859479396749</v>
+        <v>617.8193701850194</v>
       </c>
       <c r="D149" t="n">
-        <v>598.9717055442339</v>
+        <v>605.0712358749745</v>
       </c>
       <c r="E149" t="n">
-        <v>610.8612670898438</v>
+        <v>607.7067260742188</v>
       </c>
       <c r="F149" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B150" t="n">
-        <v>613.6365485572411</v>
+        <v>606.8981537761392</v>
       </c>
       <c r="C150" t="n">
-        <v>617.8193701850194</v>
+        <v>612.9477660987843</v>
       </c>
       <c r="D150" t="n">
-        <v>605.0712358749745</v>
+        <v>601.7170456287333</v>
       </c>
       <c r="E150" t="n">
-        <v>607.7067260742188</v>
+        <v>609.3638916015625</v>
       </c>
       <c r="F150" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="n">
-        <v>606.8981537761392</v>
+        <v>612.2588828439087</v>
       </c>
       <c r="C151" t="n">
-        <v>612.9477660987843</v>
+        <v>613.2970785161436</v>
       </c>
       <c r="D151" t="n">
-        <v>601.7170456287333</v>
+        <v>599.3310648754198</v>
       </c>
       <c r="E151" t="n">
-        <v>609.3638916015625</v>
+        <v>603.9232177734375</v>
       </c>
       <c r="F151" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B152" t="n">
-        <v>612.2588828439087</v>
+        <v>600.0199080772063</v>
       </c>
       <c r="C152" t="n">
-        <v>613.2970785161436</v>
+        <v>618.8875416216711</v>
       </c>
       <c r="D152" t="n">
-        <v>599.3310648754198</v>
+        <v>597.0749516023062</v>
       </c>
       <c r="E152" t="n">
-        <v>603.9232177734375</v>
+        <v>611.8296508789062</v>
       </c>
       <c r="F152" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B153" t="n">
-        <v>600.0199080772063</v>
+        <v>613.6664846485507</v>
       </c>
       <c r="C153" t="n">
-        <v>618.8875416216711</v>
+        <v>623.9089111604618</v>
       </c>
       <c r="D153" t="n">
-        <v>597.0749516023062</v>
+        <v>612.4885142038465</v>
       </c>
       <c r="E153" t="n">
-        <v>611.8296508789062</v>
+        <v>615.7529296875</v>
       </c>
       <c r="F153" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B154" t="n">
-        <v>613.6664238202088</v>
+        <v>614.145727971313</v>
       </c>
       <c r="C154" t="n">
-        <v>623.9088493168618</v>
+        <v>615.7130447332122</v>
       </c>
       <c r="D154" t="n">
-        <v>612.4884534922683</v>
+        <v>605.0213768033159</v>
       </c>
       <c r="E154" t="n">
-        <v>615.7528686523438</v>
+        <v>608.5852661132812</v>
       </c>
       <c r="F154" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B155" t="n">
-        <v>614.1456663784968</v>
+        <v>603.533915527778</v>
       </c>
       <c r="C155" t="n">
-        <v>615.7129829832094</v>
+        <v>603.8732987260729</v>
       </c>
       <c r="D155" t="n">
-        <v>605.0213161255829</v>
+        <v>597.0550476209405</v>
       </c>
       <c r="E155" t="n">
-        <v>608.585205078125</v>
+        <v>597.8336791992188</v>
       </c>
       <c r="F155" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B156" t="n">
-        <v>603.533915527778</v>
+        <v>593.8005792809215</v>
       </c>
       <c r="C156" t="n">
-        <v>603.8732987260729</v>
+        <v>602.7152673522038</v>
       </c>
       <c r="D156" t="n">
-        <v>597.0550476209405</v>
+        <v>591.5843523282613</v>
       </c>
       <c r="E156" t="n">
-        <v>597.8336791992188</v>
+        <v>601.966552734375</v>
       </c>
       <c r="F156" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B157" t="n">
-        <v>593.8006394881057</v>
+        <v>597.8037594995824</v>
       </c>
       <c r="C157" t="n">
-        <v>602.7153284632744</v>
+        <v>618.837657653709</v>
       </c>
       <c r="D157" t="n">
-        <v>591.5844123107358</v>
+        <v>595.6374345129168</v>
       </c>
       <c r="E157" t="n">
-        <v>601.9666137695312</v>
+        <v>615.5732421875</v>
       </c>
       <c r="F157" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B158" t="n">
-        <v>597.8037594995824</v>
+        <v>614.944289073115</v>
       </c>
       <c r="C158" t="n">
-        <v>618.837657653709</v>
+        <v>622.6610217742586</v>
       </c>
       <c r="D158" t="n">
-        <v>595.6374345129168</v>
+        <v>613.9460028895547</v>
       </c>
       <c r="E158" t="n">
-        <v>615.5732421875</v>
+        <v>617.3701171875</v>
       </c>
       <c r="F158" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B159" t="n">
-        <v>614.944289073115</v>
+        <v>612.9377281921389</v>
       </c>
       <c r="C159" t="n">
-        <v>622.6610217742586</v>
+        <v>620.1353935587166</v>
       </c>
       <c r="D159" t="n">
-        <v>613.9460028895547</v>
+        <v>608.2657561335159</v>
       </c>
       <c r="E159" t="n">
-        <v>617.3701171875</v>
+        <v>613.1773071289062</v>
       </c>
       <c r="F159" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B160" t="n">
-        <v>612.9377892034477</v>
+        <v>608.0660990208263</v>
       </c>
       <c r="C160" t="n">
-        <v>620.135455286475</v>
+        <v>614.5350350972873</v>
       </c>
       <c r="D160" t="n">
-        <v>608.2658166797805</v>
+        <v>602.6554048207697</v>
       </c>
       <c r="E160" t="n">
-        <v>613.1773681640625</v>
+        <v>610.1625366210938</v>
       </c>
       <c r="F160" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B161" t="n">
-        <v>608.0660990208263</v>
+        <v>607.8763927177921</v>
       </c>
       <c r="C161" t="n">
-        <v>614.5350350972873</v>
+        <v>612.8778161384099</v>
       </c>
       <c r="D161" t="n">
-        <v>602.6554048207697</v>
+        <v>599.5207424161133</v>
       </c>
       <c r="E161" t="n">
-        <v>610.1625366210938</v>
+        <v>601.5772094726562</v>
       </c>
       <c r="F161" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B162" t="n">
-        <v>607.8764543920544</v>
+        <v>599.7304526335664</v>
       </c>
       <c r="C162" t="n">
-        <v>612.8778783201094</v>
+        <v>606.9580352784536</v>
       </c>
       <c r="D162" t="n">
-        <v>599.5208032426234</v>
+        <v>596.7854960328639</v>
       </c>
       <c r="E162" t="n">
-        <v>601.5772705078125</v>
+        <v>604.0230712890625</v>
       </c>
       <c r="F162" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B163" t="n">
-        <v>599.7304526335664</v>
+        <v>598.9717538809448</v>
       </c>
       <c r="C163" t="n">
-        <v>606.9580352784536</v>
+        <v>608.5552775708169</v>
       </c>
       <c r="D163" t="n">
-        <v>596.7854960328639</v>
+        <v>593.7906457726523</v>
       </c>
       <c r="E163" t="n">
-        <v>604.0230712890625</v>
+        <v>606.339111328125</v>
       </c>
       <c r="F163" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B164" t="n">
-        <v>598.9716935873996</v>
+        <v>606.8381854335279</v>
       </c>
       <c r="C164" t="n">
-        <v>608.5552163125774</v>
+        <v>613.7563010923075</v>
       </c>
       <c r="D164" t="n">
-        <v>593.7905860006466</v>
+        <v>605.9097866322771</v>
       </c>
       <c r="E164" t="n">
-        <v>606.3390502929688</v>
+        <v>609.214111328125</v>
       </c>
       <c r="F164" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B165" t="n">
-        <v>606.838246230648</v>
+        <v>607.8465495511928</v>
       </c>
       <c r="C165" t="n">
-        <v>613.7563625825306</v>
+        <v>613.4169431409898</v>
       </c>
       <c r="D165" t="n">
-        <v>605.9098473363839</v>
+        <v>604.2626749853522</v>
       </c>
       <c r="E165" t="n">
-        <v>609.2141723632812</v>
+        <v>611.2906494140625</v>
       </c>
       <c r="F165" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B166" t="n">
-        <v>607.8464888599174</v>
+        <v>608.3555996261091</v>
       </c>
       <c r="C166" t="n">
-        <v>613.4168818935308</v>
+        <v>637.4057020013258</v>
       </c>
       <c r="D166" t="n">
-        <v>604.2626146519137</v>
+        <v>607.9562607968793</v>
       </c>
       <c r="E166" t="n">
-        <v>611.2905883789062</v>
+        <v>634.1712646484375</v>
       </c>
       <c r="F166" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B167" t="n">
-        <v>608.3556581766634</v>
+        <v>638.4040398455469</v>
       </c>
       <c r="C167" t="n">
-        <v>637.4057633477772</v>
+        <v>641.8980416273442</v>
       </c>
       <c r="D167" t="n">
-        <v>607.9563193089997</v>
+        <v>628.2315007921775</v>
       </c>
       <c r="E167" t="n">
-        <v>634.1713256835938</v>
+        <v>634.2012329101562</v>
       </c>
       <c r="F167" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B168" t="n">
-        <v>638.4040398455469</v>
+        <v>632.4143189973911</v>
       </c>
       <c r="C168" t="n">
-        <v>641.8980416273442</v>
+        <v>633.4126052152244</v>
       </c>
       <c r="D168" t="n">
-        <v>628.2315007921775</v>
+        <v>622.281689514161</v>
       </c>
       <c r="E168" t="n">
-        <v>634.2012329101562</v>
+        <v>631.426025390625</v>
       </c>
       <c r="F168" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B169" t="n">
-        <v>632.4143189973911</v>
+        <v>629.3196791836195</v>
       </c>
       <c r="C169" t="n">
-        <v>633.4126052152244</v>
+        <v>634.6604862727559</v>
       </c>
       <c r="D169" t="n">
-        <v>622.281689514161</v>
+        <v>598.5025873828931</v>
       </c>
       <c r="E169" t="n">
-        <v>631.426025390625</v>
+        <v>599.44091796875</v>
       </c>
       <c r="F169" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B170" t="n">
-        <v>629.3196151062037</v>
+        <v>602.2062063737548</v>
       </c>
       <c r="C170" t="n">
-        <v>634.6604216515384</v>
+        <v>607.8365556216692</v>
       </c>
       <c r="D170" t="n">
-        <v>598.5025264432778</v>
+        <v>595.6574508079194</v>
       </c>
       <c r="E170" t="n">
-        <v>599.4408569335938</v>
+        <v>596.6058349609375</v>
       </c>
       <c r="F170" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B171" t="n">
-        <v>602.2061447656582</v>
+        <v>601.9665545007575</v>
       </c>
       <c r="C171" t="n">
-        <v>607.8364934375654</v>
+        <v>623.0803311577063</v>
       </c>
       <c r="D171" t="n">
-        <v>595.6573898697867</v>
+        <v>599.2412527816401</v>
       </c>
       <c r="E171" t="n">
-        <v>596.6057739257812</v>
+        <v>621.9122924804688</v>
       </c>
       <c r="F171" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B172" t="n">
-        <v>601.9666135784172</v>
+        <v>622.6011661035562</v>
       </c>
       <c r="C172" t="n">
-        <v>623.0803923074952</v>
+        <v>641.2991089275577</v>
       </c>
       <c r="D172" t="n">
-        <v>599.2413115918356</v>
+        <v>621.3633009071642</v>
       </c>
       <c r="E172" t="n">
-        <v>621.912353515625</v>
+        <v>626.4945068359375</v>
       </c>
       <c r="F172" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B173" t="n">
-        <v>622.601105447702</v>
+        <v>622.3915225332053</v>
       </c>
       <c r="C173" t="n">
-        <v>641.2990464500883</v>
+        <v>628.0717733238163</v>
       </c>
       <c r="D173" t="n">
-        <v>621.3632403719068</v>
+        <v>581.9109692668093</v>
       </c>
       <c r="E173" t="n">
-        <v>626.4944458007812</v>
+        <v>591.9837036132812</v>
       </c>
       <c r="F173" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B174" t="n">
-        <v>622.3915867034917</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="C174" t="n">
-        <v>628.0718380797523</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="D174" t="n">
-        <v>581.9110292634388</v>
+        <v>578.2273099921849</v>
       </c>
       <c r="E174" t="n">
-        <v>591.9837646484375</v>
+        <v>584.3867797851562</v>
       </c>
       <c r="F174" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B175" t="n">
-        <v>590.9854370177134</v>
+        <v>589.9871222602228</v>
       </c>
       <c r="C175" t="n">
-        <v>590.9854370177134</v>
+        <v>596.6057643945405</v>
       </c>
       <c r="D175" t="n">
-        <v>578.2273099921849</v>
+        <v>580.0142532419713</v>
       </c>
       <c r="E175" t="n">
-        <v>584.3867797851562</v>
+        <v>583.588134765625</v>
       </c>
       <c r="F175" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B176" t="n">
-        <v>589.9871222602228</v>
+        <v>579.7347558037309</v>
       </c>
       <c r="C176" t="n">
-        <v>596.6057643945405</v>
+        <v>590.3066340250939</v>
       </c>
       <c r="D176" t="n">
-        <v>580.0142532419713</v>
+        <v>569.6221111934292</v>
       </c>
       <c r="E176" t="n">
-        <v>583.588134765625</v>
+        <v>570.00146484375</v>
       </c>
       <c r="F176" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B177" t="n">
-        <v>579.7347558037309</v>
+        <v>564.8602908302337</v>
       </c>
       <c r="C177" t="n">
-        <v>590.3066340250939</v>
+        <v>571.1893911411966</v>
       </c>
       <c r="D177" t="n">
-        <v>569.6221111934292</v>
+        <v>556.0553993401948</v>
       </c>
       <c r="E177" t="n">
-        <v>570.00146484375</v>
+        <v>567.455810546875</v>
       </c>
       <c r="F177" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B178" t="n">
-        <v>564.8602908302337</v>
+        <v>571.968101190783</v>
       </c>
       <c r="C178" t="n">
-        <v>571.1893911411966</v>
+        <v>575.0827493186854</v>
       </c>
       <c r="D178" t="n">
-        <v>556.0553993401948</v>
+        <v>559.9387644415484</v>
       </c>
       <c r="E178" t="n">
-        <v>567.455810546875</v>
+        <v>566.00830078125</v>
       </c>
       <c r="F178" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B179" t="n">
-        <v>571.9680395129554</v>
+        <v>579.4427159724761</v>
       </c>
       <c r="C179" t="n">
-        <v>575.0826873049916</v>
+        <v>600.795858737961</v>
       </c>
       <c r="D179" t="n">
-        <v>559.938704060897</v>
+        <v>578.8431525395191</v>
       </c>
       <c r="E179" t="n">
-        <v>566.0082397460938</v>
+        <v>593.011962890625</v>
       </c>
       <c r="F179" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B180" t="n">
-        <v>579.4427159724761</v>
+        <v>593.1818700134238</v>
       </c>
       <c r="C180" t="n">
-        <v>600.795858737961</v>
+        <v>605.3322537623429</v>
       </c>
       <c r="D180" t="n">
-        <v>578.8431525395191</v>
+        <v>591.5331468141493</v>
       </c>
       <c r="E180" t="n">
-        <v>593.011962890625</v>
+        <v>599.7366943359375</v>
       </c>
       <c r="F180" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G180" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B181" t="n">
-        <v>593.1818700134238</v>
+        <v>591.5331725816898</v>
       </c>
       <c r="C181" t="n">
-        <v>605.3322537623429</v>
+        <v>593.3417428489197</v>
       </c>
       <c r="D181" t="n">
-        <v>591.5331468141493</v>
+        <v>565.7435277503374</v>
       </c>
       <c r="E181" t="n">
-        <v>599.7366943359375</v>
+        <v>567.1324462890625</v>
       </c>
       <c r="F181" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B182" t="n">
-        <v>591.5331725816898</v>
+        <v>572.3682769745303</v>
       </c>
       <c r="C182" t="n">
-        <v>593.3417428489197</v>
+        <v>579.7624046842873</v>
       </c>
       <c r="D182" t="n">
-        <v>565.7435277503374</v>
+        <v>562.6559105294999</v>
       </c>
       <c r="E182" t="n">
-        <v>567.1324462890625</v>
+        <v>576.7647705078125</v>
       </c>
       <c r="F182" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B183" t="n">
-        <v>572.3682769745303</v>
+        <v>571.5689356803741</v>
       </c>
       <c r="C183" t="n">
-        <v>579.7624046842873</v>
+        <v>575.3559250048318</v>
       </c>
       <c r="D183" t="n">
-        <v>562.6559105294999</v>
+        <v>559.3685422933314</v>
       </c>
       <c r="E183" t="n">
-        <v>576.7647705078125</v>
+        <v>563.4053344726562</v>
       </c>
       <c r="F183" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B184" t="n">
-        <v>571.5689356803741</v>
+        <v>561.8066012038755</v>
       </c>
       <c r="C184" t="n">
-        <v>575.3559250048318</v>
+        <v>571.7487666818112</v>
       </c>
       <c r="D184" t="n">
-        <v>559.3685422933314</v>
+        <v>560.5775907162</v>
       </c>
       <c r="E184" t="n">
-        <v>563.4053344726562</v>
+        <v>561.7566528320312</v>
       </c>
       <c r="F184" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B185" t="n">
-        <v>561.8066012038755</v>
+        <v>561.4469285838474</v>
       </c>
       <c r="C185" t="n">
-        <v>571.7487666818112</v>
+        <v>568.591253761232</v>
       </c>
       <c r="D185" t="n">
-        <v>560.5775907162</v>
+        <v>555.1119012433646</v>
       </c>
       <c r="E185" t="n">
-        <v>561.7566528320312</v>
+        <v>557.230224609375</v>
       </c>
       <c r="F185" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B186" t="n">
-        <v>561.4469285838474</v>
+        <v>555.1118879211193</v>
       </c>
       <c r="C186" t="n">
-        <v>568.591253761232</v>
+        <v>555.9013039685537</v>
       </c>
       <c r="D186" t="n">
-        <v>555.1119012433646</v>
+        <v>539.7540133926082</v>
       </c>
       <c r="E186" t="n">
-        <v>557.230224609375</v>
+        <v>542.44189453125</v>
       </c>
       <c r="F186" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B187" t="n">
-        <v>555.1118879211193</v>
+        <v>542.9115767800729</v>
       </c>
       <c r="C187" t="n">
-        <v>555.9013039685537</v>
+        <v>556.4108722579447</v>
       </c>
       <c r="D187" t="n">
-        <v>539.7540133926082</v>
+        <v>539.9738926737891</v>
       </c>
       <c r="E187" t="n">
-        <v>542.44189453125</v>
+        <v>549.8161010742188</v>
       </c>
       <c r="F187" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B188" t="n">
-        <v>542.9115767800729</v>
+        <v>559.5583857816937</v>
       </c>
       <c r="C188" t="n">
-        <v>556.4108722579447</v>
+        <v>570.4498144711828</v>
       </c>
       <c r="D188" t="n">
-        <v>539.9738926737891</v>
+        <v>557.5599629753306</v>
       </c>
       <c r="E188" t="n">
-        <v>549.8161010742188</v>
+        <v>562.1563110351562</v>
       </c>
       <c r="F188" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B189" t="n">
-        <v>559.5583857816937</v>
+        <v>560.4976417791106</v>
       </c>
       <c r="C189" t="n">
-        <v>570.4498144711828</v>
+        <v>565.0939897966132</v>
       </c>
       <c r="D189" t="n">
-        <v>557.5599629753306</v>
+        <v>550.9951316644288</v>
       </c>
       <c r="E189" t="n">
-        <v>562.1563110351562</v>
+        <v>562.8457641601562</v>
       </c>
       <c r="F189" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B190" t="n">
-        <v>560.4976417791106</v>
+        <v>607.4305787144307</v>
       </c>
       <c r="C190" t="n">
-        <v>565.0939897966132</v>
+        <v>627.784571153574</v>
       </c>
       <c r="D190" t="n">
-        <v>550.9951316644288</v>
+        <v>594.6306830487989</v>
       </c>
       <c r="E190" t="n">
-        <v>562.8457641601562</v>
+        <v>612.4266357421875</v>
       </c>
       <c r="F190" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B191" t="n">
-        <v>607.4305787144307</v>
+        <v>607.4206544757068</v>
       </c>
       <c r="C191" t="n">
-        <v>627.784571153574</v>
+        <v>609.5189740900589</v>
       </c>
       <c r="D191" t="n">
-        <v>594.6306830487989</v>
+        <v>579.9622828274885</v>
       </c>
       <c r="E191" t="n">
-        <v>612.4266357421875</v>
+        <v>582.4403686523438</v>
       </c>
       <c r="F191" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B192" t="n">
-        <v>607.4206544757068</v>
+        <v>594.3709360150443</v>
       </c>
       <c r="C192" t="n">
-        <v>609.5189740900589</v>
+        <v>603.1040338931904</v>
       </c>
       <c r="D192" t="n">
-        <v>579.9622828274885</v>
+        <v>581.301233826573</v>
       </c>
       <c r="E192" t="n">
-        <v>582.4403686523438</v>
+        <v>599.8165893554688</v>
       </c>
       <c r="F192" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B193" t="n">
-        <v>594.3709360150443</v>
+        <v>607.1109147253509</v>
       </c>
       <c r="C193" t="n">
-        <v>603.1040338931904</v>
+        <v>624.8768626804635</v>
       </c>
       <c r="D193" t="n">
-        <v>581.301233826573</v>
+        <v>603.1839600389557</v>
       </c>
       <c r="E193" t="n">
-        <v>599.8165893554688</v>
+        <v>615.0946044921875</v>
       </c>
       <c r="F193" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B194" t="n">
-        <v>607.1109147253509</v>
+        <v>613.9055418180343</v>
       </c>
       <c r="C194" t="n">
-        <v>624.8768626804635</v>
+        <v>615.5142576272189</v>
       </c>
       <c r="D194" t="n">
-        <v>603.1839600389557</v>
+        <v>597.5384532703483</v>
       </c>
       <c r="E194" t="n">
-        <v>615.0946044921875</v>
+        <v>602.6444091796875</v>
       </c>
       <c r="F194" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B195" t="n">
-        <v>613.9055418180343</v>
+        <v>583.529455055522</v>
       </c>
       <c r="C195" t="n">
-        <v>615.5142576272189</v>
+        <v>632.77062206454</v>
       </c>
       <c r="D195" t="n">
-        <v>597.5384532703483</v>
+        <v>576.6149292518581</v>
       </c>
       <c r="E195" t="n">
-        <v>602.6444091796875</v>
+        <v>630.9819946289062</v>
       </c>
       <c r="F195" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B196" t="n">
-        <v>583.529455055522</v>
+        <v>659.8193113874754</v>
       </c>
       <c r="C196" t="n">
-        <v>632.77062206454</v>
+        <v>677.3254544051542</v>
       </c>
       <c r="D196" t="n">
-        <v>576.6149292518581</v>
+        <v>657.491131647921</v>
       </c>
       <c r="E196" t="n">
-        <v>630.9819946289062</v>
+        <v>668.6823120117188</v>
       </c>
       <c r="F196" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B197" t="n">
-        <v>659.8193113874754</v>
+        <v>660.858454671636</v>
       </c>
       <c r="C197" t="n">
-        <v>677.3254544051542</v>
+        <v>676.0864269737083</v>
       </c>
       <c r="D197" t="n">
-        <v>657.491131647921</v>
+        <v>653.6841239854351</v>
       </c>
       <c r="E197" t="n">
-        <v>668.6823120117188</v>
+        <v>656.2120971679688</v>
       </c>
       <c r="F197" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>660.858454671636</v>
+        <v>651.4858277274717</v>
       </c>
       <c r="C198" t="n">
-        <v>676.0864269737083</v>
+        <v>665.9743929146624</v>
       </c>
       <c r="D198" t="n">
-        <v>653.6841239854351</v>
+        <v>648.5381419230179</v>
       </c>
       <c r="E198" t="n">
-        <v>656.2120971679688</v>
+        <v>660.5186767578125</v>
       </c>
       <c r="F198" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>651.4858277274717</v>
+        <v>663.0767089741589</v>
       </c>
       <c r="C199" t="n">
-        <v>665.9743929146624</v>
+        <v>685.5390243545221</v>
       </c>
       <c r="D199" t="n">
-        <v>648.5381419230179</v>
+        <v>656.1421789132482</v>
       </c>
       <c r="E199" t="n">
-        <v>660.5186767578125</v>
+        <v>680.7727661132812</v>
       </c>
       <c r="F199" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>663.0767089741589</v>
+        <v>676.7459348014426</v>
       </c>
       <c r="C200" t="n">
-        <v>685.5390243545221</v>
+        <v>681.3622866487058</v>
       </c>
       <c r="D200" t="n">
-        <v>656.1421789132482</v>
+        <v>659.6393793096187</v>
       </c>
       <c r="E200" t="n">
-        <v>680.7727661132812</v>
+        <v>664.0159301757812</v>
       </c>
       <c r="F200" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B201" t="n">
-        <v>676.7459348014426</v>
+        <v>647.1892801723585</v>
       </c>
       <c r="C201" t="n">
-        <v>681.3622866487058</v>
+        <v>651.68573177941</v>
       </c>
       <c r="D201" t="n">
-        <v>659.6393793096187</v>
+        <v>625.5063791142821</v>
       </c>
       <c r="E201" t="n">
-        <v>664.0159301757812</v>
+        <v>645.5006103515625</v>
       </c>
       <c r="F201" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B202" t="n">
-        <v>647.1892801723585</v>
+        <v>646.1900645769782</v>
       </c>
       <c r="C202" t="n">
-        <v>651.68573177941</v>
+        <v>652.7848358303891</v>
       </c>
       <c r="D202" t="n">
-        <v>625.5063791142821</v>
+        <v>635.5084916103011</v>
       </c>
       <c r="E202" t="n">
-        <v>645.5006103515625</v>
+        <v>645.3406982421875</v>
       </c>
       <c r="F202" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B203" t="n">
-        <v>646.1900645769782</v>
+        <v>653.664124760039</v>
       </c>
       <c r="C203" t="n">
-        <v>652.7848358303891</v>
+        <v>655.3627963853286</v>
       </c>
       <c r="D203" t="n">
-        <v>635.5084916103011</v>
+        <v>642.6928027946103</v>
       </c>
       <c r="E203" t="n">
-        <v>645.3406982421875</v>
+        <v>643.3023071289062</v>
       </c>
       <c r="F203" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B204" t="n">
-        <v>653.664124760039</v>
+        <v>647.189254956408</v>
       </c>
       <c r="C204" t="n">
-        <v>655.3627963853286</v>
+        <v>648.4882176170956</v>
       </c>
       <c r="D204" t="n">
-        <v>642.6928027946103</v>
+        <v>623.5079318845419</v>
       </c>
       <c r="E204" t="n">
-        <v>643.3023071289062</v>
+        <v>626.6754150390625</v>
       </c>
       <c r="F204" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B205" t="n">
-        <v>647.189254956408</v>
+        <v>607.9301851876114</v>
       </c>
       <c r="C205" t="n">
-        <v>648.4882176170956</v>
+        <v>614.1653155952538</v>
       </c>
       <c r="D205" t="n">
-        <v>623.5079318845419</v>
+        <v>596.7490071058414</v>
       </c>
       <c r="E205" t="n">
-        <v>626.6754150390625</v>
+        <v>605.6220092773438</v>
       </c>
       <c r="F205" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B206" t="n">
-        <v>607.9301851876114</v>
+        <v>604.8226548171024</v>
       </c>
       <c r="C206" t="n">
-        <v>614.1653155952538</v>
+        <v>609.4989569016461</v>
       </c>
       <c r="D206" t="n">
-        <v>596.7490071058414</v>
+        <v>593.9812354037057</v>
       </c>
       <c r="E206" t="n">
-        <v>605.6220092773438</v>
+        <v>594.7206420898438</v>
       </c>
       <c r="F206" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B207" t="n">
-        <v>604.8226548171024</v>
+        <v>606.7411202287035</v>
       </c>
       <c r="C207" t="n">
-        <v>609.4989569016461</v>
+        <v>610.7779733376527</v>
       </c>
       <c r="D207" t="n">
-        <v>593.9812354037057</v>
+        <v>592.6622656813121</v>
       </c>
       <c r="E207" t="n">
-        <v>594.7206420898438</v>
+        <v>593.4016723632812</v>
       </c>
       <c r="F207" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B208" t="n">
-        <v>606.7411202287035</v>
+        <v>596.3493616660036</v>
       </c>
       <c r="C208" t="n">
-        <v>610.7779733376527</v>
+        <v>600.5260580457825</v>
       </c>
       <c r="D208" t="n">
-        <v>592.6622656813121</v>
+        <v>586.5370982909723</v>
       </c>
       <c r="E208" t="n">
-        <v>593.4016723632812</v>
+        <v>592.9420166015625</v>
       </c>
       <c r="F208" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B209" t="n">
-        <v>596.3493616660036</v>
+        <v>592.7821833537371</v>
       </c>
       <c r="C209" t="n">
-        <v>600.5260580457825</v>
+        <v>599.4968549179539</v>
       </c>
       <c r="D209" t="n">
-        <v>586.5370982909723</v>
+        <v>581.7608519604674</v>
       </c>
       <c r="E209" t="n">
-        <v>592.9420166015625</v>
+        <v>585.148193359375</v>
       </c>
       <c r="F209" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B210" t="n">
-        <v>592.7821833537371</v>
+        <v>525.58522592167</v>
       </c>
       <c r="C210" t="n">
-        <v>599.4968549179539</v>
+        <v>539.4542858116451</v>
       </c>
       <c r="D210" t="n">
-        <v>581.7608519604674</v>
+        <v>524.0764068649972</v>
       </c>
       <c r="E210" t="n">
-        <v>585.148193359375</v>
+        <v>538.60498046875</v>
       </c>
       <c r="F210" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B211" t="n">
-        <v>525.58522592167</v>
+        <v>543.171288392182</v>
       </c>
       <c r="C211" t="n">
-        <v>539.4542858116451</v>
+        <v>557.8897136701136</v>
       </c>
       <c r="D211" t="n">
-        <v>524.0764068649972</v>
+        <v>539.7939490076644</v>
       </c>
       <c r="E211" t="n">
-        <v>538.60498046875</v>
+        <v>556.27099609375</v>
       </c>
       <c r="F211" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B212" t="n">
-        <v>543.171288392182</v>
+        <v>561.7966164985271</v>
       </c>
       <c r="C212" t="n">
-        <v>557.8897136701136</v>
+        <v>597.0488245114987</v>
       </c>
       <c r="D212" t="n">
-        <v>539.7939490076644</v>
+        <v>558.9188827428958</v>
       </c>
       <c r="E212" t="n">
-        <v>556.27099609375</v>
+        <v>589.7745361328125</v>
       </c>
       <c r="F212" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B213" t="n">
-        <v>561.7966164985271</v>
+        <v>581.0414552494501</v>
       </c>
       <c r="C213" t="n">
-        <v>597.0488245114987</v>
+        <v>592.32253050782</v>
       </c>
       <c r="D213" t="n">
-        <v>558.9188827428958</v>
+        <v>577.794018053301</v>
       </c>
       <c r="E213" t="n">
-        <v>589.7745361328125</v>
+        <v>587.4763793945312</v>
       </c>
       <c r="F213" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B214" t="n">
-        <v>581.0414552494501</v>
+        <v>599.9865089938204</v>
       </c>
       <c r="C214" t="n">
-        <v>592.32253050782</v>
+        <v>600.5260612032997</v>
       </c>
       <c r="D214" t="n">
-        <v>577.794018053301</v>
+        <v>579.6625219517506</v>
       </c>
       <c r="E214" t="n">
-        <v>587.4763793945312</v>
+        <v>588.3057250976562</v>
       </c>
       <c r="F214" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B215" t="n">
-        <v>599.9865089938204</v>
+        <v>586.487189429669</v>
       </c>
       <c r="C215" t="n">
-        <v>600.5260612032997</v>
+        <v>594.8405827519979</v>
       </c>
       <c r="D215" t="n">
-        <v>579.6625219517506</v>
+        <v>585.5379263278069</v>
       </c>
       <c r="E215" t="n">
-        <v>588.3057250976562</v>
+        <v>589.4348754882812</v>
       </c>
       <c r="F215" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B216" t="n">
-        <v>586.487189429669</v>
+        <v>585.1781899072663</v>
       </c>
       <c r="C216" t="n">
-        <v>594.8405827519979</v>
+        <v>598.2678350979388</v>
       </c>
       <c r="D216" t="n">
-        <v>585.5379263278069</v>
+        <v>585.1581861630435</v>
       </c>
       <c r="E216" t="n">
-        <v>589.4348754882812</v>
+        <v>591.633056640625</v>
       </c>
       <c r="F216" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B217" t="n">
-        <v>585.1781899072663</v>
+        <v>598.657568915248</v>
       </c>
       <c r="C217" t="n">
-        <v>598.2678350979388</v>
+        <v>607.7304260788247</v>
       </c>
       <c r="D217" t="n">
-        <v>585.1581861630435</v>
+        <v>591.5631919202813</v>
       </c>
       <c r="E217" t="n">
-        <v>591.633056640625</v>
+        <v>594.4508666992188</v>
       </c>
       <c r="F217" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B218" t="n">
-        <v>598.657568915248</v>
+        <v>597.5284100969216</v>
       </c>
       <c r="C218" t="n">
-        <v>607.7304260788247</v>
+        <v>611.9470231090784</v>
       </c>
       <c r="D218" t="n">
-        <v>591.5631919202813</v>
+        <v>592.9320621063698</v>
       </c>
       <c r="E218" t="n">
-        <v>594.4508666992188</v>
+        <v>598.6475219726562</v>
       </c>
       <c r="F218" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B219" t="n">
-        <v>597.5284100969216</v>
+        <v>600.5960026412422</v>
       </c>
       <c r="C219" t="n">
-        <v>611.9470231090784</v>
+        <v>604.023290419805</v>
       </c>
       <c r="D219" t="n">
-        <v>592.9320621063698</v>
+        <v>577.7540447074138</v>
       </c>
       <c r="E219" t="n">
-        <v>598.6475219726562</v>
+        <v>578.3934936523438</v>
       </c>
       <c r="F219" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B220" t="n">
-        <v>600.5960026412422</v>
+        <v>580.2520897369063</v>
       </c>
       <c r="C220" t="n">
-        <v>604.023290419805</v>
+        <v>595.3801043917661</v>
       </c>
       <c r="D220" t="n">
-        <v>577.7540447074138</v>
+        <v>578.9331233348041</v>
       </c>
       <c r="E220" t="n">
-        <v>578.3934936523438</v>
+        <v>594.5007934570312</v>
       </c>
       <c r="F220" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B221" t="n">
-        <v>580.2520897369063</v>
+        <v>596.5092089028919</v>
       </c>
       <c r="C221" t="n">
-        <v>595.3801043917661</v>
+        <v>601.3853654698224</v>
       </c>
       <c r="D221" t="n">
-        <v>578.9331233348041</v>
+        <v>588.8252707092146</v>
       </c>
       <c r="E221" t="n">
-        <v>594.5007934570312</v>
+        <v>589.3848266601562</v>
       </c>
       <c r="F221" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B222" t="n">
-        <v>596.5092089028919</v>
+        <v>589.2849441761664</v>
       </c>
       <c r="C222" t="n">
-        <v>601.3853654698224</v>
+        <v>589.774548021712</v>
       </c>
       <c r="D222" t="n">
-        <v>588.8252707092146</v>
+        <v>564.3046582848494</v>
       </c>
       <c r="E222" t="n">
-        <v>589.3848266601562</v>
+        <v>568.5213012695312</v>
       </c>
       <c r="F222" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B223" t="n">
-        <v>589.2849441761664</v>
+        <v>557.0403796583744</v>
       </c>
       <c r="C223" t="n">
-        <v>589.774548021712</v>
+        <v>560.2178647510921</v>
       </c>
       <c r="D223" t="n">
-        <v>564.3046582848494</v>
+        <v>542.7816737373303</v>
       </c>
       <c r="E223" t="n">
-        <v>568.5213012695312</v>
+        <v>543.2412719726562</v>
       </c>
       <c r="F223" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B224" t="n">
-        <v>557.0403796583744</v>
+        <v>540.9131223962278</v>
       </c>
       <c r="C224" t="n">
-        <v>560.2178647510921</v>
+        <v>553.6330639150415</v>
       </c>
       <c r="D224" t="n">
-        <v>542.7816737373303</v>
+        <v>536.8463247077087</v>
       </c>
       <c r="E224" t="n">
-        <v>543.2412719726562</v>
+        <v>545.5994262695312</v>
       </c>
       <c r="F224" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B225" t="n">
-        <v>540.9131223962278</v>
+        <v>546.5187091013889</v>
       </c>
       <c r="C225" t="n">
-        <v>553.6330639150415</v>
+        <v>549.5562899225255</v>
       </c>
       <c r="D225" t="n">
-        <v>536.8463247077087</v>
+        <v>538.8847190657524</v>
       </c>
       <c r="E225" t="n">
-        <v>545.5994262695312</v>
+        <v>545.3995971679688</v>
       </c>
       <c r="F225" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B226" t="n">
-        <v>546.5187091013889</v>
+        <v>546.4587335768297</v>
       </c>
       <c r="C226" t="n">
-        <v>549.5562899225255</v>
+        <v>553.4332095869578</v>
       </c>
       <c r="D226" t="n">
-        <v>538.8847190657524</v>
+        <v>542.8015857242297</v>
       </c>
       <c r="E226" t="n">
-        <v>545.3995971679688</v>
+        <v>549.4663696289062</v>
       </c>
       <c r="F226" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B227" t="n">
-        <v>546.4587335768297</v>
+        <v>549.7661710202622</v>
       </c>
       <c r="C227" t="n">
-        <v>553.4332095869578</v>
+        <v>560.9772946036173</v>
       </c>
       <c r="D227" t="n">
-        <v>542.8015857242297</v>
+        <v>545.8692218355393</v>
       </c>
       <c r="E227" t="n">
-        <v>549.4663696289062</v>
+        <v>558.5792236328125</v>
       </c>
       <c r="F227" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B228" t="n">
-        <v>549.7661710202622</v>
+        <v>563.4353464162</v>
       </c>
       <c r="C228" t="n">
-        <v>560.9772946036173</v>
+        <v>570.3498724402046</v>
       </c>
       <c r="D228" t="n">
-        <v>545.8692218355393</v>
+        <v>560.9573215839381</v>
       </c>
       <c r="E228" t="n">
-        <v>558.5792236328125</v>
+        <v>569.6004638671875</v>
       </c>
       <c r="F228" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B229" t="n">
-        <v>563.4353464162</v>
+        <v>589.8444773654404</v>
       </c>
       <c r="C229" t="n">
-        <v>570.3498724402046</v>
+        <v>592.8721171723366</v>
       </c>
       <c r="D229" t="n">
-        <v>560.9573215839381</v>
+        <v>561.4369046651577</v>
       </c>
       <c r="E229" t="n">
-        <v>569.6004638671875</v>
+        <v>575.6856689453125</v>
       </c>
       <c r="F229" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B230" t="n">
-        <v>589.8444773654404</v>
+        <v>576.0253592943615</v>
       </c>
       <c r="C230" t="n">
-        <v>592.8721171723366</v>
+        <v>587.9260010338789</v>
       </c>
       <c r="D230" t="n">
-        <v>561.4369046651577</v>
+        <v>567.1723610665189</v>
       </c>
       <c r="E230" t="n">
-        <v>575.6856689453125</v>
+        <v>570.6495971679688</v>
       </c>
       <c r="F230" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B231" t="n">
-        <v>576.0253592943615</v>
+        <v>571.0992793335739</v>
       </c>
       <c r="C231" t="n">
-        <v>587.9260010338789</v>
+        <v>588.7253835559844</v>
       </c>
       <c r="D231" t="n">
-        <v>567.1723610665189</v>
+        <v>570.5497252457161</v>
       </c>
       <c r="E231" t="n">
-        <v>570.6495971679688</v>
+        <v>577.564208984375</v>
       </c>
       <c r="F231" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B232" t="n">
-        <v>571.0992793335739</v>
+        <v>577.1744781551006</v>
       </c>
       <c r="C232" t="n">
-        <v>588.7253835559844</v>
+        <v>578.2236379136884</v>
       </c>
       <c r="D232" t="n">
-        <v>570.5497252457161</v>
+        <v>568.6911832402849</v>
       </c>
       <c r="E232" t="n">
-        <v>577.564208984375</v>
+        <v>571.888671875</v>
       </c>
       <c r="F232" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B233" t="n">
-        <v>577.1744781551006</v>
+        <v>557.9096596695957</v>
       </c>
       <c r="C233" t="n">
-        <v>578.2236379136884</v>
+        <v>584.4887194481862</v>
       </c>
       <c r="D233" t="n">
-        <v>568.6911832402849</v>
+        <v>555.6614340241316</v>
       </c>
       <c r="E233" t="n">
-        <v>571.888671875</v>
+        <v>578.083740234375</v>
       </c>
       <c r="F233" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B234" t="n">
-        <v>557.9096596695957</v>
+        <v>578.3335366296732</v>
       </c>
       <c r="C234" t="n">
-        <v>584.4887194481862</v>
+        <v>599.9065373056851</v>
       </c>
       <c r="D234" t="n">
-        <v>555.6614340241316</v>
+        <v>576.5449702025707</v>
       </c>
       <c r="E234" t="n">
-        <v>578.083740234375</v>
+        <v>592.3824462890625</v>
       </c>
       <c r="F234" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B235" t="n">
-        <v>578.3335366296732</v>
+        <v>604.0133041368691</v>
       </c>
       <c r="C235" t="n">
-        <v>599.9065373056851</v>
+        <v>618.9715308723809</v>
       </c>
       <c r="D235" t="n">
-        <v>576.5449702025707</v>
+        <v>603.8733999005765</v>
       </c>
       <c r="E235" t="n">
-        <v>592.3824462890625</v>
+        <v>610.1984252929688</v>
       </c>
       <c r="F235" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B236" t="n">
-        <v>604.0133041368691</v>
+        <v>611.8670721034152</v>
       </c>
       <c r="C236" t="n">
-        <v>618.9715308723809</v>
+        <v>616.9730886717387</v>
       </c>
       <c r="D236" t="n">
-        <v>603.8733999005765</v>
+        <v>604.7926993516937</v>
       </c>
       <c r="E236" t="n">
-        <v>610.1984252929688</v>
+        <v>616.2836303710938</v>
       </c>
       <c r="F236" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B237" t="n">
-        <v>611.8670721034152</v>
+        <v>615.7241045276966</v>
       </c>
       <c r="C237" t="n">
-        <v>616.9730886717387</v>
+        <v>624.3072966603136</v>
       </c>
       <c r="D237" t="n">
-        <v>604.7926993516937</v>
+        <v>609.2591747857786</v>
       </c>
       <c r="E237" t="n">
-        <v>616.2836303710938</v>
+        <v>612.9962158203125</v>
       </c>
       <c r="F237" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B238" t="n">
-        <v>615.7241045276966</v>
+        <v>648.1284941622514</v>
       </c>
       <c r="C238" t="n">
-        <v>624.3072966603136</v>
+        <v>657.3411939542544</v>
       </c>
       <c r="D238" t="n">
-        <v>609.2591747857786</v>
+        <v>638.056426220049</v>
       </c>
       <c r="E238" t="n">
-        <v>612.9962158203125</v>
+        <v>653.1744995117188</v>
       </c>
       <c r="F238" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B239" t="n">
-        <v>648.1284941622514</v>
+        <v>653.1945472302951</v>
       </c>
       <c r="C239" t="n">
-        <v>657.3411939542544</v>
+        <v>662.9768054946985</v>
       </c>
       <c r="D239" t="n">
-        <v>638.056426220049</v>
+        <v>641.6336632885306</v>
       </c>
       <c r="E239" t="n">
-        <v>653.1744995117188</v>
+        <v>643.8718872070312</v>
       </c>
       <c r="F239" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B240" t="n">
-        <v>653.1945472302951</v>
+        <v>652.9947023490145</v>
       </c>
       <c r="C240" t="n">
-        <v>662.9768054946985</v>
+        <v>663.716221985592</v>
       </c>
       <c r="D240" t="n">
-        <v>641.6336632885306</v>
+        <v>645.6904688887529</v>
       </c>
       <c r="E240" t="n">
-        <v>643.8718872070312</v>
+        <v>647.51904296875</v>
       </c>
       <c r="F240" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B241" t="n">
-        <v>652.9947023490145</v>
+        <v>657.311302577125</v>
       </c>
       <c r="C241" t="n">
-        <v>663.716221985592</v>
+        <v>668.072768706455</v>
       </c>
       <c r="D241" t="n">
-        <v>645.6904688887529</v>
+        <v>648.708045415434</v>
       </c>
       <c r="E241" t="n">
-        <v>647.51904296875</v>
+        <v>665.0751342773438</v>
       </c>
       <c r="F241" t="n">
-        <v>16925000</v>
+        <v>19332300</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B242" t="n">
-        <v>657.311302577125</v>
+        <v>658.7801108800835</v>
       </c>
       <c r="C242" t="n">
-        <v>668.072768706455</v>
+        <v>678.3346866933342</v>
       </c>
       <c r="D242" t="n">
-        <v>648.708045415434</v>
+        <v>655.6825797136325</v>
       </c>
       <c r="E242" t="n">
-        <v>665.0751342773438</v>
+        <v>669.7114868164062</v>
       </c>
       <c r="F242" t="n">
-        <v>19332300</v>
+        <v>19502800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B243" t="n">
-        <v>658.7801108800835</v>
+        <v>679.3738238485387</v>
       </c>
       <c r="C243" t="n">
-        <v>678.3346866933342</v>
+        <v>684.7695900234191</v>
       </c>
       <c r="D243" t="n">
-        <v>655.6825797136325</v>
+        <v>671.3801323225093</v>
       </c>
       <c r="E243" t="n">
-        <v>669.7114868164062</v>
+        <v>672.779052734375</v>
       </c>
       <c r="F243" t="n">
-        <v>19502800</v>
+        <v>17217800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B244" t="n">
-        <v>679.3738238485387</v>
+        <v>681.9018750257407</v>
       </c>
       <c r="C244" t="n">
-        <v>684.7695900234191</v>
+        <v>682.6612854975235</v>
       </c>
       <c r="D244" t="n">
-        <v>671.3801323225093</v>
+        <v>666.5239959332205</v>
       </c>
       <c r="E244" t="n">
-        <v>672.779052734375</v>
+        <v>681.77197265625</v>
       </c>
       <c r="F244" t="n">
-        <v>17217800</v>
+        <v>15928000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B245" t="n">
-        <v>681.9018750257407</v>
+        <v>688.0769980771287</v>
       </c>
       <c r="C245" t="n">
-        <v>682.6612854975235</v>
+        <v>689.6058209010791</v>
       </c>
       <c r="D245" t="n">
-        <v>666.5239959332205</v>
+        <v>660.278927643704</v>
       </c>
       <c r="E245" t="n">
-        <v>681.77197265625</v>
+        <v>665.2250366210938</v>
       </c>
       <c r="F245" t="n">
-        <v>15928000</v>
+        <v>27596400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,25 +6813,25 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B246" t="n">
-        <v>688.0769980771287</v>
+        <v>680.2999877929688</v>
       </c>
       <c r="C246" t="n">
-        <v>689.6058209010791</v>
+        <v>753</v>
       </c>
       <c r="D246" t="n">
-        <v>660.278927643704</v>
+        <v>679.5999755859375</v>
       </c>
       <c r="E246" t="n">
-        <v>665.2250366210938</v>
+        <v>741.25</v>
       </c>
       <c r="F246" t="n">
-        <v>27596400</v>
+        <v>48720500</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -6839,25 +6839,25 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B247" t="n">
-        <v>680.2999877929688</v>
+        <v>731.4000244140625</v>
       </c>
       <c r="C247" t="n">
-        <v>753</v>
+        <v>757.27001953125</v>
       </c>
       <c r="D247" t="n">
-        <v>679.5999755859375</v>
+        <v>730</v>
       </c>
       <c r="E247" t="n">
-        <v>741.25</v>
+        <v>736.5999755859375</v>
       </c>
       <c r="F247" t="n">
-        <v>48720500</v>
+        <v>28122100</v>
       </c>
       <c r="G247" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B248" t="n">
-        <v>731.4000244140625</v>
+        <v>747.5999755859375</v>
       </c>
       <c r="C248" t="n">
-        <v>757.27001953125</v>
+        <v>763.9000244140625</v>
       </c>
       <c r="D248" t="n">
-        <v>730</v>
+        <v>739.510009765625</v>
       </c>
       <c r="E248" t="n">
-        <v>736.5999755859375</v>
+        <v>744.0999755859375</v>
       </c>
       <c r="F248" t="n">
-        <v>28122100</v>
+        <v>30829200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B249" t="n">
-        <v>747.5999755859375</v>
+        <v>744.3599853515625</v>
       </c>
       <c r="C249" t="n">
-        <v>763.9000244140625</v>
+        <v>779.8200073242188</v>
       </c>
       <c r="D249" t="n">
-        <v>739.510009765625</v>
+        <v>743.010009765625</v>
       </c>
       <c r="E249" t="n">
-        <v>744.0999755859375</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="F249" t="n">
-        <v>30829200</v>
+        <v>34808500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B250" t="n">
-        <v>744.3599853515625</v>
+        <v>768.8499755859375</v>
       </c>
       <c r="C250" t="n">
-        <v>779.8200073242188</v>
+        <v>769.5700073242188</v>
       </c>
       <c r="D250" t="n">
-        <v>743.010009765625</v>
+        <v>746.5399780273438</v>
       </c>
       <c r="E250" t="n">
-        <v>777.5900268554688</v>
+        <v>751.6599731445312</v>
       </c>
       <c r="F250" t="n">
-        <v>34808500</v>
+        <v>25826700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B251" t="n">
-        <v>768.8499755859375</v>
+        <v>750.0399780273438</v>
       </c>
       <c r="C251" t="n">
-        <v>769.5700073242188</v>
+        <v>750.5800170898438</v>
       </c>
       <c r="D251" t="n">
-        <v>746.5399780273438</v>
+        <v>713.1900024414062</v>
       </c>
       <c r="E251" t="n">
-        <v>751.6599731445312</v>
+        <v>715.6199951171875</v>
       </c>
       <c r="F251" t="n">
-        <v>25826700</v>
+        <v>27943100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B252" t="n">
-        <v>750.0399780273438</v>
+        <v>725</v>
       </c>
       <c r="C252" t="n">
-        <v>750.5800170898438</v>
+        <v>740.4500122070312</v>
       </c>
       <c r="D252" t="n">
-        <v>713.1900024414062</v>
+        <v>715.0999755859375</v>
       </c>
       <c r="E252" t="n">
-        <v>715.6199951171875</v>
+        <v>738.7899780273438</v>
       </c>
       <c r="F252" t="n">
-        <v>27713500</v>
+        <v>23460100</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>738.79</v>
+      </c>
+      <c r="D2" t="n">
         <v>715.62</v>
       </c>
-      <c r="D2" t="n">
-        <v>751.66</v>
-      </c>
       <c r="E2" t="n">
-        <v>750.425</v>
+        <v>725.335</v>
       </c>
       <c r="F2" t="n">
-        <v>750.576</v>
+        <v>740.45</v>
       </c>
       <c r="G2" t="n">
-        <v>713.1900000000001</v>
+        <v>715.1</v>
       </c>
       <c r="H2" t="n">
-        <v>27629348</v>
+        <v>23034083</v>
       </c>
       <c r="I2" t="n">
-        <v>19942625</v>
+        <v>20031174</v>
       </c>
       <c r="J2" t="n">
-        <v>1823046369280</v>
+        <v>1882072023040</v>
       </c>
       <c r="K2" t="n">
-        <v>28.330166</v>
+        <v>26.9533</v>
       </c>
       <c r="L2" t="n">
-        <v>20.547644</v>
+        <v>21.128471</v>
       </c>
       <c r="M2" t="n">
-        <v>25.26</v>
+        <v>27.41</v>
       </c>
       <c r="N2" t="n">
         <v>779.8200000000001</v>
@@ -10818,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.9802966</v>
+        <v>7.206301</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1845104345088</v>
+        <v>1904130129920</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24:32</t>
+          <t>2026-09-30 16:06:58</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="n">
-        <v>739.740790143385</v>
+        <v>719.050911987213</v>
       </c>
       <c r="C2" t="n">
-        <v>740.4583269528289</v>
+        <v>719.4096803677126</v>
       </c>
       <c r="D2" t="n">
-        <v>723.8446976774693</v>
+        <v>707.7991010033351</v>
       </c>
       <c r="E2" t="n">
-        <v>731.8973999023438</v>
+        <v>714.9149780273438</v>
       </c>
       <c r="F2" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B3" t="n">
-        <v>719.050911987213</v>
+        <v>720.1372426569798</v>
       </c>
       <c r="C3" t="n">
-        <v>719.4096803677126</v>
+        <v>725.309699629413</v>
       </c>
       <c r="D3" t="n">
-        <v>707.7991010033351</v>
+        <v>715.7122502133443</v>
       </c>
       <c r="E3" t="n">
-        <v>714.9149780273438</v>
+        <v>724.5921020507812</v>
       </c>
       <c r="F3" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B4" t="n">
-        <v>720.1372426569798</v>
+        <v>727.1633750572937</v>
       </c>
       <c r="C4" t="n">
-        <v>725.309699629413</v>
+        <v>728.5287386889415</v>
       </c>
       <c r="D4" t="n">
-        <v>715.7122502133443</v>
+        <v>707.7791166979599</v>
       </c>
       <c r="E4" t="n">
-        <v>724.5921020507812</v>
+        <v>708.1578369140625</v>
       </c>
       <c r="F4" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B5" t="n">
-        <v>727.1634377305112</v>
+        <v>702.8060849901855</v>
       </c>
       <c r="C5" t="n">
-        <v>728.528801479838</v>
+        <v>714.456569002901</v>
       </c>
       <c r="D5" t="n">
-        <v>707.7791777004747</v>
+        <v>688.1757185011091</v>
       </c>
       <c r="E5" t="n">
-        <v>708.1578979492188</v>
+        <v>713.2406616210938</v>
       </c>
       <c r="F5" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B6" t="n">
-        <v>702.8060248479621</v>
+        <v>715.2936403041813</v>
       </c>
       <c r="C6" t="n">
-        <v>714.4565078636942</v>
+        <v>716.0710326272052</v>
       </c>
       <c r="D6" t="n">
-        <v>688.1756596108709</v>
+        <v>703.3641353885179</v>
       </c>
       <c r="E6" t="n">
-        <v>713.2406005859375</v>
+        <v>710.6693725585938</v>
       </c>
       <c r="F6" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B7" t="n">
-        <v>715.2937017364883</v>
+        <v>711.0381561100638</v>
       </c>
       <c r="C7" t="n">
-        <v>716.0710941262779</v>
+        <v>717.2172088427283</v>
       </c>
       <c r="D7" t="n">
-        <v>703.3641957962709</v>
+        <v>705.4172078341599</v>
       </c>
       <c r="E7" t="n">
-        <v>710.66943359375</v>
+        <v>715.413330078125</v>
       </c>
       <c r="F7" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B8" t="n">
-        <v>711.0380954481734</v>
+        <v>715.8518398810967</v>
       </c>
       <c r="C8" t="n">
-        <v>717.2171476536749</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="D8" t="n">
-        <v>705.4171476518181</v>
+        <v>710.0315555923428</v>
       </c>
       <c r="E8" t="n">
-        <v>715.4132690429688</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="F8" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B9" t="n">
-        <v>715.8517801132227</v>
+        <v>728.4490335307075</v>
       </c>
       <c r="C9" t="n">
-        <v>731.0302734375</v>
+        <v>732.784364410351</v>
       </c>
       <c r="D9" t="n">
-        <v>710.0314963104157</v>
+        <v>702.1283419878271</v>
       </c>
       <c r="E9" t="n">
-        <v>731.0302734375</v>
+        <v>702.9156494140625</v>
       </c>
       <c r="F9" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B10" t="n">
-        <v>728.4490335307075</v>
+        <v>710.5995481500918</v>
       </c>
       <c r="C10" t="n">
-        <v>732.784364410351</v>
+        <v>717.5061127097006</v>
       </c>
       <c r="D10" t="n">
-        <v>702.1283419878271</v>
+        <v>705.2477072901073</v>
       </c>
       <c r="E10" t="n">
-        <v>702.9156494140625</v>
+        <v>713.2804565429688</v>
       </c>
       <c r="F10" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B11" t="n">
-        <v>710.5996089558437</v>
+        <v>705.3872795195668</v>
       </c>
       <c r="C11" t="n">
-        <v>717.5061741064447</v>
+        <v>713.1309705798873</v>
       </c>
       <c r="D11" t="n">
-        <v>705.2477676379041</v>
+        <v>696.9658337653736</v>
       </c>
       <c r="E11" t="n">
-        <v>713.280517578125</v>
+        <v>706.2543334960938</v>
       </c>
       <c r="F11" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B12" t="n">
-        <v>705.3873404797914</v>
+        <v>714.6358727912688</v>
       </c>
       <c r="C12" t="n">
-        <v>713.1310322093289</v>
+        <v>721.4527759491865</v>
       </c>
       <c r="D12" t="n">
-        <v>696.9658939978091</v>
+        <v>707.1114088212217</v>
       </c>
       <c r="E12" t="n">
-        <v>706.25439453125</v>
+        <v>715.1242065429688</v>
       </c>
       <c r="F12" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B13" t="n">
-        <v>714.6359337847463</v>
+        <v>715.1242355877501</v>
       </c>
       <c r="C13" t="n">
-        <v>721.4528375244799</v>
+        <v>723.0373960268438</v>
       </c>
       <c r="D13" t="n">
-        <v>707.1114691724935</v>
+        <v>701.5004654735715</v>
       </c>
       <c r="E13" t="n">
-        <v>715.124267578125</v>
+        <v>709.6627807617188</v>
       </c>
       <c r="F13" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B14" t="n">
-        <v>715.1242970926235</v>
+        <v>704.6896374063629</v>
       </c>
       <c r="C14" t="n">
-        <v>723.0374582122953</v>
+        <v>716.1108563950927</v>
       </c>
       <c r="D14" t="n">
-        <v>701.5005258067208</v>
+        <v>703.7328609179003</v>
       </c>
       <c r="E14" t="n">
-        <v>709.662841796875</v>
+        <v>714.496337890625</v>
       </c>
       <c r="F14" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="n">
-        <v>704.6896374063629</v>
+        <v>718.7519624447335</v>
       </c>
       <c r="C15" t="n">
-        <v>716.1108563950927</v>
+        <v>731.2894517891565</v>
       </c>
       <c r="D15" t="n">
-        <v>703.7328609179003</v>
+        <v>717.7453670972193</v>
       </c>
       <c r="E15" t="n">
-        <v>714.496337890625</v>
+        <v>729.69482421875</v>
       </c>
       <c r="F15" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B16" t="n">
-        <v>718.7519624447335</v>
+        <v>733.5318410857864</v>
       </c>
       <c r="C16" t="n">
-        <v>731.2894517891565</v>
+        <v>736.0034377690635</v>
       </c>
       <c r="D16" t="n">
-        <v>717.7453670972193</v>
+        <v>726.2863984755653</v>
       </c>
       <c r="E16" t="n">
-        <v>729.69482421875</v>
+        <v>730.7911376953125</v>
       </c>
       <c r="F16" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B17" t="n">
-        <v>733.5318410857864</v>
+        <v>731.3492269695964</v>
       </c>
       <c r="C17" t="n">
-        <v>736.0034377690635</v>
+        <v>738.0962989037338</v>
       </c>
       <c r="D17" t="n">
-        <v>726.2863984755653</v>
+        <v>721.5823690736463</v>
       </c>
       <c r="E17" t="n">
-        <v>730.7911376953125</v>
+        <v>730.9306030273438</v>
       </c>
       <c r="F17" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B18" t="n">
-        <v>731.3492269695964</v>
+        <v>732.2162614456487</v>
       </c>
       <c r="C18" t="n">
-        <v>738.0962989037338</v>
+        <v>739.900157838395</v>
       </c>
       <c r="D18" t="n">
-        <v>721.5823690736463</v>
+        <v>730.6216339604061</v>
       </c>
       <c r="E18" t="n">
-        <v>730.9306030273438</v>
+        <v>731.5186157226562</v>
       </c>
       <c r="F18" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B19" t="n">
-        <v>732.2163225390138</v>
+        <v>734.2991309259364</v>
       </c>
       <c r="C19" t="n">
-        <v>739.9002195728755</v>
+        <v>738.704232141329</v>
       </c>
       <c r="D19" t="n">
-        <v>730.6216949207216</v>
+        <v>728.6782441600997</v>
       </c>
       <c r="E19" t="n">
-        <v>731.5186767578125</v>
+        <v>735.8638305664062</v>
       </c>
       <c r="F19" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B20" t="n">
-        <v>734.2991918313108</v>
+        <v>747.195457385242</v>
       </c>
       <c r="C20" t="n">
-        <v>738.7042934120783</v>
+        <v>753.1951257515892</v>
       </c>
       <c r="D20" t="n">
-        <v>728.6783045992579</v>
+        <v>745.4813011827554</v>
       </c>
       <c r="E20" t="n">
-        <v>735.8638916015625</v>
+        <v>748.2817993164062</v>
       </c>
       <c r="F20" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B21" t="n">
-        <v>747.1953964386955</v>
+        <v>750.0856988126538</v>
       </c>
       <c r="C21" t="n">
-        <v>753.1950643156673</v>
+        <v>755.8362124836232</v>
       </c>
       <c r="D21" t="n">
-        <v>745.4812403760276</v>
+        <v>742.9997491476457</v>
       </c>
       <c r="E21" t="n">
-        <v>748.28173828125</v>
+        <v>748.8997192382812</v>
       </c>
       <c r="F21" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B22" t="n">
-        <v>750.0856376808406</v>
+        <v>752.1985111114485</v>
       </c>
       <c r="C22" t="n">
-        <v>755.8361508831443</v>
+        <v>756.5935760115584</v>
       </c>
       <c r="D22" t="n">
-        <v>742.9996885933356</v>
+        <v>739.9998990805568</v>
       </c>
       <c r="E22" t="n">
-        <v>748.899658203125</v>
+        <v>749.12890625</v>
       </c>
       <c r="F22" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B23" t="n">
-        <v>752.1985111114485</v>
+        <v>666.8879125335289</v>
       </c>
       <c r="C23" t="n">
-        <v>756.5935760115584</v>
+        <v>678.6579855089774</v>
       </c>
       <c r="D23" t="n">
-        <v>739.9998990805568</v>
+        <v>647.9720344844721</v>
       </c>
       <c r="E23" t="n">
-        <v>749.12890625</v>
+        <v>664.2169189453125</v>
       </c>
       <c r="F23" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B24" t="n">
-        <v>666.8879125335289</v>
+        <v>672.2297387877188</v>
       </c>
       <c r="C24" t="n">
-        <v>678.6579855089774</v>
+        <v>672.6084590133829</v>
       </c>
       <c r="D24" t="n">
-        <v>647.9720344844721</v>
+        <v>643.3875718813117</v>
       </c>
       <c r="E24" t="n">
-        <v>664.2169189453125</v>
+        <v>646.1581420898438</v>
       </c>
       <c r="F24" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B25" t="n">
-        <v>672.22980228556</v>
+        <v>653.7823467127146</v>
       </c>
       <c r="C25" t="n">
-        <v>672.6085225469975</v>
+        <v>657.1011064498967</v>
       </c>
       <c r="D25" t="n">
-        <v>643.3876326547638</v>
+        <v>634.0293422915395</v>
       </c>
       <c r="E25" t="n">
-        <v>646.158203125</v>
+        <v>635.55419921875</v>
       </c>
       <c r="F25" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B26" t="n">
-        <v>653.7823467127146</v>
+        <v>625.9168165443936</v>
       </c>
       <c r="C26" t="n">
-        <v>657.1011064498967</v>
+        <v>639.5705142822006</v>
       </c>
       <c r="D26" t="n">
-        <v>634.0293422915395</v>
+        <v>623.8937108241939</v>
       </c>
       <c r="E26" t="n">
-        <v>635.55419921875</v>
+        <v>625.1992797851562</v>
       </c>
       <c r="F26" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>625.9168165443936</v>
+        <v>630.1724007040705</v>
       </c>
       <c r="C27" t="n">
-        <v>639.5705142822006</v>
+        <v>640.0588479681868</v>
       </c>
       <c r="D27" t="n">
-        <v>623.8937108241939</v>
+        <v>624.4218873891514</v>
       </c>
       <c r="E27" t="n">
-        <v>625.1992797851562</v>
+        <v>633.8001098632812</v>
       </c>
       <c r="F27" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B28" t="n">
-        <v>630.1724007040705</v>
+        <v>633.7004019945108</v>
       </c>
       <c r="C28" t="n">
-        <v>640.0588479681868</v>
+        <v>633.8499192315176</v>
       </c>
       <c r="D28" t="n">
-        <v>624.4218873891514</v>
+        <v>615.9107705740217</v>
       </c>
       <c r="E28" t="n">
-        <v>633.8001098632812</v>
+        <v>616.8475952148438</v>
       </c>
       <c r="F28" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B29" t="n">
-        <v>633.7004019945108</v>
+        <v>614.4058308842617</v>
       </c>
       <c r="C29" t="n">
-        <v>633.8499192315176</v>
+        <v>620.0267784116583</v>
       </c>
       <c r="D29" t="n">
-        <v>615.9107705740217</v>
+        <v>599.1675434782962</v>
       </c>
       <c r="E29" t="n">
-        <v>616.8475952148438</v>
+        <v>619.6082153320312</v>
       </c>
       <c r="F29" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B30" t="n">
-        <v>614.4058308842617</v>
+        <v>628.9565496273584</v>
       </c>
       <c r="C30" t="n">
-        <v>620.0267784116583</v>
+        <v>632.8533046281837</v>
       </c>
       <c r="D30" t="n">
-        <v>599.1675434782962</v>
+        <v>616.0203887455347</v>
       </c>
       <c r="E30" t="n">
-        <v>619.6082153320312</v>
+        <v>629.624267578125</v>
       </c>
       <c r="F30" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B31" t="n">
-        <v>628.9565496273584</v>
+        <v>625.8769557835792</v>
       </c>
       <c r="C31" t="n">
-        <v>632.8533046281837</v>
+        <v>627.431679546322</v>
       </c>
       <c r="D31" t="n">
-        <v>616.0203887455347</v>
+        <v>617.29607772438</v>
       </c>
       <c r="E31" t="n">
-        <v>629.624267578125</v>
+        <v>624.9600830078125</v>
       </c>
       <c r="F31" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B32" t="n">
-        <v>625.8770169082796</v>
+        <v>626.0065293511232</v>
       </c>
       <c r="C32" t="n">
-        <v>627.4317408228605</v>
+        <v>626.8636074098682</v>
       </c>
       <c r="D32" t="n">
-        <v>617.2961380110504</v>
+        <v>605.7153735895874</v>
       </c>
       <c r="E32" t="n">
-        <v>624.9601440429688</v>
+        <v>606.951171875</v>
       </c>
       <c r="F32" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B33" t="n">
-        <v>626.0065293511232</v>
+        <v>610.9974896015757</v>
       </c>
       <c r="C33" t="n">
-        <v>626.8636074098682</v>
+        <v>615.5620236854409</v>
       </c>
       <c r="D33" t="n">
-        <v>605.7153735895874</v>
+        <v>600.9615245048305</v>
       </c>
       <c r="E33" t="n">
-        <v>606.951171875</v>
+        <v>607.8282470703125</v>
       </c>
       <c r="F33" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B34" t="n">
-        <v>610.9974896015757</v>
+        <v>599.7555439005879</v>
       </c>
       <c r="C34" t="n">
-        <v>615.5620236854409</v>
+        <v>611.6053627125183</v>
       </c>
       <c r="D34" t="n">
-        <v>600.9615245048305</v>
+        <v>593.1878563697925</v>
       </c>
       <c r="E34" t="n">
-        <v>607.8282470703125</v>
+        <v>607.399658203125</v>
       </c>
       <c r="F34" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B35" t="n">
-        <v>599.7556041676178</v>
+        <v>606.9810562524968</v>
       </c>
       <c r="C35" t="n">
-        <v>611.6054241702889</v>
+        <v>609.6221219886945</v>
       </c>
       <c r="D35" t="n">
-        <v>593.1879159768617</v>
+        <v>593.3872138938384</v>
       </c>
       <c r="E35" t="n">
-        <v>607.3997192382812</v>
+        <v>599.974853515625</v>
       </c>
       <c r="F35" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B36" t="n">
-        <v>606.980994504603</v>
+        <v>589.5999948667346</v>
       </c>
       <c r="C36" t="n">
-        <v>609.6220599721263</v>
+        <v>601.619222033871</v>
       </c>
       <c r="D36" t="n">
-        <v>593.3871535288397</v>
+        <v>581.8064849239344</v>
       </c>
       <c r="E36" t="n">
-        <v>599.9747924804688</v>
+        <v>595.66943359375</v>
       </c>
       <c r="F36" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B37" t="n">
-        <v>589.5999948667346</v>
+        <v>591.7128101062766</v>
       </c>
       <c r="C37" t="n">
-        <v>601.619222033871</v>
+        <v>593.3174134864839</v>
       </c>
       <c r="D37" t="n">
-        <v>581.8064849239344</v>
+        <v>579.2849960343485</v>
       </c>
       <c r="E37" t="n">
-        <v>595.66943359375</v>
+        <v>588.3243408203125</v>
       </c>
       <c r="F37" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B38" t="n">
-        <v>591.7128101062766</v>
+        <v>601.4598513214113</v>
       </c>
       <c r="C38" t="n">
-        <v>593.3174134864839</v>
+        <v>604.668936823252</v>
       </c>
       <c r="D38" t="n">
-        <v>579.2849960343485</v>
+        <v>581.3779446301025</v>
       </c>
       <c r="E38" t="n">
-        <v>588.3243408203125</v>
+        <v>587.1583862304688</v>
       </c>
       <c r="F38" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B39" t="n">
-        <v>601.4597887996167</v>
+        <v>586.5104667718139</v>
       </c>
       <c r="C39" t="n">
-        <v>604.6688739678727</v>
+        <v>596.097939714081</v>
       </c>
       <c r="D39" t="n">
-        <v>581.3778841958236</v>
+        <v>579.8928999224906</v>
       </c>
       <c r="E39" t="n">
-        <v>587.1583251953125</v>
+        <v>592.2410278320312</v>
       </c>
       <c r="F39" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B40" t="n">
-        <v>586.5105876609664</v>
+        <v>596.6959057641074</v>
       </c>
       <c r="C40" t="n">
-        <v>596.0980625793645</v>
+        <v>614.6151629725317</v>
       </c>
       <c r="D40" t="n">
-        <v>579.8930194476571</v>
+        <v>595.609624740878</v>
       </c>
       <c r="E40" t="n">
-        <v>592.2411499023438</v>
+        <v>610.9774780273438</v>
       </c>
       <c r="F40" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B41" t="n">
-        <v>596.6959057641074</v>
+        <v>621.8904932046078</v>
       </c>
       <c r="C41" t="n">
-        <v>614.6151629725317</v>
+        <v>634.8963639496133</v>
       </c>
       <c r="D41" t="n">
-        <v>595.609624740878</v>
+        <v>616.209750572071</v>
       </c>
       <c r="E41" t="n">
-        <v>610.9774780273438</v>
+        <v>634.0691528320312</v>
       </c>
       <c r="F41" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B42" t="n">
-        <v>621.8904932046078</v>
+        <v>635.5342418532664</v>
       </c>
       <c r="C42" t="n">
-        <v>634.8963639496133</v>
+        <v>636.2019598341516</v>
       </c>
       <c r="D42" t="n">
-        <v>616.209750572071</v>
+        <v>629.4947305871518</v>
       </c>
       <c r="E42" t="n">
-        <v>634.0691528320312</v>
+        <v>631.468017578125</v>
       </c>
       <c r="F42" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B43" t="n">
-        <v>635.5341804250853</v>
+        <v>633.9296546389559</v>
       </c>
       <c r="C43" t="n">
-        <v>636.2018983414315</v>
+        <v>645.8591590880771</v>
       </c>
       <c r="D43" t="n">
-        <v>629.4946697427255</v>
+        <v>633.3515983825566</v>
       </c>
       <c r="E43" t="n">
-        <v>631.4679565429688</v>
+        <v>645.759521484375</v>
       </c>
       <c r="F43" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B44" t="n">
-        <v>633.9296546389559</v>
+        <v>637.3879462598147</v>
       </c>
       <c r="C44" t="n">
-        <v>645.8591590880771</v>
+        <v>643.138459853903</v>
       </c>
       <c r="D44" t="n">
-        <v>633.3515983825566</v>
+        <v>635.6040193729798</v>
       </c>
       <c r="E44" t="n">
-        <v>645.759521484375</v>
+        <v>638.7034912109375</v>
       </c>
       <c r="F44" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B45" t="n">
-        <v>637.3878853503733</v>
+        <v>640.1684965318557</v>
       </c>
       <c r="C45" t="n">
-        <v>643.1383983949365</v>
+        <v>645.6797698761368</v>
       </c>
       <c r="D45" t="n">
-        <v>635.6039586340122</v>
+        <v>635.9129124654792</v>
       </c>
       <c r="E45" t="n">
-        <v>638.7034301757812</v>
+        <v>644.912353515625</v>
       </c>
       <c r="F45" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B46" t="n">
-        <v>640.1684965318557</v>
+        <v>642.2315425173783</v>
       </c>
       <c r="C46" t="n">
-        <v>645.6797698761368</v>
+        <v>646.6565355118391</v>
       </c>
       <c r="D46" t="n">
-        <v>635.9129124654792</v>
+        <v>635.394747375177</v>
       </c>
       <c r="E46" t="n">
-        <v>644.912353515625</v>
+        <v>637.4378051757812</v>
       </c>
       <c r="F46" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B47" t="n">
-        <v>642.2314810232181</v>
+        <v>673.7146932031604</v>
       </c>
       <c r="C47" t="n">
-        <v>646.6564735939825</v>
+        <v>673.8143308084973</v>
       </c>
       <c r="D47" t="n">
-        <v>635.3946865356451</v>
+        <v>657.8186021075292</v>
       </c>
       <c r="E47" t="n">
-        <v>637.437744140625</v>
+        <v>659.2936401367188</v>
       </c>
       <c r="F47" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B48" t="n">
-        <v>673.7147555733686</v>
+        <v>661.7552947151958</v>
       </c>
       <c r="C48" t="n">
-        <v>673.8143931879296</v>
+        <v>672.4091587454953</v>
       </c>
       <c r="D48" t="n">
-        <v>657.8186630061315</v>
+        <v>660.1507520483126</v>
       </c>
       <c r="E48" t="n">
-        <v>659.293701171875</v>
+        <v>671.1434326171875</v>
       </c>
       <c r="F48" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B49" t="n">
-        <v>661.7553548965755</v>
+        <v>667.0772284693074</v>
       </c>
       <c r="C49" t="n">
-        <v>672.4092198957593</v>
+        <v>674.4223082782987</v>
       </c>
       <c r="D49" t="n">
-        <v>660.1508120837719</v>
+        <v>662.8216443414645</v>
       </c>
       <c r="E49" t="n">
-        <v>671.1434936523438</v>
+        <v>664.5457763671875</v>
       </c>
       <c r="F49" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B50" t="n">
-        <v>667.0772284693074</v>
+        <v>661.5260500954003</v>
       </c>
       <c r="C50" t="n">
-        <v>674.4223082782987</v>
+        <v>662.2336109084633</v>
       </c>
       <c r="D50" t="n">
-        <v>662.8216443414645</v>
+        <v>651.1313175008097</v>
       </c>
       <c r="E50" t="n">
-        <v>664.5457763671875</v>
+        <v>654.7390747070312</v>
       </c>
       <c r="F50" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B51" t="n">
-        <v>661.5261117632423</v>
+        <v>647.7527447265774</v>
       </c>
       <c r="C51" t="n">
-        <v>662.2336726422647</v>
+        <v>652.2973264314004</v>
       </c>
       <c r="D51" t="n">
-        <v>651.1313781996487</v>
+        <v>641.2249002906431</v>
       </c>
       <c r="E51" t="n">
-        <v>654.7391357421875</v>
+        <v>647.93212890625</v>
       </c>
       <c r="F51" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B52" t="n">
-        <v>647.7528057448357</v>
+        <v>641.1152803360264</v>
       </c>
       <c r="C52" t="n">
-        <v>652.297387877758</v>
+        <v>653.0647981949571</v>
       </c>
       <c r="D52" t="n">
-        <v>641.2249606939789</v>
+        <v>638.6337077300913</v>
       </c>
       <c r="E52" t="n">
-        <v>647.9321899414062</v>
+        <v>650.5034790039062</v>
       </c>
       <c r="F52" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B53" t="n">
-        <v>641.1152803360264</v>
+        <v>647.6033016180266</v>
       </c>
       <c r="C53" t="n">
-        <v>653.0647981949571</v>
+        <v>708.5964236692454</v>
       </c>
       <c r="D53" t="n">
-        <v>638.6337077300913</v>
+        <v>636.4511276224844</v>
       </c>
       <c r="E53" t="n">
-        <v>650.5034790039062</v>
+        <v>642.0521240234375</v>
       </c>
       <c r="F53" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,25 +1821,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B54" t="n">
-        <v>647.603240055161</v>
+        <v>644.0420011784053</v>
       </c>
       <c r="C54" t="n">
-        <v>708.5963563082138</v>
+        <v>651.3232442601446</v>
       </c>
       <c r="D54" t="n">
-        <v>636.4510671197735</v>
+        <v>637.0599755890928</v>
       </c>
       <c r="E54" t="n">
-        <v>642.0520629882812</v>
+        <v>645.8473510742188</v>
       </c>
       <c r="F54" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1847,25 +1847,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B55" t="n">
-        <v>644.0420011784053</v>
+        <v>641.8476715248971</v>
       </c>
       <c r="C55" t="n">
-        <v>651.3232442601446</v>
+        <v>660.8387602004772</v>
       </c>
       <c r="D55" t="n">
-        <v>637.0599755890928</v>
+        <v>641.5484540168895</v>
       </c>
       <c r="E55" t="n">
-        <v>645.8473510742188</v>
+        <v>655.462646484375</v>
       </c>
       <c r="F55" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G55" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B56" t="n">
-        <v>641.8476715248971</v>
+        <v>653.9265104909302</v>
       </c>
       <c r="C56" t="n">
-        <v>660.8387602004772</v>
+        <v>659.5320745885969</v>
       </c>
       <c r="D56" t="n">
-        <v>641.5484540168895</v>
+        <v>647.5329968709444</v>
       </c>
       <c r="E56" t="n">
-        <v>655.462646484375</v>
+        <v>647.8322143554688</v>
       </c>
       <c r="F56" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B57" t="n">
-        <v>653.9265721002572</v>
+        <v>655.3429055936973</v>
       </c>
       <c r="C57" t="n">
-        <v>659.5321367260491</v>
+        <v>668.8381315618529</v>
       </c>
       <c r="D57" t="n">
-        <v>647.5330578779101</v>
+        <v>654.7743619360156</v>
       </c>
       <c r="E57" t="n">
-        <v>647.832275390625</v>
+        <v>662.7438354492188</v>
       </c>
       <c r="F57" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B58" t="n">
-        <v>655.3429055936973</v>
+        <v>664.7087499822148</v>
       </c>
       <c r="C58" t="n">
-        <v>668.8381315618529</v>
+        <v>669.2770065062657</v>
       </c>
       <c r="D58" t="n">
-        <v>654.7743619360156</v>
+        <v>656.4899183910027</v>
       </c>
       <c r="E58" t="n">
-        <v>662.7438354492188</v>
+        <v>657.0784301757812</v>
       </c>
       <c r="F58" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B59" t="n">
-        <v>664.7087499822148</v>
+        <v>659.9510918299604</v>
       </c>
       <c r="C59" t="n">
-        <v>669.2770065062657</v>
+        <v>671.8504516144289</v>
       </c>
       <c r="D59" t="n">
-        <v>656.4899183910027</v>
+        <v>654.9639304343692</v>
       </c>
       <c r="E59" t="n">
-        <v>657.0784301757812</v>
+        <v>659.8014526367188</v>
       </c>
       <c r="F59" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B60" t="n">
-        <v>659.9510307809619</v>
+        <v>658.3550860644432</v>
       </c>
       <c r="C60" t="n">
-        <v>671.850389464676</v>
+        <v>664.2898196014329</v>
       </c>
       <c r="D60" t="n">
-        <v>654.9638698467097</v>
+        <v>656.5597203493141</v>
       </c>
       <c r="E60" t="n">
-        <v>659.8013916015625</v>
+        <v>663.2325439453125</v>
       </c>
       <c r="F60" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B61" t="n">
-        <v>658.3551466507428</v>
+        <v>660.8288080412273</v>
       </c>
       <c r="C61" t="n">
-        <v>664.2898807338869</v>
+        <v>666.4642636433252</v>
       </c>
       <c r="D61" t="n">
-        <v>656.559780770392</v>
+        <v>660.499638357634</v>
       </c>
       <c r="E61" t="n">
-        <v>663.2326049804688</v>
+        <v>665.8358764648438</v>
       </c>
       <c r="F61" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B62" t="n">
-        <v>660.8287474650539</v>
+        <v>666.3446246130748</v>
       </c>
       <c r="C62" t="n">
-        <v>666.4642025505667</v>
+        <v>667.2323539771746</v>
       </c>
       <c r="D62" t="n">
-        <v>660.4995778116346</v>
+        <v>659.6219406041037</v>
       </c>
       <c r="E62" t="n">
-        <v>665.8358154296875</v>
+        <v>661.5868530273438</v>
       </c>
       <c r="F62" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B63" t="n">
-        <v>666.3445631389869</v>
+        <v>656.3204105957403</v>
       </c>
       <c r="C63" t="n">
-        <v>667.2322924211887</v>
+        <v>658.5546491157273</v>
       </c>
       <c r="D63" t="n">
-        <v>659.6218797502219</v>
+        <v>652.7097106878265</v>
       </c>
       <c r="E63" t="n">
-        <v>661.5867919921875</v>
+        <v>656.9986572265625</v>
       </c>
       <c r="F63" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B64" t="n">
-        <v>656.3204105957403</v>
+        <v>656.9986226731097</v>
       </c>
       <c r="C64" t="n">
-        <v>658.5546491157273</v>
+        <v>670.4938487731155</v>
       </c>
       <c r="D64" t="n">
-        <v>652.7097106878265</v>
+        <v>656.1508296487782</v>
       </c>
       <c r="E64" t="n">
-        <v>656.9986572265625</v>
+        <v>664.239990234375</v>
       </c>
       <c r="F64" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B65" t="n">
-        <v>656.9986830428769</v>
+        <v>663.0430265979899</v>
       </c>
       <c r="C65" t="n">
-        <v>670.4939103829213</v>
+        <v>663.2923846373272</v>
       </c>
       <c r="D65" t="n">
-        <v>656.1508899406441</v>
+        <v>657.7466642776019</v>
       </c>
       <c r="E65" t="n">
-        <v>664.2400512695312</v>
+        <v>658.39501953125</v>
       </c>
       <c r="F65" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B66" t="n">
-        <v>663.0430880640301</v>
+        <v>661.0282405096659</v>
       </c>
       <c r="C66" t="n">
-        <v>663.2924461264837</v>
+        <v>662.6840120988863</v>
       </c>
       <c r="D66" t="n">
-        <v>657.7467252526537</v>
+        <v>641.8476382600104</v>
       </c>
       <c r="E66" t="n">
-        <v>658.3950805664062</v>
+        <v>648.7398681640625</v>
       </c>
       <c r="F66" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B67" t="n">
-        <v>661.0282405096659</v>
+        <v>649.3383972038786</v>
       </c>
       <c r="C67" t="n">
-        <v>662.6840120988863</v>
+        <v>662.8336242718107</v>
       </c>
       <c r="D67" t="n">
-        <v>641.8476382600104</v>
+        <v>646.086758236235</v>
       </c>
       <c r="E67" t="n">
-        <v>648.7398681640625</v>
+        <v>657.098388671875</v>
       </c>
       <c r="F67" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B68" t="n">
-        <v>649.338336889516</v>
+        <v>657.8763534012292</v>
       </c>
       <c r="C68" t="n">
-        <v>662.8335627039321</v>
+        <v>663.8110870761799</v>
       </c>
       <c r="D68" t="n">
-        <v>646.0866982239037</v>
+        <v>650.2260655901538</v>
       </c>
       <c r="E68" t="n">
-        <v>657.0983276367188</v>
+        <v>658.9236450195312</v>
       </c>
       <c r="F68" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B69" t="n">
-        <v>657.8763534012292</v>
+        <v>653.956457912222</v>
       </c>
       <c r="C69" t="n">
-        <v>663.8110870761799</v>
+        <v>657.4574546517152</v>
       </c>
       <c r="D69" t="n">
-        <v>650.2260655901538</v>
+        <v>643.154250211399</v>
       </c>
       <c r="E69" t="n">
-        <v>658.9236450195312</v>
+        <v>647.0242919921875</v>
       </c>
       <c r="F69" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B70" t="n">
-        <v>653.956457912222</v>
+        <v>644.2215315163064</v>
       </c>
       <c r="C70" t="n">
-        <v>657.4574546517152</v>
+        <v>645.4383696113561</v>
       </c>
       <c r="D70" t="n">
-        <v>643.154250211399</v>
+        <v>634.0875860000896</v>
       </c>
       <c r="E70" t="n">
-        <v>647.0242919921875</v>
+        <v>644.4010620117188</v>
       </c>
       <c r="F70" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B71" t="n">
-        <v>644.2215315163064</v>
+        <v>643.7826886268982</v>
       </c>
       <c r="C71" t="n">
-        <v>645.4383696113561</v>
+        <v>653.2682792823022</v>
       </c>
       <c r="D71" t="n">
-        <v>634.0875860000896</v>
+        <v>641.1993122536916</v>
       </c>
       <c r="E71" t="n">
-        <v>644.4010620117188</v>
+        <v>651.3831176757812</v>
       </c>
       <c r="F71" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B72" t="n">
-        <v>643.7826886268982</v>
+        <v>650.8544758921091</v>
       </c>
       <c r="C72" t="n">
-        <v>653.2682792823022</v>
+        <v>652.2907198459545</v>
       </c>
       <c r="D72" t="n">
-        <v>641.1993122536916</v>
+        <v>639.5834431006995</v>
       </c>
       <c r="E72" t="n">
-        <v>651.3831176757812</v>
+        <v>640.321533203125</v>
       </c>
       <c r="F72" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B73" t="n">
-        <v>650.8544758921091</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="C73" t="n">
-        <v>652.2907198459545</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="D73" t="n">
-        <v>639.5834431006995</v>
+        <v>622.4974409136</v>
       </c>
       <c r="E73" t="n">
-        <v>640.321533203125</v>
+        <v>629.4695434570312</v>
       </c>
       <c r="F73" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B74" t="n">
-        <v>640.6208286715078</v>
+        <v>624.8913007155408</v>
       </c>
       <c r="C74" t="n">
-        <v>640.6208286715078</v>
+        <v>626.836305766559</v>
       </c>
       <c r="D74" t="n">
-        <v>622.4974409136</v>
+        <v>613.2412994138377</v>
       </c>
       <c r="E74" t="n">
-        <v>629.4695434570312</v>
+        <v>613.9395141601562</v>
       </c>
       <c r="F74" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B75" t="n">
-        <v>624.8913007155408</v>
+        <v>616.8918824768537</v>
       </c>
       <c r="C75" t="n">
-        <v>626.836305766559</v>
+        <v>622.567274451088</v>
       </c>
       <c r="D75" t="n">
-        <v>613.2412994138377</v>
+        <v>612.6527953870184</v>
       </c>
       <c r="E75" t="n">
-        <v>613.9395141601562</v>
+        <v>619.2059326171875</v>
       </c>
       <c r="F75" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B76" t="n">
-        <v>616.8918216697934</v>
+        <v>622.5772500418334</v>
       </c>
       <c r="C76" t="n">
-        <v>622.5672130846042</v>
+        <v>627.4646923832119</v>
       </c>
       <c r="D76" t="n">
-        <v>612.6527349978052</v>
+        <v>618.4878021974878</v>
       </c>
       <c r="E76" t="n">
-        <v>619.2058715820312</v>
+        <v>618.6573486328125</v>
       </c>
       <c r="F76" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B77" t="n">
-        <v>622.5772500418334</v>
+        <v>606.3191417499893</v>
       </c>
       <c r="C77" t="n">
-        <v>627.4646923832119</v>
+        <v>609.8301228712422</v>
       </c>
       <c r="D77" t="n">
-        <v>618.4878021974878</v>
+        <v>598.4593704807342</v>
       </c>
       <c r="E77" t="n">
-        <v>618.6573486328125</v>
+        <v>602.5687866210938</v>
       </c>
       <c r="F77" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B78" t="n">
-        <v>606.3191417499893</v>
+        <v>605.1820479992876</v>
       </c>
       <c r="C78" t="n">
-        <v>609.8301228712422</v>
+        <v>616.6824713366042</v>
       </c>
       <c r="D78" t="n">
-        <v>598.4593704807342</v>
+        <v>598.5391758430108</v>
       </c>
       <c r="E78" t="n">
-        <v>602.5687866210938</v>
+        <v>611.3861083984375</v>
       </c>
       <c r="F78" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B79" t="n">
-        <v>605.1820479992876</v>
+        <v>627.7339506004921</v>
       </c>
       <c r="C79" t="n">
-        <v>616.6824713366042</v>
+        <v>658.8738165275513</v>
       </c>
       <c r="D79" t="n">
-        <v>598.5391758430108</v>
+        <v>624.9411525277235</v>
       </c>
       <c r="E79" t="n">
-        <v>611.3861083984375</v>
+        <v>645.967041015625</v>
       </c>
       <c r="F79" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B80" t="n">
-        <v>627.7339506004921</v>
+        <v>643.1144139511335</v>
       </c>
       <c r="C80" t="n">
-        <v>658.8738165275513</v>
+        <v>664.7786132883346</v>
       </c>
       <c r="D80" t="n">
-        <v>624.9411525277235</v>
+        <v>642.7952283244125</v>
       </c>
       <c r="E80" t="n">
-        <v>645.967041015625</v>
+        <v>657.0684814453125</v>
       </c>
       <c r="F80" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B81" t="n">
-        <v>643.114354212172</v>
+        <v>663.4220687284304</v>
       </c>
       <c r="C81" t="n">
-        <v>664.7785515369834</v>
+        <v>673.5460296758964</v>
       </c>
       <c r="D81" t="n">
-        <v>642.7951686151001</v>
+        <v>659.5919023824141</v>
       </c>
       <c r="E81" t="n">
-        <v>657.0684204101562</v>
+        <v>670.6334838867188</v>
       </c>
       <c r="F81" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B82" t="n">
-        <v>663.4220687284304</v>
+        <v>672.8578395915863</v>
       </c>
       <c r="C82" t="n">
-        <v>673.5460296758964</v>
+        <v>675.0820939991542</v>
       </c>
       <c r="D82" t="n">
-        <v>659.5919023824141</v>
+        <v>662.9532839044604</v>
       </c>
       <c r="E82" t="n">
-        <v>670.6334838867188</v>
+        <v>671.241943359375</v>
       </c>
       <c r="F82" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B83" t="n">
-        <v>672.8577784094987</v>
+        <v>672.7679591112906</v>
       </c>
       <c r="C83" t="n">
-        <v>675.082032614818</v>
+        <v>675.9397859199995</v>
       </c>
       <c r="D83" t="n">
-        <v>662.9532236229811</v>
+        <v>664.3895050245095</v>
       </c>
       <c r="E83" t="n">
-        <v>671.2418823242188</v>
+        <v>667.0127563476562</v>
       </c>
       <c r="F83" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B84" t="n">
-        <v>672.768020673078</v>
+        <v>735.536439340887</v>
       </c>
       <c r="C84" t="n">
-        <v>675.9398477720257</v>
+        <v>742.0895763731422</v>
       </c>
       <c r="D84" t="n">
-        <v>664.3895658196245</v>
+        <v>710.7203206800697</v>
       </c>
       <c r="E84" t="n">
-        <v>667.0128173828125</v>
+        <v>736.4141845703125</v>
       </c>
       <c r="F84" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B85" t="n">
-        <v>735.536439340887</v>
+        <v>725.6319102189462</v>
       </c>
       <c r="C85" t="n">
-        <v>742.0895763731422</v>
+        <v>730.2899014488934</v>
       </c>
       <c r="D85" t="n">
-        <v>710.7203206800697</v>
+        <v>711.7576553956329</v>
       </c>
       <c r="E85" t="n">
-        <v>736.4141845703125</v>
+        <v>714.66015625</v>
       </c>
       <c r="F85" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B86" t="n">
-        <v>725.6319721911391</v>
+        <v>712.7649799285471</v>
       </c>
       <c r="C86" t="n">
-        <v>730.2899638188994</v>
+        <v>719.4477874144414</v>
       </c>
       <c r="D86" t="n">
-        <v>711.7577161829028</v>
+        <v>701.7134756957726</v>
       </c>
       <c r="E86" t="n">
-        <v>714.6602172851562</v>
+        <v>704.5960083007812</v>
       </c>
       <c r="F86" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B87" t="n">
-        <v>712.7650416713351</v>
+        <v>705.5535728195721</v>
       </c>
       <c r="C87" t="n">
-        <v>719.4478497361232</v>
+        <v>715.1588492636382</v>
       </c>
       <c r="D87" t="n">
-        <v>701.7135364812315</v>
+        <v>684.6473731061755</v>
       </c>
       <c r="E87" t="n">
-        <v>704.5960693359375</v>
+        <v>689.923828125</v>
       </c>
       <c r="F87" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B88" t="n">
-        <v>705.5536352374374</v>
+        <v>685.9640881387202</v>
       </c>
       <c r="C88" t="n">
-        <v>715.1589125312489</v>
+        <v>687.0613001828912</v>
       </c>
       <c r="D88" t="n">
-        <v>684.6474336745422</v>
+        <v>665.7461770525908</v>
       </c>
       <c r="E88" t="n">
-        <v>689.9238891601562</v>
+        <v>667.272216796875</v>
       </c>
       <c r="F88" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B89" t="n">
-        <v>685.964025393825</v>
+        <v>661.8760941724082</v>
       </c>
       <c r="C89" t="n">
-        <v>687.0612373376343</v>
+        <v>679.7500626324993</v>
       </c>
       <c r="D89" t="n">
-        <v>665.7461161570209</v>
+        <v>651.8219602792932</v>
       </c>
       <c r="E89" t="n">
-        <v>667.2721557617188</v>
+        <v>668.4890747070312</v>
       </c>
       <c r="F89" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B90" t="n">
-        <v>661.8760941724082</v>
+        <v>663.7811558190369</v>
       </c>
       <c r="C90" t="n">
-        <v>679.7500626324993</v>
+        <v>670.2644652243433</v>
       </c>
       <c r="D90" t="n">
-        <v>651.8219602792932</v>
+        <v>644.8399277739295</v>
       </c>
       <c r="E90" t="n">
-        <v>668.4890747070312</v>
+        <v>659.7615356445312</v>
       </c>
       <c r="F90" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B91" t="n">
-        <v>663.781217226052</v>
+        <v>661.4770916291903</v>
       </c>
       <c r="C91" t="n">
-        <v>670.2645272311354</v>
+        <v>681.5554070660584</v>
       </c>
       <c r="D91" t="n">
-        <v>644.8399874286738</v>
+        <v>657.0884263930592</v>
       </c>
       <c r="E91" t="n">
-        <v>659.7615966796875</v>
+        <v>675.4810180664062</v>
       </c>
       <c r="F91" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B92" t="n">
-        <v>661.4770916291903</v>
+        <v>675.8600189134125</v>
       </c>
       <c r="C92" t="n">
-        <v>681.5554070660584</v>
+        <v>678.9022357565889</v>
       </c>
       <c r="D92" t="n">
-        <v>657.0884263930592</v>
+        <v>668.0700760446862</v>
       </c>
       <c r="E92" t="n">
-        <v>675.4810180664062</v>
+        <v>668.9976806640625</v>
       </c>
       <c r="F92" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B93" t="n">
-        <v>675.8600189134125</v>
+        <v>672.2693241407737</v>
       </c>
       <c r="C93" t="n">
-        <v>678.9022357565889</v>
+        <v>677.5258114827353</v>
       </c>
       <c r="D93" t="n">
-        <v>668.0700760446862</v>
+        <v>655.4126950742984</v>
       </c>
       <c r="E93" t="n">
-        <v>668.9976806640625</v>
+        <v>666.9729614257812</v>
       </c>
       <c r="F93" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B94" t="n">
-        <v>672.2693241407737</v>
+        <v>668.2496249159107</v>
       </c>
       <c r="C94" t="n">
-        <v>677.5258114827353</v>
+        <v>674.2641703314905</v>
       </c>
       <c r="D94" t="n">
-        <v>655.4126950742984</v>
+        <v>643.6230822268304</v>
       </c>
       <c r="E94" t="n">
-        <v>666.9729614257812</v>
+        <v>648.1414184570312</v>
       </c>
       <c r="F94" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B95" t="n">
-        <v>668.2496878446467</v>
+        <v>643.4434668857905</v>
       </c>
       <c r="C95" t="n">
-        <v>674.2642338266133</v>
+        <v>649.7572295518577</v>
       </c>
       <c r="D95" t="n">
-        <v>643.6231428364971</v>
+        <v>632.9405378190771</v>
       </c>
       <c r="E95" t="n">
-        <v>648.1414794921875</v>
+        <v>638.127197265625</v>
       </c>
       <c r="F95" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B96" t="n">
-        <v>643.4434668857905</v>
+        <v>637.8579201875249</v>
       </c>
       <c r="C96" t="n">
-        <v>649.7572295518577</v>
+        <v>640.9499357932766</v>
       </c>
       <c r="D96" t="n">
-        <v>632.9405378190771</v>
+        <v>627.1853829985365</v>
       </c>
       <c r="E96" t="n">
-        <v>638.127197265625</v>
+        <v>637.6484375</v>
       </c>
       <c r="F96" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B97" t="n">
-        <v>637.8578591323172</v>
+        <v>632.1725042393389</v>
       </c>
       <c r="C97" t="n">
-        <v>640.9498744421038</v>
+        <v>643.3437568439427</v>
       </c>
       <c r="D97" t="n">
-        <v>627.1853229648948</v>
+        <v>626.5370489428796</v>
       </c>
       <c r="E97" t="n">
-        <v>637.6483764648438</v>
+        <v>641.5682983398438</v>
       </c>
       <c r="F97" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B98" t="n">
-        <v>632.1725643806327</v>
+        <v>636.9302530675583</v>
       </c>
       <c r="C98" t="n">
-        <v>643.3438180480059</v>
+        <v>645.5281132997313</v>
       </c>
       <c r="D98" t="n">
-        <v>626.5371085480483</v>
+        <v>635.0849670695593</v>
       </c>
       <c r="E98" t="n">
-        <v>641.568359375</v>
+        <v>643.1243286132812</v>
       </c>
       <c r="F98" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B99" t="n">
-        <v>636.9302530675583</v>
+        <v>638.0474756888525</v>
       </c>
       <c r="C99" t="n">
-        <v>645.5281132997313</v>
+        <v>661.6466973151385</v>
       </c>
       <c r="D99" t="n">
-        <v>635.0849670695593</v>
+        <v>637.1398390748724</v>
       </c>
       <c r="E99" t="n">
-        <v>643.1243286132812</v>
+        <v>653.9764404296875</v>
       </c>
       <c r="F99" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B100" t="n">
-        <v>638.0474161403351</v>
+        <v>650.8644258547187</v>
       </c>
       <c r="C100" t="n">
-        <v>661.6466355641227</v>
+        <v>656.0112104148094</v>
       </c>
       <c r="D100" t="n">
-        <v>637.1397796110642</v>
+        <v>634.3669181695027</v>
       </c>
       <c r="E100" t="n">
-        <v>653.9763793945312</v>
+        <v>635.6137084960938</v>
       </c>
       <c r="F100" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B101" t="n">
-        <v>650.8644258547187</v>
+        <v>631.4544476780686</v>
       </c>
       <c r="C101" t="n">
-        <v>656.0112104148094</v>
+        <v>639.4637972653206</v>
       </c>
       <c r="D101" t="n">
-        <v>634.3669181695027</v>
+        <v>627.364938784811</v>
       </c>
       <c r="E101" t="n">
-        <v>635.6137084960938</v>
+        <v>637.658447265625</v>
       </c>
       <c r="F101" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B102" t="n">
-        <v>631.4543872367445</v>
+        <v>640.8800977544264</v>
       </c>
       <c r="C102" t="n">
-        <v>639.4637360573605</v>
+        <v>652.2009281146602</v>
       </c>
       <c r="D102" t="n">
-        <v>627.364878734925</v>
+        <v>640.4910846116635</v>
       </c>
       <c r="E102" t="n">
-        <v>637.6583862304688</v>
+        <v>652.0114135742188</v>
       </c>
       <c r="F102" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B103" t="n">
-        <v>640.8800977544264</v>
+        <v>648.8795635426123</v>
       </c>
       <c r="C103" t="n">
-        <v>652.2009281146602</v>
+        <v>659.3027431401059</v>
       </c>
       <c r="D103" t="n">
-        <v>640.4910846116635</v>
+        <v>645.8374072363367</v>
       </c>
       <c r="E103" t="n">
-        <v>652.0114135742188</v>
+        <v>655.322998046875</v>
       </c>
       <c r="F103" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B104" t="n">
-        <v>648.8795031075816</v>
+        <v>641.7977293743734</v>
       </c>
       <c r="C104" t="n">
-        <v>659.3026817342861</v>
+        <v>647.7723382149427</v>
       </c>
       <c r="D104" t="n">
-        <v>645.837347084645</v>
+        <v>636.4813989665846</v>
       </c>
       <c r="E104" t="n">
-        <v>655.3229370117188</v>
+        <v>646.5155639648438</v>
       </c>
       <c r="F104" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B105" t="n">
-        <v>641.7978505538991</v>
+        <v>635.5238627543893</v>
       </c>
       <c r="C105" t="n">
-        <v>647.7724605225501</v>
+        <v>658.2453970983619</v>
       </c>
       <c r="D105" t="n">
-        <v>636.4815191423199</v>
+        <v>632.870719934867</v>
       </c>
       <c r="E105" t="n">
-        <v>646.5156860351562</v>
+        <v>651.8817749023438</v>
       </c>
       <c r="F105" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B106" t="n">
-        <v>635.5238627543893</v>
+        <v>646.6252847330551</v>
       </c>
       <c r="C106" t="n">
-        <v>658.2453970983619</v>
+        <v>657.3476806461185</v>
       </c>
       <c r="D106" t="n">
-        <v>632.870719934867</v>
+        <v>637.199599354082</v>
       </c>
       <c r="E106" t="n">
-        <v>651.8817749023438</v>
+        <v>653.3978881835938</v>
       </c>
       <c r="F106" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B107" t="n">
-        <v>646.6252847330551</v>
+        <v>656.2705097002453</v>
       </c>
       <c r="C107" t="n">
-        <v>657.3476806461185</v>
+        <v>671.0424780902056</v>
       </c>
       <c r="D107" t="n">
-        <v>637.199599354082</v>
+        <v>655.9812154011644</v>
       </c>
       <c r="E107" t="n">
-        <v>653.3978881835938</v>
+        <v>666.015380859375</v>
       </c>
       <c r="F107" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B108" t="n">
-        <v>656.2705698423595</v>
+        <v>660.2303336051802</v>
       </c>
       <c r="C108" t="n">
-        <v>671.0425395860565</v>
+        <v>668.9778340733714</v>
       </c>
       <c r="D108" t="n">
-        <v>655.981275516767</v>
+        <v>648.6401755256248</v>
       </c>
       <c r="E108" t="n">
-        <v>666.0154418945312</v>
+        <v>658.8738403320312</v>
       </c>
       <c r="F108" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B109" t="n">
-        <v>660.2302724443645</v>
+        <v>646.2363343546218</v>
       </c>
       <c r="C109" t="n">
-        <v>668.9777721022258</v>
+        <v>647.8022493056128</v>
       </c>
       <c r="D109" t="n">
-        <v>648.6401154384699</v>
+        <v>634.4765699796501</v>
       </c>
       <c r="E109" t="n">
-        <v>658.873779296875</v>
+        <v>643.2041015625</v>
       </c>
       <c r="F109" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B110" t="n">
-        <v>646.2363343546218</v>
+        <v>633.1500554179556</v>
       </c>
       <c r="C110" t="n">
-        <v>647.8022493056128</v>
+        <v>646.0867221220876</v>
       </c>
       <c r="D110" t="n">
-        <v>634.4765699796501</v>
+        <v>625.1705976379839</v>
       </c>
       <c r="E110" t="n">
-        <v>643.2041015625</v>
+        <v>645.7276611328125</v>
       </c>
       <c r="F110" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B111" t="n">
-        <v>633.1501152642575</v>
+        <v>651.8818637417822</v>
       </c>
       <c r="C111" t="n">
-        <v>646.0867831911829</v>
+        <v>658.6045478289335</v>
       </c>
       <c r="D111" t="n">
-        <v>625.1706567300553</v>
+        <v>647.3335748038755</v>
       </c>
       <c r="E111" t="n">
-        <v>645.7277221679688</v>
+        <v>652.3905639648438</v>
       </c>
       <c r="F111" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B112" t="n">
-        <v>651.8817417666538</v>
+        <v>653.0787479235273</v>
       </c>
       <c r="C112" t="n">
-        <v>658.6044245959081</v>
+        <v>657.4275379105374</v>
       </c>
       <c r="D112" t="n">
-        <v>647.333453679788</v>
+        <v>646.6951571900124</v>
       </c>
       <c r="E112" t="n">
-        <v>652.3904418945312</v>
+        <v>653.178466796875</v>
       </c>
       <c r="F112" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B113" t="n">
-        <v>653.0787479235273</v>
+        <v>647.0841872338415</v>
       </c>
       <c r="C113" t="n">
-        <v>657.4275379105374</v>
+        <v>651.8219905315074</v>
       </c>
       <c r="D113" t="n">
-        <v>646.6951571900124</v>
+        <v>635.2646391478804</v>
       </c>
       <c r="E113" t="n">
-        <v>653.178466796875</v>
+        <v>636.5413208007812</v>
       </c>
       <c r="F113" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B114" t="n">
-        <v>647.0841872338415</v>
+        <v>622.2879460132801</v>
       </c>
       <c r="C114" t="n">
-        <v>651.8219905315074</v>
+        <v>627.554356001348</v>
       </c>
       <c r="D114" t="n">
-        <v>635.2646391478804</v>
+        <v>607.9847424867846</v>
       </c>
       <c r="E114" t="n">
-        <v>636.5413208007812</v>
+        <v>612.1340942382812</v>
       </c>
       <c r="F114" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,25 +3407,25 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B115" t="n">
-        <v>622.2880080608647</v>
+        <v>630.9168848948667</v>
       </c>
       <c r="C115" t="n">
-        <v>627.55441857404</v>
+        <v>633.6621719731276</v>
       </c>
       <c r="D115" t="n">
-        <v>607.9848031082139</v>
+        <v>622.0321132511823</v>
       </c>
       <c r="E115" t="n">
-        <v>612.1341552734375</v>
+        <v>626.3746948242188</v>
       </c>
       <c r="F115" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3433,25 +3433,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B116" t="n">
-        <v>630.9168848948667</v>
+        <v>626.9137783313067</v>
       </c>
       <c r="C116" t="n">
-        <v>633.6621719731276</v>
+        <v>635.4591062750881</v>
       </c>
       <c r="D116" t="n">
-        <v>622.0321132511823</v>
+        <v>620.634579694285</v>
       </c>
       <c r="E116" t="n">
-        <v>626.3746948242188</v>
+        <v>621.5928955078125</v>
       </c>
       <c r="F116" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G116" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B117" t="n">
-        <v>626.9137167736849</v>
+        <v>615.2837809831337</v>
       </c>
       <c r="C117" t="n">
-        <v>635.4590438783874</v>
+        <v>621.5829648535273</v>
       </c>
       <c r="D117" t="n">
-        <v>620.6345187532272</v>
+        <v>613.5567043186309</v>
       </c>
       <c r="E117" t="n">
-        <v>621.5928344726562</v>
+        <v>614.6248779296875</v>
       </c>
       <c r="F117" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B118" t="n">
-        <v>615.2837198825454</v>
+        <v>611.1009505532863</v>
       </c>
       <c r="C118" t="n">
-        <v>621.5829031274002</v>
+        <v>611.9494694911245</v>
       </c>
       <c r="D118" t="n">
-        <v>613.5566433895493</v>
+        <v>601.2278849458298</v>
       </c>
       <c r="E118" t="n">
-        <v>614.6248168945312</v>
+        <v>605.6602783203125</v>
       </c>
       <c r="F118" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B119" t="n">
-        <v>611.1008889698486</v>
+        <v>602.4957192983555</v>
       </c>
       <c r="C119" t="n">
-        <v>611.9494078221777</v>
+        <v>602.9249750667714</v>
       </c>
       <c r="D119" t="n">
-        <v>601.2278243573462</v>
+        <v>586.2435901825164</v>
       </c>
       <c r="E119" t="n">
-        <v>605.6602172851562</v>
+        <v>592.642578125</v>
       </c>
       <c r="F119" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B120" t="n">
-        <v>602.4957192983555</v>
+        <v>604.7517959610541</v>
       </c>
       <c r="C120" t="n">
-        <v>602.9249750667714</v>
+        <v>607.5969482872343</v>
       </c>
       <c r="D120" t="n">
-        <v>586.2435901825164</v>
+        <v>597.9834469761715</v>
       </c>
       <c r="E120" t="n">
-        <v>592.642578125</v>
+        <v>603.0247802734375</v>
       </c>
       <c r="F120" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B121" t="n">
-        <v>604.7517959610541</v>
+        <v>598.0732713770465</v>
       </c>
       <c r="C121" t="n">
-        <v>607.5969482872343</v>
+        <v>599.9700396349708</v>
       </c>
       <c r="D121" t="n">
-        <v>597.9834469761715</v>
+        <v>589.9871770786485</v>
       </c>
       <c r="E121" t="n">
-        <v>603.0247802734375</v>
+        <v>591.9038696289062</v>
       </c>
       <c r="F121" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B122" t="n">
-        <v>598.0732713770465</v>
+        <v>597.7138608396341</v>
       </c>
       <c r="C122" t="n">
-        <v>599.9700396349708</v>
+        <v>602.6354044215132</v>
       </c>
       <c r="D122" t="n">
-        <v>589.9871770786485</v>
+        <v>592.3830467312241</v>
       </c>
       <c r="E122" t="n">
-        <v>591.9038696289062</v>
+        <v>593.8704833984375</v>
       </c>
       <c r="F122" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B123" t="n">
-        <v>597.7138608396341</v>
+        <v>581.4916747262954</v>
       </c>
       <c r="C123" t="n">
-        <v>602.6354044215132</v>
+        <v>582.0008103985165</v>
       </c>
       <c r="D123" t="n">
-        <v>592.3830467312241</v>
+        <v>542.4187412024525</v>
       </c>
       <c r="E123" t="n">
-        <v>593.8704833984375</v>
+        <v>546.6015625</v>
       </c>
       <c r="F123" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B124" t="n">
-        <v>581.4917396573854</v>
+        <v>539.1743295527585</v>
       </c>
       <c r="C124" t="n">
-        <v>582.0008753864581</v>
+        <v>542.6683311056884</v>
       </c>
       <c r="D124" t="n">
-        <v>542.4188017705425</v>
+        <v>519.368366299545</v>
       </c>
       <c r="E124" t="n">
-        <v>546.6016235351562</v>
+        <v>524.8189697265625</v>
       </c>
       <c r="F124" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B125" t="n">
-        <v>539.1743922574078</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="C125" t="n">
-        <v>542.6683942166816</v>
+        <v>538.6253045735799</v>
       </c>
       <c r="D125" t="n">
-        <v>519.3684267008094</v>
+        <v>527.6341638126921</v>
       </c>
       <c r="E125" t="n">
-        <v>524.8190307617188</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="F125" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B126" t="n">
-        <v>535.4607543945312</v>
+        <v>549.0374119135495</v>
       </c>
       <c r="C126" t="n">
-        <v>538.6253045735799</v>
+        <v>572.7067990959439</v>
       </c>
       <c r="D126" t="n">
-        <v>527.6341638126921</v>
+        <v>545.8329522821889</v>
       </c>
       <c r="E126" t="n">
-        <v>535.4607543945312</v>
+        <v>571.1494750976562</v>
       </c>
       <c r="F126" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B127" t="n">
-        <v>549.0374119135495</v>
+        <v>579.1357866530213</v>
       </c>
       <c r="C127" t="n">
-        <v>572.7067990959439</v>
+        <v>591.5344843799961</v>
       </c>
       <c r="D127" t="n">
-        <v>545.8329522821889</v>
+        <v>572.8366030750008</v>
       </c>
       <c r="E127" t="n">
-        <v>571.1494750976562</v>
+        <v>578.2373046875</v>
       </c>
       <c r="F127" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B128" t="n">
-        <v>579.135725523027</v>
+        <v>565.0699110449033</v>
       </c>
       <c r="C128" t="n">
-        <v>591.5344219412718</v>
+        <v>577.5085793033603</v>
       </c>
       <c r="D128" t="n">
-        <v>572.8365426099092</v>
+        <v>558.7408105198895</v>
       </c>
       <c r="E128" t="n">
-        <v>578.2372436523438</v>
+        <v>573.4755249023438</v>
       </c>
       <c r="F128" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B129" t="n">
-        <v>565.0699110449033</v>
+        <v>576.6999432469056</v>
       </c>
       <c r="C129" t="n">
-        <v>577.5085793033603</v>
+        <v>581.7911783704857</v>
       </c>
       <c r="D129" t="n">
-        <v>558.7408105198895</v>
+        <v>571.0196924702504</v>
       </c>
       <c r="E129" t="n">
-        <v>573.4755249023438</v>
+        <v>572.0379638671875</v>
       </c>
       <c r="F129" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B130" t="n">
-        <v>576.7000047794845</v>
+        <v>571.4988503418972</v>
       </c>
       <c r="C130" t="n">
-        <v>581.7912404462878</v>
+        <v>574.2441373249518</v>
       </c>
       <c r="D130" t="n">
-        <v>571.0197533967594</v>
+        <v>563.7921103124964</v>
       </c>
       <c r="E130" t="n">
-        <v>572.0380249023438</v>
+        <v>574.064453125</v>
       </c>
       <c r="F130" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B131" t="n">
-        <v>571.4988503418972</v>
+        <v>604.9614419693103</v>
       </c>
       <c r="C131" t="n">
-        <v>574.2441373249518</v>
+        <v>628.8704088339113</v>
       </c>
       <c r="D131" t="n">
-        <v>563.7921103124964</v>
+        <v>590.8157434643455</v>
       </c>
       <c r="E131" t="n">
-        <v>574.064453125</v>
+        <v>611.3704223632812</v>
       </c>
       <c r="F131" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B132" t="n">
-        <v>604.9614419693103</v>
+        <v>625.8955000086161</v>
       </c>
       <c r="C132" t="n">
-        <v>628.8704088339113</v>
+        <v>636.4074834525468</v>
       </c>
       <c r="D132" t="n">
-        <v>590.8157434643455</v>
+        <v>621.9323328485281</v>
       </c>
       <c r="E132" t="n">
-        <v>611.3704223632812</v>
+        <v>627.3131103515625</v>
       </c>
       <c r="F132" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B133" t="n">
-        <v>625.8954391113879</v>
+        <v>633.3826022362973</v>
       </c>
       <c r="C133" t="n">
-        <v>636.4074215325429</v>
+        <v>637.4856047359222</v>
       </c>
       <c r="D133" t="n">
-        <v>621.9322723369008</v>
+        <v>623.2600266965629</v>
       </c>
       <c r="E133" t="n">
-        <v>627.3130493164062</v>
+        <v>628.780517578125</v>
       </c>
       <c r="F133" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B134" t="n">
-        <v>633.3826022362973</v>
+        <v>628.4212176827168</v>
       </c>
       <c r="C134" t="n">
-        <v>637.4856047359222</v>
+        <v>633.9117922613585</v>
       </c>
       <c r="D134" t="n">
-        <v>623.2600266965629</v>
+        <v>623.3299819911093</v>
       </c>
       <c r="E134" t="n">
-        <v>628.780517578125</v>
+        <v>633.442626953125</v>
       </c>
       <c r="F134" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B135" t="n">
-        <v>628.4211571313969</v>
+        <v>642.117619704398</v>
       </c>
       <c r="C135" t="n">
-        <v>633.911731180996</v>
+        <v>665.1181727259973</v>
       </c>
       <c r="D135" t="n">
-        <v>623.3299219303536</v>
+        <v>638.2742422102883</v>
       </c>
       <c r="E135" t="n">
-        <v>633.4425659179688</v>
+        <v>661.3546142578125</v>
       </c>
       <c r="F135" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B136" t="n">
-        <v>642.117619704398</v>
+        <v>665.856909197143</v>
       </c>
       <c r="C136" t="n">
-        <v>665.1181727259973</v>
+        <v>677.3372007350248</v>
       </c>
       <c r="D136" t="n">
-        <v>638.2742422102883</v>
+        <v>663.081644256971</v>
       </c>
       <c r="E136" t="n">
-        <v>661.3546142578125</v>
+        <v>670.4290771484375</v>
       </c>
       <c r="F136" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B137" t="n">
-        <v>665.856909197143</v>
+        <v>674.831464225754</v>
       </c>
       <c r="C137" t="n">
-        <v>677.3372007350248</v>
+        <v>676.4187660594131</v>
       </c>
       <c r="D137" t="n">
-        <v>663.081644256971</v>
+        <v>666.605595861725</v>
       </c>
       <c r="E137" t="n">
-        <v>670.4290771484375</v>
+        <v>675.7099609375</v>
       </c>
       <c r="F137" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B138" t="n">
-        <v>674.831464225754</v>
+        <v>677.4369744478516</v>
       </c>
       <c r="C138" t="n">
-        <v>676.4187660594131</v>
+        <v>690.3348757077041</v>
       </c>
       <c r="D138" t="n">
-        <v>666.605595861725</v>
+        <v>673.9729506648888</v>
       </c>
       <c r="E138" t="n">
-        <v>675.7099609375</v>
+        <v>687.3699340820312</v>
       </c>
       <c r="F138" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B139" t="n">
-        <v>677.4369744478516</v>
+        <v>680.192296240317</v>
       </c>
       <c r="C139" t="n">
-        <v>690.3348757077041</v>
+        <v>682.2088539380842</v>
       </c>
       <c r="D139" t="n">
-        <v>673.9729506648888</v>
+        <v>666.8552067290691</v>
       </c>
       <c r="E139" t="n">
-        <v>687.3699340820312</v>
+        <v>669.7601928710938</v>
       </c>
       <c r="F139" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B140" t="n">
-        <v>680.192296240317</v>
+        <v>669.8500580611455</v>
       </c>
       <c r="C140" t="n">
-        <v>682.2088539380842</v>
+        <v>675.0411586256739</v>
       </c>
       <c r="D140" t="n">
-        <v>666.8552067290691</v>
+        <v>666.1863646700106</v>
       </c>
       <c r="E140" t="n">
-        <v>669.7601928710938</v>
+        <v>667.6937866210938</v>
       </c>
       <c r="F140" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B141" t="n">
-        <v>669.8500580611455</v>
+        <v>673.2042912464699</v>
       </c>
       <c r="C141" t="n">
-        <v>675.0411586256739</v>
+        <v>677.2174214115423</v>
       </c>
       <c r="D141" t="n">
-        <v>666.1863646700106</v>
+        <v>668.6022063234784</v>
       </c>
       <c r="E141" t="n">
-        <v>667.6937866210938</v>
+        <v>673.5636596679688</v>
       </c>
       <c r="F141" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B142" t="n">
-        <v>673.2042912464699</v>
+        <v>662.562575853328</v>
       </c>
       <c r="C142" t="n">
-        <v>677.2174214115423</v>
+        <v>668.4125184743669</v>
       </c>
       <c r="D142" t="n">
-        <v>668.6022063234784</v>
+        <v>651.9308032468797</v>
       </c>
       <c r="E142" t="n">
-        <v>673.5636596679688</v>
+        <v>658.0203857421875</v>
       </c>
       <c r="F142" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B143" t="n">
-        <v>662.562575853328</v>
+        <v>659.1883568751083</v>
       </c>
       <c r="C143" t="n">
-        <v>668.4125184743669</v>
+        <v>679.5034568571632</v>
       </c>
       <c r="D143" t="n">
-        <v>651.9308032468797</v>
+        <v>652.719481738207</v>
       </c>
       <c r="E143" t="n">
-        <v>658.0203857421875</v>
+        <v>673.8731689453125</v>
       </c>
       <c r="F143" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B144" t="n">
-        <v>659.1883568751083</v>
+        <v>669.8500343121515</v>
       </c>
       <c r="C144" t="n">
-        <v>679.5034568571632</v>
+        <v>681.330325511242</v>
       </c>
       <c r="D144" t="n">
-        <v>652.719481738207</v>
+        <v>669.6903353309991</v>
       </c>
       <c r="E144" t="n">
-        <v>673.8731689453125</v>
+        <v>677.4569702148438</v>
       </c>
       <c r="F144" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B145" t="n">
-        <v>669.8500343121515</v>
+        <v>673.0844464119266</v>
       </c>
       <c r="C145" t="n">
-        <v>681.330325511242</v>
+        <v>677.0176962940845</v>
       </c>
       <c r="D145" t="n">
-        <v>669.6903353309991</v>
+        <v>664.489217253305</v>
       </c>
       <c r="E145" t="n">
-        <v>677.4569702148438</v>
+        <v>670.189453125</v>
       </c>
       <c r="F145" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B146" t="n">
-        <v>673.0844464119266</v>
+        <v>667.7636045616339</v>
       </c>
       <c r="C146" t="n">
-        <v>677.0176962940845</v>
+        <v>673.0944797535534</v>
       </c>
       <c r="D146" t="n">
-        <v>664.489217253305</v>
+        <v>662.6723692427279</v>
       </c>
       <c r="E146" t="n">
-        <v>670.189453125</v>
+        <v>667.9732666015625</v>
       </c>
       <c r="F146" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B147" t="n">
-        <v>667.7636045616339</v>
+        <v>618.2586017744245</v>
       </c>
       <c r="C147" t="n">
-        <v>673.0944797535534</v>
+        <v>619.7859479396749</v>
       </c>
       <c r="D147" t="n">
-        <v>662.6723692427279</v>
+        <v>598.9717055442339</v>
       </c>
       <c r="E147" t="n">
-        <v>667.9732666015625</v>
+        <v>610.8612670898438</v>
       </c>
       <c r="F147" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B148" t="n">
-        <v>618.2586017744245</v>
+        <v>613.6365485572411</v>
       </c>
       <c r="C148" t="n">
-        <v>619.7859479396749</v>
+        <v>617.8193701850194</v>
       </c>
       <c r="D148" t="n">
-        <v>598.9717055442339</v>
+        <v>605.0712358749745</v>
       </c>
       <c r="E148" t="n">
-        <v>610.8612670898438</v>
+        <v>607.7067260742188</v>
       </c>
       <c r="F148" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="n">
-        <v>613.6365485572411</v>
+        <v>606.8981537761392</v>
       </c>
       <c r="C149" t="n">
-        <v>617.8193701850194</v>
+        <v>612.9477660987843</v>
       </c>
       <c r="D149" t="n">
-        <v>605.0712358749745</v>
+        <v>601.7170456287333</v>
       </c>
       <c r="E149" t="n">
-        <v>607.7067260742188</v>
+        <v>609.3638916015625</v>
       </c>
       <c r="F149" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="n">
-        <v>606.8981537761392</v>
+        <v>612.2588828439087</v>
       </c>
       <c r="C150" t="n">
-        <v>612.9477660987843</v>
+        <v>613.2970785161436</v>
       </c>
       <c r="D150" t="n">
-        <v>601.7170456287333</v>
+        <v>599.3310648754198</v>
       </c>
       <c r="E150" t="n">
-        <v>609.3638916015625</v>
+        <v>603.9232177734375</v>
       </c>
       <c r="F150" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="n">
-        <v>612.2588828439087</v>
+        <v>600.0199080772063</v>
       </c>
       <c r="C151" t="n">
-        <v>613.2970785161436</v>
+        <v>618.8875416216711</v>
       </c>
       <c r="D151" t="n">
-        <v>599.3310648754198</v>
+        <v>597.0749516023062</v>
       </c>
       <c r="E151" t="n">
-        <v>603.9232177734375</v>
+        <v>611.8296508789062</v>
       </c>
       <c r="F151" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B152" t="n">
-        <v>600.0199080772063</v>
+        <v>613.6664238202088</v>
       </c>
       <c r="C152" t="n">
-        <v>618.8875416216711</v>
+        <v>623.9088493168618</v>
       </c>
       <c r="D152" t="n">
-        <v>597.0749516023062</v>
+        <v>612.4884534922683</v>
       </c>
       <c r="E152" t="n">
-        <v>611.8296508789062</v>
+        <v>615.7528686523438</v>
       </c>
       <c r="F152" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B153" t="n">
-        <v>613.6664846485507</v>
+        <v>614.1456663784968</v>
       </c>
       <c r="C153" t="n">
-        <v>623.9089111604618</v>
+        <v>615.7129829832094</v>
       </c>
       <c r="D153" t="n">
-        <v>612.4885142038465</v>
+        <v>605.0213161255829</v>
       </c>
       <c r="E153" t="n">
-        <v>615.7529296875</v>
+        <v>608.585205078125</v>
       </c>
       <c r="F153" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B154" t="n">
-        <v>614.145727971313</v>
+        <v>603.533915527778</v>
       </c>
       <c r="C154" t="n">
-        <v>615.7130447332122</v>
+        <v>603.8732987260729</v>
       </c>
       <c r="D154" t="n">
-        <v>605.0213768033159</v>
+        <v>597.0550476209405</v>
       </c>
       <c r="E154" t="n">
-        <v>608.5852661132812</v>
+        <v>597.8336791992188</v>
       </c>
       <c r="F154" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B155" t="n">
-        <v>603.533915527778</v>
+        <v>593.8006394881057</v>
       </c>
       <c r="C155" t="n">
-        <v>603.8732987260729</v>
+        <v>602.7153284632744</v>
       </c>
       <c r="D155" t="n">
-        <v>597.0550476209405</v>
+        <v>591.5844123107358</v>
       </c>
       <c r="E155" t="n">
-        <v>597.8336791992188</v>
+        <v>601.9666137695312</v>
       </c>
       <c r="F155" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B156" t="n">
-        <v>593.8005792809215</v>
+        <v>597.8037594995824</v>
       </c>
       <c r="C156" t="n">
-        <v>602.7152673522038</v>
+        <v>618.837657653709</v>
       </c>
       <c r="D156" t="n">
-        <v>591.5843523282613</v>
+        <v>595.6374345129168</v>
       </c>
       <c r="E156" t="n">
-        <v>601.966552734375</v>
+        <v>615.5732421875</v>
       </c>
       <c r="F156" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B157" t="n">
-        <v>597.8037594995824</v>
+        <v>614.944289073115</v>
       </c>
       <c r="C157" t="n">
-        <v>618.837657653709</v>
+        <v>622.6610217742586</v>
       </c>
       <c r="D157" t="n">
-        <v>595.6374345129168</v>
+        <v>613.9460028895547</v>
       </c>
       <c r="E157" t="n">
-        <v>615.5732421875</v>
+        <v>617.3701171875</v>
       </c>
       <c r="F157" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B158" t="n">
-        <v>614.944289073115</v>
+        <v>612.9377892034477</v>
       </c>
       <c r="C158" t="n">
-        <v>622.6610217742586</v>
+        <v>620.135455286475</v>
       </c>
       <c r="D158" t="n">
-        <v>613.9460028895547</v>
+        <v>608.2658166797805</v>
       </c>
       <c r="E158" t="n">
-        <v>617.3701171875</v>
+        <v>613.1773681640625</v>
       </c>
       <c r="F158" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B159" t="n">
-        <v>612.9377281921389</v>
+        <v>608.0660990208263</v>
       </c>
       <c r="C159" t="n">
-        <v>620.1353935587166</v>
+        <v>614.5350350972873</v>
       </c>
       <c r="D159" t="n">
-        <v>608.2657561335159</v>
+        <v>602.6554048207697</v>
       </c>
       <c r="E159" t="n">
-        <v>613.1773071289062</v>
+        <v>610.1625366210938</v>
       </c>
       <c r="F159" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B160" t="n">
-        <v>608.0660990208263</v>
+        <v>607.8764543920544</v>
       </c>
       <c r="C160" t="n">
-        <v>614.5350350972873</v>
+        <v>612.8778783201094</v>
       </c>
       <c r="D160" t="n">
-        <v>602.6554048207697</v>
+        <v>599.5208032426234</v>
       </c>
       <c r="E160" t="n">
-        <v>610.1625366210938</v>
+        <v>601.5772705078125</v>
       </c>
       <c r="F160" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B161" t="n">
-        <v>607.8763927177921</v>
+        <v>599.7304526335664</v>
       </c>
       <c r="C161" t="n">
-        <v>612.8778161384099</v>
+        <v>606.9580352784536</v>
       </c>
       <c r="D161" t="n">
-        <v>599.5207424161133</v>
+        <v>596.7854960328639</v>
       </c>
       <c r="E161" t="n">
-        <v>601.5772094726562</v>
+        <v>604.0230712890625</v>
       </c>
       <c r="F161" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B162" t="n">
-        <v>599.7304526335664</v>
+        <v>598.9716935873996</v>
       </c>
       <c r="C162" t="n">
-        <v>606.9580352784536</v>
+        <v>608.5552163125774</v>
       </c>
       <c r="D162" t="n">
-        <v>596.7854960328639</v>
+        <v>593.7905860006466</v>
       </c>
       <c r="E162" t="n">
-        <v>604.0230712890625</v>
+        <v>606.3390502929688</v>
       </c>
       <c r="F162" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B163" t="n">
-        <v>598.9717538809448</v>
+        <v>606.838246230648</v>
       </c>
       <c r="C163" t="n">
-        <v>608.5552775708169</v>
+        <v>613.7563625825306</v>
       </c>
       <c r="D163" t="n">
-        <v>593.7906457726523</v>
+        <v>605.9098473363839</v>
       </c>
       <c r="E163" t="n">
-        <v>606.339111328125</v>
+        <v>609.2141723632812</v>
       </c>
       <c r="F163" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B164" t="n">
-        <v>606.8381854335279</v>
+        <v>607.8464888599174</v>
       </c>
       <c r="C164" t="n">
-        <v>613.7563010923075</v>
+        <v>613.4168818935308</v>
       </c>
       <c r="D164" t="n">
-        <v>605.9097866322771</v>
+        <v>604.2626146519137</v>
       </c>
       <c r="E164" t="n">
-        <v>609.214111328125</v>
+        <v>611.2905883789062</v>
       </c>
       <c r="F164" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B165" t="n">
-        <v>607.8465495511928</v>
+        <v>608.3556581766634</v>
       </c>
       <c r="C165" t="n">
-        <v>613.4169431409898</v>
+        <v>637.4057633477772</v>
       </c>
       <c r="D165" t="n">
-        <v>604.2626749853522</v>
+        <v>607.9563193089997</v>
       </c>
       <c r="E165" t="n">
-        <v>611.2906494140625</v>
+        <v>634.1713256835938</v>
       </c>
       <c r="F165" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B166" t="n">
-        <v>608.3555996261091</v>
+        <v>638.4040398455469</v>
       </c>
       <c r="C166" t="n">
-        <v>637.4057020013258</v>
+        <v>641.8980416273442</v>
       </c>
       <c r="D166" t="n">
-        <v>607.9562607968793</v>
+        <v>628.2315007921775</v>
       </c>
       <c r="E166" t="n">
-        <v>634.1712646484375</v>
+        <v>634.2012329101562</v>
       </c>
       <c r="F166" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B167" t="n">
-        <v>638.4040398455469</v>
+        <v>632.4143189973911</v>
       </c>
       <c r="C167" t="n">
-        <v>641.8980416273442</v>
+        <v>633.4126052152244</v>
       </c>
       <c r="D167" t="n">
-        <v>628.2315007921775</v>
+        <v>622.281689514161</v>
       </c>
       <c r="E167" t="n">
-        <v>634.2012329101562</v>
+        <v>631.426025390625</v>
       </c>
       <c r="F167" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B168" t="n">
-        <v>632.4143189973911</v>
+        <v>629.3196151062037</v>
       </c>
       <c r="C168" t="n">
-        <v>633.4126052152244</v>
+        <v>634.6604216515384</v>
       </c>
       <c r="D168" t="n">
-        <v>622.281689514161</v>
+        <v>598.5025264432778</v>
       </c>
       <c r="E168" t="n">
-        <v>631.426025390625</v>
+        <v>599.4408569335938</v>
       </c>
       <c r="F168" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B169" t="n">
-        <v>629.3196791836195</v>
+        <v>602.2061447656582</v>
       </c>
       <c r="C169" t="n">
-        <v>634.6604862727559</v>
+        <v>607.8364934375654</v>
       </c>
       <c r="D169" t="n">
-        <v>598.5025873828931</v>
+        <v>595.6573898697867</v>
       </c>
       <c r="E169" t="n">
-        <v>599.44091796875</v>
+        <v>596.6057739257812</v>
       </c>
       <c r="F169" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B170" t="n">
-        <v>602.2062063737548</v>
+        <v>601.9666135784172</v>
       </c>
       <c r="C170" t="n">
-        <v>607.8365556216692</v>
+        <v>623.0803923074952</v>
       </c>
       <c r="D170" t="n">
-        <v>595.6574508079194</v>
+        <v>599.2413115918356</v>
       </c>
       <c r="E170" t="n">
-        <v>596.6058349609375</v>
+        <v>621.912353515625</v>
       </c>
       <c r="F170" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B171" t="n">
-        <v>601.9665545007575</v>
+        <v>622.601105447702</v>
       </c>
       <c r="C171" t="n">
-        <v>623.0803311577063</v>
+        <v>641.2990464500883</v>
       </c>
       <c r="D171" t="n">
-        <v>599.2412527816401</v>
+        <v>621.3632403719068</v>
       </c>
       <c r="E171" t="n">
-        <v>621.9122924804688</v>
+        <v>626.4944458007812</v>
       </c>
       <c r="F171" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B172" t="n">
-        <v>622.6011661035562</v>
+        <v>622.3915867034917</v>
       </c>
       <c r="C172" t="n">
-        <v>641.2991089275577</v>
+        <v>628.0718380797523</v>
       </c>
       <c r="D172" t="n">
-        <v>621.3633009071642</v>
+        <v>581.9110292634388</v>
       </c>
       <c r="E172" t="n">
-        <v>626.4945068359375</v>
+        <v>591.9837646484375</v>
       </c>
       <c r="F172" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B173" t="n">
-        <v>622.3915225332053</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="C173" t="n">
-        <v>628.0717733238163</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="D173" t="n">
-        <v>581.9109692668093</v>
+        <v>578.2273099921849</v>
       </c>
       <c r="E173" t="n">
-        <v>591.9837036132812</v>
+        <v>584.3867797851562</v>
       </c>
       <c r="F173" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B174" t="n">
-        <v>590.9854370177134</v>
+        <v>589.9871222602228</v>
       </c>
       <c r="C174" t="n">
-        <v>590.9854370177134</v>
+        <v>596.6057643945405</v>
       </c>
       <c r="D174" t="n">
-        <v>578.2273099921849</v>
+        <v>580.0142532419713</v>
       </c>
       <c r="E174" t="n">
-        <v>584.3867797851562</v>
+        <v>583.588134765625</v>
       </c>
       <c r="F174" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B175" t="n">
-        <v>589.9871222602228</v>
+        <v>579.7347558037309</v>
       </c>
       <c r="C175" t="n">
-        <v>596.6057643945405</v>
+        <v>590.3066340250939</v>
       </c>
       <c r="D175" t="n">
-        <v>580.0142532419713</v>
+        <v>569.6221111934292</v>
       </c>
       <c r="E175" t="n">
-        <v>583.588134765625</v>
+        <v>570.00146484375</v>
       </c>
       <c r="F175" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B176" t="n">
-        <v>579.7347558037309</v>
+        <v>564.8602908302337</v>
       </c>
       <c r="C176" t="n">
-        <v>590.3066340250939</v>
+        <v>571.1893911411966</v>
       </c>
       <c r="D176" t="n">
-        <v>569.6221111934292</v>
+        <v>556.0553993401948</v>
       </c>
       <c r="E176" t="n">
-        <v>570.00146484375</v>
+        <v>567.455810546875</v>
       </c>
       <c r="F176" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B177" t="n">
-        <v>564.8602908302337</v>
+        <v>571.9680395129554</v>
       </c>
       <c r="C177" t="n">
-        <v>571.1893911411966</v>
+        <v>575.0826873049916</v>
       </c>
       <c r="D177" t="n">
-        <v>556.0553993401948</v>
+        <v>559.938704060897</v>
       </c>
       <c r="E177" t="n">
-        <v>567.455810546875</v>
+        <v>566.0082397460938</v>
       </c>
       <c r="F177" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B178" t="n">
-        <v>571.968101190783</v>
+        <v>579.4427159724761</v>
       </c>
       <c r="C178" t="n">
-        <v>575.0827493186854</v>
+        <v>600.795858737961</v>
       </c>
       <c r="D178" t="n">
-        <v>559.9387644415484</v>
+        <v>578.8431525395191</v>
       </c>
       <c r="E178" t="n">
-        <v>566.00830078125</v>
+        <v>593.011962890625</v>
       </c>
       <c r="F178" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,25 +5071,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B179" t="n">
-        <v>579.4427159724761</v>
+        <v>593.1818700134238</v>
       </c>
       <c r="C179" t="n">
-        <v>600.795858737961</v>
+        <v>605.3322537623429</v>
       </c>
       <c r="D179" t="n">
-        <v>578.8431525395191</v>
+        <v>591.5331468141493</v>
       </c>
       <c r="E179" t="n">
-        <v>593.011962890625</v>
+        <v>599.7366943359375</v>
       </c>
       <c r="F179" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G179" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B180" t="n">
-        <v>593.1818700134238</v>
+        <v>591.5331725816898</v>
       </c>
       <c r="C180" t="n">
-        <v>605.3322537623429</v>
+        <v>593.3417428489197</v>
       </c>
       <c r="D180" t="n">
-        <v>591.5331468141493</v>
+        <v>565.7435277503374</v>
       </c>
       <c r="E180" t="n">
-        <v>599.7366943359375</v>
+        <v>567.1324462890625</v>
       </c>
       <c r="F180" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B181" t="n">
-        <v>591.5331725816898</v>
+        <v>572.3682769745303</v>
       </c>
       <c r="C181" t="n">
-        <v>593.3417428489197</v>
+        <v>579.7624046842873</v>
       </c>
       <c r="D181" t="n">
-        <v>565.7435277503374</v>
+        <v>562.6559105294999</v>
       </c>
       <c r="E181" t="n">
-        <v>567.1324462890625</v>
+        <v>576.7647705078125</v>
       </c>
       <c r="F181" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B182" t="n">
-        <v>572.3682769745303</v>
+        <v>571.5689356803741</v>
       </c>
       <c r="C182" t="n">
-        <v>579.7624046842873</v>
+        <v>575.3559250048318</v>
       </c>
       <c r="D182" t="n">
-        <v>562.6559105294999</v>
+        <v>559.3685422933314</v>
       </c>
       <c r="E182" t="n">
-        <v>576.7647705078125</v>
+        <v>563.4053344726562</v>
       </c>
       <c r="F182" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B183" t="n">
-        <v>571.5689356803741</v>
+        <v>561.8066012038755</v>
       </c>
       <c r="C183" t="n">
-        <v>575.3559250048318</v>
+        <v>571.7487666818112</v>
       </c>
       <c r="D183" t="n">
-        <v>559.3685422933314</v>
+        <v>560.5775907162</v>
       </c>
       <c r="E183" t="n">
-        <v>563.4053344726562</v>
+        <v>561.7566528320312</v>
       </c>
       <c r="F183" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B184" t="n">
-        <v>561.8066012038755</v>
+        <v>561.4469285838474</v>
       </c>
       <c r="C184" t="n">
-        <v>571.7487666818112</v>
+        <v>568.591253761232</v>
       </c>
       <c r="D184" t="n">
-        <v>560.5775907162</v>
+        <v>555.1119012433646</v>
       </c>
       <c r="E184" t="n">
-        <v>561.7566528320312</v>
+        <v>557.230224609375</v>
       </c>
       <c r="F184" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B185" t="n">
-        <v>561.4469285838474</v>
+        <v>555.1118879211193</v>
       </c>
       <c r="C185" t="n">
-        <v>568.591253761232</v>
+        <v>555.9013039685537</v>
       </c>
       <c r="D185" t="n">
-        <v>555.1119012433646</v>
+        <v>539.7540133926082</v>
       </c>
       <c r="E185" t="n">
-        <v>557.230224609375</v>
+        <v>542.44189453125</v>
       </c>
       <c r="F185" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B186" t="n">
-        <v>555.1118879211193</v>
+        <v>542.9115767800729</v>
       </c>
       <c r="C186" t="n">
-        <v>555.9013039685537</v>
+        <v>556.4108722579447</v>
       </c>
       <c r="D186" t="n">
-        <v>539.7540133926082</v>
+        <v>539.9738926737891</v>
       </c>
       <c r="E186" t="n">
-        <v>542.44189453125</v>
+        <v>549.8161010742188</v>
       </c>
       <c r="F186" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B187" t="n">
-        <v>542.9115767800729</v>
+        <v>559.5583857816937</v>
       </c>
       <c r="C187" t="n">
-        <v>556.4108722579447</v>
+        <v>570.4498144711828</v>
       </c>
       <c r="D187" t="n">
-        <v>539.9738926737891</v>
+        <v>557.5599629753306</v>
       </c>
       <c r="E187" t="n">
-        <v>549.8161010742188</v>
+        <v>562.1563110351562</v>
       </c>
       <c r="F187" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B188" t="n">
-        <v>559.5583857816937</v>
+        <v>560.4976417791106</v>
       </c>
       <c r="C188" t="n">
-        <v>570.4498144711828</v>
+        <v>565.0939897966132</v>
       </c>
       <c r="D188" t="n">
-        <v>557.5599629753306</v>
+        <v>550.9951316644288</v>
       </c>
       <c r="E188" t="n">
-        <v>562.1563110351562</v>
+        <v>562.8457641601562</v>
       </c>
       <c r="F188" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B189" t="n">
-        <v>560.4976417791106</v>
+        <v>607.4305787144307</v>
       </c>
       <c r="C189" t="n">
-        <v>565.0939897966132</v>
+        <v>627.784571153574</v>
       </c>
       <c r="D189" t="n">
-        <v>550.9951316644288</v>
+        <v>594.6306830487989</v>
       </c>
       <c r="E189" t="n">
-        <v>562.8457641601562</v>
+        <v>612.4266357421875</v>
       </c>
       <c r="F189" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B190" t="n">
-        <v>607.4305787144307</v>
+        <v>607.4206544757068</v>
       </c>
       <c r="C190" t="n">
-        <v>627.784571153574</v>
+        <v>609.5189740900589</v>
       </c>
       <c r="D190" t="n">
-        <v>594.6306830487989</v>
+        <v>579.9622828274885</v>
       </c>
       <c r="E190" t="n">
-        <v>612.4266357421875</v>
+        <v>582.4403686523438</v>
       </c>
       <c r="F190" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B191" t="n">
-        <v>607.4206544757068</v>
+        <v>594.3709360150443</v>
       </c>
       <c r="C191" t="n">
-        <v>609.5189740900589</v>
+        <v>603.1040338931904</v>
       </c>
       <c r="D191" t="n">
-        <v>579.9622828274885</v>
+        <v>581.301233826573</v>
       </c>
       <c r="E191" t="n">
-        <v>582.4403686523438</v>
+        <v>599.8165893554688</v>
       </c>
       <c r="F191" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B192" t="n">
-        <v>594.3709360150443</v>
+        <v>607.1109147253509</v>
       </c>
       <c r="C192" t="n">
-        <v>603.1040338931904</v>
+        <v>624.8768626804635</v>
       </c>
       <c r="D192" t="n">
-        <v>581.301233826573</v>
+        <v>603.1839600389557</v>
       </c>
       <c r="E192" t="n">
-        <v>599.8165893554688</v>
+        <v>615.0946044921875</v>
       </c>
       <c r="F192" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B193" t="n">
-        <v>607.1109147253509</v>
+        <v>613.9055418180343</v>
       </c>
       <c r="C193" t="n">
-        <v>624.8768626804635</v>
+        <v>615.5142576272189</v>
       </c>
       <c r="D193" t="n">
-        <v>603.1839600389557</v>
+        <v>597.5384532703483</v>
       </c>
       <c r="E193" t="n">
-        <v>615.0946044921875</v>
+        <v>602.6444091796875</v>
       </c>
       <c r="F193" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B194" t="n">
-        <v>613.9055418180343</v>
+        <v>583.529455055522</v>
       </c>
       <c r="C194" t="n">
-        <v>615.5142576272189</v>
+        <v>632.77062206454</v>
       </c>
       <c r="D194" t="n">
-        <v>597.5384532703483</v>
+        <v>576.6149292518581</v>
       </c>
       <c r="E194" t="n">
-        <v>602.6444091796875</v>
+        <v>630.9819946289062</v>
       </c>
       <c r="F194" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B195" t="n">
-        <v>583.529455055522</v>
+        <v>659.8193113874754</v>
       </c>
       <c r="C195" t="n">
-        <v>632.77062206454</v>
+        <v>677.3254544051542</v>
       </c>
       <c r="D195" t="n">
-        <v>576.6149292518581</v>
+        <v>657.491131647921</v>
       </c>
       <c r="E195" t="n">
-        <v>630.9819946289062</v>
+        <v>668.6823120117188</v>
       </c>
       <c r="F195" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B196" t="n">
-        <v>659.8193113874754</v>
+        <v>660.858454671636</v>
       </c>
       <c r="C196" t="n">
-        <v>677.3254544051542</v>
+        <v>676.0864269737083</v>
       </c>
       <c r="D196" t="n">
-        <v>657.491131647921</v>
+        <v>653.6841239854351</v>
       </c>
       <c r="E196" t="n">
-        <v>668.6823120117188</v>
+        <v>656.2120971679688</v>
       </c>
       <c r="F196" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>660.858454671636</v>
+        <v>651.4858277274717</v>
       </c>
       <c r="C197" t="n">
-        <v>676.0864269737083</v>
+        <v>665.9743929146624</v>
       </c>
       <c r="D197" t="n">
-        <v>653.6841239854351</v>
+        <v>648.5381419230179</v>
       </c>
       <c r="E197" t="n">
-        <v>656.2120971679688</v>
+        <v>660.5186767578125</v>
       </c>
       <c r="F197" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>651.4858277274717</v>
+        <v>663.0767089741589</v>
       </c>
       <c r="C198" t="n">
-        <v>665.9743929146624</v>
+        <v>685.5390243545221</v>
       </c>
       <c r="D198" t="n">
-        <v>648.5381419230179</v>
+        <v>656.1421789132482</v>
       </c>
       <c r="E198" t="n">
-        <v>660.5186767578125</v>
+        <v>680.7727661132812</v>
       </c>
       <c r="F198" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>663.0767089741589</v>
+        <v>676.7459348014426</v>
       </c>
       <c r="C199" t="n">
-        <v>685.5390243545221</v>
+        <v>681.3622866487058</v>
       </c>
       <c r="D199" t="n">
-        <v>656.1421789132482</v>
+        <v>659.6393793096187</v>
       </c>
       <c r="E199" t="n">
-        <v>680.7727661132812</v>
+        <v>664.0159301757812</v>
       </c>
       <c r="F199" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B200" t="n">
-        <v>676.7459348014426</v>
+        <v>647.1892801723585</v>
       </c>
       <c r="C200" t="n">
-        <v>681.3622866487058</v>
+        <v>651.68573177941</v>
       </c>
       <c r="D200" t="n">
-        <v>659.6393793096187</v>
+        <v>625.5063791142821</v>
       </c>
       <c r="E200" t="n">
-        <v>664.0159301757812</v>
+        <v>645.5006103515625</v>
       </c>
       <c r="F200" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B201" t="n">
-        <v>647.1892801723585</v>
+        <v>646.1900645769782</v>
       </c>
       <c r="C201" t="n">
-        <v>651.68573177941</v>
+        <v>652.7848358303891</v>
       </c>
       <c r="D201" t="n">
-        <v>625.5063791142821</v>
+        <v>635.5084916103011</v>
       </c>
       <c r="E201" t="n">
-        <v>645.5006103515625</v>
+        <v>645.3406982421875</v>
       </c>
       <c r="F201" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B202" t="n">
-        <v>646.1900645769782</v>
+        <v>653.664124760039</v>
       </c>
       <c r="C202" t="n">
-        <v>652.7848358303891</v>
+        <v>655.3627963853286</v>
       </c>
       <c r="D202" t="n">
-        <v>635.5084916103011</v>
+        <v>642.6928027946103</v>
       </c>
       <c r="E202" t="n">
-        <v>645.3406982421875</v>
+        <v>643.3023071289062</v>
       </c>
       <c r="F202" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B203" t="n">
-        <v>653.664124760039</v>
+        <v>647.189254956408</v>
       </c>
       <c r="C203" t="n">
-        <v>655.3627963853286</v>
+        <v>648.4882176170956</v>
       </c>
       <c r="D203" t="n">
-        <v>642.6928027946103</v>
+        <v>623.5079318845419</v>
       </c>
       <c r="E203" t="n">
-        <v>643.3023071289062</v>
+        <v>626.6754150390625</v>
       </c>
       <c r="F203" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B204" t="n">
-        <v>647.189254956408</v>
+        <v>607.9301851876114</v>
       </c>
       <c r="C204" t="n">
-        <v>648.4882176170956</v>
+        <v>614.1653155952538</v>
       </c>
       <c r="D204" t="n">
-        <v>623.5079318845419</v>
+        <v>596.7490071058414</v>
       </c>
       <c r="E204" t="n">
-        <v>626.6754150390625</v>
+        <v>605.6220092773438</v>
       </c>
       <c r="F204" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B205" t="n">
-        <v>607.9301851876114</v>
+        <v>604.8226548171024</v>
       </c>
       <c r="C205" t="n">
-        <v>614.1653155952538</v>
+        <v>609.4989569016461</v>
       </c>
       <c r="D205" t="n">
-        <v>596.7490071058414</v>
+        <v>593.9812354037057</v>
       </c>
       <c r="E205" t="n">
-        <v>605.6220092773438</v>
+        <v>594.7206420898438</v>
       </c>
       <c r="F205" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B206" t="n">
-        <v>604.8226548171024</v>
+        <v>606.7411202287035</v>
       </c>
       <c r="C206" t="n">
-        <v>609.4989569016461</v>
+        <v>610.7779733376527</v>
       </c>
       <c r="D206" t="n">
-        <v>593.9812354037057</v>
+        <v>592.6622656813121</v>
       </c>
       <c r="E206" t="n">
-        <v>594.7206420898438</v>
+        <v>593.4016723632812</v>
       </c>
       <c r="F206" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B207" t="n">
-        <v>606.7411202287035</v>
+        <v>596.3493616660036</v>
       </c>
       <c r="C207" t="n">
-        <v>610.7779733376527</v>
+        <v>600.5260580457825</v>
       </c>
       <c r="D207" t="n">
-        <v>592.6622656813121</v>
+        <v>586.5370982909723</v>
       </c>
       <c r="E207" t="n">
-        <v>593.4016723632812</v>
+        <v>592.9420166015625</v>
       </c>
       <c r="F207" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B208" t="n">
-        <v>596.3493616660036</v>
+        <v>592.7821833537371</v>
       </c>
       <c r="C208" t="n">
-        <v>600.5260580457825</v>
+        <v>599.4968549179539</v>
       </c>
       <c r="D208" t="n">
-        <v>586.5370982909723</v>
+        <v>581.7608519604674</v>
       </c>
       <c r="E208" t="n">
-        <v>592.9420166015625</v>
+        <v>585.148193359375</v>
       </c>
       <c r="F208" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B209" t="n">
-        <v>592.7821833537371</v>
+        <v>525.58522592167</v>
       </c>
       <c r="C209" t="n">
-        <v>599.4968549179539</v>
+        <v>539.4542858116451</v>
       </c>
       <c r="D209" t="n">
-        <v>581.7608519604674</v>
+        <v>524.0764068649972</v>
       </c>
       <c r="E209" t="n">
-        <v>585.148193359375</v>
+        <v>538.60498046875</v>
       </c>
       <c r="F209" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B210" t="n">
-        <v>525.58522592167</v>
+        <v>543.171288392182</v>
       </c>
       <c r="C210" t="n">
-        <v>539.4542858116451</v>
+        <v>557.8897136701136</v>
       </c>
       <c r="D210" t="n">
-        <v>524.0764068649972</v>
+        <v>539.7939490076644</v>
       </c>
       <c r="E210" t="n">
-        <v>538.60498046875</v>
+        <v>556.27099609375</v>
       </c>
       <c r="F210" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B211" t="n">
-        <v>543.171288392182</v>
+        <v>561.7966164985271</v>
       </c>
       <c r="C211" t="n">
-        <v>557.8897136701136</v>
+        <v>597.0488245114987</v>
       </c>
       <c r="D211" t="n">
-        <v>539.7939490076644</v>
+        <v>558.9188827428958</v>
       </c>
       <c r="E211" t="n">
-        <v>556.27099609375</v>
+        <v>589.7745361328125</v>
       </c>
       <c r="F211" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B212" t="n">
-        <v>561.7966164985271</v>
+        <v>581.0414552494501</v>
       </c>
       <c r="C212" t="n">
-        <v>597.0488245114987</v>
+        <v>592.32253050782</v>
       </c>
       <c r="D212" t="n">
-        <v>558.9188827428958</v>
+        <v>577.794018053301</v>
       </c>
       <c r="E212" t="n">
-        <v>589.7745361328125</v>
+        <v>587.4763793945312</v>
       </c>
       <c r="F212" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B213" t="n">
-        <v>581.0414552494501</v>
+        <v>599.9865089938204</v>
       </c>
       <c r="C213" t="n">
-        <v>592.32253050782</v>
+        <v>600.5260612032997</v>
       </c>
       <c r="D213" t="n">
-        <v>577.794018053301</v>
+        <v>579.6625219517506</v>
       </c>
       <c r="E213" t="n">
-        <v>587.4763793945312</v>
+        <v>588.3057250976562</v>
       </c>
       <c r="F213" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B214" t="n">
-        <v>599.9865089938204</v>
+        <v>586.487189429669</v>
       </c>
       <c r="C214" t="n">
-        <v>600.5260612032997</v>
+        <v>594.8405827519979</v>
       </c>
       <c r="D214" t="n">
-        <v>579.6625219517506</v>
+        <v>585.5379263278069</v>
       </c>
       <c r="E214" t="n">
-        <v>588.3057250976562</v>
+        <v>589.4348754882812</v>
       </c>
       <c r="F214" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B215" t="n">
-        <v>586.487189429669</v>
+        <v>585.1781899072663</v>
       </c>
       <c r="C215" t="n">
-        <v>594.8405827519979</v>
+        <v>598.2678350979388</v>
       </c>
       <c r="D215" t="n">
-        <v>585.5379263278069</v>
+        <v>585.1581861630435</v>
       </c>
       <c r="E215" t="n">
-        <v>589.4348754882812</v>
+        <v>591.633056640625</v>
       </c>
       <c r="F215" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B216" t="n">
-        <v>585.1781899072663</v>
+        <v>598.657568915248</v>
       </c>
       <c r="C216" t="n">
-        <v>598.2678350979388</v>
+        <v>607.7304260788247</v>
       </c>
       <c r="D216" t="n">
-        <v>585.1581861630435</v>
+        <v>591.5631919202813</v>
       </c>
       <c r="E216" t="n">
-        <v>591.633056640625</v>
+        <v>594.4508666992188</v>
       </c>
       <c r="F216" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B217" t="n">
-        <v>598.657568915248</v>
+        <v>597.5284100969216</v>
       </c>
       <c r="C217" t="n">
-        <v>607.7304260788247</v>
+        <v>611.9470231090784</v>
       </c>
       <c r="D217" t="n">
-        <v>591.5631919202813</v>
+        <v>592.9320621063698</v>
       </c>
       <c r="E217" t="n">
-        <v>594.4508666992188</v>
+        <v>598.6475219726562</v>
       </c>
       <c r="F217" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B218" t="n">
-        <v>597.5284100969216</v>
+        <v>600.5960026412422</v>
       </c>
       <c r="C218" t="n">
-        <v>611.9470231090784</v>
+        <v>604.023290419805</v>
       </c>
       <c r="D218" t="n">
-        <v>592.9320621063698</v>
+        <v>577.7540447074138</v>
       </c>
       <c r="E218" t="n">
-        <v>598.6475219726562</v>
+        <v>578.3934936523438</v>
       </c>
       <c r="F218" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B219" t="n">
-        <v>600.5960026412422</v>
+        <v>580.2520897369063</v>
       </c>
       <c r="C219" t="n">
-        <v>604.023290419805</v>
+        <v>595.3801043917661</v>
       </c>
       <c r="D219" t="n">
-        <v>577.7540447074138</v>
+        <v>578.9331233348041</v>
       </c>
       <c r="E219" t="n">
-        <v>578.3934936523438</v>
+        <v>594.5007934570312</v>
       </c>
       <c r="F219" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B220" t="n">
-        <v>580.2520897369063</v>
+        <v>596.5092089028919</v>
       </c>
       <c r="C220" t="n">
-        <v>595.3801043917661</v>
+        <v>601.3853654698224</v>
       </c>
       <c r="D220" t="n">
-        <v>578.9331233348041</v>
+        <v>588.8252707092146</v>
       </c>
       <c r="E220" t="n">
-        <v>594.5007934570312</v>
+        <v>589.3848266601562</v>
       </c>
       <c r="F220" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B221" t="n">
-        <v>596.5092089028919</v>
+        <v>589.2849441761664</v>
       </c>
       <c r="C221" t="n">
-        <v>601.3853654698224</v>
+        <v>589.774548021712</v>
       </c>
       <c r="D221" t="n">
-        <v>588.8252707092146</v>
+        <v>564.3046582848494</v>
       </c>
       <c r="E221" t="n">
-        <v>589.3848266601562</v>
+        <v>568.5213012695312</v>
       </c>
       <c r="F221" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B222" t="n">
-        <v>589.2849441761664</v>
+        <v>557.0403796583744</v>
       </c>
       <c r="C222" t="n">
-        <v>589.774548021712</v>
+        <v>560.2178647510921</v>
       </c>
       <c r="D222" t="n">
-        <v>564.3046582848494</v>
+        <v>542.7816737373303</v>
       </c>
       <c r="E222" t="n">
-        <v>568.5213012695312</v>
+        <v>543.2412719726562</v>
       </c>
       <c r="F222" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B223" t="n">
-        <v>557.0403796583744</v>
+        <v>540.9131223962278</v>
       </c>
       <c r="C223" t="n">
-        <v>560.2178647510921</v>
+        <v>553.6330639150415</v>
       </c>
       <c r="D223" t="n">
-        <v>542.7816737373303</v>
+        <v>536.8463247077087</v>
       </c>
       <c r="E223" t="n">
-        <v>543.2412719726562</v>
+        <v>545.5994262695312</v>
       </c>
       <c r="F223" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B224" t="n">
-        <v>540.9131223962278</v>
+        <v>546.5187091013889</v>
       </c>
       <c r="C224" t="n">
-        <v>553.6330639150415</v>
+        <v>549.5562899225255</v>
       </c>
       <c r="D224" t="n">
-        <v>536.8463247077087</v>
+        <v>538.8847190657524</v>
       </c>
       <c r="E224" t="n">
-        <v>545.5994262695312</v>
+        <v>545.3995971679688</v>
       </c>
       <c r="F224" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B225" t="n">
-        <v>546.5187091013889</v>
+        <v>546.4587335768297</v>
       </c>
       <c r="C225" t="n">
-        <v>549.5562899225255</v>
+        <v>553.4332095869578</v>
       </c>
       <c r="D225" t="n">
-        <v>538.8847190657524</v>
+        <v>542.8015857242297</v>
       </c>
       <c r="E225" t="n">
-        <v>545.3995971679688</v>
+        <v>549.4663696289062</v>
       </c>
       <c r="F225" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B226" t="n">
-        <v>546.4587335768297</v>
+        <v>549.7661710202622</v>
       </c>
       <c r="C226" t="n">
-        <v>553.4332095869578</v>
+        <v>560.9772946036173</v>
       </c>
       <c r="D226" t="n">
-        <v>542.8015857242297</v>
+        <v>545.8692218355393</v>
       </c>
       <c r="E226" t="n">
-        <v>549.4663696289062</v>
+        <v>558.5792236328125</v>
       </c>
       <c r="F226" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B227" t="n">
-        <v>549.7661710202622</v>
+        <v>563.4353464162</v>
       </c>
       <c r="C227" t="n">
-        <v>560.9772946036173</v>
+        <v>570.3498724402046</v>
       </c>
       <c r="D227" t="n">
-        <v>545.8692218355393</v>
+        <v>560.9573215839381</v>
       </c>
       <c r="E227" t="n">
-        <v>558.5792236328125</v>
+        <v>569.6004638671875</v>
       </c>
       <c r="F227" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B228" t="n">
-        <v>563.4353464162</v>
+        <v>589.8444773654404</v>
       </c>
       <c r="C228" t="n">
-        <v>570.3498724402046</v>
+        <v>592.8721171723366</v>
       </c>
       <c r="D228" t="n">
-        <v>560.9573215839381</v>
+        <v>561.4369046651577</v>
       </c>
       <c r="E228" t="n">
-        <v>569.6004638671875</v>
+        <v>575.6856689453125</v>
       </c>
       <c r="F228" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B229" t="n">
-        <v>589.8444773654404</v>
+        <v>576.0253592943615</v>
       </c>
       <c r="C229" t="n">
-        <v>592.8721171723366</v>
+        <v>587.9260010338789</v>
       </c>
       <c r="D229" t="n">
-        <v>561.4369046651577</v>
+        <v>567.1723610665189</v>
       </c>
       <c r="E229" t="n">
-        <v>575.6856689453125</v>
+        <v>570.6495971679688</v>
       </c>
       <c r="F229" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B230" t="n">
-        <v>576.0253592943615</v>
+        <v>571.0992793335739</v>
       </c>
       <c r="C230" t="n">
-        <v>587.9260010338789</v>
+        <v>588.7253835559844</v>
       </c>
       <c r="D230" t="n">
-        <v>567.1723610665189</v>
+        <v>570.5497252457161</v>
       </c>
       <c r="E230" t="n">
-        <v>570.6495971679688</v>
+        <v>577.564208984375</v>
       </c>
       <c r="F230" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B231" t="n">
-        <v>571.0992793335739</v>
+        <v>577.1744781551006</v>
       </c>
       <c r="C231" t="n">
-        <v>588.7253835559844</v>
+        <v>578.2236379136884</v>
       </c>
       <c r="D231" t="n">
-        <v>570.5497252457161</v>
+        <v>568.6911832402849</v>
       </c>
       <c r="E231" t="n">
-        <v>577.564208984375</v>
+        <v>571.888671875</v>
       </c>
       <c r="F231" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B232" t="n">
-        <v>577.1744781551006</v>
+        <v>557.9096596695957</v>
       </c>
       <c r="C232" t="n">
-        <v>578.2236379136884</v>
+        <v>584.4887194481862</v>
       </c>
       <c r="D232" t="n">
-        <v>568.6911832402849</v>
+        <v>555.6614340241316</v>
       </c>
       <c r="E232" t="n">
-        <v>571.888671875</v>
+        <v>578.083740234375</v>
       </c>
       <c r="F232" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B233" t="n">
-        <v>557.9096596695957</v>
+        <v>578.3335366296732</v>
       </c>
       <c r="C233" t="n">
-        <v>584.4887194481862</v>
+        <v>599.9065373056851</v>
       </c>
       <c r="D233" t="n">
-        <v>555.6614340241316</v>
+        <v>576.5449702025707</v>
       </c>
       <c r="E233" t="n">
-        <v>578.083740234375</v>
+        <v>592.3824462890625</v>
       </c>
       <c r="F233" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B234" t="n">
-        <v>578.3335366296732</v>
+        <v>604.0133041368691</v>
       </c>
       <c r="C234" t="n">
-        <v>599.9065373056851</v>
+        <v>618.9715308723809</v>
       </c>
       <c r="D234" t="n">
-        <v>576.5449702025707</v>
+        <v>603.8733999005765</v>
       </c>
       <c r="E234" t="n">
-        <v>592.3824462890625</v>
+        <v>610.1984252929688</v>
       </c>
       <c r="F234" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B235" t="n">
-        <v>604.0133041368691</v>
+        <v>611.8670721034152</v>
       </c>
       <c r="C235" t="n">
-        <v>618.9715308723809</v>
+        <v>616.9730886717387</v>
       </c>
       <c r="D235" t="n">
-        <v>603.8733999005765</v>
+        <v>604.7926993516937</v>
       </c>
       <c r="E235" t="n">
-        <v>610.1984252929688</v>
+        <v>616.2836303710938</v>
       </c>
       <c r="F235" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B236" t="n">
-        <v>611.8670721034152</v>
+        <v>615.7241045276966</v>
       </c>
       <c r="C236" t="n">
-        <v>616.9730886717387</v>
+        <v>624.3072966603136</v>
       </c>
       <c r="D236" t="n">
-        <v>604.7926993516937</v>
+        <v>609.2591747857786</v>
       </c>
       <c r="E236" t="n">
-        <v>616.2836303710938</v>
+        <v>612.9962158203125</v>
       </c>
       <c r="F236" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B237" t="n">
-        <v>615.7241045276966</v>
+        <v>648.1284941622514</v>
       </c>
       <c r="C237" t="n">
-        <v>624.3072966603136</v>
+        <v>657.3411939542544</v>
       </c>
       <c r="D237" t="n">
-        <v>609.2591747857786</v>
+        <v>638.056426220049</v>
       </c>
       <c r="E237" t="n">
-        <v>612.9962158203125</v>
+        <v>653.1744995117188</v>
       </c>
       <c r="F237" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B238" t="n">
-        <v>648.1284941622514</v>
+        <v>653.1945472302951</v>
       </c>
       <c r="C238" t="n">
-        <v>657.3411939542544</v>
+        <v>662.9768054946985</v>
       </c>
       <c r="D238" t="n">
-        <v>638.056426220049</v>
+        <v>641.6336632885306</v>
       </c>
       <c r="E238" t="n">
-        <v>653.1744995117188</v>
+        <v>643.8718872070312</v>
       </c>
       <c r="F238" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B239" t="n">
-        <v>653.1945472302951</v>
+        <v>652.9947023490145</v>
       </c>
       <c r="C239" t="n">
-        <v>662.9768054946985</v>
+        <v>663.716221985592</v>
       </c>
       <c r="D239" t="n">
-        <v>641.6336632885306</v>
+        <v>645.6904688887529</v>
       </c>
       <c r="E239" t="n">
-        <v>643.8718872070312</v>
+        <v>647.51904296875</v>
       </c>
       <c r="F239" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B240" t="n">
-        <v>652.9947023490145</v>
+        <v>657.311302577125</v>
       </c>
       <c r="C240" t="n">
-        <v>663.716221985592</v>
+        <v>668.072768706455</v>
       </c>
       <c r="D240" t="n">
-        <v>645.6904688887529</v>
+        <v>648.708045415434</v>
       </c>
       <c r="E240" t="n">
-        <v>647.51904296875</v>
+        <v>665.0751342773438</v>
       </c>
       <c r="F240" t="n">
-        <v>16925000</v>
+        <v>19332300</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B241" t="n">
-        <v>657.311302577125</v>
+        <v>658.7801108800835</v>
       </c>
       <c r="C241" t="n">
-        <v>668.072768706455</v>
+        <v>678.3346866933342</v>
       </c>
       <c r="D241" t="n">
-        <v>648.708045415434</v>
+        <v>655.6825797136325</v>
       </c>
       <c r="E241" t="n">
-        <v>665.0751342773438</v>
+        <v>669.7114868164062</v>
       </c>
       <c r="F241" t="n">
-        <v>19332300</v>
+        <v>19502800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B242" t="n">
-        <v>658.7801108800835</v>
+        <v>679.3738238485387</v>
       </c>
       <c r="C242" t="n">
-        <v>678.3346866933342</v>
+        <v>684.7695900234191</v>
       </c>
       <c r="D242" t="n">
-        <v>655.6825797136325</v>
+        <v>671.3801323225093</v>
       </c>
       <c r="E242" t="n">
-        <v>669.7114868164062</v>
+        <v>672.779052734375</v>
       </c>
       <c r="F242" t="n">
-        <v>19502800</v>
+        <v>17217800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B243" t="n">
-        <v>679.3738238485387</v>
+        <v>681.9018750257407</v>
       </c>
       <c r="C243" t="n">
-        <v>684.7695900234191</v>
+        <v>682.6612854975235</v>
       </c>
       <c r="D243" t="n">
-        <v>671.3801323225093</v>
+        <v>666.5239959332205</v>
       </c>
       <c r="E243" t="n">
-        <v>672.779052734375</v>
+        <v>681.77197265625</v>
       </c>
       <c r="F243" t="n">
-        <v>17217800</v>
+        <v>15928000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B244" t="n">
-        <v>681.9018750257407</v>
+        <v>688.0769980771287</v>
       </c>
       <c r="C244" t="n">
-        <v>682.6612854975235</v>
+        <v>689.6058209010791</v>
       </c>
       <c r="D244" t="n">
-        <v>666.5239959332205</v>
+        <v>660.278927643704</v>
       </c>
       <c r="E244" t="n">
-        <v>681.77197265625</v>
+        <v>665.2250366210938</v>
       </c>
       <c r="F244" t="n">
-        <v>15928000</v>
+        <v>27596400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,25 +6787,25 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B245" t="n">
-        <v>688.0769980771287</v>
+        <v>680.2999877929688</v>
       </c>
       <c r="C245" t="n">
-        <v>689.6058209010791</v>
+        <v>753</v>
       </c>
       <c r="D245" t="n">
-        <v>660.278927643704</v>
+        <v>679.5999755859375</v>
       </c>
       <c r="E245" t="n">
-        <v>665.2250366210938</v>
+        <v>741.25</v>
       </c>
       <c r="F245" t="n">
-        <v>27596400</v>
+        <v>48720500</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -6813,25 +6813,25 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B246" t="n">
-        <v>680.2999877929688</v>
+        <v>731.4000244140625</v>
       </c>
       <c r="C246" t="n">
-        <v>753</v>
+        <v>757.27001953125</v>
       </c>
       <c r="D246" t="n">
-        <v>679.5999755859375</v>
+        <v>730</v>
       </c>
       <c r="E246" t="n">
-        <v>741.25</v>
+        <v>736.5999755859375</v>
       </c>
       <c r="F246" t="n">
-        <v>48720500</v>
+        <v>28122100</v>
       </c>
       <c r="G246" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B247" t="n">
-        <v>731.4000244140625</v>
+        <v>747.5999755859375</v>
       </c>
       <c r="C247" t="n">
-        <v>757.27001953125</v>
+        <v>763.9000244140625</v>
       </c>
       <c r="D247" t="n">
-        <v>730</v>
+        <v>739.510009765625</v>
       </c>
       <c r="E247" t="n">
-        <v>736.5999755859375</v>
+        <v>744.0999755859375</v>
       </c>
       <c r="F247" t="n">
-        <v>28122100</v>
+        <v>30829200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B248" t="n">
-        <v>747.5999755859375</v>
+        <v>744.3599853515625</v>
       </c>
       <c r="C248" t="n">
-        <v>763.9000244140625</v>
+        <v>779.8200073242188</v>
       </c>
       <c r="D248" t="n">
-        <v>739.510009765625</v>
+        <v>743.010009765625</v>
       </c>
       <c r="E248" t="n">
-        <v>744.0999755859375</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="F248" t="n">
-        <v>30829200</v>
+        <v>34808500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B249" t="n">
-        <v>744.3599853515625</v>
+        <v>768.8499755859375</v>
       </c>
       <c r="C249" t="n">
-        <v>779.8200073242188</v>
+        <v>769.5700073242188</v>
       </c>
       <c r="D249" t="n">
-        <v>743.010009765625</v>
+        <v>746.5399780273438</v>
       </c>
       <c r="E249" t="n">
-        <v>777.5900268554688</v>
+        <v>751.6599731445312</v>
       </c>
       <c r="F249" t="n">
-        <v>34808500</v>
+        <v>25826700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B250" t="n">
-        <v>768.8499755859375</v>
+        <v>750.0399780273438</v>
       </c>
       <c r="C250" t="n">
-        <v>769.5700073242188</v>
+        <v>750.5800170898438</v>
       </c>
       <c r="D250" t="n">
-        <v>746.5399780273438</v>
+        <v>713.1900024414062</v>
       </c>
       <c r="E250" t="n">
-        <v>751.6599731445312</v>
+        <v>715.6199951171875</v>
       </c>
       <c r="F250" t="n">
-        <v>25826700</v>
+        <v>27943100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B251" t="n">
-        <v>750.0399780273438</v>
+        <v>725</v>
       </c>
       <c r="C251" t="n">
-        <v>750.5800170898438</v>
+        <v>740.4500122070312</v>
       </c>
       <c r="D251" t="n">
-        <v>713.1900024414062</v>
+        <v>715.0999755859375</v>
       </c>
       <c r="E251" t="n">
-        <v>715.6199951171875</v>
+        <v>738.7899780273438</v>
       </c>
       <c r="F251" t="n">
-        <v>27943100</v>
+        <v>23591100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B252" t="n">
-        <v>725</v>
+        <v>730.27001953125</v>
       </c>
       <c r="C252" t="n">
-        <v>740.4500122070312</v>
+        <v>738.25</v>
       </c>
       <c r="D252" t="n">
-        <v>715.0999755859375</v>
+        <v>721.2999877929688</v>
       </c>
       <c r="E252" t="n">
-        <v>738.7899780273438</v>
+        <v>725.1799926757812</v>
       </c>
       <c r="F252" t="n">
-        <v>23460100</v>
+        <v>19240800</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>725.1799999999999</v>
+      </c>
+      <c r="D2" t="n">
         <v>738.79</v>
       </c>
-      <c r="D2" t="n">
-        <v>715.62</v>
-      </c>
       <c r="E2" t="n">
-        <v>725.335</v>
+        <v>729</v>
       </c>
       <c r="F2" t="n">
-        <v>740.45</v>
+        <v>738.25</v>
       </c>
       <c r="G2" t="n">
-        <v>715.1</v>
+        <v>721.3</v>
       </c>
       <c r="H2" t="n">
-        <v>23034083</v>
+        <v>19151113</v>
       </c>
       <c r="I2" t="n">
-        <v>20031174</v>
+        <v>19621914</v>
       </c>
       <c r="J2" t="n">
-        <v>1882072023040</v>
+        <v>1847400464384</v>
       </c>
       <c r="K2" t="n">
-        <v>26.9533</v>
+        <v>27.859392</v>
       </c>
       <c r="L2" t="n">
-        <v>21.128471</v>
+        <v>20.817175</v>
       </c>
       <c r="M2" t="n">
-        <v>27.41</v>
+        <v>26.03</v>
       </c>
       <c r="N2" t="n">
         <v>779.8200000000001</v>
@@ -10818,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.206301</v>
+        <v>7.073547</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1904130129920</v>
+        <v>1869458571264</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:06:58</t>
+          <t>2026-10-01 17:02:39</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B2" t="n">
-        <v>719.050911987213</v>
+        <v>720.1372426569798</v>
       </c>
       <c r="C2" t="n">
-        <v>719.4096803677126</v>
+        <v>725.309699629413</v>
       </c>
       <c r="D2" t="n">
-        <v>707.7991010033351</v>
+        <v>715.7122502133443</v>
       </c>
       <c r="E2" t="n">
-        <v>714.9149780273438</v>
+        <v>724.5921020507812</v>
       </c>
       <c r="F2" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B3" t="n">
-        <v>720.1372426569798</v>
+        <v>727.1633750572937</v>
       </c>
       <c r="C3" t="n">
-        <v>725.309699629413</v>
+        <v>728.5287386889415</v>
       </c>
       <c r="D3" t="n">
-        <v>715.7122502133443</v>
+        <v>707.7791166979599</v>
       </c>
       <c r="E3" t="n">
-        <v>724.5921020507812</v>
+        <v>708.1578369140625</v>
       </c>
       <c r="F3" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B4" t="n">
-        <v>727.1633750572937</v>
+        <v>702.8060248479621</v>
       </c>
       <c r="C4" t="n">
-        <v>728.5287386889415</v>
+        <v>714.4565078636942</v>
       </c>
       <c r="D4" t="n">
-        <v>707.7791166979599</v>
+        <v>688.1756596108709</v>
       </c>
       <c r="E4" t="n">
-        <v>708.1578369140625</v>
+        <v>713.2406005859375</v>
       </c>
       <c r="F4" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B5" t="n">
-        <v>702.8060849901855</v>
+        <v>715.2936403041813</v>
       </c>
       <c r="C5" t="n">
-        <v>714.456569002901</v>
+        <v>716.0710326272052</v>
       </c>
       <c r="D5" t="n">
-        <v>688.1757185011091</v>
+        <v>703.3641353885179</v>
       </c>
       <c r="E5" t="n">
-        <v>713.2406616210938</v>
+        <v>710.6693725585938</v>
       </c>
       <c r="F5" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B6" t="n">
-        <v>715.2936403041813</v>
+        <v>711.0380954481734</v>
       </c>
       <c r="C6" t="n">
-        <v>716.0710326272052</v>
+        <v>717.2171476536749</v>
       </c>
       <c r="D6" t="n">
-        <v>703.3641353885179</v>
+        <v>705.4171476518181</v>
       </c>
       <c r="E6" t="n">
-        <v>710.6693725585938</v>
+        <v>715.4132690429688</v>
       </c>
       <c r="F6" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B7" t="n">
-        <v>711.0381561100638</v>
+        <v>715.8518398810967</v>
       </c>
       <c r="C7" t="n">
-        <v>717.2172088427283</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="D7" t="n">
-        <v>705.4172078341599</v>
+        <v>710.0315555923428</v>
       </c>
       <c r="E7" t="n">
-        <v>715.413330078125</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="F7" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B8" t="n">
-        <v>715.8518398810967</v>
+        <v>728.4490335307075</v>
       </c>
       <c r="C8" t="n">
-        <v>731.0303344726562</v>
+        <v>732.784364410351</v>
       </c>
       <c r="D8" t="n">
-        <v>710.0315555923428</v>
+        <v>702.1283419878271</v>
       </c>
       <c r="E8" t="n">
-        <v>731.0303344726562</v>
+        <v>702.9156494140625</v>
       </c>
       <c r="F8" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="n">
-        <v>728.4490335307075</v>
+        <v>710.5996089558437</v>
       </c>
       <c r="C9" t="n">
-        <v>732.784364410351</v>
+        <v>717.5061741064447</v>
       </c>
       <c r="D9" t="n">
-        <v>702.1283419878271</v>
+        <v>705.2477676379041</v>
       </c>
       <c r="E9" t="n">
-        <v>702.9156494140625</v>
+        <v>713.280517578125</v>
       </c>
       <c r="F9" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B10" t="n">
-        <v>710.5995481500918</v>
+        <v>705.3873404797914</v>
       </c>
       <c r="C10" t="n">
-        <v>717.5061127097006</v>
+        <v>713.1310322093289</v>
       </c>
       <c r="D10" t="n">
-        <v>705.2477072901073</v>
+        <v>696.9658939978091</v>
       </c>
       <c r="E10" t="n">
-        <v>713.2804565429688</v>
+        <v>706.25439453125</v>
       </c>
       <c r="F10" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="n">
-        <v>705.3872795195668</v>
+        <v>714.6358727912688</v>
       </c>
       <c r="C11" t="n">
-        <v>713.1309705798873</v>
+        <v>721.4527759491865</v>
       </c>
       <c r="D11" t="n">
-        <v>696.9658337653736</v>
+        <v>707.1114088212217</v>
       </c>
       <c r="E11" t="n">
-        <v>706.2543334960938</v>
+        <v>715.1242065429688</v>
       </c>
       <c r="F11" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B12" t="n">
-        <v>714.6358727912688</v>
+        <v>715.1241740828767</v>
       </c>
       <c r="C12" t="n">
-        <v>721.4527759491865</v>
+        <v>723.0373338413923</v>
       </c>
       <c r="D12" t="n">
-        <v>707.1114088212217</v>
+        <v>701.5004051404221</v>
       </c>
       <c r="E12" t="n">
-        <v>715.1242065429688</v>
+        <v>709.6627197265625</v>
       </c>
       <c r="F12" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B13" t="n">
-        <v>715.1242355877501</v>
+        <v>704.6896976037913</v>
       </c>
       <c r="C13" t="n">
-        <v>723.0373960268438</v>
+        <v>716.1109175681677</v>
       </c>
       <c r="D13" t="n">
-        <v>701.5004654735715</v>
+        <v>703.732921033597</v>
       </c>
       <c r="E13" t="n">
-        <v>709.6627807617188</v>
+        <v>714.4963989257812</v>
       </c>
       <c r="F13" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B14" t="n">
-        <v>704.6896374063629</v>
+        <v>718.7519023248905</v>
       </c>
       <c r="C14" t="n">
-        <v>716.1108563950927</v>
+        <v>731.289390620618</v>
       </c>
       <c r="D14" t="n">
-        <v>703.7328609179003</v>
+        <v>717.7453070615727</v>
       </c>
       <c r="E14" t="n">
-        <v>714.496337890625</v>
+        <v>729.6947631835938</v>
       </c>
       <c r="F14" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B15" t="n">
-        <v>718.7519624447335</v>
+        <v>733.5318410857864</v>
       </c>
       <c r="C15" t="n">
-        <v>731.2894517891565</v>
+        <v>736.0034377690635</v>
       </c>
       <c r="D15" t="n">
-        <v>717.7453670972193</v>
+        <v>726.2863984755653</v>
       </c>
       <c r="E15" t="n">
-        <v>729.69482421875</v>
+        <v>730.7911376953125</v>
       </c>
       <c r="F15" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B16" t="n">
-        <v>733.5318410857864</v>
+        <v>731.3492269695964</v>
       </c>
       <c r="C16" t="n">
-        <v>736.0034377690635</v>
+        <v>738.0962989037338</v>
       </c>
       <c r="D16" t="n">
-        <v>726.2863984755653</v>
+        <v>721.5823690736463</v>
       </c>
       <c r="E16" t="n">
-        <v>730.7911376953125</v>
+        <v>730.9306030273438</v>
       </c>
       <c r="F16" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B17" t="n">
-        <v>731.3492269695964</v>
+        <v>732.2163225390138</v>
       </c>
       <c r="C17" t="n">
-        <v>738.0962989037338</v>
+        <v>739.9002195728755</v>
       </c>
       <c r="D17" t="n">
-        <v>721.5823690736463</v>
+        <v>730.6216949207216</v>
       </c>
       <c r="E17" t="n">
-        <v>730.9306030273438</v>
+        <v>731.5186767578125</v>
       </c>
       <c r="F17" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B18" t="n">
-        <v>732.2162614456487</v>
+        <v>734.2991309259364</v>
       </c>
       <c r="C18" t="n">
-        <v>739.900157838395</v>
+        <v>738.704232141329</v>
       </c>
       <c r="D18" t="n">
-        <v>730.6216339604061</v>
+        <v>728.6782441600997</v>
       </c>
       <c r="E18" t="n">
-        <v>731.5186157226562</v>
+        <v>735.8638305664062</v>
       </c>
       <c r="F18" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B19" t="n">
-        <v>734.2991309259364</v>
+        <v>747.195457385242</v>
       </c>
       <c r="C19" t="n">
-        <v>738.704232141329</v>
+        <v>753.1951257515892</v>
       </c>
       <c r="D19" t="n">
-        <v>728.6782441600997</v>
+        <v>745.4813011827554</v>
       </c>
       <c r="E19" t="n">
-        <v>735.8638305664062</v>
+        <v>748.2817993164062</v>
       </c>
       <c r="F19" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B20" t="n">
-        <v>747.195457385242</v>
+        <v>750.0856988126538</v>
       </c>
       <c r="C20" t="n">
-        <v>753.1951257515892</v>
+        <v>755.8362124836232</v>
       </c>
       <c r="D20" t="n">
-        <v>745.4813011827554</v>
+        <v>742.9997491476457</v>
       </c>
       <c r="E20" t="n">
-        <v>748.2817993164062</v>
+        <v>748.8997192382812</v>
       </c>
       <c r="F20" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B21" t="n">
-        <v>750.0856988126538</v>
+        <v>752.1985111114485</v>
       </c>
       <c r="C21" t="n">
-        <v>755.8362124836232</v>
+        <v>756.5935760115584</v>
       </c>
       <c r="D21" t="n">
-        <v>742.9997491476457</v>
+        <v>739.9998990805568</v>
       </c>
       <c r="E21" t="n">
-        <v>748.8997192382812</v>
+        <v>749.12890625</v>
       </c>
       <c r="F21" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B22" t="n">
-        <v>752.1985111114485</v>
+        <v>666.8879125335289</v>
       </c>
       <c r="C22" t="n">
-        <v>756.5935760115584</v>
+        <v>678.6579855089774</v>
       </c>
       <c r="D22" t="n">
-        <v>739.9998990805568</v>
+        <v>647.9720344844721</v>
       </c>
       <c r="E22" t="n">
-        <v>749.12890625</v>
+        <v>664.2169189453125</v>
       </c>
       <c r="F22" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B23" t="n">
-        <v>666.8879125335289</v>
+        <v>672.2297387877188</v>
       </c>
       <c r="C23" t="n">
-        <v>678.6579855089774</v>
+        <v>672.6084590133829</v>
       </c>
       <c r="D23" t="n">
-        <v>647.9720344844721</v>
+        <v>643.3875718813117</v>
       </c>
       <c r="E23" t="n">
-        <v>664.2169189453125</v>
+        <v>646.1581420898438</v>
       </c>
       <c r="F23" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B24" t="n">
-        <v>672.2297387877188</v>
+        <v>653.7823467127146</v>
       </c>
       <c r="C24" t="n">
-        <v>672.6084590133829</v>
+        <v>657.1011064498967</v>
       </c>
       <c r="D24" t="n">
-        <v>643.3875718813117</v>
+        <v>634.0293422915395</v>
       </c>
       <c r="E24" t="n">
-        <v>646.1581420898438</v>
+        <v>635.55419921875</v>
       </c>
       <c r="F24" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B25" t="n">
-        <v>653.7823467127146</v>
+        <v>625.9168776495994</v>
       </c>
       <c r="C25" t="n">
-        <v>657.1011064498967</v>
+        <v>639.5705767203505</v>
       </c>
       <c r="D25" t="n">
-        <v>634.0293422915395</v>
+        <v>623.8937717318939</v>
       </c>
       <c r="E25" t="n">
-        <v>635.55419921875</v>
+        <v>625.1993408203125</v>
       </c>
       <c r="F25" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B26" t="n">
-        <v>625.9168165443936</v>
+        <v>630.1724007040705</v>
       </c>
       <c r="C26" t="n">
-        <v>639.5705142822006</v>
+        <v>640.0588479681868</v>
       </c>
       <c r="D26" t="n">
-        <v>623.8937108241939</v>
+        <v>624.4218873891514</v>
       </c>
       <c r="E26" t="n">
-        <v>625.1992797851562</v>
+        <v>633.8001098632812</v>
       </c>
       <c r="F26" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B27" t="n">
-        <v>630.1724007040705</v>
+        <v>633.7004019945108</v>
       </c>
       <c r="C27" t="n">
-        <v>640.0588479681868</v>
+        <v>633.8499192315176</v>
       </c>
       <c r="D27" t="n">
-        <v>624.4218873891514</v>
+        <v>615.9107705740217</v>
       </c>
       <c r="E27" t="n">
-        <v>633.8001098632812</v>
+        <v>616.8475952148438</v>
       </c>
       <c r="F27" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B28" t="n">
-        <v>633.7004019945108</v>
+        <v>614.4058914069517</v>
       </c>
       <c r="C28" t="n">
-        <v>633.8499192315176</v>
+        <v>620.0268394880455</v>
       </c>
       <c r="D28" t="n">
-        <v>615.9107705740217</v>
+        <v>599.1676024999227</v>
       </c>
       <c r="E28" t="n">
-        <v>616.8475952148438</v>
+        <v>619.6082763671875</v>
       </c>
       <c r="F28" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B29" t="n">
-        <v>614.4058308842617</v>
+        <v>628.9565496273584</v>
       </c>
       <c r="C29" t="n">
-        <v>620.0267784116583</v>
+        <v>632.8533046281837</v>
       </c>
       <c r="D29" t="n">
-        <v>599.1675434782962</v>
+        <v>616.0203887455347</v>
       </c>
       <c r="E29" t="n">
-        <v>619.6082153320312</v>
+        <v>629.624267578125</v>
       </c>
       <c r="F29" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B30" t="n">
-        <v>628.9565496273584</v>
+        <v>625.8770169082796</v>
       </c>
       <c r="C30" t="n">
-        <v>632.8533046281837</v>
+        <v>627.4317408228605</v>
       </c>
       <c r="D30" t="n">
-        <v>616.0203887455347</v>
+        <v>617.2961380110504</v>
       </c>
       <c r="E30" t="n">
-        <v>629.624267578125</v>
+        <v>624.9601440429688</v>
       </c>
       <c r="F30" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B31" t="n">
-        <v>625.8769557835792</v>
+        <v>626.0065923024907</v>
       </c>
       <c r="C31" t="n">
-        <v>627.431679546322</v>
+        <v>626.8636704474237</v>
       </c>
       <c r="D31" t="n">
-        <v>617.29607772438</v>
+        <v>605.7154345004715</v>
       </c>
       <c r="E31" t="n">
-        <v>624.9600830078125</v>
+        <v>606.9512329101562</v>
       </c>
       <c r="F31" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B32" t="n">
-        <v>626.0065293511232</v>
+        <v>610.9974282481795</v>
       </c>
       <c r="C32" t="n">
-        <v>626.8636074098682</v>
+        <v>615.5619618736964</v>
       </c>
       <c r="D32" t="n">
-        <v>605.7153735895874</v>
+        <v>600.9614641591972</v>
       </c>
       <c r="E32" t="n">
-        <v>606.951171875</v>
+        <v>607.8281860351562</v>
       </c>
       <c r="F32" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B33" t="n">
-        <v>610.9974896015757</v>
+        <v>599.7556041676178</v>
       </c>
       <c r="C33" t="n">
-        <v>615.5620236854409</v>
+        <v>611.6054241702889</v>
       </c>
       <c r="D33" t="n">
-        <v>600.9615245048305</v>
+        <v>593.1879159768617</v>
       </c>
       <c r="E33" t="n">
-        <v>607.8282470703125</v>
+        <v>607.3997192382812</v>
       </c>
       <c r="F33" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B34" t="n">
-        <v>599.7555439005879</v>
+        <v>606.9810562524968</v>
       </c>
       <c r="C34" t="n">
-        <v>611.6053627125183</v>
+        <v>609.6221219886945</v>
       </c>
       <c r="D34" t="n">
-        <v>593.1878563697925</v>
+        <v>593.3872138938384</v>
       </c>
       <c r="E34" t="n">
-        <v>607.399658203125</v>
+        <v>599.974853515625</v>
       </c>
       <c r="F34" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B35" t="n">
-        <v>606.9810562524968</v>
+        <v>589.5999948667346</v>
       </c>
       <c r="C35" t="n">
-        <v>609.6221219886945</v>
+        <v>601.619222033871</v>
       </c>
       <c r="D35" t="n">
-        <v>593.3872138938384</v>
+        <v>581.8064849239344</v>
       </c>
       <c r="E35" t="n">
-        <v>599.974853515625</v>
+        <v>595.66943359375</v>
       </c>
       <c r="F35" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B36" t="n">
-        <v>589.5999948667346</v>
+        <v>591.7128714929664</v>
       </c>
       <c r="C36" t="n">
-        <v>601.619222033871</v>
+        <v>593.3174750396417</v>
       </c>
       <c r="D36" t="n">
-        <v>581.8064849239344</v>
+        <v>579.2850561317264</v>
       </c>
       <c r="E36" t="n">
-        <v>595.66943359375</v>
+        <v>588.3244018554688</v>
       </c>
       <c r="F36" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B37" t="n">
-        <v>591.7128101062766</v>
+        <v>601.4598513214113</v>
       </c>
       <c r="C37" t="n">
-        <v>593.3174134864839</v>
+        <v>604.668936823252</v>
       </c>
       <c r="D37" t="n">
-        <v>579.2849960343485</v>
+        <v>581.3779446301025</v>
       </c>
       <c r="E37" t="n">
-        <v>588.3243408203125</v>
+        <v>587.1583862304688</v>
       </c>
       <c r="F37" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B38" t="n">
-        <v>601.4598513214113</v>
+        <v>586.5104667718139</v>
       </c>
       <c r="C38" t="n">
-        <v>604.668936823252</v>
+        <v>596.097939714081</v>
       </c>
       <c r="D38" t="n">
-        <v>581.3779446301025</v>
+        <v>579.8928999224906</v>
       </c>
       <c r="E38" t="n">
-        <v>587.1583862304688</v>
+        <v>592.2410278320312</v>
       </c>
       <c r="F38" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B39" t="n">
-        <v>586.5104667718139</v>
+        <v>596.6959653725695</v>
       </c>
       <c r="C39" t="n">
-        <v>596.097939714081</v>
+        <v>614.6152243710839</v>
       </c>
       <c r="D39" t="n">
-        <v>579.8928999224906</v>
+        <v>595.6096842408232</v>
       </c>
       <c r="E39" t="n">
-        <v>592.2410278320312</v>
+        <v>610.9775390625</v>
       </c>
       <c r="F39" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B40" t="n">
-        <v>596.6959057641074</v>
+        <v>621.8904932046078</v>
       </c>
       <c r="C40" t="n">
-        <v>614.6151629725317</v>
+        <v>634.8963639496133</v>
       </c>
       <c r="D40" t="n">
-        <v>595.609624740878</v>
+        <v>616.209750572071</v>
       </c>
       <c r="E40" t="n">
-        <v>610.9774780273438</v>
+        <v>634.0691528320312</v>
       </c>
       <c r="F40" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B41" t="n">
-        <v>621.8904932046078</v>
+        <v>635.5342418532664</v>
       </c>
       <c r="C41" t="n">
-        <v>634.8963639496133</v>
+        <v>636.2019598341516</v>
       </c>
       <c r="D41" t="n">
-        <v>616.209750572071</v>
+        <v>629.4947305871518</v>
       </c>
       <c r="E41" t="n">
-        <v>634.0691528320312</v>
+        <v>631.468017578125</v>
       </c>
       <c r="F41" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B42" t="n">
-        <v>635.5342418532664</v>
+        <v>633.9296546389559</v>
       </c>
       <c r="C42" t="n">
-        <v>636.2019598341516</v>
+        <v>645.8591590880771</v>
       </c>
       <c r="D42" t="n">
-        <v>629.4947305871518</v>
+        <v>633.3515983825566</v>
       </c>
       <c r="E42" t="n">
-        <v>631.468017578125</v>
+        <v>645.759521484375</v>
       </c>
       <c r="F42" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B43" t="n">
-        <v>633.9296546389559</v>
+        <v>637.3879462598147</v>
       </c>
       <c r="C43" t="n">
-        <v>645.8591590880771</v>
+        <v>643.138459853903</v>
       </c>
       <c r="D43" t="n">
-        <v>633.3515983825566</v>
+        <v>635.6040193729798</v>
       </c>
       <c r="E43" t="n">
-        <v>645.759521484375</v>
+        <v>638.7034912109375</v>
       </c>
       <c r="F43" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B44" t="n">
-        <v>637.3879462598147</v>
+        <v>640.1684359456628</v>
       </c>
       <c r="C44" t="n">
-        <v>643.138459853903</v>
+        <v>645.6797087683515</v>
       </c>
       <c r="D44" t="n">
-        <v>635.6040193729798</v>
+        <v>635.9128522820391</v>
       </c>
       <c r="E44" t="n">
-        <v>638.7034912109375</v>
+        <v>644.9122924804688</v>
       </c>
       <c r="F44" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B45" t="n">
-        <v>640.1684965318557</v>
+        <v>642.2314810232181</v>
       </c>
       <c r="C45" t="n">
-        <v>645.6797698761368</v>
+        <v>646.6564735939825</v>
       </c>
       <c r="D45" t="n">
-        <v>635.9129124654792</v>
+        <v>635.3946865356451</v>
       </c>
       <c r="E45" t="n">
-        <v>644.912353515625</v>
+        <v>637.437744140625</v>
       </c>
       <c r="F45" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B46" t="n">
-        <v>642.2315425173783</v>
+        <v>673.7146932031604</v>
       </c>
       <c r="C46" t="n">
-        <v>646.6565355118391</v>
+        <v>673.8143308084973</v>
       </c>
       <c r="D46" t="n">
-        <v>635.394747375177</v>
+        <v>657.8186021075292</v>
       </c>
       <c r="E46" t="n">
-        <v>637.4378051757812</v>
+        <v>659.2936401367188</v>
       </c>
       <c r="F46" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B47" t="n">
-        <v>673.7146932031604</v>
+        <v>661.7552947151958</v>
       </c>
       <c r="C47" t="n">
-        <v>673.8143308084973</v>
+        <v>672.4091587454953</v>
       </c>
       <c r="D47" t="n">
-        <v>657.8186021075292</v>
+        <v>660.1507520483126</v>
       </c>
       <c r="E47" t="n">
-        <v>659.2936401367188</v>
+        <v>671.1434326171875</v>
       </c>
       <c r="F47" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B48" t="n">
-        <v>661.7552947151958</v>
+        <v>667.0772284693074</v>
       </c>
       <c r="C48" t="n">
-        <v>672.4091587454953</v>
+        <v>674.4223082782987</v>
       </c>
       <c r="D48" t="n">
-        <v>660.1507520483126</v>
+        <v>662.8216443414645</v>
       </c>
       <c r="E48" t="n">
-        <v>671.1434326171875</v>
+        <v>664.5457763671875</v>
       </c>
       <c r="F48" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B49" t="n">
-        <v>667.0772284693074</v>
+        <v>661.5260500954003</v>
       </c>
       <c r="C49" t="n">
-        <v>674.4223082782987</v>
+        <v>662.2336109084633</v>
       </c>
       <c r="D49" t="n">
-        <v>662.8216443414645</v>
+        <v>651.1313175008097</v>
       </c>
       <c r="E49" t="n">
-        <v>664.5457763671875</v>
+        <v>654.7390747070312</v>
       </c>
       <c r="F49" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B50" t="n">
-        <v>661.5260500954003</v>
+        <v>647.7527447265774</v>
       </c>
       <c r="C50" t="n">
-        <v>662.2336109084633</v>
+        <v>652.2973264314004</v>
       </c>
       <c r="D50" t="n">
-        <v>651.1313175008097</v>
+        <v>641.2249002906431</v>
       </c>
       <c r="E50" t="n">
-        <v>654.7390747070312</v>
+        <v>647.93212890625</v>
       </c>
       <c r="F50" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B51" t="n">
-        <v>647.7527447265774</v>
+        <v>641.1152803360264</v>
       </c>
       <c r="C51" t="n">
-        <v>652.2973264314004</v>
+        <v>653.0647981949571</v>
       </c>
       <c r="D51" t="n">
-        <v>641.2249002906431</v>
+        <v>638.6337077300913</v>
       </c>
       <c r="E51" t="n">
-        <v>647.93212890625</v>
+        <v>650.5034790039062</v>
       </c>
       <c r="F51" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B52" t="n">
-        <v>641.1152803360264</v>
+        <v>647.6033016180266</v>
       </c>
       <c r="C52" t="n">
-        <v>653.0647981949571</v>
+        <v>708.5964236692454</v>
       </c>
       <c r="D52" t="n">
-        <v>638.6337077300913</v>
+        <v>636.4511276224844</v>
       </c>
       <c r="E52" t="n">
-        <v>650.5034790039062</v>
+        <v>642.0521240234375</v>
       </c>
       <c r="F52" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B53" t="n">
-        <v>647.6033016180266</v>
+        <v>644.0420011784053</v>
       </c>
       <c r="C53" t="n">
-        <v>708.5964236692454</v>
+        <v>651.3232442601446</v>
       </c>
       <c r="D53" t="n">
-        <v>636.4511276224844</v>
+        <v>637.0599755890928</v>
       </c>
       <c r="E53" t="n">
-        <v>642.0521240234375</v>
+        <v>645.8473510742188</v>
       </c>
       <c r="F53" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1821,25 +1821,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B54" t="n">
-        <v>644.0420011784053</v>
+        <v>641.8476715248971</v>
       </c>
       <c r="C54" t="n">
-        <v>651.3232442601446</v>
+        <v>660.8387602004772</v>
       </c>
       <c r="D54" t="n">
-        <v>637.0599755890928</v>
+        <v>641.5484540168895</v>
       </c>
       <c r="E54" t="n">
-        <v>645.8473510742188</v>
+        <v>655.462646484375</v>
       </c>
       <c r="F54" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G54" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B55" t="n">
-        <v>641.8476715248971</v>
+        <v>653.9265104909302</v>
       </c>
       <c r="C55" t="n">
-        <v>660.8387602004772</v>
+        <v>659.5320745885969</v>
       </c>
       <c r="D55" t="n">
-        <v>641.5484540168895</v>
+        <v>647.5329968709444</v>
       </c>
       <c r="E55" t="n">
-        <v>655.462646484375</v>
+        <v>647.8322143554688</v>
       </c>
       <c r="F55" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B56" t="n">
-        <v>653.9265104909302</v>
+        <v>655.3429055936973</v>
       </c>
       <c r="C56" t="n">
-        <v>659.5320745885969</v>
+        <v>668.8381315618529</v>
       </c>
       <c r="D56" t="n">
-        <v>647.5329968709444</v>
+        <v>654.7743619360156</v>
       </c>
       <c r="E56" t="n">
-        <v>647.8322143554688</v>
+        <v>662.7438354492188</v>
       </c>
       <c r="F56" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B57" t="n">
-        <v>655.3429055936973</v>
+        <v>664.7087499822148</v>
       </c>
       <c r="C57" t="n">
-        <v>668.8381315618529</v>
+        <v>669.2770065062657</v>
       </c>
       <c r="D57" t="n">
-        <v>654.7743619360156</v>
+        <v>656.4899183910027</v>
       </c>
       <c r="E57" t="n">
-        <v>662.7438354492188</v>
+        <v>657.0784301757812</v>
       </c>
       <c r="F57" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B58" t="n">
-        <v>664.7087499822148</v>
+        <v>659.9510918299604</v>
       </c>
       <c r="C58" t="n">
-        <v>669.2770065062657</v>
+        <v>671.8504516144289</v>
       </c>
       <c r="D58" t="n">
-        <v>656.4899183910027</v>
+        <v>654.9639304343692</v>
       </c>
       <c r="E58" t="n">
-        <v>657.0784301757812</v>
+        <v>659.8014526367188</v>
       </c>
       <c r="F58" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B59" t="n">
-        <v>659.9510918299604</v>
+        <v>658.3550860644432</v>
       </c>
       <c r="C59" t="n">
-        <v>671.8504516144289</v>
+        <v>664.2898196014329</v>
       </c>
       <c r="D59" t="n">
-        <v>654.9639304343692</v>
+        <v>656.5597203493141</v>
       </c>
       <c r="E59" t="n">
-        <v>659.8014526367188</v>
+        <v>663.2325439453125</v>
       </c>
       <c r="F59" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B60" t="n">
-        <v>658.3550860644432</v>
+        <v>660.8288080412273</v>
       </c>
       <c r="C60" t="n">
-        <v>664.2898196014329</v>
+        <v>666.4642636433252</v>
       </c>
       <c r="D60" t="n">
-        <v>656.5597203493141</v>
+        <v>660.499638357634</v>
       </c>
       <c r="E60" t="n">
-        <v>663.2325439453125</v>
+        <v>665.8358764648438</v>
       </c>
       <c r="F60" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B61" t="n">
-        <v>660.8288080412273</v>
+        <v>666.3446246130748</v>
       </c>
       <c r="C61" t="n">
-        <v>666.4642636433252</v>
+        <v>667.2323539771746</v>
       </c>
       <c r="D61" t="n">
-        <v>660.499638357634</v>
+        <v>659.6219406041037</v>
       </c>
       <c r="E61" t="n">
-        <v>665.8358764648438</v>
+        <v>661.5868530273438</v>
       </c>
       <c r="F61" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B62" t="n">
-        <v>666.3446246130748</v>
+        <v>656.3204105957403</v>
       </c>
       <c r="C62" t="n">
-        <v>667.2323539771746</v>
+        <v>658.5546491157273</v>
       </c>
       <c r="D62" t="n">
-        <v>659.6219406041037</v>
+        <v>652.7097106878265</v>
       </c>
       <c r="E62" t="n">
-        <v>661.5868530273438</v>
+        <v>656.9986572265625</v>
       </c>
       <c r="F62" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B63" t="n">
-        <v>656.3204105957403</v>
+        <v>656.9986226731097</v>
       </c>
       <c r="C63" t="n">
-        <v>658.5546491157273</v>
+        <v>670.4938487731155</v>
       </c>
       <c r="D63" t="n">
-        <v>652.7097106878265</v>
+        <v>656.1508296487782</v>
       </c>
       <c r="E63" t="n">
-        <v>656.9986572265625</v>
+        <v>664.239990234375</v>
       </c>
       <c r="F63" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B64" t="n">
-        <v>656.9986226731097</v>
+        <v>663.0430265979899</v>
       </c>
       <c r="C64" t="n">
-        <v>670.4938487731155</v>
+        <v>663.2923846373272</v>
       </c>
       <c r="D64" t="n">
-        <v>656.1508296487782</v>
+        <v>657.7466642776019</v>
       </c>
       <c r="E64" t="n">
-        <v>664.239990234375</v>
+        <v>658.39501953125</v>
       </c>
       <c r="F64" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B65" t="n">
-        <v>663.0430265979899</v>
+        <v>661.0282405096659</v>
       </c>
       <c r="C65" t="n">
-        <v>663.2923846373272</v>
+        <v>662.6840120988863</v>
       </c>
       <c r="D65" t="n">
-        <v>657.7466642776019</v>
+        <v>641.8476382600104</v>
       </c>
       <c r="E65" t="n">
-        <v>658.39501953125</v>
+        <v>648.7398681640625</v>
       </c>
       <c r="F65" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B66" t="n">
-        <v>661.0282405096659</v>
+        <v>649.3383972038786</v>
       </c>
       <c r="C66" t="n">
-        <v>662.6840120988863</v>
+        <v>662.8336242718107</v>
       </c>
       <c r="D66" t="n">
-        <v>641.8476382600104</v>
+        <v>646.086758236235</v>
       </c>
       <c r="E66" t="n">
-        <v>648.7398681640625</v>
+        <v>657.098388671875</v>
       </c>
       <c r="F66" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B67" t="n">
-        <v>649.3383972038786</v>
+        <v>657.8763534012292</v>
       </c>
       <c r="C67" t="n">
-        <v>662.8336242718107</v>
+        <v>663.8110870761799</v>
       </c>
       <c r="D67" t="n">
-        <v>646.086758236235</v>
+        <v>650.2260655901538</v>
       </c>
       <c r="E67" t="n">
-        <v>657.098388671875</v>
+        <v>658.9236450195312</v>
       </c>
       <c r="F67" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B68" t="n">
-        <v>657.8763534012292</v>
+        <v>653.956457912222</v>
       </c>
       <c r="C68" t="n">
-        <v>663.8110870761799</v>
+        <v>657.4574546517152</v>
       </c>
       <c r="D68" t="n">
-        <v>650.2260655901538</v>
+        <v>643.154250211399</v>
       </c>
       <c r="E68" t="n">
-        <v>658.9236450195312</v>
+        <v>647.0242919921875</v>
       </c>
       <c r="F68" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B69" t="n">
-        <v>653.956457912222</v>
+        <v>644.2215315163064</v>
       </c>
       <c r="C69" t="n">
-        <v>657.4574546517152</v>
+        <v>645.4383696113561</v>
       </c>
       <c r="D69" t="n">
-        <v>643.154250211399</v>
+        <v>634.0875860000896</v>
       </c>
       <c r="E69" t="n">
-        <v>647.0242919921875</v>
+        <v>644.4010620117188</v>
       </c>
       <c r="F69" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B70" t="n">
-        <v>644.2215315163064</v>
+        <v>643.7826886268982</v>
       </c>
       <c r="C70" t="n">
-        <v>645.4383696113561</v>
+        <v>653.2682792823022</v>
       </c>
       <c r="D70" t="n">
-        <v>634.0875860000896</v>
+        <v>641.1993122536916</v>
       </c>
       <c r="E70" t="n">
-        <v>644.4010620117188</v>
+        <v>651.3831176757812</v>
       </c>
       <c r="F70" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B71" t="n">
-        <v>643.7826886268982</v>
+        <v>650.8544758921091</v>
       </c>
       <c r="C71" t="n">
-        <v>653.2682792823022</v>
+        <v>652.2907198459545</v>
       </c>
       <c r="D71" t="n">
-        <v>641.1993122536916</v>
+        <v>639.5834431006995</v>
       </c>
       <c r="E71" t="n">
-        <v>651.3831176757812</v>
+        <v>640.321533203125</v>
       </c>
       <c r="F71" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B72" t="n">
-        <v>650.8544758921091</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="C72" t="n">
-        <v>652.2907198459545</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="D72" t="n">
-        <v>639.5834431006995</v>
+        <v>622.4974409136</v>
       </c>
       <c r="E72" t="n">
-        <v>640.321533203125</v>
+        <v>629.4695434570312</v>
       </c>
       <c r="F72" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B73" t="n">
-        <v>640.6208286715078</v>
+        <v>624.8913007155408</v>
       </c>
       <c r="C73" t="n">
-        <v>640.6208286715078</v>
+        <v>626.836305766559</v>
       </c>
       <c r="D73" t="n">
-        <v>622.4974409136</v>
+        <v>613.2412994138377</v>
       </c>
       <c r="E73" t="n">
-        <v>629.4695434570312</v>
+        <v>613.9395141601562</v>
       </c>
       <c r="F73" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B74" t="n">
-        <v>624.8913007155408</v>
+        <v>616.8918824768537</v>
       </c>
       <c r="C74" t="n">
-        <v>626.836305766559</v>
+        <v>622.567274451088</v>
       </c>
       <c r="D74" t="n">
-        <v>613.2412994138377</v>
+        <v>612.6527953870184</v>
       </c>
       <c r="E74" t="n">
-        <v>613.9395141601562</v>
+        <v>619.2059326171875</v>
       </c>
       <c r="F74" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B75" t="n">
-        <v>616.8918824768537</v>
+        <v>622.5772500418334</v>
       </c>
       <c r="C75" t="n">
-        <v>622.567274451088</v>
+        <v>627.4646923832119</v>
       </c>
       <c r="D75" t="n">
-        <v>612.6527953870184</v>
+        <v>618.4878021974878</v>
       </c>
       <c r="E75" t="n">
-        <v>619.2059326171875</v>
+        <v>618.6573486328125</v>
       </c>
       <c r="F75" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B76" t="n">
-        <v>622.5772500418334</v>
+        <v>606.3191417499893</v>
       </c>
       <c r="C76" t="n">
-        <v>627.4646923832119</v>
+        <v>609.8301228712422</v>
       </c>
       <c r="D76" t="n">
-        <v>618.4878021974878</v>
+        <v>598.4593704807342</v>
       </c>
       <c r="E76" t="n">
-        <v>618.6573486328125</v>
+        <v>602.5687866210938</v>
       </c>
       <c r="F76" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B77" t="n">
-        <v>606.3191417499893</v>
+        <v>605.1820479992876</v>
       </c>
       <c r="C77" t="n">
-        <v>609.8301228712422</v>
+        <v>616.6824713366042</v>
       </c>
       <c r="D77" t="n">
-        <v>598.4593704807342</v>
+        <v>598.5391758430108</v>
       </c>
       <c r="E77" t="n">
-        <v>602.5687866210938</v>
+        <v>611.3861083984375</v>
       </c>
       <c r="F77" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B78" t="n">
-        <v>605.1820479992876</v>
+        <v>627.7339506004921</v>
       </c>
       <c r="C78" t="n">
-        <v>616.6824713366042</v>
+        <v>658.8738165275513</v>
       </c>
       <c r="D78" t="n">
-        <v>598.5391758430108</v>
+        <v>624.9411525277235</v>
       </c>
       <c r="E78" t="n">
-        <v>611.3861083984375</v>
+        <v>645.967041015625</v>
       </c>
       <c r="F78" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B79" t="n">
-        <v>627.7339506004921</v>
+        <v>643.1144139511335</v>
       </c>
       <c r="C79" t="n">
-        <v>658.8738165275513</v>
+        <v>664.7786132883346</v>
       </c>
       <c r="D79" t="n">
-        <v>624.9411525277235</v>
+        <v>642.7952283244125</v>
       </c>
       <c r="E79" t="n">
-        <v>645.967041015625</v>
+        <v>657.0684814453125</v>
       </c>
       <c r="F79" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B80" t="n">
-        <v>643.1144139511335</v>
+        <v>663.4220687284304</v>
       </c>
       <c r="C80" t="n">
-        <v>664.7786132883346</v>
+        <v>673.5460296758964</v>
       </c>
       <c r="D80" t="n">
-        <v>642.7952283244125</v>
+        <v>659.5919023824141</v>
       </c>
       <c r="E80" t="n">
-        <v>657.0684814453125</v>
+        <v>670.6334838867188</v>
       </c>
       <c r="F80" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B81" t="n">
-        <v>663.4220687284304</v>
+        <v>672.8578395915863</v>
       </c>
       <c r="C81" t="n">
-        <v>673.5460296758964</v>
+        <v>675.0820939991542</v>
       </c>
       <c r="D81" t="n">
-        <v>659.5919023824141</v>
+        <v>662.9532839044604</v>
       </c>
       <c r="E81" t="n">
-        <v>670.6334838867188</v>
+        <v>671.241943359375</v>
       </c>
       <c r="F81" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B82" t="n">
-        <v>672.8578395915863</v>
+        <v>672.7679591112906</v>
       </c>
       <c r="C82" t="n">
-        <v>675.0820939991542</v>
+        <v>675.9397859199995</v>
       </c>
       <c r="D82" t="n">
-        <v>662.9532839044604</v>
+        <v>664.3895050245095</v>
       </c>
       <c r="E82" t="n">
-        <v>671.241943359375</v>
+        <v>667.0127563476562</v>
       </c>
       <c r="F82" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B83" t="n">
-        <v>672.7679591112906</v>
+        <v>735.536439340887</v>
       </c>
       <c r="C83" t="n">
-        <v>675.9397859199995</v>
+        <v>742.0895763731422</v>
       </c>
       <c r="D83" t="n">
-        <v>664.3895050245095</v>
+        <v>710.7203206800697</v>
       </c>
       <c r="E83" t="n">
-        <v>667.0127563476562</v>
+        <v>736.4141845703125</v>
       </c>
       <c r="F83" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B84" t="n">
-        <v>735.536439340887</v>
+        <v>725.6319102189462</v>
       </c>
       <c r="C84" t="n">
-        <v>742.0895763731422</v>
+        <v>730.2899014488934</v>
       </c>
       <c r="D84" t="n">
-        <v>710.7203206800697</v>
+        <v>711.7576553956329</v>
       </c>
       <c r="E84" t="n">
-        <v>736.4141845703125</v>
+        <v>714.66015625</v>
       </c>
       <c r="F84" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B85" t="n">
-        <v>725.6319102189462</v>
+        <v>712.7649799285471</v>
       </c>
       <c r="C85" t="n">
-        <v>730.2899014488934</v>
+        <v>719.4477874144414</v>
       </c>
       <c r="D85" t="n">
-        <v>711.7576553956329</v>
+        <v>701.7134756957726</v>
       </c>
       <c r="E85" t="n">
-        <v>714.66015625</v>
+        <v>704.5960083007812</v>
       </c>
       <c r="F85" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B86" t="n">
-        <v>712.7649799285471</v>
+        <v>705.5535728195721</v>
       </c>
       <c r="C86" t="n">
-        <v>719.4477874144414</v>
+        <v>715.1588492636382</v>
       </c>
       <c r="D86" t="n">
-        <v>701.7134756957726</v>
+        <v>684.6473731061755</v>
       </c>
       <c r="E86" t="n">
-        <v>704.5960083007812</v>
+        <v>689.923828125</v>
       </c>
       <c r="F86" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B87" t="n">
-        <v>705.5535728195721</v>
+        <v>685.9640881387202</v>
       </c>
       <c r="C87" t="n">
-        <v>715.1588492636382</v>
+        <v>687.0613001828912</v>
       </c>
       <c r="D87" t="n">
-        <v>684.6473731061755</v>
+        <v>665.7461770525908</v>
       </c>
       <c r="E87" t="n">
-        <v>689.923828125</v>
+        <v>667.272216796875</v>
       </c>
       <c r="F87" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B88" t="n">
-        <v>685.9640881387202</v>
+        <v>661.8760941724082</v>
       </c>
       <c r="C88" t="n">
-        <v>687.0613001828912</v>
+        <v>679.7500626324993</v>
       </c>
       <c r="D88" t="n">
-        <v>665.7461770525908</v>
+        <v>651.8219602792932</v>
       </c>
       <c r="E88" t="n">
-        <v>667.272216796875</v>
+        <v>668.4890747070312</v>
       </c>
       <c r="F88" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B89" t="n">
-        <v>661.8760941724082</v>
+        <v>663.7811558190369</v>
       </c>
       <c r="C89" t="n">
-        <v>679.7500626324993</v>
+        <v>670.2644652243433</v>
       </c>
       <c r="D89" t="n">
-        <v>651.8219602792932</v>
+        <v>644.8399277739295</v>
       </c>
       <c r="E89" t="n">
-        <v>668.4890747070312</v>
+        <v>659.7615356445312</v>
       </c>
       <c r="F89" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B90" t="n">
-        <v>663.7811558190369</v>
+        <v>661.4770916291903</v>
       </c>
       <c r="C90" t="n">
-        <v>670.2644652243433</v>
+        <v>681.5554070660584</v>
       </c>
       <c r="D90" t="n">
-        <v>644.8399277739295</v>
+        <v>657.0884263930592</v>
       </c>
       <c r="E90" t="n">
-        <v>659.7615356445312</v>
+        <v>675.4810180664062</v>
       </c>
       <c r="F90" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B91" t="n">
-        <v>661.4770916291903</v>
+        <v>675.8600189134125</v>
       </c>
       <c r="C91" t="n">
-        <v>681.5554070660584</v>
+        <v>678.9022357565889</v>
       </c>
       <c r="D91" t="n">
-        <v>657.0884263930592</v>
+        <v>668.0700760446862</v>
       </c>
       <c r="E91" t="n">
-        <v>675.4810180664062</v>
+        <v>668.9976806640625</v>
       </c>
       <c r="F91" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B92" t="n">
-        <v>675.8600189134125</v>
+        <v>672.2693241407737</v>
       </c>
       <c r="C92" t="n">
-        <v>678.9022357565889</v>
+        <v>677.5258114827353</v>
       </c>
       <c r="D92" t="n">
-        <v>668.0700760446862</v>
+        <v>655.4126950742984</v>
       </c>
       <c r="E92" t="n">
-        <v>668.9976806640625</v>
+        <v>666.9729614257812</v>
       </c>
       <c r="F92" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B93" t="n">
-        <v>672.2693241407737</v>
+        <v>668.2496249159107</v>
       </c>
       <c r="C93" t="n">
-        <v>677.5258114827353</v>
+        <v>674.2641703314905</v>
       </c>
       <c r="D93" t="n">
-        <v>655.4126950742984</v>
+        <v>643.6230822268304</v>
       </c>
       <c r="E93" t="n">
-        <v>666.9729614257812</v>
+        <v>648.1414184570312</v>
       </c>
       <c r="F93" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B94" t="n">
-        <v>668.2496249159107</v>
+        <v>643.4434668857905</v>
       </c>
       <c r="C94" t="n">
-        <v>674.2641703314905</v>
+        <v>649.7572295518577</v>
       </c>
       <c r="D94" t="n">
-        <v>643.6230822268304</v>
+        <v>632.9405378190771</v>
       </c>
       <c r="E94" t="n">
-        <v>648.1414184570312</v>
+        <v>638.127197265625</v>
       </c>
       <c r="F94" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B95" t="n">
-        <v>643.4434668857905</v>
+        <v>637.8579201875249</v>
       </c>
       <c r="C95" t="n">
-        <v>649.7572295518577</v>
+        <v>640.9499357932766</v>
       </c>
       <c r="D95" t="n">
-        <v>632.9405378190771</v>
+        <v>627.1853829985365</v>
       </c>
       <c r="E95" t="n">
-        <v>638.127197265625</v>
+        <v>637.6484375</v>
       </c>
       <c r="F95" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B96" t="n">
-        <v>637.8579201875249</v>
+        <v>632.1725042393389</v>
       </c>
       <c r="C96" t="n">
-        <v>640.9499357932766</v>
+        <v>643.3437568439427</v>
       </c>
       <c r="D96" t="n">
-        <v>627.1853829985365</v>
+        <v>626.5370489428796</v>
       </c>
       <c r="E96" t="n">
-        <v>637.6484375</v>
+        <v>641.5682983398438</v>
       </c>
       <c r="F96" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B97" t="n">
-        <v>632.1725042393389</v>
+        <v>636.9302530675583</v>
       </c>
       <c r="C97" t="n">
-        <v>643.3437568439427</v>
+        <v>645.5281132997313</v>
       </c>
       <c r="D97" t="n">
-        <v>626.5370489428796</v>
+        <v>635.0849670695593</v>
       </c>
       <c r="E97" t="n">
-        <v>641.5682983398438</v>
+        <v>643.1243286132812</v>
       </c>
       <c r="F97" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B98" t="n">
-        <v>636.9302530675583</v>
+        <v>638.0474756888525</v>
       </c>
       <c r="C98" t="n">
-        <v>645.5281132997313</v>
+        <v>661.6466973151385</v>
       </c>
       <c r="D98" t="n">
-        <v>635.0849670695593</v>
+        <v>637.1398390748724</v>
       </c>
       <c r="E98" t="n">
-        <v>643.1243286132812</v>
+        <v>653.9764404296875</v>
       </c>
       <c r="F98" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B99" t="n">
-        <v>638.0474756888525</v>
+        <v>650.8644258547187</v>
       </c>
       <c r="C99" t="n">
-        <v>661.6466973151385</v>
+        <v>656.0112104148094</v>
       </c>
       <c r="D99" t="n">
-        <v>637.1398390748724</v>
+        <v>634.3669181695027</v>
       </c>
       <c r="E99" t="n">
-        <v>653.9764404296875</v>
+        <v>635.6137084960938</v>
       </c>
       <c r="F99" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B100" t="n">
-        <v>650.8644258547187</v>
+        <v>631.4544476780686</v>
       </c>
       <c r="C100" t="n">
-        <v>656.0112104148094</v>
+        <v>639.4637972653206</v>
       </c>
       <c r="D100" t="n">
-        <v>634.3669181695027</v>
+        <v>627.364938784811</v>
       </c>
       <c r="E100" t="n">
-        <v>635.6137084960938</v>
+        <v>637.658447265625</v>
       </c>
       <c r="F100" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B101" t="n">
-        <v>631.4544476780686</v>
+        <v>640.8800977544264</v>
       </c>
       <c r="C101" t="n">
-        <v>639.4637972653206</v>
+        <v>652.2009281146602</v>
       </c>
       <c r="D101" t="n">
-        <v>627.364938784811</v>
+        <v>640.4910846116635</v>
       </c>
       <c r="E101" t="n">
-        <v>637.658447265625</v>
+        <v>652.0114135742188</v>
       </c>
       <c r="F101" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B102" t="n">
-        <v>640.8800977544264</v>
+        <v>648.8795635426123</v>
       </c>
       <c r="C102" t="n">
-        <v>652.2009281146602</v>
+        <v>659.3027431401059</v>
       </c>
       <c r="D102" t="n">
-        <v>640.4910846116635</v>
+        <v>645.8374072363367</v>
       </c>
       <c r="E102" t="n">
-        <v>652.0114135742188</v>
+        <v>655.322998046875</v>
       </c>
       <c r="F102" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B103" t="n">
-        <v>648.8795635426123</v>
+        <v>641.7977293743734</v>
       </c>
       <c r="C103" t="n">
-        <v>659.3027431401059</v>
+        <v>647.7723382149427</v>
       </c>
       <c r="D103" t="n">
-        <v>645.8374072363367</v>
+        <v>636.4813989665846</v>
       </c>
       <c r="E103" t="n">
-        <v>655.322998046875</v>
+        <v>646.5155639648438</v>
       </c>
       <c r="F103" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B104" t="n">
-        <v>641.7977293743734</v>
+        <v>635.5238627543893</v>
       </c>
       <c r="C104" t="n">
-        <v>647.7723382149427</v>
+        <v>658.2453970983619</v>
       </c>
       <c r="D104" t="n">
-        <v>636.4813989665846</v>
+        <v>632.870719934867</v>
       </c>
       <c r="E104" t="n">
-        <v>646.5155639648438</v>
+        <v>651.8817749023438</v>
       </c>
       <c r="F104" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B105" t="n">
-        <v>635.5238627543893</v>
+        <v>646.6252847330551</v>
       </c>
       <c r="C105" t="n">
-        <v>658.2453970983619</v>
+        <v>657.3476806461185</v>
       </c>
       <c r="D105" t="n">
-        <v>632.870719934867</v>
+        <v>637.199599354082</v>
       </c>
       <c r="E105" t="n">
-        <v>651.8817749023438</v>
+        <v>653.3978881835938</v>
       </c>
       <c r="F105" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B106" t="n">
-        <v>646.6252847330551</v>
+        <v>656.2705097002453</v>
       </c>
       <c r="C106" t="n">
-        <v>657.3476806461185</v>
+        <v>671.0424780902056</v>
       </c>
       <c r="D106" t="n">
-        <v>637.199599354082</v>
+        <v>655.9812154011644</v>
       </c>
       <c r="E106" t="n">
-        <v>653.3978881835938</v>
+        <v>666.015380859375</v>
       </c>
       <c r="F106" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B107" t="n">
-        <v>656.2705097002453</v>
+        <v>660.2303336051802</v>
       </c>
       <c r="C107" t="n">
-        <v>671.0424780902056</v>
+        <v>668.9778340733714</v>
       </c>
       <c r="D107" t="n">
-        <v>655.9812154011644</v>
+        <v>648.6401755256248</v>
       </c>
       <c r="E107" t="n">
-        <v>666.015380859375</v>
+        <v>658.8738403320312</v>
       </c>
       <c r="F107" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B108" t="n">
-        <v>660.2303336051802</v>
+        <v>646.2363343546218</v>
       </c>
       <c r="C108" t="n">
-        <v>668.9778340733714</v>
+        <v>647.8022493056128</v>
       </c>
       <c r="D108" t="n">
-        <v>648.6401755256248</v>
+        <v>634.4765699796501</v>
       </c>
       <c r="E108" t="n">
-        <v>658.8738403320312</v>
+        <v>643.2041015625</v>
       </c>
       <c r="F108" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B109" t="n">
-        <v>646.2363343546218</v>
+        <v>633.1500554179556</v>
       </c>
       <c r="C109" t="n">
-        <v>647.8022493056128</v>
+        <v>646.0867221220876</v>
       </c>
       <c r="D109" t="n">
-        <v>634.4765699796501</v>
+        <v>625.1705976379839</v>
       </c>
       <c r="E109" t="n">
-        <v>643.2041015625</v>
+        <v>645.7276611328125</v>
       </c>
       <c r="F109" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B110" t="n">
-        <v>633.1500554179556</v>
+        <v>651.8818637417822</v>
       </c>
       <c r="C110" t="n">
-        <v>646.0867221220876</v>
+        <v>658.6045478289335</v>
       </c>
       <c r="D110" t="n">
-        <v>625.1705976379839</v>
+        <v>647.3335748038755</v>
       </c>
       <c r="E110" t="n">
-        <v>645.7276611328125</v>
+        <v>652.3905639648438</v>
       </c>
       <c r="F110" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B111" t="n">
-        <v>651.8818637417822</v>
+        <v>653.0787479235273</v>
       </c>
       <c r="C111" t="n">
-        <v>658.6045478289335</v>
+        <v>657.4275379105374</v>
       </c>
       <c r="D111" t="n">
-        <v>647.3335748038755</v>
+        <v>646.6951571900124</v>
       </c>
       <c r="E111" t="n">
-        <v>652.3905639648438</v>
+        <v>653.178466796875</v>
       </c>
       <c r="F111" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B112" t="n">
-        <v>653.0787479235273</v>
+        <v>647.0841872338415</v>
       </c>
       <c r="C112" t="n">
-        <v>657.4275379105374</v>
+        <v>651.8219905315074</v>
       </c>
       <c r="D112" t="n">
-        <v>646.6951571900124</v>
+        <v>635.2646391478804</v>
       </c>
       <c r="E112" t="n">
-        <v>653.178466796875</v>
+        <v>636.5413208007812</v>
       </c>
       <c r="F112" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B113" t="n">
-        <v>647.0841872338415</v>
+        <v>622.2879460132801</v>
       </c>
       <c r="C113" t="n">
-        <v>651.8219905315074</v>
+        <v>627.554356001348</v>
       </c>
       <c r="D113" t="n">
-        <v>635.2646391478804</v>
+        <v>607.9847424867846</v>
       </c>
       <c r="E113" t="n">
-        <v>636.5413208007812</v>
+        <v>612.1340942382812</v>
       </c>
       <c r="F113" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B114" t="n">
-        <v>622.2879460132801</v>
+        <v>630.9168848948667</v>
       </c>
       <c r="C114" t="n">
-        <v>627.554356001348</v>
+        <v>633.6621719731276</v>
       </c>
       <c r="D114" t="n">
-        <v>607.9847424867846</v>
+        <v>622.0321132511823</v>
       </c>
       <c r="E114" t="n">
-        <v>612.1340942382812</v>
+        <v>626.3746948242188</v>
       </c>
       <c r="F114" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,25 +3407,25 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B115" t="n">
-        <v>630.9168848948667</v>
+        <v>626.9137783313067</v>
       </c>
       <c r="C115" t="n">
-        <v>633.6621719731276</v>
+        <v>635.4591062750881</v>
       </c>
       <c r="D115" t="n">
-        <v>622.0321132511823</v>
+        <v>620.634579694285</v>
       </c>
       <c r="E115" t="n">
-        <v>626.3746948242188</v>
+        <v>621.5928955078125</v>
       </c>
       <c r="F115" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G115" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B116" t="n">
-        <v>626.9137783313067</v>
+        <v>615.2837809831337</v>
       </c>
       <c r="C116" t="n">
-        <v>635.4591062750881</v>
+        <v>621.5829648535273</v>
       </c>
       <c r="D116" t="n">
-        <v>620.634579694285</v>
+        <v>613.5567043186309</v>
       </c>
       <c r="E116" t="n">
-        <v>621.5928955078125</v>
+        <v>614.6248779296875</v>
       </c>
       <c r="F116" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B117" t="n">
-        <v>615.2837809831337</v>
+        <v>611.1009505532863</v>
       </c>
       <c r="C117" t="n">
-        <v>621.5829648535273</v>
+        <v>611.9494694911245</v>
       </c>
       <c r="D117" t="n">
-        <v>613.5567043186309</v>
+        <v>601.2278849458298</v>
       </c>
       <c r="E117" t="n">
-        <v>614.6248779296875</v>
+        <v>605.6602783203125</v>
       </c>
       <c r="F117" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B118" t="n">
-        <v>611.1009505532863</v>
+        <v>602.4957192983555</v>
       </c>
       <c r="C118" t="n">
-        <v>611.9494694911245</v>
+        <v>602.9249750667714</v>
       </c>
       <c r="D118" t="n">
-        <v>601.2278849458298</v>
+        <v>586.2435901825164</v>
       </c>
       <c r="E118" t="n">
-        <v>605.6602783203125</v>
+        <v>592.642578125</v>
       </c>
       <c r="F118" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B119" t="n">
-        <v>602.4957192983555</v>
+        <v>604.7517959610541</v>
       </c>
       <c r="C119" t="n">
-        <v>602.9249750667714</v>
+        <v>607.5969482872343</v>
       </c>
       <c r="D119" t="n">
-        <v>586.2435901825164</v>
+        <v>597.9834469761715</v>
       </c>
       <c r="E119" t="n">
-        <v>592.642578125</v>
+        <v>603.0247802734375</v>
       </c>
       <c r="F119" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B120" t="n">
-        <v>604.7517959610541</v>
+        <v>598.0732713770465</v>
       </c>
       <c r="C120" t="n">
-        <v>607.5969482872343</v>
+        <v>599.9700396349708</v>
       </c>
       <c r="D120" t="n">
-        <v>597.9834469761715</v>
+        <v>589.9871770786485</v>
       </c>
       <c r="E120" t="n">
-        <v>603.0247802734375</v>
+        <v>591.9038696289062</v>
       </c>
       <c r="F120" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B121" t="n">
-        <v>598.0732713770465</v>
+        <v>597.7138608396341</v>
       </c>
       <c r="C121" t="n">
-        <v>599.9700396349708</v>
+        <v>602.6354044215132</v>
       </c>
       <c r="D121" t="n">
-        <v>589.9871770786485</v>
+        <v>592.3830467312241</v>
       </c>
       <c r="E121" t="n">
-        <v>591.9038696289062</v>
+        <v>593.8704833984375</v>
       </c>
       <c r="F121" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B122" t="n">
-        <v>597.7138608396341</v>
+        <v>581.4916747262954</v>
       </c>
       <c r="C122" t="n">
-        <v>602.6354044215132</v>
+        <v>582.0008103985165</v>
       </c>
       <c r="D122" t="n">
-        <v>592.3830467312241</v>
+        <v>542.4187412024525</v>
       </c>
       <c r="E122" t="n">
-        <v>593.8704833984375</v>
+        <v>546.6015625</v>
       </c>
       <c r="F122" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B123" t="n">
-        <v>581.4916747262954</v>
+        <v>539.1743295527585</v>
       </c>
       <c r="C123" t="n">
-        <v>582.0008103985165</v>
+        <v>542.6683311056884</v>
       </c>
       <c r="D123" t="n">
-        <v>542.4187412024525</v>
+        <v>519.368366299545</v>
       </c>
       <c r="E123" t="n">
-        <v>546.6015625</v>
+        <v>524.8189697265625</v>
       </c>
       <c r="F123" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B124" t="n">
-        <v>539.1743295527585</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="C124" t="n">
-        <v>542.6683311056884</v>
+        <v>538.6253045735799</v>
       </c>
       <c r="D124" t="n">
-        <v>519.368366299545</v>
+        <v>527.6341638126921</v>
       </c>
       <c r="E124" t="n">
-        <v>524.8189697265625</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="F124" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>535.4607543945312</v>
+        <v>549.0374119135495</v>
       </c>
       <c r="C125" t="n">
-        <v>538.6253045735799</v>
+        <v>572.7067990959439</v>
       </c>
       <c r="D125" t="n">
-        <v>527.6341638126921</v>
+        <v>545.8329522821889</v>
       </c>
       <c r="E125" t="n">
-        <v>535.4607543945312</v>
+        <v>571.1494750976562</v>
       </c>
       <c r="F125" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B126" t="n">
-        <v>549.0374119135495</v>
+        <v>579.1357866530213</v>
       </c>
       <c r="C126" t="n">
-        <v>572.7067990959439</v>
+        <v>591.5344843799961</v>
       </c>
       <c r="D126" t="n">
-        <v>545.8329522821889</v>
+        <v>572.8366030750008</v>
       </c>
       <c r="E126" t="n">
-        <v>571.1494750976562</v>
+        <v>578.2373046875</v>
       </c>
       <c r="F126" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B127" t="n">
-        <v>579.1357866530213</v>
+        <v>565.0699110449033</v>
       </c>
       <c r="C127" t="n">
-        <v>591.5344843799961</v>
+        <v>577.5085793033603</v>
       </c>
       <c r="D127" t="n">
-        <v>572.8366030750008</v>
+        <v>558.7408105198895</v>
       </c>
       <c r="E127" t="n">
-        <v>578.2373046875</v>
+        <v>573.4755249023438</v>
       </c>
       <c r="F127" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B128" t="n">
-        <v>565.0699110449033</v>
+        <v>576.6999432469056</v>
       </c>
       <c r="C128" t="n">
-        <v>577.5085793033603</v>
+        <v>581.7911783704857</v>
       </c>
       <c r="D128" t="n">
-        <v>558.7408105198895</v>
+        <v>571.0196924702504</v>
       </c>
       <c r="E128" t="n">
-        <v>573.4755249023438</v>
+        <v>572.0379638671875</v>
       </c>
       <c r="F128" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B129" t="n">
-        <v>576.6999432469056</v>
+        <v>571.4988503418972</v>
       </c>
       <c r="C129" t="n">
-        <v>581.7911783704857</v>
+        <v>574.2441373249518</v>
       </c>
       <c r="D129" t="n">
-        <v>571.0196924702504</v>
+        <v>563.7921103124964</v>
       </c>
       <c r="E129" t="n">
-        <v>572.0379638671875</v>
+        <v>574.064453125</v>
       </c>
       <c r="F129" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B130" t="n">
-        <v>571.4988503418972</v>
+        <v>604.9614419693103</v>
       </c>
       <c r="C130" t="n">
-        <v>574.2441373249518</v>
+        <v>628.8704088339113</v>
       </c>
       <c r="D130" t="n">
-        <v>563.7921103124964</v>
+        <v>590.8157434643455</v>
       </c>
       <c r="E130" t="n">
-        <v>574.064453125</v>
+        <v>611.3704223632812</v>
       </c>
       <c r="F130" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B131" t="n">
-        <v>604.9614419693103</v>
+        <v>625.8955000086161</v>
       </c>
       <c r="C131" t="n">
-        <v>628.8704088339113</v>
+        <v>636.4074834525468</v>
       </c>
       <c r="D131" t="n">
-        <v>590.8157434643455</v>
+        <v>621.9323328485281</v>
       </c>
       <c r="E131" t="n">
-        <v>611.3704223632812</v>
+        <v>627.3131103515625</v>
       </c>
       <c r="F131" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B132" t="n">
-        <v>625.8955000086161</v>
+        <v>633.3826022362973</v>
       </c>
       <c r="C132" t="n">
-        <v>636.4074834525468</v>
+        <v>637.4856047359222</v>
       </c>
       <c r="D132" t="n">
-        <v>621.9323328485281</v>
+        <v>623.2600266965629</v>
       </c>
       <c r="E132" t="n">
-        <v>627.3131103515625</v>
+        <v>628.780517578125</v>
       </c>
       <c r="F132" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B133" t="n">
-        <v>633.3826022362973</v>
+        <v>628.4212176827168</v>
       </c>
       <c r="C133" t="n">
-        <v>637.4856047359222</v>
+        <v>633.9117922613585</v>
       </c>
       <c r="D133" t="n">
-        <v>623.2600266965629</v>
+        <v>623.3299819911093</v>
       </c>
       <c r="E133" t="n">
-        <v>628.780517578125</v>
+        <v>633.442626953125</v>
       </c>
       <c r="F133" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B134" t="n">
-        <v>628.4212176827168</v>
+        <v>642.117619704398</v>
       </c>
       <c r="C134" t="n">
-        <v>633.9117922613585</v>
+        <v>665.1181727259973</v>
       </c>
       <c r="D134" t="n">
-        <v>623.3299819911093</v>
+        <v>638.2742422102883</v>
       </c>
       <c r="E134" t="n">
-        <v>633.442626953125</v>
+        <v>661.3546142578125</v>
       </c>
       <c r="F134" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B135" t="n">
-        <v>642.117619704398</v>
+        <v>665.856909197143</v>
       </c>
       <c r="C135" t="n">
-        <v>665.1181727259973</v>
+        <v>677.3372007350248</v>
       </c>
       <c r="D135" t="n">
-        <v>638.2742422102883</v>
+        <v>663.081644256971</v>
       </c>
       <c r="E135" t="n">
-        <v>661.3546142578125</v>
+        <v>670.4290771484375</v>
       </c>
       <c r="F135" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B136" t="n">
-        <v>665.856909197143</v>
+        <v>674.831464225754</v>
       </c>
       <c r="C136" t="n">
-        <v>677.3372007350248</v>
+        <v>676.4187660594131</v>
       </c>
       <c r="D136" t="n">
-        <v>663.081644256971</v>
+        <v>666.605595861725</v>
       </c>
       <c r="E136" t="n">
-        <v>670.4290771484375</v>
+        <v>675.7099609375</v>
       </c>
       <c r="F136" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B137" t="n">
-        <v>674.831464225754</v>
+        <v>677.4369744478516</v>
       </c>
       <c r="C137" t="n">
-        <v>676.4187660594131</v>
+        <v>690.3348757077041</v>
       </c>
       <c r="D137" t="n">
-        <v>666.605595861725</v>
+        <v>673.9729506648888</v>
       </c>
       <c r="E137" t="n">
-        <v>675.7099609375</v>
+        <v>687.3699340820312</v>
       </c>
       <c r="F137" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B138" t="n">
-        <v>677.4369744478516</v>
+        <v>680.192296240317</v>
       </c>
       <c r="C138" t="n">
-        <v>690.3348757077041</v>
+        <v>682.2088539380842</v>
       </c>
       <c r="D138" t="n">
-        <v>673.9729506648888</v>
+        <v>666.8552067290691</v>
       </c>
       <c r="E138" t="n">
-        <v>687.3699340820312</v>
+        <v>669.7601928710938</v>
       </c>
       <c r="F138" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B139" t="n">
-        <v>680.192296240317</v>
+        <v>669.8500580611455</v>
       </c>
       <c r="C139" t="n">
-        <v>682.2088539380842</v>
+        <v>675.0411586256739</v>
       </c>
       <c r="D139" t="n">
-        <v>666.8552067290691</v>
+        <v>666.1863646700106</v>
       </c>
       <c r="E139" t="n">
-        <v>669.7601928710938</v>
+        <v>667.6937866210938</v>
       </c>
       <c r="F139" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B140" t="n">
-        <v>669.8500580611455</v>
+        <v>673.2042912464699</v>
       </c>
       <c r="C140" t="n">
-        <v>675.0411586256739</v>
+        <v>677.2174214115423</v>
       </c>
       <c r="D140" t="n">
-        <v>666.1863646700106</v>
+        <v>668.6022063234784</v>
       </c>
       <c r="E140" t="n">
-        <v>667.6937866210938</v>
+        <v>673.5636596679688</v>
       </c>
       <c r="F140" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B141" t="n">
-        <v>673.2042912464699</v>
+        <v>662.562575853328</v>
       </c>
       <c r="C141" t="n">
-        <v>677.2174214115423</v>
+        <v>668.4125184743669</v>
       </c>
       <c r="D141" t="n">
-        <v>668.6022063234784</v>
+        <v>651.9308032468797</v>
       </c>
       <c r="E141" t="n">
-        <v>673.5636596679688</v>
+        <v>658.0203857421875</v>
       </c>
       <c r="F141" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B142" t="n">
-        <v>662.562575853328</v>
+        <v>659.1883568751083</v>
       </c>
       <c r="C142" t="n">
-        <v>668.4125184743669</v>
+        <v>679.5034568571632</v>
       </c>
       <c r="D142" t="n">
-        <v>651.9308032468797</v>
+        <v>652.719481738207</v>
       </c>
       <c r="E142" t="n">
-        <v>658.0203857421875</v>
+        <v>673.8731689453125</v>
       </c>
       <c r="F142" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B143" t="n">
-        <v>659.1883568751083</v>
+        <v>669.8500343121515</v>
       </c>
       <c r="C143" t="n">
-        <v>679.5034568571632</v>
+        <v>681.330325511242</v>
       </c>
       <c r="D143" t="n">
-        <v>652.719481738207</v>
+        <v>669.6903353309991</v>
       </c>
       <c r="E143" t="n">
-        <v>673.8731689453125</v>
+        <v>677.4569702148438</v>
       </c>
       <c r="F143" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B144" t="n">
-        <v>669.8500343121515</v>
+        <v>673.0844464119266</v>
       </c>
       <c r="C144" t="n">
-        <v>681.330325511242</v>
+        <v>677.0176962940845</v>
       </c>
       <c r="D144" t="n">
-        <v>669.6903353309991</v>
+        <v>664.489217253305</v>
       </c>
       <c r="E144" t="n">
-        <v>677.4569702148438</v>
+        <v>670.189453125</v>
       </c>
       <c r="F144" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B145" t="n">
-        <v>673.0844464119266</v>
+        <v>667.7636045616339</v>
       </c>
       <c r="C145" t="n">
-        <v>677.0176962940845</v>
+        <v>673.0944797535534</v>
       </c>
       <c r="D145" t="n">
-        <v>664.489217253305</v>
+        <v>662.6723692427279</v>
       </c>
       <c r="E145" t="n">
-        <v>670.189453125</v>
+        <v>667.9732666015625</v>
       </c>
       <c r="F145" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B146" t="n">
-        <v>667.7636045616339</v>
+        <v>618.2586017744245</v>
       </c>
       <c r="C146" t="n">
-        <v>673.0944797535534</v>
+        <v>619.7859479396749</v>
       </c>
       <c r="D146" t="n">
-        <v>662.6723692427279</v>
+        <v>598.9717055442339</v>
       </c>
       <c r="E146" t="n">
-        <v>667.9732666015625</v>
+        <v>610.8612670898438</v>
       </c>
       <c r="F146" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B147" t="n">
-        <v>618.2586017744245</v>
+        <v>613.6365485572411</v>
       </c>
       <c r="C147" t="n">
-        <v>619.7859479396749</v>
+        <v>617.8193701850194</v>
       </c>
       <c r="D147" t="n">
-        <v>598.9717055442339</v>
+        <v>605.0712358749745</v>
       </c>
       <c r="E147" t="n">
-        <v>610.8612670898438</v>
+        <v>607.7067260742188</v>
       </c>
       <c r="F147" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B148" t="n">
-        <v>613.6365485572411</v>
+        <v>606.8981537761392</v>
       </c>
       <c r="C148" t="n">
-        <v>617.8193701850194</v>
+        <v>612.9477660987843</v>
       </c>
       <c r="D148" t="n">
-        <v>605.0712358749745</v>
+        <v>601.7170456287333</v>
       </c>
       <c r="E148" t="n">
-        <v>607.7067260742188</v>
+        <v>609.3638916015625</v>
       </c>
       <c r="F148" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="n">
-        <v>606.8981537761392</v>
+        <v>612.2588828439087</v>
       </c>
       <c r="C149" t="n">
-        <v>612.9477660987843</v>
+        <v>613.2970785161436</v>
       </c>
       <c r="D149" t="n">
-        <v>601.7170456287333</v>
+        <v>599.3310648754198</v>
       </c>
       <c r="E149" t="n">
-        <v>609.3638916015625</v>
+        <v>603.9232177734375</v>
       </c>
       <c r="F149" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="n">
-        <v>612.2588828439087</v>
+        <v>600.0199080772063</v>
       </c>
       <c r="C150" t="n">
-        <v>613.2970785161436</v>
+        <v>618.8875416216711</v>
       </c>
       <c r="D150" t="n">
-        <v>599.3310648754198</v>
+        <v>597.0749516023062</v>
       </c>
       <c r="E150" t="n">
-        <v>603.9232177734375</v>
+        <v>611.8296508789062</v>
       </c>
       <c r="F150" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="n">
-        <v>600.0199080772063</v>
+        <v>613.6664238202088</v>
       </c>
       <c r="C151" t="n">
-        <v>618.8875416216711</v>
+        <v>623.9088493168618</v>
       </c>
       <c r="D151" t="n">
-        <v>597.0749516023062</v>
+        <v>612.4884534922683</v>
       </c>
       <c r="E151" t="n">
-        <v>611.8296508789062</v>
+        <v>615.7528686523438</v>
       </c>
       <c r="F151" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B152" t="n">
-        <v>613.6664238202088</v>
+        <v>614.1456663784968</v>
       </c>
       <c r="C152" t="n">
-        <v>623.9088493168618</v>
+        <v>615.7129829832094</v>
       </c>
       <c r="D152" t="n">
-        <v>612.4884534922683</v>
+        <v>605.0213161255829</v>
       </c>
       <c r="E152" t="n">
-        <v>615.7528686523438</v>
+        <v>608.585205078125</v>
       </c>
       <c r="F152" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B153" t="n">
-        <v>614.1456663784968</v>
+        <v>603.533915527778</v>
       </c>
       <c r="C153" t="n">
-        <v>615.7129829832094</v>
+        <v>603.8732987260729</v>
       </c>
       <c r="D153" t="n">
-        <v>605.0213161255829</v>
+        <v>597.0550476209405</v>
       </c>
       <c r="E153" t="n">
-        <v>608.585205078125</v>
+        <v>597.8336791992188</v>
       </c>
       <c r="F153" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B154" t="n">
-        <v>603.533915527778</v>
+        <v>593.8006394881057</v>
       </c>
       <c r="C154" t="n">
-        <v>603.8732987260729</v>
+        <v>602.7153284632744</v>
       </c>
       <c r="D154" t="n">
-        <v>597.0550476209405</v>
+        <v>591.5844123107358</v>
       </c>
       <c r="E154" t="n">
-        <v>597.8336791992188</v>
+        <v>601.9666137695312</v>
       </c>
       <c r="F154" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B155" t="n">
-        <v>593.8006394881057</v>
+        <v>597.8037594995824</v>
       </c>
       <c r="C155" t="n">
-        <v>602.7153284632744</v>
+        <v>618.837657653709</v>
       </c>
       <c r="D155" t="n">
-        <v>591.5844123107358</v>
+        <v>595.6374345129168</v>
       </c>
       <c r="E155" t="n">
-        <v>601.9666137695312</v>
+        <v>615.5732421875</v>
       </c>
       <c r="F155" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B156" t="n">
-        <v>597.8037594995824</v>
+        <v>614.944289073115</v>
       </c>
       <c r="C156" t="n">
-        <v>618.837657653709</v>
+        <v>622.6610217742586</v>
       </c>
       <c r="D156" t="n">
-        <v>595.6374345129168</v>
+        <v>613.9460028895547</v>
       </c>
       <c r="E156" t="n">
-        <v>615.5732421875</v>
+        <v>617.3701171875</v>
       </c>
       <c r="F156" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B157" t="n">
-        <v>614.944289073115</v>
+        <v>612.9377892034477</v>
       </c>
       <c r="C157" t="n">
-        <v>622.6610217742586</v>
+        <v>620.135455286475</v>
       </c>
       <c r="D157" t="n">
-        <v>613.9460028895547</v>
+        <v>608.2658166797805</v>
       </c>
       <c r="E157" t="n">
-        <v>617.3701171875</v>
+        <v>613.1773681640625</v>
       </c>
       <c r="F157" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B158" t="n">
-        <v>612.9377892034477</v>
+        <v>608.0660990208263</v>
       </c>
       <c r="C158" t="n">
-        <v>620.135455286475</v>
+        <v>614.5350350972873</v>
       </c>
       <c r="D158" t="n">
-        <v>608.2658166797805</v>
+        <v>602.6554048207697</v>
       </c>
       <c r="E158" t="n">
-        <v>613.1773681640625</v>
+        <v>610.1625366210938</v>
       </c>
       <c r="F158" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B159" t="n">
-        <v>608.0660990208263</v>
+        <v>607.8764543920544</v>
       </c>
       <c r="C159" t="n">
-        <v>614.5350350972873</v>
+        <v>612.8778783201094</v>
       </c>
       <c r="D159" t="n">
-        <v>602.6554048207697</v>
+        <v>599.5208032426234</v>
       </c>
       <c r="E159" t="n">
-        <v>610.1625366210938</v>
+        <v>601.5772705078125</v>
       </c>
       <c r="F159" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B160" t="n">
-        <v>607.8764543920544</v>
+        <v>599.7304526335664</v>
       </c>
       <c r="C160" t="n">
-        <v>612.8778783201094</v>
+        <v>606.9580352784536</v>
       </c>
       <c r="D160" t="n">
-        <v>599.5208032426234</v>
+        <v>596.7854960328639</v>
       </c>
       <c r="E160" t="n">
-        <v>601.5772705078125</v>
+        <v>604.0230712890625</v>
       </c>
       <c r="F160" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B161" t="n">
-        <v>599.7304526335664</v>
+        <v>598.9716935873996</v>
       </c>
       <c r="C161" t="n">
-        <v>606.9580352784536</v>
+        <v>608.5552163125774</v>
       </c>
       <c r="D161" t="n">
-        <v>596.7854960328639</v>
+        <v>593.7905860006466</v>
       </c>
       <c r="E161" t="n">
-        <v>604.0230712890625</v>
+        <v>606.3390502929688</v>
       </c>
       <c r="F161" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B162" t="n">
-        <v>598.9716935873996</v>
+        <v>606.838246230648</v>
       </c>
       <c r="C162" t="n">
-        <v>608.5552163125774</v>
+        <v>613.7563625825306</v>
       </c>
       <c r="D162" t="n">
-        <v>593.7905860006466</v>
+        <v>605.9098473363839</v>
       </c>
       <c r="E162" t="n">
-        <v>606.3390502929688</v>
+        <v>609.2141723632812</v>
       </c>
       <c r="F162" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B163" t="n">
-        <v>606.838246230648</v>
+        <v>607.8464888599174</v>
       </c>
       <c r="C163" t="n">
-        <v>613.7563625825306</v>
+        <v>613.4168818935308</v>
       </c>
       <c r="D163" t="n">
-        <v>605.9098473363839</v>
+        <v>604.2626146519137</v>
       </c>
       <c r="E163" t="n">
-        <v>609.2141723632812</v>
+        <v>611.2905883789062</v>
       </c>
       <c r="F163" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B164" t="n">
-        <v>607.8464888599174</v>
+        <v>608.3556581766634</v>
       </c>
       <c r="C164" t="n">
-        <v>613.4168818935308</v>
+        <v>637.4057633477772</v>
       </c>
       <c r="D164" t="n">
-        <v>604.2626146519137</v>
+        <v>607.9563193089997</v>
       </c>
       <c r="E164" t="n">
-        <v>611.2905883789062</v>
+        <v>634.1713256835938</v>
       </c>
       <c r="F164" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B165" t="n">
-        <v>608.3556581766634</v>
+        <v>638.4040398455469</v>
       </c>
       <c r="C165" t="n">
-        <v>637.4057633477772</v>
+        <v>641.8980416273442</v>
       </c>
       <c r="D165" t="n">
-        <v>607.9563193089997</v>
+        <v>628.2315007921775</v>
       </c>
       <c r="E165" t="n">
-        <v>634.1713256835938</v>
+        <v>634.2012329101562</v>
       </c>
       <c r="F165" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B166" t="n">
-        <v>638.4040398455469</v>
+        <v>632.4143189973911</v>
       </c>
       <c r="C166" t="n">
-        <v>641.8980416273442</v>
+        <v>633.4126052152244</v>
       </c>
       <c r="D166" t="n">
-        <v>628.2315007921775</v>
+        <v>622.281689514161</v>
       </c>
       <c r="E166" t="n">
-        <v>634.2012329101562</v>
+        <v>631.426025390625</v>
       </c>
       <c r="F166" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B167" t="n">
-        <v>632.4143189973911</v>
+        <v>629.3196151062037</v>
       </c>
       <c r="C167" t="n">
-        <v>633.4126052152244</v>
+        <v>634.6604216515384</v>
       </c>
       <c r="D167" t="n">
-        <v>622.281689514161</v>
+        <v>598.5025264432778</v>
       </c>
       <c r="E167" t="n">
-        <v>631.426025390625</v>
+        <v>599.4408569335938</v>
       </c>
       <c r="F167" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B168" t="n">
-        <v>629.3196151062037</v>
+        <v>602.2061447656582</v>
       </c>
       <c r="C168" t="n">
-        <v>634.6604216515384</v>
+        <v>607.8364934375654</v>
       </c>
       <c r="D168" t="n">
-        <v>598.5025264432778</v>
+        <v>595.6573898697867</v>
       </c>
       <c r="E168" t="n">
-        <v>599.4408569335938</v>
+        <v>596.6057739257812</v>
       </c>
       <c r="F168" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B169" t="n">
-        <v>602.2061447656582</v>
+        <v>601.9666135784172</v>
       </c>
       <c r="C169" t="n">
-        <v>607.8364934375654</v>
+        <v>623.0803923074952</v>
       </c>
       <c r="D169" t="n">
-        <v>595.6573898697867</v>
+        <v>599.2413115918356</v>
       </c>
       <c r="E169" t="n">
-        <v>596.6057739257812</v>
+        <v>621.912353515625</v>
       </c>
       <c r="F169" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B170" t="n">
-        <v>601.9666135784172</v>
+        <v>622.601105447702</v>
       </c>
       <c r="C170" t="n">
-        <v>623.0803923074952</v>
+        <v>641.2990464500883</v>
       </c>
       <c r="D170" t="n">
-        <v>599.2413115918356</v>
+        <v>621.3632403719068</v>
       </c>
       <c r="E170" t="n">
-        <v>621.912353515625</v>
+        <v>626.4944458007812</v>
       </c>
       <c r="F170" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B171" t="n">
-        <v>622.601105447702</v>
+        <v>622.3915867034917</v>
       </c>
       <c r="C171" t="n">
-        <v>641.2990464500883</v>
+        <v>628.0718380797523</v>
       </c>
       <c r="D171" t="n">
-        <v>621.3632403719068</v>
+        <v>581.9110292634388</v>
       </c>
       <c r="E171" t="n">
-        <v>626.4944458007812</v>
+        <v>591.9837646484375</v>
       </c>
       <c r="F171" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B172" t="n">
-        <v>622.3915867034917</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="C172" t="n">
-        <v>628.0718380797523</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="D172" t="n">
-        <v>581.9110292634388</v>
+        <v>578.2273099921849</v>
       </c>
       <c r="E172" t="n">
-        <v>591.9837646484375</v>
+        <v>584.3867797851562</v>
       </c>
       <c r="F172" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B173" t="n">
-        <v>590.9854370177134</v>
+        <v>589.9871222602228</v>
       </c>
       <c r="C173" t="n">
-        <v>590.9854370177134</v>
+        <v>596.6057643945405</v>
       </c>
       <c r="D173" t="n">
-        <v>578.2273099921849</v>
+        <v>580.0142532419713</v>
       </c>
       <c r="E173" t="n">
-        <v>584.3867797851562</v>
+        <v>583.588134765625</v>
       </c>
       <c r="F173" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B174" t="n">
-        <v>589.9871222602228</v>
+        <v>579.7347558037309</v>
       </c>
       <c r="C174" t="n">
-        <v>596.6057643945405</v>
+        <v>590.3066340250939</v>
       </c>
       <c r="D174" t="n">
-        <v>580.0142532419713</v>
+        <v>569.6221111934292</v>
       </c>
       <c r="E174" t="n">
-        <v>583.588134765625</v>
+        <v>570.00146484375</v>
       </c>
       <c r="F174" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B175" t="n">
-        <v>579.7347558037309</v>
+        <v>564.8602908302337</v>
       </c>
       <c r="C175" t="n">
-        <v>590.3066340250939</v>
+        <v>571.1893911411966</v>
       </c>
       <c r="D175" t="n">
-        <v>569.6221111934292</v>
+        <v>556.0553993401948</v>
       </c>
       <c r="E175" t="n">
-        <v>570.00146484375</v>
+        <v>567.455810546875</v>
       </c>
       <c r="F175" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B176" t="n">
-        <v>564.8602908302337</v>
+        <v>571.9680395129554</v>
       </c>
       <c r="C176" t="n">
-        <v>571.1893911411966</v>
+        <v>575.0826873049916</v>
       </c>
       <c r="D176" t="n">
-        <v>556.0553993401948</v>
+        <v>559.938704060897</v>
       </c>
       <c r="E176" t="n">
-        <v>567.455810546875</v>
+        <v>566.0082397460938</v>
       </c>
       <c r="F176" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B177" t="n">
-        <v>571.9680395129554</v>
+        <v>579.4427159724761</v>
       </c>
       <c r="C177" t="n">
-        <v>575.0826873049916</v>
+        <v>600.795858737961</v>
       </c>
       <c r="D177" t="n">
-        <v>559.938704060897</v>
+        <v>578.8431525395191</v>
       </c>
       <c r="E177" t="n">
-        <v>566.0082397460938</v>
+        <v>593.011962890625</v>
       </c>
       <c r="F177" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B178" t="n">
-        <v>579.4427159724761</v>
+        <v>593.1818700134238</v>
       </c>
       <c r="C178" t="n">
-        <v>600.795858737961</v>
+        <v>605.3322537623429</v>
       </c>
       <c r="D178" t="n">
-        <v>578.8431525395191</v>
+        <v>591.5331468141493</v>
       </c>
       <c r="E178" t="n">
-        <v>593.011962890625</v>
+        <v>599.7366943359375</v>
       </c>
       <c r="F178" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G178" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B179" t="n">
-        <v>593.1818700134238</v>
+        <v>591.5331725816898</v>
       </c>
       <c r="C179" t="n">
-        <v>605.3322537623429</v>
+        <v>593.3417428489197</v>
       </c>
       <c r="D179" t="n">
-        <v>591.5331468141493</v>
+        <v>565.7435277503374</v>
       </c>
       <c r="E179" t="n">
-        <v>599.7366943359375</v>
+        <v>567.1324462890625</v>
       </c>
       <c r="F179" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B180" t="n">
-        <v>591.5331725816898</v>
+        <v>572.3682769745303</v>
       </c>
       <c r="C180" t="n">
-        <v>593.3417428489197</v>
+        <v>579.7624046842873</v>
       </c>
       <c r="D180" t="n">
-        <v>565.7435277503374</v>
+        <v>562.6559105294999</v>
       </c>
       <c r="E180" t="n">
-        <v>567.1324462890625</v>
+        <v>576.7647705078125</v>
       </c>
       <c r="F180" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B181" t="n">
-        <v>572.3682769745303</v>
+        <v>571.5689356803741</v>
       </c>
       <c r="C181" t="n">
-        <v>579.7624046842873</v>
+        <v>575.3559250048318</v>
       </c>
       <c r="D181" t="n">
-        <v>562.6559105294999</v>
+        <v>559.3685422933314</v>
       </c>
       <c r="E181" t="n">
-        <v>576.7647705078125</v>
+        <v>563.4053344726562</v>
       </c>
       <c r="F181" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B182" t="n">
-        <v>571.5689356803741</v>
+        <v>561.8066012038755</v>
       </c>
       <c r="C182" t="n">
-        <v>575.3559250048318</v>
+        <v>571.7487666818112</v>
       </c>
       <c r="D182" t="n">
-        <v>559.3685422933314</v>
+        <v>560.5775907162</v>
       </c>
       <c r="E182" t="n">
-        <v>563.4053344726562</v>
+        <v>561.7566528320312</v>
       </c>
       <c r="F182" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B183" t="n">
-        <v>561.8066012038755</v>
+        <v>561.4469285838474</v>
       </c>
       <c r="C183" t="n">
-        <v>571.7487666818112</v>
+        <v>568.591253761232</v>
       </c>
       <c r="D183" t="n">
-        <v>560.5775907162</v>
+        <v>555.1119012433646</v>
       </c>
       <c r="E183" t="n">
-        <v>561.7566528320312</v>
+        <v>557.230224609375</v>
       </c>
       <c r="F183" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B184" t="n">
-        <v>561.4469285838474</v>
+        <v>555.1118879211193</v>
       </c>
       <c r="C184" t="n">
-        <v>568.591253761232</v>
+        <v>555.9013039685537</v>
       </c>
       <c r="D184" t="n">
-        <v>555.1119012433646</v>
+        <v>539.7540133926082</v>
       </c>
       <c r="E184" t="n">
-        <v>557.230224609375</v>
+        <v>542.44189453125</v>
       </c>
       <c r="F184" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B185" t="n">
-        <v>555.1118879211193</v>
+        <v>542.9115767800729</v>
       </c>
       <c r="C185" t="n">
-        <v>555.9013039685537</v>
+        <v>556.4108722579447</v>
       </c>
       <c r="D185" t="n">
-        <v>539.7540133926082</v>
+        <v>539.9738926737891</v>
       </c>
       <c r="E185" t="n">
-        <v>542.44189453125</v>
+        <v>549.8161010742188</v>
       </c>
       <c r="F185" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B186" t="n">
-        <v>542.9115767800729</v>
+        <v>559.5583857816937</v>
       </c>
       <c r="C186" t="n">
-        <v>556.4108722579447</v>
+        <v>570.4498144711828</v>
       </c>
       <c r="D186" t="n">
-        <v>539.9738926737891</v>
+        <v>557.5599629753306</v>
       </c>
       <c r="E186" t="n">
-        <v>549.8161010742188</v>
+        <v>562.1563110351562</v>
       </c>
       <c r="F186" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B187" t="n">
-        <v>559.5583857816937</v>
+        <v>560.4976417791106</v>
       </c>
       <c r="C187" t="n">
-        <v>570.4498144711828</v>
+        <v>565.0939897966132</v>
       </c>
       <c r="D187" t="n">
-        <v>557.5599629753306</v>
+        <v>550.9951316644288</v>
       </c>
       <c r="E187" t="n">
-        <v>562.1563110351562</v>
+        <v>562.8457641601562</v>
       </c>
       <c r="F187" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>560.4976417791106</v>
+        <v>607.4305787144307</v>
       </c>
       <c r="C188" t="n">
-        <v>565.0939897966132</v>
+        <v>627.784571153574</v>
       </c>
       <c r="D188" t="n">
-        <v>550.9951316644288</v>
+        <v>594.6306830487989</v>
       </c>
       <c r="E188" t="n">
-        <v>562.8457641601562</v>
+        <v>612.4266357421875</v>
       </c>
       <c r="F188" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B189" t="n">
-        <v>607.4305787144307</v>
+        <v>607.4206544757068</v>
       </c>
       <c r="C189" t="n">
-        <v>627.784571153574</v>
+        <v>609.5189740900589</v>
       </c>
       <c r="D189" t="n">
-        <v>594.6306830487989</v>
+        <v>579.9622828274885</v>
       </c>
       <c r="E189" t="n">
-        <v>612.4266357421875</v>
+        <v>582.4403686523438</v>
       </c>
       <c r="F189" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B190" t="n">
-        <v>607.4206544757068</v>
+        <v>594.3709360150443</v>
       </c>
       <c r="C190" t="n">
-        <v>609.5189740900589</v>
+        <v>603.1040338931904</v>
       </c>
       <c r="D190" t="n">
-        <v>579.9622828274885</v>
+        <v>581.301233826573</v>
       </c>
       <c r="E190" t="n">
-        <v>582.4403686523438</v>
+        <v>599.8165893554688</v>
       </c>
       <c r="F190" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B191" t="n">
-        <v>594.3709360150443</v>
+        <v>607.1109147253509</v>
       </c>
       <c r="C191" t="n">
-        <v>603.1040338931904</v>
+        <v>624.8768626804635</v>
       </c>
       <c r="D191" t="n">
-        <v>581.301233826573</v>
+        <v>603.1839600389557</v>
       </c>
       <c r="E191" t="n">
-        <v>599.8165893554688</v>
+        <v>615.0946044921875</v>
       </c>
       <c r="F191" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B192" t="n">
-        <v>607.1109147253509</v>
+        <v>613.9055418180343</v>
       </c>
       <c r="C192" t="n">
-        <v>624.8768626804635</v>
+        <v>615.5142576272189</v>
       </c>
       <c r="D192" t="n">
-        <v>603.1839600389557</v>
+        <v>597.5384532703483</v>
       </c>
       <c r="E192" t="n">
-        <v>615.0946044921875</v>
+        <v>602.6444091796875</v>
       </c>
       <c r="F192" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B193" t="n">
-        <v>613.9055418180343</v>
+        <v>583.529455055522</v>
       </c>
       <c r="C193" t="n">
-        <v>615.5142576272189</v>
+        <v>632.77062206454</v>
       </c>
       <c r="D193" t="n">
-        <v>597.5384532703483</v>
+        <v>576.6149292518581</v>
       </c>
       <c r="E193" t="n">
-        <v>602.6444091796875</v>
+        <v>630.9819946289062</v>
       </c>
       <c r="F193" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B194" t="n">
-        <v>583.529455055522</v>
+        <v>659.8193113874754</v>
       </c>
       <c r="C194" t="n">
-        <v>632.77062206454</v>
+        <v>677.3254544051542</v>
       </c>
       <c r="D194" t="n">
-        <v>576.6149292518581</v>
+        <v>657.491131647921</v>
       </c>
       <c r="E194" t="n">
-        <v>630.9819946289062</v>
+        <v>668.6823120117188</v>
       </c>
       <c r="F194" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B195" t="n">
-        <v>659.8193113874754</v>
+        <v>660.858454671636</v>
       </c>
       <c r="C195" t="n">
-        <v>677.3254544051542</v>
+        <v>676.0864269737083</v>
       </c>
       <c r="D195" t="n">
-        <v>657.491131647921</v>
+        <v>653.6841239854351</v>
       </c>
       <c r="E195" t="n">
-        <v>668.6823120117188</v>
+        <v>656.2120971679688</v>
       </c>
       <c r="F195" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>660.858454671636</v>
+        <v>651.4858277274717</v>
       </c>
       <c r="C196" t="n">
-        <v>676.0864269737083</v>
+        <v>665.9743929146624</v>
       </c>
       <c r="D196" t="n">
-        <v>653.6841239854351</v>
+        <v>648.5381419230179</v>
       </c>
       <c r="E196" t="n">
-        <v>656.2120971679688</v>
+        <v>660.5186767578125</v>
       </c>
       <c r="F196" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>651.4858277274717</v>
+        <v>663.0767089741589</v>
       </c>
       <c r="C197" t="n">
-        <v>665.9743929146624</v>
+        <v>685.5390243545221</v>
       </c>
       <c r="D197" t="n">
-        <v>648.5381419230179</v>
+        <v>656.1421789132482</v>
       </c>
       <c r="E197" t="n">
-        <v>660.5186767578125</v>
+        <v>680.7727661132812</v>
       </c>
       <c r="F197" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>663.0767089741589</v>
+        <v>676.7459348014426</v>
       </c>
       <c r="C198" t="n">
-        <v>685.5390243545221</v>
+        <v>681.3622866487058</v>
       </c>
       <c r="D198" t="n">
-        <v>656.1421789132482</v>
+        <v>659.6393793096187</v>
       </c>
       <c r="E198" t="n">
-        <v>680.7727661132812</v>
+        <v>664.0159301757812</v>
       </c>
       <c r="F198" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B199" t="n">
-        <v>676.7459348014426</v>
+        <v>647.1892801723585</v>
       </c>
       <c r="C199" t="n">
-        <v>681.3622866487058</v>
+        <v>651.68573177941</v>
       </c>
       <c r="D199" t="n">
-        <v>659.6393793096187</v>
+        <v>625.5063791142821</v>
       </c>
       <c r="E199" t="n">
-        <v>664.0159301757812</v>
+        <v>645.5006103515625</v>
       </c>
       <c r="F199" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B200" t="n">
-        <v>647.1892801723585</v>
+        <v>646.1900645769782</v>
       </c>
       <c r="C200" t="n">
-        <v>651.68573177941</v>
+        <v>652.7848358303891</v>
       </c>
       <c r="D200" t="n">
-        <v>625.5063791142821</v>
+        <v>635.5084916103011</v>
       </c>
       <c r="E200" t="n">
-        <v>645.5006103515625</v>
+        <v>645.3406982421875</v>
       </c>
       <c r="F200" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B201" t="n">
-        <v>646.1900645769782</v>
+        <v>653.664124760039</v>
       </c>
       <c r="C201" t="n">
-        <v>652.7848358303891</v>
+        <v>655.3627963853286</v>
       </c>
       <c r="D201" t="n">
-        <v>635.5084916103011</v>
+        <v>642.6928027946103</v>
       </c>
       <c r="E201" t="n">
-        <v>645.3406982421875</v>
+        <v>643.3023071289062</v>
       </c>
       <c r="F201" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B202" t="n">
-        <v>653.664124760039</v>
+        <v>647.189254956408</v>
       </c>
       <c r="C202" t="n">
-        <v>655.3627963853286</v>
+        <v>648.4882176170956</v>
       </c>
       <c r="D202" t="n">
-        <v>642.6928027946103</v>
+        <v>623.5079318845419</v>
       </c>
       <c r="E202" t="n">
-        <v>643.3023071289062</v>
+        <v>626.6754150390625</v>
       </c>
       <c r="F202" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B203" t="n">
-        <v>647.189254956408</v>
+        <v>607.9301851876114</v>
       </c>
       <c r="C203" t="n">
-        <v>648.4882176170956</v>
+        <v>614.1653155952538</v>
       </c>
       <c r="D203" t="n">
-        <v>623.5079318845419</v>
+        <v>596.7490071058414</v>
       </c>
       <c r="E203" t="n">
-        <v>626.6754150390625</v>
+        <v>605.6220092773438</v>
       </c>
       <c r="F203" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B204" t="n">
-        <v>607.9301851876114</v>
+        <v>604.8226548171024</v>
       </c>
       <c r="C204" t="n">
-        <v>614.1653155952538</v>
+        <v>609.4989569016461</v>
       </c>
       <c r="D204" t="n">
-        <v>596.7490071058414</v>
+        <v>593.9812354037057</v>
       </c>
       <c r="E204" t="n">
-        <v>605.6220092773438</v>
+        <v>594.7206420898438</v>
       </c>
       <c r="F204" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B205" t="n">
-        <v>604.8226548171024</v>
+        <v>606.7411202287035</v>
       </c>
       <c r="C205" t="n">
-        <v>609.4989569016461</v>
+        <v>610.7779733376527</v>
       </c>
       <c r="D205" t="n">
-        <v>593.9812354037057</v>
+        <v>592.6622656813121</v>
       </c>
       <c r="E205" t="n">
-        <v>594.7206420898438</v>
+        <v>593.4016723632812</v>
       </c>
       <c r="F205" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B206" t="n">
-        <v>606.7411202287035</v>
+        <v>596.3493616660036</v>
       </c>
       <c r="C206" t="n">
-        <v>610.7779733376527</v>
+        <v>600.5260580457825</v>
       </c>
       <c r="D206" t="n">
-        <v>592.6622656813121</v>
+        <v>586.5370982909723</v>
       </c>
       <c r="E206" t="n">
-        <v>593.4016723632812</v>
+        <v>592.9420166015625</v>
       </c>
       <c r="F206" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B207" t="n">
-        <v>596.3493616660036</v>
+        <v>592.7821833537371</v>
       </c>
       <c r="C207" t="n">
-        <v>600.5260580457825</v>
+        <v>599.4968549179539</v>
       </c>
       <c r="D207" t="n">
-        <v>586.5370982909723</v>
+        <v>581.7608519604674</v>
       </c>
       <c r="E207" t="n">
-        <v>592.9420166015625</v>
+        <v>585.148193359375</v>
       </c>
       <c r="F207" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B208" t="n">
-        <v>592.7821833537371</v>
+        <v>525.58522592167</v>
       </c>
       <c r="C208" t="n">
-        <v>599.4968549179539</v>
+        <v>539.4542858116451</v>
       </c>
       <c r="D208" t="n">
-        <v>581.7608519604674</v>
+        <v>524.0764068649972</v>
       </c>
       <c r="E208" t="n">
-        <v>585.148193359375</v>
+        <v>538.60498046875</v>
       </c>
       <c r="F208" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B209" t="n">
-        <v>525.58522592167</v>
+        <v>543.171288392182</v>
       </c>
       <c r="C209" t="n">
-        <v>539.4542858116451</v>
+        <v>557.8897136701136</v>
       </c>
       <c r="D209" t="n">
-        <v>524.0764068649972</v>
+        <v>539.7939490076644</v>
       </c>
       <c r="E209" t="n">
-        <v>538.60498046875</v>
+        <v>556.27099609375</v>
       </c>
       <c r="F209" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B210" t="n">
-        <v>543.171288392182</v>
+        <v>561.7966164985271</v>
       </c>
       <c r="C210" t="n">
-        <v>557.8897136701136</v>
+        <v>597.0488245114987</v>
       </c>
       <c r="D210" t="n">
-        <v>539.7939490076644</v>
+        <v>558.9188827428958</v>
       </c>
       <c r="E210" t="n">
-        <v>556.27099609375</v>
+        <v>589.7745361328125</v>
       </c>
       <c r="F210" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B211" t="n">
-        <v>561.7966164985271</v>
+        <v>581.0414552494501</v>
       </c>
       <c r="C211" t="n">
-        <v>597.0488245114987</v>
+        <v>592.32253050782</v>
       </c>
       <c r="D211" t="n">
-        <v>558.9188827428958</v>
+        <v>577.794018053301</v>
       </c>
       <c r="E211" t="n">
-        <v>589.7745361328125</v>
+        <v>587.4763793945312</v>
       </c>
       <c r="F211" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B212" t="n">
-        <v>581.0414552494501</v>
+        <v>599.9865089938204</v>
       </c>
       <c r="C212" t="n">
-        <v>592.32253050782</v>
+        <v>600.5260612032997</v>
       </c>
       <c r="D212" t="n">
-        <v>577.794018053301</v>
+        <v>579.6625219517506</v>
       </c>
       <c r="E212" t="n">
-        <v>587.4763793945312</v>
+        <v>588.3057250976562</v>
       </c>
       <c r="F212" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B213" t="n">
-        <v>599.9865089938204</v>
+        <v>586.487189429669</v>
       </c>
       <c r="C213" t="n">
-        <v>600.5260612032997</v>
+        <v>594.8405827519979</v>
       </c>
       <c r="D213" t="n">
-        <v>579.6625219517506</v>
+        <v>585.5379263278069</v>
       </c>
       <c r="E213" t="n">
-        <v>588.3057250976562</v>
+        <v>589.4348754882812</v>
       </c>
       <c r="F213" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B214" t="n">
-        <v>586.487189429669</v>
+        <v>585.1781899072663</v>
       </c>
       <c r="C214" t="n">
-        <v>594.8405827519979</v>
+        <v>598.2678350979388</v>
       </c>
       <c r="D214" t="n">
-        <v>585.5379263278069</v>
+        <v>585.1581861630435</v>
       </c>
       <c r="E214" t="n">
-        <v>589.4348754882812</v>
+        <v>591.633056640625</v>
       </c>
       <c r="F214" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B215" t="n">
-        <v>585.1781899072663</v>
+        <v>598.657568915248</v>
       </c>
       <c r="C215" t="n">
-        <v>598.2678350979388</v>
+        <v>607.7304260788247</v>
       </c>
       <c r="D215" t="n">
-        <v>585.1581861630435</v>
+        <v>591.5631919202813</v>
       </c>
       <c r="E215" t="n">
-        <v>591.633056640625</v>
+        <v>594.4508666992188</v>
       </c>
       <c r="F215" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B216" t="n">
-        <v>598.657568915248</v>
+        <v>597.5284100969216</v>
       </c>
       <c r="C216" t="n">
-        <v>607.7304260788247</v>
+        <v>611.9470231090784</v>
       </c>
       <c r="D216" t="n">
-        <v>591.5631919202813</v>
+        <v>592.9320621063698</v>
       </c>
       <c r="E216" t="n">
-        <v>594.4508666992188</v>
+        <v>598.6475219726562</v>
       </c>
       <c r="F216" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B217" t="n">
-        <v>597.5284100969216</v>
+        <v>600.5960026412422</v>
       </c>
       <c r="C217" t="n">
-        <v>611.9470231090784</v>
+        <v>604.023290419805</v>
       </c>
       <c r="D217" t="n">
-        <v>592.9320621063698</v>
+        <v>577.7540447074138</v>
       </c>
       <c r="E217" t="n">
-        <v>598.6475219726562</v>
+        <v>578.3934936523438</v>
       </c>
       <c r="F217" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B218" t="n">
-        <v>600.5960026412422</v>
+        <v>580.2520897369063</v>
       </c>
       <c r="C218" t="n">
-        <v>604.023290419805</v>
+        <v>595.3801043917661</v>
       </c>
       <c r="D218" t="n">
-        <v>577.7540447074138</v>
+        <v>578.9331233348041</v>
       </c>
       <c r="E218" t="n">
-        <v>578.3934936523438</v>
+        <v>594.5007934570312</v>
       </c>
       <c r="F218" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B219" t="n">
-        <v>580.2520897369063</v>
+        <v>596.5092089028919</v>
       </c>
       <c r="C219" t="n">
-        <v>595.3801043917661</v>
+        <v>601.3853654698224</v>
       </c>
       <c r="D219" t="n">
-        <v>578.9331233348041</v>
+        <v>588.8252707092146</v>
       </c>
       <c r="E219" t="n">
-        <v>594.5007934570312</v>
+        <v>589.3848266601562</v>
       </c>
       <c r="F219" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B220" t="n">
-        <v>596.5092089028919</v>
+        <v>589.2849441761664</v>
       </c>
       <c r="C220" t="n">
-        <v>601.3853654698224</v>
+        <v>589.774548021712</v>
       </c>
       <c r="D220" t="n">
-        <v>588.8252707092146</v>
+        <v>564.3046582848494</v>
       </c>
       <c r="E220" t="n">
-        <v>589.3848266601562</v>
+        <v>568.5213012695312</v>
       </c>
       <c r="F220" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B221" t="n">
-        <v>589.2849441761664</v>
+        <v>557.0403796583744</v>
       </c>
       <c r="C221" t="n">
-        <v>589.774548021712</v>
+        <v>560.2178647510921</v>
       </c>
       <c r="D221" t="n">
-        <v>564.3046582848494</v>
+        <v>542.7816737373303</v>
       </c>
       <c r="E221" t="n">
-        <v>568.5213012695312</v>
+        <v>543.2412719726562</v>
       </c>
       <c r="F221" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B222" t="n">
-        <v>557.0403796583744</v>
+        <v>540.9131223962278</v>
       </c>
       <c r="C222" t="n">
-        <v>560.2178647510921</v>
+        <v>553.6330639150415</v>
       </c>
       <c r="D222" t="n">
-        <v>542.7816737373303</v>
+        <v>536.8463247077087</v>
       </c>
       <c r="E222" t="n">
-        <v>543.2412719726562</v>
+        <v>545.5994262695312</v>
       </c>
       <c r="F222" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B223" t="n">
-        <v>540.9131223962278</v>
+        <v>546.5187091013889</v>
       </c>
       <c r="C223" t="n">
-        <v>553.6330639150415</v>
+        <v>549.5562899225255</v>
       </c>
       <c r="D223" t="n">
-        <v>536.8463247077087</v>
+        <v>538.8847190657524</v>
       </c>
       <c r="E223" t="n">
-        <v>545.5994262695312</v>
+        <v>545.3995971679688</v>
       </c>
       <c r="F223" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B224" t="n">
-        <v>546.5187091013889</v>
+        <v>546.4587335768297</v>
       </c>
       <c r="C224" t="n">
-        <v>549.5562899225255</v>
+        <v>553.4332095869578</v>
       </c>
       <c r="D224" t="n">
-        <v>538.8847190657524</v>
+        <v>542.8015857242297</v>
       </c>
       <c r="E224" t="n">
-        <v>545.3995971679688</v>
+        <v>549.4663696289062</v>
       </c>
       <c r="F224" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B225" t="n">
-        <v>546.4587335768297</v>
+        <v>549.7661710202622</v>
       </c>
       <c r="C225" t="n">
-        <v>553.4332095869578</v>
+        <v>560.9772946036173</v>
       </c>
       <c r="D225" t="n">
-        <v>542.8015857242297</v>
+        <v>545.8692218355393</v>
       </c>
       <c r="E225" t="n">
-        <v>549.4663696289062</v>
+        <v>558.5792236328125</v>
       </c>
       <c r="F225" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B226" t="n">
-        <v>549.7661710202622</v>
+        <v>563.4353464162</v>
       </c>
       <c r="C226" t="n">
-        <v>560.9772946036173</v>
+        <v>570.3498724402046</v>
       </c>
       <c r="D226" t="n">
-        <v>545.8692218355393</v>
+        <v>560.9573215839381</v>
       </c>
       <c r="E226" t="n">
-        <v>558.5792236328125</v>
+        <v>569.6004638671875</v>
       </c>
       <c r="F226" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B227" t="n">
-        <v>563.4353464162</v>
+        <v>589.8444773654404</v>
       </c>
       <c r="C227" t="n">
-        <v>570.3498724402046</v>
+        <v>592.8721171723366</v>
       </c>
       <c r="D227" t="n">
-        <v>560.9573215839381</v>
+        <v>561.4369046651577</v>
       </c>
       <c r="E227" t="n">
-        <v>569.6004638671875</v>
+        <v>575.6856689453125</v>
       </c>
       <c r="F227" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B228" t="n">
-        <v>589.8444773654404</v>
+        <v>576.0253592943615</v>
       </c>
       <c r="C228" t="n">
-        <v>592.8721171723366</v>
+        <v>587.9260010338789</v>
       </c>
       <c r="D228" t="n">
-        <v>561.4369046651577</v>
+        <v>567.1723610665189</v>
       </c>
       <c r="E228" t="n">
-        <v>575.6856689453125</v>
+        <v>570.6495971679688</v>
       </c>
       <c r="F228" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B229" t="n">
-        <v>576.0253592943615</v>
+        <v>571.0992793335739</v>
       </c>
       <c r="C229" t="n">
-        <v>587.9260010338789</v>
+        <v>588.7253835559844</v>
       </c>
       <c r="D229" t="n">
-        <v>567.1723610665189</v>
+        <v>570.5497252457161</v>
       </c>
       <c r="E229" t="n">
-        <v>570.6495971679688</v>
+        <v>577.564208984375</v>
       </c>
       <c r="F229" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B230" t="n">
-        <v>571.0992793335739</v>
+        <v>577.1744781551006</v>
       </c>
       <c r="C230" t="n">
-        <v>588.7253835559844</v>
+        <v>578.2236379136884</v>
       </c>
       <c r="D230" t="n">
-        <v>570.5497252457161</v>
+        <v>568.6911832402849</v>
       </c>
       <c r="E230" t="n">
-        <v>577.564208984375</v>
+        <v>571.888671875</v>
       </c>
       <c r="F230" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B231" t="n">
-        <v>577.1744781551006</v>
+        <v>557.9096596695957</v>
       </c>
       <c r="C231" t="n">
-        <v>578.2236379136884</v>
+        <v>584.4887194481862</v>
       </c>
       <c r="D231" t="n">
-        <v>568.6911832402849</v>
+        <v>555.6614340241316</v>
       </c>
       <c r="E231" t="n">
-        <v>571.888671875</v>
+        <v>578.083740234375</v>
       </c>
       <c r="F231" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B232" t="n">
-        <v>557.9096596695957</v>
+        <v>578.3335366296732</v>
       </c>
       <c r="C232" t="n">
-        <v>584.4887194481862</v>
+        <v>599.9065373056851</v>
       </c>
       <c r="D232" t="n">
-        <v>555.6614340241316</v>
+        <v>576.5449702025707</v>
       </c>
       <c r="E232" t="n">
-        <v>578.083740234375</v>
+        <v>592.3824462890625</v>
       </c>
       <c r="F232" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B233" t="n">
-        <v>578.3335366296732</v>
+        <v>604.0133041368691</v>
       </c>
       <c r="C233" t="n">
-        <v>599.9065373056851</v>
+        <v>618.9715308723809</v>
       </c>
       <c r="D233" t="n">
-        <v>576.5449702025707</v>
+        <v>603.8733999005765</v>
       </c>
       <c r="E233" t="n">
-        <v>592.3824462890625</v>
+        <v>610.1984252929688</v>
       </c>
       <c r="F233" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B234" t="n">
-        <v>604.0133041368691</v>
+        <v>611.8670721034152</v>
       </c>
       <c r="C234" t="n">
-        <v>618.9715308723809</v>
+        <v>616.9730886717387</v>
       </c>
       <c r="D234" t="n">
-        <v>603.8733999005765</v>
+        <v>604.7926993516937</v>
       </c>
       <c r="E234" t="n">
-        <v>610.1984252929688</v>
+        <v>616.2836303710938</v>
       </c>
       <c r="F234" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B235" t="n">
-        <v>611.8670721034152</v>
+        <v>615.7241045276966</v>
       </c>
       <c r="C235" t="n">
-        <v>616.9730886717387</v>
+        <v>624.3072966603136</v>
       </c>
       <c r="D235" t="n">
-        <v>604.7926993516937</v>
+        <v>609.2591747857786</v>
       </c>
       <c r="E235" t="n">
-        <v>616.2836303710938</v>
+        <v>612.9962158203125</v>
       </c>
       <c r="F235" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B236" t="n">
-        <v>615.7241045276966</v>
+        <v>648.1284941622514</v>
       </c>
       <c r="C236" t="n">
-        <v>624.3072966603136</v>
+        <v>657.3411939542544</v>
       </c>
       <c r="D236" t="n">
-        <v>609.2591747857786</v>
+        <v>638.056426220049</v>
       </c>
       <c r="E236" t="n">
-        <v>612.9962158203125</v>
+        <v>653.1744995117188</v>
       </c>
       <c r="F236" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B237" t="n">
-        <v>648.1284941622514</v>
+        <v>653.1945472302951</v>
       </c>
       <c r="C237" t="n">
-        <v>657.3411939542544</v>
+        <v>662.9768054946985</v>
       </c>
       <c r="D237" t="n">
-        <v>638.056426220049</v>
+        <v>641.6336632885306</v>
       </c>
       <c r="E237" t="n">
-        <v>653.1744995117188</v>
+        <v>643.8718872070312</v>
       </c>
       <c r="F237" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B238" t="n">
-        <v>653.1945472302951</v>
+        <v>652.9947023490145</v>
       </c>
       <c r="C238" t="n">
-        <v>662.9768054946985</v>
+        <v>663.716221985592</v>
       </c>
       <c r="D238" t="n">
-        <v>641.6336632885306</v>
+        <v>645.6904688887529</v>
       </c>
       <c r="E238" t="n">
-        <v>643.8718872070312</v>
+        <v>647.51904296875</v>
       </c>
       <c r="F238" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B239" t="n">
-        <v>652.9947023490145</v>
+        <v>657.311302577125</v>
       </c>
       <c r="C239" t="n">
-        <v>663.716221985592</v>
+        <v>668.072768706455</v>
       </c>
       <c r="D239" t="n">
-        <v>645.6904688887529</v>
+        <v>648.708045415434</v>
       </c>
       <c r="E239" t="n">
-        <v>647.51904296875</v>
+        <v>665.0751342773438</v>
       </c>
       <c r="F239" t="n">
-        <v>16925000</v>
+        <v>19332300</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B240" t="n">
-        <v>657.311302577125</v>
+        <v>658.7801108800835</v>
       </c>
       <c r="C240" t="n">
-        <v>668.072768706455</v>
+        <v>678.3346866933342</v>
       </c>
       <c r="D240" t="n">
-        <v>648.708045415434</v>
+        <v>655.6825797136325</v>
       </c>
       <c r="E240" t="n">
-        <v>665.0751342773438</v>
+        <v>669.7114868164062</v>
       </c>
       <c r="F240" t="n">
-        <v>19332300</v>
+        <v>19502800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B241" t="n">
-        <v>658.7801108800835</v>
+        <v>679.3738238485387</v>
       </c>
       <c r="C241" t="n">
-        <v>678.3346866933342</v>
+        <v>684.7695900234191</v>
       </c>
       <c r="D241" t="n">
-        <v>655.6825797136325</v>
+        <v>671.3801323225093</v>
       </c>
       <c r="E241" t="n">
-        <v>669.7114868164062</v>
+        <v>672.779052734375</v>
       </c>
       <c r="F241" t="n">
-        <v>19502800</v>
+        <v>17217800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B242" t="n">
-        <v>679.3738238485387</v>
+        <v>681.9018750257407</v>
       </c>
       <c r="C242" t="n">
-        <v>684.7695900234191</v>
+        <v>682.6612854975235</v>
       </c>
       <c r="D242" t="n">
-        <v>671.3801323225093</v>
+        <v>666.5239959332205</v>
       </c>
       <c r="E242" t="n">
-        <v>672.779052734375</v>
+        <v>681.77197265625</v>
       </c>
       <c r="F242" t="n">
-        <v>17217800</v>
+        <v>15928000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B243" t="n">
-        <v>681.9018750257407</v>
+        <v>688.0769980771287</v>
       </c>
       <c r="C243" t="n">
-        <v>682.6612854975235</v>
+        <v>689.6058209010791</v>
       </c>
       <c r="D243" t="n">
-        <v>666.5239959332205</v>
+        <v>660.278927643704</v>
       </c>
       <c r="E243" t="n">
-        <v>681.77197265625</v>
+        <v>665.2250366210938</v>
       </c>
       <c r="F243" t="n">
-        <v>15928000</v>
+        <v>27596400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,25 +6761,25 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B244" t="n">
-        <v>688.0769980771287</v>
+        <v>680.2999877929688</v>
       </c>
       <c r="C244" t="n">
-        <v>689.6058209010791</v>
+        <v>753</v>
       </c>
       <c r="D244" t="n">
-        <v>660.278927643704</v>
+        <v>679.5999755859375</v>
       </c>
       <c r="E244" t="n">
-        <v>665.2250366210938</v>
+        <v>741.25</v>
       </c>
       <c r="F244" t="n">
-        <v>27596400</v>
+        <v>48720500</v>
       </c>
       <c r="G244" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -6787,25 +6787,25 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B245" t="n">
-        <v>680.2999877929688</v>
+        <v>731.4000244140625</v>
       </c>
       <c r="C245" t="n">
-        <v>753</v>
+        <v>757.27001953125</v>
       </c>
       <c r="D245" t="n">
-        <v>679.5999755859375</v>
+        <v>730</v>
       </c>
       <c r="E245" t="n">
-        <v>741.25</v>
+        <v>736.5999755859375</v>
       </c>
       <c r="F245" t="n">
-        <v>48720500</v>
+        <v>28122100</v>
       </c>
       <c r="G245" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B246" t="n">
-        <v>731.4000244140625</v>
+        <v>747.5999755859375</v>
       </c>
       <c r="C246" t="n">
-        <v>757.27001953125</v>
+        <v>763.9000244140625</v>
       </c>
       <c r="D246" t="n">
-        <v>730</v>
+        <v>739.510009765625</v>
       </c>
       <c r="E246" t="n">
-        <v>736.5999755859375</v>
+        <v>744.0999755859375</v>
       </c>
       <c r="F246" t="n">
-        <v>28122100</v>
+        <v>30829200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B247" t="n">
-        <v>747.5999755859375</v>
+        <v>744.3599853515625</v>
       </c>
       <c r="C247" t="n">
-        <v>763.9000244140625</v>
+        <v>779.8200073242188</v>
       </c>
       <c r="D247" t="n">
-        <v>739.510009765625</v>
+        <v>743.010009765625</v>
       </c>
       <c r="E247" t="n">
-        <v>744.0999755859375</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="F247" t="n">
-        <v>30829200</v>
+        <v>34808500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B248" t="n">
-        <v>744.3599853515625</v>
+        <v>768.8499755859375</v>
       </c>
       <c r="C248" t="n">
-        <v>779.8200073242188</v>
+        <v>769.5700073242188</v>
       </c>
       <c r="D248" t="n">
-        <v>743.010009765625</v>
+        <v>746.5399780273438</v>
       </c>
       <c r="E248" t="n">
-        <v>777.5900268554688</v>
+        <v>751.6599731445312</v>
       </c>
       <c r="F248" t="n">
-        <v>34808500</v>
+        <v>25826700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B249" t="n">
-        <v>768.8499755859375</v>
+        <v>750.0399780273438</v>
       </c>
       <c r="C249" t="n">
-        <v>769.5700073242188</v>
+        <v>750.5800170898438</v>
       </c>
       <c r="D249" t="n">
-        <v>746.5399780273438</v>
+        <v>713.1900024414062</v>
       </c>
       <c r="E249" t="n">
-        <v>751.6599731445312</v>
+        <v>715.6199951171875</v>
       </c>
       <c r="F249" t="n">
-        <v>25826700</v>
+        <v>27943100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B250" t="n">
-        <v>750.0399780273438</v>
+        <v>725</v>
       </c>
       <c r="C250" t="n">
-        <v>750.5800170898438</v>
+        <v>740.4500122070312</v>
       </c>
       <c r="D250" t="n">
-        <v>713.1900024414062</v>
+        <v>715.0999755859375</v>
       </c>
       <c r="E250" t="n">
-        <v>715.6199951171875</v>
+        <v>738.7899780273438</v>
       </c>
       <c r="F250" t="n">
-        <v>27943100</v>
+        <v>23591100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B251" t="n">
-        <v>725</v>
+        <v>730.27001953125</v>
       </c>
       <c r="C251" t="n">
-        <v>740.4500122070312</v>
+        <v>738.25</v>
       </c>
       <c r="D251" t="n">
-        <v>715.0999755859375</v>
+        <v>721.2999877929688</v>
       </c>
       <c r="E251" t="n">
-        <v>738.7899780273438</v>
+        <v>725.1799926757812</v>
       </c>
       <c r="F251" t="n">
-        <v>23591100</v>
+        <v>19293000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B252" t="n">
-        <v>730.27001953125</v>
+        <v>728.530029296875</v>
       </c>
       <c r="C252" t="n">
-        <v>738.25</v>
+        <v>735.8800048828125</v>
       </c>
       <c r="D252" t="n">
-        <v>721.2999877929688</v>
+        <v>721.510009765625</v>
       </c>
       <c r="E252" t="n">
-        <v>725.1799926757812</v>
+        <v>725.9299926757812</v>
       </c>
       <c r="F252" t="n">
-        <v>19240800</v>
+        <v>12384700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>725.9299999999999</v>
+      </c>
+      <c r="D2" t="n">
         <v>725.1799999999999</v>
       </c>
-      <c r="D2" t="n">
-        <v>738.79</v>
-      </c>
       <c r="E2" t="n">
-        <v>729</v>
+        <v>728.525</v>
       </c>
       <c r="F2" t="n">
-        <v>738.25</v>
+        <v>735.88</v>
       </c>
       <c r="G2" t="n">
-        <v>721.3</v>
+        <v>721.51</v>
       </c>
       <c r="H2" t="n">
-        <v>19151113</v>
+        <v>12256112</v>
       </c>
       <c r="I2" t="n">
-        <v>19621914</v>
+        <v>19468738</v>
       </c>
       <c r="J2" t="n">
-        <v>1847400464384</v>
+        <v>1849311100928</v>
       </c>
       <c r="K2" t="n">
-        <v>27.859392</v>
+        <v>27.321415</v>
       </c>
       <c r="L2" t="n">
-        <v>20.817175</v>
+        <v>20.796753</v>
       </c>
       <c r="M2" t="n">
-        <v>26.03</v>
+        <v>26.57</v>
       </c>
       <c r="N2" t="n">
         <v>779.8200000000001</v>
@@ -10818,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.073547</v>
+        <v>7.0808625</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1869458571264</v>
+        <v>1871369207808</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:02:39</t>
+          <t>2026-10-02 19:38:21</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B2" t="n">
-        <v>720.1372426569798</v>
+        <v>727.1634377305112</v>
       </c>
       <c r="C2" t="n">
-        <v>725.309699629413</v>
+        <v>728.528801479838</v>
       </c>
       <c r="D2" t="n">
-        <v>715.7122502133443</v>
+        <v>707.7791777004747</v>
       </c>
       <c r="E2" t="n">
-        <v>724.5921020507812</v>
+        <v>708.1578979492188</v>
       </c>
       <c r="F2" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B3" t="n">
-        <v>727.1633750572937</v>
+        <v>702.8060248479621</v>
       </c>
       <c r="C3" t="n">
-        <v>728.5287386889415</v>
+        <v>714.4565078636942</v>
       </c>
       <c r="D3" t="n">
-        <v>707.7791166979599</v>
+        <v>688.1756596108709</v>
       </c>
       <c r="E3" t="n">
-        <v>708.1578369140625</v>
+        <v>713.2406005859375</v>
       </c>
       <c r="F3" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B4" t="n">
-        <v>702.8060248479621</v>
+        <v>715.2936403041813</v>
       </c>
       <c r="C4" t="n">
-        <v>714.4565078636942</v>
+        <v>716.0710326272052</v>
       </c>
       <c r="D4" t="n">
-        <v>688.1756596108709</v>
+        <v>703.3641353885179</v>
       </c>
       <c r="E4" t="n">
-        <v>713.2406005859375</v>
+        <v>710.6693725585938</v>
       </c>
       <c r="F4" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B5" t="n">
-        <v>715.2936403041813</v>
+        <v>711.0380954481734</v>
       </c>
       <c r="C5" t="n">
-        <v>716.0710326272052</v>
+        <v>717.2171476536749</v>
       </c>
       <c r="D5" t="n">
-        <v>703.3641353885179</v>
+        <v>705.4171476518181</v>
       </c>
       <c r="E5" t="n">
-        <v>710.6693725585938</v>
+        <v>715.4132690429688</v>
       </c>
       <c r="F5" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B6" t="n">
-        <v>711.0380954481734</v>
+        <v>715.8517801132227</v>
       </c>
       <c r="C6" t="n">
-        <v>717.2171476536749</v>
+        <v>731.0302734375</v>
       </c>
       <c r="D6" t="n">
-        <v>705.4171476518181</v>
+        <v>710.0314963104157</v>
       </c>
       <c r="E6" t="n">
-        <v>715.4132690429688</v>
+        <v>731.0302734375</v>
       </c>
       <c r="F6" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B7" t="n">
-        <v>715.8518398810967</v>
+        <v>728.4490335307075</v>
       </c>
       <c r="C7" t="n">
-        <v>731.0303344726562</v>
+        <v>732.784364410351</v>
       </c>
       <c r="D7" t="n">
-        <v>710.0315555923428</v>
+        <v>702.1283419878271</v>
       </c>
       <c r="E7" t="n">
-        <v>731.0303344726562</v>
+        <v>702.9156494140625</v>
       </c>
       <c r="F7" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B8" t="n">
-        <v>728.4490335307075</v>
+        <v>710.5996089558437</v>
       </c>
       <c r="C8" t="n">
-        <v>732.784364410351</v>
+        <v>717.5061741064447</v>
       </c>
       <c r="D8" t="n">
-        <v>702.1283419878271</v>
+        <v>705.2477676379041</v>
       </c>
       <c r="E8" t="n">
-        <v>702.9156494140625</v>
+        <v>713.280517578125</v>
       </c>
       <c r="F8" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B9" t="n">
-        <v>710.5996089558437</v>
+        <v>705.3873404797914</v>
       </c>
       <c r="C9" t="n">
-        <v>717.5061741064447</v>
+        <v>713.1310322093289</v>
       </c>
       <c r="D9" t="n">
-        <v>705.2477676379041</v>
+        <v>696.9658939978091</v>
       </c>
       <c r="E9" t="n">
-        <v>713.280517578125</v>
+        <v>706.25439453125</v>
       </c>
       <c r="F9" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B10" t="n">
-        <v>705.3873404797914</v>
+        <v>714.6359337847463</v>
       </c>
       <c r="C10" t="n">
-        <v>713.1310322093289</v>
+        <v>721.4528375244799</v>
       </c>
       <c r="D10" t="n">
-        <v>696.9658939978091</v>
+        <v>707.1114691724935</v>
       </c>
       <c r="E10" t="n">
-        <v>706.25439453125</v>
+        <v>715.124267578125</v>
       </c>
       <c r="F10" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B11" t="n">
-        <v>714.6358727912688</v>
+        <v>715.1242355877501</v>
       </c>
       <c r="C11" t="n">
-        <v>721.4527759491865</v>
+        <v>723.0373960268438</v>
       </c>
       <c r="D11" t="n">
-        <v>707.1114088212217</v>
+        <v>701.5004654735715</v>
       </c>
       <c r="E11" t="n">
-        <v>715.1242065429688</v>
+        <v>709.6627807617188</v>
       </c>
       <c r="F11" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B12" t="n">
-        <v>715.1241740828767</v>
+        <v>704.6896374063629</v>
       </c>
       <c r="C12" t="n">
-        <v>723.0373338413923</v>
+        <v>716.1108563950927</v>
       </c>
       <c r="D12" t="n">
-        <v>701.5004051404221</v>
+        <v>703.7328609179003</v>
       </c>
       <c r="E12" t="n">
-        <v>709.6627197265625</v>
+        <v>714.496337890625</v>
       </c>
       <c r="F12" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B13" t="n">
-        <v>704.6896976037913</v>
+        <v>718.7519624447335</v>
       </c>
       <c r="C13" t="n">
-        <v>716.1109175681677</v>
+        <v>731.2894517891565</v>
       </c>
       <c r="D13" t="n">
-        <v>703.732921033597</v>
+        <v>717.7453670972193</v>
       </c>
       <c r="E13" t="n">
-        <v>714.4963989257812</v>
+        <v>729.69482421875</v>
       </c>
       <c r="F13" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B14" t="n">
-        <v>718.7519023248905</v>
+        <v>733.5318410857864</v>
       </c>
       <c r="C14" t="n">
-        <v>731.289390620618</v>
+        <v>736.0034377690635</v>
       </c>
       <c r="D14" t="n">
-        <v>717.7453070615727</v>
+        <v>726.2863984755653</v>
       </c>
       <c r="E14" t="n">
-        <v>729.6947631835938</v>
+        <v>730.7911376953125</v>
       </c>
       <c r="F14" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B15" t="n">
-        <v>733.5318410857864</v>
+        <v>731.3492269695964</v>
       </c>
       <c r="C15" t="n">
-        <v>736.0034377690635</v>
+        <v>738.0962989037338</v>
       </c>
       <c r="D15" t="n">
-        <v>726.2863984755653</v>
+        <v>721.5823690736463</v>
       </c>
       <c r="E15" t="n">
-        <v>730.7911376953125</v>
+        <v>730.9306030273438</v>
       </c>
       <c r="F15" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B16" t="n">
-        <v>731.3492269695964</v>
+        <v>732.2163225390138</v>
       </c>
       <c r="C16" t="n">
-        <v>738.0962989037338</v>
+        <v>739.9002195728755</v>
       </c>
       <c r="D16" t="n">
-        <v>721.5823690736463</v>
+        <v>730.6216949207216</v>
       </c>
       <c r="E16" t="n">
-        <v>730.9306030273438</v>
+        <v>731.5186767578125</v>
       </c>
       <c r="F16" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B17" t="n">
-        <v>732.2163225390138</v>
+        <v>734.2991918313108</v>
       </c>
       <c r="C17" t="n">
-        <v>739.9002195728755</v>
+        <v>738.7042934120783</v>
       </c>
       <c r="D17" t="n">
-        <v>730.6216949207216</v>
+        <v>728.6783045992579</v>
       </c>
       <c r="E17" t="n">
-        <v>731.5186767578125</v>
+        <v>735.8638916015625</v>
       </c>
       <c r="F17" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B18" t="n">
-        <v>734.2991309259364</v>
+        <v>747.1953964386955</v>
       </c>
       <c r="C18" t="n">
-        <v>738.704232141329</v>
+        <v>753.1950643156673</v>
       </c>
       <c r="D18" t="n">
-        <v>728.6782441600997</v>
+        <v>745.4812403760276</v>
       </c>
       <c r="E18" t="n">
-        <v>735.8638305664062</v>
+        <v>748.28173828125</v>
       </c>
       <c r="F18" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B19" t="n">
-        <v>747.195457385242</v>
+        <v>750.0856988126538</v>
       </c>
       <c r="C19" t="n">
-        <v>753.1951257515892</v>
+        <v>755.8362124836232</v>
       </c>
       <c r="D19" t="n">
-        <v>745.4813011827554</v>
+        <v>742.9997491476457</v>
       </c>
       <c r="E19" t="n">
-        <v>748.2817993164062</v>
+        <v>748.8997192382812</v>
       </c>
       <c r="F19" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B20" t="n">
-        <v>750.0856988126538</v>
+        <v>752.1985111114485</v>
       </c>
       <c r="C20" t="n">
-        <v>755.8362124836232</v>
+        <v>756.5935760115584</v>
       </c>
       <c r="D20" t="n">
-        <v>742.9997491476457</v>
+        <v>739.9998990805568</v>
       </c>
       <c r="E20" t="n">
-        <v>748.8997192382812</v>
+        <v>749.12890625</v>
       </c>
       <c r="F20" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B21" t="n">
-        <v>752.1985111114485</v>
+        <v>666.8879738141238</v>
       </c>
       <c r="C21" t="n">
-        <v>756.5935760115584</v>
+        <v>678.658047871129</v>
       </c>
       <c r="D21" t="n">
-        <v>739.9998990805568</v>
+        <v>647.9720940268795</v>
       </c>
       <c r="E21" t="n">
-        <v>749.12890625</v>
+        <v>664.2169799804688</v>
       </c>
       <c r="F21" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B22" t="n">
-        <v>666.8879125335289</v>
+        <v>672.2297387877188</v>
       </c>
       <c r="C22" t="n">
-        <v>678.6579855089774</v>
+        <v>672.6084590133829</v>
       </c>
       <c r="D22" t="n">
-        <v>647.9720344844721</v>
+        <v>643.3875718813117</v>
       </c>
       <c r="E22" t="n">
-        <v>664.2169189453125</v>
+        <v>646.1581420898438</v>
       </c>
       <c r="F22" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B23" t="n">
-        <v>672.2297387877188</v>
+        <v>653.7823467127146</v>
       </c>
       <c r="C23" t="n">
-        <v>672.6084590133829</v>
+        <v>657.1011064498967</v>
       </c>
       <c r="D23" t="n">
-        <v>643.3875718813117</v>
+        <v>634.0293422915395</v>
       </c>
       <c r="E23" t="n">
-        <v>646.1581420898438</v>
+        <v>635.55419921875</v>
       </c>
       <c r="F23" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B24" t="n">
-        <v>653.7823467127146</v>
+        <v>625.9168165443936</v>
       </c>
       <c r="C24" t="n">
-        <v>657.1011064498967</v>
+        <v>639.5705142822006</v>
       </c>
       <c r="D24" t="n">
-        <v>634.0293422915395</v>
+        <v>623.8937108241939</v>
       </c>
       <c r="E24" t="n">
-        <v>635.55419921875</v>
+        <v>625.1992797851562</v>
       </c>
       <c r="F24" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B25" t="n">
-        <v>625.9168776495994</v>
+        <v>630.1724007040705</v>
       </c>
       <c r="C25" t="n">
-        <v>639.5705767203505</v>
+        <v>640.0588479681868</v>
       </c>
       <c r="D25" t="n">
-        <v>623.8937717318939</v>
+        <v>624.4218873891514</v>
       </c>
       <c r="E25" t="n">
-        <v>625.1993408203125</v>
+        <v>633.8001098632812</v>
       </c>
       <c r="F25" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B26" t="n">
-        <v>630.1724007040705</v>
+        <v>633.7004019945108</v>
       </c>
       <c r="C26" t="n">
-        <v>640.0588479681868</v>
+        <v>633.8499192315176</v>
       </c>
       <c r="D26" t="n">
-        <v>624.4218873891514</v>
+        <v>615.9107705740217</v>
       </c>
       <c r="E26" t="n">
-        <v>633.8001098632812</v>
+        <v>616.8475952148438</v>
       </c>
       <c r="F26" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B27" t="n">
-        <v>633.7004019945108</v>
+        <v>614.4058308842617</v>
       </c>
       <c r="C27" t="n">
-        <v>633.8499192315176</v>
+        <v>620.0267784116583</v>
       </c>
       <c r="D27" t="n">
-        <v>615.9107705740217</v>
+        <v>599.1675434782962</v>
       </c>
       <c r="E27" t="n">
-        <v>616.8475952148438</v>
+        <v>619.6082153320312</v>
       </c>
       <c r="F27" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B28" t="n">
-        <v>614.4058914069517</v>
+        <v>628.9565496273584</v>
       </c>
       <c r="C28" t="n">
-        <v>620.0268394880455</v>
+        <v>632.8533046281837</v>
       </c>
       <c r="D28" t="n">
-        <v>599.1676024999227</v>
+        <v>616.0203887455347</v>
       </c>
       <c r="E28" t="n">
-        <v>619.6082763671875</v>
+        <v>629.624267578125</v>
       </c>
       <c r="F28" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B29" t="n">
-        <v>628.9565496273584</v>
+        <v>625.8770169082796</v>
       </c>
       <c r="C29" t="n">
-        <v>632.8533046281837</v>
+        <v>627.4317408228605</v>
       </c>
       <c r="D29" t="n">
-        <v>616.0203887455347</v>
+        <v>617.2961380110504</v>
       </c>
       <c r="E29" t="n">
-        <v>629.624267578125</v>
+        <v>624.9601440429688</v>
       </c>
       <c r="F29" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B30" t="n">
-        <v>625.8770169082796</v>
+        <v>626.0065293511232</v>
       </c>
       <c r="C30" t="n">
-        <v>627.4317408228605</v>
+        <v>626.8636074098682</v>
       </c>
       <c r="D30" t="n">
-        <v>617.2961380110504</v>
+        <v>605.7153735895874</v>
       </c>
       <c r="E30" t="n">
-        <v>624.9601440429688</v>
+        <v>606.951171875</v>
       </c>
       <c r="F30" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B31" t="n">
-        <v>626.0065923024907</v>
+        <v>610.9974282481795</v>
       </c>
       <c r="C31" t="n">
-        <v>626.8636704474237</v>
+        <v>615.5619618736964</v>
       </c>
       <c r="D31" t="n">
-        <v>605.7154345004715</v>
+        <v>600.9614641591972</v>
       </c>
       <c r="E31" t="n">
-        <v>606.9512329101562</v>
+        <v>607.8281860351562</v>
       </c>
       <c r="F31" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B32" t="n">
-        <v>610.9974282481795</v>
+        <v>599.7556041676178</v>
       </c>
       <c r="C32" t="n">
-        <v>615.5619618736964</v>
+        <v>611.6054241702889</v>
       </c>
       <c r="D32" t="n">
-        <v>600.9614641591972</v>
+        <v>593.1879159768617</v>
       </c>
       <c r="E32" t="n">
-        <v>607.8281860351562</v>
+        <v>607.3997192382812</v>
       </c>
       <c r="F32" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B33" t="n">
-        <v>599.7556041676178</v>
+        <v>606.980994504603</v>
       </c>
       <c r="C33" t="n">
-        <v>611.6054241702889</v>
+        <v>609.6220599721263</v>
       </c>
       <c r="D33" t="n">
-        <v>593.1879159768617</v>
+        <v>593.3871535288397</v>
       </c>
       <c r="E33" t="n">
-        <v>607.3997192382812</v>
+        <v>599.9747924804688</v>
       </c>
       <c r="F33" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B34" t="n">
-        <v>606.9810562524968</v>
+        <v>589.6000552799869</v>
       </c>
       <c r="C34" t="n">
-        <v>609.6221219886945</v>
+        <v>601.6192836786712</v>
       </c>
       <c r="D34" t="n">
-        <v>593.3872138938384</v>
+        <v>581.8065445386262</v>
       </c>
       <c r="E34" t="n">
-        <v>599.974853515625</v>
+        <v>595.6694946289062</v>
       </c>
       <c r="F34" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B35" t="n">
-        <v>589.5999948667346</v>
+        <v>591.7128101062766</v>
       </c>
       <c r="C35" t="n">
-        <v>601.619222033871</v>
+        <v>593.3174134864839</v>
       </c>
       <c r="D35" t="n">
-        <v>581.8064849239344</v>
+        <v>579.2849960343485</v>
       </c>
       <c r="E35" t="n">
-        <v>595.66943359375</v>
+        <v>588.3243408203125</v>
       </c>
       <c r="F35" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B36" t="n">
-        <v>591.7128714929664</v>
+        <v>601.4597887996167</v>
       </c>
       <c r="C36" t="n">
-        <v>593.3174750396417</v>
+        <v>604.6688739678727</v>
       </c>
       <c r="D36" t="n">
-        <v>579.2850561317264</v>
+        <v>581.3778841958236</v>
       </c>
       <c r="E36" t="n">
-        <v>588.3244018554688</v>
+        <v>587.1583251953125</v>
       </c>
       <c r="F36" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B37" t="n">
-        <v>601.4598513214113</v>
+        <v>586.5105272163902</v>
       </c>
       <c r="C37" t="n">
-        <v>604.668936823252</v>
+        <v>596.0980011467227</v>
       </c>
       <c r="D37" t="n">
-        <v>581.3779446301025</v>
+        <v>579.8929596850738</v>
       </c>
       <c r="E37" t="n">
-        <v>587.1583862304688</v>
+        <v>592.2410888671875</v>
       </c>
       <c r="F37" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B38" t="n">
-        <v>586.5104667718139</v>
+        <v>596.6959653725695</v>
       </c>
       <c r="C38" t="n">
-        <v>596.097939714081</v>
+        <v>614.6152243710839</v>
       </c>
       <c r="D38" t="n">
-        <v>579.8928999224906</v>
+        <v>595.6096842408232</v>
       </c>
       <c r="E38" t="n">
-        <v>592.2410278320312</v>
+        <v>610.9775390625</v>
       </c>
       <c r="F38" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B39" t="n">
-        <v>596.6959653725695</v>
+        <v>621.8904932046078</v>
       </c>
       <c r="C39" t="n">
-        <v>614.6152243710839</v>
+        <v>634.8963639496133</v>
       </c>
       <c r="D39" t="n">
-        <v>595.6096842408232</v>
+        <v>616.209750572071</v>
       </c>
       <c r="E39" t="n">
-        <v>610.9775390625</v>
+        <v>634.0691528320312</v>
       </c>
       <c r="F39" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B40" t="n">
-        <v>621.8904932046078</v>
+        <v>635.5341804250853</v>
       </c>
       <c r="C40" t="n">
-        <v>634.8963639496133</v>
+        <v>636.2018983414315</v>
       </c>
       <c r="D40" t="n">
-        <v>616.209750572071</v>
+        <v>629.4946697427255</v>
       </c>
       <c r="E40" t="n">
-        <v>634.0691528320312</v>
+        <v>631.4679565429688</v>
       </c>
       <c r="F40" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B41" t="n">
-        <v>635.5342418532664</v>
+        <v>633.9297145559904</v>
       </c>
       <c r="C41" t="n">
-        <v>636.2019598341516</v>
+        <v>645.8592201326509</v>
       </c>
       <c r="D41" t="n">
-        <v>629.4947305871518</v>
+        <v>633.351658244955</v>
       </c>
       <c r="E41" t="n">
-        <v>631.468017578125</v>
+        <v>645.7595825195312</v>
       </c>
       <c r="F41" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B42" t="n">
-        <v>633.9296546389559</v>
+        <v>637.3878853503733</v>
       </c>
       <c r="C42" t="n">
-        <v>645.8591590880771</v>
+        <v>643.1383983949365</v>
       </c>
       <c r="D42" t="n">
-        <v>633.3515983825566</v>
+        <v>635.6039586340122</v>
       </c>
       <c r="E42" t="n">
-        <v>645.759521484375</v>
+        <v>638.7034301757812</v>
       </c>
       <c r="F42" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B43" t="n">
-        <v>637.3879462598147</v>
+        <v>640.1684965318557</v>
       </c>
       <c r="C43" t="n">
-        <v>643.138459853903</v>
+        <v>645.6797698761368</v>
       </c>
       <c r="D43" t="n">
-        <v>635.6040193729798</v>
+        <v>635.9129124654792</v>
       </c>
       <c r="E43" t="n">
-        <v>638.7034912109375</v>
+        <v>644.912353515625</v>
       </c>
       <c r="F43" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B44" t="n">
-        <v>640.1684359456628</v>
+        <v>642.2314810232181</v>
       </c>
       <c r="C44" t="n">
-        <v>645.6797087683515</v>
+        <v>646.6564735939825</v>
       </c>
       <c r="D44" t="n">
-        <v>635.9128522820391</v>
+        <v>635.3946865356451</v>
       </c>
       <c r="E44" t="n">
-        <v>644.9122924804688</v>
+        <v>637.437744140625</v>
       </c>
       <c r="F44" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B45" t="n">
-        <v>642.2314810232181</v>
+        <v>673.7147555733686</v>
       </c>
       <c r="C45" t="n">
-        <v>646.6564735939825</v>
+        <v>673.8143931879296</v>
       </c>
       <c r="D45" t="n">
-        <v>635.3946865356451</v>
+        <v>657.8186630061315</v>
       </c>
       <c r="E45" t="n">
-        <v>637.437744140625</v>
+        <v>659.293701171875</v>
       </c>
       <c r="F45" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B46" t="n">
-        <v>673.7146932031604</v>
+        <v>661.7552947151958</v>
       </c>
       <c r="C46" t="n">
-        <v>673.8143308084973</v>
+        <v>672.4091587454953</v>
       </c>
       <c r="D46" t="n">
-        <v>657.8186021075292</v>
+        <v>660.1507520483126</v>
       </c>
       <c r="E46" t="n">
-        <v>659.2936401367188</v>
+        <v>671.1434326171875</v>
       </c>
       <c r="F46" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B47" t="n">
-        <v>661.7552947151958</v>
+        <v>667.0772284693074</v>
       </c>
       <c r="C47" t="n">
-        <v>672.4091587454953</v>
+        <v>674.4223082782987</v>
       </c>
       <c r="D47" t="n">
-        <v>660.1507520483126</v>
+        <v>662.8216443414645</v>
       </c>
       <c r="E47" t="n">
-        <v>671.1434326171875</v>
+        <v>664.5457763671875</v>
       </c>
       <c r="F47" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B48" t="n">
-        <v>667.0772284693074</v>
+        <v>661.5261117632423</v>
       </c>
       <c r="C48" t="n">
-        <v>674.4223082782987</v>
+        <v>662.2336726422647</v>
       </c>
       <c r="D48" t="n">
-        <v>662.8216443414645</v>
+        <v>651.1313781996487</v>
       </c>
       <c r="E48" t="n">
-        <v>664.5457763671875</v>
+        <v>654.7391357421875</v>
       </c>
       <c r="F48" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B49" t="n">
-        <v>661.5260500954003</v>
+        <v>647.7527447265774</v>
       </c>
       <c r="C49" t="n">
-        <v>662.2336109084633</v>
+        <v>652.2973264314004</v>
       </c>
       <c r="D49" t="n">
-        <v>651.1313175008097</v>
+        <v>641.2249002906431</v>
       </c>
       <c r="E49" t="n">
-        <v>654.7390747070312</v>
+        <v>647.93212890625</v>
       </c>
       <c r="F49" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B50" t="n">
-        <v>647.7527447265774</v>
+        <v>641.1152201817421</v>
       </c>
       <c r="C50" t="n">
-        <v>652.2973264314004</v>
+        <v>653.0647369194785</v>
       </c>
       <c r="D50" t="n">
-        <v>641.2249002906431</v>
+        <v>638.6336478086467</v>
       </c>
       <c r="E50" t="n">
-        <v>647.93212890625</v>
+        <v>650.50341796875</v>
       </c>
       <c r="F50" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B51" t="n">
-        <v>641.1152803360264</v>
+        <v>647.603240055161</v>
       </c>
       <c r="C51" t="n">
-        <v>653.0647981949571</v>
+        <v>708.5963563082138</v>
       </c>
       <c r="D51" t="n">
-        <v>638.6337077300913</v>
+        <v>636.4510671197735</v>
       </c>
       <c r="E51" t="n">
-        <v>650.5034790039062</v>
+        <v>642.0520629882812</v>
       </c>
       <c r="F51" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,25 +1769,25 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B52" t="n">
-        <v>647.6033016180266</v>
+        <v>644.0420011784053</v>
       </c>
       <c r="C52" t="n">
-        <v>708.5964236692454</v>
+        <v>651.3232442601446</v>
       </c>
       <c r="D52" t="n">
-        <v>636.4511276224844</v>
+        <v>637.0599755890928</v>
       </c>
       <c r="E52" t="n">
-        <v>642.0521240234375</v>
+        <v>645.8473510742188</v>
       </c>
       <c r="F52" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B53" t="n">
-        <v>644.0420011784053</v>
+        <v>641.8476715248971</v>
       </c>
       <c r="C53" t="n">
-        <v>651.3232442601446</v>
+        <v>660.8387602004772</v>
       </c>
       <c r="D53" t="n">
-        <v>637.0599755890928</v>
+        <v>641.5484540168895</v>
       </c>
       <c r="E53" t="n">
-        <v>645.8473510742188</v>
+        <v>655.462646484375</v>
       </c>
       <c r="F53" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G53" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B54" t="n">
-        <v>641.8476715248971</v>
+        <v>653.9265721002572</v>
       </c>
       <c r="C54" t="n">
-        <v>660.8387602004772</v>
+        <v>659.5321367260491</v>
       </c>
       <c r="D54" t="n">
-        <v>641.5484540168895</v>
+        <v>647.5330578779101</v>
       </c>
       <c r="E54" t="n">
-        <v>655.462646484375</v>
+        <v>647.832275390625</v>
       </c>
       <c r="F54" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B55" t="n">
-        <v>653.9265104909302</v>
+        <v>655.3429055936973</v>
       </c>
       <c r="C55" t="n">
-        <v>659.5320745885969</v>
+        <v>668.8381315618529</v>
       </c>
       <c r="D55" t="n">
-        <v>647.5329968709444</v>
+        <v>654.7743619360156</v>
       </c>
       <c r="E55" t="n">
-        <v>647.8322143554688</v>
+        <v>662.7438354492188</v>
       </c>
       <c r="F55" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B56" t="n">
-        <v>655.3429055936973</v>
+        <v>664.7087499822148</v>
       </c>
       <c r="C56" t="n">
-        <v>668.8381315618529</v>
+        <v>669.2770065062657</v>
       </c>
       <c r="D56" t="n">
-        <v>654.7743619360156</v>
+        <v>656.4899183910027</v>
       </c>
       <c r="E56" t="n">
-        <v>662.7438354492188</v>
+        <v>657.0784301757812</v>
       </c>
       <c r="F56" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B57" t="n">
-        <v>664.7087499822148</v>
+        <v>659.9510918299604</v>
       </c>
       <c r="C57" t="n">
-        <v>669.2770065062657</v>
+        <v>671.8504516144289</v>
       </c>
       <c r="D57" t="n">
-        <v>656.4899183910027</v>
+        <v>654.9639304343692</v>
       </c>
       <c r="E57" t="n">
-        <v>657.0784301757812</v>
+        <v>659.8014526367188</v>
       </c>
       <c r="F57" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B58" t="n">
-        <v>659.9510918299604</v>
+        <v>658.3550860644432</v>
       </c>
       <c r="C58" t="n">
-        <v>671.8504516144289</v>
+        <v>664.2898196014329</v>
       </c>
       <c r="D58" t="n">
-        <v>654.9639304343692</v>
+        <v>656.5597203493141</v>
       </c>
       <c r="E58" t="n">
-        <v>659.8014526367188</v>
+        <v>663.2325439453125</v>
       </c>
       <c r="F58" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B59" t="n">
-        <v>658.3550860644432</v>
+        <v>660.8288080412273</v>
       </c>
       <c r="C59" t="n">
-        <v>664.2898196014329</v>
+        <v>666.4642636433252</v>
       </c>
       <c r="D59" t="n">
-        <v>656.5597203493141</v>
+        <v>660.499638357634</v>
       </c>
       <c r="E59" t="n">
-        <v>663.2325439453125</v>
+        <v>665.8358764648438</v>
       </c>
       <c r="F59" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B60" t="n">
-        <v>660.8288080412273</v>
+        <v>666.3446246130748</v>
       </c>
       <c r="C60" t="n">
-        <v>666.4642636433252</v>
+        <v>667.2323539771746</v>
       </c>
       <c r="D60" t="n">
-        <v>660.499638357634</v>
+        <v>659.6219406041037</v>
       </c>
       <c r="E60" t="n">
-        <v>665.8358764648438</v>
+        <v>661.5868530273438</v>
       </c>
       <c r="F60" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B61" t="n">
-        <v>666.3446246130748</v>
+        <v>656.3204105957403</v>
       </c>
       <c r="C61" t="n">
-        <v>667.2323539771746</v>
+        <v>658.5546491157273</v>
       </c>
       <c r="D61" t="n">
-        <v>659.6219406041037</v>
+        <v>652.7097106878265</v>
       </c>
       <c r="E61" t="n">
-        <v>661.5868530273438</v>
+        <v>656.9986572265625</v>
       </c>
       <c r="F61" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B62" t="n">
-        <v>656.3204105957403</v>
+        <v>656.9986226731097</v>
       </c>
       <c r="C62" t="n">
-        <v>658.5546491157273</v>
+        <v>670.4938487731155</v>
       </c>
       <c r="D62" t="n">
-        <v>652.7097106878265</v>
+        <v>656.1508296487782</v>
       </c>
       <c r="E62" t="n">
-        <v>656.9986572265625</v>
+        <v>664.239990234375</v>
       </c>
       <c r="F62" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B63" t="n">
-        <v>656.9986226731097</v>
+        <v>663.0430265979899</v>
       </c>
       <c r="C63" t="n">
-        <v>670.4938487731155</v>
+        <v>663.2923846373272</v>
       </c>
       <c r="D63" t="n">
-        <v>656.1508296487782</v>
+        <v>657.7466642776019</v>
       </c>
       <c r="E63" t="n">
-        <v>664.239990234375</v>
+        <v>658.39501953125</v>
       </c>
       <c r="F63" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B64" t="n">
-        <v>663.0430265979899</v>
+        <v>661.0282405096659</v>
       </c>
       <c r="C64" t="n">
-        <v>663.2923846373272</v>
+        <v>662.6840120988863</v>
       </c>
       <c r="D64" t="n">
-        <v>657.7466642776019</v>
+        <v>641.8476382600104</v>
       </c>
       <c r="E64" t="n">
-        <v>658.39501953125</v>
+        <v>648.7398681640625</v>
       </c>
       <c r="F64" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B65" t="n">
-        <v>661.0282405096659</v>
+        <v>649.3383972038786</v>
       </c>
       <c r="C65" t="n">
-        <v>662.6840120988863</v>
+        <v>662.8336242718107</v>
       </c>
       <c r="D65" t="n">
-        <v>641.8476382600104</v>
+        <v>646.086758236235</v>
       </c>
       <c r="E65" t="n">
-        <v>648.7398681640625</v>
+        <v>657.098388671875</v>
       </c>
       <c r="F65" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B66" t="n">
-        <v>649.3383972038786</v>
+        <v>657.8763534012292</v>
       </c>
       <c r="C66" t="n">
-        <v>662.8336242718107</v>
+        <v>663.8110870761799</v>
       </c>
       <c r="D66" t="n">
-        <v>646.086758236235</v>
+        <v>650.2260655901538</v>
       </c>
       <c r="E66" t="n">
-        <v>657.098388671875</v>
+        <v>658.9236450195312</v>
       </c>
       <c r="F66" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B67" t="n">
-        <v>657.8763534012292</v>
+        <v>653.956457912222</v>
       </c>
       <c r="C67" t="n">
-        <v>663.8110870761799</v>
+        <v>657.4574546517152</v>
       </c>
       <c r="D67" t="n">
-        <v>650.2260655901538</v>
+        <v>643.154250211399</v>
       </c>
       <c r="E67" t="n">
-        <v>658.9236450195312</v>
+        <v>647.0242919921875</v>
       </c>
       <c r="F67" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B68" t="n">
-        <v>653.956457912222</v>
+        <v>644.2215315163064</v>
       </c>
       <c r="C68" t="n">
-        <v>657.4574546517152</v>
+        <v>645.4383696113561</v>
       </c>
       <c r="D68" t="n">
-        <v>643.154250211399</v>
+        <v>634.0875860000896</v>
       </c>
       <c r="E68" t="n">
-        <v>647.0242919921875</v>
+        <v>644.4010620117188</v>
       </c>
       <c r="F68" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B69" t="n">
-        <v>644.2215315163064</v>
+        <v>643.7826886268982</v>
       </c>
       <c r="C69" t="n">
-        <v>645.4383696113561</v>
+        <v>653.2682792823022</v>
       </c>
       <c r="D69" t="n">
-        <v>634.0875860000896</v>
+        <v>641.1993122536916</v>
       </c>
       <c r="E69" t="n">
-        <v>644.4010620117188</v>
+        <v>651.3831176757812</v>
       </c>
       <c r="F69" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B70" t="n">
-        <v>643.7826886268982</v>
+        <v>650.8544758921091</v>
       </c>
       <c r="C70" t="n">
-        <v>653.2682792823022</v>
+        <v>652.2907198459545</v>
       </c>
       <c r="D70" t="n">
-        <v>641.1993122536916</v>
+        <v>639.5834431006995</v>
       </c>
       <c r="E70" t="n">
-        <v>651.3831176757812</v>
+        <v>640.321533203125</v>
       </c>
       <c r="F70" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B71" t="n">
-        <v>650.8544758921091</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="C71" t="n">
-        <v>652.2907198459545</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="D71" t="n">
-        <v>639.5834431006995</v>
+        <v>622.4974409136</v>
       </c>
       <c r="E71" t="n">
-        <v>640.321533203125</v>
+        <v>629.4695434570312</v>
       </c>
       <c r="F71" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B72" t="n">
-        <v>640.6208286715078</v>
+        <v>624.8912385916063</v>
       </c>
       <c r="C72" t="n">
-        <v>640.6208286715078</v>
+        <v>626.8362434492608</v>
       </c>
       <c r="D72" t="n">
-        <v>622.4974409136</v>
+        <v>613.241238448095</v>
       </c>
       <c r="E72" t="n">
-        <v>629.4695434570312</v>
+        <v>613.939453125</v>
       </c>
       <c r="F72" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B73" t="n">
-        <v>624.8913007155408</v>
+        <v>616.8918216697934</v>
       </c>
       <c r="C73" t="n">
-        <v>626.836305766559</v>
+        <v>622.5672130846042</v>
       </c>
       <c r="D73" t="n">
-        <v>613.2412994138377</v>
+        <v>612.6527349978052</v>
       </c>
       <c r="E73" t="n">
-        <v>613.9395141601562</v>
+        <v>619.2058715820312</v>
       </c>
       <c r="F73" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B74" t="n">
-        <v>616.8918824768537</v>
+        <v>622.5772500418334</v>
       </c>
       <c r="C74" t="n">
-        <v>622.567274451088</v>
+        <v>627.4646923832119</v>
       </c>
       <c r="D74" t="n">
-        <v>612.6527953870184</v>
+        <v>618.4878021974878</v>
       </c>
       <c r="E74" t="n">
-        <v>619.2059326171875</v>
+        <v>618.6573486328125</v>
       </c>
       <c r="F74" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B75" t="n">
-        <v>622.5772500418334</v>
+        <v>606.3190803349536</v>
       </c>
       <c r="C75" t="n">
-        <v>627.4646923832119</v>
+        <v>609.8300611005736</v>
       </c>
       <c r="D75" t="n">
-        <v>618.4878021974878</v>
+        <v>598.4593098618273</v>
       </c>
       <c r="E75" t="n">
-        <v>618.6573486328125</v>
+        <v>602.5687255859375</v>
       </c>
       <c r="F75" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B76" t="n">
-        <v>606.3191417499893</v>
+        <v>605.1819875834877</v>
       </c>
       <c r="C76" t="n">
-        <v>609.8301228712422</v>
+        <v>616.682409772708</v>
       </c>
       <c r="D76" t="n">
-        <v>598.4593704807342</v>
+        <v>598.5391160903739</v>
       </c>
       <c r="E76" t="n">
-        <v>602.5687866210938</v>
+        <v>611.3860473632812</v>
       </c>
       <c r="F76" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B77" t="n">
-        <v>605.1820479992876</v>
+        <v>627.7339506004921</v>
       </c>
       <c r="C77" t="n">
-        <v>616.6824713366042</v>
+        <v>658.8738165275513</v>
       </c>
       <c r="D77" t="n">
-        <v>598.5391758430108</v>
+        <v>624.9411525277235</v>
       </c>
       <c r="E77" t="n">
-        <v>611.3861083984375</v>
+        <v>645.967041015625</v>
       </c>
       <c r="F77" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B78" t="n">
-        <v>627.7339506004921</v>
+        <v>643.114354212172</v>
       </c>
       <c r="C78" t="n">
-        <v>658.8738165275513</v>
+        <v>664.7785515369834</v>
       </c>
       <c r="D78" t="n">
-        <v>624.9411525277235</v>
+        <v>642.7951686151001</v>
       </c>
       <c r="E78" t="n">
-        <v>645.967041015625</v>
+        <v>657.0684204101562</v>
       </c>
       <c r="F78" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B79" t="n">
-        <v>643.1144139511335</v>
+        <v>663.4220687284304</v>
       </c>
       <c r="C79" t="n">
-        <v>664.7786132883346</v>
+        <v>673.5460296758964</v>
       </c>
       <c r="D79" t="n">
-        <v>642.7952283244125</v>
+        <v>659.5919023824141</v>
       </c>
       <c r="E79" t="n">
-        <v>657.0684814453125</v>
+        <v>670.6334838867188</v>
       </c>
       <c r="F79" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B80" t="n">
-        <v>663.4220687284304</v>
+        <v>672.8578395915863</v>
       </c>
       <c r="C80" t="n">
-        <v>673.5460296758964</v>
+        <v>675.0820939991542</v>
       </c>
       <c r="D80" t="n">
-        <v>659.5919023824141</v>
+        <v>662.9532839044604</v>
       </c>
       <c r="E80" t="n">
-        <v>670.6334838867188</v>
+        <v>671.241943359375</v>
       </c>
       <c r="F80" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B81" t="n">
-        <v>672.8578395915863</v>
+        <v>672.7679591112906</v>
       </c>
       <c r="C81" t="n">
-        <v>675.0820939991542</v>
+        <v>675.9397859199995</v>
       </c>
       <c r="D81" t="n">
-        <v>662.9532839044604</v>
+        <v>664.3895050245095</v>
       </c>
       <c r="E81" t="n">
-        <v>671.241943359375</v>
+        <v>667.0127563476562</v>
       </c>
       <c r="F81" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B82" t="n">
-        <v>672.7679591112906</v>
+        <v>735.536439340887</v>
       </c>
       <c r="C82" t="n">
-        <v>675.9397859199995</v>
+        <v>742.0895763731422</v>
       </c>
       <c r="D82" t="n">
-        <v>664.3895050245095</v>
+        <v>710.7203206800697</v>
       </c>
       <c r="E82" t="n">
-        <v>667.0127563476562</v>
+        <v>736.4141845703125</v>
       </c>
       <c r="F82" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B83" t="n">
-        <v>735.536439340887</v>
+        <v>725.6319721911391</v>
       </c>
       <c r="C83" t="n">
-        <v>742.0895763731422</v>
+        <v>730.2899638188994</v>
       </c>
       <c r="D83" t="n">
-        <v>710.7203206800697</v>
+        <v>711.7577161829028</v>
       </c>
       <c r="E83" t="n">
-        <v>736.4141845703125</v>
+        <v>714.6602172851562</v>
       </c>
       <c r="F83" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B84" t="n">
-        <v>725.6319102189462</v>
+        <v>712.7650416713351</v>
       </c>
       <c r="C84" t="n">
-        <v>730.2899014488934</v>
+        <v>719.4478497361232</v>
       </c>
       <c r="D84" t="n">
-        <v>711.7576553956329</v>
+        <v>701.7135364812315</v>
       </c>
       <c r="E84" t="n">
-        <v>714.66015625</v>
+        <v>704.5960693359375</v>
       </c>
       <c r="F84" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B85" t="n">
-        <v>712.7649799285471</v>
+        <v>705.5536352374374</v>
       </c>
       <c r="C85" t="n">
-        <v>719.4477874144414</v>
+        <v>715.1589125312489</v>
       </c>
       <c r="D85" t="n">
-        <v>701.7134756957726</v>
+        <v>684.6474336745422</v>
       </c>
       <c r="E85" t="n">
-        <v>704.5960083007812</v>
+        <v>689.9238891601562</v>
       </c>
       <c r="F85" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B86" t="n">
-        <v>705.5535728195721</v>
+        <v>685.964025393825</v>
       </c>
       <c r="C86" t="n">
-        <v>715.1588492636382</v>
+        <v>687.0612373376343</v>
       </c>
       <c r="D86" t="n">
-        <v>684.6473731061755</v>
+        <v>665.7461161570209</v>
       </c>
       <c r="E86" t="n">
-        <v>689.923828125</v>
+        <v>667.2721557617188</v>
       </c>
       <c r="F86" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B87" t="n">
-        <v>685.9640881387202</v>
+        <v>661.8760941724082</v>
       </c>
       <c r="C87" t="n">
-        <v>687.0613001828912</v>
+        <v>679.7500626324993</v>
       </c>
       <c r="D87" t="n">
-        <v>665.7461770525908</v>
+        <v>651.8219602792932</v>
       </c>
       <c r="E87" t="n">
-        <v>667.272216796875</v>
+        <v>668.4890747070312</v>
       </c>
       <c r="F87" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B88" t="n">
-        <v>661.8760941724082</v>
+        <v>663.7811558190369</v>
       </c>
       <c r="C88" t="n">
-        <v>679.7500626324993</v>
+        <v>670.2644652243433</v>
       </c>
       <c r="D88" t="n">
-        <v>651.8219602792932</v>
+        <v>644.8399277739295</v>
       </c>
       <c r="E88" t="n">
-        <v>668.4890747070312</v>
+        <v>659.7615356445312</v>
       </c>
       <c r="F88" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B89" t="n">
-        <v>663.7811558190369</v>
+        <v>661.4770916291903</v>
       </c>
       <c r="C89" t="n">
-        <v>670.2644652243433</v>
+        <v>681.5554070660584</v>
       </c>
       <c r="D89" t="n">
-        <v>644.8399277739295</v>
+        <v>657.0884263930592</v>
       </c>
       <c r="E89" t="n">
-        <v>659.7615356445312</v>
+        <v>675.4810180664062</v>
       </c>
       <c r="F89" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B90" t="n">
-        <v>661.4770916291903</v>
+        <v>675.8600189134125</v>
       </c>
       <c r="C90" t="n">
-        <v>681.5554070660584</v>
+        <v>678.9022357565889</v>
       </c>
       <c r="D90" t="n">
-        <v>657.0884263930592</v>
+        <v>668.0700760446862</v>
       </c>
       <c r="E90" t="n">
-        <v>675.4810180664062</v>
+        <v>668.9976806640625</v>
       </c>
       <c r="F90" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B91" t="n">
-        <v>675.8600189134125</v>
+        <v>672.2693241407737</v>
       </c>
       <c r="C91" t="n">
-        <v>678.9022357565889</v>
+        <v>677.5258114827353</v>
       </c>
       <c r="D91" t="n">
-        <v>668.0700760446862</v>
+        <v>655.4126950742984</v>
       </c>
       <c r="E91" t="n">
-        <v>668.9976806640625</v>
+        <v>666.9729614257812</v>
       </c>
       <c r="F91" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B92" t="n">
-        <v>672.2693241407737</v>
+        <v>668.2496878446467</v>
       </c>
       <c r="C92" t="n">
-        <v>677.5258114827353</v>
+        <v>674.2642338266133</v>
       </c>
       <c r="D92" t="n">
-        <v>655.4126950742984</v>
+        <v>643.6231428364971</v>
       </c>
       <c r="E92" t="n">
-        <v>666.9729614257812</v>
+        <v>648.1414794921875</v>
       </c>
       <c r="F92" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B93" t="n">
-        <v>668.2496249159107</v>
+        <v>643.4434668857905</v>
       </c>
       <c r="C93" t="n">
-        <v>674.2641703314905</v>
+        <v>649.7572295518577</v>
       </c>
       <c r="D93" t="n">
-        <v>643.6230822268304</v>
+        <v>632.9405378190771</v>
       </c>
       <c r="E93" t="n">
-        <v>648.1414184570312</v>
+        <v>638.127197265625</v>
       </c>
       <c r="F93" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B94" t="n">
-        <v>643.4434668857905</v>
+        <v>637.8578591323172</v>
       </c>
       <c r="C94" t="n">
-        <v>649.7572295518577</v>
+        <v>640.9498744421038</v>
       </c>
       <c r="D94" t="n">
-        <v>632.9405378190771</v>
+        <v>627.1853229648948</v>
       </c>
       <c r="E94" t="n">
-        <v>638.127197265625</v>
+        <v>637.6483764648438</v>
       </c>
       <c r="F94" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B95" t="n">
-        <v>637.8579201875249</v>
+        <v>632.1725643806327</v>
       </c>
       <c r="C95" t="n">
-        <v>640.9499357932766</v>
+        <v>643.3438180480059</v>
       </c>
       <c r="D95" t="n">
-        <v>627.1853829985365</v>
+        <v>626.5371085480483</v>
       </c>
       <c r="E95" t="n">
-        <v>637.6484375</v>
+        <v>641.568359375</v>
       </c>
       <c r="F95" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B96" t="n">
-        <v>632.1725042393389</v>
+        <v>636.9303135148713</v>
       </c>
       <c r="C96" t="n">
-        <v>643.3437568439427</v>
+        <v>645.5281745630167</v>
       </c>
       <c r="D96" t="n">
-        <v>626.5370489428796</v>
+        <v>635.085027341747</v>
       </c>
       <c r="E96" t="n">
-        <v>641.5682983398438</v>
+        <v>643.1243896484375</v>
       </c>
       <c r="F96" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B97" t="n">
-        <v>636.9302530675583</v>
+        <v>638.0474161403351</v>
       </c>
       <c r="C97" t="n">
-        <v>645.5281132997313</v>
+        <v>661.6466355641227</v>
       </c>
       <c r="D97" t="n">
-        <v>635.0849670695593</v>
+        <v>637.1397796110642</v>
       </c>
       <c r="E97" t="n">
-        <v>643.1243286132812</v>
+        <v>653.9763793945312</v>
       </c>
       <c r="F97" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B98" t="n">
-        <v>638.0474756888525</v>
+        <v>650.8644258547187</v>
       </c>
       <c r="C98" t="n">
-        <v>661.6466973151385</v>
+        <v>656.0112104148094</v>
       </c>
       <c r="D98" t="n">
-        <v>637.1398390748724</v>
+        <v>634.3669181695027</v>
       </c>
       <c r="E98" t="n">
-        <v>653.9764404296875</v>
+        <v>635.6137084960938</v>
       </c>
       <c r="F98" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B99" t="n">
-        <v>650.8644258547187</v>
+        <v>631.4543872367445</v>
       </c>
       <c r="C99" t="n">
-        <v>656.0112104148094</v>
+        <v>639.4637360573605</v>
       </c>
       <c r="D99" t="n">
-        <v>634.3669181695027</v>
+        <v>627.364878734925</v>
       </c>
       <c r="E99" t="n">
-        <v>635.6137084960938</v>
+        <v>637.6583862304688</v>
       </c>
       <c r="F99" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B100" t="n">
-        <v>631.4544476780686</v>
+        <v>640.8801577475739</v>
       </c>
       <c r="C100" t="n">
-        <v>639.4637972653206</v>
+        <v>652.2009891675571</v>
       </c>
       <c r="D100" t="n">
-        <v>627.364938784811</v>
+        <v>640.4911445683953</v>
       </c>
       <c r="E100" t="n">
-        <v>637.658447265625</v>
+        <v>652.011474609375</v>
       </c>
       <c r="F100" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B101" t="n">
-        <v>640.8800977544264</v>
+        <v>648.8795635426123</v>
       </c>
       <c r="C101" t="n">
-        <v>652.2009281146602</v>
+        <v>659.3027431401059</v>
       </c>
       <c r="D101" t="n">
-        <v>640.4910846116635</v>
+        <v>645.8374072363367</v>
       </c>
       <c r="E101" t="n">
-        <v>652.0114135742188</v>
+        <v>655.322998046875</v>
       </c>
       <c r="F101" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B102" t="n">
-        <v>648.8795635426123</v>
+        <v>641.7977899641362</v>
       </c>
       <c r="C102" t="n">
-        <v>659.3027431401059</v>
+        <v>647.7723993687464</v>
       </c>
       <c r="D102" t="n">
-        <v>645.8374072363367</v>
+        <v>636.4814590544522</v>
       </c>
       <c r="E102" t="n">
-        <v>655.322998046875</v>
+        <v>646.515625</v>
       </c>
       <c r="F102" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B103" t="n">
-        <v>641.7977293743734</v>
+        <v>635.5238627543893</v>
       </c>
       <c r="C103" t="n">
-        <v>647.7723382149427</v>
+        <v>658.2453970983619</v>
       </c>
       <c r="D103" t="n">
-        <v>636.4813989665846</v>
+        <v>632.870719934867</v>
       </c>
       <c r="E103" t="n">
-        <v>646.5155639648438</v>
+        <v>651.8817749023438</v>
       </c>
       <c r="F103" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B104" t="n">
-        <v>635.5238627543893</v>
+        <v>646.6253451355694</v>
       </c>
       <c r="C104" t="n">
-        <v>658.2453970983619</v>
+        <v>657.3477420502325</v>
       </c>
       <c r="D104" t="n">
-        <v>632.870719934867</v>
+        <v>637.1996588761248</v>
       </c>
       <c r="E104" t="n">
-        <v>651.8817749023438</v>
+        <v>653.39794921875</v>
       </c>
       <c r="F104" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B105" t="n">
-        <v>646.6252847330551</v>
+        <v>656.2705097002453</v>
       </c>
       <c r="C105" t="n">
-        <v>657.3476806461185</v>
+        <v>671.0424780902056</v>
       </c>
       <c r="D105" t="n">
-        <v>637.199599354082</v>
+        <v>655.9812154011644</v>
       </c>
       <c r="E105" t="n">
-        <v>653.3978881835938</v>
+        <v>666.015380859375</v>
       </c>
       <c r="F105" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B106" t="n">
-        <v>656.2705097002453</v>
+        <v>660.2303336051802</v>
       </c>
       <c r="C106" t="n">
-        <v>671.0424780902056</v>
+        <v>668.9778340733714</v>
       </c>
       <c r="D106" t="n">
-        <v>655.9812154011644</v>
+        <v>648.6401755256248</v>
       </c>
       <c r="E106" t="n">
-        <v>666.015380859375</v>
+        <v>658.8738403320312</v>
       </c>
       <c r="F106" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B107" t="n">
-        <v>660.2303336051802</v>
+        <v>646.2363956775138</v>
       </c>
       <c r="C107" t="n">
-        <v>668.9778340733714</v>
+        <v>647.8023107770981</v>
       </c>
       <c r="D107" t="n">
-        <v>648.6401755256248</v>
+        <v>634.4766301866302</v>
       </c>
       <c r="E107" t="n">
-        <v>658.8738403320312</v>
+        <v>643.2041625976562</v>
       </c>
       <c r="F107" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B108" t="n">
-        <v>646.2363343546218</v>
+        <v>633.1500554179556</v>
       </c>
       <c r="C108" t="n">
-        <v>647.8022493056128</v>
+        <v>646.0867221220876</v>
       </c>
       <c r="D108" t="n">
-        <v>634.4765699796501</v>
+        <v>625.1705976379839</v>
       </c>
       <c r="E108" t="n">
-        <v>643.2041015625</v>
+        <v>645.7276611328125</v>
       </c>
       <c r="F108" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B109" t="n">
-        <v>633.1500554179556</v>
+        <v>651.881802754218</v>
       </c>
       <c r="C109" t="n">
-        <v>646.0867221220876</v>
+        <v>658.6044862124207</v>
       </c>
       <c r="D109" t="n">
-        <v>625.1705976379839</v>
+        <v>647.3335142418318</v>
       </c>
       <c r="E109" t="n">
-        <v>645.7276611328125</v>
+        <v>652.3905029296875</v>
       </c>
       <c r="F109" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B110" t="n">
-        <v>651.8818637417822</v>
+        <v>653.0787479235273</v>
       </c>
       <c r="C110" t="n">
-        <v>658.6045478289335</v>
+        <v>657.4275379105374</v>
       </c>
       <c r="D110" t="n">
-        <v>647.3335748038755</v>
+        <v>646.6951571900124</v>
       </c>
       <c r="E110" t="n">
-        <v>652.3905639648438</v>
+        <v>653.178466796875</v>
       </c>
       <c r="F110" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B111" t="n">
-        <v>653.0787479235273</v>
+        <v>647.0841872338415</v>
       </c>
       <c r="C111" t="n">
-        <v>657.4275379105374</v>
+        <v>651.8219905315074</v>
       </c>
       <c r="D111" t="n">
-        <v>646.6951571900124</v>
+        <v>635.2646391478804</v>
       </c>
       <c r="E111" t="n">
-        <v>653.178466796875</v>
+        <v>636.5413208007812</v>
       </c>
       <c r="F111" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B112" t="n">
-        <v>647.0841872338415</v>
+        <v>622.2880080608647</v>
       </c>
       <c r="C112" t="n">
-        <v>651.8219905315074</v>
+        <v>627.55441857404</v>
       </c>
       <c r="D112" t="n">
-        <v>635.2646391478804</v>
+        <v>607.9848031082139</v>
       </c>
       <c r="E112" t="n">
-        <v>636.5413208007812</v>
+        <v>612.1341552734375</v>
       </c>
       <c r="F112" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,25 +3355,25 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B113" t="n">
-        <v>622.2879460132801</v>
+        <v>630.9168848948667</v>
       </c>
       <c r="C113" t="n">
-        <v>627.554356001348</v>
+        <v>633.6621719731276</v>
       </c>
       <c r="D113" t="n">
-        <v>607.9847424867846</v>
+        <v>622.0321132511823</v>
       </c>
       <c r="E113" t="n">
-        <v>612.1340942382812</v>
+        <v>626.3746948242188</v>
       </c>
       <c r="F113" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B114" t="n">
-        <v>630.9168848948667</v>
+        <v>626.9137167736849</v>
       </c>
       <c r="C114" t="n">
-        <v>633.6621719731276</v>
+        <v>635.4590438783874</v>
       </c>
       <c r="D114" t="n">
-        <v>622.0321132511823</v>
+        <v>620.6345187532272</v>
       </c>
       <c r="E114" t="n">
-        <v>626.3746948242188</v>
+        <v>621.5928344726562</v>
       </c>
       <c r="F114" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G114" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B115" t="n">
-        <v>626.9137783313067</v>
+        <v>615.2837198825454</v>
       </c>
       <c r="C115" t="n">
-        <v>635.4591062750881</v>
+        <v>621.5829031274002</v>
       </c>
       <c r="D115" t="n">
-        <v>620.634579694285</v>
+        <v>613.5566433895493</v>
       </c>
       <c r="E115" t="n">
-        <v>621.5928955078125</v>
+        <v>614.6248168945312</v>
       </c>
       <c r="F115" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B116" t="n">
-        <v>615.2837809831337</v>
+        <v>611.1008889698486</v>
       </c>
       <c r="C116" t="n">
-        <v>621.5829648535273</v>
+        <v>611.9494078221777</v>
       </c>
       <c r="D116" t="n">
-        <v>613.5567043186309</v>
+        <v>601.2278243573462</v>
       </c>
       <c r="E116" t="n">
-        <v>614.6248779296875</v>
+        <v>605.6602172851562</v>
       </c>
       <c r="F116" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B117" t="n">
-        <v>611.1009505532863</v>
+        <v>602.4957192983555</v>
       </c>
       <c r="C117" t="n">
-        <v>611.9494694911245</v>
+        <v>602.9249750667714</v>
       </c>
       <c r="D117" t="n">
-        <v>601.2278849458298</v>
+        <v>586.2435901825164</v>
       </c>
       <c r="E117" t="n">
-        <v>605.6602783203125</v>
+        <v>592.642578125</v>
       </c>
       <c r="F117" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B118" t="n">
-        <v>602.4957192983555</v>
+        <v>604.7517959610541</v>
       </c>
       <c r="C118" t="n">
-        <v>602.9249750667714</v>
+        <v>607.5969482872343</v>
       </c>
       <c r="D118" t="n">
-        <v>586.2435901825164</v>
+        <v>597.9834469761715</v>
       </c>
       <c r="E118" t="n">
-        <v>592.642578125</v>
+        <v>603.0247802734375</v>
       </c>
       <c r="F118" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B119" t="n">
-        <v>604.7517959610541</v>
+        <v>598.0732713770465</v>
       </c>
       <c r="C119" t="n">
-        <v>607.5969482872343</v>
+        <v>599.9700396349708</v>
       </c>
       <c r="D119" t="n">
-        <v>597.9834469761715</v>
+        <v>589.9871770786485</v>
       </c>
       <c r="E119" t="n">
-        <v>603.0247802734375</v>
+        <v>591.9038696289062</v>
       </c>
       <c r="F119" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B120" t="n">
-        <v>598.0732713770465</v>
+        <v>597.7138608396341</v>
       </c>
       <c r="C120" t="n">
-        <v>599.9700396349708</v>
+        <v>602.6354044215132</v>
       </c>
       <c r="D120" t="n">
-        <v>589.9871770786485</v>
+        <v>592.3830467312241</v>
       </c>
       <c r="E120" t="n">
-        <v>591.9038696289062</v>
+        <v>593.8704833984375</v>
       </c>
       <c r="F120" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B121" t="n">
-        <v>597.7138608396341</v>
+        <v>581.4917396573854</v>
       </c>
       <c r="C121" t="n">
-        <v>602.6354044215132</v>
+        <v>582.0008753864581</v>
       </c>
       <c r="D121" t="n">
-        <v>592.3830467312241</v>
+        <v>542.4188017705425</v>
       </c>
       <c r="E121" t="n">
-        <v>593.8704833984375</v>
+        <v>546.6016235351562</v>
       </c>
       <c r="F121" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B122" t="n">
-        <v>581.4916747262954</v>
+        <v>539.1743922574078</v>
       </c>
       <c r="C122" t="n">
-        <v>582.0008103985165</v>
+        <v>542.6683942166816</v>
       </c>
       <c r="D122" t="n">
-        <v>542.4187412024525</v>
+        <v>519.3684267008094</v>
       </c>
       <c r="E122" t="n">
-        <v>546.6015625</v>
+        <v>524.8190307617188</v>
       </c>
       <c r="F122" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B123" t="n">
-        <v>539.1743295527585</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="C123" t="n">
-        <v>542.6683311056884</v>
+        <v>538.6253045735799</v>
       </c>
       <c r="D123" t="n">
-        <v>519.368366299545</v>
+        <v>527.6341638126921</v>
       </c>
       <c r="E123" t="n">
-        <v>524.8189697265625</v>
+        <v>535.4607543945312</v>
       </c>
       <c r="F123" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>535.4607543945312</v>
+        <v>549.0374119135495</v>
       </c>
       <c r="C124" t="n">
-        <v>538.6253045735799</v>
+        <v>572.7067990959439</v>
       </c>
       <c r="D124" t="n">
-        <v>527.6341638126921</v>
+        <v>545.8329522821889</v>
       </c>
       <c r="E124" t="n">
-        <v>535.4607543945312</v>
+        <v>571.1494750976562</v>
       </c>
       <c r="F124" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B125" t="n">
-        <v>549.0374119135495</v>
+        <v>579.135725523027</v>
       </c>
       <c r="C125" t="n">
-        <v>572.7067990959439</v>
+        <v>591.5344219412718</v>
       </c>
       <c r="D125" t="n">
-        <v>545.8329522821889</v>
+        <v>572.8365426099092</v>
       </c>
       <c r="E125" t="n">
-        <v>571.1494750976562</v>
+        <v>578.2372436523438</v>
       </c>
       <c r="F125" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B126" t="n">
-        <v>579.1357866530213</v>
+        <v>565.0699110449033</v>
       </c>
       <c r="C126" t="n">
-        <v>591.5344843799961</v>
+        <v>577.5085793033603</v>
       </c>
       <c r="D126" t="n">
-        <v>572.8366030750008</v>
+        <v>558.7408105198895</v>
       </c>
       <c r="E126" t="n">
-        <v>578.2373046875</v>
+        <v>573.4755249023438</v>
       </c>
       <c r="F126" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B127" t="n">
-        <v>565.0699110449033</v>
+        <v>576.7000047794845</v>
       </c>
       <c r="C127" t="n">
-        <v>577.5085793033603</v>
+        <v>581.7912404462878</v>
       </c>
       <c r="D127" t="n">
-        <v>558.7408105198895</v>
+        <v>571.0197533967594</v>
       </c>
       <c r="E127" t="n">
-        <v>573.4755249023438</v>
+        <v>572.0380249023438</v>
       </c>
       <c r="F127" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B128" t="n">
-        <v>576.6999432469056</v>
+        <v>571.4988503418972</v>
       </c>
       <c r="C128" t="n">
-        <v>581.7911783704857</v>
+        <v>574.2441373249518</v>
       </c>
       <c r="D128" t="n">
-        <v>571.0196924702504</v>
+        <v>563.7921103124964</v>
       </c>
       <c r="E128" t="n">
-        <v>572.0379638671875</v>
+        <v>574.064453125</v>
       </c>
       <c r="F128" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B129" t="n">
-        <v>571.4988503418972</v>
+        <v>604.9614419693103</v>
       </c>
       <c r="C129" t="n">
-        <v>574.2441373249518</v>
+        <v>628.8704088339113</v>
       </c>
       <c r="D129" t="n">
-        <v>563.7921103124964</v>
+        <v>590.8157434643455</v>
       </c>
       <c r="E129" t="n">
-        <v>574.064453125</v>
+        <v>611.3704223632812</v>
       </c>
       <c r="F129" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B130" t="n">
-        <v>604.9614419693103</v>
+        <v>625.8954391113879</v>
       </c>
       <c r="C130" t="n">
-        <v>628.8704088339113</v>
+        <v>636.4074215325429</v>
       </c>
       <c r="D130" t="n">
-        <v>590.8157434643455</v>
+        <v>621.9322723369008</v>
       </c>
       <c r="E130" t="n">
-        <v>611.3704223632812</v>
+        <v>627.3130493164062</v>
       </c>
       <c r="F130" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B131" t="n">
-        <v>625.8955000086161</v>
+        <v>633.3826022362973</v>
       </c>
       <c r="C131" t="n">
-        <v>636.4074834525468</v>
+        <v>637.4856047359222</v>
       </c>
       <c r="D131" t="n">
-        <v>621.9323328485281</v>
+        <v>623.2600266965629</v>
       </c>
       <c r="E131" t="n">
-        <v>627.3131103515625</v>
+        <v>628.780517578125</v>
       </c>
       <c r="F131" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B132" t="n">
-        <v>633.3826022362973</v>
+        <v>628.4211571313969</v>
       </c>
       <c r="C132" t="n">
-        <v>637.4856047359222</v>
+        <v>633.911731180996</v>
       </c>
       <c r="D132" t="n">
-        <v>623.2600266965629</v>
+        <v>623.3299219303536</v>
       </c>
       <c r="E132" t="n">
-        <v>628.780517578125</v>
+        <v>633.4425659179688</v>
       </c>
       <c r="F132" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B133" t="n">
-        <v>628.4212176827168</v>
+        <v>642.117619704398</v>
       </c>
       <c r="C133" t="n">
-        <v>633.9117922613585</v>
+        <v>665.1181727259973</v>
       </c>
       <c r="D133" t="n">
-        <v>623.3299819911093</v>
+        <v>638.2742422102883</v>
       </c>
       <c r="E133" t="n">
-        <v>633.442626953125</v>
+        <v>661.3546142578125</v>
       </c>
       <c r="F133" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B134" t="n">
-        <v>642.117619704398</v>
+        <v>665.856909197143</v>
       </c>
       <c r="C134" t="n">
-        <v>665.1181727259973</v>
+        <v>677.3372007350248</v>
       </c>
       <c r="D134" t="n">
-        <v>638.2742422102883</v>
+        <v>663.081644256971</v>
       </c>
       <c r="E134" t="n">
-        <v>661.3546142578125</v>
+        <v>670.4290771484375</v>
       </c>
       <c r="F134" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B135" t="n">
-        <v>665.856909197143</v>
+        <v>674.831464225754</v>
       </c>
       <c r="C135" t="n">
-        <v>677.3372007350248</v>
+        <v>676.4187660594131</v>
       </c>
       <c r="D135" t="n">
-        <v>663.081644256971</v>
+        <v>666.605595861725</v>
       </c>
       <c r="E135" t="n">
-        <v>670.4290771484375</v>
+        <v>675.7099609375</v>
       </c>
       <c r="F135" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B136" t="n">
-        <v>674.831464225754</v>
+        <v>677.4369744478516</v>
       </c>
       <c r="C136" t="n">
-        <v>676.4187660594131</v>
+        <v>690.3348757077041</v>
       </c>
       <c r="D136" t="n">
-        <v>666.605595861725</v>
+        <v>673.9729506648888</v>
       </c>
       <c r="E136" t="n">
-        <v>675.7099609375</v>
+        <v>687.3699340820312</v>
       </c>
       <c r="F136" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B137" t="n">
-        <v>677.4369744478516</v>
+        <v>680.192296240317</v>
       </c>
       <c r="C137" t="n">
-        <v>690.3348757077041</v>
+        <v>682.2088539380842</v>
       </c>
       <c r="D137" t="n">
-        <v>673.9729506648888</v>
+        <v>666.8552067290691</v>
       </c>
       <c r="E137" t="n">
-        <v>687.3699340820312</v>
+        <v>669.7601928710938</v>
       </c>
       <c r="F137" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B138" t="n">
-        <v>680.192296240317</v>
+        <v>669.8500580611455</v>
       </c>
       <c r="C138" t="n">
-        <v>682.2088539380842</v>
+        <v>675.0411586256739</v>
       </c>
       <c r="D138" t="n">
-        <v>666.8552067290691</v>
+        <v>666.1863646700106</v>
       </c>
       <c r="E138" t="n">
-        <v>669.7601928710938</v>
+        <v>667.6937866210938</v>
       </c>
       <c r="F138" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B139" t="n">
-        <v>669.8500580611455</v>
+        <v>673.2042912464699</v>
       </c>
       <c r="C139" t="n">
-        <v>675.0411586256739</v>
+        <v>677.2174214115423</v>
       </c>
       <c r="D139" t="n">
-        <v>666.1863646700106</v>
+        <v>668.6022063234784</v>
       </c>
       <c r="E139" t="n">
-        <v>667.6937866210938</v>
+        <v>673.5636596679688</v>
       </c>
       <c r="F139" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B140" t="n">
-        <v>673.2042912464699</v>
+        <v>662.562575853328</v>
       </c>
       <c r="C140" t="n">
-        <v>677.2174214115423</v>
+        <v>668.4125184743669</v>
       </c>
       <c r="D140" t="n">
-        <v>668.6022063234784</v>
+        <v>651.9308032468797</v>
       </c>
       <c r="E140" t="n">
-        <v>673.5636596679688</v>
+        <v>658.0203857421875</v>
       </c>
       <c r="F140" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B141" t="n">
-        <v>662.562575853328</v>
+        <v>659.1883568751083</v>
       </c>
       <c r="C141" t="n">
-        <v>668.4125184743669</v>
+        <v>679.5034568571632</v>
       </c>
       <c r="D141" t="n">
-        <v>651.9308032468797</v>
+        <v>652.719481738207</v>
       </c>
       <c r="E141" t="n">
-        <v>658.0203857421875</v>
+        <v>673.8731689453125</v>
       </c>
       <c r="F141" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B142" t="n">
-        <v>659.1883568751083</v>
+        <v>669.8500343121515</v>
       </c>
       <c r="C142" t="n">
-        <v>679.5034568571632</v>
+        <v>681.330325511242</v>
       </c>
       <c r="D142" t="n">
-        <v>652.719481738207</v>
+        <v>669.6903353309991</v>
       </c>
       <c r="E142" t="n">
-        <v>673.8731689453125</v>
+        <v>677.4569702148438</v>
       </c>
       <c r="F142" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B143" t="n">
-        <v>669.8500343121515</v>
+        <v>673.0844464119266</v>
       </c>
       <c r="C143" t="n">
-        <v>681.330325511242</v>
+        <v>677.0176962940845</v>
       </c>
       <c r="D143" t="n">
-        <v>669.6903353309991</v>
+        <v>664.489217253305</v>
       </c>
       <c r="E143" t="n">
-        <v>677.4569702148438</v>
+        <v>670.189453125</v>
       </c>
       <c r="F143" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B144" t="n">
-        <v>673.0844464119266</v>
+        <v>667.7636045616339</v>
       </c>
       <c r="C144" t="n">
-        <v>677.0176962940845</v>
+        <v>673.0944797535534</v>
       </c>
       <c r="D144" t="n">
-        <v>664.489217253305</v>
+        <v>662.6723692427279</v>
       </c>
       <c r="E144" t="n">
-        <v>670.189453125</v>
+        <v>667.9732666015625</v>
       </c>
       <c r="F144" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B145" t="n">
-        <v>667.7636045616339</v>
+        <v>618.2586017744245</v>
       </c>
       <c r="C145" t="n">
-        <v>673.0944797535534</v>
+        <v>619.7859479396749</v>
       </c>
       <c r="D145" t="n">
-        <v>662.6723692427279</v>
+        <v>598.9717055442339</v>
       </c>
       <c r="E145" t="n">
-        <v>667.9732666015625</v>
+        <v>610.8612670898438</v>
       </c>
       <c r="F145" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B146" t="n">
-        <v>618.2586017744245</v>
+        <v>613.6365485572411</v>
       </c>
       <c r="C146" t="n">
-        <v>619.7859479396749</v>
+        <v>617.8193701850194</v>
       </c>
       <c r="D146" t="n">
-        <v>598.9717055442339</v>
+        <v>605.0712358749745</v>
       </c>
       <c r="E146" t="n">
-        <v>610.8612670898438</v>
+        <v>607.7067260742188</v>
       </c>
       <c r="F146" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B147" t="n">
-        <v>613.6365485572411</v>
+        <v>606.8981537761392</v>
       </c>
       <c r="C147" t="n">
-        <v>617.8193701850194</v>
+        <v>612.9477660987843</v>
       </c>
       <c r="D147" t="n">
-        <v>605.0712358749745</v>
+        <v>601.7170456287333</v>
       </c>
       <c r="E147" t="n">
-        <v>607.7067260742188</v>
+        <v>609.3638916015625</v>
       </c>
       <c r="F147" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="n">
-        <v>606.8981537761392</v>
+        <v>612.2588828439087</v>
       </c>
       <c r="C148" t="n">
-        <v>612.9477660987843</v>
+        <v>613.2970785161436</v>
       </c>
       <c r="D148" t="n">
-        <v>601.7170456287333</v>
+        <v>599.3310648754198</v>
       </c>
       <c r="E148" t="n">
-        <v>609.3638916015625</v>
+        <v>603.9232177734375</v>
       </c>
       <c r="F148" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B149" t="n">
-        <v>612.2588828439087</v>
+        <v>600.0199080772063</v>
       </c>
       <c r="C149" t="n">
-        <v>613.2970785161436</v>
+        <v>618.8875416216711</v>
       </c>
       <c r="D149" t="n">
-        <v>599.3310648754198</v>
+        <v>597.0749516023062</v>
       </c>
       <c r="E149" t="n">
-        <v>603.9232177734375</v>
+        <v>611.8296508789062</v>
       </c>
       <c r="F149" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="n">
-        <v>600.0199080772063</v>
+        <v>613.6664846485507</v>
       </c>
       <c r="C150" t="n">
-        <v>618.8875416216711</v>
+        <v>623.9089111604618</v>
       </c>
       <c r="D150" t="n">
-        <v>597.0749516023062</v>
+        <v>612.4885142038465</v>
       </c>
       <c r="E150" t="n">
-        <v>611.8296508789062</v>
+        <v>615.7529296875</v>
       </c>
       <c r="F150" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B151" t="n">
-        <v>613.6664238202088</v>
+        <v>614.145727971313</v>
       </c>
       <c r="C151" t="n">
-        <v>623.9088493168618</v>
+        <v>615.7130447332122</v>
       </c>
       <c r="D151" t="n">
-        <v>612.4884534922683</v>
+        <v>605.0213768033159</v>
       </c>
       <c r="E151" t="n">
-        <v>615.7528686523438</v>
+        <v>608.5852661132812</v>
       </c>
       <c r="F151" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B152" t="n">
-        <v>614.1456663784968</v>
+        <v>603.533915527778</v>
       </c>
       <c r="C152" t="n">
-        <v>615.7129829832094</v>
+        <v>603.8732987260729</v>
       </c>
       <c r="D152" t="n">
-        <v>605.0213161255829</v>
+        <v>597.0550476209405</v>
       </c>
       <c r="E152" t="n">
-        <v>608.585205078125</v>
+        <v>597.8336791992188</v>
       </c>
       <c r="F152" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B153" t="n">
-        <v>603.533915527778</v>
+        <v>593.8005792809215</v>
       </c>
       <c r="C153" t="n">
-        <v>603.8732987260729</v>
+        <v>602.7152673522038</v>
       </c>
       <c r="D153" t="n">
-        <v>597.0550476209405</v>
+        <v>591.5843523282613</v>
       </c>
       <c r="E153" t="n">
-        <v>597.8336791992188</v>
+        <v>601.966552734375</v>
       </c>
       <c r="F153" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B154" t="n">
-        <v>593.8006394881057</v>
+        <v>597.8037594995824</v>
       </c>
       <c r="C154" t="n">
-        <v>602.7153284632744</v>
+        <v>618.837657653709</v>
       </c>
       <c r="D154" t="n">
-        <v>591.5844123107358</v>
+        <v>595.6374345129168</v>
       </c>
       <c r="E154" t="n">
-        <v>601.9666137695312</v>
+        <v>615.5732421875</v>
       </c>
       <c r="F154" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B155" t="n">
-        <v>597.8037594995824</v>
+        <v>614.944289073115</v>
       </c>
       <c r="C155" t="n">
-        <v>618.837657653709</v>
+        <v>622.6610217742586</v>
       </c>
       <c r="D155" t="n">
-        <v>595.6374345129168</v>
+        <v>613.9460028895547</v>
       </c>
       <c r="E155" t="n">
-        <v>615.5732421875</v>
+        <v>617.3701171875</v>
       </c>
       <c r="F155" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B156" t="n">
-        <v>614.944289073115</v>
+        <v>612.9377281921389</v>
       </c>
       <c r="C156" t="n">
-        <v>622.6610217742586</v>
+        <v>620.1353935587166</v>
       </c>
       <c r="D156" t="n">
-        <v>613.9460028895547</v>
+        <v>608.2657561335159</v>
       </c>
       <c r="E156" t="n">
-        <v>617.3701171875</v>
+        <v>613.1773071289062</v>
       </c>
       <c r="F156" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B157" t="n">
-        <v>612.9377892034477</v>
+        <v>608.0660990208263</v>
       </c>
       <c r="C157" t="n">
-        <v>620.135455286475</v>
+        <v>614.5350350972873</v>
       </c>
       <c r="D157" t="n">
-        <v>608.2658166797805</v>
+        <v>602.6554048207697</v>
       </c>
       <c r="E157" t="n">
-        <v>613.1773681640625</v>
+        <v>610.1625366210938</v>
       </c>
       <c r="F157" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B158" t="n">
-        <v>608.0660990208263</v>
+        <v>607.8763927177921</v>
       </c>
       <c r="C158" t="n">
-        <v>614.5350350972873</v>
+        <v>612.8778161384099</v>
       </c>
       <c r="D158" t="n">
-        <v>602.6554048207697</v>
+        <v>599.5207424161133</v>
       </c>
       <c r="E158" t="n">
-        <v>610.1625366210938</v>
+        <v>601.5772094726562</v>
       </c>
       <c r="F158" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B159" t="n">
-        <v>607.8764543920544</v>
+        <v>599.7304526335664</v>
       </c>
       <c r="C159" t="n">
-        <v>612.8778783201094</v>
+        <v>606.9580352784536</v>
       </c>
       <c r="D159" t="n">
-        <v>599.5208032426234</v>
+        <v>596.7854960328639</v>
       </c>
       <c r="E159" t="n">
-        <v>601.5772705078125</v>
+        <v>604.0230712890625</v>
       </c>
       <c r="F159" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B160" t="n">
-        <v>599.7304526335664</v>
+        <v>598.9717538809448</v>
       </c>
       <c r="C160" t="n">
-        <v>606.9580352784536</v>
+        <v>608.5552775708169</v>
       </c>
       <c r="D160" t="n">
-        <v>596.7854960328639</v>
+        <v>593.7906457726523</v>
       </c>
       <c r="E160" t="n">
-        <v>604.0230712890625</v>
+        <v>606.339111328125</v>
       </c>
       <c r="F160" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B161" t="n">
-        <v>598.9716935873996</v>
+        <v>606.8381854335279</v>
       </c>
       <c r="C161" t="n">
-        <v>608.5552163125774</v>
+        <v>613.7563010923075</v>
       </c>
       <c r="D161" t="n">
-        <v>593.7905860006466</v>
+        <v>605.9097866322771</v>
       </c>
       <c r="E161" t="n">
-        <v>606.3390502929688</v>
+        <v>609.214111328125</v>
       </c>
       <c r="F161" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B162" t="n">
-        <v>606.838246230648</v>
+        <v>607.8465495511928</v>
       </c>
       <c r="C162" t="n">
-        <v>613.7563625825306</v>
+        <v>613.4169431409898</v>
       </c>
       <c r="D162" t="n">
-        <v>605.9098473363839</v>
+        <v>604.2626749853522</v>
       </c>
       <c r="E162" t="n">
-        <v>609.2141723632812</v>
+        <v>611.2906494140625</v>
       </c>
       <c r="F162" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B163" t="n">
-        <v>607.8464888599174</v>
+        <v>608.3555996261091</v>
       </c>
       <c r="C163" t="n">
-        <v>613.4168818935308</v>
+        <v>637.4057020013258</v>
       </c>
       <c r="D163" t="n">
-        <v>604.2626146519137</v>
+        <v>607.9562607968793</v>
       </c>
       <c r="E163" t="n">
-        <v>611.2905883789062</v>
+        <v>634.1712646484375</v>
       </c>
       <c r="F163" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B164" t="n">
-        <v>608.3556581766634</v>
+        <v>638.4040398455469</v>
       </c>
       <c r="C164" t="n">
-        <v>637.4057633477772</v>
+        <v>641.8980416273442</v>
       </c>
       <c r="D164" t="n">
-        <v>607.9563193089997</v>
+        <v>628.2315007921775</v>
       </c>
       <c r="E164" t="n">
-        <v>634.1713256835938</v>
+        <v>634.2012329101562</v>
       </c>
       <c r="F164" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B165" t="n">
-        <v>638.4040398455469</v>
+        <v>632.4143189973911</v>
       </c>
       <c r="C165" t="n">
-        <v>641.8980416273442</v>
+        <v>633.4126052152244</v>
       </c>
       <c r="D165" t="n">
-        <v>628.2315007921775</v>
+        <v>622.281689514161</v>
       </c>
       <c r="E165" t="n">
-        <v>634.2012329101562</v>
+        <v>631.426025390625</v>
       </c>
       <c r="F165" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B166" t="n">
-        <v>632.4143189973911</v>
+        <v>629.3196791836195</v>
       </c>
       <c r="C166" t="n">
-        <v>633.4126052152244</v>
+        <v>634.6604862727559</v>
       </c>
       <c r="D166" t="n">
-        <v>622.281689514161</v>
+        <v>598.5025873828931</v>
       </c>
       <c r="E166" t="n">
-        <v>631.426025390625</v>
+        <v>599.44091796875</v>
       </c>
       <c r="F166" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B167" t="n">
-        <v>629.3196151062037</v>
+        <v>602.2062063737548</v>
       </c>
       <c r="C167" t="n">
-        <v>634.6604216515384</v>
+        <v>607.8365556216692</v>
       </c>
       <c r="D167" t="n">
-        <v>598.5025264432778</v>
+        <v>595.6574508079194</v>
       </c>
       <c r="E167" t="n">
-        <v>599.4408569335938</v>
+        <v>596.6058349609375</v>
       </c>
       <c r="F167" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B168" t="n">
-        <v>602.2061447656582</v>
+        <v>601.9665545007575</v>
       </c>
       <c r="C168" t="n">
-        <v>607.8364934375654</v>
+        <v>623.0803311577063</v>
       </c>
       <c r="D168" t="n">
-        <v>595.6573898697867</v>
+        <v>599.2412527816401</v>
       </c>
       <c r="E168" t="n">
-        <v>596.6057739257812</v>
+        <v>621.9122924804688</v>
       </c>
       <c r="F168" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B169" t="n">
-        <v>601.9666135784172</v>
+        <v>622.6011661035562</v>
       </c>
       <c r="C169" t="n">
-        <v>623.0803923074952</v>
+        <v>641.2991089275577</v>
       </c>
       <c r="D169" t="n">
-        <v>599.2413115918356</v>
+        <v>621.3633009071642</v>
       </c>
       <c r="E169" t="n">
-        <v>621.912353515625</v>
+        <v>626.4945068359375</v>
       </c>
       <c r="F169" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B170" t="n">
-        <v>622.601105447702</v>
+        <v>622.3915225332053</v>
       </c>
       <c r="C170" t="n">
-        <v>641.2990464500883</v>
+        <v>628.0717733238163</v>
       </c>
       <c r="D170" t="n">
-        <v>621.3632403719068</v>
+        <v>581.9109692668093</v>
       </c>
       <c r="E170" t="n">
-        <v>626.4944458007812</v>
+        <v>591.9837036132812</v>
       </c>
       <c r="F170" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B171" t="n">
-        <v>622.3915867034917</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="C171" t="n">
-        <v>628.0718380797523</v>
+        <v>590.9854370177134</v>
       </c>
       <c r="D171" t="n">
-        <v>581.9110292634388</v>
+        <v>578.2273099921849</v>
       </c>
       <c r="E171" t="n">
-        <v>591.9837646484375</v>
+        <v>584.3867797851562</v>
       </c>
       <c r="F171" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B172" t="n">
-        <v>590.9854370177134</v>
+        <v>589.9871222602228</v>
       </c>
       <c r="C172" t="n">
-        <v>590.9854370177134</v>
+        <v>596.6057643945405</v>
       </c>
       <c r="D172" t="n">
-        <v>578.2273099921849</v>
+        <v>580.0142532419713</v>
       </c>
       <c r="E172" t="n">
-        <v>584.3867797851562</v>
+        <v>583.588134765625</v>
       </c>
       <c r="F172" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B173" t="n">
-        <v>589.9871222602228</v>
+        <v>579.7347558037309</v>
       </c>
       <c r="C173" t="n">
-        <v>596.6057643945405</v>
+        <v>590.3066340250939</v>
       </c>
       <c r="D173" t="n">
-        <v>580.0142532419713</v>
+        <v>569.6221111934292</v>
       </c>
       <c r="E173" t="n">
-        <v>583.588134765625</v>
+        <v>570.00146484375</v>
       </c>
       <c r="F173" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B174" t="n">
-        <v>579.7347558037309</v>
+        <v>564.8602908302337</v>
       </c>
       <c r="C174" t="n">
-        <v>590.3066340250939</v>
+        <v>571.1893911411966</v>
       </c>
       <c r="D174" t="n">
-        <v>569.6221111934292</v>
+        <v>556.0553993401948</v>
       </c>
       <c r="E174" t="n">
-        <v>570.00146484375</v>
+        <v>567.455810546875</v>
       </c>
       <c r="F174" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B175" t="n">
-        <v>564.8602908302337</v>
+        <v>571.968101190783</v>
       </c>
       <c r="C175" t="n">
-        <v>571.1893911411966</v>
+        <v>575.0827493186854</v>
       </c>
       <c r="D175" t="n">
-        <v>556.0553993401948</v>
+        <v>559.9387644415484</v>
       </c>
       <c r="E175" t="n">
-        <v>567.455810546875</v>
+        <v>566.00830078125</v>
       </c>
       <c r="F175" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,25 +4993,25 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B176" t="n">
-        <v>571.9680395129554</v>
+        <v>579.4427159724761</v>
       </c>
       <c r="C176" t="n">
-        <v>575.0826873049916</v>
+        <v>600.795858737961</v>
       </c>
       <c r="D176" t="n">
-        <v>559.938704060897</v>
+        <v>578.8431525395191</v>
       </c>
       <c r="E176" t="n">
-        <v>566.0082397460938</v>
+        <v>593.011962890625</v>
       </c>
       <c r="F176" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B177" t="n">
-        <v>579.4427159724761</v>
+        <v>593.1818700134238</v>
       </c>
       <c r="C177" t="n">
-        <v>600.795858737961</v>
+        <v>605.3322537623429</v>
       </c>
       <c r="D177" t="n">
-        <v>578.8431525395191</v>
+        <v>591.5331468141493</v>
       </c>
       <c r="E177" t="n">
-        <v>593.011962890625</v>
+        <v>599.7366943359375</v>
       </c>
       <c r="F177" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G177" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B178" t="n">
-        <v>593.1818700134238</v>
+        <v>591.5331725816898</v>
       </c>
       <c r="C178" t="n">
-        <v>605.3322537623429</v>
+        <v>593.3417428489197</v>
       </c>
       <c r="D178" t="n">
-        <v>591.5331468141493</v>
+        <v>565.7435277503374</v>
       </c>
       <c r="E178" t="n">
-        <v>599.7366943359375</v>
+        <v>567.1324462890625</v>
       </c>
       <c r="F178" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B179" t="n">
-        <v>591.5331725816898</v>
+        <v>572.3682769745303</v>
       </c>
       <c r="C179" t="n">
-        <v>593.3417428489197</v>
+        <v>579.7624046842873</v>
       </c>
       <c r="D179" t="n">
-        <v>565.7435277503374</v>
+        <v>562.6559105294999</v>
       </c>
       <c r="E179" t="n">
-        <v>567.1324462890625</v>
+        <v>576.7647705078125</v>
       </c>
       <c r="F179" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B180" t="n">
-        <v>572.3682769745303</v>
+        <v>571.5689356803741</v>
       </c>
       <c r="C180" t="n">
-        <v>579.7624046842873</v>
+        <v>575.3559250048318</v>
       </c>
       <c r="D180" t="n">
-        <v>562.6559105294999</v>
+        <v>559.3685422933314</v>
       </c>
       <c r="E180" t="n">
-        <v>576.7647705078125</v>
+        <v>563.4053344726562</v>
       </c>
       <c r="F180" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B181" t="n">
-        <v>571.5689356803741</v>
+        <v>561.8066012038755</v>
       </c>
       <c r="C181" t="n">
-        <v>575.3559250048318</v>
+        <v>571.7487666818112</v>
       </c>
       <c r="D181" t="n">
-        <v>559.3685422933314</v>
+        <v>560.5775907162</v>
       </c>
       <c r="E181" t="n">
-        <v>563.4053344726562</v>
+        <v>561.7566528320312</v>
       </c>
       <c r="F181" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B182" t="n">
-        <v>561.8066012038755</v>
+        <v>561.4469285838474</v>
       </c>
       <c r="C182" t="n">
-        <v>571.7487666818112</v>
+        <v>568.591253761232</v>
       </c>
       <c r="D182" t="n">
-        <v>560.5775907162</v>
+        <v>555.1119012433646</v>
       </c>
       <c r="E182" t="n">
-        <v>561.7566528320312</v>
+        <v>557.230224609375</v>
       </c>
       <c r="F182" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B183" t="n">
-        <v>561.4469285838474</v>
+        <v>555.1118879211193</v>
       </c>
       <c r="C183" t="n">
-        <v>568.591253761232</v>
+        <v>555.9013039685537</v>
       </c>
       <c r="D183" t="n">
-        <v>555.1119012433646</v>
+        <v>539.7540133926082</v>
       </c>
       <c r="E183" t="n">
-        <v>557.230224609375</v>
+        <v>542.44189453125</v>
       </c>
       <c r="F183" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B184" t="n">
-        <v>555.1118879211193</v>
+        <v>542.9115767800729</v>
       </c>
       <c r="C184" t="n">
-        <v>555.9013039685537</v>
+        <v>556.4108722579447</v>
       </c>
       <c r="D184" t="n">
-        <v>539.7540133926082</v>
+        <v>539.9738926737891</v>
       </c>
       <c r="E184" t="n">
-        <v>542.44189453125</v>
+        <v>549.8161010742188</v>
       </c>
       <c r="F184" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B185" t="n">
-        <v>542.9115767800729</v>
+        <v>559.5583857816937</v>
       </c>
       <c r="C185" t="n">
-        <v>556.4108722579447</v>
+        <v>570.4498144711828</v>
       </c>
       <c r="D185" t="n">
-        <v>539.9738926737891</v>
+        <v>557.5599629753306</v>
       </c>
       <c r="E185" t="n">
-        <v>549.8161010742188</v>
+        <v>562.1563110351562</v>
       </c>
       <c r="F185" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B186" t="n">
-        <v>559.5583857816937</v>
+        <v>560.4976417791106</v>
       </c>
       <c r="C186" t="n">
-        <v>570.4498144711828</v>
+        <v>565.0939897966132</v>
       </c>
       <c r="D186" t="n">
-        <v>557.5599629753306</v>
+        <v>550.9951316644288</v>
       </c>
       <c r="E186" t="n">
-        <v>562.1563110351562</v>
+        <v>562.8457641601562</v>
       </c>
       <c r="F186" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B187" t="n">
-        <v>560.4976417791106</v>
+        <v>607.4305787144307</v>
       </c>
       <c r="C187" t="n">
-        <v>565.0939897966132</v>
+        <v>627.784571153574</v>
       </c>
       <c r="D187" t="n">
-        <v>550.9951316644288</v>
+        <v>594.6306830487989</v>
       </c>
       <c r="E187" t="n">
-        <v>562.8457641601562</v>
+        <v>612.4266357421875</v>
       </c>
       <c r="F187" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B188" t="n">
-        <v>607.4305787144307</v>
+        <v>607.4206544757068</v>
       </c>
       <c r="C188" t="n">
-        <v>627.784571153574</v>
+        <v>609.5189740900589</v>
       </c>
       <c r="D188" t="n">
-        <v>594.6306830487989</v>
+        <v>579.9622828274885</v>
       </c>
       <c r="E188" t="n">
-        <v>612.4266357421875</v>
+        <v>582.4403686523438</v>
       </c>
       <c r="F188" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B189" t="n">
-        <v>607.4206544757068</v>
+        <v>594.3709360150443</v>
       </c>
       <c r="C189" t="n">
-        <v>609.5189740900589</v>
+        <v>603.1040338931904</v>
       </c>
       <c r="D189" t="n">
-        <v>579.9622828274885</v>
+        <v>581.301233826573</v>
       </c>
       <c r="E189" t="n">
-        <v>582.4403686523438</v>
+        <v>599.8165893554688</v>
       </c>
       <c r="F189" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B190" t="n">
-        <v>594.3709360150443</v>
+        <v>607.1109147253509</v>
       </c>
       <c r="C190" t="n">
-        <v>603.1040338931904</v>
+        <v>624.8768626804635</v>
       </c>
       <c r="D190" t="n">
-        <v>581.301233826573</v>
+        <v>603.1839600389557</v>
       </c>
       <c r="E190" t="n">
-        <v>599.8165893554688</v>
+        <v>615.0946044921875</v>
       </c>
       <c r="F190" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B191" t="n">
-        <v>607.1109147253509</v>
+        <v>613.9055418180343</v>
       </c>
       <c r="C191" t="n">
-        <v>624.8768626804635</v>
+        <v>615.5142576272189</v>
       </c>
       <c r="D191" t="n">
-        <v>603.1839600389557</v>
+        <v>597.5384532703483</v>
       </c>
       <c r="E191" t="n">
-        <v>615.0946044921875</v>
+        <v>602.6444091796875</v>
       </c>
       <c r="F191" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B192" t="n">
-        <v>613.9055418180343</v>
+        <v>583.529455055522</v>
       </c>
       <c r="C192" t="n">
-        <v>615.5142576272189</v>
+        <v>632.77062206454</v>
       </c>
       <c r="D192" t="n">
-        <v>597.5384532703483</v>
+        <v>576.6149292518581</v>
       </c>
       <c r="E192" t="n">
-        <v>602.6444091796875</v>
+        <v>630.9819946289062</v>
       </c>
       <c r="F192" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B193" t="n">
-        <v>583.529455055522</v>
+        <v>659.8193113874754</v>
       </c>
       <c r="C193" t="n">
-        <v>632.77062206454</v>
+        <v>677.3254544051542</v>
       </c>
       <c r="D193" t="n">
-        <v>576.6149292518581</v>
+        <v>657.491131647921</v>
       </c>
       <c r="E193" t="n">
-        <v>630.9819946289062</v>
+        <v>668.6823120117188</v>
       </c>
       <c r="F193" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B194" t="n">
-        <v>659.8193113874754</v>
+        <v>660.858454671636</v>
       </c>
       <c r="C194" t="n">
-        <v>677.3254544051542</v>
+        <v>676.0864269737083</v>
       </c>
       <c r="D194" t="n">
-        <v>657.491131647921</v>
+        <v>653.6841239854351</v>
       </c>
       <c r="E194" t="n">
-        <v>668.6823120117188</v>
+        <v>656.2120971679688</v>
       </c>
       <c r="F194" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>660.858454671636</v>
+        <v>651.4858277274717</v>
       </c>
       <c r="C195" t="n">
-        <v>676.0864269737083</v>
+        <v>665.9743929146624</v>
       </c>
       <c r="D195" t="n">
-        <v>653.6841239854351</v>
+        <v>648.5381419230179</v>
       </c>
       <c r="E195" t="n">
-        <v>656.2120971679688</v>
+        <v>660.5186767578125</v>
       </c>
       <c r="F195" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>651.4858277274717</v>
+        <v>663.0767089741589</v>
       </c>
       <c r="C196" t="n">
-        <v>665.9743929146624</v>
+        <v>685.5390243545221</v>
       </c>
       <c r="D196" t="n">
-        <v>648.5381419230179</v>
+        <v>656.1421789132482</v>
       </c>
       <c r="E196" t="n">
-        <v>660.5186767578125</v>
+        <v>680.7727661132812</v>
       </c>
       <c r="F196" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>663.0767089741589</v>
+        <v>676.7459348014426</v>
       </c>
       <c r="C197" t="n">
-        <v>685.5390243545221</v>
+        <v>681.3622866487058</v>
       </c>
       <c r="D197" t="n">
-        <v>656.1421789132482</v>
+        <v>659.6393793096187</v>
       </c>
       <c r="E197" t="n">
-        <v>680.7727661132812</v>
+        <v>664.0159301757812</v>
       </c>
       <c r="F197" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B198" t="n">
-        <v>676.7459348014426</v>
+        <v>647.1892801723585</v>
       </c>
       <c r="C198" t="n">
-        <v>681.3622866487058</v>
+        <v>651.68573177941</v>
       </c>
       <c r="D198" t="n">
-        <v>659.6393793096187</v>
+        <v>625.5063791142821</v>
       </c>
       <c r="E198" t="n">
-        <v>664.0159301757812</v>
+        <v>645.5006103515625</v>
       </c>
       <c r="F198" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B199" t="n">
-        <v>647.1892801723585</v>
+        <v>646.1900645769782</v>
       </c>
       <c r="C199" t="n">
-        <v>651.68573177941</v>
+        <v>652.7848358303891</v>
       </c>
       <c r="D199" t="n">
-        <v>625.5063791142821</v>
+        <v>635.5084916103011</v>
       </c>
       <c r="E199" t="n">
-        <v>645.5006103515625</v>
+        <v>645.3406982421875</v>
       </c>
       <c r="F199" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B200" t="n">
-        <v>646.1900645769782</v>
+        <v>653.664124760039</v>
       </c>
       <c r="C200" t="n">
-        <v>652.7848358303891</v>
+        <v>655.3627963853286</v>
       </c>
       <c r="D200" t="n">
-        <v>635.5084916103011</v>
+        <v>642.6928027946103</v>
       </c>
       <c r="E200" t="n">
-        <v>645.3406982421875</v>
+        <v>643.3023071289062</v>
       </c>
       <c r="F200" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B201" t="n">
-        <v>653.664124760039</v>
+        <v>647.189254956408</v>
       </c>
       <c r="C201" t="n">
-        <v>655.3627963853286</v>
+        <v>648.4882176170956</v>
       </c>
       <c r="D201" t="n">
-        <v>642.6928027946103</v>
+        <v>623.5079318845419</v>
       </c>
       <c r="E201" t="n">
-        <v>643.3023071289062</v>
+        <v>626.6754150390625</v>
       </c>
       <c r="F201" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B202" t="n">
-        <v>647.189254956408</v>
+        <v>607.9301851876114</v>
       </c>
       <c r="C202" t="n">
-        <v>648.4882176170956</v>
+        <v>614.1653155952538</v>
       </c>
       <c r="D202" t="n">
-        <v>623.5079318845419</v>
+        <v>596.7490071058414</v>
       </c>
       <c r="E202" t="n">
-        <v>626.6754150390625</v>
+        <v>605.6220092773438</v>
       </c>
       <c r="F202" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B203" t="n">
-        <v>607.9301851876114</v>
+        <v>604.8226548171024</v>
       </c>
       <c r="C203" t="n">
-        <v>614.1653155952538</v>
+        <v>609.4989569016461</v>
       </c>
       <c r="D203" t="n">
-        <v>596.7490071058414</v>
+        <v>593.9812354037057</v>
       </c>
       <c r="E203" t="n">
-        <v>605.6220092773438</v>
+        <v>594.7206420898438</v>
       </c>
       <c r="F203" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B204" t="n">
-        <v>604.8226548171024</v>
+        <v>606.7411202287035</v>
       </c>
       <c r="C204" t="n">
-        <v>609.4989569016461</v>
+        <v>610.7779733376527</v>
       </c>
       <c r="D204" t="n">
-        <v>593.9812354037057</v>
+        <v>592.6622656813121</v>
       </c>
       <c r="E204" t="n">
-        <v>594.7206420898438</v>
+        <v>593.4016723632812</v>
       </c>
       <c r="F204" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B205" t="n">
-        <v>606.7411202287035</v>
+        <v>596.3493616660036</v>
       </c>
       <c r="C205" t="n">
-        <v>610.7779733376527</v>
+        <v>600.5260580457825</v>
       </c>
       <c r="D205" t="n">
-        <v>592.6622656813121</v>
+        <v>586.5370982909723</v>
       </c>
       <c r="E205" t="n">
-        <v>593.4016723632812</v>
+        <v>592.9420166015625</v>
       </c>
       <c r="F205" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B206" t="n">
-        <v>596.3493616660036</v>
+        <v>592.7821833537371</v>
       </c>
       <c r="C206" t="n">
-        <v>600.5260580457825</v>
+        <v>599.4968549179539</v>
       </c>
       <c r="D206" t="n">
-        <v>586.5370982909723</v>
+        <v>581.7608519604674</v>
       </c>
       <c r="E206" t="n">
-        <v>592.9420166015625</v>
+        <v>585.148193359375</v>
       </c>
       <c r="F206" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B207" t="n">
-        <v>592.7821833537371</v>
+        <v>525.58522592167</v>
       </c>
       <c r="C207" t="n">
-        <v>599.4968549179539</v>
+        <v>539.4542858116451</v>
       </c>
       <c r="D207" t="n">
-        <v>581.7608519604674</v>
+        <v>524.0764068649972</v>
       </c>
       <c r="E207" t="n">
-        <v>585.148193359375</v>
+        <v>538.60498046875</v>
       </c>
       <c r="F207" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B208" t="n">
-        <v>525.58522592167</v>
+        <v>543.171288392182</v>
       </c>
       <c r="C208" t="n">
-        <v>539.4542858116451</v>
+        <v>557.8897136701136</v>
       </c>
       <c r="D208" t="n">
-        <v>524.0764068649972</v>
+        <v>539.7939490076644</v>
       </c>
       <c r="E208" t="n">
-        <v>538.60498046875</v>
+        <v>556.27099609375</v>
       </c>
       <c r="F208" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B209" t="n">
-        <v>543.171288392182</v>
+        <v>561.7966164985271</v>
       </c>
       <c r="C209" t="n">
-        <v>557.8897136701136</v>
+        <v>597.0488245114987</v>
       </c>
       <c r="D209" t="n">
-        <v>539.7939490076644</v>
+        <v>558.9188827428958</v>
       </c>
       <c r="E209" t="n">
-        <v>556.27099609375</v>
+        <v>589.7745361328125</v>
       </c>
       <c r="F209" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B210" t="n">
-        <v>561.7966164985271</v>
+        <v>581.0414552494501</v>
       </c>
       <c r="C210" t="n">
-        <v>597.0488245114987</v>
+        <v>592.32253050782</v>
       </c>
       <c r="D210" t="n">
-        <v>558.9188827428958</v>
+        <v>577.794018053301</v>
       </c>
       <c r="E210" t="n">
-        <v>589.7745361328125</v>
+        <v>587.4763793945312</v>
       </c>
       <c r="F210" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B211" t="n">
-        <v>581.0414552494501</v>
+        <v>599.9865089938204</v>
       </c>
       <c r="C211" t="n">
-        <v>592.32253050782</v>
+        <v>600.5260612032997</v>
       </c>
       <c r="D211" t="n">
-        <v>577.794018053301</v>
+        <v>579.6625219517506</v>
       </c>
       <c r="E211" t="n">
-        <v>587.4763793945312</v>
+        <v>588.3057250976562</v>
       </c>
       <c r="F211" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B212" t="n">
-        <v>599.9865089938204</v>
+        <v>586.487189429669</v>
       </c>
       <c r="C212" t="n">
-        <v>600.5260612032997</v>
+        <v>594.8405827519979</v>
       </c>
       <c r="D212" t="n">
-        <v>579.6625219517506</v>
+        <v>585.5379263278069</v>
       </c>
       <c r="E212" t="n">
-        <v>588.3057250976562</v>
+        <v>589.4348754882812</v>
       </c>
       <c r="F212" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B213" t="n">
-        <v>586.487189429669</v>
+        <v>585.1781899072663</v>
       </c>
       <c r="C213" t="n">
-        <v>594.8405827519979</v>
+        <v>598.2678350979388</v>
       </c>
       <c r="D213" t="n">
-        <v>585.5379263278069</v>
+        <v>585.1581861630435</v>
       </c>
       <c r="E213" t="n">
-        <v>589.4348754882812</v>
+        <v>591.633056640625</v>
       </c>
       <c r="F213" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B214" t="n">
-        <v>585.1781899072663</v>
+        <v>598.657568915248</v>
       </c>
       <c r="C214" t="n">
-        <v>598.2678350979388</v>
+        <v>607.7304260788247</v>
       </c>
       <c r="D214" t="n">
-        <v>585.1581861630435</v>
+        <v>591.5631919202813</v>
       </c>
       <c r="E214" t="n">
-        <v>591.633056640625</v>
+        <v>594.4508666992188</v>
       </c>
       <c r="F214" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B215" t="n">
-        <v>598.657568915248</v>
+        <v>597.5284100969216</v>
       </c>
       <c r="C215" t="n">
-        <v>607.7304260788247</v>
+        <v>611.9470231090784</v>
       </c>
       <c r="D215" t="n">
-        <v>591.5631919202813</v>
+        <v>592.9320621063698</v>
       </c>
       <c r="E215" t="n">
-        <v>594.4508666992188</v>
+        <v>598.6475219726562</v>
       </c>
       <c r="F215" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B216" t="n">
-        <v>597.5284100969216</v>
+        <v>600.5960026412422</v>
       </c>
       <c r="C216" t="n">
-        <v>611.9470231090784</v>
+        <v>604.023290419805</v>
       </c>
       <c r="D216" t="n">
-        <v>592.9320621063698</v>
+        <v>577.7540447074138</v>
       </c>
       <c r="E216" t="n">
-        <v>598.6475219726562</v>
+        <v>578.3934936523438</v>
       </c>
       <c r="F216" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B217" t="n">
-        <v>600.5960026412422</v>
+        <v>580.2520897369063</v>
       </c>
       <c r="C217" t="n">
-        <v>604.023290419805</v>
+        <v>595.3801043917661</v>
       </c>
       <c r="D217" t="n">
-        <v>577.7540447074138</v>
+        <v>578.9331233348041</v>
       </c>
       <c r="E217" t="n">
-        <v>578.3934936523438</v>
+        <v>594.5007934570312</v>
       </c>
       <c r="F217" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B218" t="n">
-        <v>580.2520897369063</v>
+        <v>596.5092089028919</v>
       </c>
       <c r="C218" t="n">
-        <v>595.3801043917661</v>
+        <v>601.3853654698224</v>
       </c>
       <c r="D218" t="n">
-        <v>578.9331233348041</v>
+        <v>588.8252707092146</v>
       </c>
       <c r="E218" t="n">
-        <v>594.5007934570312</v>
+        <v>589.3848266601562</v>
       </c>
       <c r="F218" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B219" t="n">
-        <v>596.5092089028919</v>
+        <v>589.2849441761664</v>
       </c>
       <c r="C219" t="n">
-        <v>601.3853654698224</v>
+        <v>589.774548021712</v>
       </c>
       <c r="D219" t="n">
-        <v>588.8252707092146</v>
+        <v>564.3046582848494</v>
       </c>
       <c r="E219" t="n">
-        <v>589.3848266601562</v>
+        <v>568.5213012695312</v>
       </c>
       <c r="F219" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B220" t="n">
-        <v>589.2849441761664</v>
+        <v>557.0403796583744</v>
       </c>
       <c r="C220" t="n">
-        <v>589.774548021712</v>
+        <v>560.2178647510921</v>
       </c>
       <c r="D220" t="n">
-        <v>564.3046582848494</v>
+        <v>542.7816737373303</v>
       </c>
       <c r="E220" t="n">
-        <v>568.5213012695312</v>
+        <v>543.2412719726562</v>
       </c>
       <c r="F220" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B221" t="n">
-        <v>557.0403796583744</v>
+        <v>540.9131223962278</v>
       </c>
       <c r="C221" t="n">
-        <v>560.2178647510921</v>
+        <v>553.6330639150415</v>
       </c>
       <c r="D221" t="n">
-        <v>542.7816737373303</v>
+        <v>536.8463247077087</v>
       </c>
       <c r="E221" t="n">
-        <v>543.2412719726562</v>
+        <v>545.5994262695312</v>
       </c>
       <c r="F221" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B222" t="n">
-        <v>540.9131223962278</v>
+        <v>546.5187091013889</v>
       </c>
       <c r="C222" t="n">
-        <v>553.6330639150415</v>
+        <v>549.5562899225255</v>
       </c>
       <c r="D222" t="n">
-        <v>536.8463247077087</v>
+        <v>538.8847190657524</v>
       </c>
       <c r="E222" t="n">
-        <v>545.5994262695312</v>
+        <v>545.3995971679688</v>
       </c>
       <c r="F222" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B223" t="n">
-        <v>546.5187091013889</v>
+        <v>546.4587335768297</v>
       </c>
       <c r="C223" t="n">
-        <v>549.5562899225255</v>
+        <v>553.4332095869578</v>
       </c>
       <c r="D223" t="n">
-        <v>538.8847190657524</v>
+        <v>542.8015857242297</v>
       </c>
       <c r="E223" t="n">
-        <v>545.3995971679688</v>
+        <v>549.4663696289062</v>
       </c>
       <c r="F223" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B224" t="n">
-        <v>546.4587335768297</v>
+        <v>549.7661710202622</v>
       </c>
       <c r="C224" t="n">
-        <v>553.4332095869578</v>
+        <v>560.9772946036173</v>
       </c>
       <c r="D224" t="n">
-        <v>542.8015857242297</v>
+        <v>545.8692218355393</v>
       </c>
       <c r="E224" t="n">
-        <v>549.4663696289062</v>
+        <v>558.5792236328125</v>
       </c>
       <c r="F224" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B225" t="n">
-        <v>549.7661710202622</v>
+        <v>563.4353464162</v>
       </c>
       <c r="C225" t="n">
-        <v>560.9772946036173</v>
+        <v>570.3498724402046</v>
       </c>
       <c r="D225" t="n">
-        <v>545.8692218355393</v>
+        <v>560.9573215839381</v>
       </c>
       <c r="E225" t="n">
-        <v>558.5792236328125</v>
+        <v>569.6004638671875</v>
       </c>
       <c r="F225" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B226" t="n">
-        <v>563.4353464162</v>
+        <v>589.8444773654404</v>
       </c>
       <c r="C226" t="n">
-        <v>570.3498724402046</v>
+        <v>592.8721171723366</v>
       </c>
       <c r="D226" t="n">
-        <v>560.9573215839381</v>
+        <v>561.4369046651577</v>
       </c>
       <c r="E226" t="n">
-        <v>569.6004638671875</v>
+        <v>575.6856689453125</v>
       </c>
       <c r="F226" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B227" t="n">
-        <v>589.8444773654404</v>
+        <v>576.0253592943615</v>
       </c>
       <c r="C227" t="n">
-        <v>592.8721171723366</v>
+        <v>587.9260010338789</v>
       </c>
       <c r="D227" t="n">
-        <v>561.4369046651577</v>
+        <v>567.1723610665189</v>
       </c>
       <c r="E227" t="n">
-        <v>575.6856689453125</v>
+        <v>570.6495971679688</v>
       </c>
       <c r="F227" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B228" t="n">
-        <v>576.0253592943615</v>
+        <v>571.0992793335739</v>
       </c>
       <c r="C228" t="n">
-        <v>587.9260010338789</v>
+        <v>588.7253835559844</v>
       </c>
       <c r="D228" t="n">
-        <v>567.1723610665189</v>
+        <v>570.5497252457161</v>
       </c>
       <c r="E228" t="n">
-        <v>570.6495971679688</v>
+        <v>577.564208984375</v>
       </c>
       <c r="F228" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B229" t="n">
-        <v>571.0992793335739</v>
+        <v>577.1744781551006</v>
       </c>
       <c r="C229" t="n">
-        <v>588.7253835559844</v>
+        <v>578.2236379136884</v>
       </c>
       <c r="D229" t="n">
-        <v>570.5497252457161</v>
+        <v>568.6911832402849</v>
       </c>
       <c r="E229" t="n">
-        <v>577.564208984375</v>
+        <v>571.888671875</v>
       </c>
       <c r="F229" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B230" t="n">
-        <v>577.1744781551006</v>
+        <v>557.9096596695957</v>
       </c>
       <c r="C230" t="n">
-        <v>578.2236379136884</v>
+        <v>584.4887194481862</v>
       </c>
       <c r="D230" t="n">
-        <v>568.6911832402849</v>
+        <v>555.6614340241316</v>
       </c>
       <c r="E230" t="n">
-        <v>571.888671875</v>
+        <v>578.083740234375</v>
       </c>
       <c r="F230" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B231" t="n">
-        <v>557.9096596695957</v>
+        <v>578.3335366296732</v>
       </c>
       <c r="C231" t="n">
-        <v>584.4887194481862</v>
+        <v>599.9065373056851</v>
       </c>
       <c r="D231" t="n">
-        <v>555.6614340241316</v>
+        <v>576.5449702025707</v>
       </c>
       <c r="E231" t="n">
-        <v>578.083740234375</v>
+        <v>592.3824462890625</v>
       </c>
       <c r="F231" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B232" t="n">
-        <v>578.3335366296732</v>
+        <v>604.0133041368691</v>
       </c>
       <c r="C232" t="n">
-        <v>599.9065373056851</v>
+        <v>618.9715308723809</v>
       </c>
       <c r="D232" t="n">
-        <v>576.5449702025707</v>
+        <v>603.8733999005765</v>
       </c>
       <c r="E232" t="n">
-        <v>592.3824462890625</v>
+        <v>610.1984252929688</v>
       </c>
       <c r="F232" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B233" t="n">
-        <v>604.0133041368691</v>
+        <v>611.8670721034152</v>
       </c>
       <c r="C233" t="n">
-        <v>618.9715308723809</v>
+        <v>616.9730886717387</v>
       </c>
       <c r="D233" t="n">
-        <v>603.8733999005765</v>
+        <v>604.7926993516937</v>
       </c>
       <c r="E233" t="n">
-        <v>610.1984252929688</v>
+        <v>616.2836303710938</v>
       </c>
       <c r="F233" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B234" t="n">
-        <v>611.8670721034152</v>
+        <v>615.7241045276966</v>
       </c>
       <c r="C234" t="n">
-        <v>616.9730886717387</v>
+        <v>624.3072966603136</v>
       </c>
       <c r="D234" t="n">
-        <v>604.7926993516937</v>
+        <v>609.2591747857786</v>
       </c>
       <c r="E234" t="n">
-        <v>616.2836303710938</v>
+        <v>612.9962158203125</v>
       </c>
       <c r="F234" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B235" t="n">
-        <v>615.7241045276966</v>
+        <v>648.1284941622514</v>
       </c>
       <c r="C235" t="n">
-        <v>624.3072966603136</v>
+        <v>657.3411939542544</v>
       </c>
       <c r="D235" t="n">
-        <v>609.2591747857786</v>
+        <v>638.056426220049</v>
       </c>
       <c r="E235" t="n">
-        <v>612.9962158203125</v>
+        <v>653.1744995117188</v>
       </c>
       <c r="F235" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B236" t="n">
-        <v>648.1284941622514</v>
+        <v>653.1945472302951</v>
       </c>
       <c r="C236" t="n">
-        <v>657.3411939542544</v>
+        <v>662.9768054946985</v>
       </c>
       <c r="D236" t="n">
-        <v>638.056426220049</v>
+        <v>641.6336632885306</v>
       </c>
       <c r="E236" t="n">
-        <v>653.1744995117188</v>
+        <v>643.8718872070312</v>
       </c>
       <c r="F236" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B237" t="n">
-        <v>653.1945472302951</v>
+        <v>652.9947023490145</v>
       </c>
       <c r="C237" t="n">
-        <v>662.9768054946985</v>
+        <v>663.716221985592</v>
       </c>
       <c r="D237" t="n">
-        <v>641.6336632885306</v>
+        <v>645.6904688887529</v>
       </c>
       <c r="E237" t="n">
-        <v>643.8718872070312</v>
+        <v>647.51904296875</v>
       </c>
       <c r="F237" t="n">
-        <v>21531900</v>
+        <v>16925000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B238" t="n">
-        <v>652.9947023490145</v>
+        <v>657.311302577125</v>
       </c>
       <c r="C238" t="n">
-        <v>663.716221985592</v>
+        <v>668.072768706455</v>
       </c>
       <c r="D238" t="n">
-        <v>645.6904688887529</v>
+        <v>648.708045415434</v>
       </c>
       <c r="E238" t="n">
-        <v>647.51904296875</v>
+        <v>665.0751342773438</v>
       </c>
       <c r="F238" t="n">
-        <v>16925000</v>
+        <v>19332300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B239" t="n">
-        <v>657.311302577125</v>
+        <v>658.7801108800835</v>
       </c>
       <c r="C239" t="n">
-        <v>668.072768706455</v>
+        <v>678.3346866933342</v>
       </c>
       <c r="D239" t="n">
-        <v>648.708045415434</v>
+        <v>655.6825797136325</v>
       </c>
       <c r="E239" t="n">
-        <v>665.0751342773438</v>
+        <v>669.7114868164062</v>
       </c>
       <c r="F239" t="n">
-        <v>19332300</v>
+        <v>19502800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B240" t="n">
-        <v>658.7801108800835</v>
+        <v>679.3738238485387</v>
       </c>
       <c r="C240" t="n">
-        <v>678.3346866933342</v>
+        <v>684.7695900234191</v>
       </c>
       <c r="D240" t="n">
-        <v>655.6825797136325</v>
+        <v>671.3801323225093</v>
       </c>
       <c r="E240" t="n">
-        <v>669.7114868164062</v>
+        <v>672.779052734375</v>
       </c>
       <c r="F240" t="n">
-        <v>19502800</v>
+        <v>17217800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B241" t="n">
-        <v>679.3738238485387</v>
+        <v>681.9018750257407</v>
       </c>
       <c r="C241" t="n">
-        <v>684.7695900234191</v>
+        <v>682.6612854975235</v>
       </c>
       <c r="D241" t="n">
-        <v>671.3801323225093</v>
+        <v>666.5239959332205</v>
       </c>
       <c r="E241" t="n">
-        <v>672.779052734375</v>
+        <v>681.77197265625</v>
       </c>
       <c r="F241" t="n">
-        <v>17217800</v>
+        <v>15928000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B242" t="n">
-        <v>681.9018750257407</v>
+        <v>688.0769980771287</v>
       </c>
       <c r="C242" t="n">
-        <v>682.6612854975235</v>
+        <v>689.6058209010791</v>
       </c>
       <c r="D242" t="n">
-        <v>666.5239959332205</v>
+        <v>660.278927643704</v>
       </c>
       <c r="E242" t="n">
-        <v>681.77197265625</v>
+        <v>665.2250366210938</v>
       </c>
       <c r="F242" t="n">
-        <v>15928000</v>
+        <v>27596400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,25 +6735,25 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B243" t="n">
-        <v>688.0769980771287</v>
+        <v>680.2999877929688</v>
       </c>
       <c r="C243" t="n">
-        <v>689.6058209010791</v>
+        <v>753</v>
       </c>
       <c r="D243" t="n">
-        <v>660.278927643704</v>
+        <v>679.5999755859375</v>
       </c>
       <c r="E243" t="n">
-        <v>665.2250366210938</v>
+        <v>741.25</v>
       </c>
       <c r="F243" t="n">
-        <v>27596400</v>
+        <v>48720500</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -6761,25 +6761,25 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B244" t="n">
-        <v>680.2999877929688</v>
+        <v>731.4000244140625</v>
       </c>
       <c r="C244" t="n">
-        <v>753</v>
+        <v>757.27001953125</v>
       </c>
       <c r="D244" t="n">
-        <v>679.5999755859375</v>
+        <v>730</v>
       </c>
       <c r="E244" t="n">
-        <v>741.25</v>
+        <v>736.5999755859375</v>
       </c>
       <c r="F244" t="n">
-        <v>48720500</v>
+        <v>28122100</v>
       </c>
       <c r="G244" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B245" t="n">
-        <v>731.4000244140625</v>
+        <v>747.5999755859375</v>
       </c>
       <c r="C245" t="n">
-        <v>757.27001953125</v>
+        <v>763.9000244140625</v>
       </c>
       <c r="D245" t="n">
-        <v>730</v>
+        <v>739.510009765625</v>
       </c>
       <c r="E245" t="n">
-        <v>736.5999755859375</v>
+        <v>744.0999755859375</v>
       </c>
       <c r="F245" t="n">
-        <v>28122100</v>
+        <v>30829200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B246" t="n">
-        <v>747.5999755859375</v>
+        <v>744.3599853515625</v>
       </c>
       <c r="C246" t="n">
-        <v>763.9000244140625</v>
+        <v>779.8200073242188</v>
       </c>
       <c r="D246" t="n">
-        <v>739.510009765625</v>
+        <v>743.010009765625</v>
       </c>
       <c r="E246" t="n">
-        <v>744.0999755859375</v>
+        <v>777.5900268554688</v>
       </c>
       <c r="F246" t="n">
-        <v>30829200</v>
+        <v>34808500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B247" t="n">
-        <v>744.3599853515625</v>
+        <v>768.8499755859375</v>
       </c>
       <c r="C247" t="n">
-        <v>779.8200073242188</v>
+        <v>769.5700073242188</v>
       </c>
       <c r="D247" t="n">
-        <v>743.010009765625</v>
+        <v>746.5399780273438</v>
       </c>
       <c r="E247" t="n">
-        <v>777.5900268554688</v>
+        <v>751.6599731445312</v>
       </c>
       <c r="F247" t="n">
-        <v>34808500</v>
+        <v>25826700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B248" t="n">
-        <v>768.8499755859375</v>
+        <v>750.0399780273438</v>
       </c>
       <c r="C248" t="n">
-        <v>769.5700073242188</v>
+        <v>750.5800170898438</v>
       </c>
       <c r="D248" t="n">
-        <v>746.5399780273438</v>
+        <v>713.1900024414062</v>
       </c>
       <c r="E248" t="n">
-        <v>751.6599731445312</v>
+        <v>715.6199951171875</v>
       </c>
       <c r="F248" t="n">
-        <v>25826700</v>
+        <v>27943100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B249" t="n">
-        <v>750.0399780273438</v>
+        <v>725</v>
       </c>
       <c r="C249" t="n">
-        <v>750.5800170898438</v>
+        <v>740.4500122070312</v>
       </c>
       <c r="D249" t="n">
-        <v>713.1900024414062</v>
+        <v>715.0999755859375</v>
       </c>
       <c r="E249" t="n">
-        <v>715.6199951171875</v>
+        <v>738.7899780273438</v>
       </c>
       <c r="F249" t="n">
-        <v>27943100</v>
+        <v>23591100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>725</v>
+        <v>730.27001953125</v>
       </c>
       <c r="C250" t="n">
-        <v>740.4500122070312</v>
+        <v>738.25</v>
       </c>
       <c r="D250" t="n">
-        <v>715.0999755859375</v>
+        <v>721.2999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>738.7899780273438</v>
+        <v>725.1799926757812</v>
       </c>
       <c r="F250" t="n">
-        <v>23591100</v>
+        <v>19293000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B251" t="n">
-        <v>730.27001953125</v>
+        <v>728.530029296875</v>
       </c>
       <c r="C251" t="n">
-        <v>738.25</v>
+        <v>735.8800048828125</v>
       </c>
       <c r="D251" t="n">
-        <v>721.2999877929688</v>
+        <v>721.510009765625</v>
       </c>
       <c r="E251" t="n">
-        <v>725.1799926757812</v>
+        <v>725.9299926757812</v>
       </c>
       <c r="F251" t="n">
-        <v>19293000</v>
+        <v>12408400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B252" t="n">
-        <v>728.530029296875</v>
+        <v>733.2050170898438</v>
       </c>
       <c r="C252" t="n">
-        <v>735.8800048828125</v>
+        <v>741.5800170898438</v>
       </c>
       <c r="D252" t="n">
-        <v>721.510009765625</v>
+        <v>726.2000122070312</v>
       </c>
       <c r="E252" t="n">
-        <v>725.9299926757812</v>
+        <v>728.0800170898438</v>
       </c>
       <c r="F252" t="n">
-        <v>12384700</v>
+        <v>12873427</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,34 +10776,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>728.08</v>
+      </c>
+      <c r="D2" t="n">
         <v>725.9299999999999</v>
       </c>
-      <c r="D2" t="n">
-        <v>725.1799999999999</v>
-      </c>
       <c r="E2" t="n">
-        <v>728.525</v>
+        <v>733.205</v>
       </c>
       <c r="F2" t="n">
-        <v>735.88</v>
+        <v>741.58</v>
       </c>
       <c r="G2" t="n">
-        <v>721.51</v>
+        <v>726.2</v>
       </c>
       <c r="H2" t="n">
-        <v>12256112</v>
+        <v>12873427</v>
       </c>
       <c r="I2" t="n">
         <v>19468738</v>
       </c>
       <c r="J2" t="n">
-        <v>1849311100928</v>
+        <v>1854788337664</v>
       </c>
       <c r="K2" t="n">
-        <v>27.321415</v>
+        <v>27.402334</v>
       </c>
       <c r="L2" t="n">
-        <v>20.796753</v>
+        <v>20.858347</v>
       </c>
       <c r="M2" t="n">
         <v>26.57</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.0808625</v>
+        <v>7.1018343</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:38:21</t>
+          <t>2026-10-03 05:34:25</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B2" t="n">
-        <v>727.1634377305112</v>
+        <v>702.8060849901855</v>
       </c>
       <c r="C2" t="n">
-        <v>728.528801479838</v>
+        <v>714.456569002901</v>
       </c>
       <c r="D2" t="n">
-        <v>707.7791777004747</v>
+        <v>688.1757185011091</v>
       </c>
       <c r="E2" t="n">
-        <v>708.1578979492188</v>
+        <v>713.2406616210938</v>
       </c>
       <c r="F2" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B3" t="n">
-        <v>702.8060248479621</v>
+        <v>715.2936403041813</v>
       </c>
       <c r="C3" t="n">
-        <v>714.4565078636942</v>
+        <v>716.0710326272052</v>
       </c>
       <c r="D3" t="n">
-        <v>688.1756596108709</v>
+        <v>703.3641353885179</v>
       </c>
       <c r="E3" t="n">
-        <v>713.2406005859375</v>
+        <v>710.6693725585938</v>
       </c>
       <c r="F3" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B4" t="n">
-        <v>715.2936403041813</v>
+        <v>711.0382167719541</v>
       </c>
       <c r="C4" t="n">
-        <v>716.0710326272052</v>
+        <v>717.2172700317816</v>
       </c>
       <c r="D4" t="n">
-        <v>703.3641353885179</v>
+        <v>705.4172680165016</v>
       </c>
       <c r="E4" t="n">
-        <v>710.6693725585938</v>
+        <v>715.4133911132812</v>
       </c>
       <c r="F4" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B5" t="n">
-        <v>711.0380954481734</v>
+        <v>715.8518398810967</v>
       </c>
       <c r="C5" t="n">
-        <v>717.2171476536749</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="D5" t="n">
-        <v>705.4171476518181</v>
+        <v>710.0315555923428</v>
       </c>
       <c r="E5" t="n">
-        <v>715.4132690429688</v>
+        <v>731.0303344726562</v>
       </c>
       <c r="F5" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B6" t="n">
-        <v>715.8517801132227</v>
+        <v>728.4490335307075</v>
       </c>
       <c r="C6" t="n">
-        <v>731.0302734375</v>
+        <v>732.784364410351</v>
       </c>
       <c r="D6" t="n">
-        <v>710.0314963104157</v>
+        <v>702.1283419878271</v>
       </c>
       <c r="E6" t="n">
-        <v>731.0302734375</v>
+        <v>702.9156494140625</v>
       </c>
       <c r="F6" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B7" t="n">
-        <v>728.4490335307075</v>
+        <v>710.5995481500918</v>
       </c>
       <c r="C7" t="n">
-        <v>732.784364410351</v>
+        <v>717.5061127097006</v>
       </c>
       <c r="D7" t="n">
-        <v>702.1283419878271</v>
+        <v>705.2477072901073</v>
       </c>
       <c r="E7" t="n">
-        <v>702.9156494140625</v>
+        <v>713.2804565429688</v>
       </c>
       <c r="F7" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B8" t="n">
-        <v>710.5996089558437</v>
+        <v>705.3872795195668</v>
       </c>
       <c r="C8" t="n">
-        <v>717.5061741064447</v>
+        <v>713.1309705798873</v>
       </c>
       <c r="D8" t="n">
-        <v>705.2477676379041</v>
+        <v>696.9658337653736</v>
       </c>
       <c r="E8" t="n">
-        <v>713.280517578125</v>
+        <v>706.2543334960938</v>
       </c>
       <c r="F8" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="n">
-        <v>705.3873404797914</v>
+        <v>714.6358727912688</v>
       </c>
       <c r="C9" t="n">
-        <v>713.1310322093289</v>
+        <v>721.4527759491865</v>
       </c>
       <c r="D9" t="n">
-        <v>696.9658939978091</v>
+        <v>707.1114088212217</v>
       </c>
       <c r="E9" t="n">
-        <v>706.25439453125</v>
+        <v>715.1242065429688</v>
       </c>
       <c r="F9" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B10" t="n">
-        <v>714.6359337847463</v>
+        <v>715.1242355877501</v>
       </c>
       <c r="C10" t="n">
-        <v>721.4528375244799</v>
+        <v>723.0373960268438</v>
       </c>
       <c r="D10" t="n">
-        <v>707.1114691724935</v>
+        <v>701.5004654735715</v>
       </c>
       <c r="E10" t="n">
-        <v>715.124267578125</v>
+        <v>709.6627807617188</v>
       </c>
       <c r="F10" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B11" t="n">
-        <v>715.1242355877501</v>
+        <v>704.6896374063629</v>
       </c>
       <c r="C11" t="n">
-        <v>723.0373960268438</v>
+        <v>716.1108563950927</v>
       </c>
       <c r="D11" t="n">
-        <v>701.5004654735715</v>
+        <v>703.7328609179003</v>
       </c>
       <c r="E11" t="n">
-        <v>709.6627807617188</v>
+        <v>714.496337890625</v>
       </c>
       <c r="F11" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B12" t="n">
-        <v>704.6896374063629</v>
+        <v>718.7519023248905</v>
       </c>
       <c r="C12" t="n">
-        <v>716.1108563950927</v>
+        <v>731.289390620618</v>
       </c>
       <c r="D12" t="n">
-        <v>703.7328609179003</v>
+        <v>717.7453070615727</v>
       </c>
       <c r="E12" t="n">
-        <v>714.496337890625</v>
+        <v>729.6947631835938</v>
       </c>
       <c r="F12" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B13" t="n">
-        <v>718.7519624447335</v>
+        <v>733.5319023498442</v>
       </c>
       <c r="C13" t="n">
-        <v>731.2894517891565</v>
+        <v>736.0034992395473</v>
       </c>
       <c r="D13" t="n">
-        <v>717.7453670972193</v>
+        <v>726.286459134489</v>
       </c>
       <c r="E13" t="n">
-        <v>729.69482421875</v>
+        <v>730.7911987304688</v>
       </c>
       <c r="F13" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B14" t="n">
-        <v>733.5318410857864</v>
+        <v>731.3492880397093</v>
       </c>
       <c r="C14" t="n">
-        <v>736.0034377690635</v>
+        <v>738.0963605372498</v>
       </c>
       <c r="D14" t="n">
-        <v>726.2863984755653</v>
+        <v>721.5824293281937</v>
       </c>
       <c r="E14" t="n">
-        <v>730.7911376953125</v>
+        <v>730.9306640625</v>
       </c>
       <c r="F14" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B15" t="n">
-        <v>731.3492269695964</v>
+        <v>732.2162614456487</v>
       </c>
       <c r="C15" t="n">
-        <v>738.0962989037338</v>
+        <v>739.900157838395</v>
       </c>
       <c r="D15" t="n">
-        <v>721.5823690736463</v>
+        <v>730.6216339604061</v>
       </c>
       <c r="E15" t="n">
-        <v>730.9306030273438</v>
+        <v>731.5186157226562</v>
       </c>
       <c r="F15" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B16" t="n">
-        <v>732.2163225390138</v>
+        <v>734.2991309259364</v>
       </c>
       <c r="C16" t="n">
-        <v>739.9002195728755</v>
+        <v>738.704232141329</v>
       </c>
       <c r="D16" t="n">
-        <v>730.6216949207216</v>
+        <v>728.6782441600997</v>
       </c>
       <c r="E16" t="n">
-        <v>731.5186767578125</v>
+        <v>735.8638305664062</v>
       </c>
       <c r="F16" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B17" t="n">
-        <v>734.2991918313108</v>
+        <v>747.195457385242</v>
       </c>
       <c r="C17" t="n">
-        <v>738.7042934120783</v>
+        <v>753.1951257515892</v>
       </c>
       <c r="D17" t="n">
-        <v>728.6783045992579</v>
+        <v>745.4813011827554</v>
       </c>
       <c r="E17" t="n">
-        <v>735.8638916015625</v>
+        <v>748.2817993164062</v>
       </c>
       <c r="F17" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B18" t="n">
-        <v>747.1953964386955</v>
+        <v>750.0856376808406</v>
       </c>
       <c r="C18" t="n">
-        <v>753.1950643156673</v>
+        <v>755.8361508831443</v>
       </c>
       <c r="D18" t="n">
-        <v>745.4812403760276</v>
+        <v>742.9996885933356</v>
       </c>
       <c r="E18" t="n">
-        <v>748.28173828125</v>
+        <v>748.899658203125</v>
       </c>
       <c r="F18" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B19" t="n">
-        <v>750.0856988126538</v>
+        <v>752.1984498261967</v>
       </c>
       <c r="C19" t="n">
-        <v>755.8362124836232</v>
+        <v>756.5935143682193</v>
       </c>
       <c r="D19" t="n">
-        <v>742.9997491476457</v>
+        <v>739.9998387891849</v>
       </c>
       <c r="E19" t="n">
-        <v>748.8997192382812</v>
+        <v>749.1288452148438</v>
       </c>
       <c r="F19" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B20" t="n">
-        <v>752.1985111114485</v>
+        <v>666.8879125335289</v>
       </c>
       <c r="C20" t="n">
-        <v>756.5935760115584</v>
+        <v>678.6579855089774</v>
       </c>
       <c r="D20" t="n">
-        <v>739.9998990805568</v>
+        <v>647.9720344844721</v>
       </c>
       <c r="E20" t="n">
-        <v>749.12890625</v>
+        <v>664.2169189453125</v>
       </c>
       <c r="F20" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B21" t="n">
-        <v>666.8879738141238</v>
+        <v>672.22980228556</v>
       </c>
       <c r="C21" t="n">
-        <v>678.658047871129</v>
+        <v>672.6085225469975</v>
       </c>
       <c r="D21" t="n">
-        <v>647.9720940268795</v>
+        <v>643.3876326547638</v>
       </c>
       <c r="E21" t="n">
-        <v>664.2169799804688</v>
+        <v>646.158203125</v>
       </c>
       <c r="F21" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B22" t="n">
-        <v>672.2297387877188</v>
+        <v>653.7822839270266</v>
       </c>
       <c r="C22" t="n">
-        <v>672.6084590133829</v>
+        <v>657.1010433454932</v>
       </c>
       <c r="D22" t="n">
-        <v>643.3875718813117</v>
+        <v>634.0292814028221</v>
       </c>
       <c r="E22" t="n">
-        <v>646.1581420898438</v>
+        <v>635.5541381835938</v>
       </c>
       <c r="F22" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B23" t="n">
-        <v>653.7823467127146</v>
+        <v>625.9168165443936</v>
       </c>
       <c r="C23" t="n">
-        <v>657.1011064498967</v>
+        <v>639.5705142822006</v>
       </c>
       <c r="D23" t="n">
-        <v>634.0293422915395</v>
+        <v>623.8937108241939</v>
       </c>
       <c r="E23" t="n">
-        <v>635.55419921875</v>
+        <v>625.1992797851562</v>
       </c>
       <c r="F23" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B24" t="n">
-        <v>625.9168165443936</v>
+        <v>630.1724007040705</v>
       </c>
       <c r="C24" t="n">
-        <v>639.5705142822006</v>
+        <v>640.0588479681868</v>
       </c>
       <c r="D24" t="n">
-        <v>623.8937108241939</v>
+        <v>624.4218873891514</v>
       </c>
       <c r="E24" t="n">
-        <v>625.1992797851562</v>
+        <v>633.8001098632812</v>
       </c>
       <c r="F24" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B25" t="n">
-        <v>630.1724007040705</v>
+        <v>633.7004019945108</v>
       </c>
       <c r="C25" t="n">
-        <v>640.0588479681868</v>
+        <v>633.8499192315176</v>
       </c>
       <c r="D25" t="n">
-        <v>624.4218873891514</v>
+        <v>615.9107705740217</v>
       </c>
       <c r="E25" t="n">
-        <v>633.8001098632812</v>
+        <v>616.8475952148438</v>
       </c>
       <c r="F25" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B26" t="n">
-        <v>633.7004019945108</v>
+        <v>614.4058914069517</v>
       </c>
       <c r="C26" t="n">
-        <v>633.8499192315176</v>
+        <v>620.0268394880455</v>
       </c>
       <c r="D26" t="n">
-        <v>615.9107705740217</v>
+        <v>599.1676024999227</v>
       </c>
       <c r="E26" t="n">
-        <v>616.8475952148438</v>
+        <v>619.6082763671875</v>
       </c>
       <c r="F26" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B27" t="n">
-        <v>614.4058308842617</v>
+        <v>628.9566105977867</v>
       </c>
       <c r="C27" t="n">
-        <v>620.0267784116583</v>
+        <v>632.8533659763596</v>
       </c>
       <c r="D27" t="n">
-        <v>599.1675434782962</v>
+        <v>616.0204484619443</v>
       </c>
       <c r="E27" t="n">
-        <v>619.6082153320312</v>
+        <v>629.6243286132812</v>
       </c>
       <c r="F27" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B28" t="n">
-        <v>628.9565496273584</v>
+        <v>625.8769557835792</v>
       </c>
       <c r="C28" t="n">
-        <v>632.8533046281837</v>
+        <v>627.431679546322</v>
       </c>
       <c r="D28" t="n">
-        <v>616.0203887455347</v>
+        <v>617.29607772438</v>
       </c>
       <c r="E28" t="n">
-        <v>629.624267578125</v>
+        <v>624.9600830078125</v>
       </c>
       <c r="F28" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B29" t="n">
-        <v>625.8770169082796</v>
+        <v>626.0065293511232</v>
       </c>
       <c r="C29" t="n">
-        <v>627.4317408228605</v>
+        <v>626.8636074098682</v>
       </c>
       <c r="D29" t="n">
-        <v>617.2961380110504</v>
+        <v>605.7153735895874</v>
       </c>
       <c r="E29" t="n">
-        <v>624.9601440429688</v>
+        <v>606.951171875</v>
       </c>
       <c r="F29" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B30" t="n">
-        <v>626.0065293511232</v>
+        <v>610.9974896015757</v>
       </c>
       <c r="C30" t="n">
-        <v>626.8636074098682</v>
+        <v>615.5620236854409</v>
       </c>
       <c r="D30" t="n">
-        <v>605.7153735895874</v>
+        <v>600.9615245048305</v>
       </c>
       <c r="E30" t="n">
-        <v>606.951171875</v>
+        <v>607.8282470703125</v>
       </c>
       <c r="F30" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B31" t="n">
-        <v>610.9974282481795</v>
+        <v>599.7555439005879</v>
       </c>
       <c r="C31" t="n">
-        <v>615.5619618736964</v>
+        <v>611.6053627125183</v>
       </c>
       <c r="D31" t="n">
-        <v>600.9614641591972</v>
+        <v>593.1878563697925</v>
       </c>
       <c r="E31" t="n">
-        <v>607.8281860351562</v>
+        <v>607.399658203125</v>
       </c>
       <c r="F31" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B32" t="n">
-        <v>599.7556041676178</v>
+        <v>606.9810562524968</v>
       </c>
       <c r="C32" t="n">
-        <v>611.6054241702889</v>
+        <v>609.6221219886945</v>
       </c>
       <c r="D32" t="n">
-        <v>593.1879159768617</v>
+        <v>593.3872138938384</v>
       </c>
       <c r="E32" t="n">
-        <v>607.3997192382812</v>
+        <v>599.974853515625</v>
       </c>
       <c r="F32" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B33" t="n">
-        <v>606.980994504603</v>
+        <v>589.6000552799869</v>
       </c>
       <c r="C33" t="n">
-        <v>609.6220599721263</v>
+        <v>601.6192836786712</v>
       </c>
       <c r="D33" t="n">
-        <v>593.3871535288397</v>
+        <v>581.8065445386262</v>
       </c>
       <c r="E33" t="n">
-        <v>599.9747924804688</v>
+        <v>595.6694946289062</v>
       </c>
       <c r="F33" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B34" t="n">
-        <v>589.6000552799869</v>
+        <v>591.7128714929664</v>
       </c>
       <c r="C34" t="n">
-        <v>601.6192836786712</v>
+        <v>593.3174750396417</v>
       </c>
       <c r="D34" t="n">
-        <v>581.8065445386262</v>
+        <v>579.2850561317264</v>
       </c>
       <c r="E34" t="n">
-        <v>595.6694946289062</v>
+        <v>588.3244018554688</v>
       </c>
       <c r="F34" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B35" t="n">
-        <v>591.7128101062766</v>
+        <v>601.4597887996167</v>
       </c>
       <c r="C35" t="n">
-        <v>593.3174134864839</v>
+        <v>604.6688739678727</v>
       </c>
       <c r="D35" t="n">
-        <v>579.2849960343485</v>
+        <v>581.3778841958236</v>
       </c>
       <c r="E35" t="n">
-        <v>588.3243408203125</v>
+        <v>587.1583251953125</v>
       </c>
       <c r="F35" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B36" t="n">
-        <v>601.4597887996167</v>
+        <v>586.5105272163902</v>
       </c>
       <c r="C36" t="n">
-        <v>604.6688739678727</v>
+        <v>596.0980011467227</v>
       </c>
       <c r="D36" t="n">
-        <v>581.3778841958236</v>
+        <v>579.8929596850738</v>
       </c>
       <c r="E36" t="n">
-        <v>587.1583251953125</v>
+        <v>592.2410888671875</v>
       </c>
       <c r="F36" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B37" t="n">
-        <v>586.5105272163902</v>
+        <v>596.6959057641074</v>
       </c>
       <c r="C37" t="n">
-        <v>596.0980011467227</v>
+        <v>614.6151629725317</v>
       </c>
       <c r="D37" t="n">
-        <v>579.8929596850738</v>
+        <v>595.609624740878</v>
       </c>
       <c r="E37" t="n">
-        <v>592.2410888671875</v>
+        <v>610.9774780273438</v>
       </c>
       <c r="F37" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B38" t="n">
-        <v>596.6959653725695</v>
+        <v>621.8904333417628</v>
       </c>
       <c r="C38" t="n">
-        <v>614.6152243710839</v>
+        <v>634.8963028348302</v>
       </c>
       <c r="D38" t="n">
-        <v>595.6096842408232</v>
+        <v>616.2096912560512</v>
       </c>
       <c r="E38" t="n">
-        <v>610.9775390625</v>
+        <v>634.069091796875</v>
       </c>
       <c r="F38" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B39" t="n">
-        <v>621.8904932046078</v>
+        <v>635.5342418532664</v>
       </c>
       <c r="C39" t="n">
-        <v>634.8963639496133</v>
+        <v>636.2019598341516</v>
       </c>
       <c r="D39" t="n">
-        <v>616.209750572071</v>
+        <v>629.4947305871518</v>
       </c>
       <c r="E39" t="n">
-        <v>634.0691528320312</v>
+        <v>631.468017578125</v>
       </c>
       <c r="F39" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B40" t="n">
-        <v>635.5341804250853</v>
+        <v>633.9296546389559</v>
       </c>
       <c r="C40" t="n">
-        <v>636.2018983414315</v>
+        <v>645.8591590880771</v>
       </c>
       <c r="D40" t="n">
-        <v>629.4946697427255</v>
+        <v>633.3515983825566</v>
       </c>
       <c r="E40" t="n">
-        <v>631.4679565429688</v>
+        <v>645.759521484375</v>
       </c>
       <c r="F40" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B41" t="n">
-        <v>633.9297145559904</v>
+        <v>637.3878244409318</v>
       </c>
       <c r="C41" t="n">
-        <v>645.8592201326509</v>
+        <v>643.1383369359702</v>
       </c>
       <c r="D41" t="n">
-        <v>633.351658244955</v>
+        <v>635.6038978950446</v>
       </c>
       <c r="E41" t="n">
-        <v>645.7595825195312</v>
+        <v>638.703369140625</v>
       </c>
       <c r="F41" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B42" t="n">
-        <v>637.3878853503733</v>
+        <v>640.1684965318557</v>
       </c>
       <c r="C42" t="n">
-        <v>643.1383983949365</v>
+        <v>645.6797698761368</v>
       </c>
       <c r="D42" t="n">
-        <v>635.6039586340122</v>
+        <v>635.9129124654792</v>
       </c>
       <c r="E42" t="n">
-        <v>638.7034301757812</v>
+        <v>644.912353515625</v>
       </c>
       <c r="F42" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B43" t="n">
-        <v>640.1684965318557</v>
+        <v>642.2314810232181</v>
       </c>
       <c r="C43" t="n">
-        <v>645.6797698761368</v>
+        <v>646.6564735939825</v>
       </c>
       <c r="D43" t="n">
-        <v>635.9129124654792</v>
+        <v>635.3946865356451</v>
       </c>
       <c r="E43" t="n">
-        <v>644.912353515625</v>
+        <v>637.437744140625</v>
       </c>
       <c r="F43" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B44" t="n">
-        <v>642.2314810232181</v>
+        <v>673.7146932031604</v>
       </c>
       <c r="C44" t="n">
-        <v>646.6564735939825</v>
+        <v>673.8143308084973</v>
       </c>
       <c r="D44" t="n">
-        <v>635.3946865356451</v>
+        <v>657.8186021075292</v>
       </c>
       <c r="E44" t="n">
-        <v>637.437744140625</v>
+        <v>659.2936401367188</v>
       </c>
       <c r="F44" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B45" t="n">
-        <v>673.7147555733686</v>
+        <v>661.7552947151958</v>
       </c>
       <c r="C45" t="n">
-        <v>673.8143931879296</v>
+        <v>672.4091587454953</v>
       </c>
       <c r="D45" t="n">
-        <v>657.8186630061315</v>
+        <v>660.1507520483126</v>
       </c>
       <c r="E45" t="n">
-        <v>659.293701171875</v>
+        <v>671.1434326171875</v>
       </c>
       <c r="F45" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B46" t="n">
-        <v>661.7552947151958</v>
+        <v>667.0772284693074</v>
       </c>
       <c r="C46" t="n">
-        <v>672.4091587454953</v>
+        <v>674.4223082782987</v>
       </c>
       <c r="D46" t="n">
-        <v>660.1507520483126</v>
+        <v>662.8216443414645</v>
       </c>
       <c r="E46" t="n">
-        <v>671.1434326171875</v>
+        <v>664.5457763671875</v>
       </c>
       <c r="F46" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B47" t="n">
-        <v>667.0772284693074</v>
+        <v>661.5260500954003</v>
       </c>
       <c r="C47" t="n">
-        <v>674.4223082782987</v>
+        <v>662.2336109084633</v>
       </c>
       <c r="D47" t="n">
-        <v>662.8216443414645</v>
+        <v>651.1313175008097</v>
       </c>
       <c r="E47" t="n">
-        <v>664.5457763671875</v>
+        <v>654.7390747070312</v>
       </c>
       <c r="F47" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B48" t="n">
-        <v>661.5261117632423</v>
+        <v>647.7528057448357</v>
       </c>
       <c r="C48" t="n">
-        <v>662.2336726422647</v>
+        <v>652.297387877758</v>
       </c>
       <c r="D48" t="n">
-        <v>651.1313781996487</v>
+        <v>641.2249606939789</v>
       </c>
       <c r="E48" t="n">
-        <v>654.7391357421875</v>
+        <v>647.9321899414062</v>
       </c>
       <c r="F48" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B49" t="n">
-        <v>647.7527447265774</v>
+        <v>641.1152803360264</v>
       </c>
       <c r="C49" t="n">
-        <v>652.2973264314004</v>
+        <v>653.0647981949571</v>
       </c>
       <c r="D49" t="n">
-        <v>641.2249002906431</v>
+        <v>638.6337077300913</v>
       </c>
       <c r="E49" t="n">
-        <v>647.93212890625</v>
+        <v>650.5034790039062</v>
       </c>
       <c r="F49" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B50" t="n">
-        <v>641.1152201817421</v>
+        <v>647.6031784922952</v>
       </c>
       <c r="C50" t="n">
-        <v>653.0647369194785</v>
+        <v>708.5962889471821</v>
       </c>
       <c r="D50" t="n">
-        <v>638.6336478086467</v>
+        <v>636.4510066170626</v>
       </c>
       <c r="E50" t="n">
-        <v>650.50341796875</v>
+        <v>642.052001953125</v>
       </c>
       <c r="F50" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,25 +1743,25 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B51" t="n">
-        <v>647.603240055161</v>
+        <v>644.0420011784053</v>
       </c>
       <c r="C51" t="n">
-        <v>708.5963563082138</v>
+        <v>651.3232442601446</v>
       </c>
       <c r="D51" t="n">
-        <v>636.4510671197735</v>
+        <v>637.0599755890928</v>
       </c>
       <c r="E51" t="n">
-        <v>642.0520629882812</v>
+        <v>645.8473510742188</v>
       </c>
       <c r="F51" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1769,25 +1769,25 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B52" t="n">
-        <v>644.0420011784053</v>
+        <v>641.8476117575357</v>
       </c>
       <c r="C52" t="n">
-        <v>651.3232442601446</v>
+        <v>660.8386986647098</v>
       </c>
       <c r="D52" t="n">
-        <v>637.0599755890928</v>
+        <v>641.5483942773906</v>
       </c>
       <c r="E52" t="n">
-        <v>645.8473510742188</v>
+        <v>655.4625854492188</v>
       </c>
       <c r="F52" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G52" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B53" t="n">
-        <v>641.8476715248971</v>
+        <v>653.9265104909302</v>
       </c>
       <c r="C53" t="n">
-        <v>660.8387602004772</v>
+        <v>659.5320745885969</v>
       </c>
       <c r="D53" t="n">
-        <v>641.5484540168895</v>
+        <v>647.5329968709444</v>
       </c>
       <c r="E53" t="n">
-        <v>655.462646484375</v>
+        <v>647.8322143554688</v>
       </c>
       <c r="F53" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B54" t="n">
-        <v>653.9265721002572</v>
+        <v>655.3429659472675</v>
       </c>
       <c r="C54" t="n">
-        <v>659.5321367260491</v>
+        <v>668.8381931582612</v>
       </c>
       <c r="D54" t="n">
-        <v>647.5330578779101</v>
+        <v>654.774422237226</v>
       </c>
       <c r="E54" t="n">
-        <v>647.832275390625</v>
+        <v>662.743896484375</v>
       </c>
       <c r="F54" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B55" t="n">
-        <v>655.3429055936973</v>
+        <v>664.7087499822148</v>
       </c>
       <c r="C55" t="n">
-        <v>668.8381315618529</v>
+        <v>669.2770065062657</v>
       </c>
       <c r="D55" t="n">
-        <v>654.7743619360156</v>
+        <v>656.4899183910027</v>
       </c>
       <c r="E55" t="n">
-        <v>662.7438354492188</v>
+        <v>657.0784301757812</v>
       </c>
       <c r="F55" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B56" t="n">
-        <v>664.7087499822148</v>
+        <v>659.9510307809619</v>
       </c>
       <c r="C56" t="n">
-        <v>669.2770065062657</v>
+        <v>671.850389464676</v>
       </c>
       <c r="D56" t="n">
-        <v>656.4899183910027</v>
+        <v>654.9638698467097</v>
       </c>
       <c r="E56" t="n">
-        <v>657.0784301757812</v>
+        <v>659.8013916015625</v>
       </c>
       <c r="F56" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B57" t="n">
-        <v>659.9510918299604</v>
+        <v>658.3550860644432</v>
       </c>
       <c r="C57" t="n">
-        <v>671.8504516144289</v>
+        <v>664.2898196014329</v>
       </c>
       <c r="D57" t="n">
-        <v>654.9639304343692</v>
+        <v>656.5597203493141</v>
       </c>
       <c r="E57" t="n">
-        <v>659.8014526367188</v>
+        <v>663.2325439453125</v>
       </c>
       <c r="F57" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B58" t="n">
-        <v>658.3550860644432</v>
+        <v>660.8288686174008</v>
       </c>
       <c r="C58" t="n">
-        <v>664.2898196014329</v>
+        <v>666.4643247360839</v>
       </c>
       <c r="D58" t="n">
-        <v>656.5597203493141</v>
+        <v>660.4996989036335</v>
       </c>
       <c r="E58" t="n">
-        <v>663.2325439453125</v>
+        <v>665.8359375</v>
       </c>
       <c r="F58" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B59" t="n">
-        <v>660.8288080412273</v>
+        <v>666.3445631389869</v>
       </c>
       <c r="C59" t="n">
-        <v>666.4642636433252</v>
+        <v>667.2322924211887</v>
       </c>
       <c r="D59" t="n">
-        <v>660.499638357634</v>
+        <v>659.6218797502219</v>
       </c>
       <c r="E59" t="n">
-        <v>665.8358764648438</v>
+        <v>661.5867919921875</v>
       </c>
       <c r="F59" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B60" t="n">
-        <v>666.3446246130748</v>
+        <v>656.3204105957403</v>
       </c>
       <c r="C60" t="n">
-        <v>667.2323539771746</v>
+        <v>658.5546491157273</v>
       </c>
       <c r="D60" t="n">
-        <v>659.6219406041037</v>
+        <v>652.7097106878265</v>
       </c>
       <c r="E60" t="n">
-        <v>661.5868530273438</v>
+        <v>656.9986572265625</v>
       </c>
       <c r="F60" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B61" t="n">
-        <v>656.3204105957403</v>
+        <v>656.9986226731097</v>
       </c>
       <c r="C61" t="n">
-        <v>658.5546491157273</v>
+        <v>670.4938487731155</v>
       </c>
       <c r="D61" t="n">
-        <v>652.7097106878265</v>
+        <v>656.1508296487782</v>
       </c>
       <c r="E61" t="n">
-        <v>656.9986572265625</v>
+        <v>664.239990234375</v>
       </c>
       <c r="F61" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B62" t="n">
-        <v>656.9986226731097</v>
+        <v>663.0430880640301</v>
       </c>
       <c r="C62" t="n">
-        <v>670.4938487731155</v>
+        <v>663.2924461264837</v>
       </c>
       <c r="D62" t="n">
-        <v>656.1508296487782</v>
+        <v>657.7467252526537</v>
       </c>
       <c r="E62" t="n">
-        <v>664.239990234375</v>
+        <v>658.3950805664062</v>
       </c>
       <c r="F62" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B63" t="n">
-        <v>663.0430265979899</v>
+        <v>661.0283027009447</v>
       </c>
       <c r="C63" t="n">
-        <v>663.2923846373272</v>
+        <v>662.6840744459444</v>
       </c>
       <c r="D63" t="n">
-        <v>657.7466642776019</v>
+        <v>641.8476986467276</v>
       </c>
       <c r="E63" t="n">
-        <v>658.39501953125</v>
+        <v>648.7399291992188</v>
       </c>
       <c r="F63" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B64" t="n">
-        <v>661.0282405096659</v>
+        <v>649.3383972038786</v>
       </c>
       <c r="C64" t="n">
-        <v>662.6840120988863</v>
+        <v>662.8336242718107</v>
       </c>
       <c r="D64" t="n">
-        <v>641.8476382600104</v>
+        <v>646.086758236235</v>
       </c>
       <c r="E64" t="n">
-        <v>648.7398681640625</v>
+        <v>657.098388671875</v>
       </c>
       <c r="F64" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B65" t="n">
-        <v>649.3383972038786</v>
+        <v>657.8764143393763</v>
       </c>
       <c r="C65" t="n">
-        <v>662.8336242718107</v>
+        <v>663.8111485640529</v>
       </c>
       <c r="D65" t="n">
-        <v>646.086758236235</v>
+        <v>650.2261258196658</v>
       </c>
       <c r="E65" t="n">
-        <v>657.098388671875</v>
+        <v>658.9237060546875</v>
       </c>
       <c r="F65" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B66" t="n">
-        <v>657.8763534012292</v>
+        <v>653.9565196013041</v>
       </c>
       <c r="C66" t="n">
-        <v>663.8110870761799</v>
+        <v>657.4575166710536</v>
       </c>
       <c r="D66" t="n">
-        <v>650.2260655901538</v>
+        <v>643.1543108814861</v>
       </c>
       <c r="E66" t="n">
-        <v>658.9236450195312</v>
+        <v>647.0243530273438</v>
       </c>
       <c r="F66" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B67" t="n">
-        <v>653.956457912222</v>
+        <v>644.2215315163064</v>
       </c>
       <c r="C67" t="n">
-        <v>657.4574546517152</v>
+        <v>645.4383696113561</v>
       </c>
       <c r="D67" t="n">
-        <v>643.154250211399</v>
+        <v>634.0875860000896</v>
       </c>
       <c r="E67" t="n">
-        <v>647.0242919921875</v>
+        <v>644.4010620117188</v>
       </c>
       <c r="F67" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B68" t="n">
-        <v>644.2215315163064</v>
+        <v>643.7826283039087</v>
       </c>
       <c r="C68" t="n">
-        <v>645.4383696113561</v>
+        <v>653.2682180705046</v>
       </c>
       <c r="D68" t="n">
-        <v>634.0875860000896</v>
+        <v>641.1992521727667</v>
       </c>
       <c r="E68" t="n">
-        <v>644.4010620117188</v>
+        <v>651.383056640625</v>
       </c>
       <c r="F68" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B69" t="n">
-        <v>643.7826886268982</v>
+        <v>650.8545379312607</v>
       </c>
       <c r="C69" t="n">
-        <v>653.2682792823022</v>
+        <v>652.2907820220081</v>
       </c>
       <c r="D69" t="n">
-        <v>641.1993122536916</v>
+        <v>639.5835040655014</v>
       </c>
       <c r="E69" t="n">
-        <v>651.3831176757812</v>
+        <v>640.3215942382812</v>
       </c>
       <c r="F69" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B70" t="n">
-        <v>650.8544758921091</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="C70" t="n">
-        <v>652.2907198459545</v>
+        <v>640.6208286715078</v>
       </c>
       <c r="D70" t="n">
-        <v>639.5834431006995</v>
+        <v>622.4974409136</v>
       </c>
       <c r="E70" t="n">
-        <v>640.321533203125</v>
+        <v>629.4695434570312</v>
       </c>
       <c r="F70" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B71" t="n">
-        <v>640.6208286715078</v>
+        <v>624.8913007155408</v>
       </c>
       <c r="C71" t="n">
-        <v>640.6208286715078</v>
+        <v>626.836305766559</v>
       </c>
       <c r="D71" t="n">
-        <v>622.4974409136</v>
+        <v>613.2412994138377</v>
       </c>
       <c r="E71" t="n">
-        <v>629.4695434570312</v>
+        <v>613.9395141601562</v>
       </c>
       <c r="F71" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B72" t="n">
-        <v>624.8912385916063</v>
+        <v>616.8918824768537</v>
       </c>
       <c r="C72" t="n">
-        <v>626.8362434492608</v>
+        <v>622.567274451088</v>
       </c>
       <c r="D72" t="n">
-        <v>613.241238448095</v>
+        <v>612.6527953870184</v>
       </c>
       <c r="E72" t="n">
-        <v>613.939453125</v>
+        <v>619.2059326171875</v>
       </c>
       <c r="F72" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B73" t="n">
-        <v>616.8918216697934</v>
+        <v>622.5772500418334</v>
       </c>
       <c r="C73" t="n">
-        <v>622.5672130846042</v>
+        <v>627.4646923832119</v>
       </c>
       <c r="D73" t="n">
-        <v>612.6527349978052</v>
+        <v>618.4878021974878</v>
       </c>
       <c r="E73" t="n">
-        <v>619.2058715820312</v>
+        <v>618.6573486328125</v>
       </c>
       <c r="F73" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B74" t="n">
-        <v>622.5772500418334</v>
+        <v>606.3191417499893</v>
       </c>
       <c r="C74" t="n">
-        <v>627.4646923832119</v>
+        <v>609.8301228712422</v>
       </c>
       <c r="D74" t="n">
-        <v>618.4878021974878</v>
+        <v>598.4593704807342</v>
       </c>
       <c r="E74" t="n">
-        <v>618.6573486328125</v>
+        <v>602.5687866210938</v>
       </c>
       <c r="F74" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B75" t="n">
-        <v>606.3190803349536</v>
+        <v>605.1820479992876</v>
       </c>
       <c r="C75" t="n">
-        <v>609.8300611005736</v>
+        <v>616.6824713366042</v>
       </c>
       <c r="D75" t="n">
-        <v>598.4593098618273</v>
+        <v>598.5391758430108</v>
       </c>
       <c r="E75" t="n">
-        <v>602.5687255859375</v>
+        <v>611.3861083984375</v>
       </c>
       <c r="F75" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B76" t="n">
-        <v>605.1819875834877</v>
+        <v>627.7339506004921</v>
       </c>
       <c r="C76" t="n">
-        <v>616.682409772708</v>
+        <v>658.8738165275513</v>
       </c>
       <c r="D76" t="n">
-        <v>598.5391160903739</v>
+        <v>624.9411525277235</v>
       </c>
       <c r="E76" t="n">
-        <v>611.3860473632812</v>
+        <v>645.967041015625</v>
       </c>
       <c r="F76" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B77" t="n">
-        <v>627.7339506004921</v>
+        <v>643.1144139511335</v>
       </c>
       <c r="C77" t="n">
-        <v>658.8738165275513</v>
+        <v>664.7786132883346</v>
       </c>
       <c r="D77" t="n">
-        <v>624.9411525277235</v>
+        <v>642.7952283244125</v>
       </c>
       <c r="E77" t="n">
-        <v>645.967041015625</v>
+        <v>657.0684814453125</v>
       </c>
       <c r="F77" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B78" t="n">
-        <v>643.114354212172</v>
+        <v>663.4221291072672</v>
       </c>
       <c r="C78" t="n">
-        <v>664.7785515369834</v>
+        <v>673.5460909761269</v>
       </c>
       <c r="D78" t="n">
-        <v>642.7951686151001</v>
+        <v>659.5919624126628</v>
       </c>
       <c r="E78" t="n">
-        <v>657.0684204101562</v>
+        <v>670.633544921875</v>
       </c>
       <c r="F78" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B79" t="n">
-        <v>663.4220687284304</v>
+        <v>672.8578395915863</v>
       </c>
       <c r="C79" t="n">
-        <v>673.5460296758964</v>
+        <v>675.0820939991542</v>
       </c>
       <c r="D79" t="n">
-        <v>659.5919023824141</v>
+        <v>662.9532839044604</v>
       </c>
       <c r="E79" t="n">
-        <v>670.6334838867188</v>
+        <v>671.241943359375</v>
       </c>
       <c r="F79" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B80" t="n">
-        <v>672.8578395915863</v>
+        <v>672.768020673078</v>
       </c>
       <c r="C80" t="n">
-        <v>675.0820939991542</v>
+        <v>675.9398477720257</v>
       </c>
       <c r="D80" t="n">
-        <v>662.9532839044604</v>
+        <v>664.3895658196245</v>
       </c>
       <c r="E80" t="n">
-        <v>671.241943359375</v>
+        <v>667.0128173828125</v>
       </c>
       <c r="F80" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B81" t="n">
-        <v>672.7679591112906</v>
+        <v>735.536439340887</v>
       </c>
       <c r="C81" t="n">
-        <v>675.9397859199995</v>
+        <v>742.0895763731422</v>
       </c>
       <c r="D81" t="n">
-        <v>664.3895050245095</v>
+        <v>710.7203206800697</v>
       </c>
       <c r="E81" t="n">
-        <v>667.0127563476562</v>
+        <v>736.4141845703125</v>
       </c>
       <c r="F81" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B82" t="n">
-        <v>735.536439340887</v>
+        <v>725.6319102189462</v>
       </c>
       <c r="C82" t="n">
-        <v>742.0895763731422</v>
+        <v>730.2899014488934</v>
       </c>
       <c r="D82" t="n">
-        <v>710.7203206800697</v>
+        <v>711.7576553956329</v>
       </c>
       <c r="E82" t="n">
-        <v>736.4141845703125</v>
+        <v>714.66015625</v>
       </c>
       <c r="F82" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B83" t="n">
-        <v>725.6319721911391</v>
+        <v>712.7649799285471</v>
       </c>
       <c r="C83" t="n">
-        <v>730.2899638188994</v>
+        <v>719.4477874144414</v>
       </c>
       <c r="D83" t="n">
-        <v>711.7577161829028</v>
+        <v>701.7134756957726</v>
       </c>
       <c r="E83" t="n">
-        <v>714.6602172851562</v>
+        <v>704.5960083007812</v>
       </c>
       <c r="F83" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B84" t="n">
-        <v>712.7650416713351</v>
+        <v>705.5535728195721</v>
       </c>
       <c r="C84" t="n">
-        <v>719.4478497361232</v>
+        <v>715.1588492636382</v>
       </c>
       <c r="D84" t="n">
-        <v>701.7135364812315</v>
+        <v>684.6473731061755</v>
       </c>
       <c r="E84" t="n">
-        <v>704.5960693359375</v>
+        <v>689.923828125</v>
       </c>
       <c r="F84" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B85" t="n">
-        <v>705.5536352374374</v>
+        <v>685.964025393825</v>
       </c>
       <c r="C85" t="n">
-        <v>715.1589125312489</v>
+        <v>687.0612373376343</v>
       </c>
       <c r="D85" t="n">
-        <v>684.6474336745422</v>
+        <v>665.7461161570209</v>
       </c>
       <c r="E85" t="n">
-        <v>689.9238891601562</v>
+        <v>667.2721557617188</v>
       </c>
       <c r="F85" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B86" t="n">
-        <v>685.964025393825</v>
+        <v>661.876033741038</v>
       </c>
       <c r="C86" t="n">
-        <v>687.0612373376343</v>
+        <v>679.7500005691794</v>
       </c>
       <c r="D86" t="n">
-        <v>665.7461161570209</v>
+        <v>651.8219007658969</v>
       </c>
       <c r="E86" t="n">
-        <v>667.2721557617188</v>
+        <v>668.489013671875</v>
       </c>
       <c r="F86" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B87" t="n">
-        <v>661.8760941724082</v>
+        <v>663.7811558190369</v>
       </c>
       <c r="C87" t="n">
-        <v>679.7500626324993</v>
+        <v>670.2644652243433</v>
       </c>
       <c r="D87" t="n">
-        <v>651.8219602792932</v>
+        <v>644.8399277739295</v>
       </c>
       <c r="E87" t="n">
-        <v>668.4890747070312</v>
+        <v>659.7615356445312</v>
       </c>
       <c r="F87" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B88" t="n">
-        <v>663.7811558190369</v>
+        <v>661.4770916291903</v>
       </c>
       <c r="C88" t="n">
-        <v>670.2644652243433</v>
+        <v>681.5554070660584</v>
       </c>
       <c r="D88" t="n">
-        <v>644.8399277739295</v>
+        <v>657.0884263930592</v>
       </c>
       <c r="E88" t="n">
-        <v>659.7615356445312</v>
+        <v>675.4810180664062</v>
       </c>
       <c r="F88" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B89" t="n">
-        <v>661.4770916291903</v>
+        <v>675.8600805746455</v>
       </c>
       <c r="C89" t="n">
-        <v>681.5554070660584</v>
+        <v>678.9022976953746</v>
       </c>
       <c r="D89" t="n">
-        <v>657.0884263930592</v>
+        <v>668.0701369952135</v>
       </c>
       <c r="E89" t="n">
-        <v>675.4810180664062</v>
+        <v>668.9977416992188</v>
       </c>
       <c r="F89" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B90" t="n">
-        <v>675.8600189134125</v>
+        <v>672.2693241407737</v>
       </c>
       <c r="C90" t="n">
-        <v>678.9022357565889</v>
+        <v>677.5258114827353</v>
       </c>
       <c r="D90" t="n">
-        <v>668.0700760446862</v>
+        <v>655.4126950742984</v>
       </c>
       <c r="E90" t="n">
-        <v>668.9976806640625</v>
+        <v>666.9729614257812</v>
       </c>
       <c r="F90" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B91" t="n">
-        <v>672.2693241407737</v>
+        <v>668.2496249159107</v>
       </c>
       <c r="C91" t="n">
-        <v>677.5258114827353</v>
+        <v>674.2641703314905</v>
       </c>
       <c r="D91" t="n">
-        <v>655.4126950742984</v>
+        <v>643.6230822268304</v>
       </c>
       <c r="E91" t="n">
-        <v>666.9729614257812</v>
+        <v>648.1414184570312</v>
       </c>
       <c r="F91" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G91" t="n">
 